--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09E0F1A-342D-4C1A-81B9-15C39EC1C757}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA9525A-9B13-4A4F-ADE3-9E6D75A6AECE}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AF$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AG$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="74">
   <si>
     <t>Trung bình/Kỳ</t>
   </si>
@@ -94,145 +94,160 @@
     <t>100-350</t>
   </si>
   <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>131421090000</t>
+  </si>
+  <si>
+    <t>161643553900.0</t>
+  </si>
+  <si>
+    <t>87/251</t>
+  </si>
+  <si>
+    <t>166820986360.0</t>
+  </si>
+  <si>
+    <t>85/251</t>
+  </si>
+  <si>
+    <t>170433084440.0</t>
+  </si>
+  <si>
+    <t>84/251</t>
+  </si>
+  <si>
+    <t>170803812640.0</t>
+  </si>
+  <si>
+    <t>81/251</t>
+  </si>
+  <si>
+    <t>171413667160.0</t>
+  </si>
+  <si>
+    <t>86/251</t>
+  </si>
+  <si>
+    <t>186740852920.0</t>
+  </si>
+  <si>
+    <t>63/251</t>
+  </si>
+  <si>
+    <t>167688031760.0</t>
+  </si>
+  <si>
+    <t>148641587120.0</t>
+  </si>
+  <si>
+    <t>94/251</t>
+  </si>
+  <si>
+    <t>157811392240.0</t>
+  </si>
+  <si>
+    <t>78/251</t>
+  </si>
+  <si>
+    <t>169944938680.0</t>
+  </si>
+  <si>
+    <t>79/251</t>
+  </si>
+  <si>
+    <t>153958977980.0</t>
+  </si>
+  <si>
+    <t>98/251</t>
+  </si>
+  <si>
+    <t>166054694380.0</t>
+  </si>
+  <si>
+    <t>166937578280.0</t>
+  </si>
+  <si>
+    <t>171029502840.0</t>
+  </si>
+  <si>
+    <t>74/251</t>
+  </si>
+  <si>
+    <t>161107982100.0</t>
+  </si>
+  <si>
+    <t>82/251</t>
+  </si>
+  <si>
+    <t>174643537020.0</t>
+  </si>
+  <si>
+    <t>130897500000</t>
+  </si>
+  <si>
+    <t>175487208060.0</t>
+  </si>
+  <si>
+    <t>171216874920.0</t>
+  </si>
+  <si>
+    <t>157289866920.0</t>
+  </si>
+  <si>
+    <t>107/251</t>
+  </si>
+  <si>
+    <t>167310505260.0</t>
+  </si>
+  <si>
+    <t>80/251</t>
+  </si>
+  <si>
+    <t>168885007860.0</t>
+  </si>
+  <si>
+    <t>88/251</t>
+  </si>
+  <si>
     <t>130373910000</t>
   </si>
   <si>
     <t>182036153640</t>
   </si>
   <si>
-    <t>78/251</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>131421090000</t>
-  </si>
-  <si>
-    <t>148641587120.0</t>
-  </si>
-  <si>
-    <t>94/251</t>
-  </si>
-  <si>
-    <t>171216874920.0</t>
-  </si>
-  <si>
-    <t>87/251</t>
-  </si>
-  <si>
-    <t>168885007860.0</t>
-  </si>
-  <si>
-    <t>88/251</t>
-  </si>
-  <si>
-    <t>166937578280.0</t>
-  </si>
-  <si>
-    <t>186740852920.0</t>
-  </si>
-  <si>
-    <t>63/251</t>
-  </si>
-  <si>
-    <t>174643537020.0</t>
-  </si>
-  <si>
-    <t>84/251</t>
-  </si>
-  <si>
-    <t>171029502840.0</t>
-  </si>
-  <si>
-    <t>74/251</t>
-  </si>
-  <si>
-    <t>170803812640.0</t>
-  </si>
-  <si>
-    <t>81/251</t>
-  </si>
-  <si>
-    <t>153958977980.0</t>
-  </si>
-  <si>
-    <t>98/251</t>
-  </si>
-  <si>
-    <t>130897500000</t>
-  </si>
-  <si>
-    <t>175487208060.0</t>
-  </si>
-  <si>
-    <t>157289866920.0</t>
-  </si>
-  <si>
-    <t>107/251</t>
-  </si>
-  <si>
-    <t>161643553900.0</t>
-  </si>
-  <si>
-    <t>161107982100.0</t>
-  </si>
-  <si>
-    <t>82/251</t>
-  </si>
-  <si>
-    <t>157811392240.0</t>
-  </si>
-  <si>
-    <t>166054694380.0</t>
-  </si>
-  <si>
-    <t>171413667160.0</t>
-  </si>
-  <si>
-    <t>86/251</t>
-  </si>
-  <si>
-    <t>170433084440.0</t>
-  </si>
-  <si>
-    <t>167688031760.0</t>
-  </si>
-  <si>
-    <t>166820986360.0</t>
-  </si>
-  <si>
-    <t>85/251</t>
-  </si>
-  <si>
-    <t>162047657400.0</t>
-  </si>
-  <si>
-    <t>73/251</t>
-  </si>
-  <si>
-    <t>158502824060.0</t>
-  </si>
-  <si>
-    <t>165094255060.0</t>
-  </si>
-  <si>
-    <t>79/251</t>
-  </si>
-  <si>
-    <t>164603681240.0</t>
-  </si>
-  <si>
-    <t>75/251</t>
-  </si>
-  <si>
-    <t>167783153220.0</t>
-  </si>
-  <si>
-    <t>170009604480.0</t>
-  </si>
-  <si>
-    <t>80/251</t>
+    <t>131498900000</t>
+  </si>
+  <si>
+    <t>170463432200.0</t>
+  </si>
+  <si>
+    <t>170939923080.0</t>
+  </si>
+  <si>
+    <t>166858889160.0</t>
+  </si>
+  <si>
+    <t>164732142100.0</t>
+  </si>
+  <si>
+    <t>179650048180.0</t>
+  </si>
+  <si>
+    <t>167470427040.0</t>
+  </si>
+  <si>
+    <t>89/251</t>
+  </si>
+  <si>
+    <t>173795020080.0</t>
+  </si>
+  <si>
+    <t>161436994660.0</t>
+  </si>
+  <si>
+    <t>Tất cả vé&gt;=3+</t>
   </si>
 </sst>
 </file>
@@ -266,7 +281,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,6 +365,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -365,7 +386,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,6 +423,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -418,7 +440,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
@@ -701,56 +723,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AG53"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9" style="18" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="8" style="7" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="18" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="18" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" style="18" customWidth="1"/>
-    <col min="10" max="14" width="6.42578125" style="18" customWidth="1"/>
-    <col min="15" max="15" width="8" style="18" customWidth="1"/>
-    <col min="16" max="16" width="9" style="18" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" style="18" customWidth="1"/>
-    <col min="18" max="22" width="9.28515625" style="18" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="19" customWidth="1"/>
-    <col min="24" max="26" width="9.28515625" style="18" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" style="18" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" style="18" customWidth="1"/>
-    <col min="29" max="32" width="6.5703125" style="18" customWidth="1"/>
+    <col min="2" max="2" width="9" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.26953125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" style="19" customWidth="1"/>
+    <col min="8" max="9" width="14.1796875" style="19" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="19" customWidth="1"/>
+    <col min="11" max="15" width="6.453125" style="19" customWidth="1"/>
+    <col min="16" max="16" width="8" style="19" customWidth="1"/>
+    <col min="17" max="17" width="9" style="19" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="19" customWidth="1"/>
+    <col min="19" max="23" width="9.26953125" style="19" customWidth="1"/>
+    <col min="24" max="24" width="9.26953125" style="20" customWidth="1"/>
+    <col min="25" max="27" width="9.26953125" style="19" customWidth="1"/>
+    <col min="28" max="28" width="6.54296875" style="19" customWidth="1"/>
+    <col min="29" max="29" width="7.7265625" style="19" customWidth="1"/>
+    <col min="30" max="33" width="6.54296875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="I1" s="24" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="J1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="R1" s="25" t="s">
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="S1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="20" t="s">
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="21"/>
       <c r="W1" s="22"/>
-      <c r="X1" s="23" t="s">
+      <c r="X1" s="23"/>
+      <c r="Y1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-    </row>
-    <row r="2" spans="1:26" s="2" customFormat="1" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+    </row>
+    <row r="2" spans="1:27" s="2" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -775,1139 +797,1194 @@
       <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="4">
         <v>3</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4">
+      <c r="L2" s="4">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4">
+      <c r="N2" s="4">
         <v>5</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="3">
         <v>3</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="3">
+      <c r="V2" s="3">
         <v>4</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="X2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="3">
+      <c r="Y2" s="3">
         <v>5</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
-        <v>10</v>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A3" s="19">
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C3">
-        <v>251</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
+      <c r="D3" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <f>(E3-D3)</f>
-        <v>51662243640</v>
+        <v>35516488280</v>
       </c>
       <c r="G3">
         <f>(E3/D3)*100</f>
-        <v>139.62621328147634</v>
+        <v>127.02495336174735</v>
       </c>
       <c r="H3">
-        <v>37417</v>
-      </c>
-      <c r="I3">
-        <v>127.78486055776889</v>
+        <v>37835</v>
+      </c>
+      <c r="I3" s="19">
+        <f>(T3+W3+Z3)</f>
+        <v>3232</v>
       </c>
       <c r="J3">
-        <v>11.64541832669323</v>
+        <v>128.23904382470121</v>
       </c>
       <c r="K3">
-        <v>8.6374501992031867</v>
+        <v>12.011952191235061</v>
       </c>
       <c r="L3">
-        <v>0.80478087649402386</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="M3">
-        <v>0.1752988047808765</v>
+        <v>0.85657370517928288</v>
       </c>
       <c r="N3">
-        <v>2.3904382470119521E-2</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="O3">
-        <v>127.1513944223108</v>
-      </c>
-      <c r="P3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3">
-        <v>31.075697211155379</v>
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="P3">
+        <v>127.87250996015941</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>25</v>
       </c>
       <c r="R3">
-        <v>32074</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="S3">
-        <v>2923</v>
+        <v>32188</v>
       </c>
       <c r="T3">
-        <v>34997</v>
+        <v>3015</v>
       </c>
       <c r="U3">
-        <v>2168</v>
+        <v>35203</v>
       </c>
       <c r="V3">
-        <v>202</v>
-      </c>
-      <c r="W3" s="18">
-        <v>2370</v>
-      </c>
-      <c r="X3">
-        <v>44</v>
+        <v>2217</v>
+      </c>
+      <c r="W3">
+        <v>215</v>
+      </c>
+      <c r="X3" s="19">
+        <v>2592</v>
       </c>
       <c r="Y3">
-        <v>6</v>
-      </c>
-      <c r="Z3" s="12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="Z3">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>39</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <f>(E4-D4)</f>
-        <v>17220497120</v>
+        <v>29938094660</v>
       </c>
       <c r="G4">
         <f>(E4/D4)*100</f>
-        <v>113.10329804752037</v>
+        <v>122.76680235347976</v>
       </c>
       <c r="H4">
-        <v>37789</v>
-      </c>
-      <c r="I4">
-        <v>128.48605577689241</v>
+        <v>37872</v>
+      </c>
+      <c r="I4" s="19">
+        <f t="shared" ref="I4:I32" si="0">(T4+W4+Z4)</f>
+        <v>3231</v>
       </c>
       <c r="J4">
-        <v>11.597609561752989</v>
+        <v>128.36254980079681</v>
       </c>
       <c r="K4">
-        <v>10.342629482071709</v>
+        <v>12.055776892430281</v>
       </c>
       <c r="L4">
-        <v>0.71713147410358569</v>
+        <v>10.314741035856571</v>
       </c>
       <c r="M4">
-        <v>0.12749003984063739</v>
+        <v>0.8127490039840638</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.14741035856573709</v>
       </c>
       <c r="O4">
-        <v>128.43426294820719</v>
-      </c>
-      <c r="P4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4">
-        <v>37.450199203187253</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P4">
+        <v>127.95617529880479</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>29</v>
       </c>
       <c r="R4">
-        <v>32250</v>
+        <v>33.466135458167329</v>
       </c>
       <c r="S4">
-        <v>2911</v>
+        <v>32219</v>
       </c>
       <c r="T4">
-        <v>35161</v>
+        <v>3026</v>
       </c>
       <c r="U4">
-        <v>2288</v>
+        <v>35245</v>
       </c>
       <c r="V4">
-        <v>180</v>
-      </c>
-      <c r="W4" s="18">
-        <v>2596</v>
-      </c>
-      <c r="X4">
-        <v>32</v>
+        <v>2233</v>
+      </c>
+      <c r="W4">
+        <v>204</v>
+      </c>
+      <c r="X4" s="19">
+        <v>2589</v>
       </c>
       <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="18">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
-        <v>12</v>
+        <v>37</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A5" s="19">
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="F5">
         <f>(E5-D5)</f>
-        <v>39795784920</v>
+        <v>43222447020</v>
       </c>
       <c r="G5">
         <f>(E5/D5)*100</f>
-        <v>130.28112528970809</v>
+        <v>132.88851661479904</v>
       </c>
       <c r="H5">
-        <v>37906</v>
-      </c>
-      <c r="I5">
-        <v>128.71713147410361</v>
+        <v>37865</v>
+      </c>
+      <c r="I5" s="19">
+        <f t="shared" si="0"/>
+        <v>3199</v>
       </c>
       <c r="J5">
-        <v>11.812749003984059</v>
+        <v>128.4581673306773</v>
       </c>
       <c r="K5">
-        <v>10.30278884462151</v>
+        <v>11.908366533864539</v>
       </c>
       <c r="L5">
-        <v>0.79681274900398402</v>
+        <v>10.314741035856571</v>
       </c>
       <c r="M5">
-        <v>0.18326693227091631</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="N5">
-        <v>3.9840637450199202E-3</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="O5">
-        <v>128.13545816733071</v>
-      </c>
-      <c r="P5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5">
-        <v>34.661354581673308</v>
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="P5">
+        <v>128.00398406374501</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>29</v>
       </c>
       <c r="R5">
-        <v>32308</v>
+        <v>33.466135458167329</v>
       </c>
       <c r="S5">
-        <v>2965</v>
+        <v>32243</v>
       </c>
       <c r="T5">
-        <v>35273</v>
+        <v>2989</v>
       </c>
       <c r="U5">
-        <v>2198</v>
+        <v>35232</v>
       </c>
       <c r="V5">
-        <v>200</v>
-      </c>
-      <c r="W5" s="18">
-        <v>2586</v>
-      </c>
-      <c r="X5">
-        <v>46</v>
+        <v>2208</v>
+      </c>
+      <c r="W5">
+        <v>205</v>
+      </c>
+      <c r="X5" s="19">
+        <v>2589</v>
       </c>
       <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="18">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="Z5">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="F6">
         <f>(E6-D6)</f>
-        <v>37463917860</v>
+        <v>38964532200</v>
       </c>
       <c r="G6">
         <f>(E6/D6)*100</f>
-        <v>128.50677761080814</v>
+        <v>129.63107083025028</v>
       </c>
       <c r="H6">
-        <v>37875</v>
-      </c>
-      <c r="I6">
-        <v>128.601593625498</v>
+        <v>37906</v>
+      </c>
+      <c r="I6" s="19">
+        <f t="shared" si="0"/>
+        <v>3196</v>
       </c>
       <c r="J6">
+        <v>128.65737051792831</v>
+      </c>
+      <c r="K6">
         <v>11.8605577689243</v>
       </c>
-      <c r="K6">
-        <v>10.27490039840638</v>
-      </c>
       <c r="L6">
-        <v>0.8366533864541833</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="M6">
-        <v>0.14342629482071709</v>
+        <v>0.86852589641434264</v>
       </c>
       <c r="N6">
-        <v>1.5936254980079681E-2</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="O6">
-        <v>128.03585657370519</v>
-      </c>
-      <c r="P6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6">
-        <v>35.059760956175303</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P6">
+        <v>128.09561752988051</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>48</v>
       </c>
       <c r="R6">
-        <v>32279</v>
+        <v>29.482071713147409</v>
       </c>
       <c r="S6">
+        <v>32293</v>
+      </c>
+      <c r="T6">
         <v>2977</v>
       </c>
-      <c r="T6">
-        <v>35256</v>
-      </c>
       <c r="U6">
-        <v>2209</v>
+        <v>35270</v>
       </c>
       <c r="V6">
-        <v>210</v>
+        <v>2198</v>
       </c>
       <c r="W6">
-        <v>2579</v>
+        <v>218</v>
       </c>
       <c r="X6">
-        <v>36</v>
+        <v>2592</v>
       </c>
       <c r="Y6">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="Z6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F7">
         <f>(E7-D7)</f>
-        <v>35516488280</v>
+        <v>42296120080</v>
       </c>
       <c r="G7">
         <f>(E7/D7)*100</f>
-        <v>127.02495336174735</v>
+        <v>132.16461892837125</v>
       </c>
       <c r="H7">
-        <v>37835</v>
-      </c>
-      <c r="I7">
-        <v>128.23904382470121</v>
+        <v>37880</v>
+      </c>
+      <c r="I7" s="19">
+        <f t="shared" si="0"/>
+        <v>3196</v>
       </c>
       <c r="J7">
-        <v>12.011952191235061</v>
+        <v>128.53784860557769</v>
       </c>
       <c r="K7">
-        <v>10.32669322709163</v>
+        <v>11.89243027888446</v>
       </c>
       <c r="L7">
-        <v>0.85657370517928288</v>
+        <v>10.31872509960159</v>
       </c>
       <c r="M7">
-        <v>0.151394422310757</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="N7">
-        <v>7.9681274900398405E-3</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="O7">
-        <v>127.87250996015941</v>
-      </c>
-      <c r="P7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7">
-        <v>34.661354581673308</v>
+        <v>2.3904382470119521E-2</v>
+      </c>
+      <c r="P7">
+        <v>128.09561752988051</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>29</v>
       </c>
       <c r="R7">
-        <v>32188</v>
+        <v>33.466135458167329</v>
       </c>
       <c r="S7">
-        <v>3015</v>
+        <v>32263</v>
       </c>
       <c r="T7">
-        <v>35203</v>
+        <v>2985</v>
       </c>
       <c r="U7">
+        <v>35248</v>
+      </c>
+      <c r="V7">
         <v>2217</v>
       </c>
-      <c r="V7">
-        <v>215</v>
-      </c>
-      <c r="W7" s="18">
-        <v>2592</v>
+      <c r="W7">
+        <v>205</v>
       </c>
       <c r="X7">
-        <v>38</v>
+        <v>2590</v>
       </c>
       <c r="Y7">
-        <v>2</v>
-      </c>
-      <c r="Z7" s="18">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="Z7">
+        <v>6</v>
+      </c>
+      <c r="AA7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F8">
         <f>(E8-D8)</f>
-        <v>55319762920</v>
+        <v>37463917860</v>
       </c>
       <c r="G8">
         <f>(E8/D8)*100</f>
-        <v>142.09352008874677</v>
+        <v>128.50677761080814</v>
       </c>
       <c r="H8">
-        <v>37866</v>
-      </c>
-      <c r="I8">
-        <v>128.69721115537851</v>
+        <v>37875</v>
+      </c>
+      <c r="I8" s="19">
+        <f t="shared" si="0"/>
+        <v>3191</v>
       </c>
       <c r="J8">
-        <v>11.60956175298805</v>
+        <v>128.601593625498</v>
       </c>
       <c r="K8">
-        <v>10.366533864541831</v>
+        <v>11.8605577689243</v>
       </c>
       <c r="L8">
-        <v>0.92828685258964139</v>
+        <v>10.27490039840638</v>
       </c>
       <c r="M8">
-        <v>0.15537848605577689</v>
+        <v>0.8366533864541833</v>
       </c>
       <c r="N8">
-        <v>3.1872509960159362E-2</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="O8">
-        <v>128.17928286852589</v>
-      </c>
-      <c r="P8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8">
-        <v>25.099601593625501</v>
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="P8">
+        <v>128.03585657370519</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>60</v>
       </c>
       <c r="R8">
-        <v>32303</v>
+        <v>35.059760956175303</v>
       </c>
       <c r="S8">
-        <v>2914</v>
+        <v>32279</v>
       </c>
       <c r="T8">
-        <v>35217</v>
+        <v>2977</v>
       </c>
       <c r="U8">
-        <v>2181</v>
+        <v>35256</v>
       </c>
       <c r="V8">
-        <v>233</v>
-      </c>
-      <c r="W8" s="11">
-        <v>2602</v>
-      </c>
-      <c r="X8">
-        <v>39</v>
+        <v>2209</v>
+      </c>
+      <c r="W8">
+        <v>210</v>
+      </c>
+      <c r="X8" s="19">
+        <v>2579</v>
       </c>
       <c r="Y8">
-        <v>8</v>
-      </c>
-      <c r="Z8" s="11">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>16</v>
+        <v>36</v>
+      </c>
+      <c r="Z8">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A9" s="18">
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F9">
         <f>(E9-D9)</f>
-        <v>43222447020</v>
+        <v>44589708060</v>
       </c>
       <c r="G9">
         <f>(E9/D9)*100</f>
-        <v>132.88851661479904</v>
+        <v>134.06459868217496</v>
       </c>
       <c r="H9">
-        <v>37865</v>
-      </c>
-      <c r="I9">
-        <v>128.4581673306773</v>
+        <v>37749</v>
+      </c>
+      <c r="I9" s="19">
+        <f t="shared" si="0"/>
+        <v>3174</v>
       </c>
       <c r="J9">
-        <v>11.908366533864539</v>
+        <v>128.02788844621509</v>
       </c>
       <c r="K9">
-        <v>10.314741035856571</v>
+        <v>11.856573705179279</v>
       </c>
       <c r="L9">
-        <v>0.81673306772908372</v>
+        <v>10.306772908366529</v>
       </c>
       <c r="M9">
-        <v>0.15537848605577689</v>
+        <v>0.78486055776892427</v>
       </c>
       <c r="N9">
-        <v>1.9920318725099601E-2</v>
+        <v>0.19920318725099601</v>
       </c>
       <c r="O9">
-        <v>128.00398406374501</v>
-      </c>
-      <c r="P9" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q9">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P9">
+        <v>127.5458167330677</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>29</v>
+      </c>
+      <c r="R9">
         <v>33.466135458167329</v>
       </c>
-      <c r="R9">
-        <v>32243</v>
-      </c>
       <c r="S9">
-        <v>2989</v>
+        <v>32135</v>
       </c>
       <c r="T9">
-        <v>35232</v>
+        <v>2976</v>
       </c>
       <c r="U9">
-        <v>2208</v>
+        <v>35111</v>
       </c>
       <c r="V9">
-        <v>205</v>
-      </c>
-      <c r="W9" s="18">
-        <v>2589</v>
-      </c>
-      <c r="X9">
-        <v>39</v>
+        <v>2186</v>
+      </c>
+      <c r="W9">
+        <v>197</v>
+      </c>
+      <c r="X9" s="17">
+        <v>2587</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="Z9">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="16">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F10">
         <f>(E10-D10)</f>
-        <v>39608412840</v>
+        <v>30222463900</v>
       </c>
       <c r="G10">
         <f>(E10/D10)*100</f>
-        <v>130.13855146080436</v>
+        <v>122.99666202738084</v>
       </c>
       <c r="H10">
-        <v>37850</v>
-      </c>
-      <c r="I10">
-        <v>128.6414342629482</v>
+        <v>37794</v>
+      </c>
+      <c r="I10" s="19">
+        <f t="shared" si="0"/>
+        <v>3172</v>
       </c>
       <c r="J10">
-        <v>11.66135458167331</v>
+        <v>128.15139442231069</v>
       </c>
       <c r="K10">
-        <v>10.32669322709163</v>
+        <v>11.84860557768924</v>
       </c>
       <c r="L10">
-        <v>0.83266932270916338</v>
+        <v>10.41832669322709</v>
       </c>
       <c r="M10">
+        <v>0.78486055776892427</v>
+      </c>
+      <c r="N10">
         <v>0.151394422310757</v>
       </c>
-      <c r="N10">
-        <v>1.5936254980079681E-2</v>
-      </c>
       <c r="O10">
-        <v>128.23904382470121</v>
-      </c>
-      <c r="P10" t="s">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P10">
+        <v>128.11155378486049</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>25</v>
+      </c>
+      <c r="R10">
+        <v>34.661354581673308</v>
+      </c>
+      <c r="S10">
+        <v>32166</v>
+      </c>
+      <c r="T10">
+        <v>2974</v>
+      </c>
+      <c r="U10">
+        <v>35140</v>
+      </c>
+      <c r="V10">
+        <v>2262</v>
+      </c>
+      <c r="W10">
+        <v>197</v>
+      </c>
+      <c r="X10" s="16">
+        <v>2615</v>
+      </c>
+      <c r="Y10">
+        <v>38</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
         <v>39</v>
       </c>
-      <c r="Q10">
-        <v>29.482071713147409</v>
-      </c>
-      <c r="R10">
-        <v>32289</v>
-      </c>
-      <c r="S10">
-        <v>2927</v>
-      </c>
-      <c r="T10">
-        <v>35216</v>
-      </c>
-      <c r="U10">
-        <v>2215</v>
-      </c>
-      <c r="V10">
-        <v>209</v>
-      </c>
-      <c r="W10">
-        <v>2592</v>
-      </c>
-      <c r="X10">
-        <v>38</v>
-      </c>
-      <c r="Y10">
-        <v>4</v>
-      </c>
-      <c r="Z10">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
-        <v>18</v>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F11">
         <f>(E11-D11)</f>
-        <v>39382722640</v>
+        <v>25868776920</v>
       </c>
       <c r="G11">
         <f>(E11/D11)*100</f>
-        <v>129.96682088087991</v>
+        <v>119.68388553161444</v>
       </c>
       <c r="H11">
-        <v>37833</v>
-      </c>
-      <c r="I11">
-        <v>128.8167330677291</v>
+        <v>37823</v>
+      </c>
+      <c r="I11" s="19">
+        <f t="shared" si="0"/>
+        <v>3171</v>
       </c>
       <c r="J11">
-        <v>11.37450199203187</v>
+        <v>128.3545816733068</v>
       </c>
       <c r="K11">
-        <v>10.37450199203187</v>
+        <v>11.908366533864539</v>
       </c>
       <c r="L11">
-        <v>0.86454183266932272</v>
+        <v>10.29482071713147</v>
       </c>
       <c r="M11">
-        <v>0.14741035856573709</v>
+        <v>0.70517928286852594</v>
       </c>
       <c r="N11">
-        <v>1.5936254980079681E-2</v>
+        <v>0.11155378486055779</v>
       </c>
       <c r="O11">
-        <v>128.49402390438249</v>
-      </c>
-      <c r="P11" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11">
-        <v>32.270916334661351</v>
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="P11">
+        <v>128.11553784860561</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>56</v>
       </c>
       <c r="R11">
-        <v>32333</v>
+        <v>42.629482071713149</v>
       </c>
       <c r="S11">
-        <v>2855</v>
+        <v>32217</v>
       </c>
       <c r="T11">
-        <v>35188</v>
+        <v>2989</v>
       </c>
       <c r="U11">
-        <v>2223</v>
+        <v>35206</v>
       </c>
       <c r="V11">
-        <v>217</v>
-      </c>
-      <c r="W11" s="18">
-        <v>2604</v>
+        <v>2275</v>
+      </c>
+      <c r="W11">
+        <v>177</v>
       </c>
       <c r="X11">
-        <v>37</v>
+        <v>2584</v>
       </c>
       <c r="Y11">
-        <v>4</v>
-      </c>
-      <c r="Z11" s="18">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="Z11">
+        <v>5</v>
+      </c>
+      <c r="AA11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A12" s="19">
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F12">
         <f>(E12-D12)</f>
-        <v>22537887980</v>
+        <v>35359989160</v>
       </c>
       <c r="G12">
         <f>(E12/D12)*100</f>
-        <v>117.14936923746409</v>
+        <v>126.8899505319056</v>
       </c>
       <c r="H12">
-        <v>37811</v>
-      </c>
-      <c r="I12">
-        <v>128.53386454183271</v>
+        <v>37887</v>
+      </c>
+      <c r="I12" s="19">
+        <f t="shared" si="0"/>
+        <v>3168</v>
       </c>
       <c r="J12">
-        <v>11.64541832669323</v>
+        <v>128.7250996015936</v>
       </c>
       <c r="K12">
-        <v>10.33067729083665</v>
+        <v>11.749003984063741</v>
       </c>
       <c r="L12">
-        <v>0.7450199203187251</v>
+        <v>10.31075697211155</v>
       </c>
       <c r="M12">
-        <v>0.1235059760956175</v>
+        <v>0.86454183266932272</v>
       </c>
       <c r="N12">
+        <v>0.151394422310757</v>
+      </c>
+      <c r="O12">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="O12">
-        <v>128.35059760956179</v>
-      </c>
-      <c r="P12" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q12">
-        <v>39.04382470119522</v>
+      <c r="P12">
+        <v>128.207171314741</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>31</v>
       </c>
       <c r="R12">
-        <v>32262</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="S12">
-        <v>2923</v>
+        <v>32310</v>
       </c>
       <c r="T12">
-        <v>35185</v>
+        <v>2949</v>
       </c>
       <c r="U12">
-        <v>2274</v>
+        <v>35259</v>
       </c>
       <c r="V12">
-        <v>187</v>
+        <v>2211</v>
       </c>
       <c r="W12">
-        <v>2593</v>
-      </c>
-      <c r="X12">
-        <v>31</v>
+        <v>217</v>
+      </c>
+      <c r="X12" s="19">
+        <v>2588</v>
       </c>
       <c r="Y12">
+        <v>38</v>
+      </c>
+      <c r="Z12">
         <v>2</v>
       </c>
-      <c r="Z12">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
-        <v>20</v>
+      <c r="AA12" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A13" s="19">
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F13">
         <f>(E13-D13)</f>
-        <v>44589708060</v>
+        <v>39795784920</v>
       </c>
       <c r="G13">
         <f>(E13/D13)*100</f>
-        <v>134.06459868217496</v>
+        <v>130.28112528970809</v>
       </c>
       <c r="H13">
-        <v>37749</v>
-      </c>
-      <c r="I13">
-        <v>128.02788844621509</v>
+        <v>37906</v>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="0"/>
+        <v>3166</v>
       </c>
       <c r="J13">
-        <v>11.856573705179279</v>
+        <v>128.71713147410361</v>
       </c>
       <c r="K13">
-        <v>10.306772908366529</v>
+        <v>11.812749003984059</v>
       </c>
       <c r="L13">
-        <v>0.78486055776892427</v>
+        <v>10.30278884462151</v>
       </c>
       <c r="M13">
-        <v>0.19920318725099601</v>
+        <v>0.79681274900398402</v>
       </c>
       <c r="N13">
+        <v>0.18326693227091631</v>
+      </c>
+      <c r="O13">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O13">
-        <v>127.5458167330677</v>
-      </c>
-      <c r="P13" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q13">
-        <v>33.466135458167329</v>
+      <c r="P13">
+        <v>128.13545816733071</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>25</v>
       </c>
       <c r="R13">
-        <v>32135</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="S13">
-        <v>2976</v>
+        <v>32308</v>
       </c>
       <c r="T13">
-        <v>35111</v>
+        <v>2965</v>
       </c>
       <c r="U13">
-        <v>2186</v>
+        <v>35273</v>
       </c>
       <c r="V13">
-        <v>197</v>
-      </c>
-      <c r="W13" s="17">
-        <v>2587</v>
-      </c>
-      <c r="X13">
-        <v>50</v>
+        <v>2198</v>
+      </c>
+      <c r="W13">
+        <v>200</v>
+      </c>
+      <c r="X13" s="19">
+        <v>2586</v>
       </c>
       <c r="Y13">
+        <v>46</v>
+      </c>
+      <c r="Z13">
         <v>1</v>
       </c>
-      <c r="Z13" s="16">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA13" s="19">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F14">
         <f>(E14-D14)</f>
-        <v>25868776920</v>
+        <v>26390302240</v>
       </c>
       <c r="G14">
         <f>(E14/D14)*100</f>
-        <v>119.68388553161444</v>
+        <v>120.08072086451268</v>
       </c>
       <c r="H14">
-        <v>37823</v>
-      </c>
-      <c r="I14">
-        <v>128.3545816733068</v>
+        <v>37808</v>
+      </c>
+      <c r="I14" s="19">
+        <f t="shared" si="0"/>
+        <v>3165</v>
       </c>
       <c r="J14">
-        <v>11.908366533864539</v>
+        <v>128.36254980079681</v>
       </c>
       <c r="K14">
-        <v>10.29482071713147</v>
+        <v>11.7808764940239</v>
       </c>
       <c r="L14">
-        <v>0.70517928286852594</v>
+        <v>10.342629482071709</v>
       </c>
       <c r="M14">
-        <v>0.11155378486055779</v>
+        <v>0.82868525896414347</v>
       </c>
       <c r="N14">
-        <v>1.9920318725099601E-2</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="O14">
-        <v>128.11553784860561</v>
-      </c>
-      <c r="P14" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q14">
-        <v>42.629482071713149</v>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>128.13944223107569</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>40</v>
       </c>
       <c r="R14">
-        <v>32217</v>
+        <v>31.075697211155379</v>
       </c>
       <c r="S14">
-        <v>2989</v>
+        <v>32219</v>
       </c>
       <c r="T14">
-        <v>35206</v>
+        <v>2957</v>
       </c>
       <c r="U14">
-        <v>2275</v>
+        <v>35176</v>
       </c>
       <c r="V14">
-        <v>177</v>
-      </c>
-      <c r="W14" s="18">
-        <v>2584</v>
+        <v>2244</v>
+      </c>
+      <c r="W14">
+        <v>208</v>
       </c>
       <c r="X14">
-        <v>28</v>
+        <v>2596</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="Z14">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A15" s="19">
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F15">
         <f>(E15-D15)</f>
-        <v>30222463900</v>
+        <v>35971527040</v>
       </c>
       <c r="G15">
         <f>(E15/D15)*100</f>
-        <v>122.99666202738084</v>
+        <v>127.35500223956247</v>
       </c>
       <c r="H15">
-        <v>37794</v>
-      </c>
-      <c r="I15">
-        <v>128.15139442231069</v>
+        <v>37858</v>
+      </c>
+      <c r="I15" s="19">
+        <f t="shared" si="0"/>
+        <v>3165</v>
       </c>
       <c r="J15">
-        <v>11.84860557768924</v>
+        <v>128.58964143426289</v>
       </c>
       <c r="K15">
-        <v>10.41832669322709</v>
+        <v>11.768924302788839</v>
       </c>
       <c r="L15">
-        <v>0.78486055776892427</v>
+        <v>10.31872509960159</v>
       </c>
       <c r="M15">
-        <v>0.151394422310757</v>
+        <v>0.82071713147410363</v>
       </c>
       <c r="N15">
-        <v>3.9840637450199202E-3</v>
+        <v>0.13147410358565739</v>
       </c>
       <c r="O15">
-        <v>128.11155378486049</v>
-      </c>
-      <c r="P15" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q15">
-        <v>34.661354581673308</v>
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="P15">
+        <v>128.21912350597611</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>70</v>
       </c>
       <c r="R15">
-        <v>32166</v>
+        <v>35.458167330677291</v>
       </c>
       <c r="S15">
-        <v>2974</v>
+        <v>32276</v>
       </c>
       <c r="T15">
-        <v>35140</v>
+        <v>2954</v>
       </c>
       <c r="U15">
-        <v>2262</v>
+        <v>35230</v>
       </c>
       <c r="V15">
-        <v>197</v>
-      </c>
-      <c r="W15" s="16">
-        <v>2615</v>
-      </c>
-      <c r="X15">
+        <v>2232</v>
+      </c>
+      <c r="W15">
+        <v>206</v>
+      </c>
+      <c r="X15" s="19">
+        <v>2590</v>
+      </c>
+      <c r="Y15">
+        <v>33</v>
+      </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="19">
         <v>38</v>
       </c>
-      <c r="Y15">
-        <v>1</v>
-      </c>
-      <c r="Z15">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
         <v>49</v>
@@ -1923,1086 +2000,1557 @@
       <c r="H16">
         <v>37813</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="19">
+        <f t="shared" si="0"/>
+        <v>3163</v>
+      </c>
+      <c r="J16">
         <v>128.42629482071709</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>11.7609561752988</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>10.322709163346611</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.82868525896414347</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.12749003984063739</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>1.1952191235059761E-2</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>128.14741035856571</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>50</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>32.669322709163353</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>32235</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>2952</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>35187</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>2243</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>208</v>
       </c>
-      <c r="W16" s="18">
+      <c r="X16">
         <v>2591</v>
       </c>
-      <c r="X16">
+      <c r="Y16">
         <v>32</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <v>3</v>
       </c>
-      <c r="Z16" s="18">
+      <c r="AA16">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>24</v>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A17" s="18">
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F17">
         <f>(E17-D17)</f>
-        <v>26390302240</v>
+        <v>55319762920</v>
       </c>
       <c r="G17">
         <f>(E17/D17)*100</f>
-        <v>120.08072086451268</v>
+        <v>142.09352008874677</v>
       </c>
       <c r="H17">
-        <v>37808</v>
-      </c>
-      <c r="I17">
-        <v>128.36254980079681</v>
+        <v>37866</v>
+      </c>
+      <c r="I17" s="19">
+        <f t="shared" si="0"/>
+        <v>3155</v>
       </c>
       <c r="J17">
-        <v>11.7808764940239</v>
+        <v>128.69721115537851</v>
       </c>
       <c r="K17">
-        <v>10.342629482071709</v>
+        <v>11.60956175298805</v>
       </c>
       <c r="L17">
-        <v>0.82868525896414347</v>
+        <v>10.366533864541831</v>
       </c>
       <c r="M17">
-        <v>0.14342629482071709</v>
+        <v>0.92828685258964139</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="O17">
-        <v>128.13944223107569</v>
-      </c>
-      <c r="P17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17">
-        <v>31.075697211155379</v>
+        <v>3.1872509960159362E-2</v>
+      </c>
+      <c r="P17">
+        <v>128.17928286852589</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
       </c>
       <c r="R17">
-        <v>32219</v>
+        <v>25.099601593625501</v>
       </c>
       <c r="S17">
-        <v>2957</v>
+        <v>32303</v>
       </c>
       <c r="T17">
-        <v>35176</v>
+        <v>2914</v>
       </c>
       <c r="U17">
-        <v>2244</v>
+        <v>35217</v>
       </c>
       <c r="V17">
-        <v>208</v>
-      </c>
-      <c r="W17" s="18">
-        <v>2596</v>
-      </c>
-      <c r="X17">
-        <v>36</v>
+        <v>2181</v>
+      </c>
+      <c r="W17">
+        <v>233</v>
+      </c>
+      <c r="X17" s="11">
+        <v>2602</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Z17">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="AA17" s="11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>30</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F18">
         <f>(E18-D18)</f>
-        <v>34633604380</v>
+        <v>35889415260</v>
       </c>
       <c r="G18">
         <f>(E18/D18)*100</f>
-        <v>126.3531556312613</v>
+        <v>127.30871830388865</v>
       </c>
       <c r="H18">
-        <v>37851</v>
-      </c>
-      <c r="I18">
-        <v>128.83266932270919</v>
+        <v>37854</v>
+      </c>
+      <c r="I18" s="19">
+        <f t="shared" si="0"/>
+        <v>3155</v>
       </c>
       <c r="J18">
-        <v>11.474103585657369</v>
+        <v>128.68127490039839</v>
       </c>
       <c r="K18">
-        <v>10.33067729083665</v>
+        <v>11.685258964143429</v>
       </c>
       <c r="L18">
-        <v>0.8605577689243028</v>
+        <v>10.290836653386449</v>
       </c>
       <c r="M18">
-        <v>0.15936254980079681</v>
+        <v>0.87250996015936255</v>
       </c>
       <c r="N18">
-        <v>3.9840637450199202E-3</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="O18">
-        <v>128.41035856573711</v>
-      </c>
-      <c r="P18" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18">
-        <v>31.075697211155379</v>
+        <v>1.1952191235059761E-2</v>
+      </c>
+      <c r="P18">
+        <v>128.17928286852589</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>58</v>
       </c>
       <c r="R18">
-        <v>32337</v>
+        <v>31.872509960159359</v>
       </c>
       <c r="S18">
-        <v>2880</v>
+        <v>32299</v>
       </c>
       <c r="T18">
-        <v>35217</v>
+        <v>2933</v>
       </c>
       <c r="U18">
-        <v>2213</v>
+        <v>35232</v>
       </c>
       <c r="V18">
-        <v>216</v>
-      </c>
-      <c r="W18" s="18">
-        <v>2593</v>
+        <v>2208</v>
+      </c>
+      <c r="W18">
+        <v>219</v>
       </c>
       <c r="X18">
-        <v>40</v>
+        <v>2583</v>
       </c>
       <c r="Y18">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="18">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>26</v>
+        <v>36</v>
+      </c>
+      <c r="Z18">
+        <v>3</v>
+      </c>
+      <c r="AA18">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <f>(E19-D19)</f>
-        <v>39992577160</v>
+        <v>39608412840</v>
       </c>
       <c r="G19">
         <f>(E19/D19)*100</f>
-        <v>130.43086703968137</v>
+        <v>130.13855146080436</v>
       </c>
       <c r="H19">
-        <v>37861</v>
-      </c>
-      <c r="I19">
-        <v>128.97211155378491</v>
+        <v>37850</v>
+      </c>
+      <c r="I19" s="19">
+        <f t="shared" si="0"/>
+        <v>3140</v>
       </c>
       <c r="J19">
-        <v>11.314741035856571</v>
+        <v>128.6414342629482</v>
       </c>
       <c r="K19">
-        <v>10.37450199203187</v>
+        <v>11.66135458167331</v>
       </c>
       <c r="L19">
-        <v>0.8366533864541833</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="M19">
-        <v>0.17131474103585659</v>
+        <v>0.83266932270916338</v>
       </c>
       <c r="N19">
-        <v>7.9681274900398405E-3</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="O19">
-        <v>128.58964143426289</v>
-      </c>
-      <c r="P19" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q19">
-        <v>34.262948207171313</v>
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="P19">
+        <v>128.23904382470121</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>48</v>
       </c>
       <c r="R19">
-        <v>32372</v>
+        <v>29.482071713147409</v>
       </c>
       <c r="S19">
-        <v>2840</v>
+        <v>32289</v>
       </c>
       <c r="T19">
-        <v>35212</v>
+        <v>2927</v>
       </c>
       <c r="U19">
-        <v>2214</v>
+        <v>35216</v>
       </c>
       <c r="V19">
-        <v>210</v>
-      </c>
-      <c r="W19" s="18">
-        <v>2604</v>
-      </c>
-      <c r="X19">
-        <v>43</v>
+        <v>2215</v>
+      </c>
+      <c r="W19">
+        <v>209</v>
+      </c>
+      <c r="X19" s="19">
+        <v>2592</v>
       </c>
       <c r="Y19">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="Z19">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="AA19" s="19">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A20" s="27">
+        <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>26</v>
+      <c r="C20">
+        <v>251</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F20">
         <f>(E20-D20)</f>
-        <v>39011994440</v>
+        <v>51662243640</v>
       </c>
       <c r="G20">
         <f>(E20/D20)*100</f>
-        <v>129.68472901875947</v>
+        <v>139.62621328147634</v>
       </c>
       <c r="H20">
-        <v>37873</v>
-      </c>
-      <c r="I20">
-        <v>128.85258964143429</v>
+        <v>37417</v>
+      </c>
+      <c r="I20" s="19">
+        <f t="shared" si="0"/>
+        <v>3131</v>
       </c>
       <c r="J20">
-        <v>11.466135458167329</v>
+        <v>127.78486055776889</v>
       </c>
       <c r="K20">
-        <v>10.38247011952191</v>
+        <v>11.64541832669323</v>
       </c>
       <c r="L20">
-        <v>0.78087649402390436</v>
+        <v>8.6374501992031867</v>
       </c>
       <c r="M20">
-        <v>0.18326693227091631</v>
+        <v>0.80478087649402386</v>
       </c>
       <c r="N20">
-        <v>3.9840637450199202E-3</v>
+        <v>0.1752988047808765</v>
       </c>
       <c r="O20">
-        <v>128.4980079681275</v>
-      </c>
-      <c r="P20" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q20">
-        <v>33.466135458167329</v>
+        <v>2.3904382470119521E-2</v>
+      </c>
+      <c r="P20">
+        <v>127.1513944223108</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>40</v>
       </c>
       <c r="R20">
-        <v>32342</v>
+        <v>31.075697211155379</v>
       </c>
       <c r="S20">
-        <v>2878</v>
+        <v>32074</v>
       </c>
       <c r="T20">
-        <v>35220</v>
+        <v>2923</v>
       </c>
       <c r="U20">
-        <v>2222</v>
+        <v>34997</v>
       </c>
       <c r="V20">
-        <v>196</v>
-      </c>
-      <c r="W20" s="10">
-        <v>2606</v>
-      </c>
-      <c r="X20">
-        <v>46</v>
+        <v>2168</v>
+      </c>
+      <c r="W20">
+        <v>202</v>
+      </c>
+      <c r="X20" s="19">
+        <v>2370</v>
       </c>
       <c r="Y20">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="11">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="Z20">
+        <v>6</v>
+      </c>
+      <c r="AA20" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F21">
         <f>(E21-D21)</f>
-        <v>36266941760</v>
+        <v>48151148180</v>
       </c>
       <c r="G21">
         <f>(E21/D21)*100</f>
-        <v>127.59598308003686</v>
+        <v>136.6171490255812</v>
       </c>
       <c r="H21">
-        <v>37874</v>
-      </c>
-      <c r="I21">
-        <v>128.796812749004</v>
+        <v>37914</v>
+      </c>
+      <c r="I21" s="19">
+        <f t="shared" si="0"/>
+        <v>3127</v>
       </c>
       <c r="J21">
-        <v>11.55776892430279</v>
+        <v>128.90438247011949</v>
       </c>
       <c r="K21">
-        <v>10.358565737051791</v>
+        <v>11.613545816733071</v>
       </c>
       <c r="L21">
-        <v>0.72908366533864544</v>
+        <v>10.34661354581673</v>
       </c>
       <c r="M21">
-        <v>0.17131474103585659</v>
+        <v>0.82071713147410363</v>
       </c>
       <c r="N21">
-        <v>7.9681274900398405E-3</v>
+        <v>0.1633466135458167</v>
       </c>
       <c r="O21">
-        <v>128.45418326693229</v>
-      </c>
-      <c r="P21" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q21">
-        <v>34.661354581673308</v>
+        <v>2.3904382470119521E-2</v>
+      </c>
+      <c r="P21">
+        <v>128.37051792828689</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>31</v>
       </c>
       <c r="R21">
-        <v>32328</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="S21">
-        <v>2901</v>
+        <v>32355</v>
       </c>
       <c r="T21">
-        <v>35229</v>
+        <v>2915</v>
       </c>
       <c r="U21">
-        <v>2237</v>
+        <v>35270</v>
       </c>
       <c r="V21">
-        <v>183</v>
-      </c>
-      <c r="W21" s="18">
-        <v>2600</v>
+        <v>2203</v>
+      </c>
+      <c r="W21">
+        <v>206</v>
       </c>
       <c r="X21">
-        <v>43</v>
+        <v>2597</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="Z21">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="AA21">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A22" s="19">
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="F22">
         <f>(E22-D22)</f>
-        <v>35399896360</v>
+        <v>22537887980</v>
       </c>
       <c r="G22">
         <f>(E22/D22)*100</f>
-        <v>126.93623706819051</v>
+        <v>117.14936923746409</v>
       </c>
       <c r="H22">
-        <v>37826</v>
-      </c>
-      <c r="I22">
-        <v>128.70119521912349</v>
+        <v>37811</v>
+      </c>
+      <c r="I22" s="19">
+        <f t="shared" si="0"/>
+        <v>3112</v>
       </c>
       <c r="J22">
-        <v>11.446215139442231</v>
+        <v>128.53386454183271</v>
       </c>
       <c r="K22">
-        <v>10.39840637450199</v>
+        <v>11.64541832669323</v>
       </c>
       <c r="L22">
-        <v>0.81673306772908372</v>
+        <v>10.33067729083665</v>
       </c>
       <c r="M22">
-        <v>0.1394422310756972</v>
+        <v>0.7450199203187251</v>
       </c>
       <c r="N22">
-        <v>1.5936254980079681E-2</v>
+        <v>0.1235059760956175</v>
       </c>
       <c r="O22">
-        <v>128.47011952191241</v>
-      </c>
-      <c r="P22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q22">
-        <v>33.864541832669318</v>
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="P22">
+        <v>128.35059760956179</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>44</v>
       </c>
       <c r="R22">
-        <v>32304</v>
+        <v>39.04382470119522</v>
       </c>
       <c r="S22">
-        <v>2873</v>
+        <v>32262</v>
       </c>
       <c r="T22">
-        <v>35177</v>
+        <v>2923</v>
       </c>
       <c r="U22">
-        <v>2249</v>
+        <v>35185</v>
       </c>
       <c r="V22">
-        <v>205</v>
-      </c>
-      <c r="W22" s="12">
-        <v>2610</v>
-      </c>
-      <c r="X22">
-        <v>35</v>
+        <v>2274</v>
+      </c>
+      <c r="W22">
+        <v>187</v>
+      </c>
+      <c r="X22" s="19">
+        <v>2593</v>
       </c>
       <c r="Y22">
-        <v>4</v>
-      </c>
-      <c r="Z22" s="18">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="Z22">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F23">
         <f>(E23-D23)</f>
-        <v>30626567400</v>
+        <v>39441023080</v>
       </c>
       <c r="G23">
         <f>(E23/D23)*100</f>
-        <v>123.30414958512365</v>
+        <v>129.99342434043174</v>
       </c>
       <c r="H23">
-        <v>37794</v>
-      </c>
-      <c r="I23">
-        <v>128.39442231075699</v>
+        <v>37924</v>
+      </c>
+      <c r="I23" s="19">
+        <f t="shared" si="0"/>
+        <v>3104</v>
       </c>
       <c r="J23">
-        <v>11.685258964143429</v>
+        <v>129.04780876494021</v>
       </c>
       <c r="K23">
-        <v>10.350597609561749</v>
+        <v>11.533864541832671</v>
       </c>
       <c r="L23">
-        <v>0.90438247011952189</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="M23">
-        <v>0.1394422310756972</v>
+        <v>0.82868525896414347</v>
       </c>
       <c r="N23">
+        <v>0.17928286852589639</v>
+      </c>
+      <c r="O23">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O23">
-        <v>128.15537848605581</v>
-      </c>
-      <c r="P23" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q23">
-        <v>29.083665338645421</v>
+      <c r="P23">
+        <v>128.46215139442231</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>31</v>
       </c>
       <c r="R23">
-        <v>32227</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="S23">
-        <v>2933</v>
+        <v>32391</v>
       </c>
       <c r="T23">
-        <v>35160</v>
+        <v>2895</v>
       </c>
       <c r="U23">
-        <v>2227</v>
+        <v>35286</v>
       </c>
       <c r="V23">
-        <v>227</v>
+        <v>2200</v>
       </c>
       <c r="W23">
-        <v>2598</v>
+        <v>208</v>
       </c>
       <c r="X23">
+        <v>2592</v>
+      </c>
+      <c r="Y23">
+        <v>45</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A24" s="19">
         <v>35</v>
-      </c>
-      <c r="Y23">
-        <v>1</v>
-      </c>
-      <c r="Z23">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F24">
         <f>(E24-D24)</f>
-        <v>27081734060</v>
+        <v>33233242100</v>
       </c>
       <c r="G24">
         <f>(E24/D24)*100</f>
-        <v>120.60684024154722</v>
+        <v>125.272638858576</v>
       </c>
       <c r="H24">
-        <v>37773</v>
-      </c>
-      <c r="I24">
-        <v>128.4780876494024</v>
+        <v>37875</v>
+      </c>
+      <c r="I24" s="19">
+        <f t="shared" si="0"/>
+        <v>3104</v>
       </c>
       <c r="J24">
-        <v>11.52988047808765</v>
+        <v>128.88446215139439</v>
       </c>
       <c r="K24">
-        <v>10.35458167330677</v>
+        <v>11.553784860557769</v>
       </c>
       <c r="L24">
-        <v>0.8605577689243028</v>
+        <v>10.306772908366529</v>
       </c>
       <c r="M24">
-        <v>0.1155378486055777</v>
+        <v>0.79681274900398402</v>
       </c>
       <c r="N24">
-        <v>1.1952191235059761E-2</v>
+        <v>0.13545816733067731</v>
       </c>
       <c r="O24">
-        <v>128.34661354581669</v>
-      </c>
-      <c r="P24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24">
-        <v>31.075697211155379</v>
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="P24">
+        <v>128.46215139442231</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>25</v>
       </c>
       <c r="R24">
-        <v>32248</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="S24">
-        <v>2894</v>
+        <v>32350</v>
       </c>
       <c r="T24">
-        <v>35142</v>
+        <v>2900</v>
       </c>
       <c r="U24">
-        <v>2255</v>
+        <v>35250</v>
       </c>
       <c r="V24">
-        <v>216</v>
+        <v>2235</v>
       </c>
       <c r="W24">
-        <v>2599</v>
-      </c>
-      <c r="X24">
-        <v>29</v>
+        <v>200</v>
+      </c>
+      <c r="X24" s="19">
+        <v>2587</v>
       </c>
       <c r="Y24">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="Z24">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>32</v>
+        <v>4</v>
+      </c>
+      <c r="AA24" s="19">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A25" s="19">
+        <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="F25">
         <f>(E25-D25)</f>
-        <v>33673165060</v>
+        <v>34633604380</v>
       </c>
       <c r="G25">
         <f>(E25/D25)*100</f>
-        <v>125.62234498283343</v>
+        <v>126.3531556312613</v>
       </c>
       <c r="H25">
-        <v>37796</v>
-      </c>
-      <c r="I25">
-        <v>128.3266932270916</v>
+        <v>37851</v>
+      </c>
+      <c r="I25" s="19">
+        <f t="shared" si="0"/>
+        <v>3097</v>
       </c>
       <c r="J25">
-        <v>11.768924302788839</v>
+        <v>128.83266932270919</v>
       </c>
       <c r="K25">
-        <v>10.34661354581673</v>
+        <v>11.474103585657369</v>
       </c>
       <c r="L25">
-        <v>0.89243027888446214</v>
+        <v>10.33067729083665</v>
       </c>
       <c r="M25">
-        <v>0.1235059760956175</v>
+        <v>0.8605577689243028</v>
       </c>
       <c r="N25">
-        <v>1.5936254980079681E-2</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="O25">
-        <v>128.07171314741029</v>
-      </c>
-      <c r="P25" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q25">
-        <v>31.474103585657371</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P25">
+        <v>128.41035856573711</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>40</v>
       </c>
       <c r="R25">
-        <v>32210</v>
+        <v>31.075697211155379</v>
       </c>
       <c r="S25">
-        <v>2954</v>
+        <v>32337</v>
       </c>
       <c r="T25">
-        <v>35164</v>
+        <v>2880</v>
       </c>
       <c r="U25">
-        <v>2233</v>
+        <v>35217</v>
       </c>
       <c r="V25">
-        <v>224</v>
+        <v>2213</v>
       </c>
       <c r="W25">
-        <v>2597</v>
-      </c>
-      <c r="X25">
-        <v>31</v>
+        <v>216</v>
+      </c>
+      <c r="X25" s="19">
+        <v>2593</v>
       </c>
       <c r="Y25">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="Z25">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="18">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="AA25" s="19">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>11</v>
       </c>
       <c r="B26" t="s">
         <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="F26">
         <f>(E26-D26)</f>
-        <v>33182591240</v>
+        <v>17220497120</v>
       </c>
       <c r="G26">
         <f>(E26/D26)*100</f>
-        <v>125.24906104492058</v>
+        <v>113.10329804752037</v>
       </c>
       <c r="H26">
-        <v>37811</v>
-      </c>
-      <c r="I26">
-        <v>128.33864541832671</v>
+        <v>37789</v>
+      </c>
+      <c r="I26" s="19">
+        <f t="shared" si="0"/>
+        <v>3091</v>
       </c>
       <c r="J26">
-        <v>11.820717131474099</v>
+        <v>128.48605577689241</v>
       </c>
       <c r="K26">
-        <v>10.334661354581669</v>
+        <v>11.597609561752989</v>
       </c>
       <c r="L26">
-        <v>0.89641434262948205</v>
+        <v>10.342629482071709</v>
       </c>
       <c r="M26">
-        <v>0.1394422310756972</v>
+        <v>0.71713147410358569</v>
       </c>
       <c r="N26">
-        <v>7.9681274900398405E-3</v>
+        <v>0.12749003984063739</v>
       </c>
       <c r="O26">
-        <v>128.02390438247011</v>
-      </c>
-      <c r="P26" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q26">
-        <v>29.880478087649401</v>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>128.43426294820719</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>38</v>
       </c>
       <c r="R26">
-        <v>32213</v>
+        <v>37.450199203187253</v>
       </c>
       <c r="S26">
-        <v>2967</v>
+        <v>32250</v>
       </c>
       <c r="T26">
-        <v>35180</v>
+        <v>2911</v>
       </c>
       <c r="U26">
-        <v>2221</v>
+        <v>35161</v>
       </c>
       <c r="V26">
-        <v>225</v>
-      </c>
-      <c r="W26" s="18">
-        <v>2594</v>
-      </c>
-      <c r="X26">
-        <v>35</v>
+        <v>2288</v>
+      </c>
+      <c r="W26">
+        <v>180</v>
+      </c>
+      <c r="X26" s="19">
+        <v>2596</v>
       </c>
       <c r="Y26">
-        <v>2</v>
-      </c>
-      <c r="Z26" s="18">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A27" s="19">
+        <v>28</v>
       </c>
       <c r="B27" t="s">
         <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="F27">
         <f>(E27-D27)</f>
-        <v>36362063220</v>
+        <v>36266941760</v>
       </c>
       <c r="G27">
         <f>(E27/D27)*100</f>
-        <v>127.66836222405399</v>
+        <v>127.59598308003686</v>
       </c>
       <c r="H27">
-        <v>37820</v>
-      </c>
-      <c r="I27">
-        <v>128.49402390438249</v>
+        <v>37874</v>
+      </c>
+      <c r="I27" s="19">
+        <f t="shared" si="0"/>
+        <v>3086</v>
       </c>
       <c r="J27">
-        <v>11.733067729083659</v>
+        <v>128.796812749004</v>
       </c>
       <c r="K27">
-        <v>10.306772908366529</v>
+        <v>11.55776892430279</v>
       </c>
       <c r="L27">
-        <v>0.89641434262948205</v>
+        <v>10.358565737051791</v>
       </c>
       <c r="M27">
-        <v>0.1235059760956175</v>
+        <v>0.72908366533864544</v>
       </c>
       <c r="N27">
-        <v>1.9920318725099601E-2</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="O27">
-        <v>128.09960159362549</v>
-      </c>
-      <c r="P27" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q27">
-        <v>29.482071713147409</v>
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="P27">
+        <v>128.45418326693229</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>25</v>
       </c>
       <c r="R27">
-        <v>32252</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="S27">
-        <v>2945</v>
+        <v>32328</v>
       </c>
       <c r="T27">
-        <v>35197</v>
+        <v>2901</v>
       </c>
       <c r="U27">
-        <v>2218</v>
+        <v>35229</v>
       </c>
       <c r="V27">
-        <v>225</v>
+        <v>2237</v>
       </c>
       <c r="W27">
-        <v>2587</v>
-      </c>
-      <c r="X27">
+        <v>183</v>
+      </c>
+      <c r="X27" s="19">
+        <v>2600</v>
+      </c>
+      <c r="Y27">
+        <v>43</v>
+      </c>
+      <c r="Z27">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A28" s="18">
         <v>31</v>
-      </c>
-      <c r="Y27">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A28" s="18">
-        <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F28">
         <f>(E28-D28)</f>
-        <v>38588514480</v>
+        <v>38523848680</v>
       </c>
       <c r="G28">
         <f>(E28/D28)*100</f>
-        <v>129.36249766304633</v>
+        <v>129.31329262297245</v>
       </c>
       <c r="H28">
-        <v>37848</v>
-      </c>
-      <c r="I28">
-        <v>128.77689243027891</v>
+        <v>37883</v>
+      </c>
+      <c r="I28" s="19">
+        <f t="shared" si="0"/>
+        <v>3086</v>
       </c>
       <c r="J28">
-        <v>11.56573705179283</v>
+        <v>128.84860557768931</v>
       </c>
       <c r="K28">
-        <v>10.29482071713147</v>
+        <v>11.553784860557769</v>
       </c>
       <c r="L28">
+        <v>10.334661354581669</v>
+      </c>
+      <c r="M28">
+        <v>0.73705179282868527</v>
+      </c>
+      <c r="N28">
+        <v>0.18725099601593631</v>
+      </c>
+      <c r="O28">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P28">
+        <v>128.45418326693229</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>42</v>
+      </c>
+      <c r="R28">
+        <v>31.474103585657371</v>
+      </c>
+      <c r="S28">
+        <v>32341</v>
+      </c>
+      <c r="T28">
+        <v>2900</v>
+      </c>
+      <c r="U28">
+        <v>35241</v>
+      </c>
+      <c r="V28">
+        <v>2217</v>
+      </c>
+      <c r="W28">
+        <v>185</v>
+      </c>
+      <c r="X28" s="10">
+        <v>2594</v>
+      </c>
+      <c r="Y28">
+        <v>47</v>
+      </c>
+      <c r="Z28">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29">
+        <f>(E29-D29)</f>
+        <v>35399896360</v>
+      </c>
+      <c r="G29">
+        <f>(E29/D29)*100</f>
+        <v>126.93623706819051</v>
+      </c>
+      <c r="H29">
+        <v>37826</v>
+      </c>
+      <c r="I29" s="19">
+        <f t="shared" si="0"/>
+        <v>3082</v>
+      </c>
+      <c r="J29">
+        <v>128.70119521912349</v>
+      </c>
+      <c r="K29">
+        <v>11.446215139442231</v>
+      </c>
+      <c r="L29">
+        <v>10.39840637450199</v>
+      </c>
+      <c r="M29">
         <v>0.81673306772908372</v>
       </c>
-      <c r="M28">
-        <v>0.1235059760956175</v>
-      </c>
-      <c r="N28">
-        <v>2.7888446215139438E-2</v>
-      </c>
-      <c r="O28">
-        <v>128.33864541832671</v>
-      </c>
-      <c r="P28" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q28">
-        <v>31.872509960159359</v>
-      </c>
-      <c r="R28">
-        <v>32323</v>
-      </c>
-      <c r="S28">
-        <v>2903</v>
-      </c>
-      <c r="T28">
-        <v>35226</v>
-      </c>
-      <c r="U28">
-        <v>2227</v>
-      </c>
-      <c r="V28">
+      <c r="N29">
+        <v>0.1394422310756972</v>
+      </c>
+      <c r="O29">
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="P29">
+        <v>128.47011952191241</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>27</v>
+      </c>
+      <c r="R29">
+        <v>33.864541832669318</v>
+      </c>
+      <c r="S29">
+        <v>32304</v>
+      </c>
+      <c r="T29">
+        <v>2873</v>
+      </c>
+      <c r="U29">
+        <v>35177</v>
+      </c>
+      <c r="V29">
+        <v>2249</v>
+      </c>
+      <c r="W29">
         <v>205</v>
       </c>
-      <c r="W28" s="18">
-        <v>2584</v>
-      </c>
-      <c r="X28">
+      <c r="X29" s="12">
+        <v>2610</v>
+      </c>
+      <c r="Y29">
+        <v>35</v>
+      </c>
+      <c r="Z29">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="19">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30">
+        <f>(E30-D30)</f>
+        <v>39382722640</v>
+      </c>
+      <c r="G30">
+        <f>(E30/D30)*100</f>
+        <v>129.96682088087991</v>
+      </c>
+      <c r="H30">
+        <v>37833</v>
+      </c>
+      <c r="I30" s="19">
+        <f t="shared" si="0"/>
+        <v>3076</v>
+      </c>
+      <c r="J30">
+        <v>128.8167330677291</v>
+      </c>
+      <c r="K30">
+        <v>11.37450199203187</v>
+      </c>
+      <c r="L30">
+        <v>10.37450199203187</v>
+      </c>
+      <c r="M30">
+        <v>0.86454183266932272</v>
+      </c>
+      <c r="N30">
+        <v>0.14741035856573709</v>
+      </c>
+      <c r="O30">
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="P30">
+        <v>128.49402390438249</v>
+      </c>
+      <c r="Q30" t="s">
         <v>31</v>
       </c>
-      <c r="Y28">
-        <v>7</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="R30">
+        <v>32.270916334661351</v>
+      </c>
+      <c r="S30">
+        <v>32333</v>
+      </c>
+      <c r="T30">
+        <v>2855</v>
+      </c>
+      <c r="U30">
+        <v>35188</v>
+      </c>
+      <c r="V30">
+        <v>2223</v>
+      </c>
+      <c r="W30">
+        <v>217</v>
+      </c>
+      <c r="X30">
+        <v>2604</v>
+      </c>
+      <c r="Y30">
         <v>37</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="Z30">
+        <v>4</v>
+      </c>
+      <c r="AA30">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31" s="18">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31">
+        <f>(E31-D31)</f>
+        <v>39011994440</v>
+      </c>
+      <c r="G31">
+        <f>(E31/D31)*100</f>
+        <v>129.68472901875947</v>
+      </c>
+      <c r="H31">
+        <v>37873</v>
+      </c>
+      <c r="I31" s="19">
+        <f t="shared" si="0"/>
+        <v>3075</v>
+      </c>
+      <c r="J31">
+        <v>128.85258964143429</v>
+      </c>
+      <c r="K31">
+        <v>11.466135458167329</v>
+      </c>
+      <c r="L31">
+        <v>10.38247011952191</v>
+      </c>
+      <c r="M31">
+        <v>0.78087649402390436</v>
+      </c>
+      <c r="N31">
+        <v>0.18326693227091631</v>
+      </c>
+      <c r="O31">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="P31">
+        <v>128.4980079681275</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R31">
+        <v>33.466135458167329</v>
+      </c>
+      <c r="S31">
+        <v>32342</v>
+      </c>
+      <c r="T31">
+        <v>2878</v>
+      </c>
+      <c r="U31">
+        <v>35220</v>
+      </c>
+      <c r="V31">
+        <v>2222</v>
+      </c>
+      <c r="W31">
+        <v>196</v>
+      </c>
+      <c r="X31" s="10">
+        <v>2606</v>
+      </c>
+      <c r="Y31">
+        <v>46</v>
+      </c>
+      <c r="Z31">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A32" s="19">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32">
+        <f>(E32-D32)</f>
+        <v>39992577160</v>
+      </c>
+      <c r="G32">
+        <f>(E32/D32)*100</f>
+        <v>130.43086703968137</v>
+      </c>
+      <c r="H32">
+        <v>37861</v>
+      </c>
+      <c r="I32" s="19">
+        <f t="shared" si="0"/>
+        <v>3052</v>
+      </c>
+      <c r="J32">
+        <v>128.97211155378491</v>
+      </c>
+      <c r="K32">
+        <v>11.314741035856571</v>
+      </c>
+      <c r="L32">
+        <v>10.37450199203187</v>
+      </c>
+      <c r="M32">
+        <v>0.8366533864541833</v>
+      </c>
+      <c r="N32">
+        <v>0.17131474103585659</v>
+      </c>
+      <c r="O32">
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="P32">
+        <v>128.58964143426289</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>33</v>
+      </c>
+      <c r="R32">
+        <v>34.262948207171313</v>
+      </c>
+      <c r="S32">
+        <v>32372</v>
+      </c>
+      <c r="T32">
+        <v>2840</v>
+      </c>
+      <c r="U32">
+        <v>35212</v>
+      </c>
+      <c r="V32">
+        <v>2214</v>
+      </c>
+      <c r="W32">
+        <v>210</v>
+      </c>
+      <c r="X32">
+        <v>2604</v>
+      </c>
+      <c r="Y32">
+        <v>43</v>
+      </c>
+      <c r="Z32">
+        <v>2</v>
+      </c>
+      <c r="AA32" s="19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="19">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="19">
         <v>41</v>
       </c>
     </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="19">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="19">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="19">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="19">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="19">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="19">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="19">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="19">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="19">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="19">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="19">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="19">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="19">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="19">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="19">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AF2" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState ref="A3:AF34">
-      <sortCondition ref="A2"/>
+  <autoFilter ref="A2:AG2" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState ref="A3:AG53">
+      <sortCondition descending="1" ref="I2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="S1:U1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0F59A0-4578-4482-B318-4A469DFA09E8}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F3B955-25D8-4153-AD54-BBD10B0A694C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="106">
   <si>
     <t>Trung bình/Kỳ</t>
   </si>
@@ -498,7 +498,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -542,6 +542,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -556,7 +558,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
@@ -844,9 +845,9 @@
   <cols>
     <col min="2" max="2" width="9" style="21" customWidth="1"/>
     <col min="3" max="3" width="4.26953125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.453125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="5.54296875" style="11" customWidth="1"/>
     <col min="7" max="7" width="13.1796875" style="21" customWidth="1"/>
     <col min="8" max="9" width="14.1796875" style="21" customWidth="1"/>
     <col min="10" max="10" width="8.453125" style="21" customWidth="1"/>
@@ -863,33 +864,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="X1" s="25" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="X1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="27" t="s">
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="26" t="s">
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
     </row>
     <row r="2" spans="1:32" s="2" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -991,7 +992,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -999,103 +1000,103 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <f>(E3-D3)</f>
-        <v>55319762920</v>
-      </c>
-      <c r="G3" s="29">
+        <v>52737617120</v>
+      </c>
+      <c r="G3" s="10">
         <f>(E3/D3)*100</f>
-        <v>142.09352008874677</v>
+        <v>140.12873209315185</v>
       </c>
       <c r="H3">
-        <v>37866</v>
+        <v>37925</v>
       </c>
       <c r="I3">
         <f>(W3+Z3+AC3)</f>
-        <v>37879.5577689243</v>
+        <v>37932.167330677294</v>
       </c>
       <c r="J3">
-        <v>128.69721115537851</v>
+        <v>128.8565737051793</v>
       </c>
       <c r="K3" s="21">
-        <v>11.60956175298805</v>
-      </c>
-      <c r="L3" s="21">
+        <v>11.71713147410359</v>
+      </c>
+      <c r="L3" s="24">
         <f>J3+K3</f>
-        <v>140.30677290836655</v>
+        <v>140.57370517928288</v>
       </c>
       <c r="M3">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="N3" s="29">
-        <v>0.92828685258964139</v>
-      </c>
-      <c r="O3" s="10">
+        <v>10.31872509960159</v>
+      </c>
+      <c r="N3" s="23">
+        <v>0.8127490039840638</v>
+      </c>
+      <c r="O3" s="23">
         <f>(AC3+AF3)/C3</f>
-        <v>10.553784860557769</v>
+        <v>10.52191235059761</v>
       </c>
       <c r="P3" s="21">
-        <v>0.15537848605577689</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="Q3">
-        <v>3.1872509960159362E-2</v>
-      </c>
-      <c r="R3" s="21">
+        <v>2.3904382470119521E-2</v>
+      </c>
+      <c r="R3" s="24">
         <f>AF3/C3</f>
-        <v>0.18725099601593626</v>
+        <v>0.20318725099601595</v>
       </c>
       <c r="S3">
-        <v>128.17928286852589</v>
+        <v>128.19521912350601</v>
       </c>
       <c r="T3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3" s="29">
-        <v>25.099601593625501</v>
+        <v>31</v>
+      </c>
+      <c r="U3" s="8">
+        <v>31.075697211155379</v>
       </c>
       <c r="V3" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="9">
-        <v>60.557768924302792</v>
+        <v>32</v>
+      </c>
+      <c r="W3" s="23">
+        <v>58.167330677290842</v>
       </c>
       <c r="X3">
-        <v>32303</v>
+        <v>32343</v>
       </c>
       <c r="Y3">
-        <v>2914</v>
+        <v>2941</v>
       </c>
       <c r="Z3">
-        <v>35217</v>
+        <v>35284</v>
       </c>
       <c r="AA3">
-        <v>2181</v>
-      </c>
-      <c r="AB3" s="29">
-        <v>233</v>
-      </c>
-      <c r="AC3" s="9">
-        <v>2602</v>
+        <v>2182</v>
+      </c>
+      <c r="AB3" s="23">
+        <v>204</v>
+      </c>
+      <c r="AC3" s="23">
+        <v>2590</v>
       </c>
       <c r="AD3">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AE3">
-        <v>8</v>
-      </c>
-      <c r="AF3" s="9">
-        <v>47</v>
+        <v>6</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>10</v>
+      <c r="A4" s="23">
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1103,103 +1104,103 @@
       <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="F4">
         <f>(E4-D4)</f>
-        <v>52737617120</v>
-      </c>
-      <c r="G4" s="10">
+        <v>17220497120</v>
+      </c>
+      <c r="G4" s="23">
         <f>(E4/D4)*100</f>
-        <v>140.12873209315185</v>
+        <v>113.10329804752037</v>
       </c>
       <c r="H4">
-        <v>37925</v>
+        <v>37789</v>
       </c>
       <c r="I4">
         <f>(W4+Z4+AC4)</f>
-        <v>37932.167330677294</v>
+        <v>37810.784860557767</v>
       </c>
       <c r="J4">
-        <v>128.8565737051793</v>
+        <v>128.48605577689241</v>
       </c>
       <c r="K4">
-        <v>11.71713147410359</v>
-      </c>
-      <c r="L4" s="29">
+        <v>11.597609561752989</v>
+      </c>
+      <c r="L4" s="23">
         <f>J4+K4</f>
-        <v>140.57370517928288</v>
+        <v>140.0836653386454</v>
       </c>
       <c r="M4">
-        <v>10.31872509960159</v>
+        <v>10.342629482071709</v>
       </c>
       <c r="N4" s="21">
-        <v>0.8127490039840638</v>
+        <v>0.71713147410358569</v>
       </c>
       <c r="O4" s="21">
         <f>(AC4+AF4)/C4</f>
-        <v>10.52191235059761</v>
+        <v>10.47011952191235</v>
       </c>
       <c r="P4" s="21">
-        <v>0.17928286852589639</v>
+        <v>0.12749003984063739</v>
       </c>
       <c r="Q4">
-        <v>2.3904382470119521E-2</v>
-      </c>
-      <c r="R4" s="29">
+        <v>0</v>
+      </c>
+      <c r="R4" s="23">
         <f>AF4/C4</f>
-        <v>0.20318725099601595</v>
+        <v>0.12749003984063745</v>
       </c>
       <c r="S4">
-        <v>128.19521912350601</v>
+        <v>128.43426294820719</v>
       </c>
       <c r="T4" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="8">
-        <v>31.075697211155379</v>
+        <v>100</v>
+      </c>
+      <c r="U4" s="23">
+        <v>37.450199203187253</v>
       </c>
       <c r="V4" t="s">
+        <v>101</v>
+      </c>
+      <c r="W4" s="21">
+        <v>53.784860557768923</v>
+      </c>
+      <c r="X4">
+        <v>32250</v>
+      </c>
+      <c r="Y4">
+        <v>2911</v>
+      </c>
+      <c r="Z4">
+        <v>35161</v>
+      </c>
+      <c r="AA4">
+        <v>2288</v>
+      </c>
+      <c r="AB4" s="21">
+        <v>180</v>
+      </c>
+      <c r="AC4" s="21">
+        <v>2596</v>
+      </c>
+      <c r="AD4">
         <v>32</v>
       </c>
-      <c r="W4" s="21">
-        <v>58.167330677290842</v>
-      </c>
-      <c r="X4">
-        <v>32343</v>
-      </c>
-      <c r="Y4">
-        <v>2941</v>
-      </c>
-      <c r="Z4">
-        <v>35284</v>
-      </c>
-      <c r="AA4">
-        <v>2182</v>
-      </c>
-      <c r="AB4" s="21">
-        <v>204</v>
-      </c>
-      <c r="AC4" s="21">
-        <v>2590</v>
-      </c>
-      <c r="AD4">
-        <v>45</v>
-      </c>
       <c r="AE4">
-        <v>6</v>
-      </c>
-      <c r="AF4" s="10">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="23">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="21">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1207,95 +1208,95 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>35</v>
+      <c r="D5" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F5">
         <f>(E5-D5)</f>
-        <v>48151148180</v>
-      </c>
-      <c r="G5" s="8">
+        <v>39795784920</v>
+      </c>
+      <c r="G5" s="23">
         <f>(E5/D5)*100</f>
-        <v>136.6171490255812</v>
+        <v>130.28112528970809</v>
       </c>
       <c r="H5">
-        <v>37914</v>
+        <v>37906</v>
       </c>
       <c r="I5" s="21">
         <f>(W5+Z5+AC5)</f>
-        <v>37926.760956175298</v>
+        <v>37917.964143426296</v>
       </c>
       <c r="J5">
-        <v>128.90438247011949</v>
+        <v>128.71713147410361</v>
       </c>
       <c r="K5" s="21">
-        <v>11.613545816733071</v>
+        <v>11.812749003984059</v>
       </c>
       <c r="L5" s="10">
         <f>J5+K5</f>
-        <v>140.51792828685257</v>
+        <v>140.52988047808768</v>
       </c>
       <c r="M5">
-        <v>10.34661354581673</v>
+        <v>10.30278884462151</v>
       </c>
       <c r="N5" s="21">
-        <v>0.82071713147410363</v>
+        <v>0.79681274900398402</v>
       </c>
       <c r="O5" s="21">
         <f>(AC5+AF5)/C5</f>
-        <v>10.533864541832669</v>
+        <v>10.490039840637451</v>
       </c>
       <c r="P5" s="21">
-        <v>0.1633466135458167</v>
+        <v>0.18326693227091631</v>
       </c>
       <c r="Q5" s="21">
-        <v>2.3904382470119521E-2</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="R5" s="21">
         <f>AF5/C5</f>
         <v>0.18725099601593626</v>
       </c>
       <c r="S5">
-        <v>128.37051792828689</v>
+        <v>128.13545816733071</v>
       </c>
       <c r="T5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="U5" s="21">
-        <v>32.270916334661351</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="W5" s="21">
-        <v>59.760956175298809</v>
+        <v>58.964143426294832</v>
       </c>
       <c r="X5">
-        <v>32355</v>
+        <v>32308</v>
       </c>
       <c r="Y5">
-        <v>2915</v>
+        <v>2965</v>
       </c>
       <c r="Z5">
-        <v>35270</v>
+        <v>35273</v>
       </c>
       <c r="AA5">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="AB5">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AC5" s="21">
-        <v>2597</v>
+        <v>2586</v>
       </c>
       <c r="AD5">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="AE5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF5" s="9">
         <v>47</v>
@@ -1303,7 +1304,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="21">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1311,103 +1312,103 @@
       <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F6">
         <f>(E6-D6)</f>
-        <v>47480999320</v>
-      </c>
-      <c r="G6" s="8">
+        <v>37463917860</v>
+      </c>
+      <c r="G6" s="23">
         <f>(E6/D6)*100</f>
-        <v>136.12890390728003</v>
+        <v>128.50677761080814</v>
       </c>
       <c r="H6">
-        <v>37866</v>
-      </c>
-      <c r="I6" s="8">
+        <v>37875</v>
+      </c>
+      <c r="I6" s="23">
         <f>(W6+Z6+AC6)</f>
-        <v>37881.948207171314</v>
+        <v>37892.768924302785</v>
       </c>
       <c r="J6">
-        <v>128.3585657370518</v>
-      </c>
-      <c r="K6" s="8">
-        <v>11.94820717131474</v>
-      </c>
-      <c r="L6" s="21">
+        <v>128.601593625498</v>
+      </c>
+      <c r="K6" s="23">
+        <v>11.8605577689243</v>
+      </c>
+      <c r="L6" s="10">
         <f>J6+K6</f>
-        <v>140.30677290836655</v>
+        <v>140.46215139442231</v>
       </c>
       <c r="M6">
-        <v>10.366533864541831</v>
+        <v>10.27490039840638</v>
       </c>
       <c r="N6" s="21">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="O6" s="10">
+        <v>0.8366533864541833</v>
+      </c>
+      <c r="O6" s="23">
         <f>(AC6+AF6)/C6</f>
-        <v>10.553784860557769</v>
+        <v>10.434262948207172</v>
       </c>
       <c r="P6">
-        <v>0.16733067729083659</v>
-      </c>
-      <c r="Q6" s="29">
-        <v>1.9920318725099601E-2</v>
+        <v>0.14342629482071709</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>1.5936254980079681E-2</v>
       </c>
       <c r="R6" s="21">
         <f>AF6/C6</f>
-        <v>0.18725099601593626</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="S6">
-        <v>127.9123505976096</v>
+        <v>128.03585657370519</v>
       </c>
       <c r="T6" t="s">
-        <v>31</v>
-      </c>
-      <c r="U6" s="8">
-        <v>31.075697211155379</v>
+        <v>45</v>
+      </c>
+      <c r="U6" s="23">
+        <v>35.059760956175303</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
-      </c>
-      <c r="W6" s="8">
-        <v>62.948207171314742</v>
+        <v>46</v>
+      </c>
+      <c r="W6" s="23">
+        <v>57.768924302788847</v>
       </c>
       <c r="X6">
-        <v>32218</v>
+        <v>32279</v>
       </c>
       <c r="Y6">
-        <v>2999</v>
+        <v>2977</v>
       </c>
       <c r="Z6">
-        <v>35217</v>
+        <v>35256</v>
       </c>
       <c r="AA6">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="AB6" s="21">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AC6" s="21">
-        <v>2602</v>
+        <v>2579</v>
       </c>
       <c r="AD6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE6">
-        <v>5</v>
-      </c>
-      <c r="AF6" s="9">
-        <v>47</v>
+        <v>4</v>
+      </c>
+      <c r="AF6" s="23">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="21">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1415,103 +1416,103 @@
       <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <f>(E7-D7)</f>
-        <v>47053193320</v>
-      </c>
-      <c r="G7" s="8">
+        <v>35516488280</v>
+      </c>
+      <c r="G7" s="23">
         <f>(E7/D7)*100</f>
-        <v>135.80338081201427</v>
+        <v>127.02495336174735</v>
       </c>
       <c r="H7">
-        <v>37866</v>
-      </c>
-      <c r="I7" s="21">
+        <v>37835</v>
+      </c>
+      <c r="I7" s="24">
         <f>(W7+Z7+AC7)</f>
-        <v>37882.346613545815</v>
+        <v>37852.370517928284</v>
       </c>
       <c r="J7">
-        <v>128.68127490039839</v>
+        <v>128.23904382470121</v>
       </c>
       <c r="K7" s="21">
-        <v>11.62549800796813</v>
+        <v>12.011952191235061</v>
       </c>
       <c r="L7" s="21">
         <f>J7+K7</f>
-        <v>140.30677290836653</v>
+        <v>140.25099601593627</v>
       </c>
       <c r="M7">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="N7" s="17">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="O7" s="10">
+        <v>10.32669322709163</v>
+      </c>
+      <c r="N7" s="23">
+        <v>0.85657370517928288</v>
+      </c>
+      <c r="O7" s="23">
         <f>(AC7+AF7)/C7</f>
-        <v>10.553784860557769</v>
+        <v>10.48605577689243</v>
       </c>
       <c r="P7" s="21">
-        <v>0.16733067729083659</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="Q7" s="21">
-        <v>1.9920318725099601E-2</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="R7" s="21">
         <f>AF7/C7</f>
-        <v>0.18725099601593626</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="S7">
-        <v>128.27091633466139</v>
+        <v>127.87250996015941</v>
       </c>
       <c r="T7" t="s">
-        <v>54</v>
-      </c>
-      <c r="U7" s="10">
-        <v>30.2788844621514</v>
+        <v>51</v>
+      </c>
+      <c r="U7" s="23">
+        <v>34.661354581673308</v>
       </c>
       <c r="V7" t="s">
-        <v>55</v>
-      </c>
-      <c r="W7" s="10">
-        <v>63.34661354581673</v>
+        <v>52</v>
+      </c>
+      <c r="W7" s="23">
+        <v>57.370517928286858</v>
       </c>
       <c r="X7">
-        <v>32299</v>
+        <v>32188</v>
       </c>
       <c r="Y7">
-        <v>2918</v>
+        <v>3015</v>
       </c>
       <c r="Z7">
-        <v>35217</v>
+        <v>35203</v>
       </c>
       <c r="AA7">
-        <v>2206</v>
+        <v>2217</v>
       </c>
       <c r="AB7" s="21">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AC7" s="21">
-        <v>2602</v>
+        <v>2592</v>
       </c>
       <c r="AD7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE7">
-        <v>5</v>
-      </c>
-      <c r="AF7" s="9">
-        <v>47</v>
+        <v>2</v>
+      </c>
+      <c r="AF7" s="23">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1523,99 +1524,99 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <f>(E8-D8)</f>
-        <v>44542337720</v>
-      </c>
-      <c r="G8" s="9">
+        <v>55319762920</v>
+      </c>
+      <c r="G8" s="24">
         <f>(E8/D8)*100</f>
-        <v>133.8928384477712</v>
+        <v>142.09352008874677</v>
       </c>
       <c r="H8">
-        <v>37897</v>
+        <v>37866</v>
       </c>
       <c r="I8" s="21">
         <f>(W8+Z8+AC8)</f>
-        <v>37902.972111553783</v>
+        <v>37879.5577689243</v>
       </c>
       <c r="J8">
-        <v>128.53784860557769</v>
+        <v>128.69721115537851</v>
       </c>
       <c r="K8" s="21">
-        <v>11.89243027888446</v>
-      </c>
-      <c r="L8" s="8">
+        <v>11.60956175298805</v>
+      </c>
+      <c r="L8" s="23">
         <f>J8+K8</f>
-        <v>140.43027888446215</v>
+        <v>140.30677290836655</v>
       </c>
       <c r="M8">
-        <v>10.350597609561749</v>
-      </c>
-      <c r="N8" s="21">
-        <v>0.78884462151394419</v>
+        <v>10.366533864541831</v>
+      </c>
+      <c r="N8" s="24">
+        <v>0.92828685258964139</v>
       </c>
       <c r="O8" s="10">
         <f>(AC8+AF8)/C8</f>
         <v>10.553784860557769</v>
       </c>
-      <c r="P8" s="29">
-        <v>0.19920318725099601</v>
+      <c r="P8" s="23">
+        <v>0.15537848605577689</v>
       </c>
       <c r="Q8" s="21">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="R8" s="29">
+        <v>3.1872509960159362E-2</v>
+      </c>
+      <c r="R8" s="23">
         <f>AF8/C8</f>
-        <v>0.20318725099601595</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S8">
-        <v>128.0637450199203</v>
+        <v>128.17928286852589</v>
       </c>
       <c r="T8" t="s">
-        <v>48</v>
-      </c>
-      <c r="U8" s="21">
-        <v>33.466135458167329</v>
+        <v>28</v>
+      </c>
+      <c r="U8" s="24">
+        <v>25.099601593625501</v>
       </c>
       <c r="V8" t="s">
-        <v>49</v>
-      </c>
-      <c r="W8" s="21">
-        <v>56.972111553784863</v>
+        <v>29</v>
+      </c>
+      <c r="W8" s="9">
+        <v>60.557768924302792</v>
       </c>
       <c r="X8">
-        <v>32263</v>
+        <v>32303</v>
       </c>
       <c r="Y8">
-        <v>2985</v>
+        <v>2914</v>
       </c>
       <c r="Z8">
-        <v>35248</v>
+        <v>35217</v>
       </c>
       <c r="AA8">
-        <v>2196</v>
-      </c>
-      <c r="AB8" s="21">
-        <v>198</v>
-      </c>
-      <c r="AC8" s="14">
-        <v>2598</v>
+        <v>2181</v>
+      </c>
+      <c r="AB8" s="24">
+        <v>233</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>2602</v>
       </c>
       <c r="AD8">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="29">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="AF8" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="21">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -1623,103 +1624,103 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <f>(E9-D9)</f>
-        <v>44202953560</v>
+        <v>43222447020</v>
       </c>
       <c r="G9" s="9">
         <f>(E9/D9)*100</f>
-        <v>133.6345966693778</v>
+        <v>132.88851661479904</v>
       </c>
       <c r="H9">
-        <v>37866</v>
+        <v>37865</v>
       </c>
       <c r="I9" s="21">
         <f>(W9+Z9+AC9)</f>
-        <v>37877.167330677294</v>
+        <v>37878.768924302785</v>
       </c>
       <c r="J9">
-        <v>128.82071713147411</v>
+        <v>128.4581673306773</v>
       </c>
       <c r="K9" s="21">
-        <v>11.48605577689243</v>
-      </c>
-      <c r="L9" s="21">
+        <v>11.908366533864539</v>
+      </c>
+      <c r="L9" s="8">
         <f>J9+K9</f>
-        <v>140.30677290836655</v>
+        <v>140.36653386454185</v>
       </c>
       <c r="M9">
-        <v>10.366533864541831</v>
+        <v>10.314741035856571</v>
       </c>
       <c r="N9" s="21">
-        <v>0.75697211155378485</v>
-      </c>
-      <c r="O9" s="10">
+        <v>0.81673306772908372</v>
+      </c>
+      <c r="O9" s="23">
         <f>(AC9+AF9)/C9</f>
-        <v>10.553784860557769</v>
+        <v>10.490039840637451</v>
       </c>
       <c r="P9">
-        <v>0.16733067729083659</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="Q9" s="21">
         <v>1.9920318725099601E-2</v>
       </c>
       <c r="R9" s="21">
         <f>AF9/C9</f>
-        <v>0.18725099601593626</v>
+        <v>0.1752988047808765</v>
       </c>
       <c r="S9">
-        <v>128.50597609561751</v>
+        <v>128.00398406374501</v>
       </c>
       <c r="T9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="U9" s="21">
-        <v>34.661354581673308</v>
+        <v>33.466135458167329</v>
       </c>
       <c r="V9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="W9" s="21">
-        <v>58.167330677290842</v>
+        <v>57.768924302788847</v>
       </c>
       <c r="X9">
-        <v>32334</v>
+        <v>32243</v>
       </c>
       <c r="Y9">
-        <v>2883</v>
+        <v>2989</v>
       </c>
       <c r="Z9">
-        <v>35217</v>
+        <v>35232</v>
       </c>
       <c r="AA9">
-        <v>2224</v>
+        <v>2208</v>
       </c>
       <c r="AB9">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="AC9">
-        <v>2602</v>
+        <v>2589</v>
       </c>
       <c r="AD9">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AE9">
         <v>5</v>
       </c>
-      <c r="AF9" s="9">
-        <v>47</v>
+      <c r="AF9" s="23">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1731,61 +1732,61 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F10">
         <f>(E10-D10)</f>
-        <v>43222447020</v>
-      </c>
-      <c r="G10" s="9">
+        <v>39608412840</v>
+      </c>
+      <c r="G10" s="23">
         <f>(E10/D10)*100</f>
-        <v>132.88851661479904</v>
+        <v>130.13855146080436</v>
       </c>
       <c r="H10">
-        <v>37865</v>
+        <v>37850</v>
       </c>
       <c r="I10">
         <f>(W10+Z10+AC10)</f>
-        <v>37878.768924302785</v>
+        <v>37865.768924302785</v>
       </c>
       <c r="J10">
-        <v>128.4581673306773</v>
+        <v>128.6414342629482</v>
       </c>
       <c r="K10" s="21">
-        <v>11.908366533864539</v>
-      </c>
-      <c r="L10" s="8">
+        <v>11.66135458167331</v>
+      </c>
+      <c r="L10" s="23">
         <f>J10+K10</f>
-        <v>140.36653386454185</v>
+        <v>140.30278884462152</v>
       </c>
       <c r="M10">
-        <v>10.314741035856571</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="N10" s="21">
-        <v>0.81673306772908372</v>
+        <v>0.83266932270916338</v>
       </c>
       <c r="O10" s="21">
         <f>(AC10+AF10)/C10</f>
-        <v>10.490039840637451</v>
+        <v>10.49402390438247</v>
       </c>
       <c r="P10" s="21">
-        <v>0.15537848605577689</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="Q10">
-        <v>1.9920318725099601E-2</v>
+        <v>1.5936254980079681E-2</v>
       </c>
       <c r="R10" s="21">
         <f>AF10/C10</f>
-        <v>0.1752988047808765</v>
+        <v>0.16733067729083664</v>
       </c>
       <c r="S10">
-        <v>128.00398406374501</v>
+        <v>128.23904382470121</v>
       </c>
       <c r="T10" t="s">
-        <v>48</v>
-      </c>
-      <c r="U10" s="21">
-        <v>33.466135458167329</v>
+        <v>76</v>
+      </c>
+      <c r="U10" s="10">
+        <v>29.482071713147409</v>
       </c>
       <c r="V10" t="s">
         <v>46</v>
@@ -1794,36 +1795,36 @@
         <v>57.768924302788847</v>
       </c>
       <c r="X10">
-        <v>32243</v>
+        <v>32289</v>
       </c>
       <c r="Y10">
-        <v>2989</v>
+        <v>2927</v>
       </c>
       <c r="Z10">
-        <v>35232</v>
+        <v>35216</v>
       </c>
       <c r="AA10">
-        <v>2208</v>
+        <v>2215</v>
       </c>
       <c r="AB10">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AC10" s="21">
-        <v>2589</v>
+        <v>2592</v>
       </c>
       <c r="AD10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF10" s="21">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" s="21">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1831,103 +1832,103 @@
       <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>35</v>
+      <c r="D11" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F11">
         <f>(E11-D11)</f>
-        <v>42296120080</v>
+        <v>39434570980</v>
       </c>
       <c r="G11">
         <f>(E11/D11)*100</f>
-        <v>132.16461892837125</v>
+        <v>130.12629804236141</v>
       </c>
       <c r="H11">
-        <v>37880</v>
+        <v>37684</v>
       </c>
       <c r="I11" s="21">
         <f>(W11+Z11+AC11)</f>
-        <v>37896.167330677294</v>
+        <v>37700.768924302785</v>
       </c>
       <c r="J11">
-        <v>128.53784860557769</v>
+        <v>128.29880478087651</v>
       </c>
       <c r="K11" s="21">
-        <v>11.89243027888446</v>
-      </c>
-      <c r="L11" s="8">
+        <v>11.342629482071709</v>
+      </c>
+      <c r="L11" s="23">
         <f>J11+K11</f>
-        <v>140.43027888446215</v>
+        <v>139.64143426294822</v>
       </c>
       <c r="M11">
-        <v>10.31872509960159</v>
+        <v>10.33067729083665</v>
       </c>
       <c r="N11" s="21">
-        <v>0.81673306772908372</v>
+        <v>0.8605577689243028</v>
       </c>
       <c r="O11" s="21">
         <f>(AC11+AF11)/C11</f>
-        <v>10.48605577689243</v>
+        <v>10.49402390438247</v>
       </c>
       <c r="P11">
-        <v>0.14342629482071709</v>
+        <v>0.14741035856573709</v>
       </c>
       <c r="Q11" s="21">
-        <v>2.3904382470119521E-2</v>
+        <v>1.5936254980079681E-2</v>
       </c>
       <c r="R11" s="21">
         <f>AF11/C11</f>
-        <v>0.16733067729083664</v>
+        <v>0.16334661354581673</v>
       </c>
       <c r="S11">
-        <v>128.09561752988051</v>
+        <v>127.96812749003981</v>
       </c>
       <c r="T11" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="U11" s="21">
-        <v>33.466135458167329</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="V11" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="W11" s="21">
-        <v>58.167330677290842</v>
+        <v>57.768924302788847</v>
       </c>
       <c r="X11">
-        <v>32263</v>
+        <v>32203</v>
       </c>
       <c r="Y11">
-        <v>2985</v>
+        <v>2847</v>
       </c>
       <c r="Z11">
-        <v>35248</v>
+        <v>35050</v>
       </c>
       <c r="AA11">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="AB11">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="AC11">
-        <v>2590</v>
+        <v>2593</v>
       </c>
       <c r="AD11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF11" s="21">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" s="21">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1935,103 +1936,103 @@
       <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F12">
         <f>(E12-D12)</f>
-        <v>40406397600</v>
+        <v>22537887980</v>
       </c>
       <c r="G12">
         <f>(E12/D12)*100</f>
-        <v>130.74574834221812</v>
+        <v>117.14936923746409</v>
       </c>
       <c r="H12">
-        <v>37866</v>
+        <v>37811</v>
       </c>
       <c r="I12" s="21">
         <f>(W12+Z12+AC12)</f>
-        <v>37876.768924302785</v>
+        <v>37829.792828685262</v>
       </c>
       <c r="J12">
-        <v>128.45019920318731</v>
+        <v>128.53386454183271</v>
       </c>
       <c r="K12" s="21">
-        <v>11.856573705179279</v>
+        <v>11.64541832669323</v>
       </c>
       <c r="L12" s="21">
         <f>J12+K12</f>
-        <v>140.30677290836658</v>
+        <v>140.17928286852595</v>
       </c>
       <c r="M12">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0.76494023904382469</v>
-      </c>
-      <c r="O12" s="10">
+        <v>10.33067729083665</v>
+      </c>
+      <c r="N12" s="23">
+        <v>0.7450199203187251</v>
+      </c>
+      <c r="O12" s="23">
         <f>(AC12+AF12)/C12</f>
-        <v>10.553784860557769</v>
+        <v>10.46215139442231</v>
       </c>
       <c r="P12" s="21">
-        <v>0.17928286852589639</v>
+        <v>0.1235059760956175</v>
       </c>
       <c r="Q12">
         <v>7.9681274900398405E-3</v>
       </c>
       <c r="R12" s="21">
         <f>AF12/C12</f>
-        <v>0.18725099601593626</v>
+        <v>0.13147410358565736</v>
       </c>
       <c r="S12">
-        <v>128.10756972111551</v>
+        <v>128.35059760956179</v>
       </c>
       <c r="T12" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="U12" s="21">
-        <v>32.669322709163353</v>
+        <v>39.04382470119522</v>
       </c>
       <c r="V12" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="W12">
-        <v>57.768924302788847</v>
+        <v>51.792828685258961</v>
       </c>
       <c r="X12">
-        <v>32241</v>
+        <v>32262</v>
       </c>
       <c r="Y12">
-        <v>2976</v>
+        <v>2923</v>
       </c>
       <c r="Z12">
-        <v>35217</v>
+        <v>35185</v>
       </c>
       <c r="AA12">
-        <v>2222</v>
+        <v>2274</v>
       </c>
       <c r="AB12">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AC12" s="21">
-        <v>2602</v>
+        <v>2593</v>
       </c>
       <c r="AD12">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AE12">
         <v>2</v>
       </c>
-      <c r="AF12" s="9">
-        <v>47</v>
+      <c r="AF12" s="23">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A13" s="21">
-        <v>26</v>
+      <c r="A13" s="15">
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -2039,103 +2040,103 @@
       <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <f>(E13-D13)</f>
-        <v>39992577160</v>
-      </c>
-      <c r="G13" s="21">
+        <v>44542337720</v>
+      </c>
+      <c r="G13" s="9">
         <f>(E13/D13)*100</f>
-        <v>130.43086703968137</v>
+        <v>133.8928384477712</v>
       </c>
       <c r="H13">
-        <v>37861</v>
+        <v>37897</v>
       </c>
       <c r="I13">
         <f>(W13+Z13+AC13)</f>
-        <v>37870.183266932268</v>
+        <v>37902.972111553783</v>
       </c>
       <c r="J13">
-        <v>128.97211155378491</v>
+        <v>128.53784860557769</v>
       </c>
       <c r="K13" s="21">
-        <v>11.314741035856571</v>
-      </c>
-      <c r="L13" s="21">
+        <v>11.89243027888446</v>
+      </c>
+      <c r="L13" s="8">
         <f>J13+K13</f>
-        <v>140.28685258964148</v>
+        <v>140.43027888446215</v>
       </c>
       <c r="M13">
-        <v>10.37450199203187</v>
+        <v>10.350597609561749</v>
       </c>
       <c r="N13" s="21">
-        <v>0.8366533864541833</v>
+        <v>0.78884462151394419</v>
       </c>
       <c r="O13" s="10">
         <f>(AC13+AF13)/C13</f>
         <v>10.553784860557769</v>
       </c>
-      <c r="P13" s="21">
-        <v>0.17131474103585659</v>
+      <c r="P13" s="24">
+        <v>0.19920318725099601</v>
       </c>
       <c r="Q13">
-        <v>7.9681274900398405E-3</v>
-      </c>
-      <c r="R13" s="21">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="R13" s="24">
         <f>AF13/C13</f>
-        <v>0.17928286852589642</v>
+        <v>0.20318725099601595</v>
       </c>
       <c r="S13">
-        <v>128.58964143426289</v>
+        <v>128.0637450199203</v>
       </c>
       <c r="T13" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="U13" s="21">
-        <v>34.262948207171313</v>
+        <v>33.466135458167329</v>
       </c>
       <c r="V13" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="W13" s="21">
-        <v>54.183266932270911</v>
+        <v>56.972111553784863</v>
       </c>
       <c r="X13">
-        <v>32372</v>
+        <v>32263</v>
       </c>
       <c r="Y13">
-        <v>2840</v>
+        <v>2985</v>
       </c>
       <c r="Z13">
-        <v>35212</v>
+        <v>35248</v>
       </c>
       <c r="AA13">
-        <v>2214</v>
+        <v>2196</v>
       </c>
       <c r="AB13">
-        <v>210</v>
-      </c>
-      <c r="AC13" s="21">
-        <v>2604</v>
+        <v>198</v>
+      </c>
+      <c r="AC13" s="14">
+        <v>2598</v>
       </c>
       <c r="AD13">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AE13">
-        <v>2</v>
-      </c>
-      <c r="AF13" s="21">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="AF13" s="24">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -2147,99 +2148,99 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F14">
         <f>(E14-D14)</f>
-        <v>39795784920</v>
+        <v>25868776920</v>
       </c>
       <c r="G14" s="21">
         <f>(E14/D14)*100</f>
-        <v>130.28112528970809</v>
+        <v>119.68388553161444</v>
       </c>
       <c r="H14">
-        <v>37906</v>
+        <v>37823</v>
       </c>
       <c r="I14" s="21">
         <f>(W14+Z14+AC14)</f>
-        <v>37917.964143426296</v>
+        <v>37841.394422310754</v>
       </c>
       <c r="J14">
-        <v>128.71713147410361</v>
+        <v>128.3545816733068</v>
       </c>
       <c r="K14" s="21">
-        <v>11.812749003984059</v>
-      </c>
-      <c r="L14" s="10">
+        <v>11.908366533864539</v>
+      </c>
+      <c r="L14" s="23">
         <f>J14+K14</f>
-        <v>140.52988047808768</v>
+        <v>140.26294820717135</v>
       </c>
       <c r="M14">
-        <v>10.30278884462151</v>
+        <v>10.29482071713147</v>
       </c>
       <c r="N14" s="21">
-        <v>0.79681274900398402</v>
+        <v>0.70517928286852594</v>
       </c>
       <c r="O14" s="21">
         <f>(AC14+AF14)/C14</f>
-        <v>10.490039840637451</v>
+        <v>10.426294820717132</v>
       </c>
       <c r="P14">
-        <v>0.18326693227091631</v>
+        <v>0.11155378486055779</v>
       </c>
       <c r="Q14" s="21">
-        <v>3.9840637450199202E-3</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="R14" s="21">
         <f>AF14/C14</f>
-        <v>0.18725099601593626</v>
+        <v>0.13147410358565736</v>
       </c>
       <c r="S14">
-        <v>128.13545816733071</v>
+        <v>128.11553784860561</v>
       </c>
       <c r="T14" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="U14">
-        <v>34.661354581673308</v>
+        <v>42.629482071713149</v>
       </c>
       <c r="V14" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="W14" s="21">
-        <v>58.964143426294832</v>
+        <v>51.394422310756973</v>
       </c>
       <c r="X14">
-        <v>32308</v>
+        <v>32217</v>
       </c>
       <c r="Y14">
-        <v>2965</v>
+        <v>2989</v>
       </c>
       <c r="Z14">
-        <v>35273</v>
+        <v>35206</v>
       </c>
       <c r="AA14">
-        <v>2198</v>
+        <v>2275</v>
       </c>
       <c r="AB14">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="AC14" s="21">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="AD14">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AE14">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="9">
-        <v>47</v>
+        <v>5</v>
+      </c>
+      <c r="AF14" s="23">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="21">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -2248,64 +2249,64 @@
         <v>25</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F15">
         <f>(E15-D15)</f>
-        <v>39608412840</v>
+        <v>30283207180</v>
       </c>
       <c r="G15" s="21">
         <f>(E15/D15)*100</f>
-        <v>130.13855146080436</v>
+        <v>123.13505390095303</v>
       </c>
       <c r="H15">
-        <v>37850</v>
+        <v>37644</v>
       </c>
       <c r="I15">
         <f>(W15+Z15+AC15)</f>
-        <v>37865.768924302785</v>
+        <v>37662.768924302785</v>
       </c>
       <c r="J15">
-        <v>128.6414342629482</v>
-      </c>
-      <c r="K15" s="21">
-        <v>11.66135458167331</v>
+        <v>127.6294820717131</v>
+      </c>
+      <c r="K15" s="24">
+        <v>11.812749003984059</v>
       </c>
       <c r="L15" s="21">
         <f>J15+K15</f>
-        <v>140.30278884462152</v>
+        <v>139.44223107569715</v>
       </c>
       <c r="M15">
-        <v>10.32669322709163</v>
+        <v>10.378486055776889</v>
       </c>
       <c r="N15" s="21">
-        <v>0.83266932270916338</v>
+        <v>0.78087649402390436</v>
       </c>
       <c r="O15" s="21">
         <f>(AC15+AF15)/C15</f>
-        <v>10.49402390438247</v>
+        <v>10.533864541832669</v>
       </c>
       <c r="P15">
         <v>0.151394422310757</v>
       </c>
       <c r="Q15">
-        <v>1.5936254980079681E-2</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="R15" s="21">
         <f>AF15/C15</f>
-        <v>0.16733067729083664</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="S15">
-        <v>128.23904382470121</v>
+        <v>127.593625498008</v>
       </c>
       <c r="T15" t="s">
-        <v>76</v>
-      </c>
-      <c r="U15" s="10">
-        <v>29.482071713147409</v>
+        <v>51</v>
+      </c>
+      <c r="U15" s="23">
+        <v>34.661354581673308</v>
       </c>
       <c r="V15" t="s">
         <v>46</v>
@@ -2314,36 +2315,36 @@
         <v>57.768924302788847</v>
       </c>
       <c r="X15">
-        <v>32289</v>
+        <v>32035</v>
       </c>
       <c r="Y15">
-        <v>2927</v>
+        <v>2965</v>
       </c>
       <c r="Z15">
-        <v>35216</v>
+        <v>35000</v>
       </c>
       <c r="AA15">
-        <v>2215</v>
+        <v>2253</v>
       </c>
       <c r="AB15" s="21">
-        <v>209</v>
-      </c>
-      <c r="AC15" s="21">
-        <v>2592</v>
+        <v>196</v>
+      </c>
+      <c r="AC15" s="24">
+        <v>2605</v>
       </c>
       <c r="AD15">
         <v>38</v>
       </c>
       <c r="AE15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="21">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" s="21">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -2352,102 +2353,102 @@
         <v>25</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F16">
         <f>(E16-D16)</f>
-        <v>39434570980</v>
+        <v>29686892100</v>
       </c>
       <c r="G16" s="21">
         <f>(E16/D16)*100</f>
-        <v>130.12629804236141</v>
+        <v>122.58913854694097</v>
       </c>
       <c r="H16">
-        <v>37684</v>
+        <v>37813</v>
       </c>
       <c r="I16">
         <f>(W16+Z16+AC16)</f>
-        <v>37700.768924302785</v>
+        <v>37837.362549800797</v>
       </c>
       <c r="J16">
-        <v>128.29880478087651</v>
+        <v>128.42629482071709</v>
       </c>
       <c r="K16" s="21">
-        <v>11.342629482071709</v>
+        <v>11.7609561752988</v>
       </c>
       <c r="L16" s="21">
         <f>J16+K16</f>
-        <v>139.64143426294822</v>
+        <v>140.18725099601588</v>
       </c>
       <c r="M16">
-        <v>10.33067729083665</v>
+        <v>10.322709163346611</v>
       </c>
       <c r="N16" s="21">
-        <v>0.8605577689243028</v>
+        <v>0.82868525896414347</v>
       </c>
       <c r="O16" s="21">
         <f>(AC16+AF16)/C16</f>
-        <v>10.49402390438247</v>
+        <v>10.46215139442231</v>
       </c>
       <c r="P16">
-        <v>0.14741035856573709</v>
+        <v>0.12749003984063739</v>
       </c>
       <c r="Q16">
-        <v>1.5936254980079681E-2</v>
+        <v>1.1952191235059761E-2</v>
       </c>
       <c r="R16" s="21">
         <f>AF16/C16</f>
-        <v>0.16334661354581673</v>
+        <v>0.1394422310756972</v>
       </c>
       <c r="S16">
-        <v>127.96812749003981</v>
+        <v>128.14741035856571</v>
       </c>
       <c r="T16" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="U16">
-        <v>32.270916334661351</v>
+        <v>32.669322709163353</v>
       </c>
       <c r="V16" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="W16">
-        <v>57.768924302788847</v>
+        <v>59.362549800796813</v>
       </c>
       <c r="X16">
-        <v>32203</v>
+        <v>32235</v>
       </c>
       <c r="Y16">
-        <v>2847</v>
+        <v>2952</v>
       </c>
       <c r="Z16">
-        <v>35050</v>
+        <v>35187</v>
       </c>
       <c r="AA16">
-        <v>2213</v>
+        <v>2243</v>
       </c>
       <c r="AB16">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AC16" s="21">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="AD16">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AE16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF16" s="21">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="21">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -2455,103 +2456,103 @@
       <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>35</v>
+      <c r="D17" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="F17">
         <f>(E17-D17)</f>
-        <v>39441023080</v>
+        <v>26390302240</v>
       </c>
       <c r="G17" s="21">
         <f>(E17/D17)*100</f>
-        <v>129.99342434043174</v>
+        <v>120.08072086451268</v>
       </c>
       <c r="H17">
-        <v>37924</v>
+        <v>37808</v>
       </c>
       <c r="I17">
         <f>(W17+Z17+AC17)</f>
-        <v>37936.167330677294</v>
+        <v>37830.964143426296</v>
       </c>
       <c r="J17">
-        <v>129.04780876494021</v>
+        <v>128.36254980079681</v>
       </c>
       <c r="K17" s="21">
-        <v>11.533864541832671</v>
-      </c>
-      <c r="L17" s="29">
+        <v>11.7808764940239</v>
+      </c>
+      <c r="L17" s="23">
         <f>J17+K17</f>
-        <v>140.58167330677287</v>
+        <v>140.1434262948207</v>
       </c>
       <c r="M17">
-        <v>10.32669322709163</v>
+        <v>10.342629482071709</v>
       </c>
       <c r="N17" s="21">
         <v>0.82868525896414347</v>
       </c>
       <c r="O17" s="21">
         <f>(AC17+AF17)/C17</f>
-        <v>10.509960159362549</v>
+        <v>10.48605577689243</v>
       </c>
       <c r="P17">
-        <v>0.17928286852589639</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="Q17">
-        <v>3.9840637450199202E-3</v>
+        <v>0</v>
       </c>
       <c r="R17" s="21">
         <f>AF17/C17</f>
-        <v>0.18326693227091634</v>
+        <v>0.14342629482071714</v>
       </c>
       <c r="S17">
-        <v>128.46215139442231</v>
+        <v>128.13944223107569</v>
       </c>
       <c r="T17" t="s">
-        <v>37</v>
-      </c>
-      <c r="U17" s="21">
-        <v>32.270916334661351</v>
+        <v>31</v>
+      </c>
+      <c r="U17" s="8">
+        <v>31.075697211155379</v>
       </c>
       <c r="V17" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="W17" s="21">
-        <v>58.167330677290842</v>
+        <v>58.964143426294832</v>
       </c>
       <c r="X17">
-        <v>32391</v>
+        <v>32219</v>
       </c>
       <c r="Y17">
-        <v>2895</v>
+        <v>2957</v>
       </c>
       <c r="Z17">
-        <v>35286</v>
+        <v>35176</v>
       </c>
       <c r="AA17">
-        <v>2200</v>
+        <v>2244</v>
       </c>
       <c r="AB17" s="21">
         <v>208</v>
       </c>
       <c r="AC17" s="21">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="AD17">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AE17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="21">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="21">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -2559,103 +2560,103 @@
       <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>38</v>
+      <c r="D18" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F18">
         <f>(E18-D18)</f>
-        <v>39156912800</v>
+        <v>34633604380</v>
       </c>
       <c r="G18" s="21">
         <f>(E18/D18)*100</f>
-        <v>129.89647856461158</v>
+        <v>126.3531556312613</v>
       </c>
       <c r="H18">
-        <v>37755</v>
+        <v>37851</v>
       </c>
       <c r="I18">
         <f>(W18+Z18+AC18)</f>
-        <v>37775.541832669325</v>
+        <v>37867.370517928284</v>
       </c>
       <c r="J18">
-        <v>128.1434262948207</v>
+        <v>128.83266932270919</v>
       </c>
       <c r="K18">
-        <v>11.812749003984059</v>
+        <v>11.474103585657369</v>
       </c>
       <c r="L18" s="21">
         <f>J18+K18</f>
-        <v>139.95617529880477</v>
+        <v>140.30677290836655</v>
       </c>
       <c r="M18">
-        <v>10.28685258964143</v>
-      </c>
-      <c r="N18" s="8">
-        <v>0.86852589641434264</v>
+        <v>10.33067729083665</v>
+      </c>
+      <c r="N18" s="23">
+        <v>0.8605577689243028</v>
       </c>
       <c r="O18" s="21">
         <f>(AC18+AF18)/C18</f>
-        <v>10.46215139442231</v>
+        <v>10.49402390438247</v>
       </c>
       <c r="P18" s="21">
-        <v>0.17131474103585659</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="Q18">
         <v>3.9840637450199202E-3</v>
       </c>
       <c r="R18" s="21">
         <f>AF18/C18</f>
-        <v>0.1752988047808765</v>
+        <v>0.16334661354581673</v>
       </c>
       <c r="S18">
-        <v>127.5816733067729</v>
+        <v>128.41035856573711</v>
       </c>
       <c r="T18" t="s">
+        <v>31</v>
+      </c>
+      <c r="U18" s="8">
+        <v>31.075697211155379</v>
+      </c>
+      <c r="V18" t="s">
+        <v>52</v>
+      </c>
+      <c r="W18" s="23">
+        <v>57.370517928286858</v>
+      </c>
+      <c r="X18">
+        <v>32337</v>
+      </c>
+      <c r="Y18">
+        <v>2880</v>
+      </c>
+      <c r="Z18">
+        <v>35217</v>
+      </c>
+      <c r="AA18">
+        <v>2213</v>
+      </c>
+      <c r="AB18">
+        <v>216</v>
+      </c>
+      <c r="AC18" s="21">
+        <v>2593</v>
+      </c>
+      <c r="AD18">
         <v>40</v>
-      </c>
-      <c r="U18" s="10">
-        <v>29.083665338645421</v>
-      </c>
-      <c r="V18" t="s">
-        <v>41</v>
-      </c>
-      <c r="W18" s="29">
-        <v>64.541832669322702</v>
-      </c>
-      <c r="X18">
-        <v>32164</v>
-      </c>
-      <c r="Y18">
-        <v>2965</v>
-      </c>
-      <c r="Z18">
-        <v>35129</v>
-      </c>
-      <c r="AA18">
-        <v>2188</v>
-      </c>
-      <c r="AB18">
-        <v>218</v>
-      </c>
-      <c r="AC18" s="21">
-        <v>2582</v>
-      </c>
-      <c r="AD18">
-        <v>43</v>
       </c>
       <c r="AE18">
         <v>1</v>
       </c>
       <c r="AF18" s="21">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A19" s="15">
-        <v>27</v>
+      <c r="A19" s="23">
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -2663,103 +2664,103 @@
       <c r="C19" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F19">
         <f>(E19-D19)</f>
-        <v>39011994440</v>
+        <v>39992577160</v>
       </c>
       <c r="G19" s="21">
         <f>(E19/D19)*100</f>
-        <v>129.68472901875947</v>
+        <v>130.43086703968137</v>
       </c>
       <c r="H19">
-        <v>37873</v>
+        <v>37861</v>
       </c>
       <c r="I19" s="21">
         <f>(W19+Z19+AC19)</f>
-        <v>37880.58167330677</v>
+        <v>37870.183266932268</v>
       </c>
       <c r="J19">
-        <v>128.85258964143429</v>
-      </c>
-      <c r="K19" s="8">
-        <v>11.466135458167329</v>
+        <v>128.97211155378491</v>
+      </c>
+      <c r="K19" s="23">
+        <v>11.314741035856571</v>
       </c>
       <c r="L19" s="21">
         <f>J19+K19</f>
-        <v>140.31872509960164</v>
+        <v>140.28685258964148</v>
       </c>
       <c r="M19">
-        <v>10.38247011952191</v>
+        <v>10.37450199203187</v>
       </c>
       <c r="N19" s="21">
-        <v>0.78087649402390436</v>
-      </c>
-      <c r="O19" s="29">
+        <v>0.8366533864541833</v>
+      </c>
+      <c r="O19" s="10">
         <f>(AC19+AF19)/C19</f>
-        <v>10.569721115537849</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P19">
-        <v>0.18326693227091631</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="Q19" s="21">
-        <v>3.9840637450199202E-3</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="R19" s="21">
         <f>AF19/C19</f>
-        <v>0.18725099601593626</v>
+        <v>0.17928286852589642</v>
       </c>
       <c r="S19">
-        <v>128.4980079681275</v>
+        <v>128.58964143426289</v>
       </c>
       <c r="T19" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="U19" s="21">
-        <v>33.466135458167329</v>
+        <v>34.262948207171313</v>
       </c>
       <c r="V19" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="W19" s="21">
-        <v>54.581673306772913</v>
+        <v>54.183266932270911</v>
       </c>
       <c r="X19">
-        <v>32342</v>
+        <v>32372</v>
       </c>
       <c r="Y19">
-        <v>2878</v>
+        <v>2840</v>
       </c>
       <c r="Z19">
-        <v>35220</v>
+        <v>35212</v>
       </c>
       <c r="AA19">
-        <v>2222</v>
+        <v>2214</v>
       </c>
       <c r="AB19" s="21">
-        <v>196</v>
-      </c>
-      <c r="AC19" s="8">
-        <v>2606</v>
+        <v>210</v>
+      </c>
+      <c r="AC19" s="23">
+        <v>2604</v>
       </c>
       <c r="AD19">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AE19">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="9">
-        <v>47</v>
+        <v>2</v>
+      </c>
+      <c r="AF19" s="23">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="15">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -2767,103 +2768,103 @@
       <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>61</v>
+      <c r="D20" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F20">
         <f>(E20-D20)</f>
-        <v>38708700340</v>
+        <v>39011994440</v>
       </c>
       <c r="G20" s="21">
         <f>(E20/D20)*100</f>
-        <v>129.57176442636413</v>
+        <v>129.68472901875947</v>
       </c>
       <c r="H20">
-        <v>37735</v>
+        <v>37873</v>
       </c>
       <c r="I20" s="21">
         <f>(W20+Z20+AC20)</f>
-        <v>37742.378486055779</v>
+        <v>37880.58167330677</v>
       </c>
       <c r="J20">
-        <v>128.34661354581669</v>
-      </c>
-      <c r="K20" s="21">
-        <v>11.509960159362549</v>
+        <v>128.85258964143429</v>
+      </c>
+      <c r="K20" s="8">
+        <v>11.466135458167329</v>
       </c>
       <c r="L20" s="21">
         <f>J20+K20</f>
-        <v>139.85657370517924</v>
+        <v>140.31872509960164</v>
       </c>
       <c r="M20">
-        <v>10.290836653386449</v>
+        <v>10.38247011952191</v>
       </c>
       <c r="N20" s="21">
-        <v>0.73705179282868527</v>
-      </c>
-      <c r="O20" s="21">
+        <v>0.78087649402390436</v>
+      </c>
+      <c r="O20" s="24">
         <f>(AC20+AF20)/C20</f>
-        <v>10.482071713147411</v>
-      </c>
-      <c r="P20" s="10">
-        <v>0.18725099601593631</v>
+        <v>10.569721115537849</v>
+      </c>
+      <c r="P20" s="23">
+        <v>0.18326693227091631</v>
       </c>
       <c r="Q20" s="21">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="R20" s="10">
+      <c r="R20" s="23">
         <f>AF20/C20</f>
-        <v>0.19123505976095617</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S20">
-        <v>127.9402390438247</v>
+        <v>128.4980079681275</v>
       </c>
       <c r="T20" t="s">
-        <v>31</v>
-      </c>
-      <c r="U20" s="8">
-        <v>31.075697211155379</v>
+        <v>48</v>
+      </c>
+      <c r="U20" s="23">
+        <v>33.466135458167329</v>
       </c>
       <c r="V20" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="W20" s="21">
-        <v>55.378486055776889</v>
+        <v>54.581673306772913</v>
       </c>
       <c r="X20">
-        <v>32215</v>
+        <v>32342</v>
       </c>
       <c r="Y20">
-        <v>2889</v>
+        <v>2878</v>
       </c>
       <c r="Z20">
-        <v>35104</v>
+        <v>35220</v>
       </c>
       <c r="AA20">
-        <v>2206</v>
+        <v>2222</v>
       </c>
       <c r="AB20" s="21">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="AC20" s="8">
-        <v>2583</v>
+        <v>2606</v>
       </c>
       <c r="AD20">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AE20">
         <v>1</v>
       </c>
-      <c r="AF20" s="8">
-        <v>48</v>
+      <c r="AF20" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" s="21">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -2871,103 +2872,103 @@
       <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="F21">
         <f>(E21-D21)</f>
-        <v>38695690640</v>
+        <v>36266941760</v>
       </c>
       <c r="G21" s="21">
         <f>(E21/D21)*100</f>
-        <v>129.44404938355024</v>
+        <v>127.59598308003686</v>
       </c>
       <c r="H21">
-        <v>37866</v>
+        <v>37874</v>
       </c>
       <c r="I21" s="21">
         <f>(W21+Z21+AC21)</f>
-        <v>37875.972111553783</v>
+        <v>37880.792828685262</v>
       </c>
       <c r="J21">
-        <v>129.36653386454179</v>
+        <v>128.796812749004</v>
       </c>
       <c r="K21" s="21">
-        <v>10.9402390438247</v>
-      </c>
-      <c r="L21" s="21">
+        <v>11.55776892430279</v>
+      </c>
+      <c r="L21" s="8">
         <f>J21+K21</f>
-        <v>140.3067729083665</v>
+        <v>140.3545816733068</v>
       </c>
       <c r="M21">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="N21" s="16">
-        <v>0.79282868525896411</v>
-      </c>
-      <c r="O21" s="10">
+        <v>10.358565737051791</v>
+      </c>
+      <c r="N21" s="23">
+        <v>0.72908366533864544</v>
+      </c>
+      <c r="O21" s="23">
         <f>(AC21+AF21)/C21</f>
-        <v>10.553784860557769</v>
+        <v>10.53784860557769</v>
       </c>
       <c r="P21">
-        <v>0.18326693227091631</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="Q21">
-        <v>3.9840637450199202E-3</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="R21" s="21">
         <f>AF21/C21</f>
-        <v>0.18725099601593626</v>
+        <v>0.17928286852589642</v>
       </c>
       <c r="S21">
-        <v>129.04382470119521</v>
+        <v>128.45418326693229</v>
       </c>
       <c r="T21" t="s">
-        <v>31</v>
-      </c>
-      <c r="U21" s="8">
-        <v>31.075697211155379</v>
+        <v>51</v>
+      </c>
+      <c r="U21" s="23">
+        <v>34.661354581673308</v>
       </c>
       <c r="V21" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="W21">
-        <v>56.972111553784863</v>
+        <v>51.792828685258961</v>
       </c>
       <c r="X21">
-        <v>32471</v>
+        <v>32328</v>
       </c>
       <c r="Y21">
-        <v>2746</v>
+        <v>2901</v>
       </c>
       <c r="Z21">
-        <v>35217</v>
+        <v>35229</v>
       </c>
       <c r="AA21">
-        <v>2215</v>
+        <v>2237</v>
       </c>
       <c r="AB21">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="AC21" s="21">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="AD21">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="9">
-        <v>47</v>
+        <v>2</v>
+      </c>
+      <c r="AF21" s="23">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" s="21">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -2979,99 +2980,99 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F22">
         <f>(E22-D22)</f>
-        <v>37463917860</v>
+        <v>35399896360</v>
       </c>
       <c r="G22" s="21">
         <f>(E22/D22)*100</f>
-        <v>128.50677761080814</v>
+        <v>126.93623706819051</v>
       </c>
       <c r="H22">
-        <v>37875</v>
+        <v>37826</v>
       </c>
       <c r="I22">
         <f>(W22+Z22+AC22)</f>
-        <v>37892.768924302785</v>
+        <v>37839.589641434264</v>
       </c>
       <c r="J22">
-        <v>128.601593625498</v>
-      </c>
-      <c r="K22" s="21">
-        <v>11.8605577689243</v>
-      </c>
-      <c r="L22" s="10">
+        <v>128.70119521912349</v>
+      </c>
+      <c r="K22" s="10">
+        <v>11.446215139442231</v>
+      </c>
+      <c r="L22" s="23">
         <f>J22+K22</f>
-        <v>140.46215139442231</v>
+        <v>140.14741035856571</v>
       </c>
       <c r="M22">
-        <v>10.27490039840638</v>
+        <v>10.39840637450199</v>
       </c>
       <c r="N22" s="21">
-        <v>0.8366533864541833</v>
-      </c>
-      <c r="O22" s="21">
+        <v>0.81673306772908372</v>
+      </c>
+      <c r="O22" s="10">
         <f>(AC22+AF22)/C22</f>
-        <v>10.434262948207172</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P22" s="21">
-        <v>0.14342629482071709</v>
+        <v>0.1394422310756972</v>
       </c>
       <c r="Q22">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="R22" s="21">
         <f>AF22/C22</f>
-        <v>0.15936254980079681</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="S22">
-        <v>128.03585657370519</v>
+        <v>128.47011952191241</v>
       </c>
       <c r="T22" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="U22">
-        <v>35.059760956175303</v>
+        <v>33.864541832669318</v>
       </c>
       <c r="V22" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="W22">
-        <v>57.768924302788847</v>
+        <v>52.589641434262937</v>
       </c>
       <c r="X22">
-        <v>32279</v>
+        <v>32304</v>
       </c>
       <c r="Y22">
-        <v>2977</v>
+        <v>2873</v>
       </c>
       <c r="Z22">
-        <v>35256</v>
+        <v>35177</v>
       </c>
       <c r="AA22">
-        <v>2209</v>
+        <v>2249</v>
       </c>
       <c r="AB22">
-        <v>210</v>
-      </c>
-      <c r="AC22" s="21">
-        <v>2579</v>
+        <v>205</v>
+      </c>
+      <c r="AC22" s="10">
+        <v>2610</v>
       </c>
       <c r="AD22">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE22">
         <v>4</v>
       </c>
       <c r="AF22" s="21">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" s="21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -3079,103 +3080,103 @@
       <c r="C23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="F23">
         <f>(E23-D23)</f>
-        <v>36266941760</v>
+        <v>35889415260</v>
       </c>
       <c r="G23" s="21">
         <f>(E23/D23)*100</f>
-        <v>127.59598308003686</v>
+        <v>127.30871830388865</v>
       </c>
       <c r="H23">
-        <v>37874</v>
+        <v>37854</v>
       </c>
       <c r="I23" s="21">
         <f>(W23+Z23+AC23)</f>
-        <v>37880.792828685262</v>
+        <v>37870.77689243028</v>
       </c>
       <c r="J23">
-        <v>128.796812749004</v>
+        <v>128.68127490039839</v>
       </c>
       <c r="K23">
-        <v>11.55776892430279</v>
+        <v>11.685258964143429</v>
       </c>
       <c r="L23" s="8">
         <f>J23+K23</f>
-        <v>140.3545816733068</v>
+        <v>140.36653386454182</v>
       </c>
       <c r="M23">
-        <v>10.358565737051791</v>
-      </c>
-      <c r="N23" s="21">
-        <v>0.72908366533864544</v>
+        <v>10.290836653386449</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0.87250996015936255</v>
       </c>
       <c r="O23" s="21">
         <f>(AC23+AF23)/C23</f>
-        <v>10.53784860557769</v>
+        <v>10.446215139442231</v>
       </c>
       <c r="P23" s="21">
-        <v>0.17131474103585659</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="Q23">
-        <v>7.9681274900398405E-3</v>
+        <v>1.1952191235059761E-2</v>
       </c>
       <c r="R23" s="21">
         <f>AF23/C23</f>
-        <v>0.17928286852589642</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="S23">
-        <v>128.45418326693229</v>
+        <v>128.17928286852589</v>
       </c>
       <c r="T23" t="s">
-        <v>51</v>
-      </c>
-      <c r="U23">
-        <v>34.661354581673308</v>
+        <v>66</v>
+      </c>
+      <c r="U23" s="8">
+        <v>31.872509960159359</v>
       </c>
       <c r="V23" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="W23" s="21">
-        <v>51.792828685258961</v>
+        <v>55.776892430278878</v>
       </c>
       <c r="X23">
-        <v>32328</v>
+        <v>32299</v>
       </c>
       <c r="Y23">
-        <v>2901</v>
+        <v>2933</v>
       </c>
       <c r="Z23">
-        <v>35229</v>
+        <v>35232</v>
       </c>
       <c r="AA23">
-        <v>2237</v>
+        <v>2208</v>
       </c>
       <c r="AB23">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="AC23" s="21">
-        <v>2600</v>
+        <v>2583</v>
       </c>
       <c r="AD23">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="AE23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF23" s="21">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A24" s="21">
-        <v>37</v>
+      <c r="A24" s="15">
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -3184,102 +3185,102 @@
         <v>25</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F24">
         <f>(E24-D24)</f>
-        <v>35971527040</v>
+        <v>38708700340</v>
       </c>
       <c r="G24">
         <f>(E24/D24)*100</f>
-        <v>127.35500223956247</v>
+        <v>129.57176442636413</v>
       </c>
       <c r="H24">
-        <v>37858</v>
+        <v>37735</v>
       </c>
       <c r="I24" s="21">
         <f>(W24+Z24+AC24)</f>
-        <v>37876.573705179282</v>
+        <v>37742.378486055779</v>
       </c>
       <c r="J24">
-        <v>128.58964143426289</v>
+        <v>128.34661354581669</v>
       </c>
       <c r="K24" s="21">
-        <v>11.768924302788839</v>
-      </c>
-      <c r="L24" s="8">
+        <v>11.509960159362549</v>
+      </c>
+      <c r="L24" s="23">
         <f>J24+K24</f>
-        <v>140.35856573705172</v>
+        <v>139.85657370517924</v>
       </c>
       <c r="M24">
-        <v>10.31872509960159</v>
+        <v>10.290836653386449</v>
       </c>
       <c r="N24" s="21">
-        <v>0.82071713147410363</v>
+        <v>0.73705179282868527</v>
       </c>
       <c r="O24" s="21">
         <f>(AC24+AF24)/C24</f>
-        <v>10.47011952191235</v>
-      </c>
-      <c r="P24" s="21">
-        <v>0.13147410358565739</v>
+        <v>10.482071713147411</v>
+      </c>
+      <c r="P24" s="10">
+        <v>0.18725099601593631</v>
       </c>
       <c r="Q24">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="R24" s="21">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="R24" s="10">
         <f>AF24/C24</f>
-        <v>0.15139442231075698</v>
+        <v>0.19123505976095617</v>
       </c>
       <c r="S24">
-        <v>128.21912350597611</v>
+        <v>127.9402390438247</v>
       </c>
       <c r="T24" t="s">
-        <v>70</v>
-      </c>
-      <c r="U24">
-        <v>35.458167330677291</v>
+        <v>31</v>
+      </c>
+      <c r="U24" s="8">
+        <v>31.075697211155379</v>
       </c>
       <c r="V24" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="W24">
-        <v>56.573705179282882</v>
+        <v>55.378486055776889</v>
       </c>
       <c r="X24">
-        <v>32276</v>
+        <v>32215</v>
       </c>
       <c r="Y24">
-        <v>2954</v>
+        <v>2889</v>
       </c>
       <c r="Z24">
-        <v>35230</v>
+        <v>35104</v>
       </c>
       <c r="AA24">
-        <v>2232</v>
+        <v>2206</v>
       </c>
       <c r="AB24">
-        <v>206</v>
-      </c>
-      <c r="AC24" s="21">
-        <v>2590</v>
+        <v>185</v>
+      </c>
+      <c r="AC24" s="8">
+        <v>2583</v>
       </c>
       <c r="AD24">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="AE24">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="21">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="AF24" s="8">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -3288,102 +3289,102 @@
         <v>25</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F25">
         <f>(E25-D25)</f>
-        <v>35889415260</v>
+        <v>39156912800</v>
       </c>
       <c r="G25">
         <f>(E25/D25)*100</f>
-        <v>127.30871830388865</v>
+        <v>129.89647856461158</v>
       </c>
       <c r="H25">
-        <v>37854</v>
+        <v>37755</v>
       </c>
       <c r="I25" s="21">
         <f>(W25+Z25+AC25)</f>
-        <v>37870.77689243028</v>
+        <v>37775.541832669325</v>
       </c>
       <c r="J25">
-        <v>128.68127490039839</v>
+        <v>128.1434262948207</v>
       </c>
       <c r="K25" s="21">
-        <v>11.685258964143429</v>
-      </c>
-      <c r="L25" s="8">
+        <v>11.812749003984059</v>
+      </c>
+      <c r="L25" s="23">
         <f>J25+K25</f>
-        <v>140.36653386454182</v>
+        <v>139.95617529880477</v>
       </c>
       <c r="M25">
-        <v>10.290836653386449</v>
-      </c>
-      <c r="N25" s="10">
-        <v>0.87250996015936255</v>
+        <v>10.28685258964143</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0.86852589641434264</v>
       </c>
       <c r="O25" s="21">
         <f>(AC25+AF25)/C25</f>
-        <v>10.446215139442231</v>
+        <v>10.46215139442231</v>
       </c>
       <c r="P25">
-        <v>0.14342629482071709</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="Q25">
-        <v>1.1952191235059761E-2</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="R25" s="21">
         <f>AF25/C25</f>
-        <v>0.15537848605577689</v>
+        <v>0.1752988047808765</v>
       </c>
       <c r="S25">
-        <v>128.17928286852589</v>
+        <v>127.5816733067729</v>
       </c>
       <c r="T25" t="s">
-        <v>66</v>
-      </c>
-      <c r="U25" s="8">
-        <v>31.872509960159359</v>
+        <v>40</v>
+      </c>
+      <c r="U25" s="10">
+        <v>29.083665338645421</v>
       </c>
       <c r="V25" t="s">
-        <v>67</v>
-      </c>
-      <c r="W25" s="21">
-        <v>55.776892430278878</v>
+        <v>41</v>
+      </c>
+      <c r="W25" s="24">
+        <v>64.541832669322702</v>
       </c>
       <c r="X25">
-        <v>32299</v>
+        <v>32164</v>
       </c>
       <c r="Y25">
-        <v>2933</v>
+        <v>2965</v>
       </c>
       <c r="Z25">
-        <v>35232</v>
+        <v>35129</v>
       </c>
       <c r="AA25">
-        <v>2208</v>
+        <v>2188</v>
       </c>
       <c r="AB25">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC25" s="21">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="AD25">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="AE25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF25">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" s="21">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -3391,103 +3392,103 @@
       <c r="C26" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>26</v>
+      <c r="D26" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F26">
         <f>(E26-D26)</f>
-        <v>35516488280</v>
+        <v>39441023080</v>
       </c>
       <c r="G26">
         <f>(E26/D26)*100</f>
-        <v>127.02495336174735</v>
+        <v>129.99342434043174</v>
       </c>
       <c r="H26">
-        <v>37835</v>
-      </c>
-      <c r="I26" s="29">
+        <v>37924</v>
+      </c>
+      <c r="I26" s="23">
         <f>(W26+Z26+AC26)</f>
-        <v>37852.370517928284</v>
+        <v>37936.167330677294</v>
       </c>
       <c r="J26">
-        <v>128.23904382470121</v>
+        <v>129.04780876494021</v>
       </c>
       <c r="K26">
-        <v>12.011952191235061</v>
-      </c>
-      <c r="L26" s="21">
+        <v>11.533864541832671</v>
+      </c>
+      <c r="L26" s="24">
         <f>J26+K26</f>
-        <v>140.25099601593627</v>
+        <v>140.58167330677287</v>
       </c>
       <c r="M26">
         <v>10.32669322709163</v>
       </c>
       <c r="N26" s="21">
-        <v>0.85657370517928288</v>
+        <v>0.82868525896414347</v>
       </c>
       <c r="O26" s="21">
         <f>(AC26+AF26)/C26</f>
-        <v>10.48605577689243</v>
+        <v>10.509960159362549</v>
       </c>
       <c r="P26" s="21">
-        <v>0.151394422310757</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="Q26">
-        <v>7.9681274900398405E-3</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="R26" s="21">
         <f>AF26/C26</f>
-        <v>0.15936254980079681</v>
+        <v>0.18326693227091634</v>
       </c>
       <c r="S26">
-        <v>127.87250996015941</v>
+        <v>128.46215139442231</v>
       </c>
       <c r="T26" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="U26" s="21">
-        <v>34.661354581673308</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="V26" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="W26">
-        <v>57.370517928286858</v>
+        <v>58.167330677290842</v>
       </c>
       <c r="X26">
-        <v>32188</v>
+        <v>32391</v>
       </c>
       <c r="Y26">
-        <v>3015</v>
+        <v>2895</v>
       </c>
       <c r="Z26">
-        <v>35203</v>
+        <v>35286</v>
       </c>
       <c r="AA26">
-        <v>2217</v>
+        <v>2200</v>
       </c>
       <c r="AB26">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AC26" s="21">
         <v>2592</v>
       </c>
       <c r="AD26">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AE26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF26" s="21">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -3495,103 +3496,103 @@
       <c r="C27" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>26</v>
+      <c r="D27" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F27">
         <f>(E27-D27)</f>
-        <v>35399896360</v>
+        <v>35359989160</v>
       </c>
       <c r="G27" s="21">
         <f>(E27/D27)*100</f>
-        <v>126.93623706819051</v>
+        <v>126.8899505319056</v>
       </c>
       <c r="H27">
-        <v>37826</v>
+        <v>37887</v>
       </c>
       <c r="I27" s="21">
         <f>(W27+Z27+AC27)</f>
-        <v>37839.589641434264</v>
+        <v>37902.77689243028</v>
       </c>
       <c r="J27">
-        <v>128.70119521912349</v>
-      </c>
-      <c r="K27" s="10">
-        <v>11.446215139442231</v>
-      </c>
-      <c r="L27" s="21">
+        <v>128.7250996015936</v>
+      </c>
+      <c r="K27" s="23">
+        <v>11.749003984063741</v>
+      </c>
+      <c r="L27" s="10">
         <f>J27+K27</f>
-        <v>140.14741035856571</v>
+        <v>140.47410358565733</v>
       </c>
       <c r="M27">
-        <v>10.39840637450199</v>
+        <v>10.31075697211155</v>
       </c>
       <c r="N27" s="21">
-        <v>0.81673306772908372</v>
-      </c>
-      <c r="O27" s="10">
+        <v>0.86454183266932272</v>
+      </c>
+      <c r="O27" s="23">
         <f>(AC27+AF27)/C27</f>
-        <v>10.553784860557769</v>
+        <v>10.47011952191235</v>
       </c>
       <c r="P27">
-        <v>0.1394422310756972</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="Q27">
-        <v>1.5936254980079681E-2</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="R27" s="21">
         <f>AF27/C27</f>
-        <v>0.15537848605577689</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="S27">
-        <v>128.47011952191241</v>
+        <v>128.207171314741</v>
       </c>
       <c r="T27" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="U27">
-        <v>33.864541832669318</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="V27" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="W27">
-        <v>52.589641434262937</v>
+        <v>55.776892430278878</v>
       </c>
       <c r="X27">
-        <v>32304</v>
+        <v>32310</v>
       </c>
       <c r="Y27">
-        <v>2873</v>
+        <v>2949</v>
       </c>
       <c r="Z27">
-        <v>35177</v>
+        <v>35259</v>
       </c>
       <c r="AA27">
-        <v>2249</v>
+        <v>2211</v>
       </c>
       <c r="AB27">
-        <v>205</v>
-      </c>
-      <c r="AC27" s="10">
-        <v>2610</v>
+        <v>217</v>
+      </c>
+      <c r="AC27" s="23">
+        <v>2588</v>
       </c>
       <c r="AD27">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AE27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF27" s="21">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -3603,99 +3604,99 @@
         <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="F28">
         <f>(E28-D28)</f>
-        <v>35359989160</v>
+        <v>33233242100</v>
       </c>
       <c r="G28">
         <f>(E28/D28)*100</f>
-        <v>126.8899505319056</v>
+        <v>125.272638858576</v>
       </c>
       <c r="H28">
-        <v>37887</v>
+        <v>37875</v>
       </c>
       <c r="I28" s="21">
         <f>(W28+Z28+AC28)</f>
-        <v>37902.77689243028</v>
+        <v>37892.378486055779</v>
       </c>
       <c r="J28">
-        <v>128.7250996015936</v>
+        <v>128.88446215139439</v>
       </c>
       <c r="K28" s="21">
-        <v>11.749003984063741</v>
-      </c>
-      <c r="L28" s="10">
+        <v>11.553784860557769</v>
+      </c>
+      <c r="L28" s="8">
         <f>J28+K28</f>
-        <v>140.47410358565733</v>
+        <v>140.43824701195217</v>
       </c>
       <c r="M28">
-        <v>10.31075697211155</v>
+        <v>10.306772908366529</v>
       </c>
       <c r="N28">
-        <v>0.86454183266932272</v>
+        <v>0.79681274900398402</v>
       </c>
       <c r="O28" s="21">
         <f>(AC28+AF28)/C28</f>
-        <v>10.47011952191235</v>
+        <v>10.458167330677291</v>
       </c>
       <c r="P28">
-        <v>0.151394422310757</v>
+        <v>0.13545816733067731</v>
       </c>
       <c r="Q28" s="21">
-        <v>7.9681274900398405E-3</v>
+        <v>1.5936254980079681E-2</v>
       </c>
       <c r="R28" s="21">
         <f>AF28/C28</f>
-        <v>0.15936254980079681</v>
+        <v>0.15139442231075698</v>
       </c>
       <c r="S28">
-        <v>128.207171314741</v>
+        <v>128.46215139442231</v>
       </c>
       <c r="T28" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="U28">
-        <v>32.270916334661351</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="V28" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="W28" s="21">
-        <v>55.776892430278878</v>
+        <v>55.378486055776889</v>
       </c>
       <c r="X28">
-        <v>32310</v>
+        <v>32350</v>
       </c>
       <c r="Y28">
-        <v>2949</v>
+        <v>2900</v>
       </c>
       <c r="Z28">
-        <v>35259</v>
+        <v>35250</v>
       </c>
       <c r="AA28">
-        <v>2211</v>
+        <v>2235</v>
       </c>
       <c r="AB28">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="AC28" s="21">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="AD28">
+        <v>34</v>
+      </c>
+      <c r="AE28">
+        <v>4</v>
+      </c>
+      <c r="AF28" s="21">
         <v>38</v>
-      </c>
-      <c r="AE28">
-        <v>2</v>
-      </c>
-      <c r="AF28" s="21">
-        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" s="21">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -3703,103 +3704,103 @@
       <c r="C29" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>26</v>
+      <c r="D29" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F29">
         <f>(E29-D29)</f>
-        <v>34633604380</v>
-      </c>
-      <c r="G29">
+        <v>48151148180</v>
+      </c>
+      <c r="G29" s="8">
         <f>(E29/D29)*100</f>
-        <v>126.3531556312613</v>
+        <v>136.6171490255812</v>
       </c>
       <c r="H29">
-        <v>37851</v>
+        <v>37914</v>
       </c>
       <c r="I29">
         <f>(W29+Z29+AC29)</f>
-        <v>37867.370517928284</v>
+        <v>37926.760956175298</v>
       </c>
       <c r="J29">
-        <v>128.83266932270919</v>
+        <v>128.90438247011949</v>
       </c>
       <c r="K29" s="21">
-        <v>11.474103585657369</v>
-      </c>
-      <c r="L29" s="21">
+        <v>11.613545816733071</v>
+      </c>
+      <c r="L29" s="10">
         <f>J29+K29</f>
-        <v>140.30677290836655</v>
+        <v>140.51792828685257</v>
       </c>
       <c r="M29">
-        <v>10.33067729083665</v>
+        <v>10.34661354581673</v>
       </c>
       <c r="N29" s="21">
-        <v>0.8605577689243028</v>
+        <v>0.82071713147410363</v>
       </c>
       <c r="O29" s="21">
         <f>(AC29+AF29)/C29</f>
-        <v>10.49402390438247</v>
+        <v>10.533864541832669</v>
       </c>
       <c r="P29" s="21">
-        <v>0.15936254980079681</v>
+        <v>0.1633466135458167</v>
       </c>
       <c r="Q29">
-        <v>3.9840637450199202E-3</v>
+        <v>2.3904382470119521E-2</v>
       </c>
       <c r="R29" s="21">
         <f>AF29/C29</f>
-        <v>0.16334661354581673</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S29">
-        <v>128.41035856573711</v>
+        <v>128.37051792828689</v>
       </c>
       <c r="T29" t="s">
-        <v>31</v>
-      </c>
-      <c r="U29" s="8">
-        <v>31.075697211155379</v>
+        <v>37</v>
+      </c>
+      <c r="U29" s="23">
+        <v>32.270916334661351</v>
       </c>
       <c r="V29" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="W29">
-        <v>57.370517928286858</v>
+        <v>59.760956175298809</v>
       </c>
       <c r="X29">
-        <v>32337</v>
+        <v>32355</v>
       </c>
       <c r="Y29">
-        <v>2880</v>
+        <v>2915</v>
       </c>
       <c r="Z29">
-        <v>35217</v>
+        <v>35270</v>
       </c>
       <c r="AA29">
-        <v>2213</v>
+        <v>2203</v>
       </c>
       <c r="AB29">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="AC29" s="21">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="AD29">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AE29">
-        <v>1</v>
-      </c>
-      <c r="AF29" s="21">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="AF29" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" s="21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -3811,91 +3812,91 @@
         <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F30">
         <f>(E30-D30)</f>
-        <v>33233242100</v>
+        <v>35971527040</v>
       </c>
       <c r="G30">
         <f>(E30/D30)*100</f>
-        <v>125.272638858576</v>
+        <v>127.35500223956247</v>
       </c>
       <c r="H30">
-        <v>37875</v>
+        <v>37858</v>
       </c>
       <c r="I30" s="21">
         <f>(W30+Z30+AC30)</f>
-        <v>37892.378486055779</v>
+        <v>37876.573705179282</v>
       </c>
       <c r="J30">
-        <v>128.88446215139439</v>
+        <v>128.58964143426289</v>
       </c>
       <c r="K30">
-        <v>11.553784860557769</v>
+        <v>11.768924302788839</v>
       </c>
       <c r="L30" s="8">
         <f>J30+K30</f>
-        <v>140.43824701195217</v>
+        <v>140.35856573705172</v>
       </c>
       <c r="M30">
-        <v>10.306772908366529</v>
+        <v>10.31872509960159</v>
       </c>
       <c r="N30" s="21">
-        <v>0.79681274900398402</v>
+        <v>0.82071713147410363</v>
       </c>
       <c r="O30" s="21">
         <f>(AC30+AF30)/C30</f>
-        <v>10.458167330677291</v>
+        <v>10.47011952191235</v>
       </c>
       <c r="P30">
-        <v>0.13545816733067731</v>
+        <v>0.13147410358565739</v>
       </c>
       <c r="Q30">
-        <v>1.5936254980079681E-2</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="R30" s="21">
         <f>AF30/C30</f>
         <v>0.15139442231075698</v>
       </c>
       <c r="S30">
-        <v>128.46215139442231</v>
+        <v>128.21912350597611</v>
       </c>
       <c r="T30" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="U30">
-        <v>34.661354581673308</v>
+        <v>35.458167330677291</v>
       </c>
       <c r="V30" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="W30">
-        <v>55.378486055776889</v>
+        <v>56.573705179282882</v>
       </c>
       <c r="X30">
-        <v>32350</v>
+        <v>32276</v>
       </c>
       <c r="Y30">
-        <v>2900</v>
+        <v>2954</v>
       </c>
       <c r="Z30">
-        <v>35250</v>
+        <v>35230</v>
       </c>
       <c r="AA30">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="AB30">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="AC30">
-        <v>2587</v>
+        <v>2590</v>
       </c>
       <c r="AD30">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AE30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF30" s="21">
         <v>38</v>
@@ -3903,7 +3904,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" s="21">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -3911,98 +3912,98 @@
       <c r="C31" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>61</v>
+      <c r="D31" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F31">
         <f>(E31-D31)</f>
-        <v>30283207180</v>
+        <v>42296120080</v>
       </c>
       <c r="G31">
         <f>(E31/D31)*100</f>
-        <v>123.13505390095303</v>
+        <v>132.16461892837125</v>
       </c>
       <c r="H31">
-        <v>37644</v>
+        <v>37880</v>
       </c>
       <c r="I31" s="21">
         <f>(W31+Z31+AC31)</f>
-        <v>37662.768924302785</v>
+        <v>37896.167330677294</v>
       </c>
       <c r="J31">
-        <v>127.6294820717131</v>
-      </c>
-      <c r="K31" s="29">
-        <v>11.812749003984059</v>
-      </c>
-      <c r="L31" s="21">
+        <v>128.53784860557769</v>
+      </c>
+      <c r="K31" s="23">
+        <v>11.89243027888446</v>
+      </c>
+      <c r="L31" s="8">
         <f>J31+K31</f>
-        <v>139.44223107569715</v>
+        <v>140.43027888446215</v>
       </c>
       <c r="M31">
-        <v>10.378486055776889</v>
+        <v>10.31872509960159</v>
       </c>
       <c r="N31" s="21">
-        <v>0.78087649402390436</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="O31" s="21">
         <f>(AC31+AF31)/C31</f>
-        <v>10.533864541832669</v>
+        <v>10.48605577689243</v>
       </c>
       <c r="P31">
-        <v>0.151394422310757</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="Q31">
-        <v>3.9840637450199202E-3</v>
+        <v>2.3904382470119521E-2</v>
       </c>
       <c r="R31" s="21">
         <f>AF31/C31</f>
-        <v>0.15537848605577689</v>
+        <v>0.16733067729083664</v>
       </c>
       <c r="S31">
-        <v>127.593625498008</v>
+        <v>128.09561752988051</v>
       </c>
       <c r="T31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="U31">
-        <v>34.661354581673308</v>
+        <v>33.466135458167329</v>
       </c>
       <c r="V31" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="W31">
-        <v>57.768924302788847</v>
+        <v>58.167330677290842</v>
       </c>
       <c r="X31">
-        <v>32035</v>
+        <v>32263</v>
       </c>
       <c r="Y31">
-        <v>2965</v>
+        <v>2985</v>
       </c>
       <c r="Z31">
-        <v>35000</v>
+        <v>35248</v>
       </c>
       <c r="AA31">
-        <v>2253</v>
+        <v>2217</v>
       </c>
       <c r="AB31">
-        <v>196</v>
-      </c>
-      <c r="AC31" s="29">
-        <v>2605</v>
+        <v>205</v>
+      </c>
+      <c r="AC31" s="23">
+        <v>2590</v>
       </c>
       <c r="AD31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF31" s="21">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
@@ -4111,7 +4112,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="21">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -4119,103 +4120,103 @@
       <c r="C33" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F33">
         <f>(E33-D33)</f>
-        <v>29686892100</v>
+        <v>38695690640</v>
       </c>
       <c r="G33">
         <f>(E33/D33)*100</f>
-        <v>122.58913854694097</v>
+        <v>129.44404938355024</v>
       </c>
       <c r="H33">
-        <v>37813</v>
+        <v>37866</v>
       </c>
       <c r="I33">
         <f>(W33+Z33+AC33)</f>
-        <v>37837.362549800797</v>
+        <v>37875.972111553783</v>
       </c>
       <c r="J33">
-        <v>128.42629482071709</v>
+        <v>129.36653386454179</v>
       </c>
       <c r="K33">
-        <v>11.7609561752988</v>
+        <v>10.9402390438247</v>
       </c>
       <c r="L33" s="21">
         <f>J33+K33</f>
-        <v>140.18725099601588</v>
+        <v>140.3067729083665</v>
       </c>
       <c r="M33">
-        <v>10.322709163346611</v>
-      </c>
-      <c r="N33" s="21">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="O33" s="21">
+        <v>10.366533864541831</v>
+      </c>
+      <c r="N33" s="16">
+        <v>0.79282868525896411</v>
+      </c>
+      <c r="O33" s="10">
         <f>(AC33+AF33)/C33</f>
-        <v>10.46215139442231</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P33" s="21">
-        <v>0.12749003984063739</v>
+        <v>0.18326693227091631</v>
       </c>
       <c r="Q33">
-        <v>1.1952191235059761E-2</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="R33" s="21">
         <f>AF33/C33</f>
-        <v>0.1394422310756972</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S33">
-        <v>128.14741035856571</v>
+        <v>129.04382470119521</v>
       </c>
       <c r="T33" t="s">
-        <v>80</v>
-      </c>
-      <c r="U33" s="21">
-        <v>32.669322709163353</v>
+        <v>31</v>
+      </c>
+      <c r="U33" s="8">
+        <v>31.075697211155379</v>
       </c>
       <c r="V33" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="W33" s="21">
-        <v>59.362549800796813</v>
+        <v>56.972111553784863</v>
       </c>
       <c r="X33">
-        <v>32235</v>
+        <v>32471</v>
       </c>
       <c r="Y33">
-        <v>2952</v>
+        <v>2746</v>
       </c>
       <c r="Z33">
-        <v>35187</v>
+        <v>35217</v>
       </c>
       <c r="AA33">
-        <v>2243</v>
+        <v>2215</v>
       </c>
       <c r="AB33">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="AC33" s="21">
-        <v>2591</v>
+        <v>2602</v>
       </c>
       <c r="AD33">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AE33">
-        <v>3</v>
-      </c>
-      <c r="AF33" s="21">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="AF33" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -4223,103 +4224,103 @@
       <c r="C34" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="F34">
         <f>(E34-D34)</f>
-        <v>26390302240</v>
-      </c>
-      <c r="G34">
+        <v>47053193320</v>
+      </c>
+      <c r="G34" s="8">
         <f>(E34/D34)*100</f>
-        <v>120.08072086451268</v>
+        <v>135.80338081201427</v>
       </c>
       <c r="H34">
-        <v>37808</v>
+        <v>37866</v>
       </c>
       <c r="I34" s="21">
         <f>(W34+Z34+AC34)</f>
-        <v>37830.964143426296</v>
+        <v>37882.346613545815</v>
       </c>
       <c r="J34">
-        <v>128.36254980079681</v>
+        <v>128.68127490039839</v>
       </c>
       <c r="K34" s="21">
-        <v>11.7808764940239</v>
+        <v>11.62549800796813</v>
       </c>
       <c r="L34" s="21">
         <f>J34+K34</f>
-        <v>140.1434262948207</v>
+        <v>140.30677290836653</v>
       </c>
       <c r="M34">
-        <v>10.342629482071709</v>
-      </c>
-      <c r="N34" s="21">
+        <v>10.366533864541831</v>
+      </c>
+      <c r="N34" s="17">
         <v>0.82868525896414347</v>
       </c>
-      <c r="O34" s="21">
+      <c r="O34" s="10">
         <f>(AC34+AF34)/C34</f>
-        <v>10.48605577689243</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P34">
-        <v>0.14342629482071709</v>
+        <v>0.16733067729083659</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="R34" s="21">
         <f>AF34/C34</f>
-        <v>0.14342629482071714</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S34">
-        <v>128.13944223107569</v>
+        <v>128.27091633466139</v>
       </c>
       <c r="T34" t="s">
-        <v>31</v>
-      </c>
-      <c r="U34" s="8">
-        <v>31.075697211155379</v>
+        <v>54</v>
+      </c>
+      <c r="U34" s="10">
+        <v>30.2788844621514</v>
       </c>
       <c r="V34" t="s">
-        <v>60</v>
-      </c>
-      <c r="W34" s="21">
-        <v>58.964143426294832</v>
+        <v>55</v>
+      </c>
+      <c r="W34" s="10">
+        <v>63.34661354581673</v>
       </c>
       <c r="X34">
-        <v>32219</v>
+        <v>32299</v>
       </c>
       <c r="Y34">
-        <v>2957</v>
+        <v>2918</v>
       </c>
       <c r="Z34">
-        <v>35176</v>
+        <v>35217</v>
       </c>
       <c r="AA34">
-        <v>2244</v>
+        <v>2206</v>
       </c>
       <c r="AB34">
         <v>208</v>
       </c>
       <c r="AC34" s="21">
-        <v>2596</v>
+        <v>2602</v>
       </c>
       <c r="AD34">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>36</v>
+        <v>5</v>
+      </c>
+      <c r="AF34" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" s="21">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -4327,103 +4328,103 @@
       <c r="C35" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F35">
         <f>(E35-D35)</f>
-        <v>25868776920</v>
+        <v>40406397600</v>
       </c>
       <c r="G35">
         <f>(E35/D35)*100</f>
-        <v>119.68388553161444</v>
+        <v>130.74574834221812</v>
       </c>
       <c r="H35">
-        <v>37823</v>
+        <v>37866</v>
       </c>
       <c r="I35">
         <f>(W35+Z35+AC35)</f>
-        <v>37841.394422310754</v>
+        <v>37876.768924302785</v>
       </c>
       <c r="J35">
-        <v>128.3545816733068</v>
+        <v>128.45019920318731</v>
       </c>
       <c r="K35">
-        <v>11.908366533864539</v>
+        <v>11.856573705179279</v>
       </c>
       <c r="L35" s="21">
         <f>J35+K35</f>
-        <v>140.26294820717135</v>
+        <v>140.30677290836658</v>
       </c>
       <c r="M35">
-        <v>10.29482071713147</v>
-      </c>
-      <c r="N35" s="21">
-        <v>0.70517928286852594</v>
-      </c>
-      <c r="O35" s="21">
+        <v>10.366533864541831</v>
+      </c>
+      <c r="N35" s="17">
+        <v>0.76494023904382469</v>
+      </c>
+      <c r="O35" s="10">
         <f>(AC35+AF35)/C35</f>
-        <v>10.426294820717132</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P35" s="21">
-        <v>0.11155378486055779</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="Q35">
-        <v>1.9920318725099601E-2</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="R35" s="21">
         <f>AF35/C35</f>
-        <v>0.13147410358565736</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S35">
-        <v>128.11553784860561</v>
+        <v>128.10756972111551</v>
       </c>
       <c r="T35" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="U35">
-        <v>42.629482071713149</v>
+        <v>32.669322709163353</v>
       </c>
       <c r="V35" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="W35">
-        <v>51.394422310756973</v>
+        <v>57.768924302788847</v>
       </c>
       <c r="X35">
-        <v>32217</v>
+        <v>32241</v>
       </c>
       <c r="Y35">
-        <v>2989</v>
+        <v>2976</v>
       </c>
       <c r="Z35">
-        <v>35206</v>
+        <v>35217</v>
       </c>
       <c r="AA35">
-        <v>2275</v>
+        <v>2222</v>
       </c>
       <c r="AB35">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="AC35" s="21">
-        <v>2584</v>
+        <v>2602</v>
       </c>
       <c r="AD35">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AE35">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="21">
-        <v>33</v>
+        <v>2</v>
+      </c>
+      <c r="AF35" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -4431,103 +4432,103 @@
       <c r="C36" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="F36">
         <f>(E36-D36)</f>
-        <v>22537887980</v>
-      </c>
-      <c r="G36">
+        <v>47480999320</v>
+      </c>
+      <c r="G36" s="8">
         <f>(E36/D36)*100</f>
-        <v>117.14936923746409</v>
+        <v>136.12890390728003</v>
       </c>
       <c r="H36">
-        <v>37811</v>
-      </c>
-      <c r="I36" s="21">
+        <v>37866</v>
+      </c>
+      <c r="I36" s="8">
         <f>(W36+Z36+AC36)</f>
-        <v>37829.792828685262</v>
+        <v>37881.948207171314</v>
       </c>
       <c r="J36">
-        <v>128.53386454183271</v>
-      </c>
-      <c r="K36" s="21">
-        <v>11.64541832669323</v>
+        <v>128.3585657370518</v>
+      </c>
+      <c r="K36" s="8">
+        <v>11.94820717131474</v>
       </c>
       <c r="L36" s="21">
         <f>J36+K36</f>
-        <v>140.17928286852595</v>
+        <v>140.30677290836655</v>
       </c>
       <c r="M36">
-        <v>10.33067729083665</v>
+        <v>10.366533864541831</v>
       </c>
       <c r="N36" s="21">
-        <v>0.7450199203187251</v>
-      </c>
-      <c r="O36" s="21">
+        <v>0.82868525896414347</v>
+      </c>
+      <c r="O36" s="10">
         <f>(AC36+AF36)/C36</f>
-        <v>10.46215139442231</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P36">
-        <v>0.1235059760956175</v>
-      </c>
-      <c r="Q36" s="21">
-        <v>7.9681274900398405E-3</v>
+        <v>0.16733067729083659</v>
+      </c>
+      <c r="Q36" s="24">
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="R36" s="21">
         <f>AF36/C36</f>
-        <v>0.13147410358565736</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S36">
-        <v>128.35059760956179</v>
+        <v>127.9123505976096</v>
       </c>
       <c r="T36" t="s">
-        <v>95</v>
-      </c>
-      <c r="U36">
-        <v>39.04382470119522</v>
+        <v>31</v>
+      </c>
+      <c r="U36" s="8">
+        <v>31.075697211155379</v>
       </c>
       <c r="V36" t="s">
-        <v>91</v>
-      </c>
-      <c r="W36" s="21">
-        <v>51.792828685258961</v>
+        <v>34</v>
+      </c>
+      <c r="W36" s="8">
+        <v>62.948207171314742</v>
       </c>
       <c r="X36">
-        <v>32262</v>
+        <v>32218</v>
       </c>
       <c r="Y36">
-        <v>2923</v>
+        <v>2999</v>
       </c>
       <c r="Z36">
-        <v>35185</v>
+        <v>35217</v>
       </c>
       <c r="AA36">
-        <v>2274</v>
+        <v>2206</v>
       </c>
       <c r="AB36">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="AC36">
-        <v>2593</v>
+        <v>2602</v>
       </c>
       <c r="AD36">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AE36">
-        <v>2</v>
-      </c>
-      <c r="AF36">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="AF36" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" s="21">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -4535,98 +4536,98 @@
       <c r="C37" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="F37">
         <f>(E37-D37)</f>
-        <v>17220497120</v>
-      </c>
-      <c r="G37">
+        <v>44202953560</v>
+      </c>
+      <c r="G37" s="9">
         <f>(E37/D37)*100</f>
-        <v>113.10329804752037</v>
+        <v>133.6345966693778</v>
       </c>
       <c r="H37">
-        <v>37789</v>
+        <v>37866</v>
       </c>
       <c r="I37">
         <f>(W37+Z37+AC37)</f>
-        <v>37810.784860557767</v>
+        <v>37877.167330677294</v>
       </c>
       <c r="J37">
-        <v>128.48605577689241</v>
+        <v>128.82071713147411</v>
       </c>
       <c r="K37" s="21">
-        <v>11.597609561752989</v>
+        <v>11.48605577689243</v>
       </c>
       <c r="L37" s="21">
         <f>J37+K37</f>
-        <v>140.0836653386454</v>
+        <v>140.30677290836655</v>
       </c>
       <c r="M37">
-        <v>10.342629482071709</v>
+        <v>10.366533864541831</v>
       </c>
       <c r="N37" s="21">
-        <v>0.71713147410358569</v>
-      </c>
-      <c r="O37" s="21">
+        <v>0.75697211155378485</v>
+      </c>
+      <c r="O37" s="10">
         <f>(AC37+AF37)/C37</f>
-        <v>10.47011952191235</v>
+        <v>10.553784860557769</v>
       </c>
       <c r="P37">
-        <v>0.12749003984063739</v>
+        <v>0.16733067729083659</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="R37" s="21">
         <f>AF37/C37</f>
-        <v>0.12749003984063745</v>
+        <v>0.18725099601593626</v>
       </c>
       <c r="S37">
-        <v>128.43426294820719</v>
+        <v>128.50597609561751</v>
       </c>
       <c r="T37" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="U37">
-        <v>37.450199203187253</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="V37" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="W37" s="21">
-        <v>53.784860557768923</v>
+        <v>58.167330677290842</v>
       </c>
       <c r="X37">
-        <v>32250</v>
+        <v>32334</v>
       </c>
       <c r="Y37">
-        <v>2911</v>
+        <v>2883</v>
       </c>
       <c r="Z37">
-        <v>35161</v>
+        <v>35217</v>
       </c>
       <c r="AA37">
-        <v>2288</v>
+        <v>2224</v>
       </c>
       <c r="AB37" s="21">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AC37" s="21">
-        <v>2596</v>
+        <v>2602</v>
       </c>
       <c r="AD37">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="21">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="AF37" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
@@ -4712,7 +4713,7 @@
   </sheetData>
   <autoFilter ref="A2:AL2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AL53">
-      <sortCondition descending="1" ref="G2"/>
+      <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F3B955-25D8-4153-AD54-BBD10B0A694C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625A8FBB-D351-40B3-8227-1B252D112A1F}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,7 +357,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,8 +386,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,19 +467,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,7 +492,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -528,10 +522,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -542,8 +533,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,6 +549,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
@@ -843,54 +836,55 @@
   <dimension ref="A1:AL53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9" style="21" customWidth="1"/>
-    <col min="3" max="3" width="4.26953125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9" style="18" customWidth="1"/>
+    <col min="3" max="3" width="4.26953125" style="18" customWidth="1"/>
     <col min="4" max="4" width="12.90625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.453125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="5.54296875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" style="21" customWidth="1"/>
-    <col min="8" max="9" width="14.1796875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" style="21" customWidth="1"/>
-    <col min="11" max="18" width="6.453125" style="21" customWidth="1"/>
-    <col min="19" max="19" width="8" style="21" customWidth="1"/>
-    <col min="20" max="20" width="9" style="21" customWidth="1"/>
-    <col min="21" max="23" width="9.1796875" style="21" customWidth="1"/>
-    <col min="24" max="28" width="9.26953125" style="21" customWidth="1"/>
-    <col min="29" max="29" width="9.26953125" style="22" customWidth="1"/>
-    <col min="30" max="32" width="9.26953125" style="21" customWidth="1"/>
-    <col min="33" max="33" width="6.54296875" style="21" customWidth="1"/>
-    <col min="34" max="34" width="7.7265625" style="21" customWidth="1"/>
-    <col min="35" max="38" width="6.54296875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" style="18" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" style="18" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" style="18" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="18" customWidth="1"/>
+    <col min="11" max="18" width="6.453125" style="18" customWidth="1"/>
+    <col min="19" max="19" width="8" style="18" customWidth="1"/>
+    <col min="20" max="20" width="9" style="18" customWidth="1"/>
+    <col min="21" max="23" width="9.1796875" style="18" customWidth="1"/>
+    <col min="24" max="28" width="9.26953125" style="18" customWidth="1"/>
+    <col min="29" max="29" width="9.26953125" style="19" customWidth="1"/>
+    <col min="30" max="32" width="9.26953125" style="18" customWidth="1"/>
+    <col min="33" max="33" width="6.54296875" style="18" customWidth="1"/>
+    <col min="34" max="34" width="7.7265625" style="18" customWidth="1"/>
+    <col min="35" max="38" width="6.54296875" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="X1" s="27" t="s">
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="X1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="29" t="s">
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="28" t="s">
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
     </row>
     <row r="2" spans="1:32" s="2" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -956,42 +950,42 @@
       <c r="U2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="18" t="s">
+      <c r="W2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="X2" s="19">
+      <c r="X2" s="16">
         <v>3</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="Y2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="19" t="s">
+      <c r="Z2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AA2" s="19">
+      <c r="AA2" s="16">
         <v>4</v>
       </c>
-      <c r="AB2" s="19" t="s">
+      <c r="AB2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AC2" s="20" t="s">
+      <c r="AC2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AD2" s="19">
+      <c r="AD2" s="16">
         <v>5</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AF2" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
+      <c r="A3">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -1000,7 +994,7 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E3" t="s">
@@ -1018,8 +1012,8 @@
         <v>37925</v>
       </c>
       <c r="I3">
-        <f>(W3+Z3+AC3)</f>
-        <v>37932.167330677294</v>
+        <f>Y3+AB3+AE3</f>
+        <v>3151</v>
       </c>
       <c r="J3">
         <v>128.8565737051793</v>
@@ -1027,27 +1021,27 @@
       <c r="K3" s="21">
         <v>11.71713147410359</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="20">
         <f>J3+K3</f>
         <v>140.57370517928288</v>
       </c>
       <c r="M3">
         <v>10.31872509960159</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="21">
         <v>0.8127490039840638</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="21">
         <f>(AC3+AF3)/C3</f>
         <v>10.52191235059761</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="18">
         <v>0.17928286852589639</v>
       </c>
       <c r="Q3">
         <v>2.3904382470119521E-2</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="20">
         <f>AF3/C3</f>
         <v>0.20318725099601595</v>
       </c>
@@ -1063,7 +1057,7 @@
       <c r="V3" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="23">
+      <c r="W3" s="21">
         <v>58.167330677290842</v>
       </c>
       <c r="X3">
@@ -1078,16 +1072,16 @@
       <c r="AA3">
         <v>2182</v>
       </c>
-      <c r="AB3" s="23">
+      <c r="AB3" s="21">
         <v>204</v>
       </c>
-      <c r="AC3" s="23">
+      <c r="AC3" s="8">
         <v>2590</v>
       </c>
       <c r="AD3">
         <v>45</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="10">
         <v>6</v>
       </c>
       <c r="AF3" s="10">
@@ -1095,7 +1089,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A4" s="23">
+      <c r="A4">
         <v>11</v>
       </c>
       <c r="B4" t="s">
@@ -1114,24 +1108,24 @@
         <f>(E4-D4)</f>
         <v>17220497120</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="21">
         <f>(E4/D4)*100</f>
         <v>113.10329804752037</v>
       </c>
       <c r="H4">
         <v>37789</v>
       </c>
-      <c r="I4">
-        <f>(W4+Z4+AC4)</f>
-        <v>37810.784860557767</v>
+      <c r="I4" s="21">
+        <f>Y4+AB4+AE4</f>
+        <v>3091</v>
       </c>
       <c r="J4">
         <v>128.48605577689241</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="21">
         <v>11.597609561752989</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="21">
         <f>J4+K4</f>
         <v>140.0836653386454</v>
       </c>
@@ -1151,7 +1145,7 @@
       <c r="Q4">
         <v>0</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="21">
         <f>AF4/C4</f>
         <v>0.12749003984063745</v>
       </c>
@@ -1161,13 +1155,13 @@
       <c r="T4" t="s">
         <v>100</v>
       </c>
-      <c r="U4" s="23">
+      <c r="U4" s="21">
         <v>37.450199203187253</v>
       </c>
       <c r="V4" t="s">
         <v>101</v>
       </c>
-      <c r="W4" s="21">
+      <c r="W4" s="18">
         <v>53.784860557768923</v>
       </c>
       <c r="X4">
@@ -1182,24 +1176,24 @@
       <c r="AA4">
         <v>2288</v>
       </c>
-      <c r="AB4" s="21">
+      <c r="AB4" s="18">
         <v>180</v>
       </c>
-      <c r="AC4" s="21">
+      <c r="AC4" s="8">
         <v>2596</v>
       </c>
       <c r="AD4">
         <v>32</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="21">
         <v>0</v>
       </c>
-      <c r="AF4" s="23">
+      <c r="AF4" s="21">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A5" s="21">
+      <c r="A5">
         <v>12</v>
       </c>
       <c r="B5" t="s">
@@ -1218,7 +1212,7 @@
         <f>(E5-D5)</f>
         <v>39795784920</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="21">
         <f>(E5/D5)*100</f>
         <v>130.28112528970809</v>
       </c>
@@ -1226,8 +1220,8 @@
         <v>37906</v>
       </c>
       <c r="I5" s="21">
-        <f>(W5+Z5+AC5)</f>
-        <v>37917.964143426296</v>
+        <f>Y5+AB5+AE5</f>
+        <v>3166</v>
       </c>
       <c r="J5">
         <v>128.71713147410361</v>
@@ -1295,7 +1289,7 @@
       <c r="AD5">
         <v>46</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="21">
         <v>1</v>
       </c>
       <c r="AF5" s="9">
@@ -1303,7 +1297,7 @@
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A6" s="21">
+      <c r="A6">
         <v>13</v>
       </c>
       <c r="B6" t="s">
@@ -1322,21 +1316,21 @@
         <f>(E6-D6)</f>
         <v>37463917860</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="21">
         <f>(E6/D6)*100</f>
         <v>128.50677761080814</v>
       </c>
       <c r="H6">
         <v>37875</v>
       </c>
-      <c r="I6" s="23">
-        <f>(W6+Z6+AC6)</f>
-        <v>37892.768924302785</v>
+      <c r="I6" s="21">
+        <f>Y6+AB6+AE6</f>
+        <v>3191</v>
       </c>
       <c r="J6">
         <v>128.601593625498</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="21">
         <v>11.8605577689243</v>
       </c>
       <c r="L6" s="10">
@@ -1349,14 +1343,14 @@
       <c r="N6" s="21">
         <v>0.8366533864541833</v>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="21">
         <f>(AC6+AF6)/C6</f>
         <v>10.434262948207172</v>
       </c>
       <c r="P6">
         <v>0.14342629482071709</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="21">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="R6" s="21">
@@ -1369,13 +1363,13 @@
       <c r="T6" t="s">
         <v>45</v>
       </c>
-      <c r="U6" s="23">
+      <c r="U6" s="21">
         <v>35.059760956175303</v>
       </c>
       <c r="V6" t="s">
         <v>46</v>
       </c>
-      <c r="W6" s="23">
+      <c r="W6" s="21">
         <v>57.768924302788847</v>
       </c>
       <c r="X6">
@@ -1399,15 +1393,15 @@
       <c r="AD6">
         <v>36</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="21">
         <v>4</v>
       </c>
-      <c r="AF6" s="23">
+      <c r="AF6" s="21">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A7" s="21">
+      <c r="A7">
         <v>14</v>
       </c>
       <c r="B7" t="s">
@@ -1426,16 +1420,16 @@
         <f>(E7-D7)</f>
         <v>35516488280</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="21">
         <f>(E7/D7)*100</f>
         <v>127.02495336174735</v>
       </c>
       <c r="H7">
         <v>37835</v>
       </c>
-      <c r="I7" s="24">
-        <f>(W7+Z7+AC7)</f>
-        <v>37852.370517928284</v>
+      <c r="I7" s="21">
+        <f>Y7+AB7+AE7</f>
+        <v>3232</v>
       </c>
       <c r="J7">
         <v>128.23904382470121</v>
@@ -1450,20 +1444,20 @@
       <c r="M7">
         <v>10.32669322709163</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="21">
         <v>0.85657370517928288</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="21">
         <f>(AC7+AF7)/C7</f>
         <v>10.48605577689243</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="18">
         <v>0.151394422310757</v>
       </c>
       <c r="Q7" s="21">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="R7" s="21">
+      <c r="R7" s="18">
         <f>AF7/C7</f>
         <v>0.15936254980079681</v>
       </c>
@@ -1473,13 +1467,13 @@
       <c r="T7" t="s">
         <v>51</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="21">
         <v>34.661354581673308</v>
       </c>
       <c r="V7" t="s">
         <v>52</v>
       </c>
-      <c r="W7" s="23">
+      <c r="W7" s="21">
         <v>57.370517928286858</v>
       </c>
       <c r="X7">
@@ -1497,21 +1491,21 @@
       <c r="AB7" s="21">
         <v>215</v>
       </c>
-      <c r="AC7" s="21">
+      <c r="AC7" s="8">
         <v>2592</v>
       </c>
       <c r="AD7">
         <v>38</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="21">
         <v>2</v>
       </c>
-      <c r="AF7" s="23">
+      <c r="AF7" s="21">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8">
         <v>15</v>
       </c>
       <c r="B8" t="s">
@@ -1530,7 +1524,7 @@
         <f>(E8-D8)</f>
         <v>55319762920</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="20">
         <f>(E8/D8)*100</f>
         <v>142.09352008874677</v>
       </c>
@@ -1538,8 +1532,8 @@
         <v>37866</v>
       </c>
       <c r="I8" s="21">
-        <f>(W8+Z8+AC8)</f>
-        <v>37879.5577689243</v>
+        <f>Y8+AB8+AE8</f>
+        <v>3155</v>
       </c>
       <c r="J8">
         <v>128.69721115537851</v>
@@ -1547,27 +1541,27 @@
       <c r="K8" s="21">
         <v>11.60956175298805</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="21">
         <f>J8+K8</f>
         <v>140.30677290836655</v>
       </c>
       <c r="M8">
         <v>10.366533864541831</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="20">
         <v>0.92828685258964139</v>
       </c>
       <c r="O8" s="10">
         <f>(AC8+AF8)/C8</f>
         <v>10.553784860557769</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="21">
         <v>0.15537848605577689</v>
       </c>
       <c r="Q8" s="21">
         <v>3.1872509960159362E-2</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="21">
         <f>AF8/C8</f>
         <v>0.18725099601593626</v>
       </c>
@@ -1577,7 +1571,7 @@
       <c r="T8" t="s">
         <v>28</v>
       </c>
-      <c r="U8" s="24">
+      <c r="U8" s="20">
         <v>25.099601593625501</v>
       </c>
       <c r="V8" t="s">
@@ -1598,16 +1592,16 @@
       <c r="AA8">
         <v>2181</v>
       </c>
-      <c r="AB8" s="24">
+      <c r="AB8" s="20">
         <v>233</v>
       </c>
-      <c r="AC8" s="9">
+      <c r="AC8" s="10">
         <v>2602</v>
       </c>
       <c r="AD8">
         <v>39</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="28">
         <v>8</v>
       </c>
       <c r="AF8" s="9">
@@ -1615,7 +1609,7 @@
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A9" s="21">
+      <c r="A9">
         <v>16</v>
       </c>
       <c r="B9" t="s">
@@ -1642,13 +1636,13 @@
         <v>37865</v>
       </c>
       <c r="I9" s="21">
-        <f>(W9+Z9+AC9)</f>
-        <v>37878.768924302785</v>
+        <f>Y9+AB9+AE9</f>
+        <v>3199</v>
       </c>
       <c r="J9">
         <v>128.4581673306773</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="18">
         <v>11.908366533864539</v>
       </c>
       <c r="L9" s="8">
@@ -1661,14 +1655,14 @@
       <c r="N9" s="21">
         <v>0.81673306772908372</v>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="21">
         <f>(AC9+AF9)/C9</f>
         <v>10.490039840637451</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="21">
         <v>0.15537848605577689</v>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="18">
         <v>1.9920318725099601E-2</v>
       </c>
       <c r="R9" s="21">
@@ -1705,21 +1699,21 @@
       <c r="AB9">
         <v>205</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="21">
         <v>2589</v>
       </c>
       <c r="AD9">
         <v>39</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="8">
         <v>5</v>
       </c>
-      <c r="AF9" s="23">
+      <c r="AF9" s="21">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A10" s="21">
+      <c r="A10">
         <v>17</v>
       </c>
       <c r="B10" t="s">
@@ -1738,24 +1732,24 @@
         <f>(E10-D10)</f>
         <v>39608412840</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="21">
         <f>(E10/D10)*100</f>
         <v>130.13855146080436</v>
       </c>
       <c r="H10">
         <v>37850</v>
       </c>
-      <c r="I10">
-        <f>(W10+Z10+AC10)</f>
-        <v>37865.768924302785</v>
+      <c r="I10" s="21">
+        <f>Y10+AB10+AE10</f>
+        <v>3140</v>
       </c>
       <c r="J10">
         <v>128.6414342629482</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="18">
         <v>11.66135458167331</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="21">
         <f>J10+K10</f>
         <v>140.30278884462152</v>
       </c>
@@ -1769,13 +1763,13 @@
         <f>(AC10+AF10)/C10</f>
         <v>10.49402390438247</v>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="18">
         <v>0.151394422310757</v>
       </c>
       <c r="Q10">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="R10" s="21">
+      <c r="R10" s="18">
         <f>AF10/C10</f>
         <v>0.16733067729083664</v>
       </c>
@@ -1791,7 +1785,7 @@
       <c r="V10" t="s">
         <v>46</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="21">
         <v>57.768924302788847</v>
       </c>
       <c r="X10">
@@ -1809,13 +1803,13 @@
       <c r="AB10">
         <v>209</v>
       </c>
-      <c r="AC10" s="21">
+      <c r="AC10" s="8">
         <v>2592</v>
       </c>
       <c r="AD10">
         <v>38</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="21">
         <v>4</v>
       </c>
       <c r="AF10" s="21">
@@ -1823,7 +1817,7 @@
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A11" s="21">
+      <c r="A11">
         <v>18</v>
       </c>
       <c r="B11" t="s">
@@ -1842,7 +1836,7 @@
         <f>(E11-D11)</f>
         <v>39434570980</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="21">
         <f>(E11/D11)*100</f>
         <v>130.12629804236141</v>
       </c>
@@ -1850,8 +1844,8 @@
         <v>37684</v>
       </c>
       <c r="I11" s="21">
-        <f>(W11+Z11+AC11)</f>
-        <v>37700.768924302785</v>
+        <f>Y11+AB11+AE11</f>
+        <v>3067</v>
       </c>
       <c r="J11">
         <v>128.29880478087651</v>
@@ -1859,7 +1853,7 @@
       <c r="K11" s="21">
         <v>11.342629482071709</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L11" s="21">
         <f>J11+K11</f>
         <v>139.64143426294822</v>
       </c>
@@ -1879,7 +1873,7 @@
       <c r="Q11" s="21">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="R11" s="21">
+      <c r="R11" s="18">
         <f>AF11/C11</f>
         <v>0.16334661354581673</v>
       </c>
@@ -1913,13 +1907,13 @@
       <c r="AB11">
         <v>216</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="8">
         <v>2593</v>
       </c>
       <c r="AD11">
         <v>37</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="21">
         <v>4</v>
       </c>
       <c r="AF11" s="21">
@@ -1927,7 +1921,7 @@
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A12" s="21">
+      <c r="A12">
         <v>19</v>
       </c>
       <c r="B12" t="s">
@@ -1946,7 +1940,7 @@
         <f>(E12-D12)</f>
         <v>22537887980</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="21">
         <f>(E12/D12)*100</f>
         <v>117.14936923746409</v>
       </c>
@@ -1954,13 +1948,13 @@
         <v>37811</v>
       </c>
       <c r="I12" s="21">
-        <f>(W12+Z12+AC12)</f>
-        <v>37829.792828685262</v>
+        <f>Y12+AB12+AE12</f>
+        <v>3112</v>
       </c>
       <c r="J12">
         <v>128.53386454183271</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="18">
         <v>11.64541832669323</v>
       </c>
       <c r="L12" s="21">
@@ -1970,20 +1964,20 @@
       <c r="M12">
         <v>10.33067729083665</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="21">
         <v>0.7450199203187251</v>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="21">
         <f>(AC12+AF12)/C12</f>
         <v>10.46215139442231</v>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="18">
         <v>0.1235059760956175</v>
       </c>
       <c r="Q12">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="R12" s="21">
+      <c r="R12" s="18">
         <f>AF12/C12</f>
         <v>0.13147410358565736</v>
       </c>
@@ -2017,21 +2011,21 @@
       <c r="AB12">
         <v>187</v>
       </c>
-      <c r="AC12" s="21">
+      <c r="AC12" s="8">
         <v>2593</v>
       </c>
       <c r="AD12">
         <v>31</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="21">
         <v>2</v>
       </c>
-      <c r="AF12" s="23">
+      <c r="AF12" s="21">
         <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A13" s="15">
+      <c r="A13">
         <v>20</v>
       </c>
       <c r="B13" t="s">
@@ -2057,9 +2051,9 @@
       <c r="H13">
         <v>37897</v>
       </c>
-      <c r="I13">
-        <f>(W13+Z13+AC13)</f>
-        <v>37902.972111553783</v>
+      <c r="I13" s="21">
+        <f>Y13+AB13+AE13</f>
+        <v>3184</v>
       </c>
       <c r="J13">
         <v>128.53784860557769</v>
@@ -2074,20 +2068,20 @@
       <c r="M13">
         <v>10.350597609561749</v>
       </c>
-      <c r="N13" s="21">
+      <c r="N13" s="18">
         <v>0.78884462151394419</v>
       </c>
       <c r="O13" s="10">
         <f>(AC13+AF13)/C13</f>
         <v>10.553784860557769</v>
       </c>
-      <c r="P13" s="24">
+      <c r="P13" s="20">
         <v>0.19920318725099601</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="21">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="R13" s="24">
+      <c r="R13" s="20">
         <f>AF13/C13</f>
         <v>0.20318725099601595</v>
       </c>
@@ -2121,7 +2115,7 @@
       <c r="AB13">
         <v>198</v>
       </c>
-      <c r="AC13" s="14">
+      <c r="AC13" s="8">
         <v>2598</v>
       </c>
       <c r="AD13">
@@ -2130,7 +2124,7 @@
       <c r="AE13">
         <v>1</v>
       </c>
-      <c r="AF13" s="24">
+      <c r="AF13" s="20">
         <v>51</v>
       </c>
     </row>
@@ -2162,16 +2156,16 @@
         <v>37823</v>
       </c>
       <c r="I14" s="21">
-        <f>(W14+Z14+AC14)</f>
-        <v>37841.394422310754</v>
+        <f>Y14+AB14+AE14</f>
+        <v>3171</v>
       </c>
       <c r="J14">
         <v>128.3545816733068</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="18">
         <v>11.908366533864539</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="21">
         <f>J14+K14</f>
         <v>140.26294820717135</v>
       </c>
@@ -2185,10 +2179,10 @@
         <f>(AC14+AF14)/C14</f>
         <v>10.426294820717132</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="21">
         <v>0.11155378486055779</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="18">
         <v>1.9920318725099601E-2</v>
       </c>
       <c r="R14" s="21">
@@ -2201,7 +2195,7 @@
       <c r="T14" t="s">
         <v>97</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="21">
         <v>42.629482071713149</v>
       </c>
       <c r="V14" t="s">
@@ -2231,15 +2225,15 @@
       <c r="AD14">
         <v>28</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="8">
         <v>5</v>
       </c>
-      <c r="AF14" s="23">
+      <c r="AF14" s="21">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A15" s="21">
+      <c r="A15">
         <v>22</v>
       </c>
       <c r="B15" t="s">
@@ -2265,14 +2259,14 @@
       <c r="H15">
         <v>37644</v>
       </c>
-      <c r="I15">
-        <f>(W15+Z15+AC15)</f>
-        <v>37662.768924302785</v>
+      <c r="I15" s="21">
+        <f>Y15+AB15+AE15</f>
+        <v>3162</v>
       </c>
       <c r="J15">
         <v>127.6294820717131</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="20">
         <v>11.812749003984059</v>
       </c>
       <c r="L15" s="21">
@@ -2282,10 +2276,10 @@
       <c r="M15">
         <v>10.378486055776889</v>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="18">
         <v>0.78087649402390436</v>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="18">
         <f>(AC15+AF15)/C15</f>
         <v>10.533864541832669</v>
       </c>
@@ -2295,7 +2289,7 @@
       <c r="Q15">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="R15" s="21">
+      <c r="R15" s="18">
         <f>AF15/C15</f>
         <v>0.15537848605577689</v>
       </c>
@@ -2305,13 +2299,13 @@
       <c r="T15" t="s">
         <v>51</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="21">
         <v>34.661354581673308</v>
       </c>
       <c r="V15" t="s">
         <v>46</v>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="18">
         <v>57.768924302788847</v>
       </c>
       <c r="X15">
@@ -2326,16 +2320,16 @@
       <c r="AA15">
         <v>2253</v>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="18">
         <v>196</v>
       </c>
-      <c r="AC15" s="24">
+      <c r="AC15" s="10">
         <v>2605</v>
       </c>
       <c r="AD15">
         <v>38</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="21">
         <v>1</v>
       </c>
       <c r="AF15" s="21">
@@ -2343,7 +2337,7 @@
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A16" s="21">
+      <c r="A16">
         <v>23</v>
       </c>
       <c r="B16" t="s">
@@ -2362,16 +2356,16 @@
         <f>(E16-D16)</f>
         <v>29686892100</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="18">
         <f>(E16/D16)*100</f>
         <v>122.58913854694097</v>
       </c>
       <c r="H16">
         <v>37813</v>
       </c>
-      <c r="I16">
-        <f>(W16+Z16+AC16)</f>
-        <v>37837.362549800797</v>
+      <c r="I16" s="21">
+        <f>Y16+AB16+AE16</f>
+        <v>3163</v>
       </c>
       <c r="J16">
         <v>128.42629482071709</v>
@@ -2379,14 +2373,14 @@
       <c r="K16" s="21">
         <v>11.7609561752988</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="18">
         <f>J16+K16</f>
         <v>140.18725099601588</v>
       </c>
       <c r="M16">
         <v>10.322709163346611</v>
       </c>
-      <c r="N16" s="21">
+      <c r="N16" s="18">
         <v>0.82868525896414347</v>
       </c>
       <c r="O16" s="21">
@@ -2399,7 +2393,7 @@
       <c r="Q16">
         <v>1.1952191235059761E-2</v>
       </c>
-      <c r="R16" s="21">
+      <c r="R16" s="18">
         <f>AF16/C16</f>
         <v>0.1394422310756972</v>
       </c>
@@ -2409,7 +2403,7 @@
       <c r="T16" t="s">
         <v>80</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="21">
         <v>32.669322709163353</v>
       </c>
       <c r="V16" t="s">
@@ -2433,7 +2427,7 @@
       <c r="AB16">
         <v>208</v>
       </c>
-      <c r="AC16" s="21">
+      <c r="AC16" s="8">
         <v>2591</v>
       </c>
       <c r="AD16">
@@ -2442,12 +2436,12 @@
       <c r="AE16">
         <v>3</v>
       </c>
-      <c r="AF16" s="21">
+      <c r="AF16" s="18">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A17" s="21">
+      <c r="A17">
         <v>24</v>
       </c>
       <c r="B17" t="s">
@@ -2466,34 +2460,34 @@
         <f>(E17-D17)</f>
         <v>26390302240</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="18">
         <f>(E17/D17)*100</f>
         <v>120.08072086451268</v>
       </c>
       <c r="H17">
         <v>37808</v>
       </c>
-      <c r="I17">
-        <f>(W17+Z17+AC17)</f>
-        <v>37830.964143426296</v>
+      <c r="I17" s="21">
+        <f>Y17+AB17+AE17</f>
+        <v>3165</v>
       </c>
       <c r="J17">
         <v>128.36254980079681</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="18">
         <v>11.7808764940239</v>
       </c>
-      <c r="L17" s="23">
+      <c r="L17" s="21">
         <f>J17+K17</f>
         <v>140.1434262948207</v>
       </c>
       <c r="M17">
         <v>10.342629482071709</v>
       </c>
-      <c r="N17" s="21">
+      <c r="N17" s="18">
         <v>0.82868525896414347</v>
       </c>
-      <c r="O17" s="21">
+      <c r="O17" s="18">
         <f>(AC17+AF17)/C17</f>
         <v>10.48605577689243</v>
       </c>
@@ -2503,7 +2497,7 @@
       <c r="Q17">
         <v>0</v>
       </c>
-      <c r="R17" s="21">
+      <c r="R17" s="18">
         <f>AF17/C17</f>
         <v>0.14342629482071714</v>
       </c>
@@ -2519,7 +2513,7 @@
       <c r="V17" t="s">
         <v>60</v>
       </c>
-      <c r="W17" s="21">
+      <c r="W17" s="18">
         <v>58.964143426294832</v>
       </c>
       <c r="X17">
@@ -2534,10 +2528,10 @@
       <c r="AA17">
         <v>2244</v>
       </c>
-      <c r="AB17" s="21">
+      <c r="AB17" s="18">
         <v>208</v>
       </c>
-      <c r="AC17" s="21">
+      <c r="AC17" s="8">
         <v>2596</v>
       </c>
       <c r="AD17">
@@ -2546,12 +2540,12 @@
       <c r="AE17">
         <v>0</v>
       </c>
-      <c r="AF17" s="21">
+      <c r="AF17" s="18">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A18" s="21">
+      <c r="A18">
         <v>25</v>
       </c>
       <c r="B18" t="s">
@@ -2577,14 +2571,14 @@
       <c r="H18">
         <v>37851</v>
       </c>
-      <c r="I18">
-        <f>(W18+Z18+AC18)</f>
-        <v>37867.370517928284</v>
+      <c r="I18" s="21">
+        <f>Y18+AB18+AE18</f>
+        <v>3097</v>
       </c>
       <c r="J18">
         <v>128.83266932270919</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="21">
         <v>11.474103585657369</v>
       </c>
       <c r="L18" s="21">
@@ -2594,20 +2588,20 @@
       <c r="M18">
         <v>10.33067729083665</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="21">
         <v>0.8605577689243028</v>
       </c>
-      <c r="O18" s="21">
+      <c r="O18" s="18">
         <f>(AC18+AF18)/C18</f>
         <v>10.49402390438247</v>
       </c>
-      <c r="P18" s="21">
+      <c r="P18" s="18">
         <v>0.15936254980079681</v>
       </c>
       <c r="Q18">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="R18" s="21">
+      <c r="R18" s="18">
         <f>AF18/C18</f>
         <v>0.16334661354581673</v>
       </c>
@@ -2623,7 +2617,7 @@
       <c r="V18" t="s">
         <v>52</v>
       </c>
-      <c r="W18" s="23">
+      <c r="W18" s="21">
         <v>57.370517928286858</v>
       </c>
       <c r="X18">
@@ -2641,13 +2635,13 @@
       <c r="AB18">
         <v>216</v>
       </c>
-      <c r="AC18" s="21">
+      <c r="AC18" s="8">
         <v>2593</v>
       </c>
       <c r="AD18">
         <v>40</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="21">
         <v>1</v>
       </c>
       <c r="AF18" s="21">
@@ -2655,7 +2649,7 @@
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A19" s="23">
+      <c r="A19">
         <v>26</v>
       </c>
       <c r="B19" t="s">
@@ -2664,7 +2658,7 @@
       <c r="C19" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
@@ -2682,13 +2676,13 @@
         <v>37861</v>
       </c>
       <c r="I19" s="21">
-        <f>(W19+Z19+AC19)</f>
-        <v>37870.183266932268</v>
+        <f>Y19+AB19+AE19</f>
+        <v>3052</v>
       </c>
       <c r="J19">
         <v>128.97211155378491</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="21">
         <v>11.314741035856571</v>
       </c>
       <c r="L19" s="21">
@@ -2708,10 +2702,10 @@
       <c r="P19">
         <v>0.17131474103585659</v>
       </c>
-      <c r="Q19" s="21">
+      <c r="Q19" s="18">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="R19" s="21">
+      <c r="R19" s="18">
         <f>AF19/C19</f>
         <v>0.17928286852589642</v>
       </c>
@@ -2745,21 +2739,21 @@
       <c r="AB19" s="21">
         <v>210</v>
       </c>
-      <c r="AC19" s="23">
+      <c r="AC19" s="10">
         <v>2604</v>
       </c>
       <c r="AD19">
         <v>43</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="21">
         <v>2</v>
       </c>
-      <c r="AF19" s="23">
+      <c r="AF19" s="21">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A20" s="15">
+      <c r="A20">
         <v>27</v>
       </c>
       <c r="B20" t="s">
@@ -2786,8 +2780,8 @@
         <v>37873</v>
       </c>
       <c r="I20" s="21">
-        <f>(W20+Z20+AC20)</f>
-        <v>37880.58167330677</v>
+        <f>Y20+AB20+AE20</f>
+        <v>3075</v>
       </c>
       <c r="J20">
         <v>128.85258964143429</v>
@@ -2805,17 +2799,17 @@
       <c r="N20" s="21">
         <v>0.78087649402390436</v>
       </c>
-      <c r="O20" s="24">
+      <c r="O20" s="20">
         <f>(AC20+AF20)/C20</f>
         <v>10.569721115537849</v>
       </c>
-      <c r="P20" s="23">
+      <c r="P20" s="21">
         <v>0.18326693227091631</v>
       </c>
-      <c r="Q20" s="21">
+      <c r="Q20" s="18">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="R20" s="23">
+      <c r="R20" s="21">
         <f>AF20/C20</f>
         <v>0.18725099601593626</v>
       </c>
@@ -2825,13 +2819,13 @@
       <c r="T20" t="s">
         <v>48</v>
       </c>
-      <c r="U20" s="23">
+      <c r="U20" s="21">
         <v>33.466135458167329</v>
       </c>
       <c r="V20" t="s">
         <v>74</v>
       </c>
-      <c r="W20" s="21">
+      <c r="W20" s="18">
         <v>54.581673306772913</v>
       </c>
       <c r="X20">
@@ -2846,16 +2840,16 @@
       <c r="AA20">
         <v>2222</v>
       </c>
-      <c r="AB20" s="21">
+      <c r="AB20" s="18">
         <v>196</v>
       </c>
-      <c r="AC20" s="8">
+      <c r="AC20" s="10">
         <v>2606</v>
       </c>
       <c r="AD20">
         <v>46</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="21">
         <v>1</v>
       </c>
       <c r="AF20" s="9">
@@ -2863,7 +2857,7 @@
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A21" s="21">
+      <c r="A21">
         <v>28</v>
       </c>
       <c r="B21" t="s">
@@ -2890,13 +2884,13 @@
         <v>37874</v>
       </c>
       <c r="I21" s="21">
-        <f>(W21+Z21+AC21)</f>
-        <v>37880.792828685262</v>
+        <f>Y21+AB21+AE21</f>
+        <v>3086</v>
       </c>
       <c r="J21">
         <v>128.796812749004</v>
       </c>
-      <c r="K21" s="21">
+      <c r="K21" s="18">
         <v>11.55776892430279</v>
       </c>
       <c r="L21" s="8">
@@ -2906,10 +2900,10 @@
       <c r="M21">
         <v>10.358565737051791</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="21">
         <v>0.72908366533864544</v>
       </c>
-      <c r="O21" s="23">
+      <c r="O21" s="21">
         <f>(AC21+AF21)/C21</f>
         <v>10.53784860557769</v>
       </c>
@@ -2929,7 +2923,7 @@
       <c r="T21" t="s">
         <v>51</v>
       </c>
-      <c r="U21" s="23">
+      <c r="U21" s="21">
         <v>34.661354581673308</v>
       </c>
       <c r="V21" t="s">
@@ -2953,21 +2947,21 @@
       <c r="AB21">
         <v>183</v>
       </c>
-      <c r="AC21" s="21">
+      <c r="AC21" s="10">
         <v>2600</v>
       </c>
       <c r="AD21">
         <v>43</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="21">
         <v>2</v>
       </c>
-      <c r="AF21" s="23">
+      <c r="AF21" s="21">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A22" s="21">
+      <c r="A22">
         <v>29</v>
       </c>
       <c r="B22" t="s">
@@ -2986,16 +2980,16 @@
         <f>(E22-D22)</f>
         <v>35399896360</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="18">
         <f>(E22/D22)*100</f>
         <v>126.93623706819051</v>
       </c>
       <c r="H22">
         <v>37826</v>
       </c>
-      <c r="I22">
-        <f>(W22+Z22+AC22)</f>
-        <v>37839.589641434264</v>
+      <c r="I22" s="21">
+        <f>Y22+AB22+AE22</f>
+        <v>3082</v>
       </c>
       <c r="J22">
         <v>128.70119521912349</v>
@@ -3003,27 +2997,27 @@
       <c r="K22" s="10">
         <v>11.446215139442231</v>
       </c>
-      <c r="L22" s="23">
+      <c r="L22" s="21">
         <f>J22+K22</f>
         <v>140.14741035856571</v>
       </c>
       <c r="M22">
         <v>10.39840637450199</v>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="18">
         <v>0.81673306772908372</v>
       </c>
       <c r="O22" s="10">
         <f>(AC22+AF22)/C22</f>
         <v>10.553784860557769</v>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="18">
         <v>0.1394422310756972</v>
       </c>
       <c r="Q22">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="R22" s="21">
+      <c r="R22" s="18">
         <f>AF22/C22</f>
         <v>0.15537848605577689</v>
       </c>
@@ -3033,7 +3027,7 @@
       <c r="T22" t="s">
         <v>84</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="21">
         <v>33.864541832669318</v>
       </c>
       <c r="V22" t="s">
@@ -3057,7 +3051,7 @@
       <c r="AB22">
         <v>205</v>
       </c>
-      <c r="AC22" s="10">
+      <c r="AC22" s="29">
         <v>2610</v>
       </c>
       <c r="AD22">
@@ -3066,12 +3060,12 @@
       <c r="AE22">
         <v>4</v>
       </c>
-      <c r="AF22" s="21">
+      <c r="AF22" s="18">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A23" s="21">
+      <c r="A23">
         <v>30</v>
       </c>
       <c r="B23" t="s">
@@ -3080,7 +3074,7 @@
       <c r="C23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E23" t="s">
@@ -3098,8 +3092,8 @@
         <v>37854</v>
       </c>
       <c r="I23" s="21">
-        <f>(W23+Z23+AC23)</f>
-        <v>37870.77689243028</v>
+        <f>Y23+AB23+AE23</f>
+        <v>3155</v>
       </c>
       <c r="J23">
         <v>128.68127490039839</v>
@@ -3121,7 +3115,7 @@
         <f>(AC23+AF23)/C23</f>
         <v>10.446215139442231</v>
       </c>
-      <c r="P23" s="21">
+      <c r="P23" s="18">
         <v>0.14342629482071709</v>
       </c>
       <c r="Q23">
@@ -3167,7 +3161,7 @@
       <c r="AD23">
         <v>36</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="21">
         <v>3</v>
       </c>
       <c r="AF23" s="21">
@@ -3175,7 +3169,7 @@
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A24" s="15">
+      <c r="A24">
         <v>31</v>
       </c>
       <c r="B24" t="s">
@@ -3194,7 +3188,7 @@
         <f>(E24-D24)</f>
         <v>38708700340</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="21">
         <f>(E24/D24)*100</f>
         <v>129.57176442636413</v>
       </c>
@@ -3202,16 +3196,16 @@
         <v>37735</v>
       </c>
       <c r="I24" s="21">
-        <f>(W24+Z24+AC24)</f>
-        <v>37742.378486055779</v>
+        <f>Y24+AB24+AE24</f>
+        <v>3075</v>
       </c>
       <c r="J24">
         <v>128.34661354581669</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="18">
         <v>11.509960159362549</v>
       </c>
-      <c r="L24" s="23">
+      <c r="L24" s="21">
         <f>J24+K24</f>
         <v>139.85657370517924</v>
       </c>
@@ -3221,7 +3215,7 @@
       <c r="N24" s="21">
         <v>0.73705179282868527</v>
       </c>
-      <c r="O24" s="21">
+      <c r="O24" s="18">
         <f>(AC24+AF24)/C24</f>
         <v>10.482071713147411</v>
       </c>
@@ -3265,13 +3259,13 @@
       <c r="AB24">
         <v>185</v>
       </c>
-      <c r="AC24" s="8">
+      <c r="AC24" s="21">
         <v>2583</v>
       </c>
       <c r="AD24">
         <v>47</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="21">
         <v>1</v>
       </c>
       <c r="AF24" s="8">
@@ -3279,7 +3273,7 @@
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="A25" s="21">
         <v>32</v>
       </c>
       <c r="B25" t="s">
@@ -3298,7 +3292,7 @@
         <f>(E25-D25)</f>
         <v>39156912800</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="21">
         <f>(E25/D25)*100</f>
         <v>129.89647856461158</v>
       </c>
@@ -3306,16 +3300,16 @@
         <v>37755</v>
       </c>
       <c r="I25" s="21">
-        <f>(W25+Z25+AC25)</f>
-        <v>37775.541832669325</v>
+        <f>Y25+AB25+AE25</f>
+        <v>3184</v>
       </c>
       <c r="J25">
         <v>128.1434262948207</v>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="18">
         <v>11.812749003984059</v>
       </c>
-      <c r="L25" s="23">
+      <c r="L25" s="21">
         <f>J25+K25</f>
         <v>139.95617529880477</v>
       </c>
@@ -3325,7 +3319,7 @@
       <c r="N25" s="8">
         <v>0.86852589641434264</v>
       </c>
-      <c r="O25" s="21">
+      <c r="O25" s="18">
         <f>(AC25+AF25)/C25</f>
         <v>10.46215139442231</v>
       </c>
@@ -3351,7 +3345,7 @@
       <c r="V25" t="s">
         <v>41</v>
       </c>
-      <c r="W25" s="24">
+      <c r="W25" s="20">
         <v>64.541832669322702</v>
       </c>
       <c r="X25">
@@ -3378,12 +3372,12 @@
       <c r="AE25">
         <v>1</v>
       </c>
-      <c r="AF25">
+      <c r="AF25" s="21">
         <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A26" s="21">
+      <c r="A26" s="18">
         <v>33</v>
       </c>
       <c r="B26" t="s">
@@ -3392,7 +3386,7 @@
       <c r="C26" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E26" t="s">
@@ -3409,9 +3403,9 @@
       <c r="H26">
         <v>37924</v>
       </c>
-      <c r="I26" s="23">
-        <f>(W26+Z26+AC26)</f>
-        <v>37936.167330677294</v>
+      <c r="I26" s="21">
+        <f>Y26+AB26+AE26</f>
+        <v>3104</v>
       </c>
       <c r="J26">
         <v>129.04780876494021</v>
@@ -3419,7 +3413,7 @@
       <c r="K26">
         <v>11.533864541832671</v>
       </c>
-      <c r="L26" s="24">
+      <c r="L26" s="20">
         <f>J26+K26</f>
         <v>140.58167330677287</v>
       </c>
@@ -3429,17 +3423,17 @@
       <c r="N26" s="21">
         <v>0.82868525896414347</v>
       </c>
-      <c r="O26" s="21">
+      <c r="O26" s="18">
         <f>(AC26+AF26)/C26</f>
         <v>10.509960159362549</v>
       </c>
-      <c r="P26" s="21">
+      <c r="P26" s="18">
         <v>0.17928286852589639</v>
       </c>
       <c r="Q26">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="R26" s="21">
+      <c r="R26" s="18">
         <f>AF26/C26</f>
         <v>0.18326693227091634</v>
       </c>
@@ -3455,7 +3449,7 @@
       <c r="V26" t="s">
         <v>32</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="21">
         <v>58.167330677290842</v>
       </c>
       <c r="X26">
@@ -3473,7 +3467,7 @@
       <c r="AB26">
         <v>208</v>
       </c>
-      <c r="AC26" s="21">
+      <c r="AC26" s="8">
         <v>2592</v>
       </c>
       <c r="AD26">
@@ -3482,7 +3476,7 @@
       <c r="AE26">
         <v>1</v>
       </c>
-      <c r="AF26" s="21">
+      <c r="AF26" s="18">
         <v>46</v>
       </c>
     </row>
@@ -3496,7 +3490,7 @@
       <c r="C27" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E27" t="s">
@@ -3506,7 +3500,7 @@
         <f>(E27-D27)</f>
         <v>35359989160</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="18">
         <f>(E27/D27)*100</f>
         <v>126.8899505319056</v>
       </c>
@@ -3514,13 +3508,13 @@
         <v>37887</v>
       </c>
       <c r="I27" s="21">
-        <f>(W27+Z27+AC27)</f>
-        <v>37902.77689243028</v>
+        <f>Y27+AB27+AE27</f>
+        <v>3168</v>
       </c>
       <c r="J27">
         <v>128.7250996015936</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="21">
         <v>11.749003984063741</v>
       </c>
       <c r="L27" s="10">
@@ -3533,7 +3527,7 @@
       <c r="N27" s="21">
         <v>0.86454183266932272</v>
       </c>
-      <c r="O27" s="23">
+      <c r="O27" s="21">
         <f>(AC27+AF27)/C27</f>
         <v>10.47011952191235</v>
       </c>
@@ -3543,7 +3537,7 @@
       <c r="Q27">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="R27" s="21">
+      <c r="R27" s="18">
         <f>AF27/C27</f>
         <v>0.15936254980079681</v>
       </c>
@@ -3553,7 +3547,7 @@
       <c r="T27" t="s">
         <v>37</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="21">
         <v>32.270916334661351</v>
       </c>
       <c r="V27" t="s">
@@ -3577,7 +3571,7 @@
       <c r="AB27">
         <v>217</v>
       </c>
-      <c r="AC27" s="23">
+      <c r="AC27" s="21">
         <v>2588</v>
       </c>
       <c r="AD27">
@@ -3591,7 +3585,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="A28" s="21">
         <v>35</v>
       </c>
       <c r="B28" t="s">
@@ -3610,7 +3604,7 @@
         <f>(E28-D28)</f>
         <v>33233242100</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="21">
         <f>(E28/D28)*100</f>
         <v>125.272638858576</v>
       </c>
@@ -3618,8 +3612,8 @@
         <v>37875</v>
       </c>
       <c r="I28" s="21">
-        <f>(W28+Z28+AC28)</f>
-        <v>37892.378486055779</v>
+        <f>Y28+AB28+AE28</f>
+        <v>3104</v>
       </c>
       <c r="J28">
         <v>128.88446215139439</v>
@@ -3641,10 +3635,10 @@
         <f>(AC28+AF28)/C28</f>
         <v>10.458167330677291</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="21">
         <v>0.13545816733067731</v>
       </c>
-      <c r="Q28" s="21">
+      <c r="Q28" s="18">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="R28" s="21">
@@ -3657,13 +3651,13 @@
       <c r="T28" t="s">
         <v>51</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="21">
         <v>34.661354581673308</v>
       </c>
       <c r="V28" t="s">
         <v>87</v>
       </c>
-      <c r="W28" s="21">
+      <c r="W28" s="18">
         <v>55.378486055776889</v>
       </c>
       <c r="X28">
@@ -3704,7 +3698,7 @@
       <c r="C29" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E29" t="s">
@@ -3721,9 +3715,9 @@
       <c r="H29">
         <v>37914</v>
       </c>
-      <c r="I29">
-        <f>(W29+Z29+AC29)</f>
-        <v>37926.760956175298</v>
+      <c r="I29" s="21">
+        <f>Y29+AB29+AE29</f>
+        <v>3127</v>
       </c>
       <c r="J29">
         <v>128.90438247011949</v>
@@ -3745,13 +3739,13 @@
         <f>(AC29+AF29)/C29</f>
         <v>10.533864541832669</v>
       </c>
-      <c r="P29" s="21">
+      <c r="P29" s="18">
         <v>0.1633466135458167</v>
       </c>
       <c r="Q29">
         <v>2.3904382470119521E-2</v>
       </c>
-      <c r="R29" s="21">
+      <c r="R29" s="18">
         <f>AF29/C29</f>
         <v>0.18725099601593626</v>
       </c>
@@ -3761,7 +3755,7 @@
       <c r="T29" t="s">
         <v>37</v>
       </c>
-      <c r="U29" s="23">
+      <c r="U29" s="21">
         <v>32.270916334661351</v>
       </c>
       <c r="V29" t="s">
@@ -3785,13 +3779,13 @@
       <c r="AB29">
         <v>206</v>
       </c>
-      <c r="AC29" s="21">
+      <c r="AC29" s="8">
         <v>2597</v>
       </c>
       <c r="AD29">
         <v>41</v>
       </c>
-      <c r="AE29">
+      <c r="AE29" s="10">
         <v>6</v>
       </c>
       <c r="AF29" s="9">
@@ -3799,7 +3793,7 @@
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A30" s="21">
+      <c r="A30" s="18">
         <v>37</v>
       </c>
       <c r="B30" t="s">
@@ -3826,13 +3820,13 @@
         <v>37858</v>
       </c>
       <c r="I30" s="21">
-        <f>(W30+Z30+AC30)</f>
-        <v>37876.573705179282</v>
+        <f>Y30+AB30+AE30</f>
+        <v>3165</v>
       </c>
       <c r="J30">
         <v>128.58964143426289</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="21">
         <v>11.768924302788839</v>
       </c>
       <c r="L30" s="8">
@@ -3842,10 +3836,10 @@
       <c r="M30">
         <v>10.31872509960159</v>
       </c>
-      <c r="N30" s="21">
+      <c r="N30" s="18">
         <v>0.82071713147410363</v>
       </c>
-      <c r="O30" s="21">
+      <c r="O30" s="18">
         <f>(AC30+AF30)/C30</f>
         <v>10.47011952191235</v>
       </c>
@@ -3855,7 +3849,7 @@
       <c r="Q30">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="R30" s="21">
+      <c r="R30" s="18">
         <f>AF30/C30</f>
         <v>0.15139442231075698</v>
       </c>
@@ -3889,13 +3883,13 @@
       <c r="AB30">
         <v>206</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="8">
         <v>2590</v>
       </c>
       <c r="AD30">
         <v>33</v>
       </c>
-      <c r="AE30">
+      <c r="AE30" s="8">
         <v>5</v>
       </c>
       <c r="AF30" s="21">
@@ -3903,7 +3897,7 @@
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A31" s="21">
+      <c r="A31" s="18">
         <v>38</v>
       </c>
       <c r="B31" t="s">
@@ -3912,7 +3906,7 @@
       <c r="C31" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E31" t="s">
@@ -3930,13 +3924,13 @@
         <v>37880</v>
       </c>
       <c r="I31" s="21">
-        <f>(W31+Z31+AC31)</f>
-        <v>37896.167330677294</v>
+        <f>Y31+AB31+AE31</f>
+        <v>3196</v>
       </c>
       <c r="J31">
         <v>128.53784860557769</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K31" s="21">
         <v>11.89243027888446</v>
       </c>
       <c r="L31" s="8">
@@ -3959,7 +3953,7 @@
       <c r="Q31">
         <v>2.3904382470119521E-2</v>
       </c>
-      <c r="R31" s="21">
+      <c r="R31" s="18">
         <f>AF31/C31</f>
         <v>0.16733067729083664</v>
       </c>
@@ -3969,7 +3963,7 @@
       <c r="T31" t="s">
         <v>48</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="21">
         <v>33.466135458167329</v>
       </c>
       <c r="V31" t="s">
@@ -3993,13 +3987,13 @@
       <c r="AB31">
         <v>205</v>
       </c>
-      <c r="AC31" s="23">
+      <c r="AC31" s="8">
         <v>2590</v>
       </c>
       <c r="AD31">
         <v>36</v>
       </c>
-      <c r="AE31">
+      <c r="AE31" s="10">
         <v>6</v>
       </c>
       <c r="AF31" s="21">
@@ -4007,7 +4001,7 @@
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="A32" s="21">
         <v>39</v>
       </c>
       <c r="B32" t="s">
@@ -4026,16 +4020,16 @@
         <f>(E32-D32)</f>
         <v>29938094660</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="21">
         <f>(E32/D32)*100</f>
         <v>122.76680235347976</v>
       </c>
       <c r="H32">
         <v>37872</v>
       </c>
-      <c r="I32" s="10">
-        <f>(W32+Z32+AC32)</f>
-        <v>37890.573705179282</v>
+      <c r="I32" s="21">
+        <f>Y32+AB32+AE32</f>
+        <v>3231</v>
       </c>
       <c r="J32">
         <v>128.36254980079681</v>
@@ -4050,14 +4044,14 @@
       <c r="M32">
         <v>10.314741035856571</v>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="14">
         <v>0.8127490039840638</v>
       </c>
       <c r="O32" s="21">
         <f>(AC32+AF32)/C32</f>
         <v>10.466135458167331</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="21">
         <v>0.14741035856573709</v>
       </c>
       <c r="Q32">
@@ -4097,16 +4091,16 @@
       <c r="AB32">
         <v>204</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="21">
         <v>2589</v>
       </c>
       <c r="AD32">
         <v>37</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="21">
         <v>1</v>
       </c>
-      <c r="AF32">
+      <c r="AF32" s="21">
         <v>38</v>
       </c>
     </row>
@@ -4120,7 +4114,7 @@
       <c r="C33" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E33" t="s">
@@ -4137,24 +4131,24 @@
       <c r="H33">
         <v>37866</v>
       </c>
-      <c r="I33">
-        <f>(W33+Z33+AC33)</f>
-        <v>37875.972111553783</v>
+      <c r="I33" s="21">
+        <f>Y33+AB33+AE33</f>
+        <v>2946</v>
       </c>
       <c r="J33">
         <v>129.36653386454179</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="21">
         <v>10.9402390438247</v>
       </c>
-      <c r="L33" s="21">
+      <c r="L33" s="18">
         <f>J33+K33</f>
         <v>140.3067729083665</v>
       </c>
       <c r="M33">
         <v>10.366533864541831</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="14">
         <v>0.79282868525896411</v>
       </c>
       <c r="O33" s="10">
@@ -4183,7 +4177,7 @@
       <c r="V33" t="s">
         <v>49</v>
       </c>
-      <c r="W33" s="21">
+      <c r="W33" s="18">
         <v>56.972111553784863</v>
       </c>
       <c r="X33">
@@ -4201,7 +4195,7 @@
       <c r="AB33">
         <v>199</v>
       </c>
-      <c r="AC33" s="21">
+      <c r="AC33" s="10">
         <v>2602</v>
       </c>
       <c r="AD33">
@@ -4215,7 +4209,7 @@
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A34">
+      <c r="A34" s="21">
         <v>41</v>
       </c>
       <c r="B34" t="s">
@@ -4224,7 +4218,7 @@
       <c r="C34" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E34" t="s">
@@ -4242,8 +4236,8 @@
         <v>37866</v>
       </c>
       <c r="I34" s="21">
-        <f>(W34+Z34+AC34)</f>
-        <v>37882.346613545815</v>
+        <f>Y34+AB34+AE34</f>
+        <v>3131</v>
       </c>
       <c r="J34">
         <v>128.68127490039839</v>
@@ -4258,14 +4252,14 @@
       <c r="M34">
         <v>10.366533864541831</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34">
         <v>0.82868525896414347</v>
       </c>
       <c r="O34" s="10">
         <f>(AC34+AF34)/C34</f>
         <v>10.553784860557769</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="21">
         <v>0.16733067729083659</v>
       </c>
       <c r="Q34">
@@ -4305,13 +4299,13 @@
       <c r="AB34">
         <v>208</v>
       </c>
-      <c r="AC34" s="21">
+      <c r="AC34" s="10">
         <v>2602</v>
       </c>
       <c r="AD34">
         <v>42</v>
       </c>
-      <c r="AE34">
+      <c r="AE34" s="8">
         <v>5</v>
       </c>
       <c r="AF34" s="9">
@@ -4328,7 +4322,7 @@
       <c r="C35" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E35" t="s">
@@ -4345,9 +4339,9 @@
       <c r="H35">
         <v>37866</v>
       </c>
-      <c r="I35">
-        <f>(W35+Z35+AC35)</f>
-        <v>37876.768924302785</v>
+      <c r="I35" s="21">
+        <f>Y35+AB35+AE35</f>
+        <v>3170</v>
       </c>
       <c r="J35">
         <v>128.45019920318731</v>
@@ -4362,7 +4356,7 @@
       <c r="M35">
         <v>10.366533864541831</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35">
         <v>0.76494023904382469</v>
       </c>
       <c r="O35" s="10">
@@ -4385,7 +4379,7 @@
       <c r="T35" t="s">
         <v>80</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="21">
         <v>32.669322709163353</v>
       </c>
       <c r="V35" t="s">
@@ -4409,13 +4403,13 @@
       <c r="AB35">
         <v>192</v>
       </c>
-      <c r="AC35" s="21">
+      <c r="AC35" s="10">
         <v>2602</v>
       </c>
       <c r="AD35">
         <v>45</v>
       </c>
-      <c r="AE35">
+      <c r="AE35" s="21">
         <v>2</v>
       </c>
       <c r="AF35" s="9">
@@ -4432,7 +4426,7 @@
       <c r="C36" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E36" t="s">
@@ -4449,9 +4443,9 @@
       <c r="H36">
         <v>37866</v>
       </c>
-      <c r="I36" s="8">
-        <f>(W36+Z36+AC36)</f>
-        <v>37881.948207171314</v>
+      <c r="I36" s="21">
+        <f>Y36+AB36+AE36</f>
+        <v>3212</v>
       </c>
       <c r="J36">
         <v>128.3585657370518</v>
@@ -4459,7 +4453,7 @@
       <c r="K36" s="8">
         <v>11.94820717131474</v>
       </c>
-      <c r="L36" s="21">
+      <c r="L36" s="18">
         <f>J36+K36</f>
         <v>140.30677290836655</v>
       </c>
@@ -4476,10 +4470,10 @@
       <c r="P36">
         <v>0.16733067729083659</v>
       </c>
-      <c r="Q36" s="24">
+      <c r="Q36" s="20">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="R36" s="21">
+      <c r="R36" s="18">
         <f>AF36/C36</f>
         <v>0.18725099601593626</v>
       </c>
@@ -4513,13 +4507,13 @@
       <c r="AB36">
         <v>208</v>
       </c>
-      <c r="AC36">
+      <c r="AC36" s="10">
         <v>2602</v>
       </c>
       <c r="AD36">
         <v>42</v>
       </c>
-      <c r="AE36">
+      <c r="AE36" s="8">
         <v>5</v>
       </c>
       <c r="AF36" s="9">
@@ -4527,7 +4521,7 @@
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A37" s="21">
+      <c r="A37" s="18">
         <v>44</v>
       </c>
       <c r="B37" t="s">
@@ -4536,7 +4530,7 @@
       <c r="C37" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="21" t="s">
         <v>26</v>
       </c>
       <c r="E37" t="s">
@@ -4553,14 +4547,14 @@
       <c r="H37">
         <v>37866</v>
       </c>
-      <c r="I37">
-        <f>(W37+Z37+AC37)</f>
-        <v>37877.167330677294</v>
+      <c r="I37" s="21">
+        <f>Y37+AB37+AE37</f>
+        <v>3078</v>
       </c>
       <c r="J37">
         <v>128.82071713147411</v>
       </c>
-      <c r="K37" s="21">
+      <c r="K37" s="18">
         <v>11.48605577689243</v>
       </c>
       <c r="L37" s="21">
@@ -4583,7 +4577,7 @@
       <c r="Q37">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="R37" s="21">
+      <c r="R37" s="18">
         <f>AF37/C37</f>
         <v>0.18725099601593626</v>
       </c>
@@ -4593,13 +4587,13 @@
       <c r="T37" t="s">
         <v>51</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="21">
         <v>34.661354581673308</v>
       </c>
       <c r="V37" t="s">
         <v>32</v>
       </c>
-      <c r="W37" s="21">
+      <c r="W37" s="18">
         <v>58.167330677290842</v>
       </c>
       <c r="X37">
@@ -4614,16 +4608,16 @@
       <c r="AA37">
         <v>2224</v>
       </c>
-      <c r="AB37" s="21">
+      <c r="AB37" s="18">
         <v>190</v>
       </c>
-      <c r="AC37" s="21">
+      <c r="AC37" s="10">
         <v>2602</v>
       </c>
       <c r="AD37">
         <v>42</v>
       </c>
-      <c r="AE37">
+      <c r="AE37" s="8">
         <v>5</v>
       </c>
       <c r="AF37" s="9">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFF39CB-401C-4A70-95D2-0E66094197F2}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E887D-6B92-4824-909E-60625FAD6C52}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1270" windowWidth="30890" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AK$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AM$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="86">
   <si>
     <t>Trung bình/Kỳ</t>
   </si>
@@ -281,9 +281,18 @@
  &gt;=90%</t>
   </si>
   <si>
-    <t>Số chu kỳ 10 kỳ 
+    <t>Tỉ lệ chu kỳ 10 kỳ 
 thu hồi 
 10 &gt;=90%</t>
+  </si>
+  <si>
+    <t>Số chu kỳ 10 kỳ thu hồi
+ &gt;=100%</t>
+  </si>
+  <si>
+    <t>Tỉ lệ chu kỳ 10 kỳ 
+thu hồi 
+10 &gt;=100%</t>
   </si>
 </sst>
 </file>
@@ -344,7 +353,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,6 +438,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -443,7 +458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -502,6 +517,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -515,6 +531,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -797,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9" style="21" customWidth="1"/>
@@ -810,45 +829,46 @@
     <col min="16" max="16" width="8" style="21" customWidth="1"/>
     <col min="17" max="17" width="9" style="21" customWidth="1"/>
     <col min="18" max="20" width="9.1796875" style="21" customWidth="1"/>
-    <col min="21" max="21" width="11.36328125" style="21" customWidth="1"/>
-    <col min="22" max="22" width="11.81640625" style="21" customWidth="1"/>
-    <col min="23" max="27" width="9.26953125" style="21" customWidth="1"/>
-    <col min="28" max="28" width="9.26953125" style="22" customWidth="1"/>
-    <col min="29" max="31" width="9.26953125" style="21" customWidth="1"/>
-    <col min="32" max="34" width="18.7265625" style="20" customWidth="1"/>
-    <col min="35" max="37" width="6.54296875" style="21" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="21" customWidth="1"/>
+    <col min="22" max="22" width="16.90625" style="21" customWidth="1"/>
+    <col min="23" max="24" width="16.90625" style="28" customWidth="1"/>
+    <col min="25" max="29" width="9.26953125" style="21" customWidth="1"/>
+    <col min="30" max="30" width="9.26953125" style="22" customWidth="1"/>
+    <col min="31" max="33" width="9.26953125" style="21" customWidth="1"/>
+    <col min="34" max="36" width="18.7265625" style="20" customWidth="1"/>
+    <col min="37" max="39" width="6.54296875" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="G1" s="33" t="s">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="G1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="W1" s="28" t="s">
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Y1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="31" t="s">
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="30" t="s">
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
     </row>
-    <row r="2" spans="1:34" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -909,50 +929,56 @@
       <c r="T2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="V2" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="12">
+      <c r="W2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="12">
         <v>3</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="AA2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="12">
+      <c r="AB2" s="12">
         <v>4</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AC2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="AB2" s="13" t="s">
+      <c r="AD2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AC2" s="12">
+      <c r="AE2" s="12">
         <v>5</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AF2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AG2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AH2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AI2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AH2" s="6" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" s="21">
         <v>10</v>
       </c>
@@ -1019,44 +1045,46 @@
       <c r="V3" s="21">
         <v>92</v>
       </c>
-      <c r="W3">
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3">
         <v>32343</v>
       </c>
-      <c r="X3">
+      <c r="Z3">
         <v>2941</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>35284</v>
       </c>
-      <c r="Z3">
+      <c r="AB3">
         <v>2182</v>
       </c>
-      <c r="AA3">
+      <c r="AC3">
         <v>204</v>
       </c>
-      <c r="AB3" s="7">
+      <c r="AD3" s="7">
         <v>2590</v>
       </c>
-      <c r="AC3">
+      <c r="AE3">
         <v>45</v>
       </c>
-      <c r="AD3" s="9">
+      <c r="AF3" s="9">
         <v>6</v>
       </c>
-      <c r="AE3" s="16">
+      <c r="AG3" s="16">
         <v>51</v>
       </c>
-      <c r="AF3" s="24">
+      <c r="AH3" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG3" s="24">
+      <c r="AI3" s="24">
         <v>184158707120</v>
       </c>
-      <c r="AH3" s="24">
+      <c r="AJ3" s="24">
         <v>52737617120</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>11</v>
       </c>
@@ -1123,44 +1151,46 @@
       <c r="V4" s="21">
         <v>84</v>
       </c>
-      <c r="W4">
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4">
         <v>32250</v>
       </c>
-      <c r="X4">
+      <c r="Z4">
         <v>2911</v>
       </c>
-      <c r="Y4">
+      <c r="AA4">
         <v>35161</v>
       </c>
-      <c r="Z4">
+      <c r="AB4">
         <v>2288</v>
       </c>
-      <c r="AA4">
+      <c r="AC4">
         <v>180</v>
       </c>
-      <c r="AB4" s="7">
+      <c r="AD4" s="7">
         <v>2596</v>
       </c>
-      <c r="AC4">
+      <c r="AE4">
         <v>32</v>
       </c>
-      <c r="AD4">
+      <c r="AF4">
         <v>0</v>
       </c>
-      <c r="AE4" s="21">
+      <c r="AG4" s="21">
         <v>32</v>
       </c>
-      <c r="AF4" s="23">
+      <c r="AH4" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG4" s="24">
+      <c r="AI4" s="24">
         <v>148641587120</v>
       </c>
-      <c r="AH4" s="24">
+      <c r="AJ4" s="24">
         <v>17220497120</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>12</v>
       </c>
@@ -1227,44 +1257,46 @@
       <c r="V5" s="21">
         <v>92</v>
       </c>
-      <c r="W5">
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5">
         <v>32308</v>
       </c>
-      <c r="X5">
+      <c r="Z5">
         <v>2965</v>
       </c>
-      <c r="Y5">
+      <c r="AA5">
         <v>35273</v>
       </c>
-      <c r="Z5">
+      <c r="AB5">
         <v>2198</v>
       </c>
-      <c r="AA5">
+      <c r="AC5">
         <v>200</v>
       </c>
-      <c r="AB5" s="21">
+      <c r="AD5" s="21">
         <v>2586</v>
       </c>
-      <c r="AC5">
+      <c r="AE5">
         <v>46</v>
       </c>
-      <c r="AD5" s="21">
+      <c r="AF5" s="21">
         <v>1</v>
       </c>
-      <c r="AE5" s="8">
+      <c r="AG5" s="8">
         <v>47</v>
       </c>
-      <c r="AF5" s="23">
+      <c r="AH5" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG5" s="24">
+      <c r="AI5" s="24">
         <v>171216874920</v>
       </c>
-      <c r="AH5" s="24">
+      <c r="AJ5" s="24">
         <v>39795784920</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" s="21">
         <v>13</v>
       </c>
@@ -1331,44 +1363,46 @@
       <c r="V6" s="21">
         <v>88</v>
       </c>
-      <c r="W6">
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6">
         <v>32142</v>
       </c>
-      <c r="X6">
+      <c r="Z6">
         <v>2967</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
         <v>35109</v>
       </c>
-      <c r="Z6">
+      <c r="AB6">
         <v>2204</v>
       </c>
-      <c r="AA6">
+      <c r="AC6">
         <v>209</v>
       </c>
-      <c r="AB6" s="21">
+      <c r="AD6" s="21">
         <v>2569</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <v>35</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <v>4</v>
       </c>
-      <c r="AE6" s="21">
+      <c r="AG6" s="21">
         <v>39</v>
       </c>
-      <c r="AF6" s="23">
+      <c r="AH6" s="23">
         <v>130897500000</v>
       </c>
-      <c r="AG6" s="24">
+      <c r="AI6" s="24">
         <v>167220295100</v>
       </c>
-      <c r="AH6" s="24">
+      <c r="AJ6" s="24">
         <v>36322795100</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>14</v>
       </c>
@@ -1435,44 +1469,46 @@
       <c r="V7" s="21">
         <v>88</v>
       </c>
-      <c r="W7">
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7">
         <v>32188</v>
       </c>
-      <c r="X7">
+      <c r="Z7">
         <v>3015</v>
       </c>
-      <c r="Y7">
+      <c r="AA7">
         <v>35203</v>
       </c>
-      <c r="Z7">
+      <c r="AB7">
         <v>2217</v>
       </c>
-      <c r="AA7">
+      <c r="AC7">
         <v>215</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AD7" s="7">
         <v>2592</v>
       </c>
-      <c r="AC7">
+      <c r="AE7">
         <v>38</v>
       </c>
-      <c r="AD7">
+      <c r="AF7">
         <v>2</v>
       </c>
-      <c r="AE7">
+      <c r="AG7">
         <v>40</v>
       </c>
-      <c r="AF7" s="23">
+      <c r="AH7" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG7" s="24">
+      <c r="AI7" s="24">
         <v>166937578280</v>
       </c>
-      <c r="AH7" s="24">
+      <c r="AJ7" s="24">
         <v>35516488280</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>15</v>
       </c>
@@ -1539,44 +1575,46 @@
       <c r="V8" s="21">
         <v>92</v>
       </c>
-      <c r="W8">
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8">
         <v>32303</v>
       </c>
-      <c r="X8">
+      <c r="Z8">
         <v>2914</v>
       </c>
-      <c r="Y8">
+      <c r="AA8">
         <v>35217</v>
       </c>
-      <c r="Z8">
+      <c r="AB8">
         <v>2181</v>
       </c>
-      <c r="AA8" s="14">
+      <c r="AC8" s="14">
         <v>233</v>
       </c>
-      <c r="AB8" s="9">
+      <c r="AD8" s="9">
         <v>2602</v>
       </c>
-      <c r="AC8">
+      <c r="AE8">
         <v>39</v>
       </c>
-      <c r="AD8" s="15">
+      <c r="AF8" s="15">
         <v>8</v>
       </c>
-      <c r="AE8" s="8">
+      <c r="AG8" s="8">
         <v>47</v>
       </c>
-      <c r="AF8" s="23">
+      <c r="AH8" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG8" s="24">
+      <c r="AI8" s="24">
         <v>186740852920</v>
       </c>
-      <c r="AH8" s="24">
+      <c r="AJ8" s="24">
         <v>55319762920</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>16</v>
       </c>
@@ -1643,44 +1681,46 @@
       <c r="V9" s="21">
         <v>88</v>
       </c>
-      <c r="W9">
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9">
         <v>32243</v>
       </c>
-      <c r="X9">
+      <c r="Z9">
         <v>2989</v>
       </c>
-      <c r="Y9">
+      <c r="AA9">
         <v>35232</v>
       </c>
-      <c r="Z9">
+      <c r="AB9">
         <v>2208</v>
       </c>
-      <c r="AA9">
+      <c r="AC9">
         <v>205</v>
       </c>
-      <c r="AB9">
+      <c r="AD9">
         <v>2589</v>
       </c>
-      <c r="AC9">
+      <c r="AE9">
         <v>39</v>
       </c>
-      <c r="AD9" s="7">
+      <c r="AF9" s="7">
         <v>5</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>44</v>
       </c>
-      <c r="AF9" s="23">
+      <c r="AH9" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG9" s="24">
+      <c r="AI9" s="24">
         <v>174643537020</v>
       </c>
-      <c r="AH9" s="24">
+      <c r="AJ9" s="24">
         <v>43222447020</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>17</v>
       </c>
@@ -1747,44 +1787,46 @@
       <c r="V10" s="21">
         <v>92</v>
       </c>
-      <c r="W10">
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10">
         <v>32155</v>
       </c>
-      <c r="X10">
+      <c r="Z10">
         <v>2918</v>
       </c>
-      <c r="Y10">
+      <c r="AA10">
         <v>35073</v>
       </c>
-      <c r="Z10">
+      <c r="AB10">
         <v>2208</v>
       </c>
-      <c r="AA10">
+      <c r="AC10">
         <v>209</v>
       </c>
-      <c r="AB10" s="7">
+      <c r="AD10" s="7">
         <v>2581</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <v>37</v>
       </c>
-      <c r="AD10">
+      <c r="AF10">
         <v>4</v>
       </c>
-      <c r="AE10">
+      <c r="AG10">
         <v>41</v>
       </c>
-      <c r="AF10" s="23">
+      <c r="AH10" s="23">
         <v>130897500000</v>
       </c>
-      <c r="AG10" s="24">
+      <c r="AI10" s="24">
         <v>169505684460</v>
       </c>
-      <c r="AH10" s="24">
+      <c r="AJ10" s="24">
         <v>38608184460</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>18</v>
       </c>
@@ -1851,44 +1893,46 @@
       <c r="V11" s="21">
         <v>88</v>
       </c>
-      <c r="W11">
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11">
         <v>32333</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>2855</v>
       </c>
-      <c r="Y11">
+      <c r="AA11">
         <v>35188</v>
       </c>
-      <c r="Z11">
+      <c r="AB11">
         <v>2223</v>
       </c>
-      <c r="AA11">
+      <c r="AC11">
         <v>217</v>
       </c>
-      <c r="AB11" s="7">
+      <c r="AD11" s="7">
         <v>2604</v>
       </c>
-      <c r="AC11">
+      <c r="AE11">
         <v>37</v>
       </c>
-      <c r="AD11" s="21">
+      <c r="AF11" s="21">
         <v>4</v>
       </c>
-      <c r="AE11" s="21">
+      <c r="AG11" s="21">
         <v>41</v>
       </c>
-      <c r="AF11" s="23">
+      <c r="AH11" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG11" s="24">
+      <c r="AI11" s="24">
         <v>170803812640</v>
       </c>
-      <c r="AH11" s="24">
+      <c r="AJ11" s="24">
         <v>39382722640</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>19</v>
       </c>
@@ -1955,44 +1999,46 @@
       <c r="V12" s="21">
         <v>84</v>
       </c>
-      <c r="W12">
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12">
         <v>32262</v>
       </c>
-      <c r="X12">
+      <c r="Z12">
         <v>2923</v>
       </c>
-      <c r="Y12">
+      <c r="AA12">
         <v>35185</v>
       </c>
-      <c r="Z12">
+      <c r="AB12">
         <v>2274</v>
       </c>
-      <c r="AA12">
+      <c r="AC12">
         <v>187</v>
       </c>
-      <c r="AB12" s="7">
+      <c r="AD12" s="7">
         <v>2593</v>
       </c>
-      <c r="AC12">
+      <c r="AE12">
         <v>31</v>
       </c>
-      <c r="AD12">
+      <c r="AF12">
         <v>2</v>
       </c>
-      <c r="AE12" s="21">
+      <c r="AG12" s="21">
         <v>33</v>
       </c>
-      <c r="AF12" s="23">
+      <c r="AH12" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG12" s="24">
+      <c r="AI12" s="24">
         <v>153958977980</v>
       </c>
-      <c r="AH12" s="24">
+      <c r="AJ12" s="24">
         <v>22537887980</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="27">
         <v>20</v>
       </c>
@@ -2059,44 +2105,46 @@
       <c r="V13" s="17">
         <v>100</v>
       </c>
-      <c r="W13">
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13">
         <v>32139</v>
       </c>
-      <c r="X13">
+      <c r="Z13">
         <v>2972</v>
       </c>
-      <c r="Y13">
+      <c r="AA13">
         <v>35111</v>
       </c>
-      <c r="Z13">
+      <c r="AB13">
         <v>2186</v>
       </c>
-      <c r="AA13">
+      <c r="AC13">
         <v>197</v>
       </c>
-      <c r="AB13" s="7">
+      <c r="AD13" s="7">
         <v>2587</v>
       </c>
-      <c r="AC13">
+      <c r="AE13">
         <v>50</v>
       </c>
-      <c r="AD13">
+      <c r="AF13">
         <v>1</v>
       </c>
-      <c r="AE13" s="16">
+      <c r="AG13" s="16">
         <v>51</v>
       </c>
-      <c r="AF13" s="23">
+      <c r="AH13" s="23">
         <v>130897500000</v>
       </c>
-      <c r="AG13" s="24">
+      <c r="AI13" s="24">
         <v>175465634060</v>
       </c>
-      <c r="AH13" s="24">
+      <c r="AJ13" s="24">
         <v>44568134060</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>21</v>
       </c>
@@ -2163,44 +2211,46 @@
       <c r="V14" s="21">
         <v>72</v>
       </c>
-      <c r="W14">
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14">
         <v>32217</v>
       </c>
-      <c r="X14">
+      <c r="Z14">
         <v>2989</v>
       </c>
-      <c r="Y14">
+      <c r="AA14">
         <v>35206</v>
       </c>
-      <c r="Z14">
+      <c r="AB14">
         <v>2275</v>
       </c>
-      <c r="AA14">
+      <c r="AC14">
         <v>177</v>
       </c>
-      <c r="AB14">
+      <c r="AD14">
         <v>2584</v>
       </c>
-      <c r="AC14">
+      <c r="AE14">
         <v>28</v>
       </c>
-      <c r="AD14" s="7">
+      <c r="AF14" s="7">
         <v>5</v>
       </c>
-      <c r="AE14">
+      <c r="AG14">
         <v>33</v>
       </c>
-      <c r="AF14" s="23">
+      <c r="AH14" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG14" s="24">
+      <c r="AI14" s="24">
         <v>157289866920</v>
       </c>
-      <c r="AH14" s="24">
+      <c r="AJ14" s="24">
         <v>25868776920</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>22</v>
       </c>
@@ -2267,44 +2317,46 @@
       <c r="V15">
         <v>84</v>
       </c>
-      <c r="W15">
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15">
         <v>32166</v>
       </c>
-      <c r="X15">
+      <c r="Z15">
         <v>2974</v>
       </c>
-      <c r="Y15">
+      <c r="AA15">
         <v>35140</v>
       </c>
-      <c r="Z15">
+      <c r="AB15">
         <v>2262</v>
       </c>
-      <c r="AA15">
+      <c r="AC15">
         <v>197</v>
       </c>
-      <c r="AB15" s="9">
+      <c r="AD15" s="9">
         <v>2615</v>
       </c>
-      <c r="AC15">
+      <c r="AE15">
         <v>38</v>
       </c>
-      <c r="AD15" s="21">
+      <c r="AF15" s="21">
         <v>1</v>
       </c>
-      <c r="AE15" s="21">
+      <c r="AG15" s="21">
         <v>39</v>
       </c>
-      <c r="AF15" s="23">
+      <c r="AH15" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG15" s="24">
+      <c r="AI15" s="24">
         <v>161643553900</v>
       </c>
-      <c r="AH15" s="24">
+      <c r="AJ15" s="24">
         <v>30222463900</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>23</v>
       </c>
@@ -2371,44 +2423,46 @@
       <c r="V16">
         <v>88</v>
       </c>
-      <c r="W16">
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16">
         <v>32235</v>
       </c>
-      <c r="X16">
+      <c r="Z16">
         <v>2952</v>
       </c>
-      <c r="Y16">
+      <c r="AA16">
         <v>35187</v>
       </c>
-      <c r="Z16">
+      <c r="AB16">
         <v>2243</v>
       </c>
-      <c r="AA16">
+      <c r="AC16">
         <v>208</v>
       </c>
-      <c r="AB16" s="7">
+      <c r="AD16" s="7">
         <v>2591</v>
       </c>
-      <c r="AC16">
+      <c r="AE16">
         <v>32</v>
       </c>
-      <c r="AD16">
+      <c r="AF16">
         <v>3</v>
       </c>
-      <c r="AE16" s="21">
+      <c r="AG16" s="21">
         <v>35</v>
       </c>
-      <c r="AF16" s="23">
+      <c r="AH16" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG16" s="24">
+      <c r="AI16" s="24">
         <v>161107982100</v>
       </c>
-      <c r="AH16" s="24">
+      <c r="AJ16" s="24">
         <v>29686892100</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>24</v>
       </c>
@@ -2475,44 +2529,46 @@
       <c r="V17" s="9">
         <v>96</v>
       </c>
-      <c r="W17">
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17">
         <v>32219</v>
       </c>
-      <c r="X17">
+      <c r="Z17">
         <v>2957</v>
       </c>
-      <c r="Y17">
+      <c r="AA17">
         <v>35176</v>
       </c>
-      <c r="Z17">
+      <c r="AB17">
         <v>2244</v>
       </c>
-      <c r="AA17" s="21">
+      <c r="AC17" s="21">
         <v>208</v>
       </c>
-      <c r="AB17" s="7">
+      <c r="AD17" s="7">
         <v>2596</v>
       </c>
-      <c r="AC17">
+      <c r="AE17">
         <v>36</v>
       </c>
-      <c r="AD17" s="21">
+      <c r="AF17" s="21">
         <v>0</v>
       </c>
-      <c r="AE17" s="21">
+      <c r="AG17" s="21">
         <v>36</v>
       </c>
-      <c r="AF17" s="23">
+      <c r="AH17" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG17" s="24">
+      <c r="AI17" s="24">
         <v>157811392240</v>
       </c>
-      <c r="AH17" s="24">
+      <c r="AJ17" s="24">
         <v>26390302240</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>25</v>
       </c>
@@ -2579,44 +2635,46 @@
       <c r="V18">
         <v>92</v>
       </c>
-      <c r="W18">
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18">
         <v>32337</v>
       </c>
-      <c r="X18">
+      <c r="Z18">
         <v>2880</v>
       </c>
-      <c r="Y18">
+      <c r="AA18">
         <v>35217</v>
       </c>
-      <c r="Z18">
+      <c r="AB18">
         <v>2213</v>
       </c>
-      <c r="AA18">
+      <c r="AC18">
         <v>216</v>
       </c>
-      <c r="AB18" s="7">
+      <c r="AD18" s="7">
         <v>2593</v>
       </c>
-      <c r="AC18">
+      <c r="AE18">
         <v>40</v>
       </c>
-      <c r="AD18">
+      <c r="AF18">
         <v>1</v>
       </c>
-      <c r="AE18">
+      <c r="AG18">
         <v>41</v>
       </c>
-      <c r="AF18" s="23">
+      <c r="AH18" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG18" s="24">
+      <c r="AI18" s="24">
         <v>166054694380</v>
       </c>
-      <c r="AH18" s="24">
+      <c r="AJ18" s="24">
         <v>34633604380</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>26</v>
       </c>
@@ -2683,44 +2741,46 @@
       <c r="V19">
         <v>92</v>
       </c>
-      <c r="W19">
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19">
         <v>32372</v>
       </c>
-      <c r="X19">
+      <c r="Z19">
         <v>2840</v>
       </c>
-      <c r="Y19">
+      <c r="AA19">
         <v>35212</v>
       </c>
-      <c r="Z19">
+      <c r="AB19">
         <v>2214</v>
       </c>
-      <c r="AA19">
+      <c r="AC19">
         <v>210</v>
       </c>
-      <c r="AB19" s="9">
+      <c r="AD19" s="9">
         <v>2604</v>
       </c>
-      <c r="AC19">
+      <c r="AE19">
         <v>43</v>
       </c>
-      <c r="AD19">
+      <c r="AF19">
         <v>2</v>
       </c>
-      <c r="AE19">
+      <c r="AG19">
         <v>45</v>
       </c>
-      <c r="AF19" s="24">
+      <c r="AH19" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG19" s="24">
+      <c r="AI19" s="24">
         <v>171413667160</v>
       </c>
-      <c r="AH19" s="24">
+      <c r="AJ19" s="24">
         <v>39992577160</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>27</v>
       </c>
@@ -2787,44 +2847,46 @@
       <c r="V20" s="17">
         <v>100</v>
       </c>
-      <c r="W20">
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20">
         <v>32342</v>
       </c>
-      <c r="X20">
+      <c r="Z20">
         <v>2878</v>
       </c>
-      <c r="Y20">
+      <c r="AA20">
         <v>35220</v>
       </c>
-      <c r="Z20">
+      <c r="AB20">
         <v>2222</v>
       </c>
-      <c r="AA20">
+      <c r="AC20">
         <v>196</v>
       </c>
-      <c r="AB20" s="9">
+      <c r="AD20" s="9">
         <v>2606</v>
       </c>
-      <c r="AC20">
+      <c r="AE20">
         <v>46</v>
       </c>
-      <c r="AD20">
+      <c r="AF20">
         <v>1</v>
       </c>
-      <c r="AE20" s="8">
+      <c r="AG20" s="8">
         <v>47</v>
       </c>
-      <c r="AF20" s="23">
+      <c r="AH20" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG20" s="24">
+      <c r="AI20" s="24">
         <v>170433084440</v>
       </c>
-      <c r="AH20" s="24">
+      <c r="AJ20" s="24">
         <v>39011994440</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>28</v>
       </c>
@@ -2891,44 +2953,46 @@
       <c r="V21" s="9">
         <v>96</v>
       </c>
-      <c r="W21">
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21">
         <v>32328</v>
       </c>
-      <c r="X21">
+      <c r="Z21">
         <v>2901</v>
       </c>
-      <c r="Y21">
+      <c r="AA21">
         <v>35229</v>
       </c>
-      <c r="Z21">
+      <c r="AB21">
         <v>2237</v>
       </c>
-      <c r="AA21">
+      <c r="AC21">
         <v>183</v>
       </c>
-      <c r="AB21" s="9">
+      <c r="AD21" s="9">
         <v>2600</v>
       </c>
-      <c r="AC21">
+      <c r="AE21">
         <v>43</v>
       </c>
-      <c r="AD21">
+      <c r="AF21">
         <v>2</v>
       </c>
-      <c r="AE21">
+      <c r="AG21">
         <v>45</v>
       </c>
-      <c r="AF21" s="23">
+      <c r="AH21" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG21" s="24">
+      <c r="AI21" s="24">
         <v>167688031760</v>
       </c>
-      <c r="AH21" s="24">
+      <c r="AJ21" s="24">
         <v>36266941760</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>29</v>
       </c>
@@ -2995,44 +3059,46 @@
       <c r="V22">
         <v>88</v>
       </c>
-      <c r="W22">
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22">
         <v>32304</v>
       </c>
-      <c r="X22">
+      <c r="Z22">
         <v>2873</v>
       </c>
-      <c r="Y22">
+      <c r="AA22">
         <v>35177</v>
       </c>
-      <c r="Z22">
+      <c r="AB22">
         <v>2249</v>
       </c>
-      <c r="AA22">
+      <c r="AC22">
         <v>205</v>
       </c>
-      <c r="AB22" s="16">
+      <c r="AD22" s="16">
         <v>2610</v>
       </c>
-      <c r="AC22">
+      <c r="AE22">
         <v>35</v>
       </c>
-      <c r="AD22" s="21">
+      <c r="AF22" s="21">
         <v>4</v>
       </c>
-      <c r="AE22">
+      <c r="AG22">
         <v>39</v>
       </c>
-      <c r="AF22" s="23">
+      <c r="AH22" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AG22" s="24">
+      <c r="AI22" s="24">
         <v>166820986360</v>
       </c>
-      <c r="AH22" s="24">
+      <c r="AJ22" s="24">
         <v>35399896360</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>30</v>
       </c>
@@ -3099,44 +3165,46 @@
       <c r="V23">
         <v>84</v>
       </c>
-      <c r="W23">
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23">
         <v>32299</v>
       </c>
-      <c r="X23">
+      <c r="Z23">
         <v>2933</v>
       </c>
-      <c r="Y23">
+      <c r="AA23">
         <v>35232</v>
       </c>
-      <c r="Z23">
+      <c r="AB23">
         <v>2208</v>
       </c>
-      <c r="AA23">
+      <c r="AC23">
         <v>219</v>
       </c>
-      <c r="AB23" s="21">
+      <c r="AD23" s="21">
         <v>2583</v>
       </c>
-      <c r="AC23">
+      <c r="AE23">
         <v>36</v>
       </c>
-      <c r="AD23" s="21">
+      <c r="AF23" s="21">
         <v>3</v>
       </c>
-      <c r="AE23" s="21">
+      <c r="AG23" s="21">
         <v>39</v>
       </c>
-      <c r="AF23" s="24">
+      <c r="AH23" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG23" s="24">
+      <c r="AI23" s="24">
         <v>167310505260</v>
       </c>
-      <c r="AH23" s="24">
+      <c r="AJ23" s="24">
         <v>35889415260</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>31</v>
       </c>
@@ -3203,44 +3271,46 @@
       <c r="V24">
         <v>88</v>
       </c>
-      <c r="W24">
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24">
         <v>32341</v>
       </c>
-      <c r="X24">
+      <c r="Z24">
         <v>2900</v>
       </c>
-      <c r="Y24">
+      <c r="AA24">
         <v>35241</v>
       </c>
-      <c r="Z24">
+      <c r="AB24">
         <v>2217</v>
       </c>
-      <c r="AA24">
+      <c r="AC24">
         <v>185</v>
       </c>
-      <c r="AB24" s="21">
+      <c r="AD24" s="21">
         <v>2594</v>
       </c>
-      <c r="AC24">
+      <c r="AE24">
         <v>47</v>
       </c>
-      <c r="AD24" s="21">
+      <c r="AF24" s="21">
         <v>1</v>
       </c>
-      <c r="AE24" s="7">
+      <c r="AG24" s="7">
         <v>48</v>
       </c>
-      <c r="AF24" s="24">
+      <c r="AH24" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG24" s="24">
+      <c r="AI24" s="24">
         <v>169944938680</v>
       </c>
-      <c r="AH24" s="24">
+      <c r="AJ24" s="24">
         <v>38523848680</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>32</v>
       </c>
@@ -3307,44 +3377,46 @@
       <c r="V25">
         <v>84</v>
       </c>
-      <c r="W25">
+      <c r="W25"/>
+      <c r="X25"/>
+      <c r="Y25">
         <v>32293</v>
       </c>
-      <c r="X25">
+      <c r="Z25">
         <v>2977</v>
       </c>
-      <c r="Y25">
+      <c r="AA25">
         <v>35270</v>
       </c>
-      <c r="Z25">
+      <c r="AB25">
         <v>2198</v>
       </c>
-      <c r="AA25">
+      <c r="AC25">
         <v>218</v>
       </c>
-      <c r="AB25" s="21">
+      <c r="AD25" s="21">
         <v>2592</v>
       </c>
-      <c r="AC25">
+      <c r="AE25">
         <v>43</v>
       </c>
-      <c r="AD25">
+      <c r="AF25">
         <v>1</v>
       </c>
-      <c r="AE25" s="21">
+      <c r="AG25" s="21">
         <v>44</v>
       </c>
-      <c r="AF25" s="24">
+      <c r="AH25" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG25" s="24">
+      <c r="AI25" s="24">
         <v>170463432200</v>
       </c>
-      <c r="AH25" s="24">
+      <c r="AJ25" s="24">
         <v>38964532200</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>33</v>
       </c>
@@ -3411,44 +3483,46 @@
       <c r="V26">
         <v>92</v>
       </c>
-      <c r="W26">
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26">
         <v>32391</v>
       </c>
-      <c r="X26">
+      <c r="Z26">
         <v>2895</v>
       </c>
-      <c r="Y26">
+      <c r="AA26">
         <v>35286</v>
       </c>
-      <c r="Z26">
+      <c r="AB26">
         <v>2200</v>
       </c>
-      <c r="AA26">
+      <c r="AC26">
         <v>208</v>
       </c>
-      <c r="AB26" s="7">
+      <c r="AD26" s="7">
         <v>2592</v>
       </c>
-      <c r="AC26">
+      <c r="AE26">
         <v>45</v>
       </c>
-      <c r="AD26">
+      <c r="AF26">
         <v>1</v>
       </c>
-      <c r="AE26">
+      <c r="AG26">
         <v>46</v>
       </c>
-      <c r="AF26" s="24">
+      <c r="AH26" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG26" s="24">
+      <c r="AI26" s="24">
         <v>170939923080</v>
       </c>
-      <c r="AH26" s="24">
+      <c r="AJ26" s="24">
         <v>39441023080</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>34</v>
       </c>
@@ -3515,44 +3589,46 @@
       <c r="V27" s="9">
         <v>96</v>
       </c>
-      <c r="W27">
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27">
         <v>32310</v>
       </c>
-      <c r="X27">
+      <c r="Z27">
         <v>2949</v>
       </c>
-      <c r="Y27">
+      <c r="AA27">
         <v>35259</v>
       </c>
-      <c r="Z27">
+      <c r="AB27">
         <v>2211</v>
       </c>
-      <c r="AA27">
+      <c r="AC27">
         <v>217</v>
       </c>
-      <c r="AB27" s="21">
+      <c r="AD27" s="21">
         <v>2588</v>
       </c>
-      <c r="AC27">
+      <c r="AE27">
         <v>38</v>
       </c>
-      <c r="AD27">
+      <c r="AF27">
         <v>2</v>
       </c>
-      <c r="AE27">
+      <c r="AG27">
         <v>40</v>
       </c>
-      <c r="AF27" s="24">
+      <c r="AH27" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG27" s="24">
+      <c r="AI27" s="24">
         <v>166858889160</v>
       </c>
-      <c r="AH27" s="24">
+      <c r="AJ27" s="24">
         <v>35359989160</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>35</v>
       </c>
@@ -3619,44 +3695,46 @@
       <c r="V28" s="9">
         <v>96</v>
       </c>
-      <c r="W28">
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28">
         <v>32350</v>
       </c>
-      <c r="X28">
+      <c r="Z28">
         <v>2900</v>
       </c>
-      <c r="Y28">
+      <c r="AA28">
         <v>35250</v>
       </c>
-      <c r="Z28">
+      <c r="AB28">
         <v>2235</v>
       </c>
-      <c r="AA28">
+      <c r="AC28">
         <v>200</v>
       </c>
-      <c r="AB28">
+      <c r="AD28">
         <v>2587</v>
       </c>
-      <c r="AC28">
+      <c r="AE28">
         <v>34</v>
       </c>
-      <c r="AD28" s="21">
+      <c r="AF28" s="21">
         <v>4</v>
       </c>
-      <c r="AE28">
+      <c r="AG28">
         <v>38</v>
       </c>
-      <c r="AF28" s="24">
+      <c r="AH28" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG28" s="24">
+      <c r="AI28" s="24">
         <v>164732142100</v>
       </c>
-      <c r="AH28" s="24">
+      <c r="AJ28" s="24">
         <v>33233242100</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>36</v>
       </c>
@@ -3723,44 +3801,46 @@
       <c r="V29" s="17">
         <v>100</v>
       </c>
-      <c r="W29">
+      <c r="W29"/>
+      <c r="X29"/>
+      <c r="Y29">
         <v>32355</v>
       </c>
-      <c r="X29">
+      <c r="Z29">
         <v>2915</v>
       </c>
-      <c r="Y29">
+      <c r="AA29">
         <v>35270</v>
       </c>
-      <c r="Z29">
+      <c r="AB29">
         <v>2203</v>
       </c>
-      <c r="AA29">
+      <c r="AC29">
         <v>206</v>
       </c>
-      <c r="AB29" s="7">
+      <c r="AD29" s="7">
         <v>2597</v>
       </c>
-      <c r="AC29">
+      <c r="AE29">
         <v>41</v>
       </c>
-      <c r="AD29" s="9">
+      <c r="AF29" s="9">
         <v>6</v>
       </c>
-      <c r="AE29" s="8">
+      <c r="AG29" s="8">
         <v>47</v>
       </c>
-      <c r="AF29" s="24">
+      <c r="AH29" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG29" s="24">
+      <c r="AI29" s="24">
         <v>179650048180</v>
       </c>
-      <c r="AH29" s="24">
+      <c r="AJ29" s="24">
         <v>48151148180</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>37</v>
       </c>
@@ -3827,44 +3907,46 @@
       <c r="V30">
         <v>84</v>
       </c>
-      <c r="W30">
+      <c r="W30"/>
+      <c r="X30"/>
+      <c r="Y30">
         <v>32276</v>
       </c>
-      <c r="X30">
+      <c r="Z30">
         <v>2954</v>
       </c>
-      <c r="Y30">
+      <c r="AA30">
         <v>35230</v>
       </c>
-      <c r="Z30">
+      <c r="AB30">
         <v>2232</v>
       </c>
-      <c r="AA30">
+      <c r="AC30">
         <v>206</v>
       </c>
-      <c r="AB30" s="7">
+      <c r="AD30" s="7">
         <v>2590</v>
       </c>
-      <c r="AC30">
+      <c r="AE30">
         <v>33</v>
       </c>
-      <c r="AD30" s="7">
+      <c r="AF30" s="7">
         <v>5</v>
       </c>
-      <c r="AE30">
+      <c r="AG30">
         <v>38</v>
       </c>
-      <c r="AF30" s="24">
+      <c r="AH30" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG30" s="24">
+      <c r="AI30" s="24">
         <v>167470427040</v>
       </c>
-      <c r="AH30" s="24">
+      <c r="AJ30" s="24">
         <v>35971527040</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>38</v>
       </c>
@@ -3931,44 +4013,46 @@
       <c r="V31">
         <v>92</v>
       </c>
-      <c r="W31">
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31">
         <v>32263</v>
       </c>
-      <c r="X31">
+      <c r="Z31">
         <v>2985</v>
       </c>
-      <c r="Y31">
+      <c r="AA31">
         <v>35248</v>
       </c>
-      <c r="Z31">
+      <c r="AB31">
         <v>2217</v>
       </c>
-      <c r="AA31">
+      <c r="AC31">
         <v>205</v>
       </c>
-      <c r="AB31" s="7">
+      <c r="AD31" s="7">
         <v>2590</v>
       </c>
-      <c r="AC31">
+      <c r="AE31">
         <v>36</v>
       </c>
-      <c r="AD31" s="9">
+      <c r="AF31" s="9">
         <v>6</v>
       </c>
-      <c r="AE31">
+      <c r="AG31">
         <v>42</v>
       </c>
-      <c r="AF31" s="24">
+      <c r="AH31" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG31" s="24">
+      <c r="AI31" s="24">
         <v>173795020080</v>
       </c>
-      <c r="AH31" s="24">
+      <c r="AJ31" s="24">
         <v>42296120080</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>39</v>
       </c>
@@ -4035,44 +4119,46 @@
       <c r="V32">
         <v>76</v>
       </c>
-      <c r="W32">
+      <c r="W32"/>
+      <c r="X32"/>
+      <c r="Y32">
         <v>32219</v>
       </c>
-      <c r="X32">
+      <c r="Z32">
         <v>3026</v>
       </c>
-      <c r="Y32">
+      <c r="AA32">
         <v>35245</v>
       </c>
-      <c r="Z32">
+      <c r="AB32">
         <v>2233</v>
       </c>
-      <c r="AA32">
+      <c r="AC32">
         <v>204</v>
       </c>
-      <c r="AB32">
+      <c r="AD32">
         <v>2589</v>
       </c>
-      <c r="AC32">
+      <c r="AE32">
         <v>37</v>
       </c>
-      <c r="AD32">
+      <c r="AF32">
         <v>1</v>
       </c>
-      <c r="AE32" s="21">
+      <c r="AG32" s="21">
         <v>38</v>
       </c>
-      <c r="AF32" s="24">
+      <c r="AH32" s="24">
         <v>131498900000</v>
       </c>
-      <c r="AG32" s="24">
+      <c r="AI32" s="24">
         <v>161436994660</v>
       </c>
-      <c r="AH32" s="24">
+      <c r="AJ32" s="24">
         <v>29938094660</v>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>40</v>
       </c>
@@ -4139,44 +4225,46 @@
       <c r="V33">
         <v>88</v>
       </c>
-      <c r="W33">
+      <c r="W33"/>
+      <c r="X33"/>
+      <c r="Y33">
         <v>32471</v>
       </c>
-      <c r="X33">
+      <c r="Z33">
         <v>2746</v>
       </c>
-      <c r="Y33">
+      <c r="AA33">
         <v>35217</v>
       </c>
-      <c r="Z33">
+      <c r="AB33">
         <v>2215</v>
       </c>
-      <c r="AA33">
+      <c r="AC33">
         <v>199</v>
       </c>
-      <c r="AB33" s="9">
+      <c r="AD33" s="9">
         <v>2602</v>
       </c>
-      <c r="AC33">
+      <c r="AE33">
         <v>46</v>
       </c>
-      <c r="AD33">
+      <c r="AF33">
         <v>1</v>
       </c>
-      <c r="AE33" s="8">
+      <c r="AG33" s="8">
         <v>47</v>
       </c>
-      <c r="AF33" s="24">
+      <c r="AH33" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG33" s="24">
+      <c r="AI33" s="24">
         <v>170116780640</v>
       </c>
-      <c r="AH33" s="24">
+      <c r="AJ33" s="24">
         <v>38695690640</v>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>41</v>
       </c>
@@ -4243,44 +4331,46 @@
       <c r="V34">
         <v>92</v>
       </c>
-      <c r="W34">
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34">
         <v>32299</v>
       </c>
-      <c r="X34">
+      <c r="Z34">
         <v>2918</v>
       </c>
-      <c r="Y34">
+      <c r="AA34">
         <v>35217</v>
       </c>
-      <c r="Z34">
+      <c r="AB34">
         <v>2206</v>
       </c>
-      <c r="AA34">
+      <c r="AC34">
         <v>208</v>
       </c>
-      <c r="AB34" s="9">
+      <c r="AD34" s="9">
         <v>2602</v>
       </c>
-      <c r="AC34">
+      <c r="AE34">
         <v>42</v>
       </c>
-      <c r="AD34" s="7">
+      <c r="AF34" s="7">
         <v>5</v>
       </c>
-      <c r="AE34" s="8">
+      <c r="AG34" s="8">
         <v>47</v>
       </c>
-      <c r="AF34" s="24">
+      <c r="AH34" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG34" s="24">
+      <c r="AI34" s="24">
         <v>178474283320</v>
       </c>
-      <c r="AH34" s="24">
+      <c r="AJ34" s="24">
         <v>47053193320</v>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>42</v>
       </c>
@@ -4347,44 +4437,46 @@
       <c r="V35">
         <v>88</v>
       </c>
-      <c r="W35">
+      <c r="W35"/>
+      <c r="X35"/>
+      <c r="Y35">
         <v>32241</v>
       </c>
-      <c r="X35">
+      <c r="Z35">
         <v>2976</v>
       </c>
-      <c r="Y35">
+      <c r="AA35">
         <v>35217</v>
       </c>
-      <c r="Z35">
+      <c r="AB35">
         <v>2222</v>
       </c>
-      <c r="AA35">
+      <c r="AC35">
         <v>192</v>
       </c>
-      <c r="AB35" s="9">
+      <c r="AD35" s="9">
         <v>2602</v>
       </c>
-      <c r="AC35">
+      <c r="AE35">
         <v>45</v>
       </c>
-      <c r="AD35" s="21">
+      <c r="AF35" s="21">
         <v>2</v>
       </c>
-      <c r="AE35" s="8">
+      <c r="AG35" s="8">
         <v>47</v>
       </c>
-      <c r="AF35" s="24">
+      <c r="AH35" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG35" s="24">
+      <c r="AI35" s="24">
         <v>171827487600</v>
       </c>
-      <c r="AH35" s="24">
+      <c r="AJ35" s="24">
         <v>40406397600</v>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>43</v>
       </c>
@@ -4451,44 +4543,46 @@
       <c r="V36" s="9">
         <v>96</v>
       </c>
-      <c r="W36">
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36">
         <v>32218</v>
       </c>
-      <c r="X36">
+      <c r="Z36">
         <v>2999</v>
       </c>
-      <c r="Y36">
+      <c r="AA36">
         <v>35217</v>
       </c>
-      <c r="Z36">
+      <c r="AB36">
         <v>2206</v>
       </c>
-      <c r="AA36">
+      <c r="AC36">
         <v>208</v>
       </c>
-      <c r="AB36" s="9">
+      <c r="AD36" s="9">
         <v>2602</v>
       </c>
-      <c r="AC36">
+      <c r="AE36">
         <v>42</v>
       </c>
-      <c r="AD36" s="7">
+      <c r="AF36" s="7">
         <v>5</v>
       </c>
-      <c r="AE36" s="8">
+      <c r="AG36" s="8">
         <v>47</v>
       </c>
-      <c r="AF36" s="24">
+      <c r="AH36" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG36" s="24">
+      <c r="AI36" s="24">
         <v>178902089320</v>
       </c>
-      <c r="AH36" s="24">
+      <c r="AJ36" s="24">
         <v>47480999320</v>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>44</v>
       </c>
@@ -4555,44 +4649,46 @@
       <c r="V37">
         <v>88</v>
       </c>
-      <c r="W37">
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37">
         <v>32334</v>
       </c>
-      <c r="X37">
+      <c r="Z37">
         <v>2883</v>
       </c>
-      <c r="Y37">
+      <c r="AA37">
         <v>35217</v>
       </c>
-      <c r="Z37">
+      <c r="AB37">
         <v>2224</v>
       </c>
-      <c r="AA37">
+      <c r="AC37">
         <v>190</v>
       </c>
-      <c r="AB37" s="9">
+      <c r="AD37" s="9">
         <v>2602</v>
       </c>
-      <c r="AC37">
+      <c r="AE37">
         <v>42</v>
       </c>
-      <c r="AD37" s="7">
+      <c r="AF37" s="7">
         <v>5</v>
       </c>
-      <c r="AE37" s="8">
+      <c r="AG37" s="8">
         <v>47</v>
       </c>
-      <c r="AF37" s="24">
+      <c r="AH37" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG37" s="24">
+      <c r="AI37" s="24">
         <v>175624043560</v>
       </c>
-      <c r="AH37" s="24">
+      <c r="AJ37" s="24">
         <v>44202953560</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A38" s="27">
         <v>45</v>
       </c>
@@ -4659,44 +4755,46 @@
       <c r="V38" s="17">
         <v>100</v>
       </c>
-      <c r="W38">
+      <c r="W38"/>
+      <c r="X38"/>
+      <c r="Y38">
         <v>32297</v>
       </c>
-      <c r="X38">
+      <c r="Z38">
         <v>2951</v>
       </c>
-      <c r="Y38">
+      <c r="AA38">
         <v>35248</v>
       </c>
-      <c r="Z38">
+      <c r="AB38">
         <v>2190</v>
       </c>
-      <c r="AA38">
+      <c r="AC38">
         <v>204</v>
       </c>
-      <c r="AB38" s="7">
+      <c r="AD38" s="7">
         <v>2598</v>
       </c>
-      <c r="AC38">
+      <c r="AE38">
         <v>46</v>
       </c>
-      <c r="AD38">
+      <c r="AF38">
         <v>5</v>
       </c>
-      <c r="AE38" s="16">
+      <c r="AG38" s="16">
         <v>51</v>
       </c>
-      <c r="AF38" s="24">
+      <c r="AH38" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG38" s="24">
+      <c r="AI38" s="24">
         <v>182783664440</v>
       </c>
-      <c r="AH38" s="24">
+      <c r="AJ38" s="24">
         <v>51362574440</v>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>46</v>
       </c>
@@ -4763,44 +4861,46 @@
       <c r="V39" s="9">
         <v>96</v>
       </c>
-      <c r="W39">
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39">
         <v>32295</v>
       </c>
-      <c r="X39">
+      <c r="Z39">
         <v>2953</v>
       </c>
-      <c r="Y39">
+      <c r="AA39">
         <v>35248</v>
       </c>
-      <c r="Z39">
+      <c r="AB39">
         <v>2182</v>
       </c>
-      <c r="AA39">
+      <c r="AC39">
         <v>212</v>
       </c>
-      <c r="AB39" s="7">
+      <c r="AD39" s="7">
         <v>2598</v>
       </c>
-      <c r="AC39">
+      <c r="AE39">
         <v>48</v>
       </c>
-      <c r="AD39">
+      <c r="AF39">
         <v>3</v>
       </c>
-      <c r="AE39" s="16">
+      <c r="AG39" s="16">
         <v>51</v>
       </c>
-      <c r="AF39" s="24">
+      <c r="AH39" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG39" s="24">
+      <c r="AI39" s="24">
         <v>180922122600</v>
       </c>
-      <c r="AH39" s="24">
+      <c r="AJ39" s="24">
         <v>49501032600</v>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>47</v>
       </c>
@@ -4867,44 +4967,46 @@
       <c r="V40">
         <v>92</v>
       </c>
-      <c r="W40">
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40">
         <v>32411</v>
       </c>
-      <c r="X40">
+      <c r="Z40">
         <v>2873</v>
       </c>
-      <c r="Y40">
+      <c r="AA40">
         <v>35284</v>
       </c>
-      <c r="Z40">
+      <c r="AB40">
         <v>2196</v>
       </c>
-      <c r="AA40">
+      <c r="AC40">
         <v>190</v>
       </c>
-      <c r="AB40" s="7">
+      <c r="AD40" s="7">
         <v>2590</v>
       </c>
-      <c r="AC40">
+      <c r="AE40">
         <v>45</v>
       </c>
-      <c r="AD40" s="9">
+      <c r="AF40" s="9">
         <v>6</v>
       </c>
-      <c r="AE40" s="16">
+      <c r="AG40" s="16">
         <v>51</v>
       </c>
-      <c r="AF40" s="24">
+      <c r="AH40" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG40" s="24">
+      <c r="AI40" s="24">
         <v>181721462640</v>
       </c>
-      <c r="AH40" s="24">
+      <c r="AJ40" s="24">
         <v>50300372640</v>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>48</v>
       </c>
@@ -4971,44 +5073,46 @@
       <c r="V41">
         <v>88</v>
       </c>
-      <c r="W41">
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41">
         <v>32289</v>
       </c>
-      <c r="X41">
+      <c r="Z41">
         <v>2995</v>
       </c>
-      <c r="Y41">
+      <c r="AA41">
         <v>35284</v>
       </c>
-      <c r="Z41">
+      <c r="AB41">
         <v>2176</v>
       </c>
-      <c r="AA41">
+      <c r="AC41">
         <v>210</v>
       </c>
-      <c r="AB41" s="7">
+      <c r="AD41" s="7">
         <v>2590</v>
       </c>
-      <c r="AC41">
+      <c r="AE41">
         <v>49</v>
       </c>
-      <c r="AD41">
+      <c r="AF41">
         <v>2</v>
       </c>
-      <c r="AE41" s="16">
+      <c r="AG41" s="16">
         <v>51</v>
       </c>
-      <c r="AF41" s="24">
+      <c r="AH41" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG41" s="24">
+      <c r="AI41" s="24">
         <v>179224630240</v>
       </c>
-      <c r="AH41" s="24">
+      <c r="AJ41" s="24">
         <v>47803540240</v>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>49</v>
       </c>
@@ -5075,44 +5179,46 @@
       <c r="V42">
         <v>92</v>
       </c>
-      <c r="W42">
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="Y42">
         <v>32355</v>
       </c>
-      <c r="X42">
+      <c r="Z42">
         <v>2949</v>
       </c>
-      <c r="Y42">
+      <c r="AA42">
         <v>35304</v>
       </c>
-      <c r="Z42">
+      <c r="AB42">
         <v>2183</v>
       </c>
-      <c r="AA42">
+      <c r="AC42">
         <v>191</v>
       </c>
-      <c r="AB42" s="7">
+      <c r="AD42" s="7">
         <v>2594</v>
       </c>
-      <c r="AC42">
+      <c r="AE42">
         <v>51</v>
       </c>
-      <c r="AD42">
+      <c r="AF42">
         <v>4</v>
       </c>
-      <c r="AE42" s="18">
+      <c r="AG42" s="18">
         <v>55</v>
       </c>
-      <c r="AF42" s="24">
+      <c r="AH42" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG42" s="24">
+      <c r="AI42" s="24">
         <v>184060175480</v>
       </c>
-      <c r="AH42" s="24">
+      <c r="AJ42" s="24">
         <v>52639085480</v>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A43" s="27">
         <v>50</v>
       </c>
@@ -5179,44 +5285,46 @@
       <c r="V43" s="9">
         <v>96</v>
       </c>
-      <c r="W43">
+      <c r="W43"/>
+      <c r="X43"/>
+      <c r="Y43">
         <v>32329</v>
       </c>
-      <c r="X43">
+      <c r="Z43">
         <v>2975</v>
       </c>
-      <c r="Y43">
+      <c r="AA43">
         <v>35304</v>
       </c>
-      <c r="Z43">
+      <c r="AB43">
         <v>2179</v>
       </c>
-      <c r="AA43">
+      <c r="AC43">
         <v>195</v>
       </c>
-      <c r="AB43" s="7">
+      <c r="AD43" s="7">
         <v>2594</v>
       </c>
-      <c r="AC43">
+      <c r="AE43">
         <v>50</v>
       </c>
-      <c r="AD43" s="21">
+      <c r="AF43" s="21">
         <v>5</v>
       </c>
-      <c r="AE43" s="18">
+      <c r="AG43" s="18">
         <v>55</v>
       </c>
-      <c r="AF43" s="24">
+      <c r="AH43" s="24">
         <v>131421090000</v>
       </c>
-      <c r="AG43" s="24">
+      <c r="AI43" s="24">
         <v>186319074960</v>
       </c>
-      <c r="AH43" s="24">
+      <c r="AJ43" s="24">
         <v>54897984960</v>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>51</v>
       </c>
@@ -5283,44 +5391,46 @@
       <c r="V44" s="9">
         <v>96</v>
       </c>
-      <c r="W44">
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44">
         <v>32229</v>
       </c>
-      <c r="X44">
+      <c r="Z44">
         <v>2986</v>
       </c>
-      <c r="Y44">
+      <c r="AA44">
         <v>35215</v>
       </c>
-      <c r="Z44">
+      <c r="AB44">
         <v>2217</v>
       </c>
-      <c r="AA44">
+      <c r="AC44">
         <v>202</v>
       </c>
-      <c r="AB44">
+      <c r="AD44">
         <v>2599</v>
       </c>
-      <c r="AC44">
+      <c r="AE44">
         <v>40</v>
       </c>
-      <c r="AD44">
+      <c r="AF44">
         <v>5</v>
       </c>
-      <c r="AE44">
+      <c r="AG44">
         <v>45</v>
       </c>
-      <c r="AF44" s="25">
+      <c r="AH44" s="25">
         <v>131421090000</v>
       </c>
-      <c r="AG44" s="25">
+      <c r="AI44" s="25">
         <v>175513596500</v>
       </c>
-      <c r="AH44" s="25">
+      <c r="AJ44" s="25">
         <v>44092506500</v>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>52</v>
       </c>
@@ -5387,54 +5497,58 @@
       <c r="V45">
         <v>88</v>
       </c>
-      <c r="W45">
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45">
         <v>32347</v>
       </c>
-      <c r="X45">
+      <c r="Z45">
         <v>2868</v>
       </c>
-      <c r="Y45">
+      <c r="AA45">
         <v>35215</v>
       </c>
-      <c r="Z45">
+      <c r="AB45">
         <v>2228</v>
       </c>
-      <c r="AA45">
+      <c r="AC45">
         <v>191</v>
       </c>
-      <c r="AB45">
+      <c r="AD45">
         <v>2599</v>
       </c>
-      <c r="AC45">
+      <c r="AE45">
         <v>40</v>
       </c>
-      <c r="AD45" s="21">
+      <c r="AF45" s="21">
         <v>5</v>
       </c>
-      <c r="AE45">
+      <c r="AG45">
         <v>45</v>
       </c>
-      <c r="AF45" s="25">
+      <c r="AH45" s="25">
         <v>131421090000</v>
       </c>
-      <c r="AG45" s="25">
+      <c r="AI45" s="25">
         <v>173261091980</v>
       </c>
-      <c r="AH45" s="25">
+      <c r="AJ45" s="25">
         <v>41840001980</v>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>53</v>
       </c>
+      <c r="W46"/>
+      <c r="X46"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>55</v>
       </c>
@@ -5465,15 +5579,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AK2" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState ref="A3:AK53">
+  <autoFilter ref="A2:AM2" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState ref="A3:AM53">
       <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
-    <mergeCell ref="W1:Y1"/>
-    <mergeCell ref="AC1:AE1"/>
-    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AB1:AD1"/>
     <mergeCell ref="G1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E887D-6B92-4824-909E-60625FAD6C52}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B2E8A6-3F43-4545-A7E4-C16BC1B76BCF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1270" windowWidth="30890" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3070" yWindow="1610" windowWidth="30890" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="89">
   <si>
     <t>Trung bình/Kỳ</t>
   </si>
@@ -92,189 +92,6 @@
   <si>
     <t>Tỉ lệ
 &gt;90%</t>
-  </si>
-  <si>
-    <t>Tổng  3</t>
-  </si>
-  <si>
-    <t>Tổng 4</t>
-  </si>
-  <si>
-    <t>Tổng 5</t>
-  </si>
-  <si>
-    <t>Chi</t>
-  </si>
-  <si>
-    <t>Thu</t>
-  </si>
-  <si>
-    <t>Lãi/Lỗ</t>
-  </si>
-  <si>
-    <t>100-350</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>78/251</t>
-  </si>
-  <si>
-    <t>146/251</t>
-  </si>
-  <si>
-    <t>23/25</t>
-  </si>
-  <si>
-    <t>94/251</t>
-  </si>
-  <si>
-    <t>135/251</t>
-  </si>
-  <si>
-    <t>21/25</t>
-  </si>
-  <si>
-    <t>87/251</t>
-  </si>
-  <si>
-    <t>148/251</t>
-  </si>
-  <si>
-    <t>88/251</t>
-  </si>
-  <si>
-    <t>144/251</t>
-  </si>
-  <si>
-    <t>22/25</t>
-  </si>
-  <si>
-    <t>63/251</t>
-  </si>
-  <si>
-    <t>152/251</t>
-  </si>
-  <si>
-    <t>84/251</t>
-  </si>
-  <si>
-    <t>145/251</t>
-  </si>
-  <si>
-    <t>74/251</t>
-  </si>
-  <si>
-    <t>81/251</t>
-  </si>
-  <si>
-    <t>98/251</t>
-  </si>
-  <si>
-    <t>130/251</t>
-  </si>
-  <si>
-    <t>142/251</t>
-  </si>
-  <si>
-    <t>25/25</t>
-  </si>
-  <si>
-    <t>107/251</t>
-  </si>
-  <si>
-    <t>129/251</t>
-  </si>
-  <si>
-    <t>18/25</t>
-  </si>
-  <si>
-    <t>82/251</t>
-  </si>
-  <si>
-    <t>149/251</t>
-  </si>
-  <si>
-    <t>24/25</t>
-  </si>
-  <si>
-    <t>86/251</t>
-  </si>
-  <si>
-    <t>136/251</t>
-  </si>
-  <si>
-    <t>137/251</t>
-  </si>
-  <si>
-    <t>85/251</t>
-  </si>
-  <si>
-    <t>132/251</t>
-  </si>
-  <si>
-    <t>80/251</t>
-  </si>
-  <si>
-    <t>140/251</t>
-  </si>
-  <si>
-    <t>79/251</t>
-  </si>
-  <si>
-    <t>139/251</t>
-  </si>
-  <si>
-    <t>162/251</t>
-  </si>
-  <si>
-    <t>150/251</t>
-  </si>
-  <si>
-    <t>89/251</t>
-  </si>
-  <si>
-    <t>19/25</t>
-  </si>
-  <si>
-    <t>143/251</t>
-  </si>
-  <si>
-    <t>76/251</t>
-  </si>
-  <si>
-    <t>159/251</t>
-  </si>
-  <si>
-    <t>158/251</t>
-  </si>
-  <si>
-    <t>75/251</t>
-  </si>
-  <si>
-    <t>77/251</t>
-  </si>
-  <si>
-    <t>156/251</t>
-  </si>
-  <si>
-    <t>91/251</t>
-  </si>
-  <si>
-    <t>133/251</t>
-  </si>
-  <si>
-    <t>66/251</t>
-  </si>
-  <si>
-    <t>160/251</t>
-  </si>
-  <si>
-    <t>131421090000</t>
-  </si>
-  <si>
-    <t>176344126840.0</t>
   </si>
   <si>
     <t>Số chu kỳ 10 kỳ thu hồi
@@ -293,6 +110,198 @@
     <t>Tỉ lệ chu kỳ 10 kỳ 
 thu hồi 
 10 &gt;=100%</t>
+  </si>
+  <si>
+    <t>Tổng  3</t>
+  </si>
+  <si>
+    <t>Tổng 4</t>
+  </si>
+  <si>
+    <t>Tổng 5</t>
+  </si>
+  <si>
+    <t>Chi</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Lãi/Lỗ</t>
+  </si>
+  <si>
+    <t>100-350</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>78/251</t>
+  </si>
+  <si>
+    <t>146/251</t>
+  </si>
+  <si>
+    <t>23/25</t>
+  </si>
+  <si>
+    <t>21/25</t>
+  </si>
+  <si>
+    <t>93/251</t>
+  </si>
+  <si>
+    <t>135/251</t>
+  </si>
+  <si>
+    <t>18/25</t>
+  </si>
+  <si>
+    <t>87/251</t>
+  </si>
+  <si>
+    <t>148/251</t>
+  </si>
+  <si>
+    <t>22/25</t>
+  </si>
+  <si>
+    <t>88/251</t>
+  </si>
+  <si>
+    <t>144/251</t>
+  </si>
+  <si>
+    <t>19/25</t>
+  </si>
+  <si>
+    <t>20/25</t>
+  </si>
+  <si>
+    <t>63/251</t>
+  </si>
+  <si>
+    <t>152/251</t>
+  </si>
+  <si>
+    <t>84/251</t>
+  </si>
+  <si>
+    <t>145/251</t>
+  </si>
+  <si>
+    <t>74/251</t>
+  </si>
+  <si>
+    <t>81/251</t>
+  </si>
+  <si>
+    <t>98/251</t>
+  </si>
+  <si>
+    <t>130/251</t>
+  </si>
+  <si>
+    <t>143/251</t>
+  </si>
+  <si>
+    <t>25/25</t>
+  </si>
+  <si>
+    <t>24/25</t>
+  </si>
+  <si>
+    <t>107/251</t>
+  </si>
+  <si>
+    <t>129/251</t>
+  </si>
+  <si>
+    <t>15/25</t>
+  </si>
+  <si>
+    <t>82/251</t>
+  </si>
+  <si>
+    <t>149/251</t>
+  </si>
+  <si>
+    <t>17/25</t>
+  </si>
+  <si>
+    <t>86/251</t>
+  </si>
+  <si>
+    <t>136/251</t>
+  </si>
+  <si>
+    <t>137/251</t>
+  </si>
+  <si>
+    <t>85/251</t>
+  </si>
+  <si>
+    <t>132/251</t>
+  </si>
+  <si>
+    <t>80/251</t>
+  </si>
+  <si>
+    <t>140/251</t>
+  </si>
+  <si>
+    <t>79/251</t>
+  </si>
+  <si>
+    <t>138/251</t>
+  </si>
+  <si>
+    <t>161/251</t>
+  </si>
+  <si>
+    <t>139/251</t>
+  </si>
+  <si>
+    <t>150/251</t>
+  </si>
+  <si>
+    <t>89/251</t>
+  </si>
+  <si>
+    <t>142/251</t>
+  </si>
+  <si>
+    <t>83/251</t>
+  </si>
+  <si>
+    <t>77/251</t>
+  </si>
+  <si>
+    <t>75/251</t>
+  </si>
+  <si>
+    <t>159/251</t>
+  </si>
+  <si>
+    <t>157/251</t>
+  </si>
+  <si>
+    <t>76/251</t>
+  </si>
+  <si>
+    <t>155/251</t>
+  </si>
+  <si>
+    <t>90/251</t>
+  </si>
+  <si>
+    <t>66/251</t>
+  </si>
+  <si>
+    <t>131421090000</t>
+  </si>
+  <si>
+    <t>176344126840.0</t>
   </si>
 </sst>
 </file>
@@ -303,7 +312,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,6 +357,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -502,8 +518,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -518,6 +532,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -532,9 +550,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -819,24 +835,23 @@
   <dimension ref="A1:AM53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9" style="21" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" style="21" customWidth="1"/>
-    <col min="7" max="7" width="8.453125" style="21" customWidth="1"/>
-    <col min="8" max="15" width="6.453125" style="21" customWidth="1"/>
-    <col min="16" max="16" width="8" style="21" customWidth="1"/>
-    <col min="17" max="17" width="9" style="21" customWidth="1"/>
-    <col min="18" max="20" width="9.1796875" style="21" customWidth="1"/>
-    <col min="21" max="21" width="17.81640625" style="21" customWidth="1"/>
-    <col min="22" max="22" width="16.90625" style="21" customWidth="1"/>
-    <col min="23" max="24" width="16.90625" style="28" customWidth="1"/>
-    <col min="25" max="29" width="9.26953125" style="21" customWidth="1"/>
-    <col min="30" max="30" width="9.26953125" style="22" customWidth="1"/>
-    <col min="31" max="33" width="9.26953125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9" style="26" customWidth="1"/>
+    <col min="3" max="3" width="8.36328125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" style="26" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" style="26" customWidth="1"/>
+    <col min="8" max="15" width="6.453125" style="26" customWidth="1"/>
+    <col min="16" max="16" width="8" style="26" customWidth="1"/>
+    <col min="17" max="17" width="9" style="26" customWidth="1"/>
+    <col min="18" max="20" width="9.1796875" style="26" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="26" customWidth="1"/>
+    <col min="22" max="24" width="16.90625" style="26" customWidth="1"/>
+    <col min="25" max="29" width="9.26953125" style="26" customWidth="1"/>
+    <col min="30" max="30" width="9.26953125" style="27" customWidth="1"/>
+    <col min="31" max="33" width="9.26953125" style="26" customWidth="1"/>
     <col min="34" max="36" width="18.7265625" style="20" customWidth="1"/>
-    <col min="37" max="39" width="6.54296875" style="21" customWidth="1"/>
+    <col min="37" max="39" width="6.54296875" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
@@ -923,23 +938,23 @@
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="S2" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="T2" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="V2" s="35" t="s">
-        <v>83</v>
+      <c r="U2" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="Y2" s="12">
         <v>3</v>
@@ -948,7 +963,7 @@
         <v>10</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AB2" s="12">
         <v>4</v>
@@ -957,7 +972,7 @@
         <v>12</v>
       </c>
       <c r="AD2" s="13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE2" s="12">
         <v>5</v>
@@ -966,27 +981,27 @@
         <v>14</v>
       </c>
       <c r="AG2" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AH2" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI2" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AJ2" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3" s="21">
+      <c r="A3" s="26">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" s="17">
         <v>140.12873209315191</v>
@@ -1009,13 +1024,13 @@
       <c r="J3">
         <v>10.31872509960159</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="26">
         <v>0.8127490039840638</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="26">
         <v>0.8127490039840638</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="26">
         <v>0.17928286852589639</v>
       </c>
       <c r="N3">
@@ -1028,25 +1043,29 @@
         <v>128.19521912350601</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R3" s="7">
         <v>31.075697211155379</v>
       </c>
       <c r="S3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3">
+        <v>34</v>
+      </c>
+      <c r="T3" s="26">
         <v>58.167330677290842</v>
       </c>
       <c r="U3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" s="21">
+        <v>35</v>
+      </c>
+      <c r="V3" s="26">
         <v>92</v>
       </c>
-      <c r="W3"/>
-      <c r="X3"/>
+      <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="26">
+        <v>84</v>
+      </c>
       <c r="Y3">
         <v>32343</v>
       </c>
@@ -1074,13 +1093,13 @@
       <c r="AG3" s="16">
         <v>51</v>
       </c>
-      <c r="AH3" s="24">
+      <c r="AH3" s="22">
         <v>131421090000</v>
       </c>
-      <c r="AI3" s="24">
+      <c r="AI3" s="22">
         <v>184158707120</v>
       </c>
-      <c r="AJ3" s="24">
+      <c r="AJ3" s="22">
         <v>52737617120</v>
       </c>
     </row>
@@ -1089,36 +1108,36 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4">
-        <v>113.1032980475204</v>
+        <v>32</v>
+      </c>
+      <c r="D4" s="26">
+        <v>113.32315416260811</v>
       </c>
       <c r="E4">
-        <v>37789</v>
+        <v>37639</v>
       </c>
       <c r="F4">
-        <v>3091</v>
+        <v>3084</v>
       </c>
       <c r="G4">
-        <v>128.48605577689241</v>
-      </c>
-      <c r="H4" s="21">
-        <v>11.597609561752989</v>
-      </c>
-      <c r="I4">
-        <v>11.597609561752989</v>
+        <v>127.95617529880479</v>
+      </c>
+      <c r="H4" s="26">
+        <v>11.569721115537851</v>
+      </c>
+      <c r="I4" s="26">
+        <v>11.569721115537851</v>
       </c>
       <c r="J4">
-        <v>10.342629482071709</v>
-      </c>
-      <c r="K4">
+        <v>10.30278884462151</v>
+      </c>
+      <c r="K4" s="26">
         <v>0.71713147410358569</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="26">
         <v>0.71713147410358569</v>
       </c>
       <c r="M4">
@@ -1127,49 +1146,53 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="26">
         <v>0.12749003984063739</v>
       </c>
       <c r="P4">
-        <v>128.43426294820719</v>
+        <v>127.90039840637451</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4">
-        <v>37.450199203187253</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="26">
+        <v>37.051792828685258</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T4">
         <v>53.784860557768923</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
-      </c>
-      <c r="V4" s="21">
+        <v>36</v>
+      </c>
+      <c r="V4" s="26">
         <v>84</v>
       </c>
-      <c r="W4"/>
-      <c r="X4"/>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="26">
+        <v>72</v>
+      </c>
       <c r="Y4">
-        <v>32250</v>
+        <v>32117</v>
       </c>
       <c r="Z4">
-        <v>2911</v>
+        <v>2904</v>
       </c>
       <c r="AA4">
-        <v>35161</v>
+        <v>35021</v>
       </c>
       <c r="AB4">
-        <v>2288</v>
+        <v>2278</v>
       </c>
       <c r="AC4">
         <v>180</v>
       </c>
       <c r="AD4" s="7">
-        <v>2596</v>
+        <v>2586</v>
       </c>
       <c r="AE4">
         <v>32</v>
@@ -1177,17 +1200,17 @@
       <c r="AF4">
         <v>0</v>
       </c>
-      <c r="AG4" s="21">
+      <c r="AG4" s="26">
         <v>32</v>
       </c>
-      <c r="AH4" s="23">
-        <v>131421090000</v>
-      </c>
-      <c r="AI4" s="24">
-        <v>148641587120</v>
-      </c>
-      <c r="AJ4" s="24">
-        <v>17220497120</v>
+      <c r="AH4" s="21">
+        <v>130897500000</v>
+      </c>
+      <c r="AI4" s="22">
+        <v>148337175720</v>
+      </c>
+      <c r="AJ4" s="22">
+        <v>17439675720</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
@@ -1195,12 +1218,12 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="21">
+        <v>32</v>
+      </c>
+      <c r="D5" s="26">
         <v>130.28112528970809</v>
       </c>
       <c r="E5">
@@ -1221,10 +1244,10 @@
       <c r="J5">
         <v>10.30278884462151</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="26">
         <v>0.79681274900398402</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="26">
         <v>0.79681274900398402</v>
       </c>
       <c r="M5">
@@ -1240,25 +1263,29 @@
         <v>128.13545816733071</v>
       </c>
       <c r="Q5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="26">
+        <v>34.661354581673308</v>
+      </c>
+      <c r="S5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="26">
+        <v>58.964143426294832</v>
+      </c>
+      <c r="U5" t="s">
         <v>35</v>
       </c>
-      <c r="R5">
-        <v>34.661354581673308</v>
-      </c>
-      <c r="S5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5">
-        <v>58.964143426294832</v>
-      </c>
-      <c r="U5" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" s="21">
+      <c r="V5" s="26">
         <v>92</v>
       </c>
-      <c r="W5"/>
-      <c r="X5"/>
+      <c r="W5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" s="26">
+        <v>88</v>
+      </c>
       <c r="Y5">
         <v>32308</v>
       </c>
@@ -1271,52 +1298,52 @@
       <c r="AB5">
         <v>2198</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="26">
         <v>200</v>
       </c>
-      <c r="AD5" s="21">
+      <c r="AD5" s="26">
         <v>2586</v>
       </c>
       <c r="AE5">
         <v>46</v>
       </c>
-      <c r="AF5" s="21">
+      <c r="AF5" s="26">
         <v>1</v>
       </c>
       <c r="AG5" s="8">
         <v>47</v>
       </c>
-      <c r="AH5" s="23">
+      <c r="AH5" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI5" s="24">
+      <c r="AI5" s="22">
         <v>171216874920</v>
       </c>
-      <c r="AJ5" s="24">
+      <c r="AJ5" s="22">
         <v>39795784920</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6" s="21">
+      <c r="A6" s="26">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="21">
-        <v>127.7490365362211</v>
+        <v>32</v>
+      </c>
+      <c r="D6" s="26">
+        <v>127.7392235604194</v>
       </c>
       <c r="E6">
-        <v>37717</v>
+        <v>37720</v>
       </c>
       <c r="F6">
         <v>3180</v>
       </c>
       <c r="G6">
-        <v>128.05577689243029</v>
+        <v>128.07171314741029</v>
       </c>
       <c r="H6">
         <v>11.820717131474099</v>
@@ -1325,12 +1352,12 @@
         <v>11.820717131474099</v>
       </c>
       <c r="J6">
-        <v>10.23505976095618</v>
+        <v>10.231075697211161</v>
       </c>
       <c r="K6">
         <v>0.83266932270916338</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="26">
         <v>0.83266932270916338</v>
       </c>
       <c r="M6">
@@ -1339,49 +1366,53 @@
       <c r="N6">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="26">
         <v>0.15537848605577689</v>
       </c>
       <c r="P6">
         <v>127.51792828685259</v>
       </c>
       <c r="Q6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="R6">
         <v>35.059760956175303</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="T6">
         <v>57.370517928286858</v>
       </c>
       <c r="U6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V6" s="21">
+        <v>42</v>
+      </c>
+      <c r="V6" s="26">
         <v>88</v>
       </c>
-      <c r="W6"/>
-      <c r="X6"/>
+      <c r="W6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X6" s="26">
+        <v>76</v>
+      </c>
       <c r="Y6">
-        <v>32142</v>
+        <v>32146</v>
       </c>
       <c r="Z6">
         <v>2967</v>
       </c>
       <c r="AA6">
-        <v>35109</v>
+        <v>35113</v>
       </c>
       <c r="AB6">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="AC6">
         <v>209</v>
       </c>
-      <c r="AD6" s="21">
-        <v>2569</v>
+      <c r="AD6" s="26">
+        <v>2568</v>
       </c>
       <c r="AE6">
         <v>35</v>
@@ -1389,17 +1420,17 @@
       <c r="AF6">
         <v>4</v>
       </c>
-      <c r="AG6" s="21">
+      <c r="AG6" s="26">
         <v>39</v>
       </c>
-      <c r="AH6" s="23">
+      <c r="AH6" s="21">
         <v>130897500000</v>
       </c>
-      <c r="AI6" s="24">
-        <v>167220295100</v>
-      </c>
-      <c r="AJ6" s="24">
-        <v>36322795100</v>
+      <c r="AI6" s="22">
+        <v>167207450160</v>
+      </c>
+      <c r="AJ6" s="22">
+        <v>36309950160</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
@@ -1407,12 +1438,12 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="D7" s="26">
         <v>127.02495336174739</v>
       </c>
       <c r="E7">
@@ -1427,7 +1458,7 @@
       <c r="H7">
         <v>12.011952191235061</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="26">
         <v>12.011952191235061</v>
       </c>
       <c r="J7">
@@ -1452,25 +1483,29 @@
         <v>127.87250996015941</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="21">
+        <v>40</v>
+      </c>
+      <c r="R7" s="26">
         <v>34.661354581673308</v>
       </c>
       <c r="S7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="T7">
         <v>57.370517928286858</v>
       </c>
       <c r="U7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V7" s="21">
+        <v>42</v>
+      </c>
+      <c r="V7" s="26">
         <v>88</v>
       </c>
-      <c r="W7"/>
-      <c r="X7"/>
+      <c r="W7" t="s">
+        <v>46</v>
+      </c>
+      <c r="X7" s="26">
+        <v>80</v>
+      </c>
       <c r="Y7">
         <v>32188</v>
       </c>
@@ -1492,31 +1527,31 @@
       <c r="AE7">
         <v>38</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="26">
         <v>2</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="26">
         <v>40</v>
       </c>
-      <c r="AH7" s="23">
+      <c r="AH7" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI7" s="24">
+      <c r="AI7" s="22">
         <v>166937578280</v>
       </c>
-      <c r="AJ7" s="24">
+      <c r="AJ7" s="22">
         <v>35516488280</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="A8" s="26">
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D8" s="14">
         <v>142.0935200887468</v>
@@ -1533,7 +1568,7 @@
       <c r="H8">
         <v>11.60956175298805</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="26">
         <v>11.60956175298805</v>
       </c>
       <c r="J8">
@@ -1551,32 +1586,36 @@
       <c r="N8">
         <v>3.1872509960159362E-2</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="26">
         <v>0.18725099601593631</v>
       </c>
       <c r="P8">
         <v>128.17928286852589</v>
       </c>
       <c r="Q8" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R8" s="14">
         <v>25.099601593625501</v>
       </c>
       <c r="S8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="T8" s="8">
         <v>60.557768924302792</v>
       </c>
       <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" s="21">
+        <v>35</v>
+      </c>
+      <c r="V8" s="26">
         <v>92</v>
       </c>
-      <c r="W8"/>
-      <c r="X8"/>
+      <c r="W8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X8" s="9">
+        <v>92</v>
+      </c>
       <c r="Y8">
         <v>32303</v>
       </c>
@@ -1589,7 +1628,7 @@
       <c r="AB8">
         <v>2181</v>
       </c>
-      <c r="AC8" s="14">
+      <c r="AC8" s="26">
         <v>233</v>
       </c>
       <c r="AD8" s="9">
@@ -1604,13 +1643,13 @@
       <c r="AG8" s="8">
         <v>47</v>
       </c>
-      <c r="AH8" s="23">
+      <c r="AH8" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI8" s="24">
+      <c r="AI8" s="22">
         <v>186740852920</v>
       </c>
-      <c r="AJ8" s="24">
+      <c r="AJ8" s="22">
         <v>55319762920</v>
       </c>
     </row>
@@ -1619,10 +1658,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" s="8">
         <v>132.88851661479899</v>
@@ -1648,7 +1687,7 @@
       <c r="K9">
         <v>0.81673306772908372</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="26">
         <v>0.81673306772908372</v>
       </c>
       <c r="M9">
@@ -1657,32 +1696,36 @@
       <c r="N9">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="26">
         <v>0.1752988047808765</v>
       </c>
       <c r="P9">
         <v>128.00398406374501</v>
       </c>
       <c r="Q9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R9">
         <v>33.466135458167329</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T9">
         <v>57.768924302788847</v>
       </c>
       <c r="U9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V9" s="21">
+        <v>42</v>
+      </c>
+      <c r="V9" s="26">
         <v>88</v>
       </c>
-      <c r="W9"/>
-      <c r="X9"/>
+      <c r="W9" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" s="26">
+        <v>88</v>
+      </c>
       <c r="Y9">
         <v>32243</v>
       </c>
@@ -1698,7 +1741,7 @@
       <c r="AC9">
         <v>205</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="26">
         <v>2589</v>
       </c>
       <c r="AE9">
@@ -1707,123 +1750,127 @@
       <c r="AF9" s="7">
         <v>5</v>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="26">
         <v>44</v>
       </c>
-      <c r="AH9" s="23">
+      <c r="AH9" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI9" s="24">
+      <c r="AI9" s="22">
         <v>174643537020</v>
       </c>
-      <c r="AJ9" s="24">
+      <c r="AJ9" s="22">
         <v>43222447020</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="A10" s="26">
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10">
-        <v>129.49497466338161</v>
+        <v>32</v>
+      </c>
+      <c r="D10" s="26">
+        <v>130.13855146080439</v>
       </c>
       <c r="E10">
-        <v>37695</v>
+        <v>37850</v>
       </c>
       <c r="F10">
-        <v>3131</v>
+        <v>3140</v>
       </c>
       <c r="G10">
-        <v>128.10756972111551</v>
+        <v>128.6414342629482</v>
       </c>
       <c r="H10">
-        <v>11.62549800796813</v>
-      </c>
-      <c r="I10" s="21">
-        <v>11.62549800796813</v>
+        <v>11.66135458167331</v>
+      </c>
+      <c r="I10" s="26">
+        <v>11.66135458167331</v>
       </c>
       <c r="J10">
-        <v>10.28286852589641</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="K10">
         <v>0.83266932270916338</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="26">
         <v>0.83266932270916338</v>
       </c>
       <c r="M10">
-        <v>0.14741035856573709</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="N10">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="O10">
-        <v>0.1633466135458167</v>
+      <c r="O10" s="26">
+        <v>0.16733067729083659</v>
       </c>
       <c r="P10">
-        <v>127.7171314741036</v>
+        <v>128.23904382470121</v>
       </c>
       <c r="Q10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="R10" s="9">
         <v>29.482071713147409</v>
       </c>
       <c r="S10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T10">
-        <v>57.370517928286858</v>
+        <v>57.768924302788847</v>
       </c>
       <c r="U10" t="s">
-        <v>31</v>
-      </c>
-      <c r="V10" s="21">
+        <v>35</v>
+      </c>
+      <c r="V10" s="26">
         <v>92</v>
       </c>
-      <c r="W10"/>
-      <c r="X10"/>
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" s="26">
+        <v>84</v>
+      </c>
       <c r="Y10">
-        <v>32155</v>
+        <v>32289</v>
       </c>
       <c r="Z10">
-        <v>2918</v>
+        <v>2927</v>
       </c>
       <c r="AA10">
-        <v>35073</v>
+        <v>35216</v>
       </c>
       <c r="AB10">
-        <v>2208</v>
+        <v>2215</v>
       </c>
       <c r="AC10">
         <v>209</v>
       </c>
       <c r="AD10" s="7">
-        <v>2581</v>
+        <v>2592</v>
       </c>
       <c r="AE10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AF10">
         <v>4</v>
       </c>
-      <c r="AG10">
-        <v>41</v>
-      </c>
-      <c r="AH10" s="23">
-        <v>130897500000</v>
-      </c>
-      <c r="AI10" s="24">
-        <v>169505684460</v>
-      </c>
-      <c r="AJ10" s="24">
-        <v>38608184460</v>
+      <c r="AG10" s="26">
+        <v>42</v>
+      </c>
+      <c r="AH10" s="21">
+        <v>131421090000</v>
+      </c>
+      <c r="AI10" s="22">
+        <v>171029502840</v>
+      </c>
+      <c r="AJ10" s="22">
+        <v>39608412840</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
@@ -1831,12 +1878,12 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="21">
+        <v>32</v>
+      </c>
+      <c r="D11" s="26">
         <v>129.96682088087991</v>
       </c>
       <c r="E11">
@@ -1848,10 +1895,10 @@
       <c r="G11">
         <v>128.8167330677291</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="26">
         <v>11.37450199203187</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="26">
         <v>11.37450199203187</v>
       </c>
       <c r="J11">
@@ -1860,13 +1907,13 @@
       <c r="K11">
         <v>0.86454183266932272</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="26">
         <v>0.86454183266932272</v>
       </c>
       <c r="M11">
         <v>0.14741035856573709</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N11" s="26">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="O11">
@@ -1876,25 +1923,29 @@
         <v>128.49402390438249</v>
       </c>
       <c r="Q11" t="s">
-        <v>45</v>
-      </c>
-      <c r="R11" s="21">
+        <v>52</v>
+      </c>
+      <c r="R11" s="26">
         <v>32.270916334661351</v>
       </c>
       <c r="S11" t="s">
-        <v>30</v>
-      </c>
-      <c r="T11" s="21">
+        <v>34</v>
+      </c>
+      <c r="T11" s="26">
         <v>58.167330677290842</v>
       </c>
       <c r="U11" t="s">
-        <v>39</v>
-      </c>
-      <c r="V11" s="21">
+        <v>42</v>
+      </c>
+      <c r="V11" s="26">
         <v>88</v>
       </c>
-      <c r="W11"/>
-      <c r="X11"/>
+      <c r="W11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11">
+        <v>84</v>
+      </c>
       <c r="Y11">
         <v>32333</v>
       </c>
@@ -1916,19 +1967,19 @@
       <c r="AE11">
         <v>37</v>
       </c>
-      <c r="AF11" s="21">
+      <c r="AF11" s="26">
         <v>4</v>
       </c>
-      <c r="AG11" s="21">
+      <c r="AG11" s="26">
         <v>41</v>
       </c>
-      <c r="AH11" s="23">
+      <c r="AH11" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI11" s="24">
+      <c r="AI11" s="22">
         <v>170803812640</v>
       </c>
-      <c r="AJ11" s="24">
+      <c r="AJ11" s="22">
         <v>39382722640</v>
       </c>
     </row>
@@ -1937,12 +1988,12 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="21">
+        <v>32</v>
+      </c>
+      <c r="D12" s="26">
         <v>117.1493692374641</v>
       </c>
       <c r="E12">
@@ -1957,7 +2008,7 @@
       <c r="H12">
         <v>11.64541832669323</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="26">
         <v>11.64541832669323</v>
       </c>
       <c r="J12">
@@ -1966,7 +2017,7 @@
       <c r="K12">
         <v>0.7450199203187251</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="26">
         <v>0.7450199203187251</v>
       </c>
       <c r="M12">
@@ -1975,32 +2026,36 @@
       <c r="N12">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="O12" s="21">
+      <c r="O12" s="26">
         <v>0.13147410358565739</v>
       </c>
       <c r="P12">
         <v>128.35059760956179</v>
       </c>
       <c r="Q12" t="s">
-        <v>46</v>
-      </c>
-      <c r="R12">
+        <v>53</v>
+      </c>
+      <c r="R12" s="26">
         <v>39.04382470119522</v>
       </c>
       <c r="S12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="T12">
         <v>51.792828685258961</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
-      </c>
-      <c r="V12" s="21">
+        <v>36</v>
+      </c>
+      <c r="V12" s="26">
         <v>84</v>
       </c>
-      <c r="W12"/>
-      <c r="X12"/>
+      <c r="W12" t="s">
+        <v>39</v>
+      </c>
+      <c r="X12" s="26">
+        <v>72</v>
+      </c>
       <c r="Y12">
         <v>32262</v>
       </c>
@@ -2022,58 +2077,58 @@
       <c r="AE12">
         <v>31</v>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="26">
         <v>2</v>
       </c>
-      <c r="AG12" s="21">
+      <c r="AG12" s="26">
         <v>33</v>
       </c>
-      <c r="AH12" s="23">
+      <c r="AH12" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI12" s="24">
+      <c r="AI12" s="22">
         <v>153958977980</v>
       </c>
-      <c r="AJ12" s="24">
+      <c r="AJ12" s="22">
         <v>22537887980</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="27">
+      <c r="A13" s="25">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" s="8">
-        <v>134.0481170839779</v>
+        <v>133.8928384477712</v>
       </c>
       <c r="E13">
-        <v>37749</v>
+        <v>37897</v>
       </c>
       <c r="F13">
-        <v>3170</v>
+        <v>3184</v>
       </c>
       <c r="G13">
-        <v>128.04382470119521</v>
+        <v>128.53784860557769</v>
       </c>
       <c r="H13">
-        <v>11.8406374501992</v>
+        <v>11.89243027888446</v>
       </c>
       <c r="I13" s="7">
-        <v>11.8406374501992</v>
+        <v>11.89243027888446</v>
       </c>
       <c r="J13">
-        <v>10.306772908366529</v>
+        <v>10.350597609561749</v>
       </c>
       <c r="K13">
-        <v>0.78486055776892427</v>
+        <v>0.78884462151394419</v>
       </c>
       <c r="L13" s="9">
-        <v>0.78486055776892427</v>
+        <v>0.78884462151394419</v>
       </c>
       <c r="M13" s="14">
         <v>0.19920318725099601</v>
@@ -2085,45 +2140,49 @@
         <v>0.20318725099601601</v>
       </c>
       <c r="P13">
-        <v>127.55776892430281</v>
+        <v>128.0637450199203</v>
       </c>
       <c r="Q13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R13">
         <v>33.466135458167329</v>
       </c>
       <c r="S13" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="T13">
-        <v>56.573705179282882</v>
+        <v>56.972111553784863</v>
       </c>
       <c r="U13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="V13" s="17">
         <v>100</v>
       </c>
-      <c r="W13"/>
-      <c r="X13"/>
+      <c r="W13" t="s">
+        <v>57</v>
+      </c>
+      <c r="X13" s="35">
+        <v>96</v>
+      </c>
       <c r="Y13">
-        <v>32139</v>
+        <v>32263</v>
       </c>
       <c r="Z13">
-        <v>2972</v>
+        <v>2985</v>
       </c>
       <c r="AA13">
-        <v>35111</v>
+        <v>35248</v>
       </c>
       <c r="AB13">
-        <v>2186</v>
+        <v>2196</v>
       </c>
       <c r="AC13">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD13" s="7">
-        <v>2587</v>
+        <v>2598</v>
       </c>
       <c r="AE13">
         <v>50</v>
@@ -2134,14 +2193,14 @@
       <c r="AG13" s="16">
         <v>51</v>
       </c>
-      <c r="AH13" s="23">
-        <v>130897500000</v>
-      </c>
-      <c r="AI13" s="24">
-        <v>175465634060</v>
-      </c>
-      <c r="AJ13" s="24">
-        <v>44568134060</v>
+      <c r="AH13" s="21">
+        <v>131421090000</v>
+      </c>
+      <c r="AI13" s="22">
+        <v>175963427720</v>
+      </c>
+      <c r="AJ13" s="22">
+        <v>44542337720</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
@@ -2149,10 +2208,10 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>119.68388553161439</v>
@@ -2166,10 +2225,10 @@
       <c r="G14">
         <v>128.3545816733068</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="26">
         <v>11.908366533864539</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="26">
         <v>11.908366533864539</v>
       </c>
       <c r="J14">
@@ -2178,7 +2237,7 @@
       <c r="K14">
         <v>0.70517928286852594</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="26">
         <v>0.70517928286852594</v>
       </c>
       <c r="M14">
@@ -2194,25 +2253,29 @@
         <v>128.11553784860561</v>
       </c>
       <c r="Q14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="R14">
         <v>42.629482071713149</v>
       </c>
       <c r="S14" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="T14">
         <v>51.394422310756973</v>
       </c>
       <c r="U14" t="s">
-        <v>52</v>
-      </c>
-      <c r="V14" s="21">
+        <v>39</v>
+      </c>
+      <c r="V14" s="26">
         <v>72</v>
       </c>
-      <c r="W14"/>
-      <c r="X14"/>
+      <c r="W14" t="s">
+        <v>60</v>
+      </c>
+      <c r="X14" s="26">
+        <v>60</v>
+      </c>
       <c r="Y14">
         <v>32217</v>
       </c>
@@ -2228,7 +2291,7 @@
       <c r="AC14">
         <v>177</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="26">
         <v>2584</v>
       </c>
       <c r="AE14">
@@ -2237,16 +2300,16 @@
       <c r="AF14" s="7">
         <v>5</v>
       </c>
-      <c r="AG14">
+      <c r="AG14" s="26">
         <v>33</v>
       </c>
-      <c r="AH14" s="23">
+      <c r="AH14" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI14" s="24">
+      <c r="AI14" s="22">
         <v>157289866920</v>
       </c>
-      <c r="AJ14" s="24">
+      <c r="AJ14" s="22">
         <v>25868776920</v>
       </c>
     </row>
@@ -2255,12 +2318,12 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="21">
+        <v>32</v>
+      </c>
+      <c r="D15" s="26">
         <v>122.99666202738079</v>
       </c>
       <c r="E15">
@@ -2275,7 +2338,7 @@
       <c r="H15" s="14">
         <v>11.84860557768924</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="26">
         <v>11.84860557768924</v>
       </c>
       <c r="J15">
@@ -2284,7 +2347,7 @@
       <c r="K15">
         <v>0.78486055776892427</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="26">
         <v>0.78486055776892427</v>
       </c>
       <c r="M15">
@@ -2293,32 +2356,36 @@
       <c r="N15">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O15" s="21">
+      <c r="O15" s="26">
         <v>0.15537848605577689</v>
       </c>
       <c r="P15">
         <v>128.11155378486049</v>
       </c>
       <c r="Q15" t="s">
-        <v>35</v>
-      </c>
-      <c r="R15" s="21">
+        <v>40</v>
+      </c>
+      <c r="R15" s="26">
         <v>34.661354581673308</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
-      </c>
-      <c r="T15">
+        <v>50</v>
+      </c>
+      <c r="T15" s="26">
         <v>57.768924302788847</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
-      </c>
-      <c r="V15">
+        <v>36</v>
+      </c>
+      <c r="V15" s="26">
         <v>84</v>
       </c>
-      <c r="W15"/>
-      <c r="X15"/>
+      <c r="W15" t="s">
+        <v>45</v>
+      </c>
+      <c r="X15">
+        <v>76</v>
+      </c>
       <c r="Y15">
         <v>32166</v>
       </c>
@@ -2340,19 +2407,19 @@
       <c r="AE15">
         <v>38</v>
       </c>
-      <c r="AF15" s="21">
+      <c r="AF15" s="26">
         <v>1</v>
       </c>
-      <c r="AG15" s="21">
+      <c r="AG15" s="26">
         <v>39</v>
       </c>
-      <c r="AH15" s="23">
+      <c r="AH15" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI15" s="24">
+      <c r="AI15" s="22">
         <v>161643553900</v>
       </c>
-      <c r="AJ15" s="24">
+      <c r="AJ15" s="22">
         <v>30222463900</v>
       </c>
     </row>
@@ -2361,10 +2428,10 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>122.589138546941</v>
@@ -2381,7 +2448,7 @@
       <c r="H16">
         <v>11.7609561752988</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="26">
         <v>11.7609561752988</v>
       </c>
       <c r="J16">
@@ -2406,25 +2473,29 @@
         <v>128.14741035856571</v>
       </c>
       <c r="Q16" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16">
+        <v>61</v>
+      </c>
+      <c r="R16" s="26">
         <v>32.669322709163353</v>
       </c>
       <c r="S16" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="T16">
         <v>59.362549800796813</v>
       </c>
       <c r="U16" t="s">
-        <v>39</v>
-      </c>
-      <c r="V16">
+        <v>42</v>
+      </c>
+      <c r="V16" s="26">
         <v>88</v>
       </c>
-      <c r="W16"/>
-      <c r="X16"/>
+      <c r="W16" t="s">
+        <v>63</v>
+      </c>
+      <c r="X16">
+        <v>68</v>
+      </c>
       <c r="Y16">
         <v>32235</v>
       </c>
@@ -2449,16 +2520,16 @@
       <c r="AF16">
         <v>3</v>
       </c>
-      <c r="AG16" s="21">
+      <c r="AG16" s="26">
         <v>35</v>
       </c>
-      <c r="AH16" s="23">
+      <c r="AH16" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI16" s="24">
+      <c r="AI16" s="22">
         <v>161107982100</v>
       </c>
-      <c r="AJ16" s="24">
+      <c r="AJ16" s="22">
         <v>29686892100</v>
       </c>
     </row>
@@ -2467,12 +2538,12 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="21">
+        <v>32</v>
+      </c>
+      <c r="D17" s="26">
         <v>120.0807208645127</v>
       </c>
       <c r="E17">
@@ -2493,10 +2564,10 @@
       <c r="J17">
         <v>10.342629482071709</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="26">
         <v>0.82868525896414347</v>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="26">
         <v>0.82868525896414347</v>
       </c>
       <c r="M17">
@@ -2512,25 +2583,29 @@
         <v>128.13944223107569</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R17" s="7">
         <v>31.075697211155379</v>
       </c>
       <c r="S17" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" s="21">
+        <v>41</v>
+      </c>
+      <c r="T17" s="26">
         <v>58.964143426294832</v>
       </c>
       <c r="U17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V17" s="9">
         <v>96</v>
       </c>
-      <c r="W17"/>
-      <c r="X17"/>
+      <c r="W17" t="s">
+        <v>36</v>
+      </c>
+      <c r="X17" s="26">
+        <v>84</v>
+      </c>
       <c r="Y17">
         <v>32219</v>
       </c>
@@ -2543,7 +2618,7 @@
       <c r="AB17">
         <v>2244</v>
       </c>
-      <c r="AC17" s="21">
+      <c r="AC17">
         <v>208</v>
       </c>
       <c r="AD17" s="7">
@@ -2552,19 +2627,19 @@
       <c r="AE17">
         <v>36</v>
       </c>
-      <c r="AF17" s="21">
+      <c r="AF17" s="26">
         <v>0</v>
       </c>
-      <c r="AG17" s="21">
+      <c r="AG17" s="26">
         <v>36</v>
       </c>
-      <c r="AH17" s="23">
+      <c r="AH17" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI17" s="24">
+      <c r="AI17" s="22">
         <v>157811392240</v>
       </c>
-      <c r="AJ17" s="24">
+      <c r="AJ17" s="22">
         <v>26390302240</v>
       </c>
     </row>
@@ -2573,12 +2648,12 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18">
+        <v>32</v>
+      </c>
+      <c r="D18" s="26">
         <v>126.3531556312613</v>
       </c>
       <c r="E18">
@@ -2602,7 +2677,7 @@
       <c r="K18">
         <v>0.8605577689243028</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="26">
         <v>0.8605577689243028</v>
       </c>
       <c r="M18">
@@ -2611,32 +2686,36 @@
       <c r="N18">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="26">
         <v>0.1633466135458167</v>
       </c>
       <c r="P18">
         <v>128.41035856573711</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R18" s="7">
         <v>31.075697211155379</v>
       </c>
       <c r="S18" t="s">
-        <v>38</v>
-      </c>
-      <c r="T18">
+        <v>44</v>
+      </c>
+      <c r="T18" s="26">
         <v>57.370517928286858</v>
       </c>
       <c r="U18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="V18">
         <v>92</v>
       </c>
-      <c r="W18"/>
-      <c r="X18"/>
+      <c r="W18" t="s">
+        <v>46</v>
+      </c>
+      <c r="X18">
+        <v>80</v>
+      </c>
       <c r="Y18">
         <v>32337</v>
       </c>
@@ -2658,19 +2737,19 @@
       <c r="AE18">
         <v>40</v>
       </c>
-      <c r="AF18">
+      <c r="AF18" s="26">
         <v>1</v>
       </c>
-      <c r="AG18">
+      <c r="AG18" s="26">
         <v>41</v>
       </c>
-      <c r="AH18" s="23">
+      <c r="AH18" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI18" s="24">
+      <c r="AI18" s="22">
         <v>166054694380</v>
       </c>
-      <c r="AJ18" s="24">
+      <c r="AJ18" s="22">
         <v>34633604380</v>
       </c>
     </row>
@@ -2679,12 +2758,12 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19">
+        <v>32</v>
+      </c>
+      <c r="D19" s="26">
         <v>130.4308670396814</v>
       </c>
       <c r="E19">
@@ -2696,7 +2775,7 @@
       <c r="G19">
         <v>128.97211155378491</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="26">
         <v>11.314741035856571</v>
       </c>
       <c r="I19">
@@ -2714,7 +2793,7 @@
       <c r="M19">
         <v>0.17131474103585659</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="26">
         <v>7.9681274900398405E-3</v>
       </c>
       <c r="O19">
@@ -2724,25 +2803,29 @@
         <v>128.58964143426289</v>
       </c>
       <c r="Q19" t="s">
-        <v>56</v>
-      </c>
-      <c r="R19" s="21">
+        <v>64</v>
+      </c>
+      <c r="R19" s="26">
         <v>34.262948207171313</v>
       </c>
       <c r="S19" t="s">
-        <v>57</v>
-      </c>
-      <c r="T19">
+        <v>65</v>
+      </c>
+      <c r="T19" s="26">
         <v>54.183266932270911</v>
       </c>
       <c r="U19" t="s">
-        <v>31</v>
-      </c>
-      <c r="V19">
+        <v>35</v>
+      </c>
+      <c r="V19" s="26">
         <v>92</v>
       </c>
-      <c r="W19"/>
-      <c r="X19"/>
+      <c r="W19" t="s">
+        <v>42</v>
+      </c>
+      <c r="X19">
+        <v>88</v>
+      </c>
       <c r="Y19">
         <v>32372</v>
       </c>
@@ -2764,19 +2847,19 @@
       <c r="AE19">
         <v>43</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="26">
         <v>2</v>
       </c>
-      <c r="AG19">
+      <c r="AG19" s="26">
         <v>45</v>
       </c>
-      <c r="AH19" s="24">
+      <c r="AH19" s="22">
         <v>131421090000</v>
       </c>
-      <c r="AI19" s="24">
+      <c r="AI19" s="22">
         <v>171413667160</v>
       </c>
-      <c r="AJ19" s="24">
+      <c r="AJ19" s="22">
         <v>39992577160</v>
       </c>
     </row>
@@ -2785,12 +2868,12 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20">
+        <v>32</v>
+      </c>
+      <c r="D20" s="26">
         <v>129.6847290187595</v>
       </c>
       <c r="E20">
@@ -2805,7 +2888,7 @@
       <c r="H20" s="7">
         <v>11.466135458167329</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="26">
         <v>11.466135458167329</v>
       </c>
       <c r="J20">
@@ -2823,32 +2906,36 @@
       <c r="N20">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="26">
         <v>0.18725099601593631</v>
       </c>
       <c r="P20">
         <v>128.4980079681275</v>
       </c>
       <c r="Q20" t="s">
-        <v>42</v>
-      </c>
-      <c r="R20">
+        <v>49</v>
+      </c>
+      <c r="R20" s="26">
         <v>33.466135458167329</v>
       </c>
       <c r="S20" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="T20">
         <v>54.581673306772913</v>
       </c>
       <c r="U20" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="V20" s="17">
         <v>100</v>
       </c>
-      <c r="W20"/>
-      <c r="X20"/>
+      <c r="W20" t="s">
+        <v>42</v>
+      </c>
+      <c r="X20" s="26">
+        <v>88</v>
+      </c>
       <c r="Y20">
         <v>32342</v>
       </c>
@@ -2870,19 +2957,19 @@
       <c r="AE20">
         <v>46</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="26">
         <v>1</v>
       </c>
       <c r="AG20" s="8">
         <v>47</v>
       </c>
-      <c r="AH20" s="23">
+      <c r="AH20" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI20" s="24">
+      <c r="AI20" s="22">
         <v>170433084440</v>
       </c>
-      <c r="AJ20" s="24">
+      <c r="AJ20" s="22">
         <v>39011994440</v>
       </c>
     </row>
@@ -2891,31 +2978,31 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21">
-        <v>127.5959830800369</v>
+        <v>32</v>
+      </c>
+      <c r="D21" s="26">
+        <v>127.851006642602</v>
       </c>
       <c r="E21">
-        <v>37874</v>
+        <v>37725</v>
       </c>
       <c r="F21">
-        <v>3086</v>
+        <v>3076</v>
       </c>
       <c r="G21">
-        <v>128.796812749004</v>
+        <v>128.2868525896414</v>
       </c>
       <c r="H21">
-        <v>11.55776892430279</v>
+        <v>11.517928286852589</v>
       </c>
       <c r="I21" s="7">
-        <v>11.55776892430279</v>
+        <v>11.517928286852589</v>
       </c>
       <c r="J21">
-        <v>10.358565737051791</v>
+        <v>10.314741035856571</v>
       </c>
       <c r="K21">
         <v>0.72908366533864544</v>
@@ -2933,63 +3020,67 @@
         <v>0.17928286852589639</v>
       </c>
       <c r="P21">
-        <v>128.45418326693229</v>
+        <v>127.9322709163347</v>
       </c>
       <c r="Q21" t="s">
-        <v>35</v>
-      </c>
-      <c r="R21">
-        <v>34.661354581673308</v>
+        <v>64</v>
+      </c>
+      <c r="R21" s="26">
+        <v>34.262948207171313</v>
       </c>
       <c r="S21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="T21">
         <v>51.792828685258961</v>
       </c>
       <c r="U21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V21" s="9">
         <v>96</v>
       </c>
-      <c r="W21"/>
-      <c r="X21"/>
+      <c r="W21" t="s">
+        <v>46</v>
+      </c>
+      <c r="X21" s="26">
+        <v>80</v>
+      </c>
       <c r="Y21">
-        <v>32328</v>
+        <v>32200</v>
       </c>
       <c r="Z21">
-        <v>2901</v>
+        <v>2891</v>
       </c>
       <c r="AA21">
-        <v>35229</v>
+        <v>35091</v>
       </c>
       <c r="AB21">
-        <v>2237</v>
+        <v>2226</v>
       </c>
       <c r="AC21">
         <v>183</v>
       </c>
       <c r="AD21" s="9">
-        <v>2600</v>
+        <v>2589</v>
       </c>
       <c r="AE21">
         <v>43</v>
       </c>
-      <c r="AF21">
+      <c r="AF21" s="26">
         <v>2</v>
       </c>
       <c r="AG21">
         <v>45</v>
       </c>
-      <c r="AH21" s="23">
-        <v>131421090000</v>
-      </c>
-      <c r="AI21" s="24">
-        <v>167688031760</v>
-      </c>
-      <c r="AJ21" s="24">
-        <v>36266941760</v>
+      <c r="AH21" s="21">
+        <v>130897500000</v>
+      </c>
+      <c r="AI21" s="22">
+        <v>167353771420</v>
+      </c>
+      <c r="AJ21" s="22">
+        <v>36456271420</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
@@ -2997,10 +3088,10 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>126.93623706819049</v>
@@ -3017,7 +3108,7 @@
       <c r="H22" s="9">
         <v>11.446215139442231</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="26">
         <v>11.446215139442231</v>
       </c>
       <c r="J22">
@@ -3042,25 +3133,29 @@
         <v>128.47011952191241</v>
       </c>
       <c r="Q22" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="R22">
         <v>33.864541832669318</v>
       </c>
       <c r="S22" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="T22">
         <v>52.589641434262937</v>
       </c>
       <c r="U22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V22">
         <v>88</v>
       </c>
-      <c r="W22"/>
-      <c r="X22"/>
+      <c r="W22" t="s">
+        <v>39</v>
+      </c>
+      <c r="X22">
+        <v>72</v>
+      </c>
       <c r="Y22">
         <v>32304</v>
       </c>
@@ -3082,19 +3177,19 @@
       <c r="AE22">
         <v>35</v>
       </c>
-      <c r="AF22" s="21">
+      <c r="AF22" s="26">
         <v>4</v>
       </c>
       <c r="AG22">
         <v>39</v>
       </c>
-      <c r="AH22" s="23">
+      <c r="AH22" s="21">
         <v>131421090000</v>
       </c>
-      <c r="AI22" s="24">
+      <c r="AI22" s="22">
         <v>166820986360</v>
       </c>
-      <c r="AJ22" s="24">
+      <c r="AJ22" s="22">
         <v>35399896360</v>
       </c>
     </row>
@@ -3103,12 +3198,12 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="21">
+        <v>32</v>
+      </c>
+      <c r="D23" s="26">
         <v>127.3087183038887</v>
       </c>
       <c r="E23">
@@ -3132,7 +3227,7 @@
       <c r="K23" s="9">
         <v>0.87250996015936255</v>
       </c>
-      <c r="L23" s="21">
+      <c r="L23" s="26">
         <v>0.87250996015936255</v>
       </c>
       <c r="M23">
@@ -3148,25 +3243,29 @@
         <v>128.17928286852589</v>
       </c>
       <c r="Q23" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="R23" s="7">
         <v>31.872509960159359</v>
       </c>
       <c r="S23" t="s">
-        <v>62</v>
-      </c>
-      <c r="T23" s="21">
+        <v>70</v>
+      </c>
+      <c r="T23" s="26">
         <v>55.776892430278878</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
-      </c>
-      <c r="V23">
+        <v>36</v>
+      </c>
+      <c r="V23" s="26">
         <v>84</v>
       </c>
-      <c r="W23"/>
-      <c r="X23"/>
+      <c r="W23" t="s">
+        <v>39</v>
+      </c>
+      <c r="X23">
+        <v>72</v>
+      </c>
       <c r="Y23">
         <v>32299</v>
       </c>
@@ -3182,25 +3281,25 @@
       <c r="AC23">
         <v>219</v>
       </c>
-      <c r="AD23" s="21">
+      <c r="AD23" s="26">
         <v>2583</v>
       </c>
       <c r="AE23">
         <v>36</v>
       </c>
-      <c r="AF23" s="21">
+      <c r="AF23" s="26">
         <v>3</v>
       </c>
-      <c r="AG23" s="21">
+      <c r="AG23" s="26">
         <v>39</v>
       </c>
-      <c r="AH23" s="24">
+      <c r="AH23" s="22">
         <v>131421090000</v>
       </c>
-      <c r="AI23" s="24">
+      <c r="AI23" s="22">
         <v>167310505260</v>
       </c>
-      <c r="AJ23" s="24">
+      <c r="AJ23" s="22">
         <v>35889415260</v>
       </c>
     </row>
@@ -3209,143 +3308,147 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="21">
-        <v>129.31329262297251</v>
+        <v>32</v>
+      </c>
+      <c r="D24" s="26">
+        <v>128.67639430852381</v>
       </c>
       <c r="E24">
-        <v>37883</v>
+        <v>37726</v>
       </c>
       <c r="F24">
-        <v>3086</v>
+        <v>3077</v>
       </c>
       <c r="G24">
-        <v>128.84860557768931</v>
-      </c>
-      <c r="H24">
-        <v>11.553784860557769</v>
-      </c>
-      <c r="I24">
-        <v>11.553784860557769</v>
+        <v>128.30278884462149</v>
+      </c>
+      <c r="H24" s="26">
+        <v>11.517928286852589</v>
+      </c>
+      <c r="I24" s="26">
+        <v>11.517928286852589</v>
       </c>
       <c r="J24">
-        <v>10.334661354581669</v>
+        <v>10.29482071713147</v>
       </c>
       <c r="K24">
         <v>0.73705179282868527</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="26">
         <v>0.73705179282868527</v>
       </c>
       <c r="M24" s="9">
-        <v>0.18725099601593631</v>
+        <v>0.18326693227091631</v>
       </c>
       <c r="N24">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O24" s="21">
-        <v>0.1912350597609562</v>
+      <c r="O24" s="26">
+        <v>0.18725099601593631</v>
       </c>
       <c r="P24">
-        <v>128.45418326693229</v>
+        <v>127.92828685258959</v>
       </c>
       <c r="Q24" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="R24" s="7">
         <v>31.474103585657371</v>
       </c>
       <c r="S24" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="T24">
-        <v>55.378486055776889</v>
+        <v>54.980079681274887</v>
       </c>
       <c r="U24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V24">
         <v>88</v>
       </c>
-      <c r="W24"/>
-      <c r="X24"/>
+      <c r="W24" t="s">
+        <v>45</v>
+      </c>
+      <c r="X24">
+        <v>76</v>
+      </c>
       <c r="Y24">
-        <v>32341</v>
+        <v>32204</v>
       </c>
       <c r="Z24">
-        <v>2900</v>
+        <v>2891</v>
       </c>
       <c r="AA24">
-        <v>35241</v>
+        <v>35095</v>
       </c>
       <c r="AB24">
-        <v>2217</v>
+        <v>2211</v>
       </c>
       <c r="AC24">
         <v>185</v>
       </c>
-      <c r="AD24" s="21">
-        <v>2594</v>
+      <c r="AD24" s="26">
+        <v>2584</v>
       </c>
       <c r="AE24">
+        <v>46</v>
+      </c>
+      <c r="AF24" s="26">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="7">
         <v>47</v>
       </c>
-      <c r="AF24" s="21">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="7">
-        <v>48</v>
-      </c>
-      <c r="AH24" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI24" s="24">
-        <v>169944938680</v>
-      </c>
-      <c r="AJ24" s="24">
-        <v>38523848680</v>
+      <c r="AH24" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI24" s="22">
+        <v>168434183240</v>
+      </c>
+      <c r="AJ24" s="22">
+        <v>37536683240</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="A25" s="26">
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="21">
-        <v>129.63107083025031</v>
+        <v>32</v>
+      </c>
+      <c r="D25" s="26">
+        <v>129.67866246230199</v>
       </c>
       <c r="E25">
-        <v>37906</v>
+        <v>37755</v>
       </c>
       <c r="F25">
-        <v>3196</v>
+        <v>3184</v>
       </c>
       <c r="G25">
-        <v>128.65737051792831</v>
+        <v>128.13545816733071</v>
       </c>
       <c r="H25">
-        <v>11.8605577689243</v>
+        <v>11.820717131474099</v>
       </c>
       <c r="I25">
-        <v>11.8605577689243</v>
+        <v>11.820717131474099</v>
       </c>
       <c r="J25">
-        <v>10.32669322709163</v>
+        <v>10.28685258964143</v>
       </c>
       <c r="K25" s="7">
-        <v>0.86852589641434264</v>
-      </c>
-      <c r="L25" s="21">
-        <v>0.86852589641434264</v>
+        <v>0.8605577689243028</v>
+      </c>
+      <c r="L25" s="26">
+        <v>0.8605577689243028</v>
       </c>
       <c r="M25">
         <v>0.17131474103585659</v>
@@ -3353,49 +3456,53 @@
       <c r="N25">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O25" s="21">
+      <c r="O25" s="26">
         <v>0.1752988047808765</v>
       </c>
       <c r="P25">
-        <v>128.09561752988051</v>
+        <v>127.58565737051789</v>
       </c>
       <c r="Q25" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="R25" s="9">
         <v>29.482071713147409</v>
       </c>
       <c r="S25" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="T25" s="14">
-        <v>64.541832669322702</v>
+        <v>64.143426294820713</v>
       </c>
       <c r="U25" t="s">
-        <v>34</v>
-      </c>
-      <c r="V25">
+        <v>36</v>
+      </c>
+      <c r="V25" s="26">
         <v>84</v>
       </c>
-      <c r="W25"/>
-      <c r="X25"/>
+      <c r="W25" t="s">
+        <v>45</v>
+      </c>
+      <c r="X25" s="26">
+        <v>76</v>
+      </c>
       <c r="Y25">
-        <v>32293</v>
+        <v>32162</v>
       </c>
       <c r="Z25">
-        <v>2977</v>
+        <v>2967</v>
       </c>
       <c r="AA25">
-        <v>35270</v>
+        <v>35129</v>
       </c>
       <c r="AB25">
-        <v>2198</v>
+        <v>2190</v>
       </c>
       <c r="AC25">
-        <v>218</v>
-      </c>
-      <c r="AD25" s="21">
-        <v>2592</v>
+        <v>216</v>
+      </c>
+      <c r="AD25" s="26">
+        <v>2582</v>
       </c>
       <c r="AE25">
         <v>43</v>
@@ -3403,17 +3510,17 @@
       <c r="AF25">
         <v>1</v>
       </c>
-      <c r="AG25" s="21">
+      <c r="AG25" s="26">
         <v>44</v>
       </c>
-      <c r="AH25" s="24">
-        <v>131498900000</v>
-      </c>
-      <c r="AI25" s="24">
-        <v>170463432200</v>
-      </c>
-      <c r="AJ25" s="24">
-        <v>38964532200</v>
+      <c r="AH25" s="22">
+        <v>130975000000</v>
+      </c>
+      <c r="AI25" s="22">
+        <v>169846628160</v>
+      </c>
+      <c r="AJ25" s="22">
+        <v>38871628160</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
@@ -3421,12 +3528,12 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26">
+        <v>32</v>
+      </c>
+      <c r="D26" s="26">
         <v>129.99342434043169</v>
       </c>
       <c r="E26">
@@ -3450,7 +3557,7 @@
       <c r="K26">
         <v>0.82868525896414347</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="26">
         <v>0.82868525896414347</v>
       </c>
       <c r="M26">
@@ -3459,32 +3566,36 @@
       <c r="N26">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="26">
         <v>0.18326693227091631</v>
       </c>
       <c r="P26">
         <v>128.46215139442231</v>
       </c>
       <c r="Q26" t="s">
-        <v>45</v>
-      </c>
-      <c r="R26">
+        <v>52</v>
+      </c>
+      <c r="R26" s="26">
         <v>32.270916334661351</v>
       </c>
       <c r="S26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T26">
         <v>58.167330677290842</v>
       </c>
       <c r="U26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="V26">
         <v>92</v>
       </c>
-      <c r="W26"/>
-      <c r="X26"/>
+      <c r="W26" t="s">
+        <v>35</v>
+      </c>
+      <c r="X26" s="9">
+        <v>92</v>
+      </c>
       <c r="Y26">
         <v>32391</v>
       </c>
@@ -3506,19 +3617,19 @@
       <c r="AE26">
         <v>45</v>
       </c>
-      <c r="AF26">
+      <c r="AF26" s="26">
         <v>1</v>
       </c>
-      <c r="AG26">
+      <c r="AG26" s="26">
         <v>46</v>
       </c>
-      <c r="AH26" s="24">
+      <c r="AH26" s="22">
         <v>131498900000</v>
       </c>
-      <c r="AI26" s="24">
+      <c r="AI26" s="22">
         <v>170939923080</v>
       </c>
-      <c r="AJ26" s="24">
+      <c r="AJ26" s="22">
         <v>39441023080</v>
       </c>
     </row>
@@ -3527,12 +3638,12 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27">
+        <v>32</v>
+      </c>
+      <c r="D27" s="26">
         <v>126.8899505319056</v>
       </c>
       <c r="E27">
@@ -3544,7 +3655,7 @@
       <c r="G27">
         <v>128.7250996015936</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="26">
         <v>11.749003984063741</v>
       </c>
       <c r="I27" s="9">
@@ -3553,16 +3664,16 @@
       <c r="J27">
         <v>10.31075697211155</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="26">
         <v>0.86454183266932272</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="26">
         <v>0.86454183266932272</v>
       </c>
       <c r="M27">
         <v>0.151394422310757</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="26">
         <v>7.9681274900398405E-3</v>
       </c>
       <c r="O27">
@@ -3572,25 +3683,29 @@
         <v>128.207171314741</v>
       </c>
       <c r="Q27" t="s">
-        <v>45</v>
-      </c>
-      <c r="R27">
+        <v>52</v>
+      </c>
+      <c r="R27" s="26">
         <v>32.270916334661351</v>
       </c>
       <c r="S27" t="s">
-        <v>62</v>
-      </c>
-      <c r="T27">
+        <v>70</v>
+      </c>
+      <c r="T27" s="26">
         <v>55.776892430278878</v>
       </c>
       <c r="U27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V27" s="9">
         <v>96</v>
       </c>
-      <c r="W27"/>
-      <c r="X27"/>
+      <c r="W27" t="s">
+        <v>42</v>
+      </c>
+      <c r="X27">
+        <v>88</v>
+      </c>
       <c r="Y27">
         <v>32310</v>
       </c>
@@ -3606,25 +3721,25 @@
       <c r="AC27">
         <v>217</v>
       </c>
-      <c r="AD27" s="21">
+      <c r="AD27" s="26">
         <v>2588</v>
       </c>
       <c r="AE27">
         <v>38</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" s="26">
         <v>2</v>
       </c>
-      <c r="AG27">
+      <c r="AG27" s="26">
         <v>40</v>
       </c>
-      <c r="AH27" s="24">
+      <c r="AH27" s="22">
         <v>131498900000</v>
       </c>
-      <c r="AI27" s="24">
+      <c r="AI27" s="22">
         <v>166858889160</v>
       </c>
-      <c r="AJ27" s="24">
+      <c r="AJ27" s="22">
         <v>35359989160</v>
       </c>
     </row>
@@ -3633,31 +3748,31 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="21">
-        <v>125.272638858576</v>
+        <v>32</v>
+      </c>
+      <c r="D28" s="26">
+        <v>125.5287304447414</v>
       </c>
       <c r="E28">
-        <v>37875</v>
+        <v>37724</v>
       </c>
       <c r="F28">
-        <v>3104</v>
+        <v>3094</v>
       </c>
       <c r="G28">
-        <v>128.88446215139439</v>
+        <v>128.36254980079681</v>
       </c>
       <c r="H28">
-        <v>11.553784860557769</v>
+        <v>11.51394422310757</v>
       </c>
       <c r="I28" s="7">
-        <v>11.553784860557769</v>
+        <v>11.51394422310757</v>
       </c>
       <c r="J28">
-        <v>10.306772908366529</v>
+        <v>10.266932270916341</v>
       </c>
       <c r="K28">
         <v>0.79681274900398402</v>
@@ -3671,67 +3786,71 @@
       <c r="N28">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="26">
         <v>0.151394422310757</v>
       </c>
       <c r="P28">
-        <v>128.46215139442231</v>
+        <v>127.9402390438247</v>
       </c>
       <c r="Q28" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="R28">
-        <v>34.661354581673308</v>
+        <v>34.262948207171313</v>
       </c>
       <c r="S28" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="T28">
         <v>55.378486055776889</v>
       </c>
       <c r="U28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V28" s="9">
         <v>96</v>
       </c>
-      <c r="W28"/>
-      <c r="X28"/>
+      <c r="W28" t="s">
+        <v>42</v>
+      </c>
+      <c r="X28">
+        <v>88</v>
+      </c>
       <c r="Y28">
-        <v>32350</v>
+        <v>32219</v>
       </c>
       <c r="Z28">
-        <v>2900</v>
+        <v>2890</v>
       </c>
       <c r="AA28">
-        <v>35250</v>
+        <v>35109</v>
       </c>
       <c r="AB28">
-        <v>2235</v>
+        <v>2225</v>
       </c>
       <c r="AC28">
         <v>200</v>
       </c>
-      <c r="AD28">
-        <v>2587</v>
+      <c r="AD28" s="26">
+        <v>2577</v>
       </c>
       <c r="AE28">
         <v>34</v>
       </c>
-      <c r="AF28" s="21">
+      <c r="AF28" s="26">
         <v>4</v>
       </c>
-      <c r="AG28">
+      <c r="AG28" s="26">
         <v>38</v>
       </c>
-      <c r="AH28" s="24">
-        <v>131498900000</v>
-      </c>
-      <c r="AI28" s="24">
-        <v>164732142100</v>
-      </c>
-      <c r="AJ28" s="24">
-        <v>33233242100</v>
+      <c r="AH28" s="22">
+        <v>130975000000</v>
+      </c>
+      <c r="AI28" s="22">
+        <v>164411254700</v>
+      </c>
+      <c r="AJ28" s="22">
+        <v>33436254700</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
@@ -3739,37 +3858,37 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D29" s="7">
-        <v>136.6171490255812</v>
+        <v>136.8136510479099</v>
       </c>
       <c r="E29">
-        <v>37914</v>
+        <v>37763</v>
       </c>
       <c r="F29">
-        <v>3127</v>
+        <v>3118</v>
       </c>
       <c r="G29">
-        <v>128.90438247011949</v>
+        <v>128.3745019920319</v>
       </c>
       <c r="H29">
-        <v>11.613545816733071</v>
+        <v>11.58167330677291</v>
       </c>
       <c r="I29" s="9">
-        <v>11.613545816733071</v>
+        <v>11.58167330677291</v>
       </c>
       <c r="J29">
-        <v>10.34661354581673</v>
+        <v>10.306772908366529</v>
       </c>
       <c r="K29">
-        <v>0.82071713147410363</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="L29">
-        <v>0.82071713147410363</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="M29">
         <v>0.1633466135458167</v>
@@ -3777,49 +3896,53 @@
       <c r="N29">
         <v>2.3904382470119521E-2</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="26">
         <v>0.18725099601593631</v>
       </c>
       <c r="P29">
-        <v>128.37051792828689</v>
+        <v>127.8446215139442</v>
       </c>
       <c r="Q29" t="s">
-        <v>45</v>
-      </c>
-      <c r="R29">
+        <v>52</v>
+      </c>
+      <c r="R29" s="26">
         <v>32.270916334661351</v>
       </c>
       <c r="S29" t="s">
-        <v>66</v>
-      </c>
-      <c r="T29">
+        <v>75</v>
+      </c>
+      <c r="T29" s="26">
         <v>59.760956175298809</v>
       </c>
       <c r="U29" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="V29" s="17">
         <v>100</v>
       </c>
-      <c r="W29"/>
-      <c r="X29"/>
+      <c r="W29" t="s">
+        <v>35</v>
+      </c>
+      <c r="X29" s="9">
+        <v>92</v>
+      </c>
       <c r="Y29">
-        <v>32355</v>
+        <v>32222</v>
       </c>
       <c r="Z29">
-        <v>2915</v>
+        <v>2907</v>
       </c>
       <c r="AA29">
-        <v>35270</v>
+        <v>35129</v>
       </c>
       <c r="AB29">
-        <v>2203</v>
+        <v>2194</v>
       </c>
       <c r="AC29">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AD29" s="7">
-        <v>2597</v>
+        <v>2587</v>
       </c>
       <c r="AE29">
         <v>41</v>
@@ -3830,14 +3953,14 @@
       <c r="AG29" s="8">
         <v>47</v>
       </c>
-      <c r="AH29" s="24">
-        <v>131498900000</v>
-      </c>
-      <c r="AI29" s="24">
-        <v>179650048180</v>
-      </c>
-      <c r="AJ29" s="24">
-        <v>48151148180</v>
+      <c r="AH29" s="22">
+        <v>130975000000</v>
+      </c>
+      <c r="AI29" s="22">
+        <v>179191679460</v>
+      </c>
+      <c r="AJ29" s="22">
+        <v>48216679460</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
@@ -3845,37 +3968,37 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D30">
-        <v>127.35500223956249</v>
+        <v>127.5067412254247</v>
       </c>
       <c r="E30">
-        <v>37858</v>
+        <v>37708</v>
       </c>
       <c r="F30">
-        <v>3165</v>
+        <v>3154</v>
       </c>
       <c r="G30">
-        <v>128.58964143426289</v>
+        <v>128.07171314741029</v>
       </c>
       <c r="H30">
-        <v>11.768924302788839</v>
+        <v>11.729083665338649</v>
       </c>
       <c r="I30" s="7">
-        <v>11.768924302788839</v>
+        <v>11.729083665338649</v>
       </c>
       <c r="J30">
-        <v>10.31872509960159</v>
+        <v>10.278884462151391</v>
       </c>
       <c r="K30">
-        <v>0.82071713147410363</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="L30">
-        <v>0.82071713147410363</v>
+        <v>0.81673306772908372</v>
       </c>
       <c r="M30">
         <v>0.13147410358565739</v>
@@ -3887,45 +4010,49 @@
         <v>0.151394422310757</v>
       </c>
       <c r="P30">
-        <v>128.21912350597611</v>
+        <v>127.70119521912351</v>
       </c>
       <c r="Q30" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="R30">
         <v>35.458167330677291</v>
       </c>
       <c r="S30" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="T30">
         <v>56.573705179282882</v>
       </c>
       <c r="U30" t="s">
-        <v>34</v>
-      </c>
-      <c r="V30">
+        <v>36</v>
+      </c>
+      <c r="V30" s="26">
         <v>84</v>
       </c>
-      <c r="W30"/>
-      <c r="X30"/>
+      <c r="W30" t="s">
+        <v>45</v>
+      </c>
+      <c r="X30">
+        <v>76</v>
+      </c>
       <c r="Y30">
-        <v>32276</v>
+        <v>32146</v>
       </c>
       <c r="Z30">
-        <v>2954</v>
+        <v>2944</v>
       </c>
       <c r="AA30">
-        <v>35230</v>
+        <v>35090</v>
       </c>
       <c r="AB30">
-        <v>2232</v>
+        <v>2223</v>
       </c>
       <c r="AC30">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AD30" s="7">
-        <v>2590</v>
+        <v>2580</v>
       </c>
       <c r="AE30">
         <v>33</v>
@@ -3936,14 +4063,14 @@
       <c r="AG30">
         <v>38</v>
       </c>
-      <c r="AH30" s="24">
-        <v>131498900000</v>
-      </c>
-      <c r="AI30" s="24">
-        <v>167470427040</v>
-      </c>
-      <c r="AJ30" s="24">
-        <v>35971527040</v>
+      <c r="AH30" s="22">
+        <v>130975000000</v>
+      </c>
+      <c r="AI30" s="22">
+        <v>167001954320</v>
+      </c>
+      <c r="AJ30" s="22">
+        <v>36026954320</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
@@ -3951,36 +4078,36 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D31">
-        <v>132.16461892837131</v>
+        <v>132.44868156518419</v>
       </c>
       <c r="E31">
-        <v>37880</v>
+        <v>37730</v>
       </c>
       <c r="F31">
-        <v>3196</v>
+        <v>3186</v>
       </c>
       <c r="G31">
-        <v>128.53784860557769</v>
-      </c>
-      <c r="H31" s="21">
-        <v>11.89243027888446</v>
+        <v>128.0199203187251</v>
+      </c>
+      <c r="H31" s="26">
+        <v>11.85258964143426</v>
       </c>
       <c r="I31" s="7">
-        <v>11.89243027888446</v>
+        <v>11.85258964143426</v>
       </c>
       <c r="J31">
-        <v>10.31872509960159</v>
-      </c>
-      <c r="K31">
+        <v>10.278884462151391</v>
+      </c>
+      <c r="K31" s="26">
         <v>0.81673306772908372</v>
       </c>
-      <c r="L31" s="21">
+      <c r="L31" s="26">
         <v>0.81673306772908372</v>
       </c>
       <c r="M31">
@@ -3993,45 +4120,49 @@
         <v>0.16733067729083659</v>
       </c>
       <c r="P31">
-        <v>128.09561752988051</v>
+        <v>127.5737051792829</v>
       </c>
       <c r="Q31" t="s">
-        <v>42</v>
-      </c>
-      <c r="R31">
-        <v>33.466135458167329</v>
+        <v>78</v>
+      </c>
+      <c r="R31" s="26">
+        <v>33.067729083665327</v>
       </c>
       <c r="S31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T31">
         <v>58.167330677290842</v>
       </c>
       <c r="U31" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="V31">
         <v>92</v>
       </c>
-      <c r="W31"/>
-      <c r="X31"/>
+      <c r="W31" t="s">
+        <v>36</v>
+      </c>
+      <c r="X31">
+        <v>84</v>
+      </c>
       <c r="Y31">
-        <v>32263</v>
+        <v>32133</v>
       </c>
       <c r="Z31">
-        <v>2985</v>
+        <v>2975</v>
       </c>
       <c r="AA31">
-        <v>35248</v>
+        <v>35108</v>
       </c>
       <c r="AB31">
-        <v>2217</v>
+        <v>2207</v>
       </c>
       <c r="AC31">
         <v>205</v>
       </c>
       <c r="AD31" s="7">
-        <v>2590</v>
+        <v>2580</v>
       </c>
       <c r="AE31">
         <v>36</v>
@@ -4039,30 +4170,30 @@
       <c r="AF31" s="9">
         <v>6</v>
       </c>
-      <c r="AG31">
+      <c r="AG31" s="26">
         <v>42</v>
       </c>
-      <c r="AH31" s="24">
-        <v>131498900000</v>
-      </c>
-      <c r="AI31" s="24">
-        <v>173795020080</v>
-      </c>
-      <c r="AJ31" s="24">
-        <v>42296120080</v>
+      <c r="AH31" s="22">
+        <v>130975000000</v>
+      </c>
+      <c r="AI31" s="22">
+        <v>173474660680</v>
+      </c>
+      <c r="AJ31" s="22">
+        <v>42499660680</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="A32" s="26">
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32">
+        <v>32</v>
+      </c>
+      <c r="D32" s="26">
         <v>122.7668023534798</v>
       </c>
       <c r="E32">
@@ -4086,41 +4217,45 @@
       <c r="K32" s="10">
         <v>0.8127490039840638</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="26">
         <v>0.8127490039840638</v>
       </c>
-      <c r="M32" s="21">
+      <c r="M32" s="26">
         <v>0.14741035856573709</v>
       </c>
       <c r="N32">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="26">
         <v>0.151394422310757</v>
       </c>
       <c r="P32">
         <v>127.95617529880479</v>
       </c>
       <c r="Q32" t="s">
-        <v>42</v>
-      </c>
-      <c r="R32" s="21">
+        <v>49</v>
+      </c>
+      <c r="R32" s="26">
         <v>33.466135458167329</v>
       </c>
       <c r="S32" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="T32">
         <v>56.573705179282882</v>
       </c>
       <c r="U32" t="s">
+        <v>45</v>
+      </c>
+      <c r="V32" s="26">
+        <v>76</v>
+      </c>
+      <c r="W32" t="s">
+        <v>63</v>
+      </c>
+      <c r="X32" s="26">
         <v>68</v>
       </c>
-      <c r="V32">
-        <v>76</v>
-      </c>
-      <c r="W32"/>
-      <c r="X32"/>
       <c r="Y32">
         <v>32219</v>
       </c>
@@ -4136,7 +4271,7 @@
       <c r="AC32">
         <v>204</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" s="26">
         <v>2589</v>
       </c>
       <c r="AE32">
@@ -4145,16 +4280,16 @@
       <c r="AF32">
         <v>1</v>
       </c>
-      <c r="AG32" s="21">
+      <c r="AG32" s="26">
         <v>38</v>
       </c>
-      <c r="AH32" s="24">
+      <c r="AH32" s="22">
         <v>131498900000</v>
       </c>
-      <c r="AI32" s="24">
+      <c r="AI32" s="22">
         <v>161436994660</v>
       </c>
-      <c r="AJ32" s="24">
+      <c r="AJ32" s="22">
         <v>29938094660</v>
       </c>
     </row>
@@ -4163,31 +4298,31 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D33">
-        <v>129.44404938355021</v>
+        <v>129.70084015355519</v>
       </c>
       <c r="E33">
-        <v>37866</v>
+        <v>37716</v>
       </c>
       <c r="F33">
-        <v>2946</v>
+        <v>2932</v>
       </c>
       <c r="G33">
-        <v>129.36653386454179</v>
-      </c>
-      <c r="H33">
-        <v>10.9402390438247</v>
-      </c>
-      <c r="I33">
-        <v>10.9402390438247</v>
+        <v>128.86454183266929</v>
+      </c>
+      <c r="H33" s="26">
+        <v>10.88446215139442</v>
+      </c>
+      <c r="I33" s="26">
+        <v>10.88446215139442</v>
       </c>
       <c r="J33">
-        <v>10.366533864541831</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="K33" s="10">
         <v>0.79282868525896411</v>
@@ -4205,45 +4340,49 @@
         <v>0.18725099601593631</v>
       </c>
       <c r="P33">
-        <v>129.04382470119521</v>
+        <v>128.53784860557769</v>
       </c>
       <c r="Q33" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="R33" s="7">
-        <v>31.075697211155379</v>
+        <v>30.677290836653391</v>
       </c>
       <c r="S33" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="T33">
         <v>56.972111553784863</v>
       </c>
       <c r="U33" t="s">
-        <v>39</v>
-      </c>
-      <c r="V33">
+        <v>42</v>
+      </c>
+      <c r="V33" s="26">
         <v>88</v>
       </c>
-      <c r="W33"/>
-      <c r="X33"/>
+      <c r="W33" t="s">
+        <v>36</v>
+      </c>
+      <c r="X33">
+        <v>84</v>
+      </c>
       <c r="Y33">
-        <v>32471</v>
+        <v>32345</v>
       </c>
       <c r="Z33">
-        <v>2746</v>
+        <v>2732</v>
       </c>
       <c r="AA33">
-        <v>35217</v>
+        <v>35077</v>
       </c>
       <c r="AB33">
-        <v>2215</v>
+        <v>2205</v>
       </c>
       <c r="AC33">
         <v>199</v>
       </c>
       <c r="AD33" s="9">
-        <v>2602</v>
+        <v>2592</v>
       </c>
       <c r="AE33">
         <v>46</v>
@@ -4254,14 +4393,14 @@
       <c r="AG33" s="8">
         <v>47</v>
       </c>
-      <c r="AH33" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI33" s="24">
-        <v>170116780640</v>
-      </c>
-      <c r="AJ33" s="24">
-        <v>38695690640</v>
+      <c r="AH33" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI33" s="22">
+        <v>169775157240</v>
+      </c>
+      <c r="AJ33" s="22">
+        <v>38877657240</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
@@ -4269,31 +4408,31 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D34" s="7">
-        <v>135.8033808120143</v>
+        <v>136.10997606524191</v>
       </c>
       <c r="E34">
-        <v>37866</v>
+        <v>37716</v>
       </c>
       <c r="F34">
-        <v>3131</v>
+        <v>3123</v>
       </c>
       <c r="G34">
-        <v>128.68127490039839</v>
-      </c>
-      <c r="H34">
-        <v>11.62549800796813</v>
-      </c>
-      <c r="I34">
-        <v>11.62549800796813</v>
+        <v>128.15537848605581</v>
+      </c>
+      <c r="H34" s="26">
+        <v>11.59362549800797</v>
+      </c>
+      <c r="I34" s="26">
+        <v>11.59362549800797</v>
       </c>
       <c r="J34">
-        <v>10.366533864541831</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="K34">
         <v>0.82868525896414347</v>
@@ -4311,45 +4450,49 @@
         <v>0.18725099601593631</v>
       </c>
       <c r="P34">
-        <v>128.27091633466139</v>
+        <v>127.7410358565737</v>
       </c>
       <c r="Q34" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R34" s="9">
-        <v>30.2788844621514</v>
+        <v>29.880478087649401</v>
       </c>
       <c r="S34" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="T34" s="9">
         <v>63.34661354581673</v>
       </c>
       <c r="U34" t="s">
-        <v>31</v>
-      </c>
-      <c r="V34">
+        <v>35</v>
+      </c>
+      <c r="V34" s="26">
         <v>92</v>
       </c>
-      <c r="W34"/>
-      <c r="X34"/>
+      <c r="W34" t="s">
+        <v>42</v>
+      </c>
+      <c r="X34">
+        <v>88</v>
+      </c>
       <c r="Y34">
-        <v>32299</v>
+        <v>32167</v>
       </c>
       <c r="Z34">
-        <v>2918</v>
+        <v>2910</v>
       </c>
       <c r="AA34">
-        <v>35217</v>
+        <v>35077</v>
       </c>
       <c r="AB34">
-        <v>2206</v>
+        <v>2196</v>
       </c>
       <c r="AC34">
         <v>208</v>
       </c>
       <c r="AD34" s="9">
-        <v>2602</v>
+        <v>2592</v>
       </c>
       <c r="AE34">
         <v>42</v>
@@ -4360,27 +4503,27 @@
       <c r="AG34" s="8">
         <v>47</v>
       </c>
-      <c r="AH34" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI34" s="24">
-        <v>178474283320</v>
-      </c>
-      <c r="AJ34" s="24">
-        <v>47053193320</v>
+      <c r="AH34" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI34" s="22">
+        <v>178164555920</v>
+      </c>
+      <c r="AJ34" s="22">
+        <v>47267055920</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A35">
+      <c r="A35" s="26">
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="21">
+        <v>32</v>
+      </c>
+      <c r="D35" s="26">
         <v>130.74574834221809</v>
       </c>
       <c r="E35">
@@ -4392,7 +4535,7 @@
       <c r="G35">
         <v>128.45019920318731</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="26">
         <v>11.856573705179279</v>
       </c>
       <c r="I35">
@@ -4413,32 +4556,36 @@
       <c r="N35">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="26">
         <v>0.18725099601593631</v>
       </c>
       <c r="P35">
         <v>128.10756972111551</v>
       </c>
       <c r="Q35" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="R35">
         <v>32.669322709163353</v>
       </c>
       <c r="S35" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T35">
         <v>57.768924302788847</v>
       </c>
       <c r="U35" t="s">
-        <v>39</v>
-      </c>
-      <c r="V35">
+        <v>42</v>
+      </c>
+      <c r="V35" s="26">
         <v>88</v>
       </c>
-      <c r="W35"/>
-      <c r="X35"/>
+      <c r="W35" t="s">
+        <v>36</v>
+      </c>
+      <c r="X35" s="26">
+        <v>84</v>
+      </c>
       <c r="Y35">
         <v>32241</v>
       </c>
@@ -4460,19 +4607,19 @@
       <c r="AE35">
         <v>45</v>
       </c>
-      <c r="AF35" s="21">
+      <c r="AF35" s="26">
         <v>2</v>
       </c>
       <c r="AG35" s="8">
         <v>47</v>
       </c>
-      <c r="AH35" s="24">
+      <c r="AH35" s="22">
         <v>131421090000</v>
       </c>
-      <c r="AI35" s="24">
+      <c r="AI35" s="22">
         <v>171827487600</v>
       </c>
-      <c r="AJ35" s="24">
+      <c r="AJ35" s="22">
         <v>40406397600</v>
       </c>
     </row>
@@ -4481,87 +4628,91 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D36" s="7">
-        <v>136.12890390728001</v>
+        <v>136.19425220496959</v>
       </c>
       <c r="E36">
-        <v>37866</v>
+        <v>37716</v>
       </c>
       <c r="F36">
-        <v>3212</v>
+        <v>3198</v>
       </c>
       <c r="G36">
-        <v>128.3585657370518</v>
+        <v>127.8486055776892</v>
       </c>
       <c r="H36" s="7">
-        <v>11.94820717131474</v>
+        <v>11.900398406374499</v>
       </c>
       <c r="I36">
-        <v>11.94820717131474</v>
+        <v>11.900398406374499</v>
       </c>
       <c r="J36">
-        <v>10.366533864541831</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="K36">
-        <v>0.82868525896414347</v>
+        <v>0.82071713147410363</v>
       </c>
       <c r="L36" s="9">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="M36">
+        <v>0.82071713147410363</v>
+      </c>
+      <c r="M36" s="26">
         <v>0.16733067729083659</v>
       </c>
       <c r="N36" s="14">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O36" s="21">
+      <c r="O36" s="26">
         <v>0.18725099601593631</v>
       </c>
       <c r="P36">
-        <v>127.9123505976096</v>
+        <v>127.406374501992</v>
       </c>
       <c r="Q36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R36" s="7">
         <v>31.075697211155379</v>
       </c>
       <c r="S36" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="T36" s="7">
-        <v>62.948207171314742</v>
+        <v>62.549800796812747</v>
       </c>
       <c r="U36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V36" s="9">
         <v>96</v>
       </c>
-      <c r="W36"/>
-      <c r="X36"/>
+      <c r="W36" t="s">
+        <v>36</v>
+      </c>
+      <c r="X36">
+        <v>84</v>
+      </c>
       <c r="Y36">
-        <v>32218</v>
+        <v>32090</v>
       </c>
       <c r="Z36">
-        <v>2999</v>
+        <v>2987</v>
       </c>
       <c r="AA36">
-        <v>35217</v>
+        <v>35077</v>
       </c>
       <c r="AB36">
-        <v>2206</v>
+        <v>2198</v>
       </c>
       <c r="AC36">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AD36" s="9">
-        <v>2602</v>
+        <v>2592</v>
       </c>
       <c r="AE36">
         <v>42</v>
@@ -4572,14 +4723,14 @@
       <c r="AG36" s="8">
         <v>47</v>
       </c>
-      <c r="AH36" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI36" s="24">
-        <v>178902089320</v>
-      </c>
-      <c r="AJ36" s="24">
-        <v>47480999320</v>
+      <c r="AH36" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI36" s="22">
+        <v>178274871280</v>
+      </c>
+      <c r="AJ36" s="22">
+        <v>47377371280</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
@@ -4587,37 +4738,37 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D37" s="8">
-        <v>133.6345966693778</v>
+        <v>133.80492056761969</v>
       </c>
       <c r="E37">
-        <v>37866</v>
+        <v>37717</v>
       </c>
       <c r="F37">
-        <v>3078</v>
+        <v>3068</v>
       </c>
       <c r="G37">
-        <v>128.82071713147411</v>
+        <v>128.3067729083665</v>
       </c>
       <c r="H37">
-        <v>11.48605577689243</v>
+        <v>11.45019920318725</v>
       </c>
       <c r="I37">
-        <v>11.48605577689243</v>
+        <v>11.45019920318725</v>
       </c>
       <c r="J37">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="K37">
-        <v>0.75697211155378485</v>
+        <v>10.322709163346611</v>
+      </c>
+      <c r="K37" s="26">
+        <v>0.75298804780876494</v>
       </c>
       <c r="L37" s="9">
-        <v>0.75697211155378485</v>
+        <v>0.75298804780876494</v>
       </c>
       <c r="M37">
         <v>0.16733067729083659</v>
@@ -4625,49 +4776,53 @@
       <c r="N37">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="26">
         <v>0.18725099601593631</v>
       </c>
       <c r="P37">
-        <v>128.50597609561751</v>
+        <v>127.9880478087649</v>
       </c>
       <c r="Q37" t="s">
-        <v>35</v>
-      </c>
-      <c r="R37">
+        <v>40</v>
+      </c>
+      <c r="R37" s="26">
         <v>34.661354581673308</v>
       </c>
       <c r="S37" t="s">
-        <v>30</v>
-      </c>
-      <c r="T37">
-        <v>58.167330677290842</v>
+        <v>50</v>
+      </c>
+      <c r="T37" s="26">
+        <v>57.768924302788847</v>
       </c>
       <c r="U37" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V37">
         <v>88</v>
       </c>
-      <c r="W37"/>
-      <c r="X37"/>
+      <c r="W37" t="s">
+        <v>42</v>
+      </c>
+      <c r="X37" s="26">
+        <v>88</v>
+      </c>
       <c r="Y37">
-        <v>32334</v>
+        <v>32205</v>
       </c>
       <c r="Z37">
-        <v>2883</v>
+        <v>2874</v>
       </c>
       <c r="AA37">
-        <v>35217</v>
+        <v>35079</v>
       </c>
       <c r="AB37">
-        <v>2224</v>
+        <v>2214</v>
       </c>
       <c r="AC37">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AD37" s="9">
-        <v>2602</v>
+        <v>2591</v>
       </c>
       <c r="AE37">
         <v>42</v>
@@ -4678,46 +4833,46 @@
       <c r="AG37" s="8">
         <v>47</v>
       </c>
-      <c r="AH37" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI37" s="24">
-        <v>175624043560</v>
-      </c>
-      <c r="AJ37" s="24">
-        <v>44202953560</v>
+      <c r="AH37" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI37" s="22">
+        <v>175147295900</v>
+      </c>
+      <c r="AJ37" s="22">
+        <v>44249795900</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A38" s="27">
+      <c r="A38" s="25">
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D38" s="9">
-        <v>139.08244440827571</v>
+        <v>139.3983315494948</v>
       </c>
       <c r="E38">
-        <v>37897</v>
+        <v>37747</v>
       </c>
       <c r="F38">
-        <v>3160</v>
+        <v>3151</v>
       </c>
       <c r="G38">
-        <v>128.6733067729084</v>
+        <v>128.15139442231069</v>
       </c>
       <c r="H38">
-        <v>11.756972111553781</v>
-      </c>
-      <c r="I38">
-        <v>11.756972111553781</v>
+        <v>11.721115537848609</v>
+      </c>
+      <c r="I38" s="26">
+        <v>11.721115537848609</v>
       </c>
       <c r="J38">
-        <v>10.350597609561749</v>
+        <v>10.31075697211155</v>
       </c>
       <c r="K38">
         <v>0.8127490039840638</v>
@@ -4735,63 +4890,67 @@
         <v>0.20318725099601601</v>
       </c>
       <c r="P38">
-        <v>128.15139442231069</v>
+        <v>127.6294820717131</v>
       </c>
       <c r="Q38" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="R38">
-        <v>29.880478087649401</v>
+        <v>29.482071713147409</v>
       </c>
       <c r="S38" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="T38">
         <v>59.760956175298809</v>
       </c>
       <c r="U38" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="V38" s="17">
         <v>100</v>
       </c>
-      <c r="W38"/>
-      <c r="X38"/>
+      <c r="W38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X38" s="9">
+        <v>92</v>
+      </c>
       <c r="Y38">
-        <v>32297</v>
+        <v>32166</v>
       </c>
       <c r="Z38">
-        <v>2951</v>
+        <v>2942</v>
       </c>
       <c r="AA38">
-        <v>35248</v>
+        <v>35108</v>
       </c>
       <c r="AB38">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="AC38">
         <v>204</v>
       </c>
       <c r="AD38" s="7">
-        <v>2598</v>
+        <v>2588</v>
       </c>
       <c r="AE38">
         <v>46</v>
       </c>
-      <c r="AF38">
+      <c r="AF38" s="26">
         <v>5</v>
       </c>
       <c r="AG38" s="16">
         <v>51</v>
       </c>
-      <c r="AH38" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI38" s="24">
-        <v>182783664440</v>
-      </c>
-      <c r="AJ38" s="24">
-        <v>51362574440</v>
+      <c r="AH38" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI38" s="22">
+        <v>182468931040</v>
+      </c>
+      <c r="AJ38" s="22">
+        <v>51571431040</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
@@ -4799,31 +4958,31 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D39" s="9">
-        <v>137.66597324675971</v>
+        <v>136.18633642267841</v>
       </c>
       <c r="E39">
-        <v>37897</v>
+        <v>37593</v>
       </c>
       <c r="F39">
-        <v>3168</v>
+        <v>3151</v>
       </c>
       <c r="G39">
-        <v>128.6653386454183</v>
+        <v>127.609561752988</v>
       </c>
       <c r="H39">
-        <v>11.76494023904382</v>
+        <v>11.701195219123511</v>
       </c>
       <c r="I39">
-        <v>11.76494023904382</v>
+        <v>11.701195219123511</v>
       </c>
       <c r="J39">
-        <v>10.350597609561749</v>
+        <v>10.262948207171309</v>
       </c>
       <c r="K39">
         <v>0.84462151394422313</v>
@@ -4835,69 +4994,73 @@
         <v>0.1912350597609562</v>
       </c>
       <c r="N39">
-        <v>1.1952191235059761E-2</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="O39" s="16">
-        <v>0.20318725099601601</v>
+        <v>0.19920318725099601</v>
       </c>
       <c r="P39">
-        <v>128.11155378486049</v>
+        <v>127.0557768924303</v>
       </c>
       <c r="Q39" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="R39">
-        <v>30.677290836653391</v>
+        <v>30.2788844621514</v>
       </c>
       <c r="S39" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="T39">
-        <v>62.151394422310759</v>
+        <v>61.752988047808763</v>
       </c>
       <c r="U39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V39" s="9">
         <v>96</v>
       </c>
-      <c r="W39"/>
-      <c r="X39"/>
+      <c r="W39" t="s">
+        <v>57</v>
+      </c>
+      <c r="X39" s="35">
+        <v>96</v>
+      </c>
       <c r="Y39">
-        <v>32295</v>
+        <v>32030</v>
       </c>
       <c r="Z39">
-        <v>2953</v>
+        <v>2937</v>
       </c>
       <c r="AA39">
-        <v>35248</v>
+        <v>34967</v>
       </c>
       <c r="AB39">
-        <v>2182</v>
+        <v>2164</v>
       </c>
       <c r="AC39">
         <v>212</v>
       </c>
       <c r="AD39" s="7">
-        <v>2598</v>
+        <v>2576</v>
       </c>
       <c r="AE39">
         <v>48</v>
       </c>
-      <c r="AF39">
-        <v>3</v>
+      <c r="AF39" s="26">
+        <v>2</v>
       </c>
       <c r="AG39" s="16">
-        <v>51</v>
-      </c>
-      <c r="AH39" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI39" s="24">
-        <v>180922122600</v>
-      </c>
-      <c r="AJ39" s="24">
-        <v>49501032600</v>
+        <v>50</v>
+      </c>
+      <c r="AH39" s="22">
+        <v>130373910000</v>
+      </c>
+      <c r="AI39" s="22">
+        <v>177551451680</v>
+      </c>
+      <c r="AJ39" s="22">
+        <v>47177541680</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
@@ -4905,37 +5068,37 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D40" s="9">
-        <v>138.27420137818061</v>
+        <v>138.7589913656804</v>
       </c>
       <c r="E40">
-        <v>37925</v>
+        <v>37624</v>
       </c>
       <c r="F40">
-        <v>3069</v>
+        <v>3043</v>
       </c>
       <c r="G40">
-        <v>129.12749003984061</v>
-      </c>
-      <c r="H40" s="21">
-        <v>11.446215139442231</v>
+        <v>128.10756972111551</v>
+      </c>
+      <c r="H40" s="26">
+        <v>11.34661354581673</v>
       </c>
       <c r="I40">
-        <v>11.446215139442231</v>
+        <v>11.34661354581673</v>
       </c>
       <c r="J40">
-        <v>10.31872509960159</v>
+        <v>10.2390438247012</v>
       </c>
       <c r="K40">
-        <v>0.75697211155378485</v>
+        <v>0.75298804780876494</v>
       </c>
       <c r="L40">
-        <v>0.75697211155378485</v>
+        <v>0.75298804780876494</v>
       </c>
       <c r="M40">
         <v>0.17928286852589639</v>
@@ -4947,45 +5110,49 @@
         <v>0.20318725099601601</v>
       </c>
       <c r="P40">
-        <v>128.49402390438249</v>
+        <v>127.4741035856574</v>
       </c>
       <c r="Q40" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="R40">
-        <v>36.254980079681268</v>
+        <v>35.856573705179287</v>
       </c>
       <c r="S40" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="T40">
-        <v>52.988047808764939</v>
+        <v>52.589641434262937</v>
       </c>
       <c r="U40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="V40">
         <v>92</v>
       </c>
-      <c r="W40"/>
-      <c r="X40"/>
+      <c r="W40" t="s">
+        <v>36</v>
+      </c>
+      <c r="X40">
+        <v>84</v>
+      </c>
       <c r="Y40">
-        <v>32411</v>
+        <v>32155</v>
       </c>
       <c r="Z40">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="AA40">
-        <v>35284</v>
+        <v>35003</v>
       </c>
       <c r="AB40">
-        <v>2196</v>
+        <v>2177</v>
       </c>
       <c r="AC40">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AD40" s="7">
-        <v>2590</v>
+        <v>2570</v>
       </c>
       <c r="AE40">
         <v>45</v>
@@ -4996,14 +5163,14 @@
       <c r="AG40" s="16">
         <v>51</v>
       </c>
-      <c r="AH40" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI40" s="24">
-        <v>181721462640</v>
-      </c>
-      <c r="AJ40" s="24">
-        <v>50300372640</v>
+      <c r="AH40" s="22">
+        <v>130373910000</v>
+      </c>
+      <c r="AI40" s="22">
+        <v>180905522520</v>
+      </c>
+      <c r="AJ40" s="22">
+        <v>50531612520</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
@@ -5011,37 +5178,37 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D41" s="7">
-        <v>136.37432944742741</v>
+        <v>136.62887879944691</v>
       </c>
       <c r="E41">
-        <v>37925</v>
+        <v>37624</v>
       </c>
       <c r="F41">
-        <v>3207</v>
+        <v>3182</v>
       </c>
       <c r="G41">
-        <v>128.6414342629482</v>
-      </c>
-      <c r="H41">
-        <v>11.932270916334661</v>
-      </c>
-      <c r="I41" s="21">
-        <v>11.932270916334661</v>
+        <v>127.609561752988</v>
+      </c>
+      <c r="H41" s="26">
+        <v>11.844621513944221</v>
+      </c>
+      <c r="I41" s="26">
+        <v>11.844621513944221</v>
       </c>
       <c r="J41">
-        <v>10.31872509960159</v>
-      </c>
-      <c r="K41" s="21">
-        <v>0.8366533864541833</v>
-      </c>
-      <c r="L41">
-        <v>0.8366533864541833</v>
+        <v>10.2390438247012</v>
+      </c>
+      <c r="K41" s="26">
+        <v>0.82470119521912355</v>
+      </c>
+      <c r="L41" s="26">
+        <v>0.82470119521912355</v>
       </c>
       <c r="M41">
         <v>0.19521912350597609</v>
@@ -5053,45 +5220,49 @@
         <v>0.20318725099601601</v>
       </c>
       <c r="P41">
-        <v>128.01195219123511</v>
+        <v>126.9880478087649</v>
       </c>
       <c r="Q41" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R41" s="9">
         <v>26.294820717131469</v>
       </c>
       <c r="S41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T41" s="17">
-        <v>63.745019920318732</v>
+        <v>63.34661354581673</v>
       </c>
       <c r="U41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V41">
         <v>88</v>
       </c>
-      <c r="W41"/>
-      <c r="X41"/>
+      <c r="W41" t="s">
+        <v>36</v>
+      </c>
+      <c r="X41">
+        <v>84</v>
+      </c>
       <c r="Y41">
-        <v>32289</v>
+        <v>32030</v>
       </c>
       <c r="Z41">
-        <v>2995</v>
+        <v>2973</v>
       </c>
       <c r="AA41">
-        <v>35284</v>
+        <v>35003</v>
       </c>
       <c r="AB41">
-        <v>2176</v>
+        <v>2159</v>
       </c>
       <c r="AC41">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AD41" s="7">
-        <v>2590</v>
+        <v>2570</v>
       </c>
       <c r="AE41">
         <v>49</v>
@@ -5102,14 +5273,14 @@
       <c r="AG41" s="16">
         <v>51</v>
       </c>
-      <c r="AH41" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI41" s="24">
-        <v>179224630240</v>
-      </c>
-      <c r="AJ41" s="24">
-        <v>47803540240</v>
+      <c r="AH41" s="22">
+        <v>130373910000</v>
+      </c>
+      <c r="AI41" s="22">
+        <v>178128411480</v>
+      </c>
+      <c r="AJ41" s="22">
+        <v>47754501480</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
@@ -5117,116 +5288,120 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D42" s="17">
-        <v>140.05375809925181</v>
+        <v>139.45129589182369</v>
       </c>
       <c r="E42">
-        <v>37953</v>
+        <v>37795</v>
       </c>
       <c r="F42">
-        <v>3144</v>
+        <v>3133</v>
       </c>
       <c r="G42">
-        <v>128.90438247011949</v>
+        <v>128.36254980079681</v>
       </c>
       <c r="H42">
-        <v>11.749003984063741</v>
-      </c>
-      <c r="I42">
-        <v>11.749003984063741</v>
+        <v>11.70517928286853</v>
+      </c>
+      <c r="I42" s="26">
+        <v>11.70517928286853</v>
       </c>
       <c r="J42">
-        <v>10.334661354581669</v>
-      </c>
-      <c r="K42" s="21">
+        <v>10.29482071713147</v>
+      </c>
+      <c r="K42" s="26">
         <v>0.76095617529880477</v>
       </c>
       <c r="L42" s="9">
         <v>0.76095617529880477</v>
       </c>
-      <c r="M42">
-        <v>0.20318725099601601</v>
+      <c r="M42" s="26">
+        <v>0.19920318725099601</v>
       </c>
       <c r="N42">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="O42" s="14">
-        <v>0.21912350597609559</v>
+        <v>0.2151394422310757</v>
       </c>
       <c r="P42">
-        <v>128.2270916334661</v>
+        <v>127.70916334661359</v>
       </c>
       <c r="Q42" t="s">
-        <v>56</v>
-      </c>
-      <c r="R42" s="21">
+        <v>64</v>
+      </c>
+      <c r="R42" s="26">
         <v>34.262948207171313</v>
       </c>
       <c r="S42" t="s">
-        <v>69</v>
-      </c>
-      <c r="T42" s="21">
-        <v>56.972111553784863</v>
+        <v>77</v>
+      </c>
+      <c r="T42" s="26">
+        <v>56.573705179282882</v>
       </c>
       <c r="U42" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="V42">
         <v>92</v>
       </c>
-      <c r="W42"/>
-      <c r="X42"/>
+      <c r="W42" t="s">
+        <v>35</v>
+      </c>
+      <c r="X42" s="9">
+        <v>92</v>
+      </c>
       <c r="Y42">
-        <v>32355</v>
+        <v>32219</v>
       </c>
       <c r="Z42">
-        <v>2949</v>
+        <v>2938</v>
       </c>
       <c r="AA42">
-        <v>35304</v>
+        <v>35157</v>
       </c>
       <c r="AB42">
-        <v>2183</v>
+        <v>2177</v>
       </c>
       <c r="AC42">
         <v>191</v>
       </c>
       <c r="AD42" s="7">
-        <v>2594</v>
+        <v>2584</v>
       </c>
       <c r="AE42">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF42">
         <v>4</v>
       </c>
       <c r="AG42" s="18">
-        <v>55</v>
-      </c>
-      <c r="AH42" s="24">
-        <v>131421090000</v>
-      </c>
-      <c r="AI42" s="24">
-        <v>184060175480</v>
-      </c>
-      <c r="AJ42" s="24">
-        <v>52639085480</v>
+        <v>54</v>
+      </c>
+      <c r="AH42" s="22">
+        <v>130897500000</v>
+      </c>
+      <c r="AI42" s="22">
+        <v>182538260040</v>
+      </c>
+      <c r="AJ42" s="22">
+        <v>51640760040</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A43" s="27">
+      <c r="A43" s="25">
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D43" s="17">
         <v>141.77258380675431</v>
@@ -5243,7 +5418,7 @@
       <c r="H43">
         <v>11.85258964143426</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="26">
         <v>11.85258964143426</v>
       </c>
       <c r="J43">
@@ -5268,25 +5443,29 @@
         <v>128.1035856573705</v>
       </c>
       <c r="Q43" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="R43">
         <v>30.677290836653391</v>
       </c>
       <c r="S43" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T43">
         <v>58.964143426294832</v>
       </c>
       <c r="U43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V43" s="9">
         <v>96</v>
       </c>
-      <c r="W43"/>
-      <c r="X43"/>
+      <c r="W43" t="s">
+        <v>35</v>
+      </c>
+      <c r="X43" s="9">
+        <v>92</v>
+      </c>
       <c r="Y43">
         <v>32329</v>
       </c>
@@ -5308,19 +5487,19 @@
       <c r="AE43">
         <v>50</v>
       </c>
-      <c r="AF43" s="21">
+      <c r="AF43" s="26">
         <v>5</v>
       </c>
       <c r="AG43" s="18">
         <v>55</v>
       </c>
-      <c r="AH43" s="24">
+      <c r="AH43" s="22">
         <v>131421090000</v>
       </c>
-      <c r="AI43" s="24">
+      <c r="AI43" s="22">
         <v>186319074960</v>
       </c>
-      <c r="AJ43" s="24">
+      <c r="AJ43" s="22">
         <v>54897984960</v>
       </c>
     </row>
@@ -5329,10 +5508,10 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D44">
         <v>133.55055607893681</v>
@@ -5349,13 +5528,13 @@
       <c r="H44">
         <v>11.89641434262948</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="26">
         <v>11.89641434262948</v>
       </c>
       <c r="J44">
         <v>10.35458167330677</v>
       </c>
-      <c r="K44" s="21">
+      <c r="K44" s="26">
         <v>0.80478087649402386</v>
       </c>
       <c r="L44">
@@ -5374,25 +5553,29 @@
         <v>127.99203187251</v>
       </c>
       <c r="Q44" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="R44">
         <v>32.669322709163353</v>
       </c>
       <c r="S44" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="T44">
         <v>60.557768924302792</v>
       </c>
       <c r="U44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V44" s="9">
         <v>96</v>
       </c>
-      <c r="W44"/>
-      <c r="X44"/>
+      <c r="W44" t="s">
+        <v>36</v>
+      </c>
+      <c r="X44">
+        <v>84</v>
+      </c>
       <c r="Y44">
         <v>32229</v>
       </c>
@@ -5408,7 +5591,7 @@
       <c r="AC44">
         <v>202</v>
       </c>
-      <c r="AD44">
+      <c r="AD44" s="26">
         <v>2599</v>
       </c>
       <c r="AE44">
@@ -5420,13 +5603,13 @@
       <c r="AG44">
         <v>45</v>
       </c>
-      <c r="AH44" s="25">
+      <c r="AH44" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AI44" s="25">
+      <c r="AI44" s="23">
         <v>175513596500</v>
       </c>
-      <c r="AJ44" s="25">
+      <c r="AJ44" s="23">
         <v>44092506500</v>
       </c>
     </row>
@@ -5435,10 +5618,10 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D45">
         <v>131.83659637886129</v>
@@ -5480,25 +5663,29 @@
         <v>128.55776892430279</v>
       </c>
       <c r="Q45" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R45">
         <v>34.661354581673308</v>
       </c>
       <c r="S45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T45">
         <v>58.167330677290842</v>
       </c>
       <c r="U45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V45">
         <v>88</v>
       </c>
-      <c r="W45"/>
-      <c r="X45"/>
+      <c r="W45" t="s">
+        <v>42</v>
+      </c>
+      <c r="X45">
+        <v>88</v>
+      </c>
       <c r="Y45">
         <v>32347</v>
       </c>
@@ -5520,19 +5707,19 @@
       <c r="AE45">
         <v>40</v>
       </c>
-      <c r="AF45" s="21">
+      <c r="AF45" s="26">
         <v>5</v>
       </c>
       <c r="AG45">
         <v>45</v>
       </c>
-      <c r="AH45" s="25">
+      <c r="AH45" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AI45" s="25">
+      <c r="AI45" s="23">
         <v>173261091980</v>
       </c>
-      <c r="AJ45" s="25">
+      <c r="AJ45" s="23">
         <v>41840001980</v>
       </c>
     </row>
@@ -5540,8 +5727,6 @@
       <c r="A46">
         <v>53</v>
       </c>
-      <c r="W46"/>
-      <c r="X46"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47">
@@ -5605,16 +5790,16 @@
         <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F1">
         <f>(E1-D1)</f>
@@ -5653,7 +5838,7 @@
         <v>128.32270916334659</v>
       </c>
       <c r="Q1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="R1">
         <v>32.270916334661351</v>
@@ -5700,16 +5885,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <f>(E2-D2)</f>
@@ -5748,7 +5933,7 @@
         <v>128.32270916334659</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="R2">
         <v>32.270916334661351</v>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B2E8A6-3F43-4545-A7E4-C16BC1B76BCF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE0A464-FEFE-439C-A8A2-A8DBD3D847EC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3070" yWindow="1610" windowWidth="30890" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3070" yWindow="1610" windowWidth="26280" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -536,6 +536,8 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -550,7 +552,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -855,33 +856,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Y1" s="29" t="s">
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Y1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="32" t="s">
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="31" t="s">
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -994,7 +995,7 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3" s="26">
+      <c r="A3" s="30">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -1027,10 +1028,10 @@
       <c r="K3" s="26">
         <v>0.8127490039840638</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="30">
         <v>0.8127490039840638</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="30">
         <v>0.17928286852589639</v>
       </c>
       <c r="N3">
@@ -1057,13 +1058,13 @@
       <c r="U3" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="26">
+      <c r="V3" s="30">
         <v>92</v>
       </c>
       <c r="W3" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="26">
+      <c r="X3" s="30">
         <v>84</v>
       </c>
       <c r="Y3">
@@ -1113,7 +1114,7 @@
       <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="30">
         <v>113.32315416260811</v>
       </c>
       <c r="E4">
@@ -1125,7 +1126,7 @@
       <c r="G4">
         <v>127.95617529880479</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="30">
         <v>11.569721115537851</v>
       </c>
       <c r="I4" s="26">
@@ -1137,7 +1138,7 @@
       <c r="K4" s="26">
         <v>0.71713147410358569</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="30">
         <v>0.71713147410358569</v>
       </c>
       <c r="M4">
@@ -1146,7 +1147,7 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="30">
         <v>0.12749003984063739</v>
       </c>
       <c r="P4">
@@ -1167,13 +1168,13 @@
       <c r="U4" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="26">
+      <c r="V4" s="30">
         <v>84</v>
       </c>
       <c r="W4" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="26">
+      <c r="X4" s="30">
         <v>72</v>
       </c>
       <c r="Y4">
@@ -1200,7 +1201,7 @@
       <c r="AF4">
         <v>0</v>
       </c>
-      <c r="AG4" s="26">
+      <c r="AG4" s="30">
         <v>32</v>
       </c>
       <c r="AH4" s="21">
@@ -1214,7 +1215,7 @@
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="A5" s="30">
         <v>12</v>
       </c>
       <c r="B5" t="s">
@@ -1223,7 +1224,7 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <v>130.28112528970809</v>
       </c>
       <c r="E5">
@@ -1247,16 +1248,16 @@
       <c r="K5" s="26">
         <v>0.79681274900398402</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="30">
         <v>0.79681274900398402</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="30">
         <v>0.18326693227091631</v>
       </c>
       <c r="N5">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="30">
         <v>0.18725099601593631</v>
       </c>
       <c r="P5">
@@ -1277,13 +1278,13 @@
       <c r="U5" t="s">
         <v>35</v>
       </c>
-      <c r="V5" s="26">
+      <c r="V5" s="30">
         <v>92</v>
       </c>
       <c r="W5" t="s">
         <v>42</v>
       </c>
-      <c r="X5" s="26">
+      <c r="X5" s="30">
         <v>88</v>
       </c>
       <c r="Y5">
@@ -1301,13 +1302,13 @@
       <c r="AC5" s="26">
         <v>200</v>
       </c>
-      <c r="AD5" s="26">
+      <c r="AD5" s="30">
         <v>2586</v>
       </c>
       <c r="AE5">
         <v>46</v>
       </c>
-      <c r="AF5" s="26">
+      <c r="AF5" s="30">
         <v>1</v>
       </c>
       <c r="AG5" s="8">
@@ -1324,7 +1325,7 @@
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6" s="26">
+      <c r="A6" s="30">
         <v>13</v>
       </c>
       <c r="B6" t="s">
@@ -1333,7 +1334,7 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="30">
         <v>127.7392235604194</v>
       </c>
       <c r="E6">
@@ -1357,7 +1358,7 @@
       <c r="K6">
         <v>0.83266932270916338</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="30">
         <v>0.83266932270916338</v>
       </c>
       <c r="M6">
@@ -1366,7 +1367,7 @@
       <c r="N6">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="O6" s="26">
+      <c r="O6" s="30">
         <v>0.15537848605577689</v>
       </c>
       <c r="P6">
@@ -1387,13 +1388,13 @@
       <c r="U6" t="s">
         <v>42</v>
       </c>
-      <c r="V6" s="26">
+      <c r="V6" s="30">
         <v>88</v>
       </c>
       <c r="W6" t="s">
         <v>45</v>
       </c>
-      <c r="X6" s="26">
+      <c r="X6" s="30">
         <v>76</v>
       </c>
       <c r="Y6">
@@ -1411,7 +1412,7 @@
       <c r="AC6">
         <v>209</v>
       </c>
-      <c r="AD6" s="26">
+      <c r="AD6" s="30">
         <v>2568</v>
       </c>
       <c r="AE6">
@@ -1420,7 +1421,7 @@
       <c r="AF6">
         <v>4</v>
       </c>
-      <c r="AG6" s="26">
+      <c r="AG6" s="30">
         <v>39</v>
       </c>
       <c r="AH6" s="21">
@@ -1443,7 +1444,7 @@
       <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="30">
         <v>127.02495336174739</v>
       </c>
       <c r="E7">
@@ -1458,7 +1459,7 @@
       <c r="H7">
         <v>12.011952191235061</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="30">
         <v>12.011952191235061</v>
       </c>
       <c r="J7">
@@ -1476,7 +1477,7 @@
       <c r="N7">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="30">
         <v>0.15936254980079681</v>
       </c>
       <c r="P7">
@@ -1485,7 +1486,7 @@
       <c r="Q7" t="s">
         <v>40</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="30">
         <v>34.661354581673308</v>
       </c>
       <c r="S7" t="s">
@@ -1497,7 +1498,7 @@
       <c r="U7" t="s">
         <v>42</v>
       </c>
-      <c r="V7" s="26">
+      <c r="V7" s="30">
         <v>88</v>
       </c>
       <c r="W7" t="s">
@@ -1527,10 +1528,10 @@
       <c r="AE7">
         <v>38</v>
       </c>
-      <c r="AF7" s="26">
+      <c r="AF7" s="30">
         <v>2</v>
       </c>
-      <c r="AG7" s="26">
+      <c r="AG7" s="30">
         <v>40</v>
       </c>
       <c r="AH7" s="21">
@@ -1568,7 +1569,7 @@
       <c r="H8">
         <v>11.60956175298805</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="30">
         <v>11.60956175298805</v>
       </c>
       <c r="J8">
@@ -1586,7 +1587,7 @@
       <c r="N8">
         <v>3.1872509960159362E-2</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="30">
         <v>0.18725099601593631</v>
       </c>
       <c r="P8">
@@ -1607,7 +1608,7 @@
       <c r="U8" t="s">
         <v>35</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="30">
         <v>92</v>
       </c>
       <c r="W8" t="s">
@@ -1696,7 +1697,7 @@
       <c r="N9">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="30">
         <v>0.1752988047808765</v>
       </c>
       <c r="P9">
@@ -1705,19 +1706,19 @@
       <c r="Q9" t="s">
         <v>49</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="30">
         <v>33.466135458167329</v>
       </c>
       <c r="S9" t="s">
         <v>50</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="30">
         <v>57.768924302788847</v>
       </c>
       <c r="U9" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="26">
+      <c r="V9" s="30">
         <v>88</v>
       </c>
       <c r="W9" t="s">
@@ -1741,7 +1742,7 @@
       <c r="AC9">
         <v>205</v>
       </c>
-      <c r="AD9" s="26">
+      <c r="AD9" s="30">
         <v>2589</v>
       </c>
       <c r="AE9">
@@ -1750,7 +1751,7 @@
       <c r="AF9" s="7">
         <v>5</v>
       </c>
-      <c r="AG9" s="26">
+      <c r="AG9" s="30">
         <v>44</v>
       </c>
       <c r="AH9" s="21">
@@ -1773,7 +1774,7 @@
       <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="30">
         <v>130.13855146080439</v>
       </c>
       <c r="E10">
@@ -1788,7 +1789,7 @@
       <c r="H10">
         <v>11.66135458167331</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="30">
         <v>11.66135458167331</v>
       </c>
       <c r="J10">
@@ -1797,7 +1798,7 @@
       <c r="K10">
         <v>0.83266932270916338</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="30">
         <v>0.83266932270916338</v>
       </c>
       <c r="M10">
@@ -1806,7 +1807,7 @@
       <c r="N10">
         <v>1.5936254980079681E-2</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="30">
         <v>0.16733067729083659</v>
       </c>
       <c r="P10">
@@ -1827,13 +1828,13 @@
       <c r="U10" t="s">
         <v>35</v>
       </c>
-      <c r="V10" s="26">
+      <c r="V10" s="30">
         <v>92</v>
       </c>
       <c r="W10" t="s">
         <v>36</v>
       </c>
-      <c r="X10" s="26">
+      <c r="X10" s="30">
         <v>84</v>
       </c>
       <c r="Y10">
@@ -1860,7 +1861,7 @@
       <c r="AF10">
         <v>4</v>
       </c>
-      <c r="AG10" s="26">
+      <c r="AG10" s="30">
         <v>42</v>
       </c>
       <c r="AH10" s="21">
@@ -1883,7 +1884,7 @@
       <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="30">
         <v>129.96682088087991</v>
       </c>
       <c r="E11">
@@ -1895,7 +1896,7 @@
       <c r="G11">
         <v>128.8167330677291</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="30">
         <v>11.37450199203187</v>
       </c>
       <c r="I11" s="26">
@@ -1907,13 +1908,13 @@
       <c r="K11">
         <v>0.86454183266932272</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="30">
         <v>0.86454183266932272</v>
       </c>
       <c r="M11">
         <v>0.14741035856573709</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="30">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="O11">
@@ -1925,19 +1926,19 @@
       <c r="Q11" t="s">
         <v>52</v>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="30">
         <v>32.270916334661351</v>
       </c>
       <c r="S11" t="s">
         <v>34</v>
       </c>
-      <c r="T11" s="26">
+      <c r="T11" s="30">
         <v>58.167330677290842</v>
       </c>
       <c r="U11" t="s">
         <v>42</v>
       </c>
-      <c r="V11" s="26">
+      <c r="V11" s="30">
         <v>88</v>
       </c>
       <c r="W11" t="s">
@@ -1967,10 +1968,10 @@
       <c r="AE11">
         <v>37</v>
       </c>
-      <c r="AF11" s="26">
+      <c r="AF11" s="30">
         <v>4</v>
       </c>
-      <c r="AG11" s="26">
+      <c r="AG11" s="30">
         <v>41</v>
       </c>
       <c r="AH11" s="21">
@@ -1993,7 +1994,7 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="30">
         <v>117.1493692374641</v>
       </c>
       <c r="E12">
@@ -2008,7 +2009,7 @@
       <c r="H12">
         <v>11.64541832669323</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="30">
         <v>11.64541832669323</v>
       </c>
       <c r="J12">
@@ -2017,7 +2018,7 @@
       <c r="K12">
         <v>0.7450199203187251</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="30">
         <v>0.7450199203187251</v>
       </c>
       <c r="M12">
@@ -2026,7 +2027,7 @@
       <c r="N12">
         <v>7.9681274900398405E-3</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="30">
         <v>0.13147410358565739</v>
       </c>
       <c r="P12">
@@ -2047,13 +2048,13 @@
       <c r="U12" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="26">
+      <c r="V12" s="30">
         <v>84</v>
       </c>
       <c r="W12" t="s">
         <v>39</v>
       </c>
-      <c r="X12" s="26">
+      <c r="X12" s="30">
         <v>72</v>
       </c>
       <c r="Y12">
@@ -2077,10 +2078,10 @@
       <c r="AE12">
         <v>31</v>
       </c>
-      <c r="AF12" s="26">
+      <c r="AF12" s="30">
         <v>2</v>
       </c>
-      <c r="AG12" s="26">
+      <c r="AG12" s="30">
         <v>33</v>
       </c>
       <c r="AH12" s="21">
@@ -2115,7 +2116,7 @@
       <c r="G13">
         <v>128.53784860557769</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="30">
         <v>11.89243027888446</v>
       </c>
       <c r="I13" s="7">
@@ -2133,7 +2134,7 @@
       <c r="M13" s="14">
         <v>0.19920318725099601</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="30">
         <v>3.9840637450199202E-3</v>
       </c>
       <c r="O13" s="16">
@@ -2145,13 +2146,13 @@
       <c r="Q13" t="s">
         <v>49</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="30">
         <v>33.466135458167329</v>
       </c>
       <c r="S13" t="s">
         <v>55</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="30">
         <v>56.972111553784863</v>
       </c>
       <c r="U13" t="s">
@@ -2163,7 +2164,7 @@
       <c r="W13" t="s">
         <v>57</v>
       </c>
-      <c r="X13" s="35">
+      <c r="X13" s="29">
         <v>96</v>
       </c>
       <c r="Y13">
@@ -2187,7 +2188,7 @@
       <c r="AE13">
         <v>50</v>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="30">
         <v>1</v>
       </c>
       <c r="AG13" s="16">
@@ -2228,7 +2229,7 @@
       <c r="H14" s="26">
         <v>11.908366533864539</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="30">
         <v>11.908366533864539</v>
       </c>
       <c r="J14">
@@ -2267,7 +2268,7 @@
       <c r="U14" t="s">
         <v>39</v>
       </c>
-      <c r="V14" s="26">
+      <c r="V14" s="30">
         <v>72</v>
       </c>
       <c r="W14" t="s">
@@ -2300,7 +2301,7 @@
       <c r="AF14" s="7">
         <v>5</v>
       </c>
-      <c r="AG14" s="26">
+      <c r="AG14" s="30">
         <v>33</v>
       </c>
       <c r="AH14" s="21">
@@ -2323,7 +2324,7 @@
       <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="30">
         <v>122.99666202738079</v>
       </c>
       <c r="E15">
@@ -2338,16 +2339,16 @@
       <c r="H15" s="14">
         <v>11.84860557768924</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="30">
         <v>11.84860557768924</v>
       </c>
       <c r="J15">
         <v>10.41832669322709</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="30">
         <v>0.78486055776892427</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="30">
         <v>0.78486055776892427</v>
       </c>
       <c r="M15">
@@ -2356,7 +2357,7 @@
       <c r="N15">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O15" s="26">
+      <c r="O15" s="30">
         <v>0.15537848605577689</v>
       </c>
       <c r="P15">
@@ -2365,13 +2366,13 @@
       <c r="Q15" t="s">
         <v>40</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="30">
         <v>34.661354581673308</v>
       </c>
       <c r="S15" t="s">
         <v>50</v>
       </c>
-      <c r="T15" s="26">
+      <c r="T15" s="30">
         <v>57.768924302788847</v>
       </c>
       <c r="U15" t="s">
@@ -2383,7 +2384,7 @@
       <c r="W15" t="s">
         <v>45</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="30">
         <v>76</v>
       </c>
       <c r="Y15">
@@ -2407,10 +2408,10 @@
       <c r="AE15">
         <v>38</v>
       </c>
-      <c r="AF15" s="26">
+      <c r="AF15" s="30">
         <v>1</v>
       </c>
-      <c r="AG15" s="26">
+      <c r="AG15" s="30">
         <v>39</v>
       </c>
       <c r="AH15" s="21">
@@ -2433,7 +2434,7 @@
       <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="30">
         <v>122.589138546941</v>
       </c>
       <c r="E16">
@@ -2448,7 +2449,7 @@
       <c r="H16">
         <v>11.7609561752988</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="30">
         <v>11.7609561752988</v>
       </c>
       <c r="J16">
@@ -2457,7 +2458,7 @@
       <c r="K16">
         <v>0.82868525896414347</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="30">
         <v>0.82868525896414347</v>
       </c>
       <c r="M16">
@@ -2475,13 +2476,13 @@
       <c r="Q16" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="30">
         <v>32.669322709163353</v>
       </c>
       <c r="S16" t="s">
         <v>62</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="30">
         <v>59.362549800796813</v>
       </c>
       <c r="U16" t="s">
@@ -2517,10 +2518,10 @@
       <c r="AE16">
         <v>32</v>
       </c>
-      <c r="AF16">
+      <c r="AF16" s="30">
         <v>3</v>
       </c>
-      <c r="AG16" s="26">
+      <c r="AG16" s="30">
         <v>35</v>
       </c>
       <c r="AH16" s="21">
@@ -2543,7 +2544,7 @@
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="30">
         <v>120.0807208645127</v>
       </c>
       <c r="E17">
@@ -2564,13 +2565,13 @@
       <c r="J17">
         <v>10.342629482071709</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="30">
         <v>0.82868525896414347</v>
       </c>
-      <c r="L17" s="26">
+      <c r="L17" s="30">
         <v>0.82868525896414347</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="30">
         <v>0.14342629482071709</v>
       </c>
       <c r="N17">
@@ -2591,7 +2592,7 @@
       <c r="S17" t="s">
         <v>41</v>
       </c>
-      <c r="T17" s="26">
+      <c r="T17" s="30">
         <v>58.964143426294832</v>
       </c>
       <c r="U17" t="s">
@@ -2603,7 +2604,7 @@
       <c r="W17" t="s">
         <v>36</v>
       </c>
-      <c r="X17" s="26">
+      <c r="X17" s="30">
         <v>84</v>
       </c>
       <c r="Y17">
@@ -2627,10 +2628,10 @@
       <c r="AE17">
         <v>36</v>
       </c>
-      <c r="AF17" s="26">
+      <c r="AF17" s="30">
         <v>0</v>
       </c>
-      <c r="AG17" s="26">
+      <c r="AG17" s="30">
         <v>36</v>
       </c>
       <c r="AH17" s="21">
@@ -2674,10 +2675,10 @@
       <c r="J18">
         <v>10.33067729083665</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="30">
         <v>0.8605577689243028</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="30">
         <v>0.8605577689243028</v>
       </c>
       <c r="M18">
@@ -2740,7 +2741,7 @@
       <c r="AF18" s="26">
         <v>1</v>
       </c>
-      <c r="AG18" s="26">
+      <c r="AG18" s="30">
         <v>41</v>
       </c>
       <c r="AH18" s="21">
@@ -2805,7 +2806,7 @@
       <c r="Q19" t="s">
         <v>64</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="30">
         <v>34.262948207171313</v>
       </c>
       <c r="S19" t="s">
@@ -2850,7 +2851,7 @@
       <c r="AF19" s="26">
         <v>2</v>
       </c>
-      <c r="AG19" s="26">
+      <c r="AG19" s="30">
         <v>45</v>
       </c>
       <c r="AH19" s="22">
@@ -2873,7 +2874,7 @@
       <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="30">
         <v>129.6847290187595</v>
       </c>
       <c r="E20">
@@ -2957,7 +2958,7 @@
       <c r="AE20">
         <v>46</v>
       </c>
-      <c r="AF20" s="26">
+      <c r="AF20" s="30">
         <v>1</v>
       </c>
       <c r="AG20" s="8">
@@ -3043,7 +3044,7 @@
       <c r="W21" t="s">
         <v>46</v>
       </c>
-      <c r="X21" s="26">
+      <c r="X21" s="30">
         <v>80</v>
       </c>
       <c r="Y21">
@@ -3108,7 +3109,7 @@
       <c r="H22" s="9">
         <v>11.446215139442231</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="30">
         <v>11.446215139442231</v>
       </c>
       <c r="J22">
@@ -3147,7 +3148,7 @@
       <c r="U22" t="s">
         <v>42</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="30">
         <v>88</v>
       </c>
       <c r="W22" t="s">
@@ -3177,7 +3178,7 @@
       <c r="AE22">
         <v>35</v>
       </c>
-      <c r="AF22" s="26">
+      <c r="AF22" s="30">
         <v>4</v>
       </c>
       <c r="AG22">
@@ -3203,7 +3204,7 @@
       <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="30">
         <v>127.3087183038887</v>
       </c>
       <c r="E23">
@@ -3227,7 +3228,7 @@
       <c r="K23" s="9">
         <v>0.87250996015936255</v>
       </c>
-      <c r="L23" s="26">
+      <c r="L23" s="30">
         <v>0.87250996015936255</v>
       </c>
       <c r="M23">
@@ -3251,13 +3252,13 @@
       <c r="S23" t="s">
         <v>70</v>
       </c>
-      <c r="T23" s="26">
+      <c r="T23" s="30">
         <v>55.776892430278878</v>
       </c>
       <c r="U23" t="s">
         <v>36</v>
       </c>
-      <c r="V23" s="26">
+      <c r="V23" s="30">
         <v>84</v>
       </c>
       <c r="W23" t="s">
@@ -3281,16 +3282,16 @@
       <c r="AC23">
         <v>219</v>
       </c>
-      <c r="AD23" s="26">
+      <c r="AD23" s="30">
         <v>2583</v>
       </c>
       <c r="AE23">
         <v>36</v>
       </c>
-      <c r="AF23" s="26">
+      <c r="AF23" s="30">
         <v>3</v>
       </c>
-      <c r="AG23" s="26">
+      <c r="AG23" s="30">
         <v>39</v>
       </c>
       <c r="AH23" s="22">
@@ -3313,7 +3314,7 @@
       <c r="C24" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="30">
         <v>128.67639430852381</v>
       </c>
       <c r="E24">
@@ -3337,7 +3338,7 @@
       <c r="K24">
         <v>0.73705179282868527</v>
       </c>
-      <c r="L24" s="26">
+      <c r="L24" s="30">
         <v>0.73705179282868527</v>
       </c>
       <c r="M24" s="9">
@@ -3346,7 +3347,7 @@
       <c r="N24">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O24" s="26">
+      <c r="O24" s="30">
         <v>0.18725099601593631</v>
       </c>
       <c r="P24">
@@ -3391,13 +3392,13 @@
       <c r="AC24">
         <v>185</v>
       </c>
-      <c r="AD24" s="26">
+      <c r="AD24" s="30">
         <v>2584</v>
       </c>
       <c r="AE24">
         <v>46</v>
       </c>
-      <c r="AF24" s="26">
+      <c r="AF24" s="30">
         <v>1</v>
       </c>
       <c r="AG24" s="7">
@@ -3423,7 +3424,7 @@
       <c r="C25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="30">
         <v>129.67866246230199</v>
       </c>
       <c r="E25">
@@ -3447,7 +3448,7 @@
       <c r="K25" s="7">
         <v>0.8605577689243028</v>
       </c>
-      <c r="L25" s="26">
+      <c r="L25" s="30">
         <v>0.8605577689243028</v>
       </c>
       <c r="M25">
@@ -3456,7 +3457,7 @@
       <c r="N25">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O25" s="26">
+      <c r="O25" s="30">
         <v>0.1752988047808765</v>
       </c>
       <c r="P25">
@@ -3483,7 +3484,7 @@
       <c r="W25" t="s">
         <v>45</v>
       </c>
-      <c r="X25" s="26">
+      <c r="X25" s="30">
         <v>76</v>
       </c>
       <c r="Y25">
@@ -3501,7 +3502,7 @@
       <c r="AC25">
         <v>216</v>
       </c>
-      <c r="AD25" s="26">
+      <c r="AD25" s="30">
         <v>2582</v>
       </c>
       <c r="AE25">
@@ -3510,7 +3511,7 @@
       <c r="AF25">
         <v>1</v>
       </c>
-      <c r="AG25" s="26">
+      <c r="AG25" s="30">
         <v>44</v>
       </c>
       <c r="AH25" s="22">
@@ -3533,7 +3534,7 @@
       <c r="C26" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="30">
         <v>129.99342434043169</v>
       </c>
       <c r="E26">
@@ -3617,7 +3618,7 @@
       <c r="AE26">
         <v>45</v>
       </c>
-      <c r="AF26" s="26">
+      <c r="AF26" s="30">
         <v>1</v>
       </c>
       <c r="AG26" s="26">
@@ -3664,7 +3665,7 @@
       <c r="J27">
         <v>10.31075697211155</v>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="30">
         <v>0.86454183266932272</v>
       </c>
       <c r="L27" s="26">
@@ -3685,13 +3686,13 @@
       <c r="Q27" t="s">
         <v>52</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="30">
         <v>32.270916334661351</v>
       </c>
       <c r="S27" t="s">
         <v>70</v>
       </c>
-      <c r="T27" s="26">
+      <c r="T27" s="30">
         <v>55.776892430278878</v>
       </c>
       <c r="U27" t="s">
@@ -3721,7 +3722,7 @@
       <c r="AC27">
         <v>217</v>
       </c>
-      <c r="AD27" s="26">
+      <c r="AD27" s="30">
         <v>2588</v>
       </c>
       <c r="AE27">
@@ -3753,7 +3754,7 @@
       <c r="C28" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="30">
         <v>125.5287304447414</v>
       </c>
       <c r="E28">
@@ -3795,7 +3796,7 @@
       <c r="Q28" t="s">
         <v>64</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="30">
         <v>34.262948207171313</v>
       </c>
       <c r="S28" t="s">
@@ -3831,13 +3832,13 @@
       <c r="AC28">
         <v>200</v>
       </c>
-      <c r="AD28" s="26">
+      <c r="AD28" s="30">
         <v>2577</v>
       </c>
       <c r="AE28">
         <v>34</v>
       </c>
-      <c r="AF28" s="26">
+      <c r="AF28" s="30">
         <v>4</v>
       </c>
       <c r="AG28" s="26">
@@ -4015,7 +4016,7 @@
       <c r="Q30" t="s">
         <v>76</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="30">
         <v>35.458167330677291</v>
       </c>
       <c r="S30" t="s">
@@ -4095,7 +4096,7 @@
       <c r="G31">
         <v>128.0199203187251</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="30">
         <v>11.85258964143426</v>
       </c>
       <c r="I31" s="7">
@@ -4107,7 +4108,7 @@
       <c r="K31" s="26">
         <v>0.81673306772908372</v>
       </c>
-      <c r="L31" s="26">
+      <c r="L31" s="30">
         <v>0.81673306772908372</v>
       </c>
       <c r="M31">
@@ -4220,7 +4221,7 @@
       <c r="L32" s="26">
         <v>0.8127490039840638</v>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="30">
         <v>0.14741035856573709</v>
       </c>
       <c r="N32">
@@ -4235,7 +4236,7 @@
       <c r="Q32" t="s">
         <v>49</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="30">
         <v>33.466135458167329</v>
       </c>
       <c r="S32" t="s">
@@ -4247,7 +4248,7 @@
       <c r="U32" t="s">
         <v>45</v>
       </c>
-      <c r="V32" s="26">
+      <c r="V32" s="30">
         <v>76</v>
       </c>
       <c r="W32" t="s">
@@ -4280,7 +4281,7 @@
       <c r="AF32">
         <v>1</v>
       </c>
-      <c r="AG32" s="26">
+      <c r="AG32" s="30">
         <v>38</v>
       </c>
       <c r="AH32" s="22">
@@ -4428,7 +4429,7 @@
       <c r="H34" s="26">
         <v>11.59362549800797</v>
       </c>
-      <c r="I34" s="26">
+      <c r="I34" s="30">
         <v>11.59362549800797</v>
       </c>
       <c r="J34">
@@ -4523,7 +4524,7 @@
       <c r="C35" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="30">
         <v>130.74574834221809</v>
       </c>
       <c r="E35">
@@ -4535,7 +4536,7 @@
       <c r="G35">
         <v>128.45019920318731</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="30">
         <v>11.856573705179279</v>
       </c>
       <c r="I35">
@@ -4607,7 +4608,7 @@
       <c r="AE35">
         <v>45</v>
       </c>
-      <c r="AF35" s="26">
+      <c r="AF35" s="30">
         <v>2</v>
       </c>
       <c r="AG35" s="8">
@@ -4666,7 +4667,7 @@
       <c r="N36" s="14">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O36" s="26">
+      <c r="O36" s="30">
         <v>0.18725099601593631</v>
       </c>
       <c r="P36">
@@ -4758,13 +4759,13 @@
       <c r="H37">
         <v>11.45019920318725</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="30">
         <v>11.45019920318725</v>
       </c>
       <c r="J37">
         <v>10.322709163346611</v>
       </c>
-      <c r="K37" s="26">
+      <c r="K37" s="30">
         <v>0.75298804780876494</v>
       </c>
       <c r="L37" s="9">
@@ -4785,7 +4786,7 @@
       <c r="Q37" t="s">
         <v>40</v>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="30">
         <v>34.661354581673308</v>
       </c>
       <c r="S37" t="s">
@@ -4868,7 +4869,7 @@
       <c r="H38">
         <v>11.721115537848609</v>
       </c>
-      <c r="I38" s="26">
+      <c r="I38" s="30">
         <v>11.721115537848609</v>
       </c>
       <c r="J38">
@@ -4978,7 +4979,7 @@
       <c r="H39">
         <v>11.701195219123511</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="30">
         <v>11.701195219123511</v>
       </c>
       <c r="J39">
@@ -5023,7 +5024,7 @@
       <c r="W39" t="s">
         <v>57</v>
       </c>
-      <c r="X39" s="35">
+      <c r="X39" s="29">
         <v>96</v>
       </c>
       <c r="Y39">
@@ -5047,7 +5048,7 @@
       <c r="AE39">
         <v>48</v>
       </c>
-      <c r="AF39" s="26">
+      <c r="AF39" s="30">
         <v>2</v>
       </c>
       <c r="AG39" s="16">
@@ -5085,16 +5086,16 @@
       <c r="G40">
         <v>128.10756972111551</v>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="30">
         <v>11.34661354581673</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="30">
         <v>11.34661354581673</v>
       </c>
       <c r="J40">
         <v>10.2390438247012</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="30">
         <v>0.75298804780876494</v>
       </c>
       <c r="L40">
@@ -5198,13 +5199,13 @@
       <c r="H41" s="26">
         <v>11.844621513944221</v>
       </c>
-      <c r="I41" s="26">
+      <c r="I41" s="30">
         <v>11.844621513944221</v>
       </c>
       <c r="J41">
         <v>10.2390438247012</v>
       </c>
-      <c r="K41" s="26">
+      <c r="K41" s="30">
         <v>0.82470119521912355</v>
       </c>
       <c r="L41" s="26">
@@ -5237,7 +5238,7 @@
       <c r="U41" t="s">
         <v>42</v>
       </c>
-      <c r="V41">
+      <c r="V41" s="30">
         <v>88</v>
       </c>
       <c r="W41" t="s">
@@ -5314,7 +5315,7 @@
       <c r="J42">
         <v>10.29482071713147</v>
       </c>
-      <c r="K42" s="26">
+      <c r="K42" s="30">
         <v>0.76095617529880477</v>
       </c>
       <c r="L42" s="9">
@@ -5335,13 +5336,13 @@
       <c r="Q42" t="s">
         <v>64</v>
       </c>
-      <c r="R42" s="26">
+      <c r="R42" s="30">
         <v>34.262948207171313</v>
       </c>
       <c r="S42" t="s">
         <v>77</v>
       </c>
-      <c r="T42" s="26">
+      <c r="T42" s="30">
         <v>56.573705179282882</v>
       </c>
       <c r="U42" t="s">
@@ -5418,7 +5419,7 @@
       <c r="H43">
         <v>11.85258964143426</v>
       </c>
-      <c r="I43" s="26">
+      <c r="I43" s="30">
         <v>11.85258964143426</v>
       </c>
       <c r="J43">
@@ -5487,7 +5488,7 @@
       <c r="AE43">
         <v>50</v>
       </c>
-      <c r="AF43" s="26">
+      <c r="AF43" s="30">
         <v>5</v>
       </c>
       <c r="AG43" s="18">
@@ -5528,13 +5529,13 @@
       <c r="H44">
         <v>11.89641434262948</v>
       </c>
-      <c r="I44" s="26">
+      <c r="I44" s="30">
         <v>11.89641434262948</v>
       </c>
       <c r="J44">
         <v>10.35458167330677</v>
       </c>
-      <c r="K44" s="26">
+      <c r="K44" s="30">
         <v>0.80478087649402386</v>
       </c>
       <c r="L44">
@@ -5597,7 +5598,7 @@
       <c r="AE44">
         <v>40</v>
       </c>
-      <c r="AF44">
+      <c r="AF44" s="30">
         <v>5</v>
       </c>
       <c r="AG44">
@@ -5701,13 +5702,13 @@
       <c r="AC45">
         <v>191</v>
       </c>
-      <c r="AD45">
+      <c r="AD45" s="30">
         <v>2599</v>
       </c>
       <c r="AE45">
         <v>40</v>
       </c>
-      <c r="AF45" s="26">
+      <c r="AF45" s="30">
         <v>5</v>
       </c>
       <c r="AG45">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9F07E9-2EAB-498C-AD69-140D8AF74F8D}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72C3A6D-5E21-457E-94E4-1E66B345706C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3070" yWindow="1610" windowWidth="26280" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,7 +474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -537,6 +537,7 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -551,6 +552,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -855,33 +867,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Y1" s="30" t="s">
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Y1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="33" t="s">
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="32" t="s">
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -994,8 +1006,8 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3" s="25">
-        <v>50</v>
+      <c r="A3" s="30">
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -1004,108 +1016,108 @@
         <v>32</v>
       </c>
       <c r="D3" s="17">
-        <v>141.97365896216499</v>
+        <v>140.12873209315191</v>
       </c>
       <c r="E3">
-        <v>37803</v>
+        <v>37925</v>
       </c>
       <c r="F3">
-        <v>3162</v>
+        <v>3151</v>
       </c>
       <c r="G3">
-        <v>128.29083665338649</v>
+        <v>128.8565737051793</v>
       </c>
       <c r="H3">
-        <v>11.80478087649402</v>
-      </c>
-      <c r="I3" s="28">
-        <v>11.80478087649402</v>
+        <v>11.71713147410359</v>
+      </c>
+      <c r="I3" s="14">
+        <v>11.71713147410359</v>
       </c>
       <c r="J3">
-        <v>10.29482071713147</v>
-      </c>
-      <c r="K3">
-        <v>0.77290836653386452</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0.77290836653386452</v>
-      </c>
-      <c r="M3" s="28">
-        <v>0.19920318725099601</v>
+        <v>10.31872509960159</v>
+      </c>
+      <c r="K3" s="30">
+        <v>0.8127490039840638</v>
+      </c>
+      <c r="L3" s="30">
+        <v>0.8127490039840638</v>
+      </c>
+      <c r="M3" s="30">
+        <v>0.17928286852589639</v>
       </c>
       <c r="N3">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O3" s="14">
-        <v>0.21912350597609559</v>
+        <v>2.3904382470119521E-2</v>
+      </c>
+      <c r="O3" s="16">
+        <v>0.20318725099601601</v>
       </c>
       <c r="P3">
-        <v>127.593625498008</v>
+        <v>128.19521912350601</v>
       </c>
       <c r="Q3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3">
-        <v>30.677290836653391</v>
+        <v>51</v>
+      </c>
+      <c r="R3" s="7">
+        <v>31.075697211155379</v>
       </c>
       <c r="S3" t="s">
-        <v>54</v>
-      </c>
-      <c r="T3">
-        <v>58.56573705179283</v>
+        <v>57</v>
+      </c>
+      <c r="T3" s="7">
+        <v>58.167330677290842</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" s="9">
-        <v>96</v>
+        <v>41</v>
+      </c>
+      <c r="V3" s="7">
+        <v>92</v>
       </c>
       <c r="W3" t="s">
-        <v>41</v>
-      </c>
-      <c r="X3" s="9">
-        <v>92</v>
+        <v>45</v>
+      </c>
+      <c r="X3" s="30">
+        <v>84</v>
       </c>
       <c r="Y3">
-        <v>32201</v>
+        <v>32343</v>
       </c>
       <c r="Z3">
-        <v>2963</v>
+        <v>2941</v>
       </c>
       <c r="AA3">
-        <v>35164</v>
+        <v>35284</v>
       </c>
       <c r="AB3">
-        <v>2170</v>
+        <v>2182</v>
       </c>
       <c r="AC3">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="AD3" s="7">
-        <v>2584</v>
+        <v>2590</v>
       </c>
       <c r="AE3">
-        <v>50</v>
-      </c>
-      <c r="AF3">
-        <v>5</v>
-      </c>
-      <c r="AG3" s="18">
-        <v>55</v>
+        <v>45</v>
+      </c>
+      <c r="AF3" s="9">
+        <v>6</v>
+      </c>
+      <c r="AG3" s="16">
+        <v>51</v>
       </c>
       <c r="AH3" s="22">
-        <v>130897500000</v>
+        <v>131421090000</v>
       </c>
       <c r="AI3" s="22">
-        <v>185839970240</v>
-      </c>
-      <c r="AJ3" s="22">
-        <v>54942470240</v>
+        <v>184158707120</v>
+      </c>
+      <c r="AJ3" s="38">
+        <v>52737617120</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>49</v>
+      <c r="A4" s="30">
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -1113,109 +1125,109 @@
       <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="17">
-        <v>140.05375809925181</v>
+      <c r="D4" s="30">
+        <v>113.1032980475204</v>
       </c>
       <c r="E4">
-        <v>37953</v>
+        <v>37789</v>
       </c>
       <c r="F4">
-        <v>3144</v>
+        <v>3091</v>
       </c>
       <c r="G4">
-        <v>128.90438247011949</v>
-      </c>
-      <c r="H4" s="28">
-        <v>11.749003984063741</v>
+        <v>128.48605577689241</v>
+      </c>
+      <c r="H4" s="30">
+        <v>11.597609561752989</v>
       </c>
       <c r="I4">
-        <v>11.749003984063741</v>
+        <v>11.597609561752989</v>
       </c>
       <c r="J4">
-        <v>10.334661354581669</v>
-      </c>
-      <c r="K4">
-        <v>0.76095617529880477</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0.76095617529880477</v>
+        <v>10.342629482071709</v>
+      </c>
+      <c r="K4" s="30">
+        <v>0.71713147410358569</v>
+      </c>
+      <c r="L4" s="30">
+        <v>0.71713147410358569</v>
       </c>
       <c r="M4">
-        <v>0.20318725099601601</v>
+        <v>0.12749003984063739</v>
       </c>
       <c r="N4">
-        <v>1.5936254980079681E-2</v>
-      </c>
-      <c r="O4" s="14">
-        <v>0.21912350597609559</v>
+        <v>0</v>
+      </c>
+      <c r="O4" s="30">
+        <v>0.12749003984063739</v>
       </c>
       <c r="P4">
-        <v>128.2270916334661</v>
+        <v>128.43426294820719</v>
       </c>
       <c r="Q4" t="s">
-        <v>64</v>
-      </c>
-      <c r="R4">
-        <v>34.262948207171313</v>
+        <v>78</v>
+      </c>
+      <c r="R4" s="30">
+        <v>37.450199203187253</v>
       </c>
       <c r="S4" t="s">
-        <v>34</v>
-      </c>
-      <c r="T4">
-        <v>56.972111553784863</v>
+        <v>79</v>
+      </c>
+      <c r="T4" s="30">
+        <v>53.784860557768923</v>
       </c>
       <c r="U4" t="s">
-        <v>41</v>
-      </c>
-      <c r="V4" s="28">
-        <v>92</v>
+        <v>45</v>
+      </c>
+      <c r="V4" s="30">
+        <v>84</v>
       </c>
       <c r="W4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X4" s="9">
-        <v>92</v>
+        <v>74</v>
+      </c>
+      <c r="X4" s="30">
+        <v>72</v>
       </c>
       <c r="Y4">
-        <v>32355</v>
+        <v>32250</v>
       </c>
       <c r="Z4">
-        <v>2949</v>
+        <v>2911</v>
       </c>
       <c r="AA4">
-        <v>35304</v>
+        <v>35161</v>
       </c>
       <c r="AB4">
-        <v>2183</v>
+        <v>2288</v>
       </c>
       <c r="AC4">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="AD4" s="7">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="AE4">
-        <v>51</v>
-      </c>
-      <c r="AF4">
-        <v>4</v>
-      </c>
-      <c r="AG4" s="18">
-        <v>55</v>
-      </c>
-      <c r="AH4" s="22">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="30">
+        <v>32</v>
+      </c>
+      <c r="AH4" s="21">
         <v>131421090000</v>
       </c>
       <c r="AI4" s="22">
-        <v>184060175480</v>
+        <v>148641587120</v>
       </c>
       <c r="AJ4" s="22">
-        <v>52639085480</v>
+        <v>17220497120</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5" s="25">
-        <v>20</v>
+      <c r="A5" s="30">
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -1223,109 +1235,109 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="8">
-        <v>133.8928384477712</v>
+      <c r="D5" s="30">
+        <v>130.3355028782062</v>
       </c>
       <c r="E5">
-        <v>37897</v>
+        <v>37756</v>
       </c>
       <c r="F5">
-        <v>3184</v>
+        <v>3155</v>
       </c>
       <c r="G5">
-        <v>128.53784860557769</v>
+        <v>128.19521912350601</v>
       </c>
       <c r="H5">
-        <v>11.89243027888446</v>
-      </c>
-      <c r="I5" s="7">
-        <v>11.89243027888446</v>
+        <v>11.776892430278879</v>
+      </c>
+      <c r="I5" s="9">
+        <v>11.776892430278879</v>
       </c>
       <c r="J5">
-        <v>10.350597609561749</v>
+        <v>10.262948207171309</v>
       </c>
       <c r="K5">
         <v>0.78884462151394419</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="30">
         <v>0.78884462151394419</v>
       </c>
-      <c r="M5" s="14">
-        <v>0.19920318725099601</v>
+      <c r="M5" s="30">
+        <v>0.18326693227091631</v>
       </c>
       <c r="N5">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O5" s="16">
-        <v>0.20318725099601601</v>
+      <c r="O5" s="30">
+        <v>0.18725099601593631</v>
       </c>
       <c r="P5">
-        <v>128.0637450199203</v>
+        <v>127.6215139442231</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5">
-        <v>33.466135458167329</v>
+        <v>46</v>
+      </c>
+      <c r="R5" s="30">
+        <v>34.661354581673308</v>
       </c>
       <c r="S5" t="s">
-        <v>34</v>
-      </c>
-      <c r="T5">
-        <v>56.972111553784863</v>
+        <v>54</v>
+      </c>
+      <c r="T5" s="7">
+        <v>58.56573705179283</v>
       </c>
       <c r="U5" t="s">
-        <v>35</v>
-      </c>
-      <c r="V5" s="17">
-        <v>100</v>
+        <v>41</v>
+      </c>
+      <c r="V5" s="7">
+        <v>92</v>
       </c>
       <c r="W5" t="s">
-        <v>36</v>
-      </c>
-      <c r="X5" s="27">
-        <v>96</v>
+        <v>38</v>
+      </c>
+      <c r="X5" s="30">
+        <v>88</v>
       </c>
       <c r="Y5">
-        <v>32263</v>
+        <v>32177</v>
       </c>
       <c r="Z5">
-        <v>2985</v>
+        <v>2956</v>
       </c>
       <c r="AA5">
-        <v>35248</v>
+        <v>35133</v>
       </c>
       <c r="AB5">
-        <v>2196</v>
+        <v>2190</v>
       </c>
       <c r="AC5">
         <v>198</v>
       </c>
-      <c r="AD5" s="7">
-        <v>2598</v>
+      <c r="AD5" s="30">
+        <v>2576</v>
       </c>
       <c r="AE5">
-        <v>50</v>
-      </c>
-      <c r="AF5" s="28">
+        <v>46</v>
+      </c>
+      <c r="AF5" s="30">
         <v>1</v>
       </c>
-      <c r="AG5" s="16">
-        <v>51</v>
+      <c r="AG5" s="8">
+        <v>47</v>
       </c>
       <c r="AH5" s="21">
-        <v>131421090000</v>
+        <v>130897500000</v>
       </c>
       <c r="AI5" s="22">
-        <v>175963427720</v>
+        <v>170605914880</v>
       </c>
       <c r="AJ5" s="22">
-        <v>44542337720</v>
+        <v>39708414880</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6" s="25">
-        <v>45</v>
+      <c r="A6" s="30">
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1333,109 +1345,109 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="9">
-        <v>139.08244440827571</v>
+      <c r="D6" s="30">
+        <v>128.50677761080809</v>
       </c>
       <c r="E6">
-        <v>37897</v>
+        <v>37875</v>
       </c>
       <c r="F6">
-        <v>3160</v>
+        <v>3191</v>
       </c>
       <c r="G6">
-        <v>128.6733067729084</v>
-      </c>
-      <c r="H6">
-        <v>11.756972111553781</v>
-      </c>
-      <c r="I6">
-        <v>11.756972111553781</v>
+        <v>128.601593625498</v>
+      </c>
+      <c r="H6" s="30">
+        <v>11.8605577689243</v>
+      </c>
+      <c r="I6" s="9">
+        <v>11.8605577689243</v>
       </c>
       <c r="J6">
-        <v>10.350597609561749</v>
-      </c>
-      <c r="K6">
-        <v>0.8127490039840638</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0.8127490039840638</v>
+        <v>10.27490039840638</v>
+      </c>
+      <c r="K6" s="30">
+        <v>0.8366533864541833</v>
+      </c>
+      <c r="L6" s="30">
+        <v>0.8366533864541833</v>
       </c>
       <c r="M6">
-        <v>0.18326693227091631</v>
-      </c>
-      <c r="N6">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O6" s="16">
-        <v>0.20318725099601601</v>
+        <v>0.14342629482071709</v>
+      </c>
+      <c r="N6" s="30">
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="O6" s="30">
+        <v>0.15936254980079681</v>
       </c>
       <c r="P6">
-        <v>128.15139442231069</v>
+        <v>128.03585657370519</v>
       </c>
       <c r="Q6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R6">
-        <v>29.880478087649401</v>
+        <v>70</v>
+      </c>
+      <c r="R6" s="30">
+        <v>35.059760956175303</v>
       </c>
       <c r="S6" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6" s="30">
+        <v>57.768924302788847</v>
+      </c>
+      <c r="U6" t="s">
+        <v>38</v>
+      </c>
+      <c r="V6" s="30">
+        <v>88</v>
+      </c>
+      <c r="W6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X6" s="30">
+        <v>76</v>
+      </c>
+      <c r="Y6">
+        <v>32279</v>
+      </c>
+      <c r="Z6">
+        <v>2977</v>
+      </c>
+      <c r="AA6">
+        <v>35256</v>
+      </c>
+      <c r="AB6">
+        <v>2209</v>
+      </c>
+      <c r="AC6">
+        <v>210</v>
+      </c>
+      <c r="AD6" s="30">
+        <v>2579</v>
+      </c>
+      <c r="AE6">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="30">
+        <v>4</v>
+      </c>
+      <c r="AG6" s="30">
         <v>40</v>
       </c>
-      <c r="T6">
-        <v>59.760956175298809</v>
-      </c>
-      <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="V6" s="17">
-        <v>100</v>
-      </c>
-      <c r="W6" t="s">
-        <v>41</v>
-      </c>
-      <c r="X6" s="9">
-        <v>92</v>
-      </c>
-      <c r="Y6">
-        <v>32297</v>
-      </c>
-      <c r="Z6">
-        <v>2951</v>
-      </c>
-      <c r="AA6">
-        <v>35248</v>
-      </c>
-      <c r="AB6">
-        <v>2190</v>
-      </c>
-      <c r="AC6">
-        <v>204</v>
-      </c>
-      <c r="AD6" s="7">
-        <v>2598</v>
-      </c>
-      <c r="AE6">
-        <v>46</v>
-      </c>
-      <c r="AF6">
-        <v>5</v>
-      </c>
-      <c r="AG6" s="16">
-        <v>51</v>
-      </c>
-      <c r="AH6" s="22">
+      <c r="AH6" s="21">
         <v>131421090000</v>
       </c>
       <c r="AI6" s="22">
-        <v>182783664440</v>
+        <v>168885007860</v>
       </c>
       <c r="AJ6" s="22">
-        <v>51362574440</v>
+        <v>37463917860</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>46</v>
+      <c r="A7" s="30">
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1443,109 +1455,109 @@
       <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="9">
-        <v>137.85242265131109</v>
+      <c r="D7" s="30">
+        <v>127.02495336174739</v>
       </c>
       <c r="E7">
-        <v>37748</v>
+        <v>37835</v>
       </c>
       <c r="F7">
-        <v>3158</v>
+        <v>3232</v>
       </c>
       <c r="G7">
-        <v>128.15139442231069</v>
+        <v>128.23904382470121</v>
       </c>
       <c r="H7">
-        <v>11.729083665338649</v>
+        <v>12.011952191235061</v>
       </c>
       <c r="I7">
-        <v>11.729083665338649</v>
+        <v>12.011952191235061</v>
       </c>
       <c r="J7">
-        <v>10.306772908366529</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="K7">
-        <v>0.84063745019920322</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0.84063745019920322</v>
+        <v>0.85657370517928288</v>
+      </c>
+      <c r="L7" s="30">
+        <v>0.85657370517928288</v>
       </c>
       <c r="M7">
-        <v>0.1912350597609562</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="N7">
-        <v>1.1952191235059761E-2</v>
-      </c>
-      <c r="O7" s="16">
-        <v>0.20318725099601601</v>
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="O7" s="30">
+        <v>0.15936254980079681</v>
       </c>
       <c r="P7">
-        <v>127.593625498008</v>
+        <v>127.87250996015941</v>
       </c>
       <c r="Q7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R7" s="28">
-        <v>30.677290836653391</v>
+        <v>46</v>
+      </c>
+      <c r="R7" s="30">
+        <v>34.661354581673308</v>
       </c>
       <c r="S7" t="s">
-        <v>53</v>
-      </c>
-      <c r="T7">
-        <v>61.752988047808763</v>
+        <v>62</v>
+      </c>
+      <c r="T7" s="30">
+        <v>57.370517928286858</v>
       </c>
       <c r="U7" t="s">
-        <v>36</v>
-      </c>
-      <c r="V7" s="9">
-        <v>96</v>
+        <v>38</v>
+      </c>
+      <c r="V7" s="30">
+        <v>88</v>
       </c>
       <c r="W7" t="s">
-        <v>36</v>
-      </c>
-      <c r="X7" s="27">
-        <v>96</v>
+        <v>63</v>
+      </c>
+      <c r="X7" s="30">
+        <v>80</v>
       </c>
       <c r="Y7">
-        <v>32166</v>
+        <v>32188</v>
       </c>
       <c r="Z7">
-        <v>2944</v>
+        <v>3015</v>
       </c>
       <c r="AA7">
-        <v>35110</v>
+        <v>35203</v>
       </c>
       <c r="AB7">
-        <v>2172</v>
+        <v>2217</v>
       </c>
       <c r="AC7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD7" s="7">
-        <v>2587</v>
+        <v>2592</v>
       </c>
       <c r="AE7">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF7">
-        <v>3</v>
-      </c>
-      <c r="AG7" s="16">
-        <v>51</v>
-      </c>
-      <c r="AH7" s="22">
-        <v>130897500000</v>
+        <v>2</v>
+      </c>
+      <c r="AG7" s="30">
+        <v>40</v>
+      </c>
+      <c r="AH7" s="21">
+        <v>131421090000</v>
       </c>
       <c r="AI7" s="22">
-        <v>180445374940</v>
+        <v>166937578280</v>
       </c>
       <c r="AJ7" s="22">
-        <v>49547874940</v>
+        <v>35516488280</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>10</v>
+      <c r="A8" s="30">
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -1553,109 +1565,109 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17">
-        <v>140.12873209315191</v>
+      <c r="D8" s="14">
+        <v>141.49346514639319</v>
       </c>
       <c r="E8">
-        <v>37925</v>
+        <v>37711</v>
       </c>
       <c r="F8">
-        <v>3151</v>
+        <v>3145</v>
       </c>
       <c r="G8">
-        <v>128.8565737051793</v>
+        <v>128.16733067729081</v>
       </c>
       <c r="H8">
-        <v>11.71713147410359</v>
-      </c>
-      <c r="I8" s="14">
-        <v>11.71713147410359</v>
+        <v>11.569721115537851</v>
+      </c>
+      <c r="I8" s="30">
+        <v>11.569721115537851</v>
       </c>
       <c r="J8">
-        <v>10.31872509960159</v>
-      </c>
-      <c r="K8">
-        <v>0.8127490039840638</v>
-      </c>
-      <c r="L8">
-        <v>0.8127490039840638</v>
+        <v>10.322709163346611</v>
+      </c>
+      <c r="K8" s="14">
+        <v>0.92828685258964139</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0.92828685258964139</v>
       </c>
       <c r="M8">
-        <v>0.17928286852589639</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="N8">
-        <v>2.3904382470119521E-2</v>
-      </c>
-      <c r="O8" s="16">
-        <v>0.20318725099601601</v>
+        <v>3.1872509960159362E-2</v>
+      </c>
+      <c r="O8" s="30">
+        <v>0.18326693227091631</v>
       </c>
       <c r="P8">
-        <v>128.19521912350601</v>
+        <v>127.6573705179283</v>
       </c>
       <c r="Q8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="7">
-        <v>31.075697211155379</v>
+        <v>58</v>
+      </c>
+      <c r="R8" s="14">
+        <v>25.099601593625501</v>
       </c>
       <c r="S8" t="s">
-        <v>57</v>
-      </c>
-      <c r="T8">
-        <v>58.167330677290842</v>
+        <v>59</v>
+      </c>
+      <c r="T8" s="9">
+        <v>60.159362549800797</v>
       </c>
       <c r="U8" t="s">
         <v>41</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="7">
         <v>92</v>
       </c>
       <c r="W8" t="s">
-        <v>45</v>
-      </c>
-      <c r="X8">
-        <v>84</v>
+        <v>41</v>
+      </c>
+      <c r="X8" s="9">
+        <v>92</v>
       </c>
       <c r="Y8">
-        <v>32343</v>
+        <v>32170</v>
       </c>
       <c r="Z8">
-        <v>2941</v>
+        <v>2904</v>
       </c>
       <c r="AA8">
-        <v>35284</v>
+        <v>35074</v>
       </c>
       <c r="AB8">
-        <v>2182</v>
+        <v>2174</v>
       </c>
       <c r="AC8">
-        <v>204</v>
-      </c>
-      <c r="AD8" s="7">
-        <v>2590</v>
+        <v>233</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>2591</v>
       </c>
       <c r="AE8">
-        <v>45</v>
-      </c>
-      <c r="AF8" s="9">
-        <v>6</v>
-      </c>
-      <c r="AG8" s="16">
-        <v>51</v>
-      </c>
-      <c r="AH8" s="22">
-        <v>131421090000</v>
+        <v>38</v>
+      </c>
+      <c r="AF8" s="15">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="8">
+        <v>46</v>
+      </c>
+      <c r="AH8" s="21">
+        <v>130897500000</v>
       </c>
       <c r="AI8" s="22">
-        <v>184158707120</v>
-      </c>
-      <c r="AJ8" s="22">
-        <v>52737617120</v>
+        <v>185211408540</v>
+      </c>
+      <c r="AJ8" s="38">
+        <v>54313908540</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1663,109 +1675,109 @@
       <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="9">
-        <v>138.27420137818061</v>
+      <c r="D9" s="8">
+        <v>132.88851661479899</v>
       </c>
       <c r="E9">
-        <v>37925</v>
+        <v>37865</v>
       </c>
       <c r="F9">
-        <v>3069</v>
+        <v>3199</v>
       </c>
       <c r="G9">
-        <v>129.12749003984061</v>
+        <v>128.4581673306773</v>
       </c>
       <c r="H9">
-        <v>11.446215139442231</v>
-      </c>
-      <c r="I9" s="28">
-        <v>11.446215139442231</v>
+        <v>11.908366533864539</v>
+      </c>
+      <c r="I9" s="7">
+        <v>11.908366533864539</v>
       </c>
       <c r="J9">
-        <v>10.31872509960159</v>
-      </c>
-      <c r="K9">
-        <v>0.75697211155378485</v>
-      </c>
-      <c r="L9">
-        <v>0.75697211155378485</v>
+        <v>10.314741035856571</v>
+      </c>
+      <c r="K9" s="30">
+        <v>0.81673306772908372</v>
+      </c>
+      <c r="L9" s="30">
+        <v>0.81673306772908372</v>
       </c>
       <c r="M9">
-        <v>0.17928286852589639</v>
+        <v>0.15537848605577689</v>
       </c>
       <c r="N9">
-        <v>2.3904382470119521E-2</v>
-      </c>
-      <c r="O9" s="16">
-        <v>0.20318725099601601</v>
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="O9" s="30">
+        <v>0.1752988047808765</v>
       </c>
       <c r="P9">
-        <v>128.49402390438249</v>
+        <v>128.00398406374501</v>
       </c>
       <c r="Q9" t="s">
-        <v>68</v>
-      </c>
-      <c r="R9">
-        <v>36.254980079681268</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="30">
+        <v>33.466135458167329</v>
       </c>
       <c r="S9" t="s">
-        <v>69</v>
-      </c>
-      <c r="T9">
-        <v>52.988047808764939</v>
+        <v>61</v>
+      </c>
+      <c r="T9" s="30">
+        <v>57.768924302788847</v>
       </c>
       <c r="U9" t="s">
-        <v>41</v>
-      </c>
-      <c r="V9" s="28">
-        <v>92</v>
+        <v>38</v>
+      </c>
+      <c r="V9" s="30">
+        <v>88</v>
       </c>
       <c r="W9" t="s">
-        <v>45</v>
-      </c>
-      <c r="X9">
-        <v>84</v>
+        <v>38</v>
+      </c>
+      <c r="X9" s="30">
+        <v>88</v>
       </c>
       <c r="Y9">
-        <v>32411</v>
+        <v>32243</v>
       </c>
       <c r="Z9">
-        <v>2873</v>
+        <v>2989</v>
       </c>
       <c r="AA9">
-        <v>35284</v>
+        <v>35232</v>
       </c>
       <c r="AB9">
-        <v>2196</v>
+        <v>2208</v>
       </c>
       <c r="AC9">
-        <v>190</v>
-      </c>
-      <c r="AD9" s="7">
-        <v>2590</v>
+        <v>205</v>
+      </c>
+      <c r="AD9" s="30">
+        <v>2589</v>
       </c>
       <c r="AE9">
-        <v>45</v>
-      </c>
-      <c r="AF9" s="9">
-        <v>6</v>
-      </c>
-      <c r="AG9" s="16">
-        <v>51</v>
-      </c>
-      <c r="AH9" s="22">
+        <v>39</v>
+      </c>
+      <c r="AF9" s="7">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="30">
+        <v>44</v>
+      </c>
+      <c r="AH9" s="21">
         <v>131421090000</v>
       </c>
       <c r="AI9" s="22">
-        <v>181721462640</v>
-      </c>
-      <c r="AJ9" s="22">
-        <v>50300372640</v>
+        <v>174643537020</v>
+      </c>
+      <c r="AJ9" s="39">
+        <v>43222447020</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>48</v>
+      <c r="A10" s="30">
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1773,109 +1785,109 @@
       <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="7">
-        <v>136.62677643095921</v>
+      <c r="D10" s="30">
+        <v>130.13855146080439</v>
       </c>
       <c r="E10">
-        <v>37626</v>
+        <v>37850</v>
       </c>
       <c r="F10">
-        <v>3184</v>
+        <v>3140</v>
       </c>
       <c r="G10">
-        <v>127.61354581673309</v>
+        <v>128.6414342629482</v>
       </c>
       <c r="H10">
-        <v>11.85258964143426</v>
-      </c>
-      <c r="I10" s="28">
-        <v>11.85258964143426</v>
+        <v>11.66135458167331</v>
+      </c>
+      <c r="I10" s="30">
+        <v>11.66135458167331</v>
       </c>
       <c r="J10">
-        <v>10.23505976095618</v>
+        <v>10.32669322709163</v>
       </c>
       <c r="K10">
-        <v>0.82470119521912355</v>
-      </c>
-      <c r="L10">
-        <v>0.82470119521912355</v>
+        <v>0.83266932270916338</v>
+      </c>
+      <c r="L10" s="30">
+        <v>0.83266932270916338</v>
       </c>
       <c r="M10">
-        <v>0.19521912350597609</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="N10">
-        <v>7.9681274900398405E-3</v>
-      </c>
-      <c r="O10" s="16">
-        <v>0.20318725099601601</v>
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="O10" s="30">
+        <v>0.16733067729083659</v>
       </c>
       <c r="P10">
-        <v>126.9800796812749</v>
+        <v>128.23904382470121</v>
       </c>
       <c r="Q10" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="R10" s="9">
-        <v>25.89641434262948</v>
+        <v>29.482071713147409</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
-      </c>
-      <c r="T10" s="17">
-        <v>63.34661354581673</v>
+        <v>61</v>
+      </c>
+      <c r="T10" s="30">
+        <v>57.768924302788847</v>
       </c>
       <c r="U10" t="s">
-        <v>38</v>
-      </c>
-      <c r="V10" s="28">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="V10" s="7">
+        <v>92</v>
       </c>
       <c r="W10" t="s">
         <v>45</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="30">
         <v>84</v>
       </c>
       <c r="Y10">
-        <v>32031</v>
+        <v>32289</v>
       </c>
       <c r="Z10">
-        <v>2975</v>
+        <v>2927</v>
       </c>
       <c r="AA10">
-        <v>35006</v>
+        <v>35216</v>
       </c>
       <c r="AB10">
-        <v>2158</v>
+        <v>2215</v>
       </c>
       <c r="AC10">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AD10" s="7">
-        <v>2569</v>
+        <v>2592</v>
       </c>
       <c r="AE10">
-        <v>49</v>
-      </c>
-      <c r="AF10">
-        <v>2</v>
-      </c>
-      <c r="AG10" s="16">
-        <v>51</v>
-      </c>
-      <c r="AH10" s="22">
-        <v>130373910000</v>
+        <v>38</v>
+      </c>
+      <c r="AF10" s="30">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="30">
+        <v>42</v>
+      </c>
+      <c r="AH10" s="21">
+        <v>131421090000</v>
       </c>
       <c r="AI10" s="22">
-        <v>178125670540</v>
+        <v>171029502840</v>
       </c>
       <c r="AJ10" s="22">
-        <v>47751760540</v>
+        <v>39608412840</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>31</v>
+      <c r="A11" s="30">
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1883,109 +1895,109 @@
       <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="28">
-        <v>129.31329262297251</v>
+      <c r="D11" s="30">
+        <v>129.96682088087991</v>
       </c>
       <c r="E11">
-        <v>37883</v>
+        <v>37833</v>
       </c>
       <c r="F11">
-        <v>3086</v>
+        <v>3076</v>
       </c>
       <c r="G11">
-        <v>128.84860557768931</v>
-      </c>
-      <c r="H11" s="28">
-        <v>11.553784860557769</v>
-      </c>
-      <c r="I11">
-        <v>11.553784860557769</v>
+        <v>128.8167330677291</v>
+      </c>
+      <c r="H11" s="30">
+        <v>11.37450199203187</v>
+      </c>
+      <c r="I11" s="30">
+        <v>11.37450199203187</v>
       </c>
       <c r="J11">
-        <v>10.334661354581669</v>
+        <v>10.37450199203187</v>
       </c>
       <c r="K11">
-        <v>0.73705179282868527</v>
-      </c>
-      <c r="L11" s="28">
-        <v>0.73705179282868527</v>
-      </c>
-      <c r="M11" s="9">
-        <v>0.18725099601593631</v>
-      </c>
-      <c r="N11" s="28">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O11">
-        <v>0.1912350597609562</v>
+        <v>0.86454183266932272</v>
+      </c>
+      <c r="L11" s="30">
+        <v>0.86454183266932272</v>
+      </c>
+      <c r="M11" s="30">
+        <v>0.14741035856573709</v>
+      </c>
+      <c r="N11" s="30">
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="O11" s="30">
+        <v>0.1633466135458167</v>
       </c>
       <c r="P11">
-        <v>128.45418326693229</v>
+        <v>128.49402390438249</v>
       </c>
       <c r="Q11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R11" s="7">
-        <v>31.474103585657371</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="30">
+        <v>32.270916334661351</v>
       </c>
       <c r="S11" t="s">
-        <v>50</v>
-      </c>
-      <c r="T11" s="28">
-        <v>55.378486055776889</v>
+        <v>57</v>
+      </c>
+      <c r="T11" s="7">
+        <v>58.167330677290842</v>
       </c>
       <c r="U11" t="s">
         <v>38</v>
       </c>
-      <c r="V11" s="28">
+      <c r="V11" s="30">
         <v>88</v>
       </c>
       <c r="W11" t="s">
-        <v>48</v>
-      </c>
-      <c r="X11">
-        <v>76</v>
+        <v>45</v>
+      </c>
+      <c r="X11" s="30">
+        <v>84</v>
       </c>
       <c r="Y11">
-        <v>32341</v>
+        <v>32333</v>
       </c>
       <c r="Z11">
-        <v>2900</v>
+        <v>2855</v>
       </c>
       <c r="AA11">
-        <v>35241</v>
+        <v>35188</v>
       </c>
       <c r="AB11">
-        <v>2217</v>
+        <v>2223</v>
       </c>
       <c r="AC11">
-        <v>185</v>
-      </c>
-      <c r="AD11" s="28">
-        <v>2594</v>
+        <v>217</v>
+      </c>
+      <c r="AD11" s="7">
+        <v>2604</v>
       </c>
       <c r="AE11">
-        <v>47</v>
-      </c>
-      <c r="AF11" s="28">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="7">
-        <v>48</v>
-      </c>
-      <c r="AH11" s="22">
+        <v>37</v>
+      </c>
+      <c r="AF11" s="30">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="30">
+        <v>41</v>
+      </c>
+      <c r="AH11" s="21">
         <v>131421090000</v>
       </c>
       <c r="AI11" s="22">
-        <v>169944938680</v>
+        <v>170803812640</v>
       </c>
       <c r="AJ11" s="22">
-        <v>38523848680</v>
+        <v>39382722640</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1993,109 +2005,109 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="28">
-        <v>129.6847290187595</v>
+      <c r="D12" s="30">
+        <v>116.4762356347524</v>
       </c>
       <c r="E12">
-        <v>37873</v>
+        <v>37654</v>
       </c>
       <c r="F12">
-        <v>3075</v>
+        <v>3106</v>
       </c>
       <c r="G12">
-        <v>128.85258964143429</v>
-      </c>
-      <c r="H12" s="7">
-        <v>11.466135458167329</v>
-      </c>
-      <c r="I12">
-        <v>11.466135458167329</v>
+        <v>127.97609561752989</v>
+      </c>
+      <c r="H12" s="30">
+        <v>11.621513944223111</v>
+      </c>
+      <c r="I12" s="30">
+        <v>11.621513944223111</v>
       </c>
       <c r="J12">
-        <v>10.38247011952191</v>
+        <v>10.290836653386449</v>
       </c>
       <c r="K12">
-        <v>0.78087649402390436</v>
-      </c>
-      <c r="L12" s="14">
-        <v>0.78087649402390436</v>
+        <v>0.7450199203187251</v>
+      </c>
+      <c r="L12" s="30">
+        <v>0.7450199203187251</v>
       </c>
       <c r="M12">
-        <v>0.18326693227091631</v>
-      </c>
-      <c r="N12">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O12" s="28">
-        <v>0.18725099601593631</v>
+        <v>0.1195219123505976</v>
+      </c>
+      <c r="N12" s="30">
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="O12" s="30">
+        <v>0.12749003984063739</v>
       </c>
       <c r="P12">
-        <v>128.4980079681275</v>
+        <v>127.8167330677291</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12">
-        <v>33.466135458167329</v>
+        <v>80</v>
+      </c>
+      <c r="R12" s="30">
+        <v>39.04382470119522</v>
       </c>
       <c r="S12" t="s">
-        <v>37</v>
-      </c>
-      <c r="T12">
-        <v>54.581673306772913</v>
+        <v>81</v>
+      </c>
+      <c r="T12" s="30">
+        <v>51.394422310756973</v>
       </c>
       <c r="U12" t="s">
-        <v>35</v>
-      </c>
-      <c r="V12" s="17">
-        <v>100</v>
+        <v>63</v>
+      </c>
+      <c r="V12" s="30">
+        <v>80</v>
       </c>
       <c r="W12" t="s">
-        <v>38</v>
-      </c>
-      <c r="X12" s="28">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="X12" s="30">
+        <v>68</v>
       </c>
       <c r="Y12">
-        <v>32342</v>
+        <v>32122</v>
       </c>
       <c r="Z12">
-        <v>2878</v>
+        <v>2917</v>
       </c>
       <c r="AA12">
-        <v>35220</v>
+        <v>35039</v>
       </c>
       <c r="AB12">
-        <v>2222</v>
+        <v>2268</v>
       </c>
       <c r="AC12">
-        <v>196</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>2606</v>
+        <v>187</v>
+      </c>
+      <c r="AD12" s="7">
+        <v>2583</v>
       </c>
       <c r="AE12">
-        <v>46</v>
-      </c>
-      <c r="AF12">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="8">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="AF12" s="30">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="30">
+        <v>32</v>
       </c>
       <c r="AH12" s="21">
-        <v>131421090000</v>
+        <v>130897500000</v>
       </c>
       <c r="AI12" s="22">
-        <v>170433084440</v>
+        <v>152464480540</v>
       </c>
       <c r="AJ12" s="22">
-        <v>39011994440</v>
+        <v>21566980540</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="28">
-        <v>36</v>
+      <c r="A13" s="25">
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -2103,56 +2115,56 @@
       <c r="C13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="7">
-        <v>136.6171490255812</v>
+      <c r="D13" s="8">
+        <v>133.8928384477712</v>
       </c>
       <c r="E13">
-        <v>37914</v>
+        <v>37897</v>
       </c>
       <c r="F13">
-        <v>3127</v>
+        <v>3184</v>
       </c>
       <c r="G13">
-        <v>128.90438247011949</v>
+        <v>128.53784860557769</v>
       </c>
       <c r="H13">
-        <v>11.613545816733071</v>
-      </c>
-      <c r="I13" s="9">
-        <v>11.613545816733071</v>
+        <v>11.89243027888446</v>
+      </c>
+      <c r="I13" s="7">
+        <v>11.89243027888446</v>
       </c>
       <c r="J13">
-        <v>10.34661354581673</v>
+        <v>10.350597609561749</v>
       </c>
       <c r="K13">
-        <v>0.82071713147410363</v>
-      </c>
-      <c r="L13" s="28">
-        <v>0.82071713147410363</v>
-      </c>
-      <c r="M13">
-        <v>0.1633466135458167</v>
+        <v>0.78884462151394419</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0.78884462151394419</v>
+      </c>
+      <c r="M13" s="14">
+        <v>0.19920318725099601</v>
       </c>
       <c r="N13">
-        <v>2.3904382470119521E-2</v>
-      </c>
-      <c r="O13" s="28">
-        <v>0.18725099601593631</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0.20318725099601601</v>
       </c>
       <c r="P13">
-        <v>128.37051792828689</v>
+        <v>128.0637450199203</v>
       </c>
       <c r="Q13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R13">
-        <v>32.270916334661351</v>
+        <v>33</v>
+      </c>
+      <c r="R13" s="30">
+        <v>33.466135458167329</v>
       </c>
       <c r="S13" t="s">
-        <v>40</v>
-      </c>
-      <c r="T13">
-        <v>59.760956175298809</v>
+        <v>34</v>
+      </c>
+      <c r="T13" s="30">
+        <v>56.972111553784863</v>
       </c>
       <c r="U13" t="s">
         <v>35</v>
@@ -2161,51 +2173,51 @@
         <v>100</v>
       </c>
       <c r="W13" t="s">
-        <v>41</v>
-      </c>
-      <c r="X13" s="9">
-        <v>92</v>
+        <v>36</v>
+      </c>
+      <c r="X13" s="27">
+        <v>96</v>
       </c>
       <c r="Y13">
-        <v>32355</v>
+        <v>32263</v>
       </c>
       <c r="Z13">
-        <v>2915</v>
+        <v>2985</v>
       </c>
       <c r="AA13">
-        <v>35270</v>
+        <v>35248</v>
       </c>
       <c r="AB13">
-        <v>2203</v>
+        <v>2196</v>
       </c>
       <c r="AC13">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AD13" s="7">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="AE13">
-        <v>41</v>
-      </c>
-      <c r="AF13" s="9">
-        <v>6</v>
-      </c>
-      <c r="AG13" s="8">
-        <v>47</v>
-      </c>
-      <c r="AH13" s="22">
-        <v>131498900000</v>
+        <v>50</v>
+      </c>
+      <c r="AF13" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="16">
+        <v>51</v>
+      </c>
+      <c r="AH13" s="21">
+        <v>131421090000</v>
       </c>
       <c r="AI13" s="22">
-        <v>179650048180</v>
-      </c>
-      <c r="AJ13" s="22">
-        <v>48151148180</v>
+        <v>175963427720</v>
+      </c>
+      <c r="AJ13" s="39">
+        <v>44542337720</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>43</v>
+      <c r="A14" s="30">
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -2213,109 +2225,109 @@
       <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="7">
-        <v>136.12890390728001</v>
+      <c r="D14" s="30">
+        <v>119.68388553161439</v>
       </c>
       <c r="E14">
-        <v>37866</v>
+        <v>37823</v>
       </c>
       <c r="F14">
-        <v>3212</v>
+        <v>3171</v>
       </c>
       <c r="G14">
-        <v>128.3585657370518</v>
-      </c>
-      <c r="H14" s="7">
-        <v>11.94820717131474</v>
-      </c>
-      <c r="I14">
-        <v>11.94820717131474</v>
+        <v>128.3545816733068</v>
+      </c>
+      <c r="H14" s="30">
+        <v>11.908366533864539</v>
+      </c>
+      <c r="I14" s="30">
+        <v>11.908366533864539</v>
       </c>
       <c r="J14">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="K14">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="M14">
-        <v>0.16733067729083659</v>
-      </c>
-      <c r="N14" s="14">
+        <v>10.29482071713147</v>
+      </c>
+      <c r="K14" s="30">
+        <v>0.70517928286852594</v>
+      </c>
+      <c r="L14" s="30">
+        <v>0.70517928286852594</v>
+      </c>
+      <c r="M14" s="30">
+        <v>0.11155378486055779</v>
+      </c>
+      <c r="N14" s="30">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O14">
-        <v>0.18725099601593631</v>
+      <c r="O14" s="30">
+        <v>0.13147410358565739</v>
       </c>
       <c r="P14">
-        <v>127.9123505976096</v>
+        <v>128.11553784860561</v>
       </c>
       <c r="Q14" t="s">
-        <v>51</v>
-      </c>
-      <c r="R14" s="7">
-        <v>31.075697211155379</v>
+        <v>85</v>
+      </c>
+      <c r="R14" s="30">
+        <v>42.629482071713149</v>
       </c>
       <c r="S14" t="s">
-        <v>52</v>
-      </c>
-      <c r="T14" s="7">
-        <v>62.948207171314742</v>
+        <v>81</v>
+      </c>
+      <c r="T14" s="30">
+        <v>51.394422310756973</v>
       </c>
       <c r="U14" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14" s="9">
-        <v>96</v>
+        <v>74</v>
+      </c>
+      <c r="V14" s="30">
+        <v>72</v>
       </c>
       <c r="W14" t="s">
-        <v>45</v>
-      </c>
-      <c r="X14">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X14" s="30">
+        <v>60</v>
       </c>
       <c r="Y14">
-        <v>32218</v>
+        <v>32217</v>
       </c>
       <c r="Z14">
-        <v>2999</v>
+        <v>2989</v>
       </c>
       <c r="AA14">
-        <v>35217</v>
+        <v>35206</v>
       </c>
       <c r="AB14">
-        <v>2206</v>
+        <v>2275</v>
       </c>
       <c r="AC14">
-        <v>208</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>2602</v>
+        <v>177</v>
+      </c>
+      <c r="AD14" s="30">
+        <v>2584</v>
       </c>
       <c r="AE14">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AF14" s="7">
         <v>5</v>
       </c>
-      <c r="AG14" s="8">
-        <v>47</v>
-      </c>
-      <c r="AH14" s="22">
+      <c r="AG14" s="30">
+        <v>33</v>
+      </c>
+      <c r="AH14" s="21">
         <v>131421090000</v>
       </c>
       <c r="AI14" s="22">
-        <v>178902089320</v>
+        <v>157289866920</v>
       </c>
       <c r="AJ14" s="22">
-        <v>47480999320</v>
+        <v>25868776920</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2323,109 +2335,109 @@
       <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="28">
-        <v>130.3355028782062</v>
+      <c r="D15" s="30">
+        <v>122.99666202738079</v>
       </c>
       <c r="E15">
-        <v>37756</v>
+        <v>37794</v>
       </c>
       <c r="F15">
-        <v>3155</v>
+        <v>3172</v>
       </c>
       <c r="G15">
-        <v>128.19521912350601</v>
-      </c>
-      <c r="H15">
-        <v>11.776892430278879</v>
-      </c>
-      <c r="I15" s="9">
-        <v>11.776892430278879</v>
+        <v>128.15139442231069</v>
+      </c>
+      <c r="H15" s="14">
+        <v>11.84860557768924</v>
+      </c>
+      <c r="I15" s="30">
+        <v>11.84860557768924</v>
       </c>
       <c r="J15">
-        <v>10.262948207171309</v>
+        <v>10.41832669322709</v>
       </c>
       <c r="K15">
-        <v>0.78884462151394419</v>
-      </c>
-      <c r="L15">
-        <v>0.78884462151394419</v>
+        <v>0.78486055776892427</v>
+      </c>
+      <c r="L15" s="30">
+        <v>0.78486055776892427</v>
       </c>
       <c r="M15">
-        <v>0.18326693227091631</v>
-      </c>
-      <c r="N15">
+        <v>0.151394422310757</v>
+      </c>
+      <c r="N15" s="30">
         <v>3.9840637450199202E-3</v>
       </c>
-      <c r="O15" s="28">
-        <v>0.18725099601593631</v>
+      <c r="O15" s="30">
+        <v>0.15537848605577689</v>
       </c>
       <c r="P15">
-        <v>127.6215139442231</v>
+        <v>128.11155378486049</v>
       </c>
       <c r="Q15" t="s">
         <v>46</v>
       </c>
-      <c r="R15" s="28">
+      <c r="R15" s="30">
         <v>34.661354581673308</v>
       </c>
       <c r="S15" t="s">
-        <v>54</v>
-      </c>
-      <c r="T15">
-        <v>58.56573705179283</v>
+        <v>61</v>
+      </c>
+      <c r="T15" s="30">
+        <v>57.768924302788847</v>
       </c>
       <c r="U15" t="s">
-        <v>41</v>
-      </c>
-      <c r="V15">
-        <v>92</v>
+        <v>45</v>
+      </c>
+      <c r="V15" s="30">
+        <v>84</v>
       </c>
       <c r="W15" t="s">
+        <v>48</v>
+      </c>
+      <c r="X15" s="30">
+        <v>76</v>
+      </c>
+      <c r="Y15">
+        <v>32166</v>
+      </c>
+      <c r="Z15">
+        <v>2974</v>
+      </c>
+      <c r="AA15">
+        <v>35140</v>
+      </c>
+      <c r="AB15">
+        <v>2262</v>
+      </c>
+      <c r="AC15">
+        <v>197</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>2615</v>
+      </c>
+      <c r="AE15">
         <v>38</v>
       </c>
-      <c r="X15">
-        <v>88</v>
-      </c>
-      <c r="Y15">
-        <v>32177</v>
-      </c>
-      <c r="Z15">
-        <v>2956</v>
-      </c>
-      <c r="AA15">
-        <v>35133</v>
-      </c>
-      <c r="AB15">
-        <v>2190</v>
-      </c>
-      <c r="AC15">
-        <v>198</v>
-      </c>
-      <c r="AD15" s="28">
-        <v>2576</v>
-      </c>
-      <c r="AE15">
-        <v>46</v>
-      </c>
-      <c r="AF15" s="28">
+      <c r="AF15" s="30">
         <v>1</v>
       </c>
-      <c r="AG15" s="8">
-        <v>47</v>
+      <c r="AG15" s="30">
+        <v>39</v>
       </c>
       <c r="AH15" s="21">
-        <v>130897500000</v>
+        <v>131421090000</v>
       </c>
       <c r="AI15" s="22">
-        <v>170605914880</v>
+        <v>161643553900</v>
       </c>
       <c r="AJ15" s="22">
-        <v>39708414880</v>
+        <v>30222463900</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -2433,109 +2445,109 @@
       <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="7">
-        <v>135.8033808120143</v>
+      <c r="D16" s="30">
+        <v>122.82663205943579</v>
       </c>
       <c r="E16">
-        <v>37866</v>
+        <v>37663</v>
       </c>
       <c r="F16">
-        <v>3131</v>
+        <v>3151</v>
       </c>
       <c r="G16">
-        <v>128.68127490039839</v>
+        <v>127.9163346613546</v>
       </c>
       <c r="H16">
-        <v>11.62549800796813</v>
-      </c>
-      <c r="I16" s="28">
-        <v>11.62549800796813</v>
+        <v>11.71314741035857</v>
+      </c>
+      <c r="I16" s="30">
+        <v>11.71314741035857</v>
       </c>
       <c r="J16">
-        <v>10.366533864541831</v>
-      </c>
-      <c r="K16">
+        <v>10.28286852589641</v>
+      </c>
+      <c r="K16" s="30">
         <v>0.82868525896414347</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="30">
         <v>0.82868525896414347</v>
       </c>
-      <c r="M16">
-        <v>0.16733067729083659</v>
+      <c r="M16" s="30">
+        <v>0.12749003984063739</v>
       </c>
       <c r="N16">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O16">
-        <v>0.18725099601593631</v>
+        <v>1.1952191235059761E-2</v>
+      </c>
+      <c r="O16" s="30">
+        <v>0.1394422310756972</v>
       </c>
       <c r="P16">
-        <v>128.27091633466139</v>
+        <v>127.63346613545821</v>
       </c>
       <c r="Q16" t="s">
-        <v>66</v>
-      </c>
-      <c r="R16" s="9">
-        <v>30.2788844621514</v>
+        <v>39</v>
+      </c>
+      <c r="R16" s="30">
+        <v>32.270916334661351</v>
       </c>
       <c r="S16" t="s">
-        <v>67</v>
-      </c>
-      <c r="T16" s="9">
-        <v>63.34661354581673</v>
+        <v>71</v>
+      </c>
+      <c r="T16" s="7">
+        <v>59.362549800796813</v>
       </c>
       <c r="U16" t="s">
-        <v>41</v>
-      </c>
-      <c r="V16">
-        <v>92</v>
+        <v>38</v>
+      </c>
+      <c r="V16" s="30">
+        <v>88</v>
       </c>
       <c r="W16" t="s">
-        <v>38</v>
-      </c>
-      <c r="X16">
-        <v>88</v>
+        <v>72</v>
+      </c>
+      <c r="X16" s="30">
+        <v>68</v>
       </c>
       <c r="Y16">
-        <v>32299</v>
+        <v>32107</v>
       </c>
       <c r="Z16">
-        <v>2918</v>
+        <v>2940</v>
       </c>
       <c r="AA16">
-        <v>35217</v>
+        <v>35047</v>
       </c>
       <c r="AB16">
-        <v>2206</v>
+        <v>2233</v>
       </c>
       <c r="AC16">
         <v>208</v>
       </c>
-      <c r="AD16" s="9">
-        <v>2602</v>
+      <c r="AD16" s="7">
+        <v>2581</v>
       </c>
       <c r="AE16">
-        <v>42</v>
-      </c>
-      <c r="AF16" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG16" s="8">
-        <v>47</v>
-      </c>
-      <c r="AH16" s="22">
-        <v>131421090000</v>
+        <v>32</v>
+      </c>
+      <c r="AF16" s="30">
+        <v>3</v>
+      </c>
+      <c r="AG16" s="30">
+        <v>35</v>
+      </c>
+      <c r="AH16" s="21">
+        <v>130897500000</v>
       </c>
       <c r="AI16" s="22">
-        <v>178474283320</v>
+        <v>160776990700</v>
       </c>
       <c r="AJ16" s="22">
-        <v>47053193320</v>
+        <v>29879490700</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -2543,109 +2555,109 @@
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="28">
-        <v>129.59581040126821</v>
+      <c r="D17" s="30">
+        <v>120.2838135487691</v>
       </c>
       <c r="E17">
-        <v>37716</v>
+        <v>37658</v>
       </c>
       <c r="F17">
-        <v>2933</v>
+        <v>3147</v>
       </c>
       <c r="G17">
-        <v>128.8565737051793</v>
+        <v>127.8764940239044</v>
       </c>
       <c r="H17">
-        <v>10.89243027888446</v>
-      </c>
-      <c r="I17">
-        <v>10.89243027888446</v>
+        <v>11.709163346613551</v>
+      </c>
+      <c r="I17" s="30">
+        <v>11.709163346613551</v>
       </c>
       <c r="J17">
-        <v>10.32669322709163</v>
-      </c>
-      <c r="K17" s="10">
-        <v>0.78884462151394419</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0.78884462151394419</v>
+        <v>10.30278884462151</v>
+      </c>
+      <c r="K17" s="30">
+        <v>0.82868525896414347</v>
+      </c>
+      <c r="L17" s="30">
+        <v>0.82868525896414347</v>
       </c>
       <c r="M17">
-        <v>0.18326693227091631</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="N17">
-        <v>3.9840637450199202E-3</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>0.18725099601593631</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="P17">
-        <v>128.53386454183271</v>
+        <v>127.6494023904382</v>
       </c>
       <c r="Q17" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R17" s="7">
-        <v>31.075697211155379</v>
+        <v>30.677290836653391</v>
       </c>
       <c r="S17" t="s">
-        <v>76</v>
-      </c>
-      <c r="T17" s="28">
-        <v>56.573705179282882</v>
+        <v>44</v>
+      </c>
+      <c r="T17" s="7">
+        <v>58.964143426294832</v>
       </c>
       <c r="U17" t="s">
-        <v>38</v>
-      </c>
-      <c r="V17">
-        <v>88</v>
+        <v>36</v>
+      </c>
+      <c r="V17" s="41">
+        <v>96</v>
       </c>
       <c r="W17" t="s">
         <v>45</v>
       </c>
-      <c r="X17" s="28">
+      <c r="X17" s="30">
         <v>84</v>
       </c>
       <c r="Y17">
-        <v>32343</v>
+        <v>32097</v>
       </c>
       <c r="Z17">
-        <v>2734</v>
+        <v>2939</v>
       </c>
       <c r="AA17">
-        <v>35077</v>
+        <v>35036</v>
       </c>
       <c r="AB17">
-        <v>2206</v>
+        <v>2234</v>
       </c>
       <c r="AC17">
-        <v>198</v>
-      </c>
-      <c r="AD17" s="9">
-        <v>2592</v>
+        <v>208</v>
+      </c>
+      <c r="AD17" s="7">
+        <v>2586</v>
       </c>
       <c r="AE17">
-        <v>46</v>
-      </c>
-      <c r="AF17" s="28">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="8">
-        <v>47</v>
-      </c>
-      <c r="AH17" s="22">
+        <v>36</v>
+      </c>
+      <c r="AF17" s="30">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="30">
+        <v>36</v>
+      </c>
+      <c r="AH17" s="21">
         <v>130897500000</v>
       </c>
       <c r="AI17" s="22">
-        <v>169637675920</v>
+        <v>157448504840</v>
       </c>
       <c r="AJ17" s="22">
-        <v>38740175920</v>
+        <v>26551004840</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -2654,108 +2666,108 @@
         <v>32</v>
       </c>
       <c r="D18">
-        <v>130.74574834221809</v>
+        <v>126.3531556312613</v>
       </c>
       <c r="E18">
-        <v>37866</v>
+        <v>37851</v>
       </c>
       <c r="F18">
-        <v>3170</v>
+        <v>3097</v>
       </c>
       <c r="G18">
-        <v>128.45019920318731</v>
+        <v>128.83266932270919</v>
       </c>
       <c r="H18">
-        <v>11.856573705179279</v>
-      </c>
-      <c r="I18">
-        <v>11.856573705179279</v>
+        <v>11.474103585657369</v>
+      </c>
+      <c r="I18" s="30">
+        <v>11.474103585657369</v>
       </c>
       <c r="J18">
-        <v>10.366533864541831</v>
+        <v>10.33067729083665</v>
       </c>
       <c r="K18">
-        <v>0.76494023904382469</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0.76494023904382469</v>
+        <v>0.8605577689243028</v>
+      </c>
+      <c r="L18" s="30">
+        <v>0.8605577689243028</v>
       </c>
       <c r="M18">
-        <v>0.17928286852589639</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="N18">
-        <v>7.9681274900398405E-3</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="O18">
-        <v>0.18725099601593631</v>
+        <v>0.1633466135458167</v>
       </c>
       <c r="P18">
-        <v>128.10756972111551</v>
+        <v>128.41035856573711</v>
       </c>
       <c r="Q18" t="s">
-        <v>55</v>
-      </c>
-      <c r="R18" s="28">
-        <v>32.669322709163353</v>
+        <v>51</v>
+      </c>
+      <c r="R18" s="7">
+        <v>31.075697211155379</v>
       </c>
       <c r="S18" t="s">
-        <v>61</v>
-      </c>
-      <c r="T18">
-        <v>57.768924302788847</v>
+        <v>62</v>
+      </c>
+      <c r="T18" s="30">
+        <v>57.370517928286858</v>
       </c>
       <c r="U18" t="s">
-        <v>38</v>
-      </c>
-      <c r="V18">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="V18" s="7">
+        <v>92</v>
       </c>
       <c r="W18" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="X18">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Y18">
-        <v>32241</v>
+        <v>32337</v>
       </c>
       <c r="Z18">
-        <v>2976</v>
+        <v>2880</v>
       </c>
       <c r="AA18">
         <v>35217</v>
       </c>
       <c r="AB18">
-        <v>2222</v>
+        <v>2213</v>
       </c>
       <c r="AC18">
-        <v>192</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>2602</v>
+        <v>216</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>2593</v>
       </c>
       <c r="AE18">
-        <v>45</v>
-      </c>
-      <c r="AF18">
-        <v>2</v>
-      </c>
-      <c r="AG18" s="8">
-        <v>47</v>
-      </c>
-      <c r="AH18" s="22">
+        <v>40</v>
+      </c>
+      <c r="AF18" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="30">
+        <v>41</v>
+      </c>
+      <c r="AH18" s="21">
         <v>131421090000</v>
       </c>
       <c r="AI18" s="22">
-        <v>171827487600</v>
+        <v>166054694380</v>
       </c>
       <c r="AJ18" s="22">
-        <v>40406397600</v>
+        <v>34633604380</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -2763,62 +2775,62 @@
       <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="8">
-        <v>133.6345966693778</v>
+      <c r="D19" s="30">
+        <v>130.4308670396814</v>
       </c>
       <c r="E19">
-        <v>37866</v>
+        <v>37861</v>
       </c>
       <c r="F19">
-        <v>3078</v>
+        <v>3052</v>
       </c>
       <c r="G19">
-        <v>128.82071713147411</v>
+        <v>128.97211155378491</v>
       </c>
       <c r="H19">
-        <v>11.48605577689243</v>
-      </c>
-      <c r="I19">
-        <v>11.48605577689243</v>
+        <v>11.314741035856571</v>
+      </c>
+      <c r="I19" s="30">
+        <v>11.314741035856571</v>
       </c>
       <c r="J19">
-        <v>10.366533864541831</v>
+        <v>10.37450199203187</v>
       </c>
       <c r="K19">
-        <v>0.75697211155378485</v>
+        <v>0.8366533864541833</v>
       </c>
       <c r="L19" s="9">
-        <v>0.75697211155378485</v>
+        <v>0.8366533864541833</v>
       </c>
       <c r="M19">
-        <v>0.16733067729083659</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="N19">
-        <v>1.9920318725099601E-2</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="O19">
-        <v>0.18725099601593631</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="P19">
-        <v>128.50597609561751</v>
+        <v>128.58964143426289</v>
       </c>
       <c r="Q19" t="s">
-        <v>46</v>
-      </c>
-      <c r="R19" s="28">
-        <v>34.661354581673308</v>
+        <v>64</v>
+      </c>
+      <c r="R19" s="30">
+        <v>34.262948207171313</v>
       </c>
       <c r="S19" t="s">
-        <v>57</v>
-      </c>
-      <c r="T19">
-        <v>58.167330677290842</v>
+        <v>65</v>
+      </c>
+      <c r="T19" s="30">
+        <v>54.183266932270911</v>
       </c>
       <c r="U19" t="s">
-        <v>38</v>
-      </c>
-      <c r="V19">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="V19" s="7">
+        <v>92</v>
       </c>
       <c r="W19" t="s">
         <v>38</v>
@@ -2827,45 +2839,45 @@
         <v>88</v>
       </c>
       <c r="Y19">
-        <v>32334</v>
+        <v>32372</v>
       </c>
       <c r="Z19">
-        <v>2883</v>
+        <v>2840</v>
       </c>
       <c r="AA19">
-        <v>35217</v>
+        <v>35212</v>
       </c>
       <c r="AB19">
-        <v>2224</v>
+        <v>2214</v>
       </c>
       <c r="AC19">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AD19" s="9">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="AE19">
-        <v>42</v>
-      </c>
-      <c r="AF19" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG19" s="8">
-        <v>47</v>
+        <v>43</v>
+      </c>
+      <c r="AF19" s="30">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="30">
+        <v>45</v>
       </c>
       <c r="AH19" s="22">
         <v>131421090000</v>
       </c>
       <c r="AI19" s="22">
-        <v>175624043560</v>
+        <v>171413667160</v>
       </c>
       <c r="AJ19" s="22">
-        <v>44202953560</v>
+        <v>39992577160</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -2873,109 +2885,109 @@
       <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="14">
-        <v>141.49346514639319</v>
+      <c r="D20" s="30">
+        <v>129.6847290187595</v>
       </c>
       <c r="E20">
-        <v>37711</v>
+        <v>37873</v>
       </c>
       <c r="F20">
-        <v>3145</v>
+        <v>3075</v>
       </c>
       <c r="G20">
-        <v>128.16733067729081</v>
-      </c>
-      <c r="H20">
-        <v>11.569721115537851</v>
-      </c>
-      <c r="I20">
-        <v>11.569721115537851</v>
+        <v>128.85258964143429</v>
+      </c>
+      <c r="H20" s="7">
+        <v>11.466135458167329</v>
+      </c>
+      <c r="I20" s="30">
+        <v>11.466135458167329</v>
       </c>
       <c r="J20">
-        <v>10.322709163346611</v>
-      </c>
-      <c r="K20" s="14">
-        <v>0.92828685258964139</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0.92828685258964139</v>
+        <v>10.38247011952191</v>
+      </c>
+      <c r="K20" s="30">
+        <v>0.78087649402390436</v>
+      </c>
+      <c r="L20" s="14">
+        <v>0.78087649402390436</v>
       </c>
       <c r="M20">
-        <v>0.151394422310757</v>
-      </c>
-      <c r="N20">
-        <v>3.1872509960159362E-2</v>
-      </c>
-      <c r="O20">
         <v>0.18326693227091631</v>
       </c>
+      <c r="N20" s="30">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="O20" s="30">
+        <v>0.18725099601593631</v>
+      </c>
       <c r="P20">
-        <v>127.6573705179283</v>
+        <v>128.4980079681275</v>
       </c>
       <c r="Q20" t="s">
-        <v>58</v>
-      </c>
-      <c r="R20" s="14">
-        <v>25.099601593625501</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="30">
+        <v>33.466135458167329</v>
       </c>
       <c r="S20" t="s">
-        <v>59</v>
-      </c>
-      <c r="T20" s="8">
-        <v>60.159362549800797</v>
+        <v>37</v>
+      </c>
+      <c r="T20" s="30">
+        <v>54.581673306772913</v>
       </c>
       <c r="U20" t="s">
-        <v>41</v>
-      </c>
-      <c r="V20">
-        <v>92</v>
+        <v>35</v>
+      </c>
+      <c r="V20" s="17">
+        <v>100</v>
       </c>
       <c r="W20" t="s">
-        <v>41</v>
-      </c>
-      <c r="X20" s="9">
-        <v>92</v>
+        <v>38</v>
+      </c>
+      <c r="X20" s="30">
+        <v>88</v>
       </c>
       <c r="Y20">
-        <v>32170</v>
+        <v>32342</v>
       </c>
       <c r="Z20">
-        <v>2904</v>
+        <v>2878</v>
       </c>
       <c r="AA20">
-        <v>35074</v>
+        <v>35220</v>
       </c>
       <c r="AB20">
-        <v>2174</v>
+        <v>2222</v>
       </c>
       <c r="AC20">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="AD20" s="9">
-        <v>2591</v>
+        <v>2606</v>
       </c>
       <c r="AE20">
-        <v>38</v>
-      </c>
-      <c r="AF20" s="15">
-        <v>8</v>
+        <v>46</v>
+      </c>
+      <c r="AF20" s="30">
+        <v>1</v>
       </c>
       <c r="AG20" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH20" s="21">
-        <v>130897500000</v>
+        <v>131421090000</v>
       </c>
       <c r="AI20" s="22">
-        <v>185211408540</v>
+        <v>170433084440</v>
       </c>
       <c r="AJ20" s="22">
-        <v>54313908540</v>
+        <v>39011994440</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -2983,109 +2995,109 @@
       <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="D21">
-        <v>130.06316246611951</v>
+      <c r="D21" s="30">
+        <v>127.5959830800369</v>
       </c>
       <c r="E21">
-        <v>37774</v>
+        <v>37874</v>
       </c>
       <c r="F21">
-        <v>3097</v>
+        <v>3086</v>
       </c>
       <c r="G21">
-        <v>128.50996015936249</v>
+        <v>128.796812749004</v>
       </c>
       <c r="H21">
-        <v>11.51394422310757</v>
-      </c>
-      <c r="I21" s="14">
-        <v>11.51394422310757</v>
+        <v>11.55776892430279</v>
+      </c>
+      <c r="I21" s="7">
+        <v>11.55776892430279</v>
       </c>
       <c r="J21">
-        <v>10.28685258964143</v>
+        <v>10.358565737051791</v>
       </c>
       <c r="K21">
-        <v>0.82071713147410363</v>
-      </c>
-      <c r="L21">
-        <v>0.82071713147410363</v>
+        <v>0.72908366533864544</v>
+      </c>
+      <c r="L21" s="30">
+        <v>0.72908366533864544</v>
       </c>
       <c r="M21">
+        <v>0.17131474103585659</v>
+      </c>
+      <c r="N21">
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="O21" s="30">
         <v>0.17928286852589639</v>
       </c>
-      <c r="N21">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O21">
-        <v>0.18326693227091631</v>
-      </c>
       <c r="P21">
-        <v>127.9322709163347</v>
+        <v>128.45418326693229</v>
       </c>
       <c r="Q21" t="s">
-        <v>39</v>
-      </c>
-      <c r="R21">
-        <v>32.270916334661351</v>
+        <v>46</v>
+      </c>
+      <c r="R21" s="30">
+        <v>34.661354581673308</v>
       </c>
       <c r="S21" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="T21">
-        <v>57.768924302788847</v>
+        <v>51.792828685258961</v>
       </c>
       <c r="U21" t="s">
-        <v>41</v>
-      </c>
-      <c r="V21">
-        <v>92</v>
+        <v>36</v>
+      </c>
+      <c r="V21" s="41">
+        <v>96</v>
       </c>
       <c r="W21" t="s">
-        <v>41</v>
-      </c>
-      <c r="X21" s="9">
-        <v>92</v>
+        <v>48</v>
+      </c>
+      <c r="X21" s="30">
+        <v>76</v>
       </c>
       <c r="Y21">
-        <v>32256</v>
+        <v>32328</v>
       </c>
       <c r="Z21">
-        <v>2890</v>
+        <v>2901</v>
       </c>
       <c r="AA21">
-        <v>35146</v>
+        <v>35229</v>
       </c>
       <c r="AB21">
-        <v>2192</v>
+        <v>2237</v>
       </c>
       <c r="AC21">
-        <v>206</v>
-      </c>
-      <c r="AD21" s="7">
-        <v>2582</v>
+        <v>183</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>2600</v>
       </c>
       <c r="AE21">
+        <v>43</v>
+      </c>
+      <c r="AF21" s="30">
+        <v>2</v>
+      </c>
+      <c r="AG21" s="30">
         <v>45</v>
       </c>
-      <c r="AF21">
-        <v>1</v>
-      </c>
-      <c r="AG21">
-        <v>46</v>
-      </c>
-      <c r="AH21" s="22">
-        <v>130975000000</v>
+      <c r="AH21" s="21">
+        <v>131421090000</v>
       </c>
       <c r="AI21" s="22">
-        <v>170350227040</v>
+        <v>167688031760</v>
       </c>
       <c r="AJ21" s="22">
-        <v>39375227040</v>
+        <v>36266941760</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -3093,109 +3105,109 @@
       <c r="C22" t="s">
         <v>32</v>
       </c>
-      <c r="D22">
-        <v>127.5959830800369</v>
+      <c r="D22" s="30">
+        <v>127.1886216467083</v>
       </c>
       <c r="E22">
-        <v>37874</v>
+        <v>37677</v>
       </c>
       <c r="F22">
-        <v>3086</v>
+        <v>3072</v>
       </c>
       <c r="G22">
-        <v>128.796812749004</v>
-      </c>
-      <c r="H22">
-        <v>11.55776892430279</v>
-      </c>
-      <c r="I22" s="7">
-        <v>11.55776892430279</v>
+        <v>128.191235059761</v>
+      </c>
+      <c r="H22" s="9">
+        <v>11.40637450199203</v>
+      </c>
+      <c r="I22" s="30">
+        <v>11.40637450199203</v>
       </c>
       <c r="J22">
-        <v>10.358565737051791</v>
+        <v>10.35458167330677</v>
       </c>
       <c r="K22">
-        <v>0.72908366533864544</v>
-      </c>
-      <c r="L22">
-        <v>0.72908366533864544</v>
+        <v>0.81673306772908372</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0.81673306772908372</v>
       </c>
       <c r="M22">
-        <v>0.17131474103585659</v>
+        <v>0.1394422310756972</v>
       </c>
       <c r="N22">
-        <v>7.9681274900398405E-3</v>
-      </c>
-      <c r="O22">
-        <v>0.17928286852589639</v>
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="O22" s="30">
+        <v>0.15537848605577689</v>
       </c>
       <c r="P22">
-        <v>128.45418326693229</v>
+        <v>127.94820717131471</v>
       </c>
       <c r="Q22" t="s">
-        <v>46</v>
-      </c>
-      <c r="R22">
-        <v>34.661354581673308</v>
+        <v>33</v>
+      </c>
+      <c r="R22" s="30">
+        <v>33.466135458167329</v>
       </c>
       <c r="S22" t="s">
-        <v>47</v>
-      </c>
-      <c r="T22">
-        <v>51.792828685258961</v>
+        <v>73</v>
+      </c>
+      <c r="T22" s="30">
+        <v>52.589641434262937</v>
       </c>
       <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" s="9">
-        <v>96</v>
+        <v>38</v>
+      </c>
+      <c r="V22" s="30">
+        <v>88</v>
       </c>
       <c r="W22" t="s">
-        <v>48</v>
-      </c>
-      <c r="X22">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="X22" s="30">
+        <v>72</v>
       </c>
       <c r="Y22">
-        <v>32328</v>
+        <v>32176</v>
       </c>
       <c r="Z22">
-        <v>2901</v>
+        <v>2863</v>
       </c>
       <c r="AA22">
-        <v>35229</v>
+        <v>35039</v>
       </c>
       <c r="AB22">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="AC22">
-        <v>183</v>
-      </c>
-      <c r="AD22" s="9">
-        <v>2600</v>
+        <v>205</v>
+      </c>
+      <c r="AD22" s="16">
+        <v>2599</v>
       </c>
       <c r="AE22">
-        <v>43</v>
-      </c>
-      <c r="AF22" s="28">
-        <v>2</v>
-      </c>
-      <c r="AG22">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="AF22" s="30">
+        <v>4</v>
+      </c>
+      <c r="AG22" s="30">
+        <v>39</v>
       </c>
       <c r="AH22" s="21">
-        <v>131421090000</v>
+        <v>130897500000</v>
       </c>
       <c r="AI22" s="22">
-        <v>167688031760</v>
+        <v>166486726020</v>
       </c>
       <c r="AJ22" s="22">
-        <v>36266941760</v>
+        <v>35589226020</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -3203,109 +3215,109 @@
       <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="28">
-        <v>133.55055607893681</v>
+      <c r="D23" s="30">
+        <v>127.3087183038887</v>
       </c>
       <c r="E23">
-        <v>37859</v>
+        <v>37854</v>
       </c>
       <c r="F23">
-        <v>3193</v>
+        <v>3155</v>
       </c>
       <c r="G23">
-        <v>128.40239043824701</v>
-      </c>
-      <c r="H23">
-        <v>11.89641434262948</v>
-      </c>
-      <c r="I23">
-        <v>11.89641434262948</v>
+        <v>128.68127490039839</v>
+      </c>
+      <c r="H23" s="30">
+        <v>11.685258964143429</v>
+      </c>
+      <c r="I23" s="7">
+        <v>11.685258964143429</v>
       </c>
       <c r="J23">
-        <v>10.35458167330677</v>
-      </c>
-      <c r="K23">
-        <v>0.80478087649402386</v>
-      </c>
-      <c r="L23" s="28">
-        <v>0.80478087649402386</v>
+        <v>10.290836653386449</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0.87250996015936255</v>
+      </c>
+      <c r="L23" s="30">
+        <v>0.87250996015936255</v>
       </c>
       <c r="M23">
-        <v>0.15936254980079681</v>
-      </c>
-      <c r="N23">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O23">
-        <v>0.17928286852589639</v>
+        <v>0.14342629482071709</v>
+      </c>
+      <c r="N23" s="30">
+        <v>1.1952191235059761E-2</v>
+      </c>
+      <c r="O23" s="30">
+        <v>0.15537848605577689</v>
       </c>
       <c r="P23">
-        <v>127.99203187251</v>
+        <v>128.17928286852589</v>
       </c>
       <c r="Q23" t="s">
-        <v>55</v>
-      </c>
-      <c r="R23" s="28">
-        <v>32.669322709163353</v>
+        <v>82</v>
+      </c>
+      <c r="R23" s="7">
+        <v>31.872509960159359</v>
       </c>
       <c r="S23" t="s">
-        <v>56</v>
-      </c>
-      <c r="T23" s="28">
-        <v>60.557768924302792</v>
+        <v>49</v>
+      </c>
+      <c r="T23" s="30">
+        <v>55.776892430278878</v>
       </c>
       <c r="U23" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" s="30">
+        <v>84</v>
+      </c>
+      <c r="W23" t="s">
+        <v>74</v>
+      </c>
+      <c r="X23">
+        <v>72</v>
+      </c>
+      <c r="Y23">
+        <v>32299</v>
+      </c>
+      <c r="Z23">
+        <v>2933</v>
+      </c>
+      <c r="AA23">
+        <v>35232</v>
+      </c>
+      <c r="AB23">
+        <v>2208</v>
+      </c>
+      <c r="AC23">
+        <v>219</v>
+      </c>
+      <c r="AD23" s="30">
+        <v>2583</v>
+      </c>
+      <c r="AE23">
         <v>36</v>
       </c>
-      <c r="V23" s="9">
-        <v>96</v>
-      </c>
-      <c r="W23" t="s">
-        <v>45</v>
-      </c>
-      <c r="X23">
-        <v>84</v>
-      </c>
-      <c r="Y23">
-        <v>32229</v>
-      </c>
-      <c r="Z23">
-        <v>2986</v>
-      </c>
-      <c r="AA23">
-        <v>35215</v>
-      </c>
-      <c r="AB23">
-        <v>2217</v>
-      </c>
-      <c r="AC23">
-        <v>202</v>
-      </c>
-      <c r="AD23" s="28">
-        <v>2599</v>
-      </c>
-      <c r="AE23">
-        <v>40</v>
-      </c>
-      <c r="AF23" s="28">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="28">
-        <v>45</v>
-      </c>
-      <c r="AH23" s="23">
+      <c r="AF23" s="30">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="30">
+        <v>39</v>
+      </c>
+      <c r="AH23" s="22">
         <v>131421090000</v>
       </c>
-      <c r="AI23" s="23">
-        <v>175513596500</v>
-      </c>
-      <c r="AJ23" s="23">
-        <v>44092506500</v>
+      <c r="AI23" s="22">
+        <v>167310505260</v>
+      </c>
+      <c r="AJ23" s="22">
+        <v>35889415260</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -3313,109 +3325,109 @@
       <c r="C24" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="28">
-        <v>130.4308670396814</v>
+      <c r="D24" s="30">
+        <v>129.31329262297251</v>
       </c>
       <c r="E24">
-        <v>37861</v>
+        <v>37883</v>
       </c>
       <c r="F24">
-        <v>3052</v>
+        <v>3086</v>
       </c>
       <c r="G24">
-        <v>128.97211155378491</v>
+        <v>128.84860557768931</v>
       </c>
       <c r="H24">
-        <v>11.314741035856571</v>
-      </c>
-      <c r="I24">
-        <v>11.314741035856571</v>
+        <v>11.553784860557769</v>
+      </c>
+      <c r="I24" s="30">
+        <v>11.553784860557769</v>
       </c>
       <c r="J24">
-        <v>10.37450199203187</v>
-      </c>
-      <c r="K24">
-        <v>0.8366533864541833</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0.8366533864541833</v>
-      </c>
-      <c r="M24">
-        <v>0.17131474103585659</v>
+        <v>10.334661354581669</v>
+      </c>
+      <c r="K24" s="30">
+        <v>0.73705179282868527</v>
+      </c>
+      <c r="L24" s="30">
+        <v>0.73705179282868527</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0.18725099601593631</v>
       </c>
       <c r="N24">
-        <v>7.9681274900398405E-3</v>
-      </c>
-      <c r="O24" s="28">
-        <v>0.17928286852589639</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="O24" s="30">
+        <v>0.1912350597609562</v>
       </c>
       <c r="P24">
-        <v>128.58964143426289</v>
+        <v>128.45418326693229</v>
       </c>
       <c r="Q24" t="s">
-        <v>64</v>
-      </c>
-      <c r="R24">
-        <v>34.262948207171313</v>
+        <v>75</v>
+      </c>
+      <c r="R24" s="7">
+        <v>31.474103585657371</v>
       </c>
       <c r="S24" t="s">
-        <v>65</v>
-      </c>
-      <c r="T24">
-        <v>54.183266932270911</v>
+        <v>50</v>
+      </c>
+      <c r="T24" s="30">
+        <v>55.378486055776889</v>
       </c>
       <c r="U24" t="s">
-        <v>41</v>
-      </c>
-      <c r="V24">
-        <v>92</v>
+        <v>38</v>
+      </c>
+      <c r="V24" s="30">
+        <v>88</v>
       </c>
       <c r="W24" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="X24">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="Y24">
-        <v>32372</v>
+        <v>32341</v>
       </c>
       <c r="Z24">
-        <v>2840</v>
+        <v>2900</v>
       </c>
       <c r="AA24">
-        <v>35212</v>
+        <v>35241</v>
       </c>
       <c r="AB24">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="AC24">
-        <v>210</v>
-      </c>
-      <c r="AD24" s="9">
-        <v>2604</v>
+        <v>185</v>
+      </c>
+      <c r="AD24" s="30">
+        <v>2594</v>
       </c>
       <c r="AE24">
-        <v>43</v>
-      </c>
-      <c r="AF24" s="28">
-        <v>2</v>
-      </c>
-      <c r="AG24" s="28">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="AF24" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="7">
+        <v>48</v>
       </c>
       <c r="AH24" s="22">
         <v>131421090000</v>
       </c>
       <c r="AI24" s="22">
-        <v>171413667160</v>
+        <v>169944938680</v>
       </c>
       <c r="AJ24" s="22">
-        <v>39992577160</v>
+        <v>38523848680</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -3423,109 +3435,109 @@
       <c r="C25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="28">
-        <v>132.0141723562329</v>
+      <c r="D25" s="30">
+        <v>129.63107083025031</v>
       </c>
       <c r="E25">
-        <v>37709</v>
+        <v>37906</v>
       </c>
       <c r="F25">
-        <v>3055</v>
+        <v>3196</v>
       </c>
       <c r="G25">
-        <v>128.34661354581669</v>
-      </c>
-      <c r="H25">
-        <v>11.394422310756971</v>
-      </c>
-      <c r="I25">
-        <v>11.394422310756971</v>
+        <v>128.65737051792831</v>
+      </c>
+      <c r="H25" s="30">
+        <v>11.8605577689243</v>
+      </c>
+      <c r="I25" s="30">
+        <v>11.8605577689243</v>
       </c>
       <c r="J25">
-        <v>10.314741035856571</v>
-      </c>
-      <c r="K25">
-        <v>0.75697211155378485</v>
-      </c>
-      <c r="L25" s="28">
-        <v>0.75697211155378485</v>
+        <v>10.32669322709163</v>
+      </c>
+      <c r="K25" s="7">
+        <v>0.86852589641434264</v>
+      </c>
+      <c r="L25" s="30">
+        <v>0.86852589641434264</v>
       </c>
       <c r="M25">
-        <v>0.15936254980079681</v>
+        <v>0.17131474103585659</v>
       </c>
       <c r="N25">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O25" s="28">
-        <v>0.17928286852589639</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="O25" s="30">
+        <v>0.1752988047808765</v>
       </c>
       <c r="P25">
-        <v>128.03187250996021</v>
+        <v>128.09561752988051</v>
       </c>
       <c r="Q25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R25">
-        <v>34.661354581673308</v>
+        <v>60</v>
+      </c>
+      <c r="R25" s="9">
+        <v>29.482071713147409</v>
       </c>
       <c r="S25" t="s">
-        <v>57</v>
-      </c>
-      <c r="T25">
-        <v>58.167330677290842</v>
+        <v>83</v>
+      </c>
+      <c r="T25" s="14">
+        <v>64.541832669322702</v>
       </c>
       <c r="U25" t="s">
-        <v>38</v>
-      </c>
-      <c r="V25">
-        <v>88</v>
+        <v>45</v>
+      </c>
+      <c r="V25" s="30">
+        <v>84</v>
       </c>
       <c r="W25" t="s">
-        <v>38</v>
-      </c>
-      <c r="X25" s="28">
-        <v>88</v>
+        <v>48</v>
+      </c>
+      <c r="X25" s="30">
+        <v>76</v>
       </c>
       <c r="Y25">
-        <v>32215</v>
+        <v>32293</v>
       </c>
       <c r="Z25">
-        <v>2860</v>
+        <v>2977</v>
       </c>
       <c r="AA25">
-        <v>35075</v>
+        <v>35270</v>
       </c>
       <c r="AB25">
-        <v>2219</v>
+        <v>2198</v>
       </c>
       <c r="AC25">
-        <v>190</v>
-      </c>
-      <c r="AD25" s="28">
-        <v>2589</v>
+        <v>218</v>
+      </c>
+      <c r="AD25" s="30">
+        <v>2592</v>
       </c>
       <c r="AE25">
-        <v>40</v>
-      </c>
-      <c r="AF25">
-        <v>5</v>
-      </c>
-      <c r="AG25" s="28">
-        <v>45</v>
-      </c>
-      <c r="AH25" s="23">
-        <v>130897500000</v>
-      </c>
-      <c r="AI25" s="23">
-        <v>172803251260</v>
-      </c>
-      <c r="AJ25" s="23">
-        <v>41905751260</v>
+        <v>43</v>
+      </c>
+      <c r="AF25" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="30">
+        <v>44</v>
+      </c>
+      <c r="AH25" s="22">
+        <v>131498900000</v>
+      </c>
+      <c r="AI25" s="22">
+        <v>170463432200</v>
+      </c>
+      <c r="AJ25" s="22">
+        <v>38964532200</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>16</v>
+      <c r="A26" s="30">
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -3533,50 +3545,50 @@
       <c r="C26" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="8">
-        <v>132.88851661479899</v>
+      <c r="D26" s="30">
+        <v>130.06316246611951</v>
       </c>
       <c r="E26">
-        <v>37865</v>
+        <v>37774</v>
       </c>
       <c r="F26">
-        <v>3199</v>
+        <v>3097</v>
       </c>
       <c r="G26">
-        <v>128.4581673306773</v>
-      </c>
-      <c r="H26">
-        <v>11.908366533864539</v>
-      </c>
-      <c r="I26" s="7">
-        <v>11.908366533864539</v>
+        <v>128.50996015936249</v>
+      </c>
+      <c r="H26" s="30">
+        <v>11.51394422310757</v>
+      </c>
+      <c r="I26" s="14">
+        <v>11.51394422310757</v>
       </c>
       <c r="J26">
-        <v>10.314741035856571</v>
+        <v>10.28685258964143</v>
       </c>
       <c r="K26">
-        <v>0.81673306772908372</v>
-      </c>
-      <c r="L26">
-        <v>0.81673306772908372</v>
-      </c>
-      <c r="M26">
-        <v>0.15537848605577689</v>
+        <v>0.82071713147410363</v>
+      </c>
+      <c r="L26" s="30">
+        <v>0.82071713147410363</v>
+      </c>
+      <c r="M26" s="30">
+        <v>0.17928286852589639</v>
       </c>
       <c r="N26">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O26">
-        <v>0.1752988047808765</v>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="O26" s="30">
+        <v>0.18326693227091631</v>
       </c>
       <c r="P26">
-        <v>128.00398406374501</v>
+        <v>127.9322709163347</v>
       </c>
       <c r="Q26" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="R26">
-        <v>33.466135458167329</v>
+        <v>32.270916334661351</v>
       </c>
       <c r="S26" t="s">
         <v>61</v>
@@ -3585,57 +3597,57 @@
         <v>57.768924302788847</v>
       </c>
       <c r="U26" t="s">
-        <v>38</v>
-      </c>
-      <c r="V26">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="V26" s="7">
+        <v>92</v>
       </c>
       <c r="W26" t="s">
-        <v>38</v>
-      </c>
-      <c r="X26">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="X26" s="9">
+        <v>92</v>
       </c>
       <c r="Y26">
-        <v>32243</v>
+        <v>32256</v>
       </c>
       <c r="Z26">
-        <v>2989</v>
+        <v>2890</v>
       </c>
       <c r="AA26">
-        <v>35232</v>
+        <v>35146</v>
       </c>
       <c r="AB26">
-        <v>2208</v>
+        <v>2192</v>
       </c>
       <c r="AC26">
-        <v>205</v>
-      </c>
-      <c r="AD26">
-        <v>2589</v>
+        <v>206</v>
+      </c>
+      <c r="AD26" s="7">
+        <v>2582</v>
       </c>
       <c r="AE26">
-        <v>39</v>
-      </c>
-      <c r="AF26" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG26">
-        <v>44</v>
-      </c>
-      <c r="AH26" s="21">
-        <v>131421090000</v>
+        <v>45</v>
+      </c>
+      <c r="AF26" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="30">
+        <v>46</v>
+      </c>
+      <c r="AH26" s="22">
+        <v>130975000000</v>
       </c>
       <c r="AI26" s="22">
-        <v>174643537020</v>
+        <v>170350227040</v>
       </c>
       <c r="AJ26" s="22">
-        <v>43222447020</v>
+        <v>39375227040</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -3643,109 +3655,109 @@
       <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="D27">
-        <v>129.63107083025031</v>
+      <c r="D27" s="30">
+        <v>126.8899505319056</v>
       </c>
       <c r="E27">
-        <v>37906</v>
+        <v>37887</v>
       </c>
       <c r="F27">
-        <v>3196</v>
+        <v>3168</v>
       </c>
       <c r="G27">
-        <v>128.65737051792831</v>
-      </c>
-      <c r="H27">
-        <v>11.8605577689243</v>
-      </c>
-      <c r="I27">
-        <v>11.8605577689243</v>
+        <v>128.7250996015936</v>
+      </c>
+      <c r="H27" s="30">
+        <v>11.749003984063741</v>
+      </c>
+      <c r="I27" s="9">
+        <v>11.749003984063741</v>
       </c>
       <c r="J27">
-        <v>10.32669322709163</v>
-      </c>
-      <c r="K27" s="7">
-        <v>0.86852589641434264</v>
-      </c>
-      <c r="L27">
-        <v>0.86852589641434264</v>
+        <v>10.31075697211155</v>
+      </c>
+      <c r="K27" s="30">
+        <v>0.86454183266932272</v>
+      </c>
+      <c r="L27" s="30">
+        <v>0.86454183266932272</v>
       </c>
       <c r="M27">
-        <v>0.17131474103585659</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="N27">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O27">
-        <v>0.1752988047808765</v>
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="O27" s="30">
+        <v>0.15936254980079681</v>
       </c>
       <c r="P27">
-        <v>128.09561752988051</v>
+        <v>128.207171314741</v>
       </c>
       <c r="Q27" t="s">
-        <v>60</v>
-      </c>
-      <c r="R27" s="9">
-        <v>29.482071713147409</v>
+        <v>39</v>
+      </c>
+      <c r="R27" s="30">
+        <v>32.270916334661351</v>
       </c>
       <c r="S27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T27" s="14">
-        <v>64.541832669322702</v>
+        <v>49</v>
+      </c>
+      <c r="T27" s="30">
+        <v>55.776892430278878</v>
       </c>
       <c r="U27" t="s">
-        <v>45</v>
-      </c>
-      <c r="V27">
-        <v>84</v>
+        <v>36</v>
+      </c>
+      <c r="V27" s="41">
+        <v>96</v>
       </c>
       <c r="W27" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="X27">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="Y27">
-        <v>32293</v>
+        <v>32310</v>
       </c>
       <c r="Z27">
-        <v>2977</v>
+        <v>2949</v>
       </c>
       <c r="AA27">
-        <v>35270</v>
+        <v>35259</v>
       </c>
       <c r="AB27">
-        <v>2198</v>
+        <v>2211</v>
       </c>
       <c r="AC27">
-        <v>218</v>
-      </c>
-      <c r="AD27" s="28">
-        <v>2592</v>
+        <v>217</v>
+      </c>
+      <c r="AD27" s="30">
+        <v>2588</v>
       </c>
       <c r="AE27">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AF27">
-        <v>1</v>
-      </c>
-      <c r="AG27">
-        <v>44</v>
+        <v>2</v>
+      </c>
+      <c r="AG27" s="30">
+        <v>40</v>
       </c>
       <c r="AH27" s="22">
         <v>131498900000</v>
       </c>
       <c r="AI27" s="22">
-        <v>170463432200</v>
+        <v>166858889160</v>
       </c>
       <c r="AJ27" s="22">
-        <v>38964532200</v>
+        <v>35359989160</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -3753,109 +3765,109 @@
       <c r="C28" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="28">
-        <v>130.13855146080439</v>
+      <c r="D28" s="30">
+        <v>125.421670120252</v>
       </c>
       <c r="E28">
-        <v>37850</v>
+        <v>37726</v>
       </c>
       <c r="F28">
-        <v>3140</v>
+        <v>3097</v>
       </c>
       <c r="G28">
-        <v>128.6414342629482</v>
-      </c>
-      <c r="H28">
-        <v>11.66135458167331</v>
-      </c>
-      <c r="I28" s="28">
-        <v>11.66135458167331</v>
+        <v>128.3585657370518</v>
+      </c>
+      <c r="H28" s="30">
+        <v>11.52988047808765</v>
+      </c>
+      <c r="I28" s="7">
+        <v>11.52988047808765</v>
       </c>
       <c r="J28">
-        <v>10.32669322709163</v>
-      </c>
-      <c r="K28">
-        <v>0.83266932270916338</v>
-      </c>
-      <c r="L28">
-        <v>0.83266932270916338</v>
+        <v>10.262948207171309</v>
+      </c>
+      <c r="K28" s="30">
+        <v>0.79282868525896411</v>
+      </c>
+      <c r="L28" s="30">
+        <v>0.79282868525896411</v>
       </c>
       <c r="M28">
-        <v>0.151394422310757</v>
+        <v>0.13545816733067731</v>
       </c>
       <c r="N28">
         <v>1.5936254980079681E-2</v>
       </c>
       <c r="O28">
-        <v>0.16733067729083659</v>
+        <v>0.151394422310757</v>
       </c>
       <c r="P28">
-        <v>128.23904382470121</v>
+        <v>127.92828685258959</v>
       </c>
       <c r="Q28" t="s">
-        <v>60</v>
-      </c>
-      <c r="R28" s="9">
-        <v>29.482071713147409</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="30">
+        <v>34.661354581673308</v>
       </c>
       <c r="S28" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="T28">
-        <v>57.768924302788847</v>
+        <v>55.378486055776889</v>
       </c>
       <c r="U28" t="s">
-        <v>41</v>
-      </c>
-      <c r="V28">
-        <v>92</v>
+        <v>36</v>
+      </c>
+      <c r="V28" s="41">
+        <v>96</v>
       </c>
       <c r="W28" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="X28">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Y28">
-        <v>32289</v>
+        <v>32218</v>
       </c>
       <c r="Z28">
-        <v>2927</v>
+        <v>2894</v>
       </c>
       <c r="AA28">
-        <v>35216</v>
+        <v>35112</v>
       </c>
       <c r="AB28">
-        <v>2215</v>
+        <v>2225</v>
       </c>
       <c r="AC28">
-        <v>209</v>
-      </c>
-      <c r="AD28" s="7">
-        <v>2592</v>
+        <v>199</v>
+      </c>
+      <c r="AD28" s="30">
+        <v>2576</v>
       </c>
       <c r="AE28">
+        <v>34</v>
+      </c>
+      <c r="AF28" s="30">
+        <v>4</v>
+      </c>
+      <c r="AG28" s="30">
         <v>38</v>
       </c>
-      <c r="AF28" s="28">
-        <v>4</v>
-      </c>
-      <c r="AG28">
-        <v>42</v>
-      </c>
-      <c r="AH28" s="21">
-        <v>131421090000</v>
+      <c r="AH28" s="22">
+        <v>130975000000</v>
       </c>
       <c r="AI28" s="22">
-        <v>171029502840</v>
+        <v>164271032440</v>
       </c>
       <c r="AJ28" s="22">
-        <v>39608412840</v>
+        <v>33296032440</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>38</v>
+      <c r="A29" s="30">
+        <v>36</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -3863,109 +3875,109 @@
       <c r="C29" t="s">
         <v>32</v>
       </c>
-      <c r="D29">
-        <v>132.16461892837131</v>
+      <c r="D29" s="7">
+        <v>136.6171490255812</v>
       </c>
       <c r="E29">
-        <v>37880</v>
+        <v>37914</v>
       </c>
       <c r="F29">
-        <v>3196</v>
+        <v>3127</v>
       </c>
       <c r="G29">
-        <v>128.53784860557769</v>
+        <v>128.90438247011949</v>
       </c>
       <c r="H29">
-        <v>11.89243027888446</v>
-      </c>
-      <c r="I29" s="7">
-        <v>11.89243027888446</v>
+        <v>11.613545816733071</v>
+      </c>
+      <c r="I29" s="9">
+        <v>11.613545816733071</v>
       </c>
       <c r="J29">
-        <v>10.31872509960159</v>
+        <v>10.34661354581673</v>
       </c>
       <c r="K29">
-        <v>0.81673306772908372</v>
-      </c>
-      <c r="L29">
-        <v>0.81673306772908372</v>
-      </c>
-      <c r="M29">
-        <v>0.14342629482071709</v>
+        <v>0.82071713147410363</v>
+      </c>
+      <c r="L29" s="30">
+        <v>0.82071713147410363</v>
+      </c>
+      <c r="M29" s="30">
+        <v>0.1633466135458167</v>
       </c>
       <c r="N29">
         <v>2.3904382470119521E-2</v>
       </c>
-      <c r="O29">
-        <v>0.16733067729083659</v>
+      <c r="O29" s="30">
+        <v>0.18725099601593631</v>
       </c>
       <c r="P29">
-        <v>128.09561752988051</v>
+        <v>128.37051792828689</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29">
-        <v>33.466135458167329</v>
+        <v>39</v>
+      </c>
+      <c r="R29" s="30">
+        <v>32.270916334661351</v>
       </c>
       <c r="S29" t="s">
-        <v>57</v>
-      </c>
-      <c r="T29">
-        <v>58.167330677290842</v>
+        <v>40</v>
+      </c>
+      <c r="T29" s="7">
+        <v>59.760956175298809</v>
       </c>
       <c r="U29" t="s">
+        <v>35</v>
+      </c>
+      <c r="V29" s="17">
+        <v>100</v>
+      </c>
+      <c r="W29" t="s">
         <v>41</v>
       </c>
-      <c r="V29">
+      <c r="X29" s="9">
         <v>92</v>
       </c>
-      <c r="W29" t="s">
-        <v>45</v>
-      </c>
-      <c r="X29">
-        <v>84</v>
-      </c>
       <c r="Y29">
-        <v>32263</v>
+        <v>32355</v>
       </c>
       <c r="Z29">
-        <v>2985</v>
+        <v>2915</v>
       </c>
       <c r="AA29">
-        <v>35248</v>
+        <v>35270</v>
       </c>
       <c r="AB29">
-        <v>2217</v>
+        <v>2203</v>
       </c>
       <c r="AC29">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AD29" s="7">
-        <v>2590</v>
+        <v>2597</v>
       </c>
       <c r="AE29">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AF29" s="9">
         <v>6</v>
       </c>
-      <c r="AG29">
-        <v>42</v>
+      <c r="AG29" s="8">
+        <v>47</v>
       </c>
       <c r="AH29" s="22">
         <v>131498900000</v>
       </c>
       <c r="AI29" s="22">
-        <v>173795020080</v>
-      </c>
-      <c r="AJ29" s="22">
-        <v>42296120080</v>
+        <v>179650048180</v>
+      </c>
+      <c r="AJ29" s="39">
+        <v>48151148180</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -3973,109 +3985,109 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
-      <c r="D30">
-        <v>126.3531556312613</v>
+      <c r="D30" s="30">
+        <v>127.35500223956249</v>
       </c>
       <c r="E30">
-        <v>37851</v>
+        <v>37858</v>
       </c>
       <c r="F30">
-        <v>3097</v>
+        <v>3165</v>
       </c>
       <c r="G30">
-        <v>128.83266932270919</v>
+        <v>128.58964143426289</v>
       </c>
       <c r="H30">
-        <v>11.474103585657369</v>
-      </c>
-      <c r="I30">
-        <v>11.474103585657369</v>
+        <v>11.768924302788839</v>
+      </c>
+      <c r="I30" s="7">
+        <v>11.768924302788839</v>
       </c>
       <c r="J30">
-        <v>10.33067729083665</v>
-      </c>
-      <c r="K30">
-        <v>0.8605577689243028</v>
-      </c>
-      <c r="L30">
-        <v>0.8605577689243028</v>
+        <v>10.31872509960159</v>
+      </c>
+      <c r="K30" s="30">
+        <v>0.82071713147410363</v>
+      </c>
+      <c r="L30" s="30">
+        <v>0.82071713147410363</v>
       </c>
       <c r="M30">
-        <v>0.15936254980079681</v>
+        <v>0.13147410358565739</v>
       </c>
       <c r="N30">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O30">
-        <v>0.1633466135458167</v>
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="O30" s="30">
+        <v>0.151394422310757</v>
       </c>
       <c r="P30">
-        <v>128.41035856573711</v>
+        <v>128.21912350597611</v>
       </c>
       <c r="Q30" t="s">
-        <v>51</v>
-      </c>
-      <c r="R30" s="7">
-        <v>31.075697211155379</v>
+        <v>84</v>
+      </c>
+      <c r="R30" s="30">
+        <v>35.458167330677291</v>
       </c>
       <c r="S30" t="s">
-        <v>62</v>
-      </c>
-      <c r="T30">
-        <v>57.370517928286858</v>
+        <v>76</v>
+      </c>
+      <c r="T30" s="30">
+        <v>56.573705179282882</v>
       </c>
       <c r="U30" t="s">
-        <v>41</v>
-      </c>
-      <c r="V30">
-        <v>92</v>
+        <v>45</v>
+      </c>
+      <c r="V30" s="30">
+        <v>84</v>
       </c>
       <c r="W30" t="s">
-        <v>63</v>
-      </c>
-      <c r="X30">
-        <v>80</v>
+        <v>48</v>
+      </c>
+      <c r="X30" s="30">
+        <v>76</v>
       </c>
       <c r="Y30">
-        <v>32337</v>
+        <v>32276</v>
       </c>
       <c r="Z30">
-        <v>2880</v>
+        <v>2954</v>
       </c>
       <c r="AA30">
-        <v>35217</v>
+        <v>35230</v>
       </c>
       <c r="AB30">
-        <v>2213</v>
+        <v>2232</v>
       </c>
       <c r="AC30">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="AD30" s="7">
-        <v>2593</v>
+        <v>2590</v>
       </c>
       <c r="AE30">
-        <v>40</v>
-      </c>
-      <c r="AF30">
-        <v>1</v>
-      </c>
-      <c r="AG30">
-        <v>41</v>
-      </c>
-      <c r="AH30" s="21">
-        <v>131421090000</v>
+        <v>33</v>
+      </c>
+      <c r="AF30" s="7">
+        <v>5</v>
+      </c>
+      <c r="AG30" s="30">
+        <v>38</v>
+      </c>
+      <c r="AH30" s="22">
+        <v>131498900000</v>
       </c>
       <c r="AI30" s="22">
-        <v>166054694380</v>
+        <v>167470427040</v>
       </c>
       <c r="AJ30" s="22">
-        <v>34633604380</v>
+        <v>35971527040</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4084,61 +4096,61 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <v>129.96682088087991</v>
+        <v>132.16461892837131</v>
       </c>
       <c r="E31">
-        <v>37833</v>
+        <v>37880</v>
       </c>
       <c r="F31">
-        <v>3076</v>
+        <v>3196</v>
       </c>
       <c r="G31">
-        <v>128.8167330677291</v>
-      </c>
-      <c r="H31" s="28">
-        <v>11.37450199203187</v>
-      </c>
-      <c r="I31">
-        <v>11.37450199203187</v>
+        <v>128.53784860557769</v>
+      </c>
+      <c r="H31" s="30">
+        <v>11.89243027888446</v>
+      </c>
+      <c r="I31" s="7">
+        <v>11.89243027888446</v>
       </c>
       <c r="J31">
-        <v>10.37450199203187</v>
-      </c>
-      <c r="K31">
-        <v>0.86454183266932272</v>
-      </c>
-      <c r="L31" s="28">
-        <v>0.86454183266932272</v>
+        <v>10.31872509960159</v>
+      </c>
+      <c r="K31" s="30">
+        <v>0.81673306772908372</v>
+      </c>
+      <c r="L31" s="30">
+        <v>0.81673306772908372</v>
       </c>
       <c r="M31">
-        <v>0.14741035856573709</v>
+        <v>0.14342629482071709</v>
       </c>
       <c r="N31">
-        <v>1.5936254980079681E-2</v>
+        <v>2.3904382470119521E-2</v>
       </c>
       <c r="O31">
-        <v>0.1633466135458167</v>
+        <v>0.16733067729083659</v>
       </c>
       <c r="P31">
-        <v>128.49402390438249</v>
+        <v>128.09561752988051</v>
       </c>
       <c r="Q31" t="s">
-        <v>39</v>
-      </c>
-      <c r="R31">
-        <v>32.270916334661351</v>
+        <v>33</v>
+      </c>
+      <c r="R31" s="30">
+        <v>33.466135458167329</v>
       </c>
       <c r="S31" t="s">
         <v>57</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="7">
         <v>58.167330677290842</v>
       </c>
       <c r="U31" t="s">
-        <v>38</v>
-      </c>
-      <c r="V31">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="V31" s="7">
+        <v>92</v>
       </c>
       <c r="W31" t="s">
         <v>45</v>
@@ -4147,45 +4159,45 @@
         <v>84</v>
       </c>
       <c r="Y31">
-        <v>32333</v>
+        <v>32263</v>
       </c>
       <c r="Z31">
-        <v>2855</v>
+        <v>2985</v>
       </c>
       <c r="AA31">
-        <v>35188</v>
+        <v>35248</v>
       </c>
       <c r="AB31">
-        <v>2223</v>
+        <v>2217</v>
       </c>
       <c r="AC31">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="AD31" s="7">
-        <v>2604</v>
+        <v>2590</v>
       </c>
       <c r="AE31">
-        <v>37</v>
-      </c>
-      <c r="AF31">
-        <v>4</v>
-      </c>
-      <c r="AG31">
-        <v>41</v>
-      </c>
-      <c r="AH31" s="21">
-        <v>131421090000</v>
+        <v>36</v>
+      </c>
+      <c r="AF31" s="9">
+        <v>6</v>
+      </c>
+      <c r="AG31" s="30">
+        <v>42</v>
+      </c>
+      <c r="AH31" s="22">
+        <v>131498900000</v>
       </c>
       <c r="AI31" s="22">
-        <v>170803812640</v>
-      </c>
-      <c r="AJ31" s="22">
-        <v>39382722640</v>
+        <v>173795020080</v>
+      </c>
+      <c r="AJ31" s="39">
+        <v>42296120080</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -4193,109 +4205,109 @@
       <c r="C32" t="s">
         <v>32</v>
       </c>
-      <c r="D32">
-        <v>126.8899505319056</v>
+      <c r="D32" s="30">
+        <v>122.7668023534798</v>
       </c>
       <c r="E32">
-        <v>37887</v>
+        <v>37872</v>
       </c>
       <c r="F32">
-        <v>3168</v>
+        <v>3231</v>
       </c>
       <c r="G32">
-        <v>128.7250996015936</v>
+        <v>128.36254980079681</v>
       </c>
       <c r="H32">
-        <v>11.749003984063741</v>
-      </c>
-      <c r="I32" s="9">
-        <v>11.749003984063741</v>
+        <v>12.055776892430281</v>
+      </c>
+      <c r="I32" s="7">
+        <v>12.055776892430281</v>
       </c>
       <c r="J32">
-        <v>10.31075697211155</v>
-      </c>
-      <c r="K32">
-        <v>0.86454183266932272</v>
-      </c>
-      <c r="L32">
-        <v>0.86454183266932272</v>
-      </c>
-      <c r="M32" s="28">
+        <v>10.314741035856571</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0.8127490039840638</v>
+      </c>
+      <c r="L32" s="30">
+        <v>0.8127490039840638</v>
+      </c>
+      <c r="M32" s="30">
+        <v>0.14741035856573709</v>
+      </c>
+      <c r="N32">
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="O32" s="30">
         <v>0.151394422310757</v>
       </c>
-      <c r="N32">
-        <v>7.9681274900398405E-3</v>
-      </c>
-      <c r="O32">
-        <v>0.15936254980079681</v>
-      </c>
       <c r="P32">
-        <v>128.207171314741</v>
+        <v>127.95617529880479</v>
       </c>
       <c r="Q32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R32" s="28">
-        <v>32.270916334661351</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="30">
+        <v>33.466135458167329</v>
       </c>
       <c r="S32" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="T32">
-        <v>55.776892430278878</v>
+        <v>56.573705179282882</v>
       </c>
       <c r="U32" t="s">
-        <v>36</v>
-      </c>
-      <c r="V32" s="9">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="V32" s="30">
+        <v>76</v>
       </c>
       <c r="W32" t="s">
+        <v>72</v>
+      </c>
+      <c r="X32" s="30">
+        <v>68</v>
+      </c>
+      <c r="Y32">
+        <v>32219</v>
+      </c>
+      <c r="Z32">
+        <v>3026</v>
+      </c>
+      <c r="AA32">
+        <v>35245</v>
+      </c>
+      <c r="AB32">
+        <v>2233</v>
+      </c>
+      <c r="AC32">
+        <v>204</v>
+      </c>
+      <c r="AD32" s="30">
+        <v>2589</v>
+      </c>
+      <c r="AE32">
+        <v>37</v>
+      </c>
+      <c r="AF32" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="30">
         <v>38</v>
-      </c>
-      <c r="X32">
-        <v>88</v>
-      </c>
-      <c r="Y32">
-        <v>32310</v>
-      </c>
-      <c r="Z32">
-        <v>2949</v>
-      </c>
-      <c r="AA32">
-        <v>35259</v>
-      </c>
-      <c r="AB32">
-        <v>2211</v>
-      </c>
-      <c r="AC32">
-        <v>217</v>
-      </c>
-      <c r="AD32">
-        <v>2588</v>
-      </c>
-      <c r="AE32">
-        <v>38</v>
-      </c>
-      <c r="AF32">
-        <v>2</v>
-      </c>
-      <c r="AG32" s="28">
-        <v>40</v>
       </c>
       <c r="AH32" s="22">
         <v>131498900000</v>
       </c>
       <c r="AI32" s="22">
-        <v>166858889160</v>
+        <v>161436994660</v>
       </c>
       <c r="AJ32" s="22">
-        <v>35359989160</v>
+        <v>29938094660</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -4304,108 +4316,108 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>128.50677761080809</v>
+        <v>129.59581040126821</v>
       </c>
       <c r="E33">
-        <v>37875</v>
+        <v>37716</v>
       </c>
       <c r="F33">
-        <v>3191</v>
+        <v>2933</v>
       </c>
       <c r="G33">
-        <v>128.601593625498</v>
+        <v>128.8565737051793</v>
       </c>
       <c r="H33">
-        <v>11.8605577689243</v>
-      </c>
-      <c r="I33" s="9">
-        <v>11.8605577689243</v>
+        <v>10.89243027888446</v>
+      </c>
+      <c r="I33" s="30">
+        <v>10.89243027888446</v>
       </c>
       <c r="J33">
-        <v>10.27490039840638</v>
-      </c>
-      <c r="K33" s="28">
-        <v>0.8366533864541833</v>
-      </c>
-      <c r="L33" s="28">
-        <v>0.8366533864541833</v>
-      </c>
-      <c r="M33">
-        <v>0.14342629482071709</v>
+        <v>10.32669322709163</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0.78884462151394419</v>
+      </c>
+      <c r="L33" s="9">
+        <v>0.78884462151394419</v>
+      </c>
+      <c r="M33" s="30">
+        <v>0.18326693227091631</v>
       </c>
       <c r="N33">
-        <v>1.5936254980079681E-2</v>
+        <v>3.9840637450199202E-3</v>
       </c>
       <c r="O33">
-        <v>0.15936254980079681</v>
+        <v>0.18725099601593631</v>
       </c>
       <c r="P33">
-        <v>128.03585657370519</v>
+        <v>128.53386454183271</v>
       </c>
       <c r="Q33" t="s">
-        <v>70</v>
-      </c>
-      <c r="R33" s="28">
-        <v>35.059760956175303</v>
+        <v>51</v>
+      </c>
+      <c r="R33" s="7">
+        <v>31.075697211155379</v>
       </c>
       <c r="S33" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="T33">
-        <v>57.768924302788847</v>
+        <v>56.573705179282882</v>
       </c>
       <c r="U33" t="s">
         <v>38</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="30">
         <v>88</v>
       </c>
       <c r="W33" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="X33">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="Y33">
-        <v>32279</v>
+        <v>32343</v>
       </c>
       <c r="Z33">
-        <v>2977</v>
+        <v>2734</v>
       </c>
       <c r="AA33">
-        <v>35256</v>
+        <v>35077</v>
       </c>
       <c r="AB33">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="AC33">
-        <v>210</v>
-      </c>
-      <c r="AD33" s="28">
-        <v>2579</v>
+        <v>198</v>
+      </c>
+      <c r="AD33" s="9">
+        <v>2592</v>
       </c>
       <c r="AE33">
-        <v>36</v>
-      </c>
-      <c r="AF33">
-        <v>4</v>
-      </c>
-      <c r="AG33" s="28">
-        <v>40</v>
-      </c>
-      <c r="AH33" s="21">
-        <v>131421090000</v>
+        <v>46</v>
+      </c>
+      <c r="AF33" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="8">
+        <v>47</v>
+      </c>
+      <c r="AH33" s="22">
+        <v>130897500000</v>
       </c>
       <c r="AI33" s="22">
-        <v>168885007860</v>
+        <v>169637675920</v>
       </c>
       <c r="AJ33" s="22">
-        <v>37463917860</v>
+        <v>38740175920</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -4413,109 +4425,109 @@
       <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="D34">
-        <v>127.02495336174739</v>
+      <c r="D34" s="7">
+        <v>135.8033808120143</v>
       </c>
       <c r="E34">
-        <v>37835</v>
+        <v>37866</v>
       </c>
       <c r="F34">
-        <v>3232</v>
+        <v>3131</v>
       </c>
       <c r="G34">
-        <v>128.23904382470121</v>
-      </c>
-      <c r="H34">
-        <v>12.011952191235061</v>
-      </c>
-      <c r="I34">
-        <v>12.011952191235061</v>
+        <v>128.68127490039839</v>
+      </c>
+      <c r="H34" s="30">
+        <v>11.62549800796813</v>
+      </c>
+      <c r="I34" s="30">
+        <v>11.62549800796813</v>
       </c>
       <c r="J34">
-        <v>10.32669322709163</v>
-      </c>
-      <c r="K34">
-        <v>0.85657370517928288</v>
-      </c>
-      <c r="L34" s="28">
-        <v>0.85657370517928288</v>
-      </c>
-      <c r="M34">
-        <v>0.151394422310757</v>
+        <v>10.366533864541831</v>
+      </c>
+      <c r="K34" s="30">
+        <v>0.82868525896414347</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0.82868525896414347</v>
+      </c>
+      <c r="M34" s="30">
+        <v>0.16733067729083659</v>
       </c>
       <c r="N34">
-        <v>7.9681274900398405E-3</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="O34">
-        <v>0.15936254980079681</v>
+        <v>0.18725099601593631</v>
       </c>
       <c r="P34">
-        <v>127.87250996015941</v>
+        <v>128.27091633466139</v>
       </c>
       <c r="Q34" t="s">
-        <v>46</v>
-      </c>
-      <c r="R34">
-        <v>34.661354581673308</v>
+        <v>66</v>
+      </c>
+      <c r="R34" s="37">
+        <v>30.2788844621514</v>
       </c>
       <c r="S34" t="s">
-        <v>62</v>
-      </c>
-      <c r="T34">
-        <v>57.370517928286858</v>
+        <v>67</v>
+      </c>
+      <c r="T34" s="9">
+        <v>63.34661354581673</v>
       </c>
       <c r="U34" t="s">
+        <v>41</v>
+      </c>
+      <c r="V34" s="7">
+        <v>92</v>
+      </c>
+      <c r="W34" t="s">
         <v>38</v>
       </c>
-      <c r="V34">
+      <c r="X34">
         <v>88</v>
       </c>
-      <c r="W34" t="s">
-        <v>63</v>
-      </c>
-      <c r="X34">
-        <v>80</v>
-      </c>
       <c r="Y34">
-        <v>32188</v>
+        <v>32299</v>
       </c>
       <c r="Z34">
-        <v>3015</v>
+        <v>2918</v>
       </c>
       <c r="AA34">
-        <v>35203</v>
+        <v>35217</v>
       </c>
       <c r="AB34">
-        <v>2217</v>
+        <v>2206</v>
       </c>
       <c r="AC34">
-        <v>215</v>
-      </c>
-      <c r="AD34" s="7">
-        <v>2592</v>
+        <v>208</v>
+      </c>
+      <c r="AD34" s="9">
+        <v>2602</v>
       </c>
       <c r="AE34">
-        <v>38</v>
-      </c>
-      <c r="AF34">
-        <v>2</v>
-      </c>
-      <c r="AG34" s="28">
-        <v>40</v>
-      </c>
-      <c r="AH34" s="21">
+        <v>42</v>
+      </c>
+      <c r="AF34" s="7">
+        <v>5</v>
+      </c>
+      <c r="AG34" s="8">
+        <v>47</v>
+      </c>
+      <c r="AH34" s="22">
         <v>131421090000</v>
       </c>
       <c r="AI34" s="22">
-        <v>166937578280</v>
-      </c>
-      <c r="AJ34" s="22">
-        <v>35516488280</v>
+        <v>178474283320</v>
+      </c>
+      <c r="AJ34" s="39">
+        <v>47053193320</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -4523,109 +4535,109 @@
       <c r="C35" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="28">
-        <v>127.1886216467083</v>
+      <c r="D35" s="30">
+        <v>130.74574834221809</v>
       </c>
       <c r="E35">
-        <v>37677</v>
+        <v>37866</v>
       </c>
       <c r="F35">
-        <v>3072</v>
+        <v>3170</v>
       </c>
       <c r="G35">
-        <v>128.191235059761</v>
-      </c>
-      <c r="H35" s="9">
-        <v>11.40637450199203</v>
-      </c>
-      <c r="I35">
-        <v>11.40637450199203</v>
+        <v>128.45019920318731</v>
+      </c>
+      <c r="H35" s="30">
+        <v>11.856573705179279</v>
+      </c>
+      <c r="I35" s="30">
+        <v>11.856573705179279</v>
       </c>
       <c r="J35">
-        <v>10.35458167330677</v>
-      </c>
-      <c r="K35">
-        <v>0.81673306772908372</v>
+        <v>10.366533864541831</v>
+      </c>
+      <c r="K35" s="30">
+        <v>0.76494023904382469</v>
       </c>
       <c r="L35" s="9">
-        <v>0.81673306772908372</v>
+        <v>0.76494023904382469</v>
       </c>
       <c r="M35">
-        <v>0.1394422310756972</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="N35">
-        <v>1.5936254980079681E-2</v>
+        <v>7.9681274900398405E-3</v>
       </c>
       <c r="O35">
-        <v>0.15537848605577689</v>
+        <v>0.18725099601593631</v>
       </c>
       <c r="P35">
-        <v>127.94820717131471</v>
+        <v>128.10756972111551</v>
       </c>
       <c r="Q35" t="s">
-        <v>33</v>
-      </c>
-      <c r="R35">
-        <v>33.466135458167329</v>
+        <v>55</v>
+      </c>
+      <c r="R35" s="30">
+        <v>32.669322709163353</v>
       </c>
       <c r="S35" t="s">
-        <v>73</v>
-      </c>
-      <c r="T35">
-        <v>52.589641434262937</v>
+        <v>61</v>
+      </c>
+      <c r="T35" s="30">
+        <v>57.768924302788847</v>
       </c>
       <c r="U35" t="s">
         <v>38</v>
       </c>
-      <c r="V35">
+      <c r="V35" s="30">
         <v>88</v>
       </c>
       <c r="W35" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="X35">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="Y35">
-        <v>32176</v>
+        <v>32241</v>
       </c>
       <c r="Z35">
-        <v>2863</v>
+        <v>2976</v>
       </c>
       <c r="AA35">
-        <v>35039</v>
+        <v>35217</v>
       </c>
       <c r="AB35">
-        <v>2238</v>
+        <v>2222</v>
       </c>
       <c r="AC35">
-        <v>205</v>
-      </c>
-      <c r="AD35" s="16">
-        <v>2599</v>
+        <v>192</v>
+      </c>
+      <c r="AD35" s="9">
+        <v>2602</v>
       </c>
       <c r="AE35">
-        <v>35</v>
-      </c>
-      <c r="AF35" s="28">
-        <v>4</v>
-      </c>
-      <c r="AG35" s="28">
-        <v>39</v>
-      </c>
-      <c r="AH35" s="21">
-        <v>130897500000</v>
+        <v>45</v>
+      </c>
+      <c r="AF35" s="30">
+        <v>2</v>
+      </c>
+      <c r="AG35" s="8">
+        <v>47</v>
+      </c>
+      <c r="AH35" s="22">
+        <v>131421090000</v>
       </c>
       <c r="AI35" s="22">
-        <v>166486726020</v>
-      </c>
-      <c r="AJ35" s="22">
-        <v>35589226020</v>
+        <v>171827487600</v>
+      </c>
+      <c r="AJ35" s="39">
+        <v>40406397600</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
@@ -4633,109 +4645,109 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="28">
-        <v>122.99666202738079</v>
+      <c r="D36" s="7">
+        <v>136.12890390728001</v>
       </c>
       <c r="E36">
-        <v>37794</v>
+        <v>37866</v>
       </c>
       <c r="F36">
-        <v>3172</v>
+        <v>3212</v>
       </c>
       <c r="G36">
-        <v>128.15139442231069</v>
-      </c>
-      <c r="H36" s="14">
-        <v>11.84860557768924</v>
-      </c>
-      <c r="I36">
-        <v>11.84860557768924</v>
+        <v>128.3585657370518</v>
+      </c>
+      <c r="H36" s="7">
+        <v>11.94820717131474</v>
+      </c>
+      <c r="I36" s="30">
+        <v>11.94820717131474</v>
       </c>
       <c r="J36">
-        <v>10.41832669322709</v>
-      </c>
-      <c r="K36">
-        <v>0.78486055776892427</v>
-      </c>
-      <c r="L36">
-        <v>0.78486055776892427</v>
-      </c>
-      <c r="M36">
-        <v>0.151394422310757</v>
-      </c>
-      <c r="N36">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O36" s="28">
-        <v>0.15537848605577689</v>
+        <v>10.366533864541831</v>
+      </c>
+      <c r="K36" s="30">
+        <v>0.82868525896414347</v>
+      </c>
+      <c r="L36" s="9">
+        <v>0.82868525896414347</v>
+      </c>
+      <c r="M36" s="30">
+        <v>0.16733067729083659</v>
+      </c>
+      <c r="N36" s="14">
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="O36" s="30">
+        <v>0.18725099601593631</v>
       </c>
       <c r="P36">
-        <v>128.11155378486049</v>
+        <v>127.9123505976096</v>
       </c>
       <c r="Q36" t="s">
-        <v>46</v>
-      </c>
-      <c r="R36" s="28">
-        <v>34.661354581673308</v>
+        <v>51</v>
+      </c>
+      <c r="R36" s="7">
+        <v>31.075697211155379</v>
       </c>
       <c r="S36" t="s">
-        <v>61</v>
-      </c>
-      <c r="T36" s="28">
-        <v>57.768924302788847</v>
+        <v>52</v>
+      </c>
+      <c r="T36" s="9">
+        <v>62.948207171314742</v>
       </c>
       <c r="U36" t="s">
+        <v>36</v>
+      </c>
+      <c r="V36" s="41">
+        <v>96</v>
+      </c>
+      <c r="W36" t="s">
         <v>45</v>
       </c>
-      <c r="V36">
+      <c r="X36">
         <v>84</v>
       </c>
-      <c r="W36" t="s">
-        <v>48</v>
-      </c>
-      <c r="X36">
-        <v>76</v>
-      </c>
       <c r="Y36">
-        <v>32166</v>
+        <v>32218</v>
       </c>
       <c r="Z36">
-        <v>2974</v>
+        <v>2999</v>
       </c>
       <c r="AA36">
-        <v>35140</v>
+        <v>35217</v>
       </c>
       <c r="AB36">
-        <v>2262</v>
+        <v>2206</v>
       </c>
       <c r="AC36">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AD36" s="9">
-        <v>2615</v>
+        <v>2602</v>
       </c>
       <c r="AE36">
-        <v>38</v>
-      </c>
-      <c r="AF36">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="28">
-        <v>39</v>
-      </c>
-      <c r="AH36" s="21">
+        <v>42</v>
+      </c>
+      <c r="AF36" s="7">
+        <v>5</v>
+      </c>
+      <c r="AG36" s="8">
+        <v>47</v>
+      </c>
+      <c r="AH36" s="22">
         <v>131421090000</v>
       </c>
       <c r="AI36" s="22">
-        <v>161643553900</v>
-      </c>
-      <c r="AJ36" s="22">
-        <v>30222463900</v>
+        <v>178902089320</v>
+      </c>
+      <c r="AJ36" s="39">
+        <v>47480999320</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -4743,109 +4755,109 @@
       <c r="C37" t="s">
         <v>32</v>
       </c>
-      <c r="D37">
-        <v>127.3087183038887</v>
+      <c r="D37" s="8">
+        <v>133.6345966693778</v>
       </c>
       <c r="E37">
-        <v>37854</v>
+        <v>37866</v>
       </c>
       <c r="F37">
-        <v>3155</v>
+        <v>3078</v>
       </c>
       <c r="G37">
-        <v>128.68127490039839</v>
-      </c>
-      <c r="H37">
-        <v>11.685258964143429</v>
-      </c>
-      <c r="I37" s="7">
-        <v>11.685258964143429</v>
+        <v>128.82071713147411</v>
+      </c>
+      <c r="H37" s="30">
+        <v>11.48605577689243</v>
+      </c>
+      <c r="I37" s="30">
+        <v>11.48605577689243</v>
       </c>
       <c r="J37">
-        <v>10.290836653386449</v>
-      </c>
-      <c r="K37" s="9">
-        <v>0.87250996015936255</v>
-      </c>
-      <c r="L37">
-        <v>0.87250996015936255</v>
+        <v>10.366533864541831</v>
+      </c>
+      <c r="K37" s="30">
+        <v>0.75697211155378485</v>
+      </c>
+      <c r="L37" s="9">
+        <v>0.75697211155378485</v>
       </c>
       <c r="M37">
-        <v>0.14342629482071709</v>
+        <v>0.16733067729083659</v>
       </c>
       <c r="N37">
-        <v>1.1952191235059761E-2</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="O37">
-        <v>0.15537848605577689</v>
+        <v>0.18725099601593631</v>
       </c>
       <c r="P37">
-        <v>128.17928286852589</v>
+        <v>128.50597609561751</v>
       </c>
       <c r="Q37" t="s">
-        <v>82</v>
-      </c>
-      <c r="R37" s="7">
-        <v>31.872509960159359</v>
+        <v>46</v>
+      </c>
+      <c r="R37" s="30">
+        <v>34.661354581673308</v>
       </c>
       <c r="S37" t="s">
-        <v>49</v>
-      </c>
-      <c r="T37">
-        <v>55.776892430278878</v>
+        <v>57</v>
+      </c>
+      <c r="T37" s="7">
+        <v>58.167330677290842</v>
       </c>
       <c r="U37" t="s">
-        <v>45</v>
-      </c>
-      <c r="V37">
-        <v>84</v>
+        <v>38</v>
+      </c>
+      <c r="V37" s="30">
+        <v>88</v>
       </c>
       <c r="W37" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="X37">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="Y37">
-        <v>32299</v>
+        <v>32334</v>
       </c>
       <c r="Z37">
-        <v>2933</v>
+        <v>2883</v>
       </c>
       <c r="AA37">
-        <v>35232</v>
+        <v>35217</v>
       </c>
       <c r="AB37">
-        <v>2208</v>
+        <v>2224</v>
       </c>
       <c r="AC37">
-        <v>219</v>
-      </c>
-      <c r="AD37">
-        <v>2583</v>
+        <v>190</v>
+      </c>
+      <c r="AD37" s="9">
+        <v>2602</v>
       </c>
       <c r="AE37">
-        <v>36</v>
-      </c>
-      <c r="AF37">
-        <v>3</v>
-      </c>
-      <c r="AG37">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="AF37" s="7">
+        <v>5</v>
+      </c>
+      <c r="AG37" s="8">
+        <v>47</v>
       </c>
       <c r="AH37" s="22">
         <v>131421090000</v>
       </c>
       <c r="AI37" s="22">
-        <v>167310505260</v>
-      </c>
-      <c r="AJ37" s="22">
-        <v>35889415260</v>
+        <v>175624043560</v>
+      </c>
+      <c r="AJ37" s="39">
+        <v>44202953560</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>35</v>
+      <c r="A38" s="25">
+        <v>45</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -4853,109 +4865,109 @@
       <c r="C38" t="s">
         <v>32</v>
       </c>
-      <c r="D38">
-        <v>125.421670120252</v>
+      <c r="D38" s="9">
+        <v>139.08244440827571</v>
       </c>
       <c r="E38">
-        <v>37726</v>
+        <v>37897</v>
       </c>
       <c r="F38">
-        <v>3097</v>
+        <v>3160</v>
       </c>
       <c r="G38">
-        <v>128.3585657370518</v>
-      </c>
-      <c r="H38">
-        <v>11.52988047808765</v>
-      </c>
-      <c r="I38" s="7">
-        <v>11.52988047808765</v>
+        <v>128.6733067729084</v>
+      </c>
+      <c r="H38" s="30">
+        <v>11.756972111553781</v>
+      </c>
+      <c r="I38" s="30">
+        <v>11.756972111553781</v>
       </c>
       <c r="J38">
-        <v>10.262948207171309</v>
-      </c>
-      <c r="K38">
-        <v>0.79282868525896411</v>
-      </c>
-      <c r="L38">
-        <v>0.79282868525896411</v>
+        <v>10.350597609561749</v>
+      </c>
+      <c r="K38" s="30">
+        <v>0.8127490039840638</v>
+      </c>
+      <c r="L38" s="9">
+        <v>0.8127490039840638</v>
       </c>
       <c r="M38">
-        <v>0.13545816733067731</v>
+        <v>0.18326693227091631</v>
       </c>
       <c r="N38">
-        <v>1.5936254980079681E-2</v>
-      </c>
-      <c r="O38">
-        <v>0.151394422310757</v>
+        <v>1.9920318725099601E-2</v>
+      </c>
+      <c r="O38" s="16">
+        <v>0.20318725099601601</v>
       </c>
       <c r="P38">
-        <v>127.92828685258959</v>
+        <v>128.15139442231069</v>
       </c>
       <c r="Q38" t="s">
+        <v>42</v>
+      </c>
+      <c r="R38" s="9">
+        <v>29.880478087649401</v>
+      </c>
+      <c r="S38" t="s">
+        <v>40</v>
+      </c>
+      <c r="T38" s="7">
+        <v>59.760956175298809</v>
+      </c>
+      <c r="U38" t="s">
+        <v>35</v>
+      </c>
+      <c r="V38" s="17">
+        <v>100</v>
+      </c>
+      <c r="W38" t="s">
+        <v>41</v>
+      </c>
+      <c r="X38" s="9">
+        <v>92</v>
+      </c>
+      <c r="Y38">
+        <v>32297</v>
+      </c>
+      <c r="Z38">
+        <v>2951</v>
+      </c>
+      <c r="AA38">
+        <v>35248</v>
+      </c>
+      <c r="AB38">
+        <v>2190</v>
+      </c>
+      <c r="AC38">
+        <v>204</v>
+      </c>
+      <c r="AD38" s="7">
+        <v>2598</v>
+      </c>
+      <c r="AE38">
         <v>46</v>
       </c>
-      <c r="R38">
-        <v>34.661354581673308</v>
-      </c>
-      <c r="S38" t="s">
-        <v>50</v>
-      </c>
-      <c r="T38">
-        <v>55.378486055776889</v>
-      </c>
-      <c r="U38" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="9">
-        <v>96</v>
-      </c>
-      <c r="W38" t="s">
-        <v>38</v>
-      </c>
-      <c r="X38">
-        <v>88</v>
-      </c>
-      <c r="Y38">
-        <v>32218</v>
-      </c>
-      <c r="Z38">
-        <v>2894</v>
-      </c>
-      <c r="AA38">
-        <v>35112</v>
-      </c>
-      <c r="AB38">
-        <v>2225</v>
-      </c>
-      <c r="AC38">
-        <v>199</v>
-      </c>
-      <c r="AD38" s="28">
-        <v>2576</v>
-      </c>
-      <c r="AE38">
-        <v>34</v>
-      </c>
-      <c r="AF38">
-        <v>4</v>
-      </c>
-      <c r="AG38">
-        <v>38</v>
+      <c r="AF38" s="30">
+        <v>5</v>
+      </c>
+      <c r="AG38" s="16">
+        <v>51</v>
       </c>
       <c r="AH38" s="22">
-        <v>130975000000</v>
+        <v>131421090000</v>
       </c>
       <c r="AI38" s="22">
-        <v>164271032440</v>
-      </c>
-      <c r="AJ38" s="22">
-        <v>33296032440</v>
+        <v>182783664440</v>
+      </c>
+      <c r="AJ38" s="38">
+        <v>51362574440</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
@@ -4963,109 +4975,109 @@
       <c r="C39" t="s">
         <v>32</v>
       </c>
-      <c r="D39">
-        <v>127.35500223956249</v>
+      <c r="D39" s="9">
+        <v>137.85242265131109</v>
       </c>
       <c r="E39">
-        <v>37858</v>
+        <v>37748</v>
       </c>
       <c r="F39">
-        <v>3165</v>
+        <v>3158</v>
       </c>
       <c r="G39">
-        <v>128.58964143426289</v>
-      </c>
-      <c r="H39">
-        <v>11.768924302788839</v>
-      </c>
-      <c r="I39" s="7">
-        <v>11.768924302788839</v>
+        <v>128.15139442231069</v>
+      </c>
+      <c r="H39" s="30">
+        <v>11.729083665338649</v>
+      </c>
+      <c r="I39" s="30">
+        <v>11.729083665338649</v>
       </c>
       <c r="J39">
-        <v>10.31872509960159</v>
+        <v>10.306772908366529</v>
       </c>
       <c r="K39">
-        <v>0.82071713147410363</v>
-      </c>
-      <c r="L39">
-        <v>0.82071713147410363</v>
+        <v>0.84063745019920322</v>
+      </c>
+      <c r="L39" s="9">
+        <v>0.84063745019920322</v>
       </c>
       <c r="M39">
-        <v>0.13147410358565739</v>
+        <v>0.1912350597609562</v>
       </c>
       <c r="N39">
-        <v>1.9920318725099601E-2</v>
-      </c>
-      <c r="O39">
-        <v>0.151394422310757</v>
+        <v>1.1952191235059761E-2</v>
+      </c>
+      <c r="O39" s="16">
+        <v>0.20318725099601601</v>
       </c>
       <c r="P39">
-        <v>128.21912350597611</v>
+        <v>127.593625498008</v>
       </c>
       <c r="Q39" t="s">
-        <v>84</v>
-      </c>
-      <c r="R39">
-        <v>35.458167330677291</v>
+        <v>43</v>
+      </c>
+      <c r="R39" s="7">
+        <v>30.677290836653391</v>
       </c>
       <c r="S39" t="s">
-        <v>76</v>
-      </c>
-      <c r="T39">
-        <v>56.573705179282882</v>
+        <v>53</v>
+      </c>
+      <c r="T39" s="9">
+        <v>61.752988047808763</v>
       </c>
       <c r="U39" t="s">
-        <v>45</v>
-      </c>
-      <c r="V39">
-        <v>84</v>
+        <v>36</v>
+      </c>
+      <c r="V39" s="41">
+        <v>96</v>
       </c>
       <c r="W39" t="s">
+        <v>36</v>
+      </c>
+      <c r="X39" s="27">
+        <v>96</v>
+      </c>
+      <c r="Y39">
+        <v>32166</v>
+      </c>
+      <c r="Z39">
+        <v>2944</v>
+      </c>
+      <c r="AA39">
+        <v>35110</v>
+      </c>
+      <c r="AB39">
+        <v>2172</v>
+      </c>
+      <c r="AC39">
+        <v>211</v>
+      </c>
+      <c r="AD39" s="7">
+        <v>2587</v>
+      </c>
+      <c r="AE39">
         <v>48</v>
       </c>
-      <c r="X39">
-        <v>76</v>
-      </c>
-      <c r="Y39">
-        <v>32276</v>
-      </c>
-      <c r="Z39">
-        <v>2954</v>
-      </c>
-      <c r="AA39">
-        <v>35230</v>
-      </c>
-      <c r="AB39">
-        <v>2232</v>
-      </c>
-      <c r="AC39">
-        <v>206</v>
-      </c>
-      <c r="AD39" s="7">
-        <v>2590</v>
-      </c>
-      <c r="AE39">
-        <v>33</v>
-      </c>
-      <c r="AF39" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG39">
-        <v>38</v>
+      <c r="AF39" s="30">
+        <v>3</v>
+      </c>
+      <c r="AG39" s="16">
+        <v>51</v>
       </c>
       <c r="AH39" s="22">
-        <v>131498900000</v>
+        <v>130897500000</v>
       </c>
       <c r="AI39" s="22">
-        <v>167470427040</v>
-      </c>
-      <c r="AJ39" s="22">
-        <v>35971527040</v>
+        <v>180445374940</v>
+      </c>
+      <c r="AJ39" s="39">
+        <v>49547874940</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
@@ -5073,109 +5085,109 @@
       <c r="C40" t="s">
         <v>32</v>
       </c>
-      <c r="D40">
-        <v>122.7668023534798</v>
+      <c r="D40" s="9">
+        <v>138.27420137818061</v>
       </c>
       <c r="E40">
-        <v>37872</v>
+        <v>37925</v>
       </c>
       <c r="F40">
-        <v>3231</v>
+        <v>3069</v>
       </c>
       <c r="G40">
-        <v>128.36254980079681</v>
+        <v>129.12749003984061</v>
       </c>
       <c r="H40" s="28">
-        <v>12.055776892430281</v>
-      </c>
-      <c r="I40" s="7">
-        <v>12.055776892430281</v>
+        <v>11.446215139442231</v>
+      </c>
+      <c r="I40" s="30">
+        <v>11.446215139442231</v>
       </c>
       <c r="J40">
-        <v>10.314741035856571</v>
-      </c>
-      <c r="K40" s="10">
-        <v>0.8127490039840638</v>
+        <v>10.31872509960159</v>
+      </c>
+      <c r="K40" s="30">
+        <v>0.75697211155378485</v>
       </c>
       <c r="L40">
-        <v>0.8127490039840638</v>
+        <v>0.75697211155378485</v>
       </c>
       <c r="M40">
-        <v>0.14741035856573709</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="N40">
-        <v>3.9840637450199202E-3</v>
-      </c>
-      <c r="O40">
-        <v>0.151394422310757</v>
+        <v>2.3904382470119521E-2</v>
+      </c>
+      <c r="O40" s="16">
+        <v>0.20318725099601601</v>
       </c>
       <c r="P40">
-        <v>127.95617529880479</v>
+        <v>128.49402390438249</v>
       </c>
       <c r="Q40" t="s">
-        <v>33</v>
-      </c>
-      <c r="R40">
-        <v>33.466135458167329</v>
+        <v>68</v>
+      </c>
+      <c r="R40" s="30">
+        <v>36.254980079681268</v>
       </c>
       <c r="S40" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="T40">
-        <v>56.573705179282882</v>
+        <v>52.988047808764939</v>
       </c>
       <c r="U40" t="s">
-        <v>48</v>
-      </c>
-      <c r="V40">
-        <v>76</v>
+        <v>41</v>
+      </c>
+      <c r="V40" s="7">
+        <v>92</v>
       </c>
       <c r="W40" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="X40">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="Y40">
-        <v>32219</v>
+        <v>32411</v>
       </c>
       <c r="Z40">
-        <v>3026</v>
+        <v>2873</v>
       </c>
       <c r="AA40">
-        <v>35245</v>
+        <v>35284</v>
       </c>
       <c r="AB40">
-        <v>2233</v>
+        <v>2196</v>
       </c>
       <c r="AC40">
-        <v>204</v>
-      </c>
-      <c r="AD40" s="28">
-        <v>2589</v>
+        <v>190</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>2590</v>
       </c>
       <c r="AE40">
-        <v>37</v>
-      </c>
-      <c r="AF40">
-        <v>1</v>
-      </c>
-      <c r="AG40">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="AF40" s="9">
+        <v>6</v>
+      </c>
+      <c r="AG40" s="16">
+        <v>51</v>
       </c>
       <c r="AH40" s="22">
-        <v>131498900000</v>
+        <v>131421090000</v>
       </c>
       <c r="AI40" s="22">
-        <v>161436994660</v>
-      </c>
-      <c r="AJ40" s="22">
-        <v>29938094660</v>
+        <v>181721462640</v>
+      </c>
+      <c r="AJ40" s="38">
+        <v>50300372640</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>31</v>
@@ -5183,62 +5195,62 @@
       <c r="C41" t="s">
         <v>32</v>
       </c>
-      <c r="D41">
-        <v>120.2838135487691</v>
+      <c r="D41" s="7">
+        <v>136.62677643095921</v>
       </c>
       <c r="E41">
-        <v>37658</v>
+        <v>37626</v>
       </c>
       <c r="F41">
-        <v>3147</v>
+        <v>3184</v>
       </c>
       <c r="G41">
-        <v>127.8764940239044</v>
+        <v>127.61354581673309</v>
       </c>
       <c r="H41">
-        <v>11.709163346613551</v>
-      </c>
-      <c r="I41" s="28">
-        <v>11.709163346613551</v>
+        <v>11.85258964143426</v>
+      </c>
+      <c r="I41" s="30">
+        <v>11.85258964143426</v>
       </c>
       <c r="J41">
-        <v>10.30278884462151</v>
-      </c>
-      <c r="K41" s="28">
-        <v>0.82868525896414347</v>
+        <v>10.23505976095618</v>
+      </c>
+      <c r="K41" s="30">
+        <v>0.82470119521912355</v>
       </c>
       <c r="L41">
-        <v>0.82868525896414347</v>
+        <v>0.82470119521912355</v>
       </c>
       <c r="M41">
-        <v>0.14342629482071709</v>
+        <v>0.19521912350597609</v>
       </c>
       <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0.14342629482071709</v>
+        <v>7.9681274900398405E-3</v>
+      </c>
+      <c r="O41" s="16">
+        <v>0.20318725099601601</v>
       </c>
       <c r="P41">
-        <v>127.6494023904382</v>
+        <v>126.9800796812749</v>
       </c>
       <c r="Q41" t="s">
-        <v>43</v>
-      </c>
-      <c r="R41" s="7">
-        <v>30.677290836653391</v>
+        <v>77</v>
+      </c>
+      <c r="R41" s="9">
+        <v>25.89641434262948</v>
       </c>
       <c r="S41" t="s">
-        <v>44</v>
-      </c>
-      <c r="T41">
-        <v>58.964143426294832</v>
+        <v>67</v>
+      </c>
+      <c r="T41" s="17">
+        <v>63.34661354581673</v>
       </c>
       <c r="U41" t="s">
-        <v>36</v>
-      </c>
-      <c r="V41" s="9">
-        <v>96</v>
+        <v>38</v>
+      </c>
+      <c r="V41" s="30">
+        <v>88</v>
       </c>
       <c r="W41" t="s">
         <v>45</v>
@@ -5247,45 +5259,45 @@
         <v>84</v>
       </c>
       <c r="Y41">
-        <v>32097</v>
+        <v>32031</v>
       </c>
       <c r="Z41">
-        <v>2939</v>
+        <v>2975</v>
       </c>
       <c r="AA41">
-        <v>35036</v>
+        <v>35006</v>
       </c>
       <c r="AB41">
-        <v>2234</v>
+        <v>2158</v>
       </c>
       <c r="AC41">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AD41" s="7">
-        <v>2586</v>
+        <v>2569</v>
       </c>
       <c r="AE41">
-        <v>36</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>36</v>
-      </c>
-      <c r="AH41" s="21">
-        <v>130897500000</v>
+        <v>49</v>
+      </c>
+      <c r="AF41" s="30">
+        <v>2</v>
+      </c>
+      <c r="AG41" s="16">
+        <v>51</v>
+      </c>
+      <c r="AH41" s="22">
+        <v>130373910000</v>
       </c>
       <c r="AI41" s="22">
-        <v>157448504840</v>
-      </c>
-      <c r="AJ41" s="22">
-        <v>26551004840</v>
+        <v>178125670540</v>
+      </c>
+      <c r="AJ41" s="39">
+        <v>47751760540</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
@@ -5293,109 +5305,109 @@
       <c r="C42" t="s">
         <v>32</v>
       </c>
-      <c r="D42">
-        <v>122.82663205943579</v>
+      <c r="D42" s="17">
+        <v>140.05375809925181</v>
       </c>
       <c r="E42">
-        <v>37663</v>
+        <v>37953</v>
       </c>
       <c r="F42">
-        <v>3151</v>
+        <v>3144</v>
       </c>
       <c r="G42">
-        <v>127.9163346613546</v>
-      </c>
-      <c r="H42">
-        <v>11.71314741035857</v>
-      </c>
-      <c r="I42">
-        <v>11.71314741035857</v>
+        <v>128.90438247011949</v>
+      </c>
+      <c r="H42" s="30">
+        <v>11.749003984063741</v>
+      </c>
+      <c r="I42" s="30">
+        <v>11.749003984063741</v>
       </c>
       <c r="J42">
-        <v>10.28286852589641</v>
-      </c>
-      <c r="K42" s="28">
-        <v>0.82868525896414347</v>
-      </c>
-      <c r="L42">
-        <v>0.82868525896414347</v>
+        <v>10.334661354581669</v>
+      </c>
+      <c r="K42" s="30">
+        <v>0.76095617529880477</v>
+      </c>
+      <c r="L42" s="9">
+        <v>0.76095617529880477</v>
       </c>
       <c r="M42">
-        <v>0.12749003984063739</v>
+        <v>0.20318725099601601</v>
       </c>
       <c r="N42">
-        <v>1.1952191235059761E-2</v>
-      </c>
-      <c r="O42">
-        <v>0.1394422310756972</v>
+        <v>1.5936254980079681E-2</v>
+      </c>
+      <c r="O42" s="14">
+        <v>0.21912350597609559</v>
       </c>
       <c r="P42">
-        <v>127.63346613545821</v>
+        <v>128.2270916334661</v>
       </c>
       <c r="Q42" t="s">
-        <v>39</v>
-      </c>
-      <c r="R42" s="28">
-        <v>32.270916334661351</v>
+        <v>64</v>
+      </c>
+      <c r="R42" s="30">
+        <v>34.262948207171313</v>
       </c>
       <c r="S42" t="s">
-        <v>71</v>
-      </c>
-      <c r="T42" s="28">
-        <v>59.362549800796813</v>
+        <v>34</v>
+      </c>
+      <c r="T42" s="30">
+        <v>56.972111553784863</v>
       </c>
       <c r="U42" t="s">
-        <v>38</v>
-      </c>
-      <c r="V42">
-        <v>88</v>
+        <v>41</v>
+      </c>
+      <c r="V42" s="7">
+        <v>92</v>
       </c>
       <c r="W42" t="s">
-        <v>72</v>
-      </c>
-      <c r="X42">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="X42" s="9">
+        <v>92</v>
       </c>
       <c r="Y42">
-        <v>32107</v>
+        <v>32355</v>
       </c>
       <c r="Z42">
-        <v>2940</v>
+        <v>2949</v>
       </c>
       <c r="AA42">
-        <v>35047</v>
+        <v>35304</v>
       </c>
       <c r="AB42">
-        <v>2233</v>
+        <v>2183</v>
       </c>
       <c r="AC42">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="AD42" s="7">
-        <v>2581</v>
+        <v>2594</v>
       </c>
       <c r="AE42">
-        <v>32</v>
-      </c>
-      <c r="AF42">
-        <v>3</v>
-      </c>
-      <c r="AG42">
-        <v>35</v>
-      </c>
-      <c r="AH42" s="21">
-        <v>130897500000</v>
+        <v>51</v>
+      </c>
+      <c r="AF42" s="30">
+        <v>4</v>
+      </c>
+      <c r="AG42" s="18">
+        <v>55</v>
+      </c>
+      <c r="AH42" s="22">
+        <v>131421090000</v>
       </c>
       <c r="AI42" s="22">
-        <v>160776990700</v>
-      </c>
-      <c r="AJ42" s="22">
-        <v>29879490700</v>
+        <v>184060175480</v>
+      </c>
+      <c r="AJ42" s="38">
+        <v>52639085480</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>21</v>
+      <c r="A43" s="25">
+        <v>50</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
@@ -5403,109 +5415,109 @@
       <c r="C43" t="s">
         <v>32</v>
       </c>
-      <c r="D43">
-        <v>119.68388553161439</v>
+      <c r="D43" s="17">
+        <v>141.97365896216499</v>
       </c>
       <c r="E43">
-        <v>37823</v>
+        <v>37803</v>
       </c>
       <c r="F43">
-        <v>3171</v>
+        <v>3162</v>
       </c>
       <c r="G43">
-        <v>128.3545816733068</v>
+        <v>128.29083665338649</v>
       </c>
       <c r="H43">
-        <v>11.908366533864539</v>
-      </c>
-      <c r="I43" s="28">
-        <v>11.908366533864539</v>
+        <v>11.80478087649402</v>
+      </c>
+      <c r="I43" s="30">
+        <v>11.80478087649402</v>
       </c>
       <c r="J43">
         <v>10.29482071713147</v>
       </c>
       <c r="K43">
-        <v>0.70517928286852594</v>
-      </c>
-      <c r="L43">
-        <v>0.70517928286852594</v>
+        <v>0.77290836653386452</v>
+      </c>
+      <c r="L43" s="9">
+        <v>0.77290836653386452</v>
       </c>
       <c r="M43">
-        <v>0.11155378486055779</v>
+        <v>0.19920318725099601</v>
       </c>
       <c r="N43">
         <v>1.9920318725099601E-2</v>
       </c>
-      <c r="O43">
-        <v>0.13147410358565739</v>
+      <c r="O43" s="14">
+        <v>0.21912350597609559</v>
       </c>
       <c r="P43">
-        <v>128.11553784860561</v>
+        <v>127.593625498008</v>
       </c>
       <c r="Q43" t="s">
-        <v>85</v>
-      </c>
-      <c r="R43">
-        <v>42.629482071713149</v>
+        <v>43</v>
+      </c>
+      <c r="R43" s="7">
+        <v>30.677290836653391</v>
       </c>
       <c r="S43" t="s">
-        <v>81</v>
-      </c>
-      <c r="T43">
-        <v>51.394422310756973</v>
+        <v>54</v>
+      </c>
+      <c r="T43" s="7">
+        <v>58.56573705179283</v>
       </c>
       <c r="U43" t="s">
-        <v>74</v>
-      </c>
-      <c r="V43">
-        <v>72</v>
+        <v>36</v>
+      </c>
+      <c r="V43" s="41">
+        <v>96</v>
       </c>
       <c r="W43" t="s">
-        <v>86</v>
-      </c>
-      <c r="X43">
-        <v>60</v>
+        <v>41</v>
+      </c>
+      <c r="X43" s="9">
+        <v>92</v>
       </c>
       <c r="Y43">
-        <v>32217</v>
+        <v>32201</v>
       </c>
       <c r="Z43">
-        <v>2989</v>
+        <v>2963</v>
       </c>
       <c r="AA43">
-        <v>35206</v>
+        <v>35164</v>
       </c>
       <c r="AB43">
-        <v>2275</v>
+        <v>2170</v>
       </c>
       <c r="AC43">
-        <v>177</v>
-      </c>
-      <c r="AD43" s="28">
+        <v>194</v>
+      </c>
+      <c r="AD43" s="7">
         <v>2584</v>
       </c>
       <c r="AE43">
-        <v>28</v>
-      </c>
-      <c r="AF43" s="7">
+        <v>50</v>
+      </c>
+      <c r="AF43" s="30">
         <v>5</v>
       </c>
-      <c r="AG43">
-        <v>33</v>
-      </c>
-      <c r="AH43" s="21">
-        <v>131421090000</v>
+      <c r="AG43" s="18">
+        <v>55</v>
+      </c>
+      <c r="AH43" s="22">
+        <v>130897500000</v>
       </c>
       <c r="AI43" s="22">
-        <v>157289866920</v>
-      </c>
-      <c r="AJ43" s="22">
-        <v>25868776920</v>
+        <v>185839970240</v>
+      </c>
+      <c r="AJ43" s="38">
+        <v>54942470240</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -5514,108 +5526,108 @@
         <v>32</v>
       </c>
       <c r="D44">
-        <v>113.1032980475204</v>
+        <v>133.55055607893681</v>
       </c>
       <c r="E44">
-        <v>37789</v>
+        <v>37859</v>
       </c>
       <c r="F44">
-        <v>3091</v>
+        <v>3193</v>
       </c>
       <c r="G44">
-        <v>128.48605577689241</v>
+        <v>128.40239043824701</v>
       </c>
       <c r="H44">
-        <v>11.597609561752989</v>
-      </c>
-      <c r="I44" s="28">
-        <v>11.597609561752989</v>
+        <v>11.89641434262948</v>
+      </c>
+      <c r="I44" s="30">
+        <v>11.89641434262948</v>
       </c>
       <c r="J44">
-        <v>10.342629482071709</v>
-      </c>
-      <c r="K44" s="28">
-        <v>0.71713147410358569</v>
+        <v>10.35458167330677</v>
+      </c>
+      <c r="K44" s="30">
+        <v>0.80478087649402386</v>
       </c>
       <c r="L44">
-        <v>0.71713147410358569</v>
+        <v>0.80478087649402386</v>
       </c>
       <c r="M44">
-        <v>0.12749003984063739</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="O44">
-        <v>0.12749003984063739</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="P44">
-        <v>128.43426294820719</v>
+        <v>127.99203187251</v>
       </c>
       <c r="Q44" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="R44">
-        <v>37.450199203187253</v>
+        <v>32.669322709163353</v>
       </c>
       <c r="S44" t="s">
-        <v>79</v>
-      </c>
-      <c r="T44">
-        <v>53.784860557768923</v>
+        <v>56</v>
+      </c>
+      <c r="T44" s="9">
+        <v>60.557768924302792</v>
       </c>
       <c r="U44" t="s">
+        <v>36</v>
+      </c>
+      <c r="V44" s="41">
+        <v>96</v>
+      </c>
+      <c r="W44" t="s">
         <v>45</v>
       </c>
-      <c r="V44">
+      <c r="X44">
         <v>84</v>
       </c>
-      <c r="W44" t="s">
-        <v>74</v>
-      </c>
-      <c r="X44">
-        <v>72</v>
-      </c>
       <c r="Y44">
-        <v>32250</v>
+        <v>32229</v>
       </c>
       <c r="Z44">
-        <v>2911</v>
+        <v>2986</v>
       </c>
       <c r="AA44">
-        <v>35161</v>
+        <v>35215</v>
       </c>
       <c r="AB44">
-        <v>2288</v>
+        <v>2217</v>
       </c>
       <c r="AC44">
-        <v>180</v>
-      </c>
-      <c r="AD44" s="7">
-        <v>2596</v>
+        <v>202</v>
+      </c>
+      <c r="AD44" s="30">
+        <v>2599</v>
       </c>
       <c r="AE44">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG44">
-        <v>32</v>
-      </c>
-      <c r="AH44" s="21">
+        <v>45</v>
+      </c>
+      <c r="AH44" s="23">
         <v>131421090000</v>
       </c>
-      <c r="AI44" s="22">
-        <v>148641587120</v>
-      </c>
-      <c r="AJ44" s="22">
-        <v>17220497120</v>
+      <c r="AI44" s="23">
+        <v>175513596500</v>
+      </c>
+      <c r="AJ44" s="40">
+        <v>44092506500</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
         <v>31</v>
@@ -5624,103 +5636,103 @@
         <v>32</v>
       </c>
       <c r="D45">
-        <v>116.4762356347524</v>
+        <v>132.0141723562329</v>
       </c>
       <c r="E45">
-        <v>37654</v>
+        <v>37709</v>
       </c>
       <c r="F45">
-        <v>3106</v>
+        <v>3055</v>
       </c>
       <c r="G45">
-        <v>127.97609561752989</v>
+        <v>128.34661354581669</v>
       </c>
       <c r="H45">
-        <v>11.621513944223111</v>
+        <v>11.394422310756971</v>
       </c>
       <c r="I45">
-        <v>11.621513944223111</v>
+        <v>11.394422310756971</v>
       </c>
       <c r="J45">
-        <v>10.290836653386449</v>
+        <v>10.314741035856571</v>
       </c>
       <c r="K45">
-        <v>0.7450199203187251</v>
+        <v>0.75697211155378485</v>
       </c>
       <c r="L45">
-        <v>0.7450199203187251</v>
+        <v>0.75697211155378485</v>
       </c>
       <c r="M45">
-        <v>0.1195219123505976</v>
+        <v>0.15936254980079681</v>
       </c>
       <c r="N45">
-        <v>7.9681274900398405E-3</v>
+        <v>1.9920318725099601E-2</v>
       </c>
       <c r="O45">
-        <v>0.12749003984063739</v>
+        <v>0.17928286852589639</v>
       </c>
       <c r="P45">
-        <v>127.8167330677291</v>
+        <v>128.03187250996021</v>
       </c>
       <c r="Q45" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="R45">
-        <v>39.04382470119522</v>
+        <v>34.661354581673308</v>
       </c>
       <c r="S45" t="s">
-        <v>81</v>
-      </c>
-      <c r="T45">
-        <v>51.394422310756973</v>
+        <v>57</v>
+      </c>
+      <c r="T45" s="7">
+        <v>58.167330677290842</v>
       </c>
       <c r="U45" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="V45">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="W45" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="X45">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="Y45">
-        <v>32122</v>
+        <v>32215</v>
       </c>
       <c r="Z45">
-        <v>2917</v>
+        <v>2860</v>
       </c>
       <c r="AA45">
-        <v>35039</v>
+        <v>35075</v>
       </c>
       <c r="AB45">
-        <v>2268</v>
+        <v>2219</v>
       </c>
       <c r="AC45">
-        <v>187</v>
-      </c>
-      <c r="AD45" s="7">
-        <v>2583</v>
+        <v>190</v>
+      </c>
+      <c r="AD45" s="30">
+        <v>2589</v>
       </c>
       <c r="AE45">
-        <v>30</v>
-      </c>
-      <c r="AF45" s="28">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="AF45" s="30">
+        <v>5</v>
       </c>
       <c r="AG45">
-        <v>32</v>
-      </c>
-      <c r="AH45" s="21">
+        <v>45</v>
+      </c>
+      <c r="AH45" s="23">
         <v>130897500000</v>
       </c>
-      <c r="AI45" s="22">
-        <v>152464480540</v>
-      </c>
-      <c r="AJ45" s="22">
-        <v>21566980540</v>
+      <c r="AI45" s="23">
+        <v>172803251260</v>
+      </c>
+      <c r="AJ45" s="40">
+        <v>41905751260</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.35">
@@ -5766,7 +5778,7 @@
   </sheetData>
   <autoFilter ref="A2:AM2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AM53">
-      <sortCondition descending="1" ref="AG2"/>
+      <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -5776,7 +5788,7 @@
     <mergeCell ref="G1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA5BCF7-BB6D-46F2-B022-0999E0867168}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8352C07B-FDB6-4924-A8A8-5C4DF3778E8E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4150" yWindow="1230" windowWidth="26280" windowHeight="18970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="95">
   <si>
     <t>Trung bình/Kỳ</t>
   </si>
@@ -367,7 +367,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +407,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -474,7 +480,8 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -486,16 +493,17 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -511,8 +519,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -797,54 +805,54 @@
   <dimension ref="A1:AM53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9" style="14" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="8.453125" style="14" customWidth="1"/>
-    <col min="8" max="15" width="6.453125" style="14" customWidth="1"/>
-    <col min="16" max="16" width="8" style="14" customWidth="1"/>
-    <col min="17" max="17" width="9" style="14" customWidth="1"/>
-    <col min="18" max="20" width="9.1796875" style="14" customWidth="1"/>
-    <col min="21" max="21" width="17.81640625" style="14" customWidth="1"/>
-    <col min="22" max="24" width="16.90625" style="14" customWidth="1"/>
-    <col min="25" max="29" width="9.26953125" style="14" customWidth="1"/>
-    <col min="30" max="30" width="9.26953125" style="15" customWidth="1"/>
-    <col min="31" max="33" width="9.26953125" style="14" customWidth="1"/>
-    <col min="34" max="34" width="25.7265625" style="23" customWidth="1"/>
-    <col min="35" max="36" width="18.7265625" style="23" customWidth="1"/>
-    <col min="37" max="39" width="6.54296875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="9" style="16" customWidth="1"/>
+    <col min="3" max="3" width="8.36328125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" style="16" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" style="16" customWidth="1"/>
+    <col min="8" max="15" width="6.453125" style="16" customWidth="1"/>
+    <col min="16" max="16" width="8" style="16" customWidth="1"/>
+    <col min="17" max="17" width="9" style="16" customWidth="1"/>
+    <col min="18" max="20" width="9.1796875" style="16" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="16" customWidth="1"/>
+    <col min="22" max="24" width="16.90625" style="16" customWidth="1"/>
+    <col min="25" max="29" width="9.26953125" style="16" customWidth="1"/>
+    <col min="30" max="30" width="9.26953125" style="17" customWidth="1"/>
+    <col min="31" max="33" width="9.26953125" style="16" customWidth="1"/>
+    <col min="34" max="34" width="25.7265625" style="25" customWidth="1"/>
+    <col min="35" max="36" width="18.7265625" style="25" customWidth="1"/>
+    <col min="37" max="39" width="6.54296875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Y1" s="17" t="s">
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Y1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="20" t="s">
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="19" t="s">
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -856,7 +864,7 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -901,49 +909,49 @@
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="W2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="X2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="8">
+      <c r="Y2" s="9">
         <v>3</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AA2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="AB2" s="8">
+      <c r="AB2" s="9">
         <v>4</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AD2" s="9" t="s">
+      <c r="AD2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AE2" s="8">
+      <c r="AE2" s="9">
         <v>5</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="AF2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="AH2" s="6" t="s">
@@ -957,8 +965,8 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>20</v>
+      <c r="A3" s="13">
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -966,109 +974,109 @@
       <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="D3">
-        <v>134.17660108042841</v>
+      <c r="D3" s="15">
+        <v>144.9974295177756</v>
       </c>
       <c r="E3">
-        <v>40464</v>
+        <v>39842</v>
       </c>
       <c r="F3">
-        <v>3382</v>
+        <v>3322</v>
       </c>
       <c r="G3">
-        <v>127.6592592592593</v>
+        <v>125.8592592592593</v>
       </c>
       <c r="H3">
-        <v>11.74444444444444</v>
+        <v>11.36296296296296</v>
       </c>
       <c r="I3">
-        <v>11.74444444444444</v>
+        <v>11.36296296296296</v>
       </c>
       <c r="J3">
-        <v>10.262962962962961</v>
+        <v>10.148148148148151</v>
       </c>
       <c r="K3">
-        <v>0.77407407407407403</v>
+        <v>0.90740740740740744</v>
       </c>
       <c r="L3">
-        <v>0.77407407407407403</v>
+        <v>0.90740740740740744</v>
       </c>
       <c r="M3">
+        <v>0.15925925925925929</v>
+      </c>
+      <c r="N3">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="O3" s="16">
         <v>0.19259259259259259</v>
       </c>
-      <c r="N3">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O3" s="13">
-        <v>0.2</v>
-      </c>
       <c r="P3">
-        <v>127.1851851851852</v>
+        <v>125.3148148148148</v>
       </c>
       <c r="Q3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="R3">
-        <v>33.703703703703702</v>
+        <v>23.703703703703709</v>
       </c>
       <c r="S3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T3" s="14">
-        <v>56.666666666666657</v>
+        <v>50</v>
+      </c>
+      <c r="T3" s="15">
+        <v>60.74074074074074</v>
       </c>
       <c r="U3" t="s">
-        <v>60</v>
-      </c>
-      <c r="V3" s="13">
-        <v>100</v>
+        <v>43</v>
+      </c>
+      <c r="V3" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W3" t="s">
-        <v>61</v>
-      </c>
-      <c r="X3" s="13">
-        <v>96.296296296296291</v>
+        <v>43</v>
+      </c>
+      <c r="X3" s="15">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y3">
-        <v>34468</v>
+        <v>33982</v>
       </c>
       <c r="Z3">
-        <v>3171</v>
+        <v>3068</v>
       </c>
       <c r="AA3">
-        <v>37639</v>
+        <v>37050</v>
       </c>
       <c r="AB3">
-        <v>2346</v>
+        <v>2287</v>
       </c>
       <c r="AC3">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="AD3">
-        <v>2771</v>
+        <v>2740</v>
       </c>
       <c r="AE3">
+        <v>43</v>
+      </c>
+      <c r="AF3">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="15">
         <v>52</v>
       </c>
-      <c r="AF3">
-        <v>2</v>
-      </c>
-      <c r="AG3" s="13">
-        <v>54</v>
-      </c>
-      <c r="AH3" s="23">
-        <v>140322120000</v>
-      </c>
-      <c r="AI3" s="23">
-        <v>188279451180</v>
-      </c>
-      <c r="AJ3" s="23">
-        <v>47957331180</v>
+      <c r="AH3" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI3" s="25">
+        <v>200426698880</v>
+      </c>
+      <c r="AJ3" s="26">
+        <v>62198938880</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>46</v>
+      <c r="A4" s="16">
+        <v>48</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -1076,109 +1084,109 @@
       <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4">
-        <v>139.81716605967711</v>
+      <c r="D4" s="16">
+        <v>135.0130755550814</v>
       </c>
       <c r="E4">
-        <v>39717</v>
+        <v>39423</v>
       </c>
       <c r="F4">
-        <v>3326</v>
+        <v>3338</v>
       </c>
       <c r="G4">
-        <v>125.3703703703704</v>
+        <v>124.3148148148148</v>
       </c>
       <c r="H4">
-        <v>11.455555555555559</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="I4">
-        <v>11.455555555555559</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="J4">
-        <v>10.074074074074071</v>
+        <v>9.9777777777777779</v>
       </c>
       <c r="K4">
-        <v>0.8481481481481481</v>
+        <v>0.82592592592592595</v>
       </c>
       <c r="L4">
-        <v>0.8481481481481481</v>
+        <v>0.82592592592592595</v>
       </c>
       <c r="M4">
-        <v>0.1851851851851852</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N4">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O4" s="13">
-        <v>0.2</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O4" s="16">
+        <v>0.18888888888888891</v>
       </c>
       <c r="P4">
-        <v>124.77407407407409</v>
+        <v>123.72592592592591</v>
       </c>
       <c r="Q4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="R4">
-        <v>28.518518518518519</v>
+        <v>24.81481481481481</v>
       </c>
       <c r="S4" t="s">
-        <v>85</v>
-      </c>
-      <c r="T4" s="13">
-        <v>61.481481481481481</v>
+        <v>88</v>
+      </c>
+      <c r="T4" s="15">
+        <v>62.222222222222221</v>
       </c>
       <c r="U4" t="s">
-        <v>61</v>
-      </c>
-      <c r="V4" s="25">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V4" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W4" t="s">
-        <v>61</v>
-      </c>
-      <c r="X4" s="13">
-        <v>96.296296296296291</v>
+        <v>36</v>
+      </c>
+      <c r="X4" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y4">
-        <v>33850</v>
+        <v>33565</v>
       </c>
       <c r="Z4">
-        <v>3093</v>
+        <v>3113</v>
       </c>
       <c r="AA4">
-        <v>36943</v>
+        <v>36678</v>
       </c>
       <c r="AB4">
-        <v>2275</v>
+        <v>2267</v>
       </c>
       <c r="AC4">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AD4">
-        <v>2720</v>
+        <v>2694</v>
       </c>
       <c r="AE4">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF4">
-        <v>4</v>
-      </c>
-      <c r="AG4" s="13">
-        <v>54</v>
-      </c>
-      <c r="AH4" s="23">
-        <v>137704170000</v>
-      </c>
-      <c r="AI4" s="23">
-        <v>192534068040</v>
-      </c>
-      <c r="AJ4" s="24">
-        <v>54829898040</v>
+        <v>2</v>
+      </c>
+      <c r="AG4" s="15">
+        <v>51</v>
+      </c>
+      <c r="AH4" s="25">
+        <v>136656990000</v>
+      </c>
+      <c r="AI4" s="25">
+        <v>184504805160</v>
+      </c>
+      <c r="AJ4" s="25">
+        <v>47847815160</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>45</v>
+      <c r="A5" s="16">
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -1186,109 +1194,109 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5">
-        <v>140.26478090942081</v>
+      <c r="D5" s="16">
+        <v>128.7079858947466</v>
       </c>
       <c r="E5">
-        <v>39870</v>
+        <v>38741</v>
       </c>
       <c r="F5">
-        <v>3318</v>
+        <v>3218</v>
       </c>
       <c r="G5">
-        <v>125.84444444444441</v>
+        <v>122.4</v>
       </c>
       <c r="H5">
-        <v>11.5</v>
+        <v>11.0962962962963</v>
       </c>
       <c r="I5">
-        <v>11.5</v>
+        <v>11.0962962962963</v>
       </c>
       <c r="J5">
-        <v>10.11851851851852</v>
+        <v>9.837037037037037</v>
       </c>
       <c r="K5">
-        <v>0.76666666666666672</v>
+        <v>0.80740740740740746</v>
       </c>
       <c r="L5">
-        <v>0.76666666666666672</v>
+        <v>0.80740740740740746</v>
       </c>
       <c r="M5">
-        <v>0.18148148148148149</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N5">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O5" s="13">
-        <v>0.20370370370370369</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O5" s="16">
+        <v>0.15185185185185179</v>
       </c>
       <c r="P5">
-        <v>125.3185185185185</v>
+        <v>122.05185185185189</v>
       </c>
       <c r="Q5" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="R5">
-        <v>30.74074074074074</v>
+        <v>27.777777777777779</v>
       </c>
       <c r="S5" t="s">
-        <v>59</v>
-      </c>
-      <c r="T5" s="14">
-        <v>56.666666666666657</v>
+        <v>48</v>
+      </c>
+      <c r="T5" s="16">
+        <v>55.925925925925917</v>
       </c>
       <c r="U5" t="s">
-        <v>60</v>
-      </c>
-      <c r="V5" s="13">
-        <v>100</v>
+        <v>43</v>
+      </c>
+      <c r="V5" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" s="13">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="X5" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y5">
-        <v>33978</v>
+        <v>33048</v>
       </c>
       <c r="Z5">
-        <v>3105</v>
+        <v>2996</v>
       </c>
       <c r="AA5">
-        <v>37083</v>
+        <v>36044</v>
       </c>
       <c r="AB5">
-        <v>2305</v>
+        <v>2274</v>
       </c>
       <c r="AC5">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AD5">
-        <v>2732</v>
+        <v>2656</v>
       </c>
       <c r="AE5">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AF5">
-        <v>6</v>
-      </c>
-      <c r="AG5" s="13">
-        <v>55</v>
-      </c>
-      <c r="AH5" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI5" s="23">
-        <v>193884864720</v>
-      </c>
-      <c r="AJ5" s="24">
-        <v>55657104720</v>
+        <v>4</v>
+      </c>
+      <c r="AG5" s="16">
+        <v>41</v>
+      </c>
+      <c r="AH5" s="25">
+        <v>134562630000</v>
+      </c>
+      <c r="AI5" s="25">
+        <v>173192850840</v>
+      </c>
+      <c r="AJ5" s="25">
+        <v>38630220840</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>15</v>
+      <c r="A6" s="13">
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1296,109 +1304,109 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="D6">
-        <v>144.9974295177756</v>
+      <c r="D6" s="15">
+        <v>139.81716605967711</v>
       </c>
       <c r="E6">
-        <v>39842</v>
+        <v>39717</v>
       </c>
       <c r="F6">
-        <v>3322</v>
+        <v>3326</v>
       </c>
       <c r="G6">
-        <v>125.8592592592593</v>
+        <v>125.3703703703704</v>
       </c>
       <c r="H6">
-        <v>11.36296296296296</v>
+        <v>11.455555555555559</v>
       </c>
       <c r="I6">
-        <v>11.36296296296296</v>
+        <v>11.455555555555559</v>
       </c>
       <c r="J6">
-        <v>10.148148148148151</v>
+        <v>10.074074074074071</v>
       </c>
       <c r="K6">
-        <v>0.90740740740740744</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L6">
-        <v>0.90740740740740744</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M6">
-        <v>0.15925925925925929</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N6">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="O6" s="14">
-        <v>0.19259259259259259</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O6" s="15">
+        <v>0.2</v>
       </c>
       <c r="P6">
-        <v>125.3148148148148</v>
+        <v>124.77407407407409</v>
       </c>
       <c r="Q6" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="R6">
-        <v>23.703703703703709</v>
+        <v>28.518518518518519</v>
       </c>
       <c r="S6" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" s="15">
+        <v>61.481481481481481</v>
+      </c>
+      <c r="U6" t="s">
+        <v>61</v>
+      </c>
+      <c r="V6" s="27">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X6" s="15">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="Y6">
+        <v>33850</v>
+      </c>
+      <c r="Z6">
+        <v>3093</v>
+      </c>
+      <c r="AA6">
+        <v>36943</v>
+      </c>
+      <c r="AB6">
+        <v>2275</v>
+      </c>
+      <c r="AC6">
+        <v>229</v>
+      </c>
+      <c r="AD6">
+        <v>2720</v>
+      </c>
+      <c r="AE6">
         <v>50</v>
       </c>
-      <c r="T6" s="13">
-        <v>60.74074074074074</v>
-      </c>
-      <c r="U6" t="s">
-        <v>43</v>
-      </c>
-      <c r="V6" s="14">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="W6" t="s">
-        <v>43</v>
-      </c>
-      <c r="X6" s="13">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="Y6">
-        <v>33982</v>
-      </c>
-      <c r="Z6">
-        <v>3068</v>
-      </c>
-      <c r="AA6">
-        <v>37050</v>
-      </c>
-      <c r="AB6">
-        <v>2287</v>
-      </c>
-      <c r="AC6">
-        <v>245</v>
-      </c>
-      <c r="AD6">
-        <v>2740</v>
-      </c>
-      <c r="AE6">
-        <v>43</v>
-      </c>
       <c r="AF6">
-        <v>9</v>
-      </c>
-      <c r="AG6" s="13">
-        <v>52</v>
-      </c>
-      <c r="AH6" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI6" s="23">
-        <v>200426698880</v>
-      </c>
-      <c r="AJ6" s="24">
-        <v>62198938880</v>
+        <v>4</v>
+      </c>
+      <c r="AG6" s="15">
+        <v>54</v>
+      </c>
+      <c r="AH6" s="25">
+        <v>137704170000</v>
+      </c>
+      <c r="AI6" s="25">
+        <v>192534068040</v>
+      </c>
+      <c r="AJ6" s="26">
+        <v>54829898040</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>33</v>
+      <c r="A7" s="13">
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1406,109 +1414,109 @@
       <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="D7">
-        <v>128.74865864506759</v>
+      <c r="D7" s="18">
+        <v>137.87772288176649</v>
       </c>
       <c r="E7">
-        <v>40033</v>
+        <v>39534</v>
       </c>
       <c r="F7">
-        <v>3269</v>
+        <v>3291</v>
       </c>
       <c r="G7">
-        <v>126.637037037037</v>
+        <v>124.8148148148148</v>
       </c>
       <c r="H7">
-        <v>11.31481481481481</v>
+        <v>11.34814814814815</v>
       </c>
       <c r="I7">
-        <v>11.31481481481481</v>
+        <v>11.34814814814815</v>
       </c>
       <c r="J7">
-        <v>10.140740740740741</v>
+        <v>10.07037037037037</v>
       </c>
       <c r="K7">
-        <v>0.78888888888888886</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L7">
-        <v>0.78888888888888886</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M7">
-        <v>0.1740740740740741</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="N7">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O7" s="14">
-        <v>0.17777777777777781</v>
+        <v>1.8518518518518521E-2</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0.18888888888888891</v>
       </c>
       <c r="P7">
-        <v>126.1111111111111</v>
+        <v>124.39259259259261</v>
       </c>
       <c r="Q7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="R7">
-        <v>32.592592592592602</v>
+        <v>29.25925925925926</v>
       </c>
       <c r="S7" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" s="14">
-        <v>55.925925925925917</v>
+        <v>75</v>
+      </c>
+      <c r="T7" s="15">
+        <v>62.592592592592588</v>
       </c>
       <c r="U7" t="s">
         <v>43</v>
       </c>
-      <c r="V7" s="14">
+      <c r="V7" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" s="13">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="X7" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y7">
-        <v>34192</v>
+        <v>33700</v>
       </c>
       <c r="Z7">
-        <v>3055</v>
+        <v>3064</v>
       </c>
       <c r="AA7">
-        <v>37247</v>
+        <v>36764</v>
       </c>
       <c r="AB7">
-        <v>2333</v>
+        <v>2293</v>
       </c>
       <c r="AC7">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="AD7">
-        <v>2738</v>
+        <v>2719</v>
       </c>
       <c r="AE7">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="14">
-        <v>48</v>
-      </c>
-      <c r="AH7" s="23">
-        <v>138833500000</v>
-      </c>
-      <c r="AI7" s="23">
-        <v>178746269000</v>
-      </c>
-      <c r="AJ7" s="23">
-        <v>39912769000</v>
+        <v>5</v>
+      </c>
+      <c r="AG7" s="15">
+        <v>51</v>
+      </c>
+      <c r="AH7" s="25">
+        <v>137180580000</v>
+      </c>
+      <c r="AI7" s="25">
+        <v>189141459940</v>
+      </c>
+      <c r="AJ7" s="26">
+        <v>51960879940</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>34</v>
+      <c r="A8" s="16">
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -1516,109 +1524,109 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8">
-        <v>126.46334539823501</v>
+      <c r="D8" s="16">
+        <v>131.30610870598051</v>
       </c>
       <c r="E8">
-        <v>40147</v>
+        <v>38933</v>
       </c>
       <c r="F8">
-        <v>3366</v>
+        <v>3060</v>
       </c>
       <c r="G8">
-        <v>126.7703703703704</v>
+        <v>123.537037037037</v>
       </c>
       <c r="H8">
-        <v>11.607407407407409</v>
+        <v>10.56296296296296</v>
       </c>
       <c r="I8">
-        <v>11.607407407407409</v>
+        <v>10.56296296296296</v>
       </c>
       <c r="J8">
-        <v>10.15925925925926</v>
+        <v>9.9111111111111114</v>
       </c>
       <c r="K8">
-        <v>0.85185185185185186</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="L8">
-        <v>0.85185185185185186</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="M8">
-        <v>0.14814814814814811</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N8">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O8" s="14">
-        <v>0.15555555555555561</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O8" s="16">
+        <v>0.1851851851851852</v>
       </c>
       <c r="P8">
-        <v>126.2703703703704</v>
+        <v>123.1740740740741</v>
       </c>
       <c r="Q8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R8">
-        <v>32.222222222222221</v>
+        <v>29.25925925925926</v>
       </c>
       <c r="S8" t="s">
-        <v>54</v>
-      </c>
-      <c r="T8" s="14">
-        <v>55.185185185185183</v>
+        <v>45</v>
+      </c>
+      <c r="T8" s="16">
+        <v>54.814814814814817</v>
       </c>
       <c r="U8" t="s">
-        <v>61</v>
-      </c>
-      <c r="V8" s="25">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V8" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X8" s="16">
-        <v>88.888888888888886</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y8">
-        <v>34228</v>
+        <v>33355</v>
       </c>
       <c r="Z8">
-        <v>3134</v>
+        <v>2852</v>
       </c>
       <c r="AA8">
-        <v>37362</v>
+        <v>36207</v>
       </c>
       <c r="AB8">
-        <v>2345</v>
+        <v>2269</v>
       </c>
       <c r="AC8">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="AD8">
-        <v>2743</v>
+        <v>2676</v>
       </c>
       <c r="AE8">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="AF8">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="14">
-        <v>42</v>
-      </c>
-      <c r="AH8" s="23">
-        <v>139357400000</v>
-      </c>
-      <c r="AI8" s="23">
-        <v>176236030100</v>
-      </c>
-      <c r="AJ8" s="23">
-        <v>36878630100</v>
+        <v>1</v>
+      </c>
+      <c r="AG8" s="15">
+        <v>50</v>
+      </c>
+      <c r="AH8" s="25">
+        <v>135086220000</v>
+      </c>
+      <c r="AI8" s="25">
+        <v>177376458880</v>
+      </c>
+      <c r="AJ8" s="25">
+        <v>42290238880</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>35</v>
+      <c r="A9" s="16">
+        <v>42</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1626,109 +1634,109 @@
       <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>126.3735355064933</v>
+      <c r="D9" s="16">
+        <v>132.19259139829359</v>
       </c>
       <c r="E9">
-        <v>40759</v>
+        <v>38919</v>
       </c>
       <c r="F9">
-        <v>3357</v>
+        <v>3226</v>
       </c>
       <c r="G9">
-        <v>128.862962962963</v>
+        <v>122.8185185185185</v>
       </c>
       <c r="H9">
-        <v>11.63703703703704</v>
+        <v>11.207407407407411</v>
       </c>
       <c r="I9">
-        <v>11.63703703703704</v>
+        <v>11.207407407407411</v>
       </c>
       <c r="J9">
-        <v>10.3</v>
+        <v>9.9333333333333336</v>
       </c>
       <c r="K9">
-        <v>0.78148148148148144</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L9">
-        <v>0.78148148148148144</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M9">
-        <v>0.1444444444444444</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="N9">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O9" s="14">
-        <v>0.15925925925925929</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O9" s="16">
+        <v>0.1851851851851852</v>
       </c>
       <c r="P9">
-        <v>128.39259259259259</v>
+        <v>122.537037037037</v>
       </c>
       <c r="Q9" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="R9">
-        <v>34.814814814814817</v>
+        <v>29.62962962962963</v>
       </c>
       <c r="S9" t="s">
-        <v>54</v>
-      </c>
-      <c r="T9" s="14">
-        <v>55.185185185185183</v>
+        <v>59</v>
+      </c>
+      <c r="T9" s="16">
+        <v>56.666666666666657</v>
       </c>
       <c r="U9" t="s">
-        <v>61</v>
-      </c>
-      <c r="V9" s="25">
-        <v>96.296296296296291</v>
+        <v>43</v>
+      </c>
+      <c r="V9" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X9" s="16">
-        <v>88.888888888888886</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y9">
-        <v>34793</v>
+        <v>33161</v>
       </c>
       <c r="Z9">
-        <v>3142</v>
+        <v>3026</v>
       </c>
       <c r="AA9">
-        <v>37935</v>
+        <v>36187</v>
       </c>
       <c r="AB9">
-        <v>2398</v>
+        <v>2284</v>
       </c>
       <c r="AC9">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="AD9">
-        <v>2781</v>
+        <v>2682</v>
       </c>
       <c r="AE9">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AF9">
-        <v>4</v>
-      </c>
-      <c r="AG9" s="14">
-        <v>43</v>
-      </c>
-      <c r="AH9" s="23">
-        <v>141453000000</v>
-      </c>
-      <c r="AI9" s="23">
-        <v>178759157180</v>
-      </c>
-      <c r="AJ9" s="23">
-        <v>37306157180</v>
+        <v>2</v>
+      </c>
+      <c r="AG9" s="15">
+        <v>50</v>
+      </c>
+      <c r="AH9" s="25">
+        <v>135086220000</v>
+      </c>
+      <c r="AI9" s="25">
+        <v>178573974840</v>
+      </c>
+      <c r="AJ9" s="25">
+        <v>43487754840</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1737,108 +1745,108 @@
         <v>32</v>
       </c>
       <c r="D10">
-        <v>133.5215300175762</v>
+        <v>127.9967155062633</v>
       </c>
       <c r="E10">
-        <v>40616</v>
+        <v>40473</v>
       </c>
       <c r="F10">
-        <v>3367</v>
+        <v>3406</v>
       </c>
       <c r="G10">
-        <v>128.28518518518521</v>
+        <v>127.71111111111109</v>
       </c>
       <c r="H10">
-        <v>11.65555555555556</v>
+        <v>11.77407407407407</v>
       </c>
       <c r="I10">
-        <v>11.65555555555556</v>
+        <v>11.77407407407407</v>
       </c>
       <c r="J10">
-        <v>10.31111111111111</v>
+        <v>10.24444444444444</v>
       </c>
       <c r="K10">
-        <v>0.79259259259259263</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="L10">
-        <v>0.79259259259259263</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="M10">
-        <v>0.15555555555555561</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N10">
-        <v>2.222222222222222E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O10">
-        <v>0.17777777777777781</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P10">
-        <v>127.8333333333333</v>
+        <v>127.1666666666667</v>
       </c>
       <c r="Q10" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="R10">
-        <v>33.703703703703702</v>
+        <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
-      </c>
-      <c r="T10" s="14">
-        <v>58.518518518518512</v>
+        <v>75</v>
+      </c>
+      <c r="T10" s="15">
+        <v>62.592592592592588</v>
       </c>
       <c r="U10" t="s">
-        <v>61</v>
-      </c>
-      <c r="V10" s="25">
-        <v>96.296296296296291</v>
+        <v>39</v>
+      </c>
+      <c r="V10" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="W10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="X10" s="16">
-        <v>88.888888888888886</v>
+        <v>74.074074074074076</v>
       </c>
       <c r="Y10">
-        <v>34637</v>
+        <v>34482</v>
       </c>
       <c r="Z10">
-        <v>3147</v>
+        <v>3179</v>
       </c>
       <c r="AA10">
-        <v>37784</v>
+        <v>37661</v>
       </c>
       <c r="AB10">
-        <v>2378</v>
+        <v>2356</v>
       </c>
       <c r="AC10">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AD10">
-        <v>2784</v>
+        <v>2766</v>
       </c>
       <c r="AE10">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>6</v>
-      </c>
-      <c r="AG10" s="14">
-        <v>48</v>
-      </c>
-      <c r="AH10" s="23">
-        <v>140929100000</v>
-      </c>
-      <c r="AI10" s="23">
-        <v>188170690560</v>
-      </c>
-      <c r="AJ10" s="23">
-        <v>47241590560</v>
+        <v>1</v>
+      </c>
+      <c r="AG10" s="16">
+        <v>46</v>
+      </c>
+      <c r="AH10" s="25">
+        <v>140405200000</v>
+      </c>
+      <c r="AI10" s="25">
+        <v>179714044400</v>
+      </c>
+      <c r="AJ10" s="25">
+        <v>39308844400</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1847,108 +1855,108 @@
         <v>32</v>
       </c>
       <c r="D11">
-        <v>130.11129182217209</v>
+        <v>134.51178644198299</v>
       </c>
       <c r="E11">
-        <v>39708</v>
+        <v>40171</v>
       </c>
       <c r="F11">
-        <v>3321</v>
+        <v>3296</v>
       </c>
       <c r="G11">
-        <v>125.3888888888889</v>
+        <v>126.93333333333329</v>
       </c>
       <c r="H11">
-        <v>11.488888888888891</v>
+        <v>11.455555555555559</v>
       </c>
       <c r="I11">
-        <v>11.488888888888891</v>
+        <v>11.455555555555559</v>
       </c>
       <c r="J11">
-        <v>10.014814814814811</v>
+        <v>10.18888888888889</v>
       </c>
       <c r="K11">
-        <v>0.8037037037037037</v>
+        <v>0.74444444444444446</v>
       </c>
       <c r="L11">
-        <v>0.8037037037037037</v>
+        <v>0.74444444444444446</v>
       </c>
       <c r="M11">
-        <v>0.16666666666666671</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N11">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O11">
-        <v>0.1740740740740741</v>
+      <c r="O11" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P11">
-        <v>124.7962962962963</v>
+        <v>126.4592592592593</v>
       </c>
       <c r="Q11" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="R11">
-        <v>32.962962962962962</v>
+        <v>30</v>
       </c>
       <c r="S11" t="s">
-        <v>42</v>
-      </c>
-      <c r="T11" s="14">
-        <v>57.777777777777771</v>
+        <v>34</v>
+      </c>
+      <c r="T11" s="16">
+        <v>56.296296296296298</v>
       </c>
       <c r="U11" t="s">
-        <v>43</v>
-      </c>
-      <c r="V11" s="14">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V11" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W11" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="X11" s="16">
-        <v>88.888888888888886</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y11">
-        <v>33855</v>
+        <v>34272</v>
       </c>
       <c r="Z11">
-        <v>3102</v>
+        <v>3093</v>
       </c>
       <c r="AA11">
-        <v>36957</v>
+        <v>37365</v>
       </c>
       <c r="AB11">
-        <v>2299</v>
+        <v>2330</v>
       </c>
       <c r="AC11">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="AD11">
-        <v>2704</v>
+        <v>2751</v>
       </c>
       <c r="AE11">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AF11">
         <v>2</v>
       </c>
-      <c r="AG11" s="14">
-        <v>47</v>
-      </c>
-      <c r="AH11" s="23">
-        <v>137704170000</v>
-      </c>
-      <c r="AI11" s="23">
-        <v>179168674480</v>
-      </c>
-      <c r="AJ11" s="23">
-        <v>41464504480</v>
+      <c r="AG11" s="15">
+        <v>55</v>
+      </c>
+      <c r="AH11" s="25">
+        <v>139274940000</v>
+      </c>
+      <c r="AI11" s="25">
+        <v>187341209860</v>
+      </c>
+      <c r="AJ11" s="25">
+        <v>48066269860</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1956,109 +1964,109 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12">
-        <v>132.74475097459981</v>
+      <c r="D12" s="16">
+        <v>130.0389277522836</v>
       </c>
       <c r="E12">
-        <v>38924</v>
+        <v>39838</v>
       </c>
       <c r="F12">
-        <v>3150</v>
+        <v>3333</v>
       </c>
       <c r="G12">
-        <v>123.2518518518519</v>
+        <v>125.8555555555556</v>
       </c>
       <c r="H12">
-        <v>10.84074074074074</v>
+        <v>11.47037037037037</v>
       </c>
       <c r="I12">
-        <v>10.84074074074074</v>
+        <v>11.47037037037037</v>
       </c>
       <c r="J12">
-        <v>9.9</v>
+        <v>10.05925925925926</v>
       </c>
       <c r="K12">
-        <v>0.81111111111111112</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L12">
-        <v>0.81111111111111112</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M12">
-        <v>0.15555555555555561</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N12">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O12" s="14">
-        <v>0.17037037037037039</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O12" s="16">
+        <v>0.162962962962963</v>
       </c>
       <c r="P12">
-        <v>122.8259259259259</v>
+        <v>125.2777777777778</v>
       </c>
       <c r="Q12" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="R12">
-        <v>31.111111111111111</v>
+        <v>30</v>
       </c>
       <c r="S12" t="s">
-        <v>54</v>
-      </c>
-      <c r="T12" s="14">
-        <v>55.185185185185183</v>
+        <v>34</v>
+      </c>
+      <c r="T12" s="16">
+        <v>56.296296296296298</v>
       </c>
       <c r="U12" t="s">
-        <v>35</v>
-      </c>
-      <c r="V12" s="14">
-        <v>88.888888888888886</v>
+        <v>39</v>
+      </c>
+      <c r="V12" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="W12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="X12" s="16">
-        <v>88.888888888888886</v>
+        <v>74.074074074074076</v>
       </c>
       <c r="Y12">
-        <v>33278</v>
+        <v>33981</v>
       </c>
       <c r="Z12">
-        <v>2927</v>
+        <v>3097</v>
       </c>
       <c r="AA12">
-        <v>36205</v>
+        <v>37078</v>
       </c>
       <c r="AB12">
-        <v>2270</v>
+        <v>2307</v>
       </c>
       <c r="AC12">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="AD12">
-        <v>2673</v>
+        <v>2716</v>
       </c>
       <c r="AE12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AF12">
-        <v>4</v>
-      </c>
-      <c r="AG12" s="14">
-        <v>46</v>
-      </c>
-      <c r="AH12" s="23">
-        <v>135086220000</v>
-      </c>
-      <c r="AI12" s="23">
-        <v>179319866340</v>
-      </c>
-      <c r="AJ12" s="23">
-        <v>44233646340</v>
+        <v>3</v>
+      </c>
+      <c r="AG12" s="16">
+        <v>44</v>
+      </c>
+      <c r="AH12" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI12" s="25">
+        <v>179749896960</v>
+      </c>
+      <c r="AJ12" s="25">
+        <v>41522136960</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -2067,31 +2075,31 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <v>134.3712618578823</v>
+        <v>136.78782871800749</v>
       </c>
       <c r="E13">
-        <v>39378</v>
+        <v>39232</v>
       </c>
       <c r="F13">
-        <v>3176</v>
+        <v>3340</v>
       </c>
       <c r="G13">
-        <v>124.6185185185185</v>
+        <v>123.562962962963</v>
       </c>
       <c r="H13">
-        <v>11.011111111111109</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="I13">
-        <v>11.011111111111109</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="J13">
-        <v>10.02962962962963</v>
+        <v>9.9888888888888889</v>
       </c>
       <c r="K13">
-        <v>0.73333333333333328</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="L13">
-        <v>0.73333333333333328</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="M13">
         <v>0.16666666666666671</v>
@@ -2099,53 +2107,53 @@
       <c r="N13">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="16">
         <v>0.1851851851851852</v>
       </c>
       <c r="P13">
-        <v>124.3148148148148</v>
+        <v>123.12222222222221</v>
       </c>
       <c r="Q13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="R13">
-        <v>32.592592592592602</v>
+        <v>30.37037037037037</v>
       </c>
       <c r="S13" t="s">
-        <v>66</v>
-      </c>
-      <c r="T13" s="14">
-        <v>57.407407407407398</v>
+        <v>82</v>
+      </c>
+      <c r="T13" s="18">
+        <v>59.629629629629633</v>
       </c>
       <c r="U13" t="s">
-        <v>35</v>
-      </c>
-      <c r="V13" s="14">
-        <v>88.888888888888886</v>
+        <v>61</v>
+      </c>
+      <c r="V13" s="27">
+        <v>96.296296296296291</v>
       </c>
       <c r="W13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X13" s="16">
-        <v>88.888888888888886</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y13">
-        <v>33647</v>
+        <v>33362</v>
       </c>
       <c r="Z13">
-        <v>2973</v>
+        <v>3123</v>
       </c>
       <c r="AA13">
-        <v>36620</v>
+        <v>36485</v>
       </c>
       <c r="AB13">
-        <v>2310</v>
+        <v>2285</v>
       </c>
       <c r="AC13">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="AD13">
-        <v>2708</v>
+        <v>2697</v>
       </c>
       <c r="AE13">
         <v>45</v>
@@ -2153,22 +2161,22 @@
       <c r="AF13">
         <v>5</v>
       </c>
-      <c r="AG13" s="13">
+      <c r="AG13" s="15">
         <v>50</v>
       </c>
-      <c r="AH13" s="23">
-        <v>136656990000</v>
-      </c>
-      <c r="AI13" s="23">
-        <v>183627721880</v>
-      </c>
-      <c r="AJ13" s="23">
-        <v>46970731880</v>
+      <c r="AH13" s="25">
+        <v>136133400000</v>
+      </c>
+      <c r="AI13" s="25">
+        <v>186213922020</v>
+      </c>
+      <c r="AJ13" s="25">
+        <v>50080522020</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>52</v>
+      <c r="A14" s="16">
+        <v>51</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -2176,32 +2184,32 @@
       <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14">
-        <v>133.9150640652789</v>
+      <c r="D14" s="16">
+        <v>136.6510792588615</v>
       </c>
       <c r="E14">
-        <v>39831</v>
+        <v>38930</v>
       </c>
       <c r="F14">
-        <v>3196</v>
+        <v>3268</v>
       </c>
       <c r="G14">
-        <v>126.1259259259259</v>
+        <v>122.762962962963</v>
       </c>
       <c r="H14">
-        <v>11.07037037037037</v>
+        <v>11.31851851851852</v>
       </c>
       <c r="I14">
-        <v>11.07037037037037</v>
+        <v>11.31851851851852</v>
       </c>
       <c r="J14">
-        <v>10.140740740740741</v>
+        <v>9.9185185185185194</v>
       </c>
       <c r="K14">
-        <v>0.74814814814814812</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="L14">
-        <v>0.74814814814814812</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="M14">
         <v>0.16666666666666671</v>
@@ -2209,53 +2217,53 @@
       <c r="N14">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="16">
         <v>0.1851851851851852</v>
       </c>
       <c r="P14">
-        <v>125.8</v>
+        <v>122.35185185185181</v>
       </c>
       <c r="Q14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="R14">
-        <v>32.592592592592602</v>
+        <v>30.37037037037037</v>
       </c>
       <c r="S14" t="s">
-        <v>68</v>
-      </c>
-      <c r="T14" s="14">
-        <v>58.148148148148152</v>
+        <v>77</v>
+      </c>
+      <c r="T14" s="18">
+        <v>58.518518518518512</v>
       </c>
       <c r="U14" t="s">
-        <v>35</v>
-      </c>
-      <c r="V14" s="14">
-        <v>88.888888888888886</v>
+        <v>60</v>
+      </c>
+      <c r="V14" s="15">
+        <v>100</v>
       </c>
       <c r="W14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X14" s="16">
-        <v>88.888888888888886</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y14">
-        <v>34054</v>
+        <v>33146</v>
       </c>
       <c r="Z14">
-        <v>2989</v>
+        <v>3056</v>
       </c>
       <c r="AA14">
-        <v>37043</v>
+        <v>36202</v>
       </c>
       <c r="AB14">
-        <v>2336</v>
+        <v>2271</v>
       </c>
       <c r="AC14">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AD14">
-        <v>2738</v>
+        <v>2678</v>
       </c>
       <c r="AE14">
         <v>45</v>
@@ -2263,22 +2271,22 @@
       <c r="AF14">
         <v>5</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AG14" s="15">
         <v>50</v>
       </c>
-      <c r="AH14" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI14" s="23">
-        <v>185107793360</v>
-      </c>
-      <c r="AJ14" s="23">
-        <v>46880033360</v>
+      <c r="AH14" s="25">
+        <v>135086220000</v>
+      </c>
+      <c r="AI14" s="25">
+        <v>184596777560</v>
+      </c>
+      <c r="AJ14" s="25">
+        <v>49510557560</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>51</v>
+      <c r="A15" s="13">
+        <v>45</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2286,26 +2294,26 @@
       <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="D15">
-        <v>136.6510792588615</v>
+      <c r="D15" s="15">
+        <v>140.26478090942081</v>
       </c>
       <c r="E15">
-        <v>38930</v>
+        <v>39870</v>
       </c>
       <c r="F15">
-        <v>3268</v>
+        <v>3318</v>
       </c>
       <c r="G15">
-        <v>122.762962962963</v>
+        <v>125.84444444444441</v>
       </c>
       <c r="H15">
-        <v>11.31851851851852</v>
+        <v>11.5</v>
       </c>
       <c r="I15">
-        <v>11.31851851851852</v>
+        <v>11.5</v>
       </c>
       <c r="J15">
-        <v>9.9185185185185194</v>
+        <v>10.11851851851852</v>
       </c>
       <c r="K15">
         <v>0.76666666666666672</v>
@@ -2314,81 +2322,81 @@
         <v>0.76666666666666672</v>
       </c>
       <c r="M15">
-        <v>0.16666666666666671</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N15">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O15">
-        <v>0.1851851851851852</v>
+        <v>2.222222222222222E-2</v>
+      </c>
+      <c r="O15" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P15">
-        <v>122.35185185185181</v>
+        <v>125.3185185185185</v>
       </c>
       <c r="Q15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R15">
-        <v>30.37037037037037</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T15" s="14">
-        <v>58.518518518518512</v>
+        <v>59</v>
+      </c>
+      <c r="T15" s="16">
+        <v>56.666666666666657</v>
       </c>
       <c r="U15" t="s">
         <v>60</v>
       </c>
-      <c r="V15" s="13">
+      <c r="V15" s="15">
         <v>100</v>
       </c>
       <c r="W15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X15" s="14">
-        <v>85.18518518518519</v>
+        <v>43</v>
+      </c>
+      <c r="X15" s="15">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y15">
-        <v>33146</v>
+        <v>33978</v>
       </c>
       <c r="Z15">
-        <v>3056</v>
+        <v>3105</v>
       </c>
       <c r="AA15">
-        <v>36202</v>
+        <v>37083</v>
       </c>
       <c r="AB15">
-        <v>2271</v>
+        <v>2305</v>
       </c>
       <c r="AC15">
         <v>207</v>
       </c>
       <c r="AD15">
-        <v>2678</v>
+        <v>2732</v>
       </c>
       <c r="AE15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF15">
-        <v>5</v>
-      </c>
-      <c r="AG15" s="13">
-        <v>50</v>
-      </c>
-      <c r="AH15" s="23">
-        <v>135086220000</v>
-      </c>
-      <c r="AI15" s="23">
-        <v>184596777560</v>
-      </c>
-      <c r="AJ15" s="23">
-        <v>49510557560</v>
+        <v>6</v>
+      </c>
+      <c r="AG15" s="15">
+        <v>55</v>
+      </c>
+      <c r="AH15" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI15" s="25">
+        <v>193884864720</v>
+      </c>
+      <c r="AJ15" s="26">
+        <v>55657104720</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>27</v>
+      <c r="A16" s="13">
+        <v>50</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -2396,109 +2404,109 @@
       <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16">
-        <v>129.5895794031575</v>
+      <c r="D16" s="18">
+        <v>137.30931200811611</v>
       </c>
       <c r="E16">
-        <v>40134</v>
+        <v>39438</v>
       </c>
       <c r="F16">
-        <v>3275</v>
+        <v>3306</v>
       </c>
       <c r="G16">
-        <v>126.8555555555556</v>
+        <v>124.4296296296296</v>
       </c>
       <c r="H16">
-        <v>11.366666666666671</v>
+        <v>11.459259259259261</v>
       </c>
       <c r="I16">
-        <v>11.366666666666671</v>
+        <v>11.459259259259261</v>
       </c>
       <c r="J16">
-        <v>10.237037037037039</v>
+        <v>9.981481481481481</v>
       </c>
       <c r="K16">
-        <v>0.7592592592592593</v>
+        <v>0.77037037037037037</v>
       </c>
       <c r="L16">
-        <v>0.7592592592592593</v>
+        <v>0.77037037037037037</v>
       </c>
       <c r="M16">
         <v>0.18148148148148149</v>
       </c>
       <c r="N16">
-        <v>3.7037037037037038E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O16">
-        <v>0.1851851851851852</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P16">
-        <v>126.537037037037</v>
+        <v>123.8185185185185</v>
       </c>
       <c r="Q16" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="R16">
-        <v>33.333333333333329</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S16" t="s">
-        <v>71</v>
-      </c>
-      <c r="T16" s="14">
-        <v>53.703703703703709</v>
+        <v>48</v>
+      </c>
+      <c r="T16" s="16">
+        <v>55.925925925925917</v>
       </c>
       <c r="U16" t="s">
         <v>61</v>
       </c>
-      <c r="V16" s="25">
+      <c r="V16" s="27">
         <v>96.296296296296291</v>
       </c>
       <c r="W16" t="s">
         <v>39</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="16">
         <v>85.18518518518519</v>
       </c>
       <c r="Y16">
-        <v>34251</v>
+        <v>33596</v>
       </c>
       <c r="Z16">
-        <v>3069</v>
+        <v>3094</v>
       </c>
       <c r="AA16">
-        <v>37320</v>
+        <v>36690</v>
       </c>
       <c r="AB16">
-        <v>2359</v>
+        <v>2275</v>
       </c>
       <c r="AC16">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AD16">
-        <v>2764</v>
+        <v>2695</v>
       </c>
       <c r="AE16">
         <v>49</v>
       </c>
       <c r="AF16">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="13">
-        <v>50</v>
-      </c>
-      <c r="AH16" s="23">
-        <v>139274940000</v>
-      </c>
-      <c r="AI16" s="23">
-        <v>180485808960</v>
-      </c>
-      <c r="AJ16" s="23">
-        <v>41210868960</v>
+        <v>4</v>
+      </c>
+      <c r="AG16" s="15">
+        <v>53</v>
+      </c>
+      <c r="AH16" s="25">
+        <v>136656990000</v>
+      </c>
+      <c r="AI16" s="25">
+        <v>187642772780</v>
+      </c>
+      <c r="AJ16" s="26">
+        <v>50985782780</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>43</v>
+      <c r="A17" s="16">
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -2506,109 +2514,109 @@
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17">
-        <v>136.78782871800749</v>
+      <c r="D17" s="16">
+        <v>119.7483337771863</v>
       </c>
       <c r="E17">
-        <v>39232</v>
+        <v>40221</v>
       </c>
       <c r="F17">
-        <v>3340</v>
+        <v>3383</v>
       </c>
       <c r="G17">
-        <v>123.562962962963</v>
+        <v>126.8888888888889</v>
       </c>
       <c r="H17">
-        <v>11.56666666666667</v>
+        <v>11.714814814814821</v>
       </c>
       <c r="I17">
-        <v>11.56666666666667</v>
+        <v>11.714814814814821</v>
       </c>
       <c r="J17">
-        <v>9.9888888888888889</v>
+        <v>10.22222222222222</v>
       </c>
       <c r="K17">
-        <v>0.78518518518518521</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="L17">
-        <v>0.78518518518518521</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="M17">
-        <v>0.16666666666666671</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N17">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O17">
-        <v>0.1851851851851852</v>
+        <v>0</v>
+      </c>
+      <c r="O17" s="16">
+        <v>0.14074074074074069</v>
       </c>
       <c r="P17">
-        <v>123.12222222222221</v>
+        <v>126.65555555555559</v>
       </c>
       <c r="Q17" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="R17">
-        <v>30.37037037037037</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S17" t="s">
-        <v>82</v>
-      </c>
-      <c r="T17">
-        <v>59.629629629629633</v>
+        <v>68</v>
+      </c>
+      <c r="T17" s="18">
+        <v>58.148148148148152</v>
       </c>
       <c r="U17" t="s">
-        <v>61</v>
-      </c>
-      <c r="V17" s="25">
-        <v>96.296296296296291</v>
+        <v>43</v>
+      </c>
+      <c r="V17" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W17" t="s">
-        <v>39</v>
-      </c>
-      <c r="X17" s="14">
-        <v>85.18518518518519</v>
+        <v>36</v>
+      </c>
+      <c r="X17" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y17">
-        <v>33362</v>
+        <v>34260</v>
       </c>
       <c r="Z17">
-        <v>3123</v>
+        <v>3163</v>
       </c>
       <c r="AA17">
-        <v>36485</v>
+        <v>37423</v>
       </c>
       <c r="AB17">
-        <v>2285</v>
+        <v>2388</v>
       </c>
       <c r="AC17">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="AD17">
-        <v>2697</v>
+        <v>2760</v>
       </c>
       <c r="AE17">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AF17">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="13">
-        <v>50</v>
-      </c>
-      <c r="AH17" s="23">
-        <v>136133400000</v>
-      </c>
-      <c r="AI17" s="23">
-        <v>186213922020</v>
-      </c>
-      <c r="AJ17" s="23">
-        <v>50080522020</v>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="16">
+        <v>38</v>
+      </c>
+      <c r="AH17" s="25">
+        <v>139798530000</v>
+      </c>
+      <c r="AI17" s="25">
+        <v>167406410320</v>
+      </c>
+      <c r="AJ17" s="25">
+        <v>27607880320</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -2617,108 +2625,108 @@
         <v>32</v>
       </c>
       <c r="D18">
-        <v>137.30931200811611</v>
+        <v>132.74475097459981</v>
       </c>
       <c r="E18">
-        <v>39438</v>
+        <v>38924</v>
       </c>
       <c r="F18">
-        <v>3306</v>
+        <v>3150</v>
       </c>
       <c r="G18">
-        <v>124.4296296296296</v>
+        <v>123.2518518518519</v>
       </c>
       <c r="H18">
-        <v>11.459259259259261</v>
+        <v>10.84074074074074</v>
       </c>
       <c r="I18">
-        <v>11.459259259259261</v>
+        <v>10.84074074074074</v>
       </c>
       <c r="J18">
-        <v>9.981481481481481</v>
+        <v>9.9</v>
       </c>
       <c r="K18">
-        <v>0.77037037037037037</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L18">
-        <v>0.77037037037037037</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M18">
-        <v>0.18148148148148149</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N18">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O18">
-        <v>0.1962962962962963</v>
+      <c r="O18" s="16">
+        <v>0.17037037037037039</v>
       </c>
       <c r="P18">
-        <v>123.8185185185185</v>
+        <v>122.8259259259259</v>
       </c>
       <c r="Q18" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="R18">
-        <v>30.74074074074074</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="T18">
-        <v>55.925925925925917</v>
+        <v>55.185185185185183</v>
       </c>
       <c r="U18" t="s">
-        <v>61</v>
-      </c>
-      <c r="V18" s="25">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V18" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W18" t="s">
-        <v>39</v>
-      </c>
-      <c r="X18" s="14">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="X18" s="18">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y18">
-        <v>33596</v>
+        <v>33278</v>
       </c>
       <c r="Z18">
-        <v>3094</v>
+        <v>2927</v>
       </c>
       <c r="AA18">
-        <v>36690</v>
+        <v>36205</v>
       </c>
       <c r="AB18">
-        <v>2275</v>
+        <v>2270</v>
       </c>
       <c r="AC18">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="AD18">
-        <v>2695</v>
+        <v>2673</v>
       </c>
       <c r="AE18">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AF18">
         <v>4</v>
       </c>
-      <c r="AG18" s="13">
-        <v>53</v>
-      </c>
-      <c r="AH18" s="23">
-        <v>136656990000</v>
-      </c>
-      <c r="AI18" s="23">
-        <v>187642772780</v>
-      </c>
-      <c r="AJ18" s="24">
-        <v>50985782780</v>
+      <c r="AG18" s="16">
+        <v>46</v>
+      </c>
+      <c r="AH18" s="25">
+        <v>135086220000</v>
+      </c>
+      <c r="AI18" s="25">
+        <v>179319866340</v>
+      </c>
+      <c r="AJ18" s="25">
+        <v>44233646340</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>26</v>
+      <c r="A19" s="13">
+        <v>10</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -2726,109 +2734,109 @@
       <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="D19">
-        <v>130.3964865868046</v>
+      <c r="D19" s="18">
+        <v>137.53042073480651</v>
       </c>
       <c r="E19">
-        <v>40277</v>
+        <v>40474</v>
       </c>
       <c r="F19">
-        <v>3252</v>
+        <v>3338</v>
       </c>
       <c r="G19">
-        <v>127.5222222222222</v>
+        <v>127.9296296296296</v>
       </c>
       <c r="H19">
-        <v>11.21111111111111</v>
+        <v>11.53333333333333</v>
       </c>
       <c r="I19">
-        <v>11.21111111111111</v>
+        <v>11.53333333333333</v>
       </c>
       <c r="J19">
-        <v>10.262962962962961</v>
+        <v>10.24814814814815</v>
       </c>
       <c r="K19">
-        <v>0.82592592592592595</v>
+        <v>0.80740740740740746</v>
       </c>
       <c r="L19">
-        <v>0.82592592592592595</v>
+        <v>0.80740740740740746</v>
       </c>
       <c r="M19">
         <v>0.17037037037037039</v>
       </c>
       <c r="N19">
-        <v>7.4074074074074077E-3</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O19">
-        <v>0.17777777777777781</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P19">
-        <v>127.137037037037</v>
+        <v>127.34444444444441</v>
       </c>
       <c r="Q19" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="R19">
-        <v>34.814814814814817</v>
+        <v>31.481481481481481</v>
       </c>
       <c r="S19" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="T19">
-        <v>53.333333333333343</v>
+        <v>56.296296296296298</v>
       </c>
       <c r="U19" t="s">
-        <v>43</v>
-      </c>
-      <c r="V19">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V19" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W19" t="s">
-        <v>39</v>
-      </c>
-      <c r="X19">
-        <v>85.18518518518519</v>
+        <v>36</v>
+      </c>
+      <c r="X19" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y19">
-        <v>34431</v>
+        <v>34541</v>
       </c>
       <c r="Z19">
-        <v>3027</v>
+        <v>3114</v>
       </c>
       <c r="AA19">
-        <v>37458</v>
+        <v>37655</v>
       </c>
       <c r="AB19">
-        <v>2356</v>
+        <v>2341</v>
       </c>
       <c r="AC19">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AD19">
-        <v>2771</v>
+        <v>2767</v>
       </c>
       <c r="AE19">
         <v>46</v>
       </c>
       <c r="AF19">
-        <v>2</v>
-      </c>
-      <c r="AG19" s="14">
-        <v>48</v>
-      </c>
-      <c r="AH19" s="23">
-        <v>139798530000</v>
-      </c>
-      <c r="AI19" s="23">
-        <v>182292371420</v>
-      </c>
-      <c r="AJ19" s="23">
-        <v>42493841420</v>
+        <v>6</v>
+      </c>
+      <c r="AG19" s="15">
+        <v>52</v>
+      </c>
+      <c r="AH19" s="25">
+        <v>140322120000</v>
+      </c>
+      <c r="AI19" s="25">
+        <v>192985602020</v>
+      </c>
+      <c r="AJ19" s="26">
+        <v>52663482020</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>38</v>
+      <c r="A20" s="16">
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -2836,109 +2844,109 @@
       <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="D20">
-        <v>132.1378544088796</v>
+      <c r="D20" s="16">
+        <v>127.35634020257579</v>
       </c>
       <c r="E20">
-        <v>40145</v>
+        <v>39835</v>
       </c>
       <c r="F20">
-        <v>3373</v>
+        <v>3285</v>
       </c>
       <c r="G20">
-        <v>126.6888888888889</v>
+        <v>125.937037037037</v>
       </c>
       <c r="H20">
-        <v>11.670370370370369</v>
+        <v>11.34444444444444</v>
       </c>
       <c r="I20">
-        <v>11.670370370370369</v>
+        <v>11.34444444444444</v>
       </c>
       <c r="J20">
-        <v>10.162962962962959</v>
+        <v>10.08888888888889</v>
       </c>
       <c r="K20">
-        <v>0.79629629629629628</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L20">
-        <v>0.79629629629629628</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M20">
-        <v>0.13703703703703701</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="N20">
-        <v>2.5925925925925929E-2</v>
-      </c>
-      <c r="O20" s="14">
-        <v>0.162962962962963</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O20" s="16">
+        <v>0.16666666666666671</v>
       </c>
       <c r="P20">
-        <v>126.2518518518519</v>
+        <v>125.462962962963</v>
       </c>
       <c r="Q20" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="R20">
-        <v>32.592592592592602</v>
+        <v>31.481481481481481</v>
       </c>
       <c r="S20" t="s">
-        <v>78</v>
-      </c>
-      <c r="T20" s="14">
-        <v>57.037037037037038</v>
+        <v>54</v>
+      </c>
+      <c r="T20" s="16">
+        <v>55.185185185185183</v>
       </c>
       <c r="U20" t="s">
-        <v>43</v>
-      </c>
-      <c r="V20">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V20" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W20" t="s">
-        <v>39</v>
-      </c>
-      <c r="X20" s="14">
-        <v>85.18518518518519</v>
+        <v>36</v>
+      </c>
+      <c r="X20" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y20">
-        <v>34206</v>
+        <v>34003</v>
       </c>
       <c r="Z20">
-        <v>3151</v>
+        <v>3063</v>
       </c>
       <c r="AA20">
-        <v>37357</v>
+        <v>37066</v>
       </c>
       <c r="AB20">
-        <v>2353</v>
+        <v>2323</v>
       </c>
       <c r="AC20">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AD20">
-        <v>2744</v>
+        <v>2724</v>
       </c>
       <c r="AE20">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AF20">
-        <v>7</v>
-      </c>
-      <c r="AG20" s="14">
-        <v>44</v>
-      </c>
-      <c r="AH20" s="23">
-        <v>139357400000</v>
-      </c>
-      <c r="AI20" s="23">
-        <v>184143878320</v>
-      </c>
-      <c r="AJ20" s="23">
-        <v>44786478320</v>
+        <v>1</v>
+      </c>
+      <c r="AG20" s="16">
+        <v>45</v>
+      </c>
+      <c r="AH20" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI20" s="25">
+        <v>176041816280</v>
+      </c>
+      <c r="AJ20" s="25">
+        <v>37814056280</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -2947,108 +2955,108 @@
         <v>32</v>
       </c>
       <c r="D21">
-        <v>137.87772288176649</v>
+        <v>126.46334539823501</v>
       </c>
       <c r="E21">
-        <v>39534</v>
+        <v>40147</v>
       </c>
       <c r="F21">
-        <v>3291</v>
+        <v>3366</v>
       </c>
       <c r="G21">
-        <v>124.8148148148148</v>
+        <v>126.7703703703704</v>
       </c>
       <c r="H21">
-        <v>11.34814814814815</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I21">
-        <v>11.34814814814815</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J21">
-        <v>10.07037037037037</v>
+        <v>10.15925925925926</v>
       </c>
       <c r="K21">
-        <v>0.82222222222222219</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="L21">
-        <v>0.82222222222222219</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="M21">
-        <v>0.17037037037037039</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="N21">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O21" s="14">
-        <v>0.18888888888888891</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O21" s="16">
+        <v>0.15555555555555561</v>
       </c>
       <c r="P21">
-        <v>124.39259259259261</v>
+        <v>126.2703703703704</v>
       </c>
       <c r="Q21" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R21">
-        <v>29.25925925925926</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="S21" t="s">
-        <v>75</v>
-      </c>
-      <c r="T21" s="13">
-        <v>62.592592592592588</v>
+        <v>54</v>
+      </c>
+      <c r="T21" s="16">
+        <v>55.185185185185183</v>
       </c>
       <c r="U21" t="s">
-        <v>43</v>
-      </c>
-      <c r="V21" s="14">
-        <v>92.592592592592595</v>
+        <v>61</v>
+      </c>
+      <c r="V21" s="27">
+        <v>96.296296296296291</v>
       </c>
       <c r="W21" t="s">
-        <v>39</v>
-      </c>
-      <c r="X21" s="14">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="X21" s="18">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y21">
-        <v>33700</v>
+        <v>34228</v>
       </c>
       <c r="Z21">
-        <v>3064</v>
+        <v>3134</v>
       </c>
       <c r="AA21">
-        <v>36764</v>
+        <v>37362</v>
       </c>
       <c r="AB21">
-        <v>2293</v>
+        <v>2345</v>
       </c>
       <c r="AC21">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="AD21">
-        <v>2719</v>
+        <v>2743</v>
       </c>
       <c r="AE21">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF21">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="13">
-        <v>51</v>
-      </c>
-      <c r="AH21" s="23">
-        <v>137180580000</v>
-      </c>
-      <c r="AI21" s="23">
-        <v>189141459940</v>
-      </c>
-      <c r="AJ21" s="24">
-        <v>51960879940</v>
+        <v>2</v>
+      </c>
+      <c r="AG21" s="16">
+        <v>42</v>
+      </c>
+      <c r="AH21" s="25">
+        <v>139357400000</v>
+      </c>
+      <c r="AI21" s="25">
+        <v>176236030100</v>
+      </c>
+      <c r="AJ21" s="25">
+        <v>36878630100</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -3057,108 +3065,108 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>132.19259139829359</v>
+        <v>126.5557330358163</v>
       </c>
       <c r="E22">
-        <v>38919</v>
+        <v>40535</v>
       </c>
       <c r="F22">
-        <v>3226</v>
+        <v>3327</v>
       </c>
       <c r="G22">
-        <v>122.8185185185185</v>
+        <v>128.15185185185189</v>
       </c>
       <c r="H22">
-        <v>11.207407407407411</v>
+        <v>11.474074074074069</v>
       </c>
       <c r="I22">
-        <v>11.207407407407411</v>
+        <v>11.474074074074069</v>
       </c>
       <c r="J22">
-        <v>9.9333333333333336</v>
+        <v>10.351851851851849</v>
       </c>
       <c r="K22">
-        <v>0.73333333333333328</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L22">
-        <v>0.73333333333333328</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M22">
-        <v>0.17777777777777781</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N22">
-        <v>7.4074074074074077E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O22">
-        <v>0.1851851851851852</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="P22">
-        <v>122.537037037037</v>
+        <v>127.9037037037037</v>
       </c>
       <c r="Q22" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="R22">
-        <v>29.62962962962963</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="S22" t="s">
-        <v>59</v>
-      </c>
-      <c r="T22" s="14">
-        <v>56.666666666666657</v>
+        <v>70</v>
+      </c>
+      <c r="T22" s="16">
+        <v>53.333333333333343</v>
       </c>
       <c r="U22" t="s">
-        <v>43</v>
-      </c>
-      <c r="V22">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V22" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W22" t="s">
-        <v>39</v>
-      </c>
-      <c r="X22" s="14">
-        <v>85.18518518518519</v>
+        <v>57</v>
+      </c>
+      <c r="X22" s="16">
+        <v>70.370370370370367</v>
       </c>
       <c r="Y22">
-        <v>33161</v>
+        <v>34601</v>
       </c>
       <c r="Z22">
-        <v>3026</v>
+        <v>3098</v>
       </c>
       <c r="AA22">
-        <v>36187</v>
+        <v>37699</v>
       </c>
       <c r="AB22">
-        <v>2284</v>
+        <v>2406</v>
       </c>
       <c r="AC22">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="AD22">
-        <v>2682</v>
+        <v>2795</v>
       </c>
       <c r="AE22">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="AF22">
-        <v>2</v>
-      </c>
-      <c r="AG22" s="13">
-        <v>50</v>
-      </c>
-      <c r="AH22" s="23">
-        <v>135086220000</v>
-      </c>
-      <c r="AI22" s="23">
-        <v>178573974840</v>
-      </c>
-      <c r="AJ22" s="23">
-        <v>43487754840</v>
+        <v>4</v>
+      </c>
+      <c r="AG22" s="16">
+        <v>41</v>
+      </c>
+      <c r="AH22" s="25">
+        <v>140845710000</v>
+      </c>
+      <c r="AI22" s="25">
+        <v>178248320740</v>
+      </c>
+      <c r="AJ22" s="25">
+        <v>37402610740</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>16</v>
+      <c r="A23" s="16">
+        <v>52</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -3166,26 +3174,26 @@
       <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="D23">
-        <v>132.08064457873661</v>
+      <c r="D23" s="16">
+        <v>133.9150640652789</v>
       </c>
       <c r="E23">
-        <v>39075</v>
+        <v>39831</v>
       </c>
       <c r="F23">
-        <v>3261</v>
+        <v>3196</v>
       </c>
       <c r="G23">
-        <v>123.34444444444441</v>
+        <v>126.1259259259259</v>
       </c>
       <c r="H23">
-        <v>11.31111111111111</v>
+        <v>11.07037037037037</v>
       </c>
       <c r="I23">
-        <v>11.31111111111111</v>
+        <v>11.07037037037037</v>
       </c>
       <c r="J23">
-        <v>9.8962962962962955</v>
+        <v>10.140740740740741</v>
       </c>
       <c r="K23">
         <v>0.74814814814814812</v>
@@ -3194,81 +3202,81 @@
         <v>0.74814814814814812</v>
       </c>
       <c r="M23">
-        <v>0.15185185185185179</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N23">
         <v>1.8518518518518521E-2</v>
       </c>
       <c r="O23">
-        <v>0.17037037037037039</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="P23">
-        <v>122.937037037037</v>
+        <v>125.8</v>
       </c>
       <c r="Q23" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="R23">
-        <v>33.333333333333329</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S23" t="s">
-        <v>51</v>
-      </c>
-      <c r="T23" s="14">
-        <v>54.444444444444443</v>
+        <v>68</v>
+      </c>
+      <c r="T23" s="18">
+        <v>58.148148148148152</v>
       </c>
       <c r="U23" t="s">
         <v>35</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="16">
         <v>88.888888888888886</v>
       </c>
       <c r="W23" t="s">
-        <v>39</v>
-      </c>
-      <c r="X23" s="14">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="X23" s="18">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y23">
-        <v>33303</v>
+        <v>34054</v>
       </c>
       <c r="Z23">
-        <v>3054</v>
+        <v>2989</v>
       </c>
       <c r="AA23">
-        <v>36357</v>
+        <v>37043</v>
       </c>
       <c r="AB23">
-        <v>2286</v>
+        <v>2336</v>
       </c>
       <c r="AC23">
         <v>202</v>
       </c>
       <c r="AD23">
-        <v>2672</v>
+        <v>2738</v>
       </c>
       <c r="AE23">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AF23">
         <v>5</v>
       </c>
-      <c r="AG23" s="14">
-        <v>46</v>
-      </c>
-      <c r="AH23" s="23">
-        <v>135609810000</v>
-      </c>
-      <c r="AI23" s="23">
-        <v>179114311160</v>
-      </c>
-      <c r="AJ23" s="23">
-        <v>43504501160</v>
+      <c r="AG23" s="15">
+        <v>50</v>
+      </c>
+      <c r="AH23" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI23" s="25">
+        <v>185107793360</v>
+      </c>
+      <c r="AJ23" s="25">
+        <v>46880033360</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>40</v>
+      <c r="A24" s="16">
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -3276,109 +3284,109 @@
       <c r="C24" t="s">
         <v>32</v>
       </c>
-      <c r="D24">
-        <v>131.30610870598051</v>
+      <c r="D24" s="16">
+        <v>134.3712618578823</v>
       </c>
       <c r="E24">
-        <v>38933</v>
+        <v>39378</v>
       </c>
       <c r="F24">
-        <v>3060</v>
+        <v>3176</v>
       </c>
       <c r="G24">
-        <v>123.537037037037</v>
+        <v>124.6185185185185</v>
       </c>
       <c r="H24">
-        <v>10.56296296296296</v>
+        <v>11.011111111111109</v>
       </c>
       <c r="I24">
-        <v>10.56296296296296</v>
+        <v>11.011111111111109</v>
       </c>
       <c r="J24">
-        <v>9.9111111111111114</v>
+        <v>10.02962962962963</v>
       </c>
       <c r="K24">
-        <v>0.76666666666666672</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L24">
-        <v>0.76666666666666672</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M24">
-        <v>0.18148148148148149</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N24">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O24" s="14">
+        <v>1.8518518518518521E-2</v>
+      </c>
+      <c r="O24" s="16">
         <v>0.1851851851851852</v>
       </c>
       <c r="P24">
-        <v>123.1740740740741</v>
+        <v>124.3148148148148</v>
       </c>
       <c r="Q24" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R24">
-        <v>29.25925925925926</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S24" t="s">
-        <v>45</v>
-      </c>
-      <c r="T24">
-        <v>54.814814814814817</v>
+        <v>66</v>
+      </c>
+      <c r="T24" s="16">
+        <v>57.407407407407398</v>
       </c>
       <c r="U24" t="s">
         <v>35</v>
       </c>
-      <c r="V24" s="14">
+      <c r="V24" s="16">
         <v>88.888888888888886</v>
       </c>
       <c r="W24" t="s">
-        <v>39</v>
-      </c>
-      <c r="X24" s="14">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="X24" s="18">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y24">
-        <v>33355</v>
+        <v>33647</v>
       </c>
       <c r="Z24">
-        <v>2852</v>
+        <v>2973</v>
       </c>
       <c r="AA24">
-        <v>36207</v>
+        <v>36620</v>
       </c>
       <c r="AB24">
-        <v>2269</v>
+        <v>2310</v>
       </c>
       <c r="AC24">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AD24">
-        <v>2676</v>
+        <v>2708</v>
       </c>
       <c r="AE24">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="13">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="15">
         <v>50</v>
       </c>
-      <c r="AH24" s="23">
-        <v>135086220000</v>
-      </c>
-      <c r="AI24" s="23">
-        <v>177376458880</v>
-      </c>
-      <c r="AJ24" s="23">
-        <v>42290238880</v>
+      <c r="AH24" s="25">
+        <v>136656990000</v>
+      </c>
+      <c r="AI24" s="25">
+        <v>183627721880</v>
+      </c>
+      <c r="AJ24" s="25">
+        <v>46970731880</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -3387,43 +3395,43 @@
         <v>32</v>
       </c>
       <c r="D25">
-        <v>137.242098764888</v>
+        <v>132.1378544088796</v>
       </c>
       <c r="E25">
-        <v>39296</v>
+        <v>40145</v>
       </c>
       <c r="F25">
-        <v>3250</v>
+        <v>3373</v>
       </c>
       <c r="G25">
-        <v>124.1111111111111</v>
+        <v>126.6888888888889</v>
       </c>
       <c r="H25">
-        <v>11.28888888888889</v>
+        <v>11.670370370370369</v>
       </c>
       <c r="I25">
-        <v>11.28888888888889</v>
+        <v>11.670370370370369</v>
       </c>
       <c r="J25">
-        <v>9.9407407407407415</v>
+        <v>10.162962962962959</v>
       </c>
       <c r="K25">
-        <v>0.73333333333333328</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L25">
-        <v>0.73333333333333328</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M25">
-        <v>0.1851851851851852</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N25">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O25" s="13">
-        <v>0.2</v>
+        <v>2.5925925925925929E-2</v>
+      </c>
+      <c r="O25" s="16">
+        <v>0.162962962962963</v>
       </c>
       <c r="P25">
-        <v>123.51111111111111</v>
+        <v>126.2518518518519</v>
       </c>
       <c r="Q25" t="s">
         <v>76</v>
@@ -3432,63 +3440,63 @@
         <v>32.592592592592602</v>
       </c>
       <c r="S25" t="s">
-        <v>89</v>
-      </c>
-      <c r="T25" s="14">
-        <v>54.074074074074083</v>
+        <v>78</v>
+      </c>
+      <c r="T25" s="16">
+        <v>57.037037037037038</v>
       </c>
       <c r="U25" t="s">
-        <v>39</v>
-      </c>
-      <c r="V25" s="14">
-        <v>85.18518518518519</v>
+        <v>43</v>
+      </c>
+      <c r="V25" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W25" t="s">
         <v>39</v>
       </c>
-      <c r="X25" s="14">
+      <c r="X25" s="16">
         <v>85.18518518518519</v>
       </c>
       <c r="Y25">
-        <v>33510</v>
+        <v>34206</v>
       </c>
       <c r="Z25">
-        <v>3048</v>
+        <v>3151</v>
       </c>
       <c r="AA25">
-        <v>36558</v>
+        <v>37357</v>
       </c>
       <c r="AB25">
-        <v>2270</v>
+        <v>2353</v>
       </c>
       <c r="AC25">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="AD25">
-        <v>2684</v>
+        <v>2744</v>
       </c>
       <c r="AE25">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="AF25">
-        <v>4</v>
-      </c>
-      <c r="AG25" s="13">
-        <v>54</v>
-      </c>
-      <c r="AH25" s="23">
-        <v>136133400000</v>
-      </c>
-      <c r="AI25" s="23">
-        <v>186832335280</v>
-      </c>
-      <c r="AJ25" s="24">
-        <v>50698935280</v>
+        <v>7</v>
+      </c>
+      <c r="AG25" s="16">
+        <v>44</v>
+      </c>
+      <c r="AH25" s="25">
+        <v>139357400000</v>
+      </c>
+      <c r="AI25" s="25">
+        <v>184143878320</v>
+      </c>
+      <c r="AJ25" s="25">
+        <v>44786478320</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -3497,108 +3505,108 @@
         <v>32</v>
       </c>
       <c r="D26">
-        <v>128.7079858947466</v>
+        <v>123.99196438593439</v>
       </c>
       <c r="E26">
-        <v>38741</v>
+        <v>40437</v>
       </c>
       <c r="F26">
-        <v>3218</v>
+        <v>3431</v>
       </c>
       <c r="G26">
-        <v>122.4</v>
+        <v>127.4777777777778</v>
       </c>
       <c r="H26">
-        <v>11.0962962962963</v>
+        <v>11.896296296296301</v>
       </c>
       <c r="I26">
-        <v>11.0962962962963</v>
+        <v>11.896296296296301</v>
       </c>
       <c r="J26">
-        <v>9.837037037037037</v>
+        <v>10.24074074074074</v>
       </c>
       <c r="K26">
-        <v>0.80740740740740746</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L26">
-        <v>0.80740740740740746</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M26">
-        <v>0.13703703703703701</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N26">
-        <v>1.4814814814814821E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O26">
         <v>0.15185185185185179</v>
       </c>
       <c r="P26">
-        <v>122.05185185185189</v>
+        <v>127.0740740740741</v>
       </c>
       <c r="Q26" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="R26">
-        <v>27.777777777777779</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S26" t="s">
-        <v>48</v>
-      </c>
-      <c r="T26" s="14">
-        <v>55.925925925925917</v>
+        <v>34</v>
+      </c>
+      <c r="T26" s="16">
+        <v>56.296296296296298</v>
       </c>
       <c r="U26" t="s">
-        <v>43</v>
-      </c>
-      <c r="V26">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="V26" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="W26" t="s">
-        <v>36</v>
-      </c>
-      <c r="X26">
-        <v>81.481481481481481</v>
+        <v>57</v>
+      </c>
+      <c r="X26" s="16">
+        <v>70.370370370370367</v>
       </c>
       <c r="Y26">
-        <v>33048</v>
+        <v>34419</v>
       </c>
       <c r="Z26">
-        <v>2996</v>
+        <v>3212</v>
       </c>
       <c r="AA26">
-        <v>36044</v>
+        <v>37631</v>
       </c>
       <c r="AB26">
-        <v>2274</v>
+        <v>2384</v>
       </c>
       <c r="AC26">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AD26">
-        <v>2656</v>
+        <v>2765</v>
       </c>
       <c r="AE26">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF26">
-        <v>4</v>
-      </c>
-      <c r="AG26" s="14">
+        <v>2</v>
+      </c>
+      <c r="AG26" s="16">
         <v>41</v>
       </c>
-      <c r="AH26" s="23">
-        <v>134562630000</v>
-      </c>
-      <c r="AI26" s="23">
-        <v>173192850840</v>
-      </c>
-      <c r="AJ26" s="23">
-        <v>38630220840</v>
+      <c r="AH26" s="25">
+        <v>140405200000</v>
+      </c>
+      <c r="AI26" s="25">
+        <v>174091165580</v>
+      </c>
+      <c r="AJ26" s="25">
+        <v>33685965580</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -3607,108 +3615,108 @@
         <v>32</v>
       </c>
       <c r="D27">
-        <v>119.7483337771863</v>
+        <v>128.74865864506759</v>
       </c>
       <c r="E27">
-        <v>40221</v>
+        <v>40033</v>
       </c>
       <c r="F27">
-        <v>3383</v>
+        <v>3269</v>
       </c>
       <c r="G27">
-        <v>126.8888888888889</v>
+        <v>126.637037037037</v>
       </c>
       <c r="H27">
-        <v>11.714814814814821</v>
+        <v>11.31481481481481</v>
       </c>
       <c r="I27">
-        <v>11.714814814814821</v>
+        <v>11.31481481481481</v>
       </c>
       <c r="J27">
-        <v>10.22222222222222</v>
+        <v>10.140740740740741</v>
       </c>
       <c r="K27">
-        <v>0.81481481481481477</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="L27">
-        <v>0.81481481481481477</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="M27">
-        <v>0.14074074074074069</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" s="14">
-        <v>0.14074074074074069</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O27" s="16">
+        <v>0.17777777777777781</v>
       </c>
       <c r="P27">
-        <v>126.65555555555559</v>
+        <v>126.1111111111111</v>
       </c>
       <c r="Q27" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="R27">
-        <v>31.111111111111111</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S27" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="T27">
-        <v>58.148148148148152</v>
+        <v>55.925925925925917</v>
       </c>
       <c r="U27" t="s">
         <v>43</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W27" t="s">
-        <v>36</v>
-      </c>
-      <c r="X27">
-        <v>81.481481481481481</v>
+        <v>43</v>
+      </c>
+      <c r="X27" s="15">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y27">
-        <v>34260</v>
+        <v>34192</v>
       </c>
       <c r="Z27">
-        <v>3163</v>
+        <v>3055</v>
       </c>
       <c r="AA27">
-        <v>37423</v>
+        <v>37247</v>
       </c>
       <c r="AB27">
-        <v>2388</v>
+        <v>2333</v>
       </c>
       <c r="AC27">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AD27">
-        <v>2760</v>
+        <v>2738</v>
       </c>
       <c r="AE27">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="14">
-        <v>38</v>
-      </c>
-      <c r="AH27" s="23">
-        <v>139798530000</v>
-      </c>
-      <c r="AI27" s="23">
-        <v>167406410320</v>
-      </c>
-      <c r="AJ27" s="23">
-        <v>27607880320</v>
+        <v>1</v>
+      </c>
+      <c r="AG27" s="16">
+        <v>48</v>
+      </c>
+      <c r="AH27" s="25">
+        <v>138833500000</v>
+      </c>
+      <c r="AI27" s="25">
+        <v>178746269000</v>
+      </c>
+      <c r="AJ27" s="25">
+        <v>39912769000</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>10</v>
+      <c r="A28" s="13">
+        <v>49</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -3716,109 +3724,109 @@
       <c r="C28" t="s">
         <v>32</v>
       </c>
-      <c r="D28">
-        <v>137.53042073480651</v>
+      <c r="D28" s="18">
+        <v>137.242098764888</v>
       </c>
       <c r="E28">
-        <v>40474</v>
+        <v>39296</v>
       </c>
       <c r="F28">
-        <v>3338</v>
+        <v>3250</v>
       </c>
       <c r="G28">
-        <v>127.9296296296296</v>
+        <v>124.1111111111111</v>
       </c>
       <c r="H28">
-        <v>11.53333333333333</v>
+        <v>11.28888888888889</v>
       </c>
       <c r="I28">
-        <v>11.53333333333333</v>
+        <v>11.28888888888889</v>
       </c>
       <c r="J28">
-        <v>10.24814814814815</v>
+        <v>9.9407407407407415</v>
       </c>
       <c r="K28">
-        <v>0.80740740740740746</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L28">
-        <v>0.80740740740740746</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M28">
-        <v>0.17037037037037039</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N28">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O28" s="14">
-        <v>0.19259259259259259</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O28" s="15">
+        <v>0.2</v>
       </c>
       <c r="P28">
-        <v>127.34444444444441</v>
+        <v>123.51111111111111</v>
       </c>
       <c r="Q28" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="R28">
-        <v>31.481481481481481</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S28" t="s">
-        <v>34</v>
-      </c>
-      <c r="T28" s="14">
-        <v>56.296296296296298</v>
+        <v>89</v>
+      </c>
+      <c r="T28" s="16">
+        <v>54.074074074074083</v>
       </c>
       <c r="U28" t="s">
-        <v>35</v>
-      </c>
-      <c r="V28" s="14">
-        <v>88.888888888888886</v>
+        <v>39</v>
+      </c>
+      <c r="V28" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="W28" t="s">
-        <v>36</v>
-      </c>
-      <c r="X28" s="14">
-        <v>81.481481481481481</v>
+        <v>39</v>
+      </c>
+      <c r="X28" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y28">
-        <v>34541</v>
+        <v>33510</v>
       </c>
       <c r="Z28">
-        <v>3114</v>
+        <v>3048</v>
       </c>
       <c r="AA28">
-        <v>37655</v>
+        <v>36558</v>
       </c>
       <c r="AB28">
-        <v>2341</v>
+        <v>2270</v>
       </c>
       <c r="AC28">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="AD28">
-        <v>2767</v>
+        <v>2684</v>
       </c>
       <c r="AE28">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF28">
-        <v>6</v>
-      </c>
-      <c r="AG28" s="13">
-        <v>52</v>
-      </c>
-      <c r="AH28" s="23">
-        <v>140322120000</v>
-      </c>
-      <c r="AI28" s="23">
-        <v>192985602020</v>
-      </c>
-      <c r="AJ28" s="24">
-        <v>52663482020</v>
+        <v>4</v>
+      </c>
+      <c r="AG28" s="15">
+        <v>54</v>
+      </c>
+      <c r="AH28" s="25">
+        <v>136133400000</v>
+      </c>
+      <c r="AI28" s="25">
+        <v>186832335280</v>
+      </c>
+      <c r="AJ28" s="26">
+        <v>50698935280</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -3826,109 +3834,109 @@
       <c r="C29" t="s">
         <v>32</v>
       </c>
-      <c r="D29">
-        <v>128.50820991384069</v>
+      <c r="D29" s="16">
+        <v>130.11129182217209</v>
       </c>
       <c r="E29">
-        <v>39809</v>
+        <v>39708</v>
       </c>
       <c r="F29">
-        <v>3388</v>
+        <v>3321</v>
       </c>
       <c r="G29">
-        <v>125.4814814814815</v>
+        <v>125.3888888888889</v>
       </c>
       <c r="H29">
-        <v>11.703703703703701</v>
+        <v>11.488888888888891</v>
       </c>
       <c r="I29">
-        <v>11.703703703703701</v>
+        <v>11.488888888888891</v>
       </c>
       <c r="J29">
-        <v>10.09259259259259</v>
+        <v>10.014814814814811</v>
       </c>
       <c r="K29">
-        <v>0.83703703703703702</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L29">
-        <v>0.83703703703703702</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M29">
-        <v>0.15555555555555561</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N29">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O29" s="14">
-        <v>0.162962962962963</v>
+      <c r="O29" s="16">
+        <v>0.1740740740740741</v>
       </c>
       <c r="P29">
-        <v>125.0703703703704</v>
+        <v>124.7962962962963</v>
       </c>
       <c r="Q29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R29">
-        <v>33.333333333333329</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S29" t="s">
-        <v>48</v>
-      </c>
-      <c r="T29" s="14">
-        <v>55.925925925925917</v>
+        <v>42</v>
+      </c>
+      <c r="T29" s="16">
+        <v>57.777777777777771</v>
       </c>
       <c r="U29" t="s">
+        <v>43</v>
+      </c>
+      <c r="V29" s="7">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W29" t="s">
         <v>35</v>
       </c>
-      <c r="V29">
+      <c r="X29" s="18">
         <v>88.888888888888886</v>
       </c>
-      <c r="W29" t="s">
-        <v>36</v>
-      </c>
-      <c r="X29" s="14">
-        <v>81.481481481481481</v>
-      </c>
       <c r="Y29">
-        <v>33880</v>
+        <v>33855</v>
       </c>
       <c r="Z29">
-        <v>3160</v>
+        <v>3102</v>
       </c>
       <c r="AA29">
-        <v>37040</v>
+        <v>36957</v>
       </c>
       <c r="AB29">
-        <v>2323</v>
+        <v>2299</v>
       </c>
       <c r="AC29">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AD29">
-        <v>2725</v>
+        <v>2704</v>
       </c>
       <c r="AE29">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AF29">
         <v>2</v>
       </c>
-      <c r="AG29" s="14">
-        <v>44</v>
-      </c>
-      <c r="AH29" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI29" s="23">
-        <v>177634019980</v>
-      </c>
-      <c r="AJ29" s="23">
-        <v>39406259980</v>
+      <c r="AG29" s="16">
+        <v>47</v>
+      </c>
+      <c r="AH29" s="25">
+        <v>137704170000</v>
+      </c>
+      <c r="AI29" s="25">
+        <v>179168674480</v>
+      </c>
+      <c r="AJ29" s="25">
+        <v>41464504480</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -3936,109 +3944,109 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
-      <c r="D30">
-        <v>127.35634020257579</v>
+      <c r="D30" s="16">
+        <v>122.09464556178879</v>
       </c>
       <c r="E30">
-        <v>39835</v>
+        <v>39768</v>
       </c>
       <c r="F30">
-        <v>3285</v>
+        <v>3342</v>
       </c>
       <c r="G30">
-        <v>125.937037037037</v>
+        <v>125.5222222222222</v>
       </c>
       <c r="H30">
-        <v>11.34444444444444</v>
+        <v>11.544444444444441</v>
       </c>
       <c r="I30">
-        <v>11.34444444444444</v>
+        <v>11.544444444444441</v>
       </c>
       <c r="J30">
         <v>10.08888888888889</v>
       </c>
       <c r="K30">
-        <v>0.81851851851851853</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L30">
-        <v>0.81851851851851853</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M30">
-        <v>0.162962962962963</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="N30">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O30" s="14">
-        <v>0.16666666666666671</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O30" s="16">
+        <v>0.1333333333333333</v>
       </c>
       <c r="P30">
-        <v>125.462962962963</v>
+        <v>125.237037037037</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R30">
-        <v>31.481481481481481</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S30" t="s">
-        <v>54</v>
-      </c>
-      <c r="T30" s="14">
-        <v>55.185185185185183</v>
+        <v>66</v>
+      </c>
+      <c r="T30" s="16">
+        <v>57.407407407407398</v>
       </c>
       <c r="U30" t="s">
-        <v>35</v>
-      </c>
-      <c r="V30" s="14">
-        <v>88.888888888888886</v>
+        <v>39</v>
+      </c>
+      <c r="V30" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="W30" t="s">
-        <v>36</v>
-      </c>
-      <c r="X30" s="14">
-        <v>81.481481481481481</v>
+        <v>67</v>
+      </c>
+      <c r="X30" s="16">
+        <v>66.666666666666657</v>
       </c>
       <c r="Y30">
-        <v>34003</v>
+        <v>33891</v>
       </c>
       <c r="Z30">
-        <v>3063</v>
+        <v>3117</v>
       </c>
       <c r="AA30">
-        <v>37066</v>
+        <v>37008</v>
       </c>
       <c r="AB30">
-        <v>2323</v>
+        <v>2358</v>
       </c>
       <c r="AC30">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD30">
         <v>2724</v>
       </c>
       <c r="AE30">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AF30">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="14">
-        <v>45</v>
-      </c>
-      <c r="AH30" s="23">
+        <v>3</v>
+      </c>
+      <c r="AG30" s="16">
+        <v>36</v>
+      </c>
+      <c r="AH30" s="25">
         <v>138227760000</v>
       </c>
-      <c r="AI30" s="23">
-        <v>176041816280</v>
-      </c>
-      <c r="AJ30" s="23">
-        <v>37814056280</v>
+      <c r="AI30" s="25">
+        <v>168768693640</v>
+      </c>
+      <c r="AJ30" s="25">
+        <v>30540933640</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4047,60 +4055,60 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <v>133.4587603019794</v>
+        <v>128.50820991384069</v>
       </c>
       <c r="E31">
-        <v>39411</v>
+        <v>39809</v>
       </c>
       <c r="F31">
-        <v>3213</v>
+        <v>3388</v>
       </c>
       <c r="G31">
-        <v>124.61481481481481</v>
+        <v>125.4814814814815</v>
       </c>
       <c r="H31">
-        <v>11.18148148148148</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="I31">
-        <v>11.18148148148148</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="J31">
-        <v>9.9851851851851858</v>
+        <v>10.09259259259259</v>
       </c>
       <c r="K31">
-        <v>0.7</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="L31">
-        <v>0.7</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="M31">
-        <v>0.16666666666666671</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N31">
-        <v>1.8518518518518521E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O31">
-        <v>0.1851851851851852</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P31">
-        <v>124.1444444444444</v>
+        <v>125.0703703703704</v>
       </c>
       <c r="Q31" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="R31">
-        <v>37.037037037037038</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S31" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="T31">
-        <v>49.629629629629633</v>
+        <v>55.925925925925917</v>
       </c>
       <c r="U31" t="s">
         <v>35</v>
       </c>
-      <c r="V31" s="14">
+      <c r="V31" s="16">
         <v>88.888888888888886</v>
       </c>
       <c r="W31" t="s">
@@ -4110,45 +4118,45 @@
         <v>81.481481481481481</v>
       </c>
       <c r="Y31">
-        <v>33646</v>
+        <v>33880</v>
       </c>
       <c r="Z31">
-        <v>3019</v>
+        <v>3160</v>
       </c>
       <c r="AA31">
-        <v>36665</v>
+        <v>37040</v>
       </c>
       <c r="AB31">
-        <v>2307</v>
+        <v>2323</v>
       </c>
       <c r="AC31">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="AD31">
-        <v>2696</v>
+        <v>2725</v>
       </c>
       <c r="AE31">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AF31">
-        <v>5</v>
-      </c>
-      <c r="AG31" s="13">
-        <v>50</v>
-      </c>
-      <c r="AH31" s="23">
-        <v>136656990000</v>
-      </c>
-      <c r="AI31" s="23">
-        <v>182380724720</v>
-      </c>
-      <c r="AJ31" s="23">
-        <v>45723734720</v>
+        <v>2</v>
+      </c>
+      <c r="AG31" s="16">
+        <v>44</v>
+      </c>
+      <c r="AH31" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI31" s="25">
+        <v>177634019980</v>
+      </c>
+      <c r="AJ31" s="25">
+        <v>39406259980</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -4157,55 +4165,55 @@
         <v>32</v>
       </c>
       <c r="D32">
-        <v>135.0130755550814</v>
+        <v>132.08064457873661</v>
       </c>
       <c r="E32">
-        <v>39423</v>
+        <v>39075</v>
       </c>
       <c r="F32">
-        <v>3338</v>
+        <v>3261</v>
       </c>
       <c r="G32">
-        <v>124.3148148148148</v>
+        <v>123.34444444444441</v>
       </c>
       <c r="H32">
-        <v>11.52962962962963</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="I32">
-        <v>11.52962962962963</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="J32">
-        <v>9.9777777777777779</v>
+        <v>9.8962962962962955</v>
       </c>
       <c r="K32">
-        <v>0.82592592592592595</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="L32">
-        <v>0.82592592592592595</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="M32">
-        <v>0.18148148148148149</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N32">
-        <v>7.4074074074074077E-3</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O32">
-        <v>0.18888888888888891</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P32">
-        <v>123.72592592592591</v>
+        <v>122.937037037037</v>
       </c>
       <c r="Q32" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="R32">
-        <v>24.81481481481481</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S32" t="s">
-        <v>88</v>
-      </c>
-      <c r="T32" s="13">
-        <v>62.222222222222221</v>
+        <v>51</v>
+      </c>
+      <c r="T32" s="16">
+        <v>54.444444444444443</v>
       </c>
       <c r="U32" t="s">
         <v>35</v>
@@ -4214,51 +4222,51 @@
         <v>88.888888888888886</v>
       </c>
       <c r="W32" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="X32">
-        <v>81.481481481481481</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y32">
-        <v>33565</v>
+        <v>33303</v>
       </c>
       <c r="Z32">
-        <v>3113</v>
+        <v>3054</v>
       </c>
       <c r="AA32">
-        <v>36678</v>
+        <v>36357</v>
       </c>
       <c r="AB32">
-        <v>2267</v>
+        <v>2286</v>
       </c>
       <c r="AC32">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="AD32">
-        <v>2694</v>
+        <v>2672</v>
       </c>
       <c r="AE32">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="AF32">
-        <v>2</v>
-      </c>
-      <c r="AG32" s="13">
-        <v>51</v>
-      </c>
-      <c r="AH32" s="23">
-        <v>136656990000</v>
-      </c>
-      <c r="AI32" s="23">
-        <v>184504805160</v>
-      </c>
-      <c r="AJ32" s="23">
-        <v>47847815160</v>
+        <v>5</v>
+      </c>
+      <c r="AG32" s="16">
+        <v>46</v>
+      </c>
+      <c r="AH32" s="25">
+        <v>135609810000</v>
+      </c>
+      <c r="AI32" s="25">
+        <v>179114311160</v>
+      </c>
+      <c r="AJ32" s="25">
+        <v>43504501160</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -4267,108 +4275,108 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>127.2320721347936</v>
+        <v>129.5895794031575</v>
       </c>
       <c r="E33">
-        <v>39986</v>
+        <v>40134</v>
       </c>
       <c r="F33">
-        <v>3291</v>
+        <v>3275</v>
       </c>
       <c r="G33">
-        <v>126.2962962962963</v>
+        <v>126.8555555555556</v>
       </c>
       <c r="H33">
-        <v>11.46296296296296</v>
+        <v>11.366666666666671</v>
       </c>
       <c r="I33">
-        <v>11.46296296296296</v>
+        <v>11.366666666666671</v>
       </c>
       <c r="J33">
-        <v>10.162962962962959</v>
+        <v>10.237037037037039</v>
       </c>
       <c r="K33">
-        <v>0.71851851851851856</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="L33">
-        <v>0.71851851851851856</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="M33">
-        <v>0.16666666666666671</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N33">
-        <v>7.4074074074074077E-3</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O33">
-        <v>0.1740740740740741</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="P33">
-        <v>125.9518518518519</v>
+        <v>126.537037037037</v>
       </c>
       <c r="Q33" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="R33">
-        <v>33.703703703703702</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T33">
-        <v>50.370370370370367</v>
+        <v>53.703703703703709</v>
       </c>
       <c r="U33" t="s">
         <v>61</v>
       </c>
-      <c r="V33" s="25">
+      <c r="V33" s="27">
         <v>96.296296296296291</v>
       </c>
       <c r="W33" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="X33">
-        <v>77.777777777777786</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y33">
-        <v>34100</v>
+        <v>34251</v>
       </c>
       <c r="Z33">
-        <v>3095</v>
+        <v>3069</v>
       </c>
       <c r="AA33">
-        <v>37195</v>
+        <v>37320</v>
       </c>
       <c r="AB33">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="AC33">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="AD33">
-        <v>2744</v>
+        <v>2764</v>
       </c>
       <c r="AE33">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF33">
-        <v>2</v>
-      </c>
-      <c r="AG33" s="14">
-        <v>47</v>
-      </c>
-      <c r="AH33" s="23">
-        <v>138751350000</v>
-      </c>
-      <c r="AI33" s="23">
-        <v>176536217720</v>
-      </c>
-      <c r="AJ33" s="23">
-        <v>37784867720</v>
+        <v>1</v>
+      </c>
+      <c r="AG33" s="15">
+        <v>50</v>
+      </c>
+      <c r="AH33" s="25">
+        <v>139274940000</v>
+      </c>
+      <c r="AI33" s="25">
+        <v>180485808960</v>
+      </c>
+      <c r="AJ33" s="25">
+        <v>41210868960</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -4377,108 +4385,108 @@
         <v>32</v>
       </c>
       <c r="D34">
-        <v>128.11040201171329</v>
+        <v>133.5215300175762</v>
       </c>
       <c r="E34">
-        <v>39530</v>
+        <v>40616</v>
       </c>
       <c r="F34">
-        <v>3326</v>
+        <v>3367</v>
       </c>
       <c r="G34">
-        <v>124.7592592592593</v>
+        <v>128.28518518518521</v>
       </c>
       <c r="H34">
-        <v>11.50740740740741</v>
+        <v>11.65555555555556</v>
       </c>
       <c r="I34">
-        <v>11.50740740740741</v>
+        <v>11.65555555555556</v>
       </c>
       <c r="J34">
-        <v>9.9851851851851858</v>
+        <v>10.31111111111111</v>
       </c>
       <c r="K34">
-        <v>0.79629629629629628</v>
+        <v>0.79259259259259263</v>
       </c>
       <c r="L34">
-        <v>0.79629629629629628</v>
+        <v>0.79259259259259263</v>
       </c>
       <c r="M34">
-        <v>0.14074074074074069</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N34">
-        <v>1.4814814814814821E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O34">
-        <v>0.15555555555555561</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="P34">
-        <v>124.2592592592593</v>
+        <v>127.8333333333333</v>
       </c>
       <c r="Q34" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="R34">
-        <v>34.444444444444443</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S34" t="s">
-        <v>45</v>
-      </c>
-      <c r="T34" s="14">
-        <v>54.814814814814817</v>
+        <v>77</v>
+      </c>
+      <c r="T34" s="18">
+        <v>58.518518518518512</v>
       </c>
       <c r="U34" t="s">
+        <v>61</v>
+      </c>
+      <c r="V34" s="27">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W34" t="s">
         <v>35</v>
       </c>
-      <c r="V34" s="14">
+      <c r="X34" s="18">
         <v>88.888888888888886</v>
       </c>
-      <c r="W34" t="s">
-        <v>46</v>
-      </c>
-      <c r="X34">
-        <v>77.777777777777786</v>
-      </c>
       <c r="Y34">
-        <v>33685</v>
+        <v>34637</v>
       </c>
       <c r="Z34">
-        <v>3107</v>
+        <v>3147</v>
       </c>
       <c r="AA34">
-        <v>36792</v>
+        <v>37784</v>
       </c>
       <c r="AB34">
-        <v>2313</v>
+        <v>2378</v>
       </c>
       <c r="AC34">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD34">
-        <v>2696</v>
+        <v>2784</v>
       </c>
       <c r="AE34">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF34">
-        <v>4</v>
-      </c>
-      <c r="AG34" s="14">
-        <v>42</v>
-      </c>
-      <c r="AH34" s="23">
-        <v>137180580000</v>
-      </c>
-      <c r="AI34" s="23">
-        <v>175742592520</v>
-      </c>
-      <c r="AJ34" s="23">
-        <v>38562012520</v>
+        <v>6</v>
+      </c>
+      <c r="AG34" s="16">
+        <v>48</v>
+      </c>
+      <c r="AH34" s="25">
+        <v>140929100000</v>
+      </c>
+      <c r="AI34" s="25">
+        <v>188170690560</v>
+      </c>
+      <c r="AJ34" s="25">
+        <v>47241590560</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -4487,108 +4495,108 @@
         <v>32</v>
       </c>
       <c r="D35">
-        <v>134.51178644198299</v>
+        <v>134.17660108042841</v>
       </c>
       <c r="E35">
-        <v>40171</v>
+        <v>40464</v>
       </c>
       <c r="F35">
-        <v>3296</v>
+        <v>3382</v>
       </c>
       <c r="G35">
-        <v>126.93333333333329</v>
+        <v>127.6592592592593</v>
       </c>
       <c r="H35">
-        <v>11.455555555555559</v>
+        <v>11.74444444444444</v>
       </c>
       <c r="I35">
-        <v>11.455555555555559</v>
+        <v>11.74444444444444</v>
       </c>
       <c r="J35">
-        <v>10.18888888888889</v>
+        <v>10.262962962962961</v>
       </c>
       <c r="K35">
-        <v>0.74444444444444446</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="L35">
-        <v>0.74444444444444446</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="M35">
-        <v>0.1962962962962963</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="N35">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O35" s="13">
-        <v>0.20370370370370369</v>
+      <c r="O35" s="15">
+        <v>0.2</v>
       </c>
       <c r="P35">
-        <v>126.4592592592593</v>
+        <v>127.1851851851852</v>
       </c>
       <c r="Q35" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="R35">
-        <v>30</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S35" t="s">
-        <v>34</v>
-      </c>
-      <c r="T35" s="14">
-        <v>56.296296296296298</v>
+        <v>59</v>
+      </c>
+      <c r="T35" s="16">
+        <v>56.666666666666657</v>
       </c>
       <c r="U35" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35" s="14">
-        <v>88.888888888888886</v>
+        <v>60</v>
+      </c>
+      <c r="V35" s="15">
+        <v>100</v>
       </c>
       <c r="W35" t="s">
-        <v>46</v>
-      </c>
-      <c r="X35" s="14">
-        <v>77.777777777777786</v>
+        <v>61</v>
+      </c>
+      <c r="X35" s="15">
+        <v>96.296296296296291</v>
       </c>
       <c r="Y35">
-        <v>34272</v>
+        <v>34468</v>
       </c>
       <c r="Z35">
-        <v>3093</v>
+        <v>3171</v>
       </c>
       <c r="AA35">
-        <v>37365</v>
+        <v>37639</v>
       </c>
       <c r="AB35">
-        <v>2330</v>
+        <v>2346</v>
       </c>
       <c r="AC35">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AD35">
-        <v>2751</v>
+        <v>2771</v>
       </c>
       <c r="AE35">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF35">
         <v>2</v>
       </c>
-      <c r="AG35" s="13">
-        <v>55</v>
-      </c>
-      <c r="AH35" s="23">
-        <v>139274940000</v>
-      </c>
-      <c r="AI35" s="23">
-        <v>187341209860</v>
-      </c>
-      <c r="AJ35" s="23">
-        <v>48066269860</v>
+      <c r="AG35" s="15">
+        <v>54</v>
+      </c>
+      <c r="AH35" s="25">
+        <v>140322120000</v>
+      </c>
+      <c r="AI35" s="25">
+        <v>188279451180</v>
+      </c>
+      <c r="AJ35" s="25">
+        <v>47957331180</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>11</v>
+      <c r="A36" s="16">
+        <v>28</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
@@ -4596,26 +4604,26 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
-      <c r="D36">
-        <v>112.9008574114774</v>
+      <c r="D36" s="16">
+        <v>127.2320721347936</v>
       </c>
       <c r="E36">
-        <v>39889</v>
+        <v>39986</v>
       </c>
       <c r="F36">
-        <v>3275</v>
+        <v>3291</v>
       </c>
       <c r="G36">
-        <v>126.04444444444449</v>
+        <v>126.2962962962963</v>
       </c>
       <c r="H36">
-        <v>11.41111111111111</v>
+        <v>11.46296296296296</v>
       </c>
       <c r="I36">
-        <v>11.41111111111111</v>
+        <v>11.46296296296296</v>
       </c>
       <c r="J36">
-        <v>10.15925925925926</v>
+        <v>10.162962962962959</v>
       </c>
       <c r="K36">
         <v>0.71851851851851856</v>
@@ -4624,81 +4632,81 @@
         <v>0.71851851851851856</v>
       </c>
       <c r="M36">
-        <v>0.1222222222222222</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0.1222222222222222</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O36" s="16">
+        <v>0.1740740740740741</v>
       </c>
       <c r="P36">
-        <v>126.01111111111111</v>
+        <v>125.9518518518519</v>
       </c>
       <c r="Q36" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="R36">
-        <v>36.666666666666657</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S36" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="T36">
-        <v>52.962962962962969</v>
+        <v>50.370370370370367</v>
       </c>
       <c r="U36" t="s">
-        <v>39</v>
-      </c>
-      <c r="V36">
-        <v>85.18518518518519</v>
+        <v>61</v>
+      </c>
+      <c r="V36" s="27">
+        <v>96.296296296296291</v>
       </c>
       <c r="W36" t="s">
-        <v>40</v>
-      </c>
-      <c r="X36">
-        <v>74.074074074074076</v>
+        <v>46</v>
+      </c>
+      <c r="X36" s="16">
+        <v>77.777777777777786</v>
       </c>
       <c r="Y36">
-        <v>34032</v>
+        <v>34100</v>
       </c>
       <c r="Z36">
-        <v>3081</v>
+        <v>3095</v>
       </c>
       <c r="AA36">
-        <v>37113</v>
+        <v>37195</v>
       </c>
       <c r="AB36">
-        <v>2417</v>
+        <v>2362</v>
       </c>
       <c r="AC36">
         <v>194</v>
       </c>
       <c r="AD36">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="AE36">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AF36">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="14">
-        <v>33</v>
-      </c>
-      <c r="AH36" s="23">
+        <v>2</v>
+      </c>
+      <c r="AG36" s="16">
+        <v>47</v>
+      </c>
+      <c r="AH36" s="25">
         <v>138751350000</v>
       </c>
-      <c r="AI36" s="23">
-        <v>156651463820</v>
-      </c>
-      <c r="AJ36" s="23">
-        <v>17900113820</v>
+      <c r="AI36" s="25">
+        <v>176536217720</v>
+      </c>
+      <c r="AJ36" s="25">
+        <v>37784867720</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>30</v>
+      <c r="A37" s="16">
+        <v>13</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -4706,109 +4714,109 @@
       <c r="C37" t="s">
         <v>32</v>
       </c>
-      <c r="D37">
-        <v>130.0389277522836</v>
+      <c r="D37" s="16">
+        <v>128.11040201171329</v>
       </c>
       <c r="E37">
-        <v>39838</v>
+        <v>39530</v>
       </c>
       <c r="F37">
-        <v>3333</v>
+        <v>3326</v>
       </c>
       <c r="G37">
-        <v>125.8555555555556</v>
+        <v>124.7592592592593</v>
       </c>
       <c r="H37">
-        <v>11.47037037037037</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I37">
-        <v>11.47037037037037</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J37">
-        <v>10.05925925925926</v>
+        <v>9.9851851851851858</v>
       </c>
       <c r="K37">
-        <v>0.86296296296296293</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L37">
-        <v>0.86296296296296293</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M37">
-        <v>0.15185185185185179</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N37">
-        <v>1.111111111111111E-2</v>
-      </c>
-      <c r="O37" s="14">
-        <v>0.162962962962963</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O37" s="16">
+        <v>0.15555555555555561</v>
       </c>
       <c r="P37">
-        <v>125.2777777777778</v>
+        <v>124.2592592592593</v>
       </c>
       <c r="Q37" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="R37">
-        <v>30</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S37" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="T37">
-        <v>56.296296296296298</v>
+        <v>54.814814814814817</v>
       </c>
       <c r="U37" t="s">
-        <v>39</v>
-      </c>
-      <c r="V37">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="V37" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W37" t="s">
-        <v>40</v>
-      </c>
-      <c r="X37">
-        <v>74.074074074074076</v>
+        <v>46</v>
+      </c>
+      <c r="X37" s="16">
+        <v>77.777777777777786</v>
       </c>
       <c r="Y37">
-        <v>33981</v>
+        <v>33685</v>
       </c>
       <c r="Z37">
-        <v>3097</v>
+        <v>3107</v>
       </c>
       <c r="AA37">
-        <v>37078</v>
+        <v>36792</v>
       </c>
       <c r="AB37">
-        <v>2307</v>
+        <v>2313</v>
       </c>
       <c r="AC37">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="AD37">
-        <v>2716</v>
+        <v>2696</v>
       </c>
       <c r="AE37">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AF37">
-        <v>3</v>
-      </c>
-      <c r="AG37" s="14">
-        <v>44</v>
-      </c>
-      <c r="AH37" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI37" s="23">
-        <v>179749896960</v>
-      </c>
-      <c r="AJ37" s="23">
-        <v>41522136960</v>
+        <v>4</v>
+      </c>
+      <c r="AG37" s="16">
+        <v>42</v>
+      </c>
+      <c r="AH37" s="25">
+        <v>137180580000</v>
+      </c>
+      <c r="AI37" s="25">
+        <v>175742592520</v>
+      </c>
+      <c r="AJ37" s="25">
+        <v>38562012520</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -4816,109 +4824,109 @@
       <c r="C38" t="s">
         <v>32</v>
       </c>
-      <c r="D38">
-        <v>127.9967155062633</v>
+      <c r="D38" s="16">
+        <v>126.3735355064933</v>
       </c>
       <c r="E38">
-        <v>40473</v>
+        <v>40759</v>
       </c>
       <c r="F38">
-        <v>3406</v>
+        <v>3357</v>
       </c>
       <c r="G38">
-        <v>127.71111111111109</v>
+        <v>128.862962962963</v>
       </c>
       <c r="H38">
-        <v>11.77407407407407</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="I38">
-        <v>11.77407407407407</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="J38">
-        <v>10.24444444444444</v>
+        <v>10.3</v>
       </c>
       <c r="K38">
-        <v>0.83703703703703702</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="L38">
-        <v>0.83703703703703702</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="M38">
-        <v>0.16666666666666671</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N38">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O38" s="14">
-        <v>0.17037037037037039</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O38" s="16">
+        <v>0.15925925925925929</v>
       </c>
       <c r="P38">
-        <v>127.1666666666667</v>
+        <v>128.39259259259259</v>
       </c>
       <c r="Q38" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="R38">
-        <v>30</v>
+        <v>34.814814814814817</v>
       </c>
       <c r="S38" t="s">
-        <v>75</v>
-      </c>
-      <c r="T38" s="13">
-        <v>62.592592592592588</v>
+        <v>54</v>
+      </c>
+      <c r="T38" s="16">
+        <v>55.185185185185183</v>
       </c>
       <c r="U38" t="s">
+        <v>61</v>
+      </c>
+      <c r="V38" s="27">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X38" s="18">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="Y38">
+        <v>34793</v>
+      </c>
+      <c r="Z38">
+        <v>3142</v>
+      </c>
+      <c r="AA38">
+        <v>37935</v>
+      </c>
+      <c r="AB38">
+        <v>2398</v>
+      </c>
+      <c r="AC38">
+        <v>211</v>
+      </c>
+      <c r="AD38">
+        <v>2781</v>
+      </c>
+      <c r="AE38">
         <v>39</v>
       </c>
-      <c r="V38" s="14">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="W38" t="s">
-        <v>40</v>
-      </c>
-      <c r="X38" s="14">
-        <v>74.074074074074076</v>
-      </c>
-      <c r="Y38">
-        <v>34482</v>
-      </c>
-      <c r="Z38">
-        <v>3179</v>
-      </c>
-      <c r="AA38">
-        <v>37661</v>
-      </c>
-      <c r="AB38">
-        <v>2356</v>
-      </c>
-      <c r="AC38">
-        <v>226</v>
-      </c>
-      <c r="AD38">
-        <v>2766</v>
-      </c>
-      <c r="AE38">
-        <v>45</v>
-      </c>
       <c r="AF38">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="14">
-        <v>46</v>
-      </c>
-      <c r="AH38" s="23">
-        <v>140405200000</v>
-      </c>
-      <c r="AI38" s="23">
-        <v>179714044400</v>
-      </c>
-      <c r="AJ38" s="23">
-        <v>39308844400</v>
+        <v>4</v>
+      </c>
+      <c r="AG38" s="16">
+        <v>43</v>
+      </c>
+      <c r="AH38" s="25">
+        <v>141453000000</v>
+      </c>
+      <c r="AI38" s="25">
+        <v>178759157180</v>
+      </c>
+      <c r="AJ38" s="25">
+        <v>37306157180</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
@@ -4927,108 +4935,108 @@
         <v>32</v>
       </c>
       <c r="D39">
-        <v>125.8321025432106</v>
+        <v>130.3964865868046</v>
       </c>
       <c r="E39">
-        <v>40418</v>
+        <v>40277</v>
       </c>
       <c r="F39">
-        <v>3367</v>
+        <v>3252</v>
       </c>
       <c r="G39">
-        <v>127.6518518518518</v>
+        <v>127.5222222222222</v>
       </c>
       <c r="H39">
-        <v>11.65925925925926</v>
+        <v>11.21111111111111</v>
       </c>
       <c r="I39">
-        <v>11.65925925925926</v>
+        <v>11.21111111111111</v>
       </c>
       <c r="J39">
-        <v>10.237037037037039</v>
+        <v>10.262962962962961</v>
       </c>
       <c r="K39">
-        <v>0.79259259259259263</v>
+        <v>0.82592592592592595</v>
       </c>
       <c r="L39">
-        <v>0.79259259259259263</v>
+        <v>0.82592592592592595</v>
       </c>
       <c r="M39">
-        <v>0.12962962962962959</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="N39">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O39" s="14">
-        <v>0.14814814814814811</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O39" s="16">
+        <v>0.17777777777777781</v>
       </c>
       <c r="P39">
-        <v>127.3111111111111</v>
+        <v>127.137037037037</v>
       </c>
       <c r="Q39" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="R39">
-        <v>36.666666666666657</v>
+        <v>34.814814814814817</v>
       </c>
       <c r="S39" t="s">
-        <v>45</v>
-      </c>
-      <c r="T39" s="14">
-        <v>54.814814814814817</v>
+        <v>70</v>
+      </c>
+      <c r="T39" s="16">
+        <v>53.333333333333343</v>
       </c>
       <c r="U39" t="s">
+        <v>43</v>
+      </c>
+      <c r="V39" s="7">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W39" t="s">
         <v>39</v>
       </c>
-      <c r="V39">
+      <c r="X39" s="16">
         <v>85.18518518518519</v>
       </c>
-      <c r="W39" t="s">
-        <v>40</v>
-      </c>
-      <c r="X39" s="14">
-        <v>74.074074074074076</v>
-      </c>
       <c r="Y39">
-        <v>34466</v>
+        <v>34431</v>
       </c>
       <c r="Z39">
-        <v>3148</v>
+        <v>3027</v>
       </c>
       <c r="AA39">
-        <v>37614</v>
+        <v>37458</v>
       </c>
       <c r="AB39">
-        <v>2390</v>
+        <v>2356</v>
       </c>
       <c r="AC39">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="AD39">
-        <v>2764</v>
+        <v>2771</v>
       </c>
       <c r="AE39">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="AF39">
-        <v>5</v>
-      </c>
-      <c r="AG39" s="14">
-        <v>40</v>
-      </c>
-      <c r="AH39" s="23">
-        <v>140405200000</v>
-      </c>
-      <c r="AI39" s="23">
-        <v>176674815240</v>
-      </c>
-      <c r="AJ39" s="23">
-        <v>36269615240</v>
+        <v>2</v>
+      </c>
+      <c r="AG39" s="16">
+        <v>48</v>
+      </c>
+      <c r="AH39" s="25">
+        <v>139798530000</v>
+      </c>
+      <c r="AI39" s="25">
+        <v>182292371420</v>
+      </c>
+      <c r="AJ39" s="25">
+        <v>42493841420</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
@@ -5037,61 +5045,61 @@
         <v>32</v>
       </c>
       <c r="D40">
-        <v>126.5557330358163</v>
+        <v>120.0642029213235</v>
       </c>
       <c r="E40">
-        <v>40535</v>
+        <v>39735</v>
       </c>
       <c r="F40">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="G40">
-        <v>128.15185185185189</v>
+        <v>125.2851851851852</v>
       </c>
       <c r="H40">
-        <v>11.474074074074069</v>
+        <v>11.55185185185185</v>
       </c>
       <c r="I40">
-        <v>11.474074074074069</v>
+        <v>11.55185185185185</v>
       </c>
       <c r="J40">
-        <v>10.351851851851849</v>
+        <v>10.18888888888889</v>
       </c>
       <c r="K40">
-        <v>0.83333333333333337</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="L40">
-        <v>0.83333333333333337</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="M40">
         <v>0.13703703703703701</v>
       </c>
       <c r="N40">
-        <v>1.4814814814814821E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O40">
-        <v>0.15185185185185179</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="P40">
-        <v>127.9037037037037</v>
+        <v>125.3111111111111</v>
       </c>
       <c r="Q40" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="R40">
-        <v>32.222222222222221</v>
+        <v>35.185185185185183</v>
       </c>
       <c r="S40" t="s">
-        <v>70</v>
-      </c>
-      <c r="T40" s="14">
-        <v>53.333333333333343</v>
+        <v>54</v>
+      </c>
+      <c r="T40" s="16">
+        <v>55.185185185185183</v>
       </c>
       <c r="U40" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="V40">
-        <v>88.888888888888886</v>
+        <v>74.074074074074076</v>
       </c>
       <c r="W40" t="s">
         <v>57</v>
@@ -5100,45 +5108,45 @@
         <v>70.370370370370367</v>
       </c>
       <c r="Y40">
-        <v>34601</v>
+        <v>33827</v>
       </c>
       <c r="Z40">
-        <v>3098</v>
+        <v>3119</v>
       </c>
       <c r="AA40">
-        <v>37699</v>
+        <v>36946</v>
       </c>
       <c r="AB40">
-        <v>2406</v>
+        <v>2394</v>
       </c>
       <c r="AC40">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="AD40">
-        <v>2795</v>
+        <v>2751</v>
       </c>
       <c r="AE40">
         <v>37</v>
       </c>
       <c r="AF40">
-        <v>4</v>
-      </c>
-      <c r="AG40" s="14">
-        <v>41</v>
-      </c>
-      <c r="AH40" s="23">
-        <v>140845710000</v>
-      </c>
-      <c r="AI40" s="23">
-        <v>178248320740</v>
-      </c>
-      <c r="AJ40" s="23">
-        <v>37402610740</v>
+        <v>1</v>
+      </c>
+      <c r="AG40" s="16">
+        <v>38</v>
+      </c>
+      <c r="AH40" s="25">
+        <v>138227760000</v>
+      </c>
+      <c r="AI40" s="25">
+        <v>165962058260</v>
+      </c>
+      <c r="AJ40" s="25">
+        <v>27734298260</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
         <v>31</v>
@@ -5147,108 +5155,108 @@
         <v>32</v>
       </c>
       <c r="D41">
-        <v>120.1030829930568</v>
+        <v>125.8321025432106</v>
       </c>
       <c r="E41">
-        <v>39642</v>
+        <v>40418</v>
       </c>
       <c r="F41">
-        <v>3252</v>
+        <v>3367</v>
       </c>
       <c r="G41">
-        <v>125.3185185185185</v>
+        <v>127.6518518518518</v>
       </c>
       <c r="H41">
-        <v>11.31111111111111</v>
+        <v>11.65925925925926</v>
       </c>
       <c r="I41">
-        <v>11.31111111111111</v>
+        <v>11.65925925925926</v>
       </c>
       <c r="J41">
-        <v>10.055555555555561</v>
+        <v>10.237037037037039</v>
       </c>
       <c r="K41">
-        <v>0.72222222222222221</v>
+        <v>0.79259259259259263</v>
       </c>
       <c r="L41">
-        <v>0.72222222222222221</v>
+        <v>0.79259259259259263</v>
       </c>
       <c r="M41">
-        <v>0.12592592592592591</v>
+        <v>0.12962962962962959</v>
       </c>
       <c r="N41">
-        <v>1.111111111111111E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O41">
-        <v>0.13703703703703701</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="P41">
-        <v>125.05185185185189</v>
+        <v>127.3111111111111</v>
       </c>
       <c r="Q41" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R41">
-        <v>37.037037037037038</v>
+        <v>36.666666666666657</v>
       </c>
       <c r="S41" t="s">
-        <v>56</v>
-      </c>
-      <c r="T41" s="14">
-        <v>51.481481481481481</v>
+        <v>45</v>
+      </c>
+      <c r="T41" s="16">
+        <v>54.814814814814817</v>
       </c>
       <c r="U41" t="s">
         <v>39</v>
       </c>
-      <c r="V41" s="14">
+      <c r="V41" s="16">
         <v>85.18518518518519</v>
       </c>
       <c r="W41" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="X41">
-        <v>70.370370370370367</v>
+        <v>74.074074074074076</v>
       </c>
       <c r="Y41">
-        <v>33836</v>
+        <v>34466</v>
       </c>
       <c r="Z41">
-        <v>3054</v>
+        <v>3148</v>
       </c>
       <c r="AA41">
-        <v>36890</v>
+        <v>37614</v>
       </c>
       <c r="AB41">
-        <v>2372</v>
+        <v>2390</v>
       </c>
       <c r="AC41">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="AD41">
-        <v>2715</v>
+        <v>2764</v>
       </c>
       <c r="AE41">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AF41">
-        <v>3</v>
-      </c>
-      <c r="AG41" s="14">
-        <v>37</v>
-      </c>
-      <c r="AH41" s="23">
-        <v>137704170000</v>
-      </c>
-      <c r="AI41" s="23">
-        <v>165386953580</v>
-      </c>
-      <c r="AJ41" s="23">
-        <v>27682783580</v>
+        <v>5</v>
+      </c>
+      <c r="AG41" s="16">
+        <v>40</v>
+      </c>
+      <c r="AH41" s="25">
+        <v>140405200000</v>
+      </c>
+      <c r="AI41" s="25">
+        <v>176674815240</v>
+      </c>
+      <c r="AJ41" s="25">
+        <v>36269615240</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
@@ -5257,108 +5265,108 @@
         <v>32</v>
       </c>
       <c r="D42">
-        <v>123.99196438593439</v>
+        <v>112.9008574114774</v>
       </c>
       <c r="E42">
-        <v>40437</v>
+        <v>39889</v>
       </c>
       <c r="F42">
-        <v>3431</v>
+        <v>3275</v>
       </c>
       <c r="G42">
-        <v>127.4777777777778</v>
+        <v>126.04444444444449</v>
       </c>
       <c r="H42">
-        <v>11.896296296296301</v>
+        <v>11.41111111111111</v>
       </c>
       <c r="I42">
-        <v>11.896296296296301</v>
+        <v>11.41111111111111</v>
       </c>
       <c r="J42">
-        <v>10.24074074074074</v>
+        <v>10.15925925925926</v>
       </c>
       <c r="K42">
-        <v>0.8037037037037037</v>
+        <v>0.71851851851851856</v>
       </c>
       <c r="L42">
-        <v>0.8037037037037037</v>
+        <v>0.71851851851851856</v>
       </c>
       <c r="M42">
-        <v>0.1444444444444444</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="N42">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O42" s="14">
-        <v>0.15185185185185179</v>
+        <v>0</v>
+      </c>
+      <c r="O42" s="16">
+        <v>0.1222222222222222</v>
       </c>
       <c r="P42">
-        <v>127.0740740740741</v>
+        <v>126.01111111111111</v>
       </c>
       <c r="Q42" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="R42">
-        <v>32.592592592592602</v>
+        <v>36.666666666666657</v>
       </c>
       <c r="S42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="T42">
-        <v>56.296296296296298</v>
+        <v>52.962962962962969</v>
       </c>
       <c r="U42" t="s">
-        <v>36</v>
-      </c>
-      <c r="V42" s="14">
-        <v>81.481481481481481</v>
+        <v>39</v>
+      </c>
+      <c r="V42" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="W42" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="X42">
-        <v>70.370370370370367</v>
+        <v>74.074074074074076</v>
       </c>
       <c r="Y42">
-        <v>34419</v>
+        <v>34032</v>
       </c>
       <c r="Z42">
-        <v>3212</v>
+        <v>3081</v>
       </c>
       <c r="AA42">
-        <v>37631</v>
+        <v>37113</v>
       </c>
       <c r="AB42">
-        <v>2384</v>
+        <v>2417</v>
       </c>
       <c r="AC42">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="AD42">
-        <v>2765</v>
+        <v>2743</v>
       </c>
       <c r="AE42">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="AF42">
-        <v>2</v>
-      </c>
-      <c r="AG42" s="14">
-        <v>41</v>
-      </c>
-      <c r="AH42" s="23">
-        <v>140405200000</v>
-      </c>
-      <c r="AI42" s="23">
-        <v>174091165580</v>
-      </c>
-      <c r="AJ42" s="23">
-        <v>33685965580</v>
+        <v>0</v>
+      </c>
+      <c r="AG42" s="16">
+        <v>33</v>
+      </c>
+      <c r="AH42" s="25">
+        <v>138751350000</v>
+      </c>
+      <c r="AI42" s="25">
+        <v>156651463820</v>
+      </c>
+      <c r="AJ42" s="25">
+        <v>17900113820</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
@@ -5367,61 +5375,61 @@
         <v>32</v>
       </c>
       <c r="D43">
-        <v>120.0642029213235</v>
+        <v>120.1030829930568</v>
       </c>
       <c r="E43">
-        <v>39735</v>
+        <v>39642</v>
       </c>
       <c r="F43">
-        <v>3325</v>
+        <v>3252</v>
       </c>
       <c r="G43">
-        <v>125.2851851851852</v>
+        <v>125.3185185185185</v>
       </c>
       <c r="H43">
-        <v>11.55185185185185</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="I43">
-        <v>11.55185185185185</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="J43">
-        <v>10.18888888888889</v>
+        <v>10.055555555555561</v>
       </c>
       <c r="K43">
-        <v>0.7592592592592593</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="L43">
-        <v>0.7592592592592593</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="M43">
+        <v>0.12592592592592591</v>
+      </c>
+      <c r="N43">
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O43">
         <v>0.13703703703703701</v>
       </c>
-      <c r="N43">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O43">
-        <v>0.14074074074074069</v>
-      </c>
       <c r="P43">
-        <v>125.3111111111111</v>
+        <v>125.05185185185189</v>
       </c>
       <c r="Q43" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="R43">
-        <v>35.185185185185183</v>
+        <v>37.037037037037038</v>
       </c>
       <c r="S43" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T43">
-        <v>55.185185185185183</v>
+        <v>51.481481481481481</v>
       </c>
       <c r="U43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V43">
-        <v>74.074074074074076</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="W43" t="s">
         <v>57</v>
@@ -5430,45 +5438,45 @@
         <v>70.370370370370367</v>
       </c>
       <c r="Y43">
-        <v>33827</v>
+        <v>33836</v>
       </c>
       <c r="Z43">
-        <v>3119</v>
+        <v>3054</v>
       </c>
       <c r="AA43">
-        <v>36946</v>
+        <v>36890</v>
       </c>
       <c r="AB43">
-        <v>2394</v>
+        <v>2372</v>
       </c>
       <c r="AC43">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AD43">
-        <v>2751</v>
+        <v>2715</v>
       </c>
       <c r="AE43">
+        <v>34</v>
+      </c>
+      <c r="AF43">
+        <v>3</v>
+      </c>
+      <c r="AG43" s="16">
         <v>37</v>
       </c>
-      <c r="AF43">
-        <v>1</v>
-      </c>
-      <c r="AG43" s="14">
-        <v>38</v>
-      </c>
-      <c r="AH43" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI43" s="23">
-        <v>165962058260</v>
-      </c>
-      <c r="AJ43" s="23">
-        <v>27734298260</v>
+      <c r="AH43" s="25">
+        <v>137704170000</v>
+      </c>
+      <c r="AI43" s="25">
+        <v>165386953580</v>
+      </c>
+      <c r="AJ43" s="25">
+        <v>27682783580</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -5477,103 +5485,103 @@
         <v>32</v>
       </c>
       <c r="D44">
-        <v>122.09464556178879</v>
+        <v>133.4587603019794</v>
       </c>
       <c r="E44">
-        <v>39768</v>
+        <v>39411</v>
       </c>
       <c r="F44">
-        <v>3342</v>
+        <v>3213</v>
       </c>
       <c r="G44">
-        <v>125.5222222222222</v>
+        <v>124.61481481481481</v>
       </c>
       <c r="H44">
-        <v>11.544444444444441</v>
+        <v>11.18148148148148</v>
       </c>
       <c r="I44">
-        <v>11.544444444444441</v>
+        <v>11.18148148148148</v>
       </c>
       <c r="J44">
-        <v>10.08888888888889</v>
+        <v>9.9851851851851858</v>
       </c>
       <c r="K44">
-        <v>0.82222222222222219</v>
+        <v>0.7</v>
       </c>
       <c r="L44">
-        <v>0.82222222222222219</v>
+        <v>0.7</v>
       </c>
       <c r="M44">
-        <v>0.1222222222222222</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N44">
-        <v>1.111111111111111E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O44">
-        <v>0.1333333333333333</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="P44">
-        <v>125.237037037037</v>
+        <v>124.1444444444444</v>
       </c>
       <c r="Q44" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="R44">
-        <v>32.962962962962962</v>
+        <v>37.037037037037038</v>
       </c>
       <c r="S44" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="T44">
-        <v>57.407407407407398</v>
+        <v>49.629629629629633</v>
       </c>
       <c r="U44" t="s">
-        <v>39</v>
-      </c>
-      <c r="V44" s="14">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="V44" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W44" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="X44">
-        <v>66.666666666666657</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="Y44">
-        <v>33891</v>
+        <v>33646</v>
       </c>
       <c r="Z44">
-        <v>3117</v>
+        <v>3019</v>
       </c>
       <c r="AA44">
-        <v>37008</v>
+        <v>36665</v>
       </c>
       <c r="AB44">
-        <v>2358</v>
+        <v>2307</v>
       </c>
       <c r="AC44">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="AD44">
-        <v>2724</v>
+        <v>2696</v>
       </c>
       <c r="AE44">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AF44">
-        <v>3</v>
-      </c>
-      <c r="AG44" s="14">
-        <v>36</v>
-      </c>
-      <c r="AH44" s="23">
-        <v>138227760000</v>
-      </c>
-      <c r="AI44" s="23">
-        <v>168768693640</v>
-      </c>
-      <c r="AJ44" s="23">
-        <v>30540933640</v>
+        <v>5</v>
+      </c>
+      <c r="AG44" s="15">
+        <v>50</v>
+      </c>
+      <c r="AH44" s="25">
+        <v>136656990000</v>
+      </c>
+      <c r="AI44" s="25">
+        <v>182380724720</v>
+      </c>
+      <c r="AJ44" s="25">
+        <v>45723734720</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.35">
@@ -5673,16 +5681,16 @@
       <c r="AF45">
         <v>5</v>
       </c>
-      <c r="AG45" s="14">
+      <c r="AG45" s="16">
         <v>36</v>
       </c>
-      <c r="AH45" s="23">
+      <c r="AH45" s="25">
         <v>139274940000</v>
       </c>
-      <c r="AI45" s="23">
+      <c r="AI45" s="25">
         <v>168388278120</v>
       </c>
-      <c r="AJ45" s="23">
+      <c r="AJ45" s="25">
         <v>29113338120</v>
       </c>
     </row>
@@ -5729,7 +5737,7 @@
   </sheetData>
   <autoFilter ref="A2:AM2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AM53">
-      <sortCondition descending="1" ref="X2"/>
+      <sortCondition ref="R2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -783,8 +783,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>15</v>
+      <c r="A3" t="n">
+        <v>35</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -796,117 +796,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
-        <v>144.9974295177756</v>
-      </c>
-      <c r="E3" t="n">
-        <v>39842</v>
+      <c r="D3" t="n">
+        <v>126.3735355064933</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>40759</v>
       </c>
       <c r="F3" t="n">
-        <v>3322</v>
+        <v>3357</v>
       </c>
       <c r="G3" t="n">
-        <v>125.8592592592593</v>
+        <v>128.862962962963</v>
       </c>
       <c r="H3" t="n">
-        <v>11.36296296296296</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="I3" t="n">
-        <v>11.36296296296296</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="J3" t="n">
-        <v>10.14814814814815</v>
+        <v>10.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.7814814814814814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.7814814814814814</v>
       </c>
       <c r="M3" t="n">
+        <v>0.1444444444444444</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01481481481481482</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.1592592592592593</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.1925925925925926</v>
-      </c>
       <c r="P3" t="n">
-        <v>125.3148148148148</v>
+        <v>128.3925925925926</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>64/270</t>
+          <t>94/270</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>23.70370370370371</v>
+        <v>34.81481481481482</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>164/270</t>
-        </is>
-      </c>
-      <c r="T3" s="15" t="n">
-        <v>60.74074074074074</v>
+          <t>149/270</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>55.18518518518518</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="V3" s="7" t="n">
-        <v>92.5925925925926</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="V3" s="19" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="X3" s="15" t="n">
-        <v>92.5925925925926</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="X3" s="16" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="Y3" t="n">
-        <v>33982</v>
+        <v>34793</v>
       </c>
       <c r="Z3" t="n">
-        <v>3068</v>
+        <v>3142</v>
       </c>
       <c r="AA3" t="n">
-        <v>37050</v>
+        <v>37935</v>
       </c>
       <c r="AB3" t="n">
-        <v>2287</v>
+        <v>2398</v>
       </c>
       <c r="AC3" t="n">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="AD3" t="n">
-        <v>2740</v>
+        <v>2781</v>
       </c>
       <c r="AE3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG3" t="n">
         <v>43</v>
       </c>
-      <c r="AF3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG3" s="15" t="n">
-        <v>52</v>
-      </c>
       <c r="AH3" s="17" t="n">
-        <v>138227760000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI3" s="17" t="n">
-        <v>200426698880</v>
-      </c>
-      <c r="AJ3" s="18" t="n">
-        <v>62198938880</v>
+        <v>178759157180</v>
+      </c>
+      <c r="AJ3" s="17" t="n">
+        <v>37306157180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -918,117 +918,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
-        <v>140.2647809094208</v>
-      </c>
-      <c r="E4" t="n">
-        <v>39870</v>
+      <c r="D4" s="16" t="n">
+        <v>136.1734986025962</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>40801</v>
       </c>
       <c r="F4" t="n">
-        <v>3318</v>
+        <v>3370</v>
       </c>
       <c r="G4" t="n">
-        <v>125.8444444444444</v>
+        <v>128.8888888888889</v>
       </c>
       <c r="H4" t="n">
-        <v>11.5</v>
+        <v>11.7037037037037</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>11.7037037037037</v>
       </c>
       <c r="J4" t="n">
-        <v>10.11851851851852</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.762962962962963</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.762962962962963</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1814814814814815</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.01481481481481482</v>
       </c>
       <c r="O4" s="15" t="n">
         <v>0.2037037037037037</v>
       </c>
       <c r="P4" t="n">
-        <v>125.3185185185185</v>
+        <v>128.2814814814815</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>83/270</t>
+          <t>92/270</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>30.74074074074074</v>
+        <v>34.07407407407408</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>153/270</t>
+          <t>151/270</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>56.66666666666666</v>
+        <v>55.92592592592592</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="V4" s="15" t="n">
-        <v>100</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="X4" s="15" t="n">
-        <v>92.5925925925926</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y4" t="n">
-        <v>33978</v>
+        <v>34800</v>
       </c>
       <c r="Z4" t="n">
-        <v>3105</v>
+        <v>3160</v>
       </c>
       <c r="AA4" t="n">
-        <v>37083</v>
+        <v>37960</v>
       </c>
       <c r="AB4" t="n">
-        <v>2305</v>
+        <v>2360</v>
       </c>
       <c r="AC4" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD4" t="n">
-        <v>2732</v>
+        <v>2786</v>
       </c>
       <c r="AE4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="15" t="n">
         <v>55</v>
       </c>
       <c r="AH4" s="17" t="n">
-        <v>138227760000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI4" s="17" t="n">
-        <v>193884864720</v>
+        <v>192507521760</v>
       </c>
       <c r="AJ4" s="18" t="n">
-        <v>55657104720</v>
+        <v>51138221760</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1040,60 +1040,60 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>139.8171660596771</v>
-      </c>
-      <c r="E5" t="n">
-        <v>39717</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3326</v>
+      <c r="D5" s="16" t="n">
+        <v>138.5605110020351</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>40801</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>3423</v>
       </c>
       <c r="G5" t="n">
-        <v>125.3703703703704</v>
+        <v>128.737037037037</v>
       </c>
       <c r="H5" t="n">
-        <v>11.45555555555556</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="I5" t="n">
-        <v>11.45555555555556</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="J5" t="n">
-        <v>10.07407407407407</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8481481481481481</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8481481481481481</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M5" t="n">
         <v>0.1851851851851852</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01481481481481482</v>
-      </c>
-      <c r="O5" s="15" t="n">
-        <v>0.2</v>
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2037037037037037</v>
       </c>
       <c r="P5" t="n">
-        <v>124.7740740740741</v>
+        <v>128.0740740740741</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>77/270</t>
+          <t>83/270</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>28.51851851851852</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>166/270</t>
-        </is>
-      </c>
-      <c r="T5" s="15" t="n">
-        <v>61.48148148148148</v>
+          <t>158/270</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>58.51851851851851</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1105,52 +1105,52 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="X5" s="15" t="n">
-        <v>96.29629629629629</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y5" t="n">
-        <v>33850</v>
+        <v>34759</v>
       </c>
       <c r="Z5" t="n">
-        <v>3093</v>
+        <v>3201</v>
       </c>
       <c r="AA5" t="n">
-        <v>36943</v>
+        <v>37960</v>
       </c>
       <c r="AB5" t="n">
-        <v>2275</v>
+        <v>2349</v>
       </c>
       <c r="AC5" t="n">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="AD5" t="n">
-        <v>2720</v>
+        <v>2786</v>
       </c>
       <c r="AE5" t="n">
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG5" s="15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH5" s="17" t="n">
-        <v>137704170000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI5" s="17" t="n">
-        <v>192534068040</v>
+        <v>195882024480</v>
       </c>
       <c r="AJ5" s="18" t="n">
-        <v>54829898040</v>
+        <v>54512724480</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>50</v>
+      <c r="A6" t="n">
+        <v>36</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1162,60 +1162,60 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
-        <v>138.5605110020351</v>
-      </c>
-      <c r="E6" t="n">
-        <v>40801</v>
+      <c r="D6" t="n">
+        <v>134.2185314698168</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>40773</v>
       </c>
       <c r="F6" t="n">
-        <v>3423</v>
+        <v>3382</v>
       </c>
       <c r="G6" t="n">
-        <v>128.737037037037</v>
+        <v>128.7740740740741</v>
       </c>
       <c r="H6" t="n">
-        <v>11.85555555555556</v>
+        <v>11.70740740740741</v>
       </c>
       <c r="I6" t="n">
-        <v>11.85555555555556</v>
+        <v>11.70740740740741</v>
       </c>
       <c r="J6" t="n">
-        <v>10.31851851851852</v>
+        <v>10.34814814814815</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8037037037037037</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8037037037037037</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1592592592592593</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.1814814814814815</v>
       </c>
       <c r="P6" t="n">
-        <v>128.0740740740741</v>
+        <v>128.3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>83/270</t>
+          <t>91/270</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>30.74074074074074</v>
+        <v>33.7037037037037</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>158/270</t>
-        </is>
-      </c>
-      <c r="T6" t="n">
-        <v>58.51851851851851</v>
+          <t>159/270</t>
+        </is>
+      </c>
+      <c r="T6" s="16" t="n">
+        <v>58.88888888888889</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1227,174 +1227,174 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>85.18518518518519</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="X6" s="16" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="Y6" t="n">
-        <v>34759</v>
+        <v>34769</v>
       </c>
       <c r="Z6" t="n">
-        <v>3201</v>
+        <v>3161</v>
       </c>
       <c r="AA6" t="n">
-        <v>37960</v>
+        <v>37930</v>
       </c>
       <c r="AB6" t="n">
-        <v>2349</v>
+        <v>2383</v>
       </c>
       <c r="AC6" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD6" t="n">
-        <v>2786</v>
+        <v>2794</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AF6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG6" s="15" t="n">
-        <v>55</v>
+        <v>6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>49</v>
       </c>
       <c r="AH6" s="17" t="n">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI6" s="17" t="n">
-        <v>195882024480</v>
-      </c>
-      <c r="AJ6" s="18" t="n">
-        <v>54512724480</v>
+        <v>189856139320</v>
+      </c>
+      <c r="AJ6" s="17" t="n">
+        <v>48403139320</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>100-369</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>126.3272132492698</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>40684</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3338</v>
+      </c>
+      <c r="G7" t="n">
+        <v>128.6222222222222</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.51481481481481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.51481481481481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.39259259259259</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.137037037037037</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.01481481481481482</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1518518518518518</v>
+      </c>
+      <c r="P7" t="n">
+        <v>128.3851851851852</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>88/270</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>32.5925925925926</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>144/270</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>19/27</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>70.37037037037037</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>34728</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3109</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>37837</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>225</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2806</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" t="n">
         <v>41</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>100-369</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>137.8777228817665</v>
-      </c>
-      <c r="E7" t="n">
-        <v>39534</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3291</v>
-      </c>
-      <c r="G7" t="n">
-        <v>124.8148148148148</v>
-      </c>
-      <c r="H7" t="n">
-        <v>11.34814814814815</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.34814814814815</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10.07037037037037</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8222222222222222</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.8222222222222222</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.1703703703703704</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.01851851851851852</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.1888888888888889</v>
-      </c>
-      <c r="P7" t="n">
-        <v>124.3925925925926</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>79/270</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>29.25925925925926</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>169/270</t>
-        </is>
-      </c>
-      <c r="T7" s="15" t="n">
-        <v>62.59259259259259</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="n">
-        <v>92.5925925925926</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>33700</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3064</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>36764</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2293</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>222</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2719</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG7" s="15" t="n">
-        <v>51</v>
-      </c>
       <c r="AH7" s="17" t="n">
-        <v>137180580000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI7" s="17" t="n">
-        <v>189141459940</v>
-      </c>
-      <c r="AJ7" s="18" t="n">
-        <v>51960879940</v>
+        <v>178587897080</v>
+      </c>
+      <c r="AJ7" s="17" t="n">
+        <v>37218597080</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>10</v>
+      <c r="A8" t="n">
+        <v>32</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1406,117 +1406,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>137.5304207348065</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40474</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3338</v>
+      <c r="D8" t="n">
+        <v>127.7335127851654</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>40773</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>3434</v>
       </c>
       <c r="G8" t="n">
-        <v>127.9296296296296</v>
+        <v>128.6518518518519</v>
       </c>
       <c r="H8" t="n">
-        <v>11.53333333333333</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="I8" t="n">
-        <v>11.53333333333333</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="J8" t="n">
-        <v>10.24814814814815</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8074074074074075</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8074074074074075</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="M8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003703703703703704</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.1703703703703704</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.02222222222222222</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.1925925925925926</v>
-      </c>
       <c r="P8" t="n">
-        <v>127.3444444444444</v>
+        <v>128.1074074074074</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>85/270</t>
+          <t>82/270</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>31.48148148148148</v>
+        <v>30.37037037037037</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>152/270</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
-        <v>56.2962962962963</v>
+          <t>170/270</t>
+        </is>
+      </c>
+      <c r="T8" s="15" t="n">
+        <v>62.96296296296296</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>23/27</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>88.88888888888889</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>20/27</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>81.48148148148148</v>
+        <v>74.07407407407408</v>
       </c>
       <c r="Y8" t="n">
-        <v>34541</v>
+        <v>34736</v>
       </c>
       <c r="Z8" t="n">
-        <v>3114</v>
+        <v>3205</v>
       </c>
       <c r="AA8" t="n">
-        <v>37655</v>
+        <v>37941</v>
       </c>
       <c r="AB8" t="n">
-        <v>2341</v>
+        <v>2374</v>
       </c>
       <c r="AC8" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="AD8" t="n">
-        <v>2767</v>
+        <v>2786</v>
       </c>
       <c r="AE8" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
         <v>46</v>
       </c>
-      <c r="AF8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG8" s="15" t="n">
-        <v>52</v>
-      </c>
       <c r="AH8" s="17" t="n">
-        <v>140322120000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI8" s="17" t="n">
-        <v>192985602020</v>
-      </c>
-      <c r="AJ8" s="18" t="n">
-        <v>52663482020</v>
+        <v>180682885840</v>
+      </c>
+      <c r="AJ8" s="17" t="n">
+        <v>39229885840</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>49</v>
+      <c r="A9" t="n">
+        <v>37</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1528,60 +1528,60 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
-        <v>136.1734986025962</v>
-      </c>
-      <c r="E9" t="n">
-        <v>40801</v>
+      <c r="D9" t="n">
+        <v>125.4517707224308</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>40718</v>
       </c>
       <c r="F9" t="n">
-        <v>3370</v>
+        <v>3381</v>
       </c>
       <c r="G9" t="n">
-        <v>128.8888888888889</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>11.7037037037037</v>
+        <v>11.70740740740741</v>
       </c>
       <c r="I9" t="n">
-        <v>11.7037037037037</v>
+        <v>11.70740740740741</v>
       </c>
       <c r="J9" t="n">
         <v>10.31851851851852</v>
       </c>
       <c r="K9" t="n">
-        <v>0.762962962962963</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="L9" t="n">
-        <v>0.762962962962963</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1888888888888889</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01481481481481482</v>
-      </c>
-      <c r="O9" s="15" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1481481481481481</v>
       </c>
       <c r="P9" t="n">
-        <v>128.2814814814815</v>
+        <v>128.3037037037037</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>92/270</t>
+          <t>100/270</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>34.07407407407408</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>151/270</t>
+          <t>148/270</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>55.92592592592592</v>
+        <v>54.81481481481482</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1593,52 +1593,52 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>20/27</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>85.18518518518519</v>
+        <v>74.07407407407408</v>
       </c>
       <c r="Y9" t="n">
-        <v>34800</v>
+        <v>34731</v>
       </c>
       <c r="Z9" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="AA9" t="n">
-        <v>37960</v>
+        <v>37892</v>
       </c>
       <c r="AB9" t="n">
-        <v>2360</v>
+        <v>2411</v>
       </c>
       <c r="AC9" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AD9" t="n">
         <v>2786</v>
       </c>
       <c r="AE9" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="AF9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG9" s="15" t="n">
-        <v>55</v>
+        <v>5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>40</v>
       </c>
       <c r="AH9" s="17" t="n">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI9" s="17" t="n">
-        <v>192507521760</v>
-      </c>
-      <c r="AJ9" s="18" t="n">
-        <v>51138221760</v>
+        <v>177455293240</v>
+      </c>
+      <c r="AJ9" s="17" t="n">
+        <v>36002293240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1651,116 +1651,116 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>136.7878287180075</v>
-      </c>
-      <c r="E10" t="n">
-        <v>39232</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3340</v>
+        <v>123.7648688681046</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>40737</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>3458</v>
       </c>
       <c r="G10" t="n">
-        <v>123.562962962963</v>
+        <v>128.4185185185185</v>
       </c>
       <c r="H10" t="n">
-        <v>11.56666666666667</v>
+        <v>11.98888888888889</v>
       </c>
       <c r="I10" t="n">
-        <v>11.56666666666667</v>
+        <v>11.98888888888889</v>
       </c>
       <c r="J10" t="n">
-        <v>9.988888888888889</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7851851851851852</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7851851851851852</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1518518518518518</v>
       </c>
       <c r="P10" t="n">
-        <v>123.1222222222222</v>
+        <v>128.0185185185185</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>82/270</t>
+          <t>89/270</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>30.37037037037037</v>
+        <v>32.96296296296296</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>161/270</t>
-        </is>
-      </c>
-      <c r="T10" s="16" t="n">
-        <v>59.62962962962963</v>
+          <t>153/270</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>56.66666666666666</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="V10" s="19" t="n">
-        <v>96.29629629629629</v>
+          <t>21/27</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>77.77777777777779</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>19/27</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>85.18518518518519</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="Y10" t="n">
-        <v>33362</v>
+        <v>34673</v>
       </c>
       <c r="Z10" t="n">
-        <v>3123</v>
+        <v>3237</v>
       </c>
       <c r="AA10" t="n">
-        <v>36485</v>
+        <v>37910</v>
       </c>
       <c r="AB10" t="n">
-        <v>2285</v>
+        <v>2403</v>
       </c>
       <c r="AC10" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AD10" t="n">
-        <v>2697</v>
+        <v>2786</v>
       </c>
       <c r="AE10" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="15" t="n">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>41</v>
       </c>
       <c r="AH10" s="17" t="n">
-        <v>136133400000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI10" s="17" t="n">
-        <v>186213922020</v>
+        <v>175069119960</v>
       </c>
       <c r="AJ10" s="17" t="n">
-        <v>50080522020</v>
+        <v>33616119960</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>51</v>
+      <c r="A11" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1769,120 +1769,120 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>136.6510792588615</v>
-      </c>
-      <c r="E11" t="n">
-        <v>38930</v>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>138.0559893517524</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>40629</v>
       </c>
       <c r="F11" t="n">
-        <v>3268</v>
+        <v>3335</v>
       </c>
       <c r="G11" t="n">
-        <v>122.762962962963</v>
+        <v>128.9479553903346</v>
       </c>
       <c r="H11" t="n">
-        <v>11.31851851851852</v>
+        <v>11.56505576208178</v>
       </c>
       <c r="I11" t="n">
-        <v>11.31851851851852</v>
+        <v>11.56505576208178</v>
       </c>
       <c r="J11" t="n">
-        <v>9.918518518518519</v>
+        <v>10.3271375464684</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8104089219330854</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8104089219330854</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1747211895910781</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.02230483271375465</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1970260223048327</v>
       </c>
       <c r="P11" t="n">
-        <v>122.3518518518518</v>
+        <v>128.3531598513011</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>82/270</t>
+          <t>85/269</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>30.37037037037037</v>
+        <v>31.59851301115242</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>158/270</t>
-        </is>
-      </c>
-      <c r="T11" s="16" t="n">
-        <v>58.51851851851851</v>
+          <t>153/269</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>56.87732342007435</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="V11" s="15" t="n">
-        <v>100</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>85.18518518518519</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="Y11" t="n">
-        <v>33146</v>
+        <v>34687</v>
       </c>
       <c r="Z11" t="n">
-        <v>3056</v>
+        <v>3111</v>
       </c>
       <c r="AA11" t="n">
-        <v>36202</v>
+        <v>37798</v>
       </c>
       <c r="AB11" t="n">
-        <v>2271</v>
+        <v>2348</v>
       </c>
       <c r="AC11" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AD11" t="n">
-        <v>2678</v>
+        <v>2778</v>
       </c>
       <c r="AE11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11" s="15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AH11" s="17" t="n">
-        <v>135086220000</v>
+        <v>140845710000</v>
       </c>
       <c r="AI11" s="17" t="n">
-        <v>184596777560</v>
-      </c>
-      <c r="AJ11" s="17" t="n">
-        <v>49510557560</v>
+        <v>194445938400</v>
+      </c>
+      <c r="AJ11" s="18" t="n">
+        <v>53600228400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1895,116 +1895,116 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>135.0130755550814</v>
-      </c>
-      <c r="E12" t="n">
-        <v>39423</v>
+        <v>134.7273627300977</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>40771</v>
       </c>
       <c r="F12" t="n">
-        <v>3338</v>
+        <v>3411</v>
       </c>
       <c r="G12" t="n">
-        <v>124.3148148148148</v>
+        <v>128.6148148148148</v>
       </c>
       <c r="H12" t="n">
-        <v>11.52962962962963</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="I12" t="n">
-        <v>11.52962962962963</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="J12" t="n">
-        <v>9.977777777777778</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K12" t="n">
-        <v>0.825925925925926</v>
+        <v>0.7814814814814814</v>
       </c>
       <c r="L12" t="n">
-        <v>0.825925925925926</v>
+        <v>0.7814814814814814</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1814814814814815</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N12" t="n">
         <v>0.007407407407407408</v>
       </c>
-      <c r="O12" t="n">
-        <v>0.1888888888888889</v>
+      <c r="O12" s="15" t="n">
+        <v>0.2037037037037037</v>
       </c>
       <c r="P12" t="n">
-        <v>123.7259259259259</v>
+        <v>128.1148148148148</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>67/270</t>
+          <t>91/270</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>24.81481481481481</v>
+        <v>33.7037037037037</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>168/270</t>
-        </is>
-      </c>
-      <c r="T12" s="15" t="n">
-        <v>62.22222222222222</v>
+          <t>155/270</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>57.4074074074074</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>88.88888888888889</v>
+          <t>27/27</t>
+        </is>
+      </c>
+      <c r="V12" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
-        <v>81.48148148148148</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="X12" s="15" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="Y12" t="n">
-        <v>33565</v>
+        <v>34726</v>
       </c>
       <c r="Z12" t="n">
-        <v>3113</v>
+        <v>3198</v>
       </c>
       <c r="AA12" t="n">
-        <v>36678</v>
+        <v>37924</v>
       </c>
       <c r="AB12" t="n">
-        <v>2267</v>
+        <v>2361</v>
       </c>
       <c r="AC12" t="n">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="AD12" t="n">
-        <v>2694</v>
+        <v>2792</v>
       </c>
       <c r="AE12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" s="15" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AH12" s="17" t="n">
-        <v>136656990000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI12" s="17" t="n">
-        <v>184504805160</v>
+        <v>190463129600</v>
       </c>
       <c r="AJ12" s="17" t="n">
-        <v>47847815160</v>
+        <v>49093829600</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2017,116 +2017,116 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>134.511786441983</v>
+        <v>119.321995058333</v>
       </c>
       <c r="E13" t="n">
-        <v>40171</v>
+        <v>40671</v>
       </c>
       <c r="F13" t="n">
-        <v>3296</v>
+        <v>3419</v>
       </c>
       <c r="G13" t="n">
-        <v>126.9333333333333</v>
+        <v>128.3185185185185</v>
       </c>
       <c r="H13" t="n">
-        <v>11.45555555555556</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="I13" t="n">
-        <v>11.45555555555556</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="J13" t="n">
-        <v>10.18888888888889</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1962962962962963</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="N13" t="n">
-        <v>0.007407407407407408</v>
-      </c>
-      <c r="O13" s="15" t="n">
-        <v>0.2037037037037037</v>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1407407407407407</v>
       </c>
       <c r="P13" t="n">
-        <v>126.4592592592593</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>81/270</t>
+          <t>86/270</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>30</v>
+        <v>31.85185185185185</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>152/270</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>56.2962962962963</v>
+          <t>158/270</t>
+        </is>
+      </c>
+      <c r="T13" s="16" t="n">
+        <v>58.51851851851851</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>88.88888888888889</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>77.77777777777779</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="Y13" t="n">
-        <v>34272</v>
+        <v>34646</v>
       </c>
       <c r="Z13" t="n">
-        <v>3093</v>
+        <v>3197</v>
       </c>
       <c r="AA13" t="n">
-        <v>37365</v>
+        <v>37843</v>
       </c>
       <c r="AB13" t="n">
-        <v>2330</v>
+        <v>2416</v>
       </c>
       <c r="AC13" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="AD13" t="n">
-        <v>2751</v>
+        <v>2790</v>
       </c>
       <c r="AE13" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" s="15" t="n">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>38</v>
       </c>
       <c r="AH13" s="17" t="n">
-        <v>139274940000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI13" s="17" t="n">
-        <v>187341209860</v>
+        <v>168684669160</v>
       </c>
       <c r="AJ13" s="17" t="n">
-        <v>48066269860</v>
+        <v>27315369160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2139,116 +2139,116 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>134.3712618578823</v>
+        <v>129.8896579809053</v>
       </c>
       <c r="E14" t="n">
-        <v>39378</v>
+        <v>40727</v>
       </c>
       <c r="F14" t="n">
-        <v>3176</v>
+        <v>3298</v>
       </c>
       <c r="G14" t="n">
-        <v>124.6185185185185</v>
+        <v>128.9148148148148</v>
       </c>
       <c r="H14" t="n">
-        <v>11.01111111111111</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="I14" t="n">
-        <v>11.01111111111111</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="J14" t="n">
-        <v>10.02962962962963</v>
+        <v>10.37407407407407</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1777777777777778</v>
       </c>
       <c r="P14" t="n">
-        <v>124.3148148148148</v>
+        <v>128.5333333333333</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>88/270</t>
+          <t>95/270</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>32.5925925925926</v>
+        <v>35.18518518518518</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>155/270</t>
+          <t>146/270</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>57.4074074074074</v>
+        <v>54.07407407407408</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>88.88888888888889</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="X14" s="16" t="n">
-        <v>88.88888888888889</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y14" t="n">
-        <v>33647</v>
+        <v>34807</v>
       </c>
       <c r="Z14" t="n">
-        <v>2973</v>
+        <v>3071</v>
       </c>
       <c r="AA14" t="n">
-        <v>36620</v>
+        <v>37878</v>
       </c>
       <c r="AB14" t="n">
-        <v>2310</v>
+        <v>2384</v>
       </c>
       <c r="AC14" t="n">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="AD14" t="n">
-        <v>2708</v>
+        <v>2801</v>
       </c>
       <c r="AE14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="15" t="n">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>48</v>
       </c>
       <c r="AH14" s="17" t="n">
-        <v>136656990000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI14" s="17" t="n">
-        <v>183627721880</v>
+        <v>183624100260</v>
       </c>
       <c r="AJ14" s="17" t="n">
-        <v>46970731880</v>
+        <v>42254800260</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2261,116 +2261,116 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>134.1766010804284</v>
+        <v>126.7059508387945</v>
       </c>
       <c r="E15" t="n">
-        <v>40464</v>
+        <v>40752</v>
       </c>
       <c r="F15" t="n">
-        <v>3382</v>
+        <v>3420</v>
       </c>
       <c r="G15" t="n">
-        <v>127.6592592592593</v>
+        <v>128.6666666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>11.74444444444444</v>
+        <v>11.7962962962963</v>
       </c>
       <c r="I15" t="n">
-        <v>11.74444444444444</v>
+        <v>11.7962962962963</v>
       </c>
       <c r="J15" t="n">
-        <v>10.26296296296296</v>
+        <v>10.31111111111111</v>
       </c>
       <c r="K15" t="n">
-        <v>0.774074074074074</v>
+        <v>0.8629629629629629</v>
       </c>
       <c r="L15" t="n">
-        <v>0.774074074074074</v>
+        <v>0.8629629629629629</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1925925925925926</v>
+        <v>0.1518518518518518</v>
       </c>
       <c r="N15" t="n">
         <v>0.007407407407407408</v>
       </c>
-      <c r="O15" s="15" t="n">
-        <v>0.2</v>
+      <c r="O15" t="n">
+        <v>0.1592592592592593</v>
       </c>
       <c r="P15" t="n">
-        <v>127.1851851851852</v>
+        <v>128.1592592592593</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>87/270</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>33.7037037037037</v>
+        <v>32.22222222222222</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>153/270</t>
+          <t>152/270</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>56.66666666666666</v>
+        <v>56.2962962962963</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>27/27</t>
-        </is>
-      </c>
-      <c r="V15" s="15" t="n">
-        <v>100</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="V15" s="19" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="X15" s="15" t="n">
-        <v>96.29629629629629</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="X15" s="16" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="Y15" t="n">
-        <v>34468</v>
+        <v>34740</v>
       </c>
       <c r="Z15" t="n">
-        <v>3171</v>
+        <v>3185</v>
       </c>
       <c r="AA15" t="n">
-        <v>37639</v>
+        <v>37925</v>
       </c>
       <c r="AB15" t="n">
-        <v>2346</v>
+        <v>2379</v>
       </c>
       <c r="AC15" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="AD15" t="n">
-        <v>2771</v>
+        <v>2784</v>
       </c>
       <c r="AE15" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AF15" t="n">
         <v>2</v>
       </c>
-      <c r="AG15" s="15" t="n">
-        <v>54</v>
+      <c r="AG15" t="n">
+        <v>43</v>
       </c>
       <c r="AH15" s="17" t="n">
-        <v>140322120000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI15" s="17" t="n">
-        <v>188279451180</v>
+        <v>179229368640</v>
       </c>
       <c r="AJ15" s="17" t="n">
-        <v>47957331180</v>
+        <v>37776368640</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2383,238 +2383,238 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>133.9150640652789</v>
+        <v>133.2479078987367</v>
       </c>
       <c r="E16" t="n">
-        <v>39831</v>
+        <v>40755</v>
       </c>
       <c r="F16" t="n">
-        <v>3196</v>
+        <v>3426</v>
       </c>
       <c r="G16" t="n">
-        <v>126.1259259259259</v>
+        <v>128.6037037037037</v>
       </c>
       <c r="H16" t="n">
-        <v>11.07037037037037</v>
+        <v>11.85185185185185</v>
       </c>
       <c r="I16" t="n">
-        <v>11.07037037037037</v>
+        <v>11.85185185185185</v>
       </c>
       <c r="J16" t="n">
-        <v>10.14074074074074</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7481481481481481</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7481481481481481</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.02592592592592593</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="P16" t="n">
-        <v>125.8</v>
+        <v>128.137037037037</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>88/270</t>
+          <t>89/270</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>32.5925925925926</v>
+        <v>32.96296296296296</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>157/270</t>
         </is>
       </c>
-      <c r="T16" s="16" t="n">
+      <c r="T16" t="n">
         <v>58.14814814814815</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>88.88888888888889</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="X16" s="16" t="n">
-        <v>88.88888888888889</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y16" t="n">
-        <v>34054</v>
+        <v>34723</v>
       </c>
       <c r="Z16" t="n">
-        <v>2989</v>
+        <v>3200</v>
       </c>
       <c r="AA16" t="n">
-        <v>37043</v>
+        <v>37923</v>
       </c>
       <c r="AB16" t="n">
-        <v>2336</v>
+        <v>2383</v>
       </c>
       <c r="AC16" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="AD16" t="n">
-        <v>2738</v>
+        <v>2786</v>
       </c>
       <c r="AE16" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG16" s="15" t="n">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>46</v>
       </c>
       <c r="AH16" s="17" t="n">
-        <v>138227760000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI16" s="17" t="n">
-        <v>185107793360</v>
+        <v>188483163160</v>
       </c>
       <c r="AJ16" s="17" t="n">
-        <v>46880033360</v>
+        <v>47030163160</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>100-369</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>120.4952906182601</v>
+      </c>
+      <c r="E17" t="n">
+        <v>40686</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3412</v>
+      </c>
+      <c r="G17" t="n">
+        <v>128.3666666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11.88518518518518</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.88518518518518</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10.3037037037037</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1148148148148148</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="P17" t="n">
+        <v>128.1111111111111</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>112/270</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>41.48148148148148</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>140/270</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>51.85185185185185</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>74.07407407407408</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>59.25925925925925</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>34659</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3209</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>37868</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2440</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>198</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2782</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>36</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>100-369</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>133.5215300175762</v>
-      </c>
-      <c r="E17" t="n">
-        <v>40616</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3367</v>
-      </c>
-      <c r="G17" t="n">
-        <v>128.2851851851852</v>
-      </c>
-      <c r="H17" t="n">
-        <v>11.65555555555556</v>
-      </c>
-      <c r="I17" t="n">
-        <v>11.65555555555556</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10.31111111111111</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7925925925925926</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.7925925925925926</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.02222222222222222</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="P17" t="n">
-        <v>127.8333333333333</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>91/270</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>33.7037037037037</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>158/270</t>
-        </is>
-      </c>
-      <c r="T17" s="16" t="n">
-        <v>58.51851851851851</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="V17" s="19" t="n">
-        <v>96.29629629629629</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="X17" s="16" t="n">
-        <v>88.88888888888889</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>34637</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3147</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>37784</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2378</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>214</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2784</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>48</v>
-      </c>
       <c r="AH17" s="17" t="n">
-        <v>140929100000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI17" s="17" t="n">
-        <v>188170690560</v>
+        <v>170343348880</v>
       </c>
       <c r="AJ17" s="17" t="n">
-        <v>47241590560</v>
+        <v>28974048880</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2627,116 +2627,116 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>133.4587603019794</v>
+        <v>129.8617456689677</v>
       </c>
       <c r="E18" t="n">
-        <v>39411</v>
+        <v>40740</v>
       </c>
       <c r="F18" t="n">
-        <v>3213</v>
+        <v>3322</v>
       </c>
       <c r="G18" t="n">
-        <v>124.6148148148148</v>
+        <v>128.7851851851852</v>
       </c>
       <c r="H18" t="n">
-        <v>11.18148148148148</v>
+        <v>11.52592592592593</v>
       </c>
       <c r="I18" t="n">
-        <v>11.18148148148148</v>
+        <v>11.52592592592593</v>
       </c>
       <c r="J18" t="n">
-        <v>9.985185185185186</v>
+        <v>10.38888888888889</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7</v>
+        <v>0.774074074074074</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7</v>
+        <v>0.774074074074074</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.003703703703703704</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="P18" t="n">
-        <v>124.1444444444444</v>
+        <v>128.4444444444445</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>100/270</t>
+          <t>91/270</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>37.03703703703704</v>
+        <v>33.7037037037037</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>134/270</t>
+          <t>147/270</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>49.62962962962963</v>
+        <v>54.44444444444444</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>27/27</t>
+        </is>
+      </c>
+      <c r="V18" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>24/27</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>88.88888888888889</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
-        <v>81.48148148148148</v>
-      </c>
       <c r="Y18" t="n">
-        <v>33646</v>
+        <v>34772</v>
       </c>
       <c r="Z18" t="n">
-        <v>3019</v>
+        <v>3112</v>
       </c>
       <c r="AA18" t="n">
-        <v>36665</v>
+        <v>37884</v>
       </c>
       <c r="AB18" t="n">
-        <v>2307</v>
+        <v>2392</v>
       </c>
       <c r="AC18" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="AD18" t="n">
-        <v>2696</v>
+        <v>2805</v>
       </c>
       <c r="AE18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH18" s="17" t="n">
-        <v>136656990000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI18" s="17" t="n">
-        <v>182380724720</v>
+        <v>183584640820</v>
       </c>
       <c r="AJ18" s="17" t="n">
-        <v>45723734720</v>
+        <v>42215340820</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2749,43 +2749,43 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>132.7447509745998</v>
+        <v>133.5813685998304</v>
       </c>
       <c r="E19" t="n">
-        <v>38924</v>
+        <v>40771</v>
       </c>
       <c r="F19" t="n">
-        <v>3150</v>
+        <v>3348</v>
       </c>
       <c r="G19" t="n">
-        <v>123.2518518518519</v>
+        <v>128.8148148148148</v>
       </c>
       <c r="H19" t="n">
-        <v>10.84074074074074</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="I19" t="n">
-        <v>10.84074074074074</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="J19" t="n">
-        <v>9.9</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01481481481481482</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.1703703703703704</v>
+        <v>0.007407407407407408</v>
+      </c>
+      <c r="O19" s="15" t="n">
+        <v>0.2037037037037037</v>
       </c>
       <c r="P19" t="n">
-        <v>122.8259259259259</v>
+        <v>128.3481481481481</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2797,11 +2797,11 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>149/270</t>
+          <t>153/270</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>55.18518518518518</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2813,52 +2813,52 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="X19" s="16" t="n">
-        <v>88.88888888888889</v>
+          <t>21/27</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>77.77777777777779</v>
       </c>
       <c r="Y19" t="n">
-        <v>33278</v>
+        <v>34780</v>
       </c>
       <c r="Z19" t="n">
-        <v>2927</v>
+        <v>3144</v>
       </c>
       <c r="AA19" t="n">
-        <v>36205</v>
+        <v>37924</v>
       </c>
       <c r="AB19" t="n">
-        <v>2270</v>
+        <v>2370</v>
       </c>
       <c r="AC19" t="n">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="AD19" t="n">
-        <v>2673</v>
+        <v>2792</v>
       </c>
       <c r="AE19" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AF19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>46</v>
+        <v>2</v>
+      </c>
+      <c r="AG19" s="15" t="n">
+        <v>55</v>
       </c>
       <c r="AH19" s="17" t="n">
-        <v>135086220000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI19" s="17" t="n">
-        <v>179319866340</v>
+        <v>188843045720</v>
       </c>
       <c r="AJ19" s="17" t="n">
-        <v>44233646340</v>
+        <v>47473745720</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2871,51 +2871,51 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>132.1925913982936</v>
+        <v>128.7777044389302</v>
       </c>
       <c r="E20" t="n">
-        <v>38919</v>
+        <v>40788</v>
       </c>
       <c r="F20" t="n">
-        <v>3226</v>
+        <v>3325</v>
       </c>
       <c r="G20" t="n">
-        <v>122.8185185185185</v>
+        <v>129.0481481481482</v>
       </c>
       <c r="H20" t="n">
-        <v>11.20740740740741</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I20" t="n">
-        <v>11.20740740740741</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J20" t="n">
-        <v>9.933333333333334</v>
+        <v>10.32962962962963</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M20" t="n">
         <v>0.1777777777777778</v>
       </c>
       <c r="N20" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.003703703703703704</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1814814814814815</v>
       </c>
       <c r="P20" t="n">
-        <v>122.537037037037</v>
+        <v>128.5111111111111</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>80/270</t>
+          <t>90/270</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>29.62962962962963</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2935,52 +2935,52 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="X20" t="n">
-        <v>85.18518518518519</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="X20" s="15" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="Y20" t="n">
-        <v>33161</v>
+        <v>34843</v>
       </c>
       <c r="Z20" t="n">
-        <v>3026</v>
+        <v>3107</v>
       </c>
       <c r="AA20" t="n">
-        <v>36187</v>
+        <v>37950</v>
       </c>
       <c r="AB20" t="n">
-        <v>2284</v>
+        <v>2376</v>
       </c>
       <c r="AC20" t="n">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="AD20" t="n">
-        <v>2682</v>
+        <v>2789</v>
       </c>
       <c r="AE20" t="n">
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" s="15" t="n">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>49</v>
       </c>
       <c r="AH20" s="17" t="n">
-        <v>135086220000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI20" s="17" t="n">
-        <v>178573974840</v>
+        <v>182159926260</v>
       </c>
       <c r="AJ20" s="17" t="n">
-        <v>43487754840</v>
+        <v>40706926260</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2993,116 +2993,116 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>132.1378544088796</v>
+        <v>113.2579520588982</v>
       </c>
       <c r="E21" t="n">
-        <v>40145</v>
+        <v>40645</v>
       </c>
       <c r="F21" t="n">
-        <v>3373</v>
+        <v>3337</v>
       </c>
       <c r="G21" t="n">
-        <v>126.6888888888889</v>
+        <v>128.4333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>11.67037037037037</v>
+        <v>11.62592592592593</v>
       </c>
       <c r="I21" t="n">
-        <v>11.67037037037037</v>
+        <v>11.62592592592593</v>
       </c>
       <c r="J21" t="n">
-        <v>10.16296296296296</v>
+        <v>10.35185185185185</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>0.137037037037037</v>
+        <v>0.1259259259259259</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02592592592592593</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.162962962962963</v>
+        <v>0.1259259259259259</v>
       </c>
       <c r="P21" t="n">
-        <v>126.2518518518519</v>
+        <v>128.3888888888889</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>88/270</t>
+          <t>100/270</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>32.5925925925926</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>154/270</t>
+          <t>147/270</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>57.03703703703704</v>
+        <v>54.44444444444444</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>92.5925925925926</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>20/27</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>85.18518518518519</v>
+        <v>74.07407407407408</v>
       </c>
       <c r="Y21" t="n">
-        <v>34206</v>
+        <v>34677</v>
       </c>
       <c r="Z21" t="n">
-        <v>3151</v>
+        <v>3139</v>
       </c>
       <c r="AA21" t="n">
-        <v>37357</v>
+        <v>37816</v>
       </c>
       <c r="AB21" t="n">
-        <v>2353</v>
+        <v>2461</v>
       </c>
       <c r="AC21" t="n">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AD21" t="n">
-        <v>2744</v>
+        <v>2795</v>
       </c>
       <c r="AE21" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AH21" s="17" t="n">
-        <v>139357400000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI21" s="17" t="n">
-        <v>184143878320</v>
+        <v>160111974020</v>
       </c>
       <c r="AJ21" s="17" t="n">
-        <v>44786478320</v>
+        <v>18742674020</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3115,116 +3115,116 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>132.0806445787366</v>
+        <v>126.4057725970207</v>
       </c>
       <c r="E22" t="n">
-        <v>39075</v>
+        <v>40733</v>
       </c>
       <c r="F22" t="n">
-        <v>3261</v>
+        <v>3334</v>
       </c>
       <c r="G22" t="n">
-        <v>123.3444444444444</v>
+        <v>128.7259259259259</v>
       </c>
       <c r="H22" t="n">
-        <v>11.31111111111111</v>
+        <v>11.60740740740741</v>
       </c>
       <c r="I22" t="n">
-        <v>11.31111111111111</v>
+        <v>11.60740740740741</v>
       </c>
       <c r="J22" t="n">
-        <v>9.896296296296295</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7481481481481481</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7481481481481481</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1518518518518518</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1703703703703704</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="P22" t="n">
-        <v>122.937037037037</v>
+        <v>128.4</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>90/270</t>
+          <t>93/270</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>33.33333333333333</v>
+        <v>34.44444444444444</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>147/270</t>
+          <t>138/270</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>54.44444444444444</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>88.88888888888889</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="V22" s="19" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>21/27</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>85.18518518518519</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="Y22" t="n">
-        <v>33303</v>
+        <v>34756</v>
       </c>
       <c r="Z22" t="n">
-        <v>3054</v>
+        <v>3134</v>
       </c>
       <c r="AA22" t="n">
-        <v>36357</v>
+        <v>37890</v>
       </c>
       <c r="AB22" t="n">
-        <v>2286</v>
+        <v>2410</v>
       </c>
       <c r="AC22" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AD22" t="n">
-        <v>2672</v>
+        <v>2796</v>
       </c>
       <c r="AE22" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AF22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH22" s="17" t="n">
-        <v>135609810000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI22" s="17" t="n">
-        <v>179114311160</v>
+        <v>178698955880</v>
       </c>
       <c r="AJ22" s="17" t="n">
-        <v>43504501160</v>
+        <v>37329655880</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3237,59 +3237,59 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>131.3061087059805</v>
+        <v>127.4071409280516</v>
       </c>
       <c r="E23" t="n">
-        <v>38933</v>
+        <v>40707</v>
       </c>
       <c r="F23" t="n">
-        <v>3060</v>
+        <v>3470</v>
       </c>
       <c r="G23" t="n">
-        <v>123.537037037037</v>
+        <v>128.2888888888889</v>
       </c>
       <c r="H23" t="n">
-        <v>10.56296296296296</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="I23" t="n">
-        <v>10.56296296296296</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="J23" t="n">
-        <v>9.911111111111111</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1814814814814815</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="N23" t="n">
-        <v>0.003703703703703704</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P23" t="n">
-        <v>123.1740740740741</v>
+        <v>127.8962962962963</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>79/270</t>
+          <t>93/270</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>29.25925925925926</v>
+        <v>34.44444444444444</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>148/270</t>
+          <t>154/270</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>54.81481481481482</v>
+        <v>57.03703703703704</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3301,52 +3301,52 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>85.18518518518519</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="Y23" t="n">
-        <v>33355</v>
+        <v>34638</v>
       </c>
       <c r="Z23" t="n">
-        <v>2852</v>
+        <v>3239</v>
       </c>
       <c r="AA23" t="n">
-        <v>36207</v>
+        <v>37877</v>
       </c>
       <c r="AB23" t="n">
-        <v>2269</v>
+        <v>2381</v>
       </c>
       <c r="AC23" t="n">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="AD23" t="n">
-        <v>2676</v>
+        <v>2786</v>
       </c>
       <c r="AE23" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="15" t="n">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>44</v>
       </c>
       <c r="AH23" s="17" t="n">
-        <v>135086220000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI23" s="17" t="n">
-        <v>177376458880</v>
+        <v>180114583280</v>
       </c>
       <c r="AJ23" s="17" t="n">
-        <v>42290238880</v>
+        <v>38745283280</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>26</v>
+      <c r="A24" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3358,60 +3358,60 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>130.3964865868046</v>
+      <c r="D24" s="15" t="n">
+        <v>143.9434335460386</v>
       </c>
       <c r="E24" t="n">
-        <v>40277</v>
+        <v>40738</v>
       </c>
       <c r="F24" t="n">
-        <v>3252</v>
+        <v>3404</v>
       </c>
       <c r="G24" t="n">
-        <v>127.5222222222222</v>
+        <v>128.6703703703704</v>
       </c>
       <c r="H24" t="n">
-        <v>11.21111111111111</v>
+        <v>11.64074074074074</v>
       </c>
       <c r="I24" t="n">
-        <v>11.21111111111111</v>
+        <v>11.64074074074074</v>
       </c>
       <c r="J24" t="n">
-        <v>10.26296296296296</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K24" t="n">
-        <v>0.825925925925926</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L24" t="n">
-        <v>0.825925925925926</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1703703703703704</v>
+        <v>0.1592592592592593</v>
       </c>
       <c r="N24" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.1925925925925926</v>
       </c>
       <c r="P24" t="n">
-        <v>127.137037037037</v>
+        <v>128.1407407407407</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>94/270</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>34.81481481481482</v>
+          <t>66/270</t>
+        </is>
+      </c>
+      <c r="R24" s="15" t="n">
+        <v>24.44444444444444</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>144/270</t>
-        </is>
-      </c>
-      <c r="T24" t="n">
-        <v>53.33333333333334</v>
+          <t>167/270</t>
+        </is>
+      </c>
+      <c r="T24" s="15" t="n">
+        <v>61.85185185185185</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3423,52 +3423,52 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="X24" t="n">
-        <v>85.18518518518519</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="X24" s="15" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="Y24" t="n">
-        <v>34431</v>
+        <v>34741</v>
       </c>
       <c r="Z24" t="n">
-        <v>3027</v>
+        <v>3143</v>
       </c>
       <c r="AA24" t="n">
-        <v>37458</v>
+        <v>37884</v>
       </c>
       <c r="AB24" t="n">
-        <v>2356</v>
+        <v>2342</v>
       </c>
       <c r="AC24" t="n">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="AD24" t="n">
-        <v>2771</v>
+        <v>2802</v>
       </c>
       <c r="AE24" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>48</v>
+        <v>9</v>
+      </c>
+      <c r="AG24" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="AH24" s="17" t="n">
-        <v>139798530000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI24" s="17" t="n">
-        <v>182292371420</v>
-      </c>
-      <c r="AJ24" s="17" t="n">
-        <v>42493841420</v>
+        <v>203491824400</v>
+      </c>
+      <c r="AJ24" s="18" t="n">
+        <v>62122524400</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3481,116 +3481,116 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>130.1112918221721</v>
+        <v>120.5562728400013</v>
       </c>
       <c r="E25" t="n">
-        <v>39708</v>
+        <v>40635</v>
       </c>
       <c r="F25" t="n">
-        <v>3321</v>
+        <v>3414</v>
       </c>
       <c r="G25" t="n">
-        <v>125.3888888888889</v>
+        <v>128.0777777777778</v>
       </c>
       <c r="H25" t="n">
-        <v>11.48888888888889</v>
+        <v>11.85185185185185</v>
       </c>
       <c r="I25" t="n">
-        <v>11.48888888888889</v>
+        <v>11.85185185185185</v>
       </c>
       <c r="J25" t="n">
-        <v>10.01481481481481</v>
+        <v>10.42592592592593</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8037037037037037</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8037037037037037</v>
+        <v>0.7888888888888889</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="N25" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.003703703703703704</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1740740740740741</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="P25" t="n">
-        <v>124.7962962962963</v>
+        <v>128.1037037037037</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>89/270</t>
+          <t>96/270</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>32.96296296296296</v>
+        <v>35.55555555555556</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>156/270</t>
+          <t>154/270</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>57.77777777777777</v>
+        <v>57.03703703703704</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>92.5925925925926</v>
+          <t>22/27</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>81.48148148148148</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="X25" s="16" t="n">
-        <v>88.88888888888889</v>
+          <t>19/27</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>70.37037037037037</v>
       </c>
       <c r="Y25" t="n">
-        <v>33855</v>
+        <v>34581</v>
       </c>
       <c r="Z25" t="n">
-        <v>3102</v>
+        <v>3200</v>
       </c>
       <c r="AA25" t="n">
-        <v>36957</v>
+        <v>37781</v>
       </c>
       <c r="AB25" t="n">
-        <v>2299</v>
+        <v>2446</v>
       </c>
       <c r="AC25" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AD25" t="n">
-        <v>2704</v>
+        <v>2815</v>
       </c>
       <c r="AE25" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="AH25" s="17" t="n">
-        <v>137704170000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI25" s="17" t="n">
-        <v>179168674480</v>
+        <v>170429559020</v>
       </c>
       <c r="AJ25" s="17" t="n">
-        <v>41464504480</v>
+        <v>29060259020</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3603,116 +3603,116 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>130.0389277522836</v>
+        <v>122.0712722776445</v>
       </c>
       <c r="E26" t="n">
-        <v>39838</v>
+        <v>40670</v>
       </c>
       <c r="F26" t="n">
-        <v>3333</v>
+        <v>3413</v>
       </c>
       <c r="G26" t="n">
-        <v>125.8555555555556</v>
+        <v>128.3740740740741</v>
       </c>
       <c r="H26" t="n">
-        <v>11.47037037037037</v>
+        <v>11.79259259259259</v>
       </c>
       <c r="I26" t="n">
-        <v>11.47037037037037</v>
+        <v>11.79259259259259</v>
       </c>
       <c r="J26" t="n">
-        <v>10.05925925925926</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8629629629629629</v>
+        <v>0.837037037037037</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8629629629629629</v>
+        <v>0.837037037037037</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1518518518518518</v>
+        <v>0.1259259259259259</v>
       </c>
       <c r="N26" t="n">
         <v>0.01111111111111111</v>
       </c>
       <c r="O26" t="n">
-        <v>0.162962962962963</v>
+        <v>0.137037037037037</v>
       </c>
       <c r="P26" t="n">
-        <v>125.2777777777778</v>
+        <v>128.1074074074074</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>81/270</t>
+          <t>91/270</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>30</v>
+        <v>33.7037037037037</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>152/270</t>
+          <t>158/270</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>56.2962962962963</v>
+        <v>58.51851851851851</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>24/27</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>85.18518518518519</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>18/27</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>74.07407407407408</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="Y26" t="n">
-        <v>33981</v>
+        <v>34661</v>
       </c>
       <c r="Z26" t="n">
-        <v>3097</v>
+        <v>3184</v>
       </c>
       <c r="AA26" t="n">
-        <v>37078</v>
+        <v>37845</v>
       </c>
       <c r="AB26" t="n">
-        <v>2307</v>
+        <v>2414</v>
       </c>
       <c r="AC26" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AD26" t="n">
-        <v>2716</v>
+        <v>2788</v>
       </c>
       <c r="AE26" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
       </c>
       <c r="AG26" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AH26" s="17" t="n">
-        <v>138227760000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI26" s="17" t="n">
-        <v>179749896960</v>
+        <v>172571303120</v>
       </c>
       <c r="AJ26" s="17" t="n">
-        <v>41522136960</v>
+        <v>31202003120</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3725,116 +3725,116 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>129.5895794031575</v>
+        <v>126.6790426209934</v>
       </c>
       <c r="E27" t="n">
-        <v>40134</v>
+        <v>40732</v>
       </c>
       <c r="F27" t="n">
-        <v>3275</v>
+        <v>3363</v>
       </c>
       <c r="G27" t="n">
-        <v>126.8555555555556</v>
+        <v>128.7666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>11.36666666666667</v>
+        <v>11.60740740740741</v>
       </c>
       <c r="I27" t="n">
-        <v>11.36666666666667</v>
+        <v>11.60740740740741</v>
       </c>
       <c r="J27" t="n">
-        <v>10.23703703703704</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1814814814814815</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="N27" t="n">
         <v>0.003703703703703704</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="P27" t="n">
-        <v>126.537037037037</v>
+        <v>128.2925925925926</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>90/270</t>
+          <t>86/270</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>33.33333333333333</v>
+        <v>31.85185185185185</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>145/270</t>
+          <t>154/270</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>53.70370370370371</v>
+        <v>57.03703703703704</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="V27" s="19" t="n">
-        <v>96.29629629629629</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>85.18518518518519</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="Y27" t="n">
-        <v>34251</v>
+        <v>34767</v>
       </c>
       <c r="Z27" t="n">
-        <v>3069</v>
+        <v>3134</v>
       </c>
       <c r="AA27" t="n">
-        <v>37320</v>
+        <v>37901</v>
       </c>
       <c r="AB27" t="n">
-        <v>2359</v>
+        <v>2378</v>
       </c>
       <c r="AC27" t="n">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="AD27" t="n">
-        <v>2764</v>
+        <v>2786</v>
       </c>
       <c r="AE27" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AF27" t="n">
         <v>1</v>
       </c>
-      <c r="AG27" s="15" t="n">
-        <v>50</v>
+      <c r="AG27" t="n">
+        <v>45</v>
       </c>
       <c r="AH27" s="17" t="n">
-        <v>139274940000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI27" s="17" t="n">
-        <v>180485808960</v>
+        <v>179085275800</v>
       </c>
       <c r="AJ27" s="17" t="n">
-        <v>41210868960</v>
+        <v>37715975800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3847,116 +3847,116 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>128.7486586450676</v>
+        <v>129.4359784054954</v>
       </c>
       <c r="E28" t="n">
-        <v>40033</v>
+        <v>40730</v>
       </c>
       <c r="F28" t="n">
-        <v>3269</v>
+        <v>3412</v>
       </c>
       <c r="G28" t="n">
-        <v>126.637037037037</v>
+        <v>128.6555555555556</v>
       </c>
       <c r="H28" t="n">
-        <v>11.31481481481481</v>
+        <v>11.73333333333333</v>
       </c>
       <c r="I28" t="n">
-        <v>11.31481481481481</v>
+        <v>11.73333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>10.14074074074074</v>
+        <v>10.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="L28" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1740740740740741</v>
+        <v>0.1518518518518518</v>
       </c>
       <c r="N28" t="n">
-        <v>0.003703703703703704</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P28" t="n">
-        <v>126.1111111111111</v>
+        <v>128.1111111111111</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>88/270</t>
+          <t>83/270</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>32.5925925925926</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>151/270</t>
+          <t>156/270</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>55.92592592592592</v>
+        <v>57.77777777777777</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="n">
-        <v>92.5925925925926</v>
+          <t>23/27</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>85.18518518518519</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="X28" s="15" t="n">
-        <v>92.5925925925926</v>
+          <t>20/27</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>74.07407407407408</v>
       </c>
       <c r="Y28" t="n">
-        <v>34192</v>
+        <v>34737</v>
       </c>
       <c r="Z28" t="n">
-        <v>3055</v>
+        <v>3168</v>
       </c>
       <c r="AA28" t="n">
-        <v>37247</v>
+        <v>37905</v>
       </c>
       <c r="AB28" t="n">
-        <v>2333</v>
+        <v>2364</v>
       </c>
       <c r="AC28" t="n">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="AD28" t="n">
-        <v>2738</v>
+        <v>2781</v>
       </c>
       <c r="AE28" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AH28" s="17" t="n">
-        <v>138833500000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI28" s="17" t="n">
-        <v>178746269000</v>
+        <v>182982736620</v>
       </c>
       <c r="AJ28" s="17" t="n">
-        <v>39912769000</v>
+        <v>41613436620</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>17</v>
+      <c r="A29" s="13" t="n">
+        <v>45</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3968,117 +3968,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>128.7079858947466</v>
+      <c r="D29" s="15" t="n">
+        <v>139.0690664238983</v>
       </c>
       <c r="E29" t="n">
-        <v>38741</v>
+        <v>40771</v>
       </c>
       <c r="F29" t="n">
-        <v>3218</v>
+        <v>3393</v>
       </c>
       <c r="G29" t="n">
-        <v>122.4</v>
+        <v>128.7</v>
       </c>
       <c r="H29" t="n">
-        <v>11.0962962962963</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="I29" t="n">
-        <v>11.0962962962963</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="J29" t="n">
-        <v>9.837037037037037</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8074074074074075</v>
+        <v>0.7851851851851852</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8074074074074075</v>
+        <v>0.7851851851851852</v>
       </c>
       <c r="M29" t="n">
-        <v>0.137037037037037</v>
+        <v>0.1814814814814815</v>
       </c>
       <c r="N29" t="n">
-        <v>0.01481481481481482</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.1518518518518518</v>
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="O29" s="15" t="n">
+        <v>0.2037037037037037</v>
       </c>
       <c r="P29" t="n">
-        <v>122.0518518518519</v>
+        <v>128.1703703703704</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>75/270</t>
+          <t>84/270</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>27.77777777777778</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>151/270</t>
+          <t>157/270</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>55.92592592592592</v>
+        <v>58.14814814814815</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>27/27</t>
+        </is>
+      </c>
+      <c r="V29" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>25/27</t>
         </is>
       </c>
-      <c r="V29" s="7" t="n">
+      <c r="X29" s="15" t="n">
         <v>92.5925925925926</v>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="X29" t="n">
-        <v>81.48148148148148</v>
-      </c>
       <c r="Y29" t="n">
-        <v>33048</v>
+        <v>34749</v>
       </c>
       <c r="Z29" t="n">
-        <v>2996</v>
+        <v>3175</v>
       </c>
       <c r="AA29" t="n">
-        <v>36044</v>
+        <v>37924</v>
       </c>
       <c r="AB29" t="n">
-        <v>2274</v>
+        <v>2360</v>
       </c>
       <c r="AC29" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AD29" t="n">
-        <v>2656</v>
+        <v>2792</v>
       </c>
       <c r="AE29" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AF29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="AG29" s="15" t="n">
+        <v>55</v>
       </c>
       <c r="AH29" s="17" t="n">
-        <v>134562630000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI29" s="17" t="n">
-        <v>173192850840</v>
-      </c>
-      <c r="AJ29" s="17" t="n">
-        <v>38630220840</v>
+        <v>196600965720</v>
+      </c>
+      <c r="AJ29" s="18" t="n">
+        <v>55231665720</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4091,59 +4091,59 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>128.5082099138407</v>
+        <v>133.9150640652789</v>
       </c>
       <c r="E30" t="n">
-        <v>39809</v>
+        <v>39831</v>
       </c>
       <c r="F30" t="n">
-        <v>3388</v>
+        <v>3196</v>
       </c>
       <c r="G30" t="n">
-        <v>125.4814814814815</v>
+        <v>126.1259259259259</v>
       </c>
       <c r="H30" t="n">
-        <v>11.7037037037037</v>
+        <v>11.07037037037037</v>
       </c>
       <c r="I30" t="n">
-        <v>11.7037037037037</v>
+        <v>11.07037037037037</v>
       </c>
       <c r="J30" t="n">
-        <v>10.09259259259259</v>
+        <v>10.14074074074074</v>
       </c>
       <c r="K30" t="n">
-        <v>0.837037037037037</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="L30" t="n">
-        <v>0.837037037037037</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N30" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="O30" t="n">
-        <v>0.162962962962963</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="P30" t="n">
-        <v>125.0703703703704</v>
+        <v>125.8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>90/270</t>
+          <t>88/270</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>33.33333333333333</v>
+        <v>32.5925925925926</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>151/270</t>
-        </is>
-      </c>
-      <c r="T30" t="n">
-        <v>55.92592592592592</v>
+          <t>157/270</t>
+        </is>
+      </c>
+      <c r="T30" s="16" t="n">
+        <v>58.14814814814815</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4155,52 +4155,52 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="X30" t="n">
-        <v>81.48148148148148</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="X30" s="16" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="Y30" t="n">
-        <v>33880</v>
+        <v>34054</v>
       </c>
       <c r="Z30" t="n">
-        <v>3160</v>
+        <v>2989</v>
       </c>
       <c r="AA30" t="n">
-        <v>37040</v>
+        <v>37043</v>
       </c>
       <c r="AB30" t="n">
-        <v>2323</v>
+        <v>2336</v>
       </c>
       <c r="AC30" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="AD30" t="n">
-        <v>2725</v>
+        <v>2738</v>
       </c>
       <c r="AE30" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="AG30" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="AH30" s="17" t="n">
         <v>138227760000</v>
       </c>
       <c r="AI30" s="17" t="n">
-        <v>177634019980</v>
+        <v>185107793360</v>
       </c>
       <c r="AJ30" s="17" t="n">
-        <v>39406259980</v>
+        <v>46880033360</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4213,116 +4213,116 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>128.1104020117133</v>
+        <v>132.2546608775739</v>
       </c>
       <c r="E31" t="n">
-        <v>39530</v>
+        <v>40777</v>
       </c>
       <c r="F31" t="n">
-        <v>3326</v>
+        <v>3411</v>
       </c>
       <c r="G31" t="n">
-        <v>124.7592592592593</v>
+        <v>128.7296296296296</v>
       </c>
       <c r="H31" t="n">
-        <v>11.50740740740741</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="I31" t="n">
-        <v>11.50740740740741</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="J31" t="n">
-        <v>9.985185185185186</v>
+        <v>10.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.8185185185185185</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.8185185185185185</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1407407407407407</v>
+        <v>0.1814814814814815</v>
       </c>
       <c r="N31" t="n">
-        <v>0.01481481481481482</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="P31" t="n">
-        <v>124.2592592592593</v>
+        <v>128.1148148148148</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>93/270</t>
+          <t>90/270</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>34.44444444444444</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>148/270</t>
+          <t>162/270</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>54.81481481481482</v>
+        <v>60</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="n">
+        <v>92.5925925925926</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>24/27</t>
         </is>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" s="16" t="n">
         <v>88.88888888888889</v>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>21/27</t>
-        </is>
-      </c>
-      <c r="X31" t="n">
-        <v>77.77777777777779</v>
-      </c>
       <c r="Y31" t="n">
-        <v>33685</v>
+        <v>34757</v>
       </c>
       <c r="Z31" t="n">
-        <v>3107</v>
+        <v>3188</v>
       </c>
       <c r="AA31" t="n">
-        <v>36792</v>
+        <v>37945</v>
       </c>
       <c r="AB31" t="n">
-        <v>2313</v>
+        <v>2356</v>
       </c>
       <c r="AC31" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AD31" t="n">
-        <v>2696</v>
+        <v>2781</v>
       </c>
       <c r="AE31" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="AF31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AH31" s="17" t="n">
-        <v>137180580000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI31" s="17" t="n">
-        <v>175742592520</v>
+        <v>186967488300</v>
       </c>
       <c r="AJ31" s="17" t="n">
-        <v>38562012520</v>
+        <v>45598188300</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4335,59 +4335,59 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>127.9967155062633</v>
+        <v>120.1030829930568</v>
       </c>
       <c r="E32" t="n">
-        <v>40473</v>
+        <v>39642</v>
       </c>
       <c r="F32" t="n">
-        <v>3406</v>
+        <v>3252</v>
       </c>
       <c r="G32" t="n">
-        <v>127.7111111111111</v>
+        <v>125.3185185185185</v>
       </c>
       <c r="H32" t="n">
-        <v>11.77407407407407</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="I32" t="n">
-        <v>11.77407407407407</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="J32" t="n">
-        <v>10.24444444444444</v>
+        <v>10.05555555555556</v>
       </c>
       <c r="K32" t="n">
-        <v>0.837037037037037</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="L32" t="n">
-        <v>0.837037037037037</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1259259259259259</v>
       </c>
       <c r="N32" t="n">
-        <v>0.003703703703703704</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1703703703703704</v>
+        <v>0.137037037037037</v>
       </c>
       <c r="P32" t="n">
-        <v>127.1666666666667</v>
+        <v>125.0518518518519</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>81/270</t>
+          <t>100/270</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>30</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>169/270</t>
-        </is>
-      </c>
-      <c r="T32" s="15" t="n">
-        <v>62.59259259259259</v>
+          <t>139/270</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>51.48148148148148</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4399,52 +4399,52 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>19/27</t>
         </is>
       </c>
       <c r="X32" t="n">
-        <v>74.07407407407408</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="Y32" t="n">
-        <v>34482</v>
+        <v>33836</v>
       </c>
       <c r="Z32" t="n">
-        <v>3179</v>
+        <v>3054</v>
       </c>
       <c r="AA32" t="n">
-        <v>37661</v>
+        <v>36890</v>
       </c>
       <c r="AB32" t="n">
-        <v>2356</v>
+        <v>2372</v>
       </c>
       <c r="AC32" t="n">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="AD32" t="n">
-        <v>2766</v>
+        <v>2715</v>
       </c>
       <c r="AE32" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG32" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AH32" s="17" t="n">
-        <v>140405200000</v>
+        <v>137704170000</v>
       </c>
       <c r="AI32" s="17" t="n">
-        <v>179714044400</v>
+        <v>165386953580</v>
       </c>
       <c r="AJ32" s="17" t="n">
-        <v>39308844400</v>
+        <v>27682783580</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>25</v>
+      <c r="A33" s="13" t="n">
+        <v>46</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4456,117 +4456,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>127.3563402025758</v>
+      <c r="D33" s="15" t="n">
+        <v>139.0996864524334</v>
       </c>
       <c r="E33" t="n">
-        <v>39835</v>
+        <v>40771</v>
       </c>
       <c r="F33" t="n">
-        <v>3285</v>
+        <v>3410</v>
       </c>
       <c r="G33" t="n">
-        <v>125.937037037037</v>
+        <v>128.7074074074074</v>
       </c>
       <c r="H33" t="n">
-        <v>11.34444444444444</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="I33" t="n">
-        <v>11.34444444444444</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="J33" t="n">
-        <v>10.08888888888889</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8185185185185185</v>
+        <v>0.8629629629629629</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8185185185185185</v>
+        <v>0.8629629629629629</v>
       </c>
       <c r="M33" t="n">
-        <v>0.162962962962963</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003703703703703704</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.01481481481481482</v>
+      </c>
+      <c r="O33" s="15" t="n">
+        <v>0.2037037037037037</v>
       </c>
       <c r="P33" t="n">
-        <v>125.462962962963</v>
+        <v>128.1074074074074</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>85/270</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>31.48148148148148</v>
+          <t>81/270</t>
+        </is>
+      </c>
+      <c r="R33" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>149/270</t>
-        </is>
-      </c>
-      <c r="T33" t="n">
-        <v>55.18518518518518</v>
+          <t>169/270</t>
+        </is>
+      </c>
+      <c r="T33" s="15" t="n">
+        <v>62.59259259259259</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>88.88888888888889</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="V33" s="19" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="X33" t="n">
-        <v>81.48148148148148</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="X33" s="15" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="Y33" t="n">
-        <v>34003</v>
+        <v>34751</v>
       </c>
       <c r="Z33" t="n">
-        <v>3063</v>
+        <v>3173</v>
       </c>
       <c r="AA33" t="n">
-        <v>37066</v>
+        <v>37924</v>
       </c>
       <c r="AB33" t="n">
-        <v>2323</v>
+        <v>2339</v>
       </c>
       <c r="AC33" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AD33" t="n">
-        <v>2724</v>
+        <v>2792</v>
       </c>
       <c r="AE33" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>45</v>
+        <v>4</v>
+      </c>
+      <c r="AG33" s="15" t="n">
+        <v>55</v>
       </c>
       <c r="AH33" s="17" t="n">
-        <v>138227760000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI33" s="17" t="n">
-        <v>176041816280</v>
-      </c>
-      <c r="AJ33" s="17" t="n">
-        <v>37814056280</v>
+        <v>196644253040</v>
+      </c>
+      <c r="AJ33" s="18" t="n">
+        <v>55274953040</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4579,67 +4579,67 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>127.2320721347936</v>
+        <v>128.1104020117133</v>
       </c>
       <c r="E34" t="n">
-        <v>39986</v>
+        <v>39530</v>
       </c>
       <c r="F34" t="n">
-        <v>3291</v>
+        <v>3326</v>
       </c>
       <c r="G34" t="n">
-        <v>126.2962962962963</v>
+        <v>124.7592592592593</v>
       </c>
       <c r="H34" t="n">
-        <v>11.46296296296296</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I34" t="n">
-        <v>11.46296296296296</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J34" t="n">
-        <v>10.16296296296296</v>
+        <v>9.985185185185186</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="N34" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.01481481481481482</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1740740740740741</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="P34" t="n">
-        <v>125.9518518518519</v>
+        <v>124.2592592592593</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>93/270</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>33.7037037037037</v>
+        <v>34.44444444444444</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>136/270</t>
+          <t>148/270</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>50.37037037037037</v>
+        <v>54.81481481481482</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="V34" s="19" t="n">
-        <v>96.29629629629629</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4650,45 +4650,45 @@
         <v>77.77777777777779</v>
       </c>
       <c r="Y34" t="n">
-        <v>34100</v>
+        <v>33685</v>
       </c>
       <c r="Z34" t="n">
-        <v>3095</v>
+        <v>3107</v>
       </c>
       <c r="AA34" t="n">
-        <v>37195</v>
+        <v>36792</v>
       </c>
       <c r="AB34" t="n">
-        <v>2362</v>
+        <v>2313</v>
       </c>
       <c r="AC34" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="AD34" t="n">
-        <v>2744</v>
+        <v>2696</v>
       </c>
       <c r="AE34" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG34" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AH34" s="17" t="n">
-        <v>138751350000</v>
+        <v>137180580000</v>
       </c>
       <c r="AI34" s="17" t="n">
-        <v>176536217720</v>
+        <v>175742592520</v>
       </c>
       <c r="AJ34" s="17" t="n">
-        <v>37784867720</v>
+        <v>38562012520</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>29</v>
+      <c r="A35" s="13" t="n">
+        <v>41</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4700,117 +4700,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>126.5557330358163</v>
+      <c r="D35" s="16" t="n">
+        <v>137.232633421825</v>
       </c>
       <c r="E35" t="n">
-        <v>40535</v>
+        <v>40738</v>
       </c>
       <c r="F35" t="n">
-        <v>3327</v>
+        <v>3383</v>
       </c>
       <c r="G35" t="n">
-        <v>128.1518518518519</v>
+        <v>128.6481481481482</v>
       </c>
       <c r="H35" t="n">
-        <v>11.47407407407407</v>
+        <v>11.66296296296296</v>
       </c>
       <c r="I35" t="n">
-        <v>11.47407407407407</v>
+        <v>11.66296296296296</v>
       </c>
       <c r="J35" t="n">
-        <v>10.35185185185185</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M35" t="n">
-        <v>0.137037037037037</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N35" t="n">
-        <v>0.01481481481481482</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1518518518518518</v>
+        <v>0.1925925925925926</v>
       </c>
       <c r="P35" t="n">
-        <v>127.9037037037037</v>
+        <v>128.2259259259259</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>87/270</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>32.22222222222222</v>
+          <t>81/270</t>
+        </is>
+      </c>
+      <c r="R35" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>144/270</t>
-        </is>
-      </c>
-      <c r="T35" t="n">
-        <v>53.33333333333334</v>
+          <t>173/270</t>
+        </is>
+      </c>
+      <c r="T35" s="15" t="n">
+        <v>64.07407407407408</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="n">
+        <v>92.5925925925926</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>24/27</t>
         </is>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>88.88888888888889</v>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="X35" t="n">
-        <v>70.37037037037037</v>
-      </c>
       <c r="Y35" t="n">
-        <v>34601</v>
+        <v>34735</v>
       </c>
       <c r="Z35" t="n">
-        <v>3098</v>
+        <v>3149</v>
       </c>
       <c r="AA35" t="n">
-        <v>37699</v>
+        <v>37884</v>
       </c>
       <c r="AB35" t="n">
-        <v>2406</v>
+        <v>2365</v>
       </c>
       <c r="AC35" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AD35" t="n">
-        <v>2795</v>
+        <v>2802</v>
       </c>
       <c r="AE35" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="AF35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="AG35" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="AH35" s="17" t="n">
-        <v>140845710000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI35" s="17" t="n">
-        <v>178248320740</v>
-      </c>
-      <c r="AJ35" s="17" t="n">
-        <v>37402610740</v>
+        <v>194004813240</v>
+      </c>
+      <c r="AJ35" s="18" t="n">
+        <v>52635513240</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4823,67 +4823,67 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>126.463345398235</v>
+        <v>134.4332309490109</v>
       </c>
       <c r="E36" t="n">
-        <v>40147</v>
+        <v>40738</v>
       </c>
       <c r="F36" t="n">
-        <v>3366</v>
+        <v>3283</v>
       </c>
       <c r="G36" t="n">
-        <v>126.7703703703704</v>
+        <v>128.9296296296296</v>
       </c>
       <c r="H36" t="n">
-        <v>11.60740740740741</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="I36" t="n">
-        <v>11.60740740740741</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="J36" t="n">
-        <v>10.15925925925926</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N36" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.1925925925925926</v>
       </c>
       <c r="P36" t="n">
-        <v>126.2703703703704</v>
+        <v>128.6111111111111</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>87/270</t>
+          <t>91/270</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>32.22222222222222</v>
+        <v>33.7037037037037</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>149/270</t>
+          <t>159/270</t>
         </is>
       </c>
       <c r="T36" t="n">
-        <v>55.18518518518518</v>
+        <v>58.88888888888889</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="V36" s="19" t="n">
-        <v>96.29629629629629</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4894,45 +4894,45 @@
         <v>88.88888888888889</v>
       </c>
       <c r="Y36" t="n">
-        <v>34228</v>
+        <v>34811</v>
       </c>
       <c r="Z36" t="n">
-        <v>3134</v>
+        <v>3073</v>
       </c>
       <c r="AA36" t="n">
-        <v>37362</v>
+        <v>37884</v>
       </c>
       <c r="AB36" t="n">
-        <v>2345</v>
+        <v>2389</v>
       </c>
       <c r="AC36" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="AD36" t="n">
-        <v>2743</v>
+        <v>2802</v>
       </c>
       <c r="AE36" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="AG36" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="AH36" s="17" t="n">
-        <v>139357400000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI36" s="17" t="n">
-        <v>176236030100</v>
+        <v>190047317560</v>
       </c>
       <c r="AJ36" s="17" t="n">
-        <v>36878630100</v>
+        <v>48678017560</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4945,116 +4945,116 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>126.3735355064933</v>
+        <v>135.7498372843326</v>
       </c>
       <c r="E37" t="n">
-        <v>40759</v>
+        <v>40780</v>
       </c>
       <c r="F37" t="n">
-        <v>3357</v>
+        <v>3318</v>
       </c>
       <c r="G37" t="n">
-        <v>128.862962962963</v>
+        <v>128.9851851851852</v>
       </c>
       <c r="H37" t="n">
-        <v>11.63703703703704</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="I37" t="n">
-        <v>11.63703703703704</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="J37" t="n">
-        <v>10.3</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7814814814814814</v>
+        <v>0.737037037037037</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7814814814814814</v>
+        <v>0.737037037037037</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N37" t="n">
-        <v>0.01481481481481482</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1592592592592593</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P37" t="n">
-        <v>128.3925925925926</v>
+        <v>128.4444444444445</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>94/270</t>
+          <t>102/270</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>34.81481481481482</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>149/270</t>
+          <t>140/270</t>
         </is>
       </c>
       <c r="T37" t="n">
-        <v>55.18518518518518</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="V37" s="19" t="n">
-        <v>96.29629629629629</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>24/27</t>
-        </is>
-      </c>
-      <c r="X37" s="16" t="n">
-        <v>88.88888888888889</v>
+          <t>22/27</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>81.48148148148148</v>
       </c>
       <c r="Y37" t="n">
-        <v>34793</v>
+        <v>34826</v>
       </c>
       <c r="Z37" t="n">
-        <v>3142</v>
+        <v>3113</v>
       </c>
       <c r="AA37" t="n">
-        <v>37935</v>
+        <v>37939</v>
       </c>
       <c r="AB37" t="n">
-        <v>2398</v>
+        <v>2377</v>
       </c>
       <c r="AC37" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="AD37" t="n">
-        <v>2781</v>
+        <v>2788</v>
       </c>
       <c r="AE37" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="AF37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>43</v>
+        <v>6</v>
+      </c>
+      <c r="AG37" s="15" t="n">
+        <v>53</v>
       </c>
       <c r="AH37" s="17" t="n">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI37" s="17" t="n">
-        <v>178759157180</v>
+        <v>191908594720</v>
       </c>
       <c r="AJ37" s="17" t="n">
-        <v>37306157180</v>
+        <v>50539294720</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5067,116 +5067,116 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>125.8321025432106</v>
+        <v>135.0868122286805</v>
       </c>
       <c r="E38" t="n">
-        <v>40418</v>
+        <v>40780</v>
       </c>
       <c r="F38" t="n">
-        <v>3367</v>
+        <v>3454</v>
       </c>
       <c r="G38" t="n">
-        <v>127.6518518518518</v>
+        <v>128.5814814814815</v>
       </c>
       <c r="H38" t="n">
-        <v>11.65925925925926</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>11.65925925925926</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="J38" t="n">
-        <v>10.23703703703704</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7925925925925926</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7925925925925926</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1296296296296296</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="N38" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P38" t="n">
-        <v>127.3111111111111</v>
+        <v>127.9962962962963</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>99/270</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>36.66666666666666</v>
+          <t>70/270</t>
+        </is>
+      </c>
+      <c r="R38" s="15" t="n">
+        <v>25.92592592592592</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>148/270</t>
-        </is>
-      </c>
-      <c r="T38" t="n">
-        <v>54.81481481481482</v>
+          <t>173/270</t>
+        </is>
+      </c>
+      <c r="T38" s="15" t="n">
+        <v>64.07407407407408</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>24/27</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>85.18518518518519</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="X38" t="n">
-        <v>74.07407407407408</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="Y38" t="n">
-        <v>34466</v>
+        <v>34717</v>
       </c>
       <c r="Z38" t="n">
-        <v>3148</v>
+        <v>3222</v>
       </c>
       <c r="AA38" t="n">
-        <v>37614</v>
+        <v>37939</v>
       </c>
       <c r="AB38" t="n">
-        <v>2390</v>
+        <v>2346</v>
       </c>
       <c r="AC38" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="AD38" t="n">
-        <v>2764</v>
+        <v>2788</v>
       </c>
       <c r="AE38" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="AF38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="AG38" s="15" t="n">
+        <v>53</v>
       </c>
       <c r="AH38" s="17" t="n">
-        <v>140405200000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI38" s="17" t="n">
-        <v>176674815240</v>
+        <v>190971280840</v>
       </c>
       <c r="AJ38" s="17" t="n">
-        <v>36269615240</v>
+        <v>49601980840</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>39</v>
+      <c r="A39" s="13" t="n">
+        <v>43</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5188,117 +5188,117 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>123.9919643859344</v>
+      <c r="D39" s="16" t="n">
+        <v>136.8162394522714</v>
       </c>
       <c r="E39" t="n">
-        <v>40437</v>
+        <v>40738</v>
       </c>
       <c r="F39" t="n">
-        <v>3431</v>
+        <v>3461</v>
       </c>
       <c r="G39" t="n">
-        <v>127.4777777777778</v>
+        <v>128.3333333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>11.8962962962963</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="I39" t="n">
-        <v>11.8962962962963</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="J39" t="n">
-        <v>10.24074074074074</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8037037037037037</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8037037037037037</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1444444444444444</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N39" t="n">
-        <v>0.007407407407407408</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1518518518518518</v>
+        <v>0.1925925925925926</v>
       </c>
       <c r="P39" t="n">
-        <v>127.0740740740741</v>
+        <v>127.8925925925926</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>88/270</t>
+          <t>84/270</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>32.5925925925926</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>152/270</t>
-        </is>
-      </c>
-      <c r="T39" t="n">
-        <v>56.2962962962963</v>
+          <t>169/270</t>
+        </is>
+      </c>
+      <c r="T39" s="16" t="n">
+        <v>62.59259259259259</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>22/27</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>81.48148148148148</v>
+          <t>26/27</t>
+        </is>
+      </c>
+      <c r="V39" s="19" t="n">
+        <v>96.29629629629629</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>23/27</t>
         </is>
       </c>
       <c r="X39" t="n">
-        <v>70.37037037037037</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y39" t="n">
-        <v>34419</v>
+        <v>34650</v>
       </c>
       <c r="Z39" t="n">
-        <v>3212</v>
+        <v>3234</v>
       </c>
       <c r="AA39" t="n">
-        <v>37631</v>
+        <v>37884</v>
       </c>
       <c r="AB39" t="n">
-        <v>2384</v>
+        <v>2372</v>
       </c>
       <c r="AC39" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AD39" t="n">
-        <v>2765</v>
+        <v>2802</v>
       </c>
       <c r="AE39" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="AG39" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="AH39" s="17" t="n">
-        <v>140405200000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI39" s="17" t="n">
-        <v>174091165580</v>
+        <v>193416160000</v>
       </c>
       <c r="AJ39" s="17" t="n">
-        <v>33685965580</v>
+        <v>52046860000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5311,116 +5311,116 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>122.0946455617888</v>
+        <v>132.0806445787366</v>
       </c>
       <c r="E40" t="n">
-        <v>39768</v>
+        <v>39075</v>
       </c>
       <c r="F40" t="n">
-        <v>3342</v>
+        <v>3261</v>
       </c>
       <c r="G40" t="n">
-        <v>125.5222222222222</v>
+        <v>123.3444444444444</v>
       </c>
       <c r="H40" t="n">
-        <v>11.54444444444444</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="I40" t="n">
-        <v>11.54444444444444</v>
+        <v>11.31111111111111</v>
       </c>
       <c r="J40" t="n">
-        <v>10.08888888888889</v>
+        <v>9.896296296296295</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.7481481481481481</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.1518518518518518</v>
       </c>
       <c r="N40" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="P40" t="n">
-        <v>125.237037037037</v>
+        <v>122.937037037037</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>89/270</t>
+          <t>90/270</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>32.96296296296296</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>155/270</t>
+          <t>147/270</t>
         </is>
       </c>
       <c r="T40" t="n">
-        <v>57.4074074074074</v>
+        <v>54.44444444444444</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
           <t>23/27</t>
         </is>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>85.18518518518519</v>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>18/27</t>
-        </is>
-      </c>
-      <c r="X40" t="n">
-        <v>66.66666666666666</v>
-      </c>
       <c r="Y40" t="n">
-        <v>33891</v>
+        <v>33303</v>
       </c>
       <c r="Z40" t="n">
-        <v>3117</v>
+        <v>3054</v>
       </c>
       <c r="AA40" t="n">
-        <v>37008</v>
+        <v>36357</v>
       </c>
       <c r="AB40" t="n">
-        <v>2358</v>
+        <v>2286</v>
       </c>
       <c r="AC40" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="AD40" t="n">
-        <v>2724</v>
+        <v>2672</v>
       </c>
       <c r="AE40" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AF40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG40" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH40" s="17" t="n">
-        <v>138227760000</v>
+        <v>135609810000</v>
       </c>
       <c r="AI40" s="17" t="n">
-        <v>168768693640</v>
+        <v>179114311160</v>
       </c>
       <c r="AJ40" s="17" t="n">
-        <v>30540933640</v>
+        <v>43504501160</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5433,116 +5433,116 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>120.9035007446422</v>
+        <v>132.7447509745998</v>
       </c>
       <c r="E41" t="n">
-        <v>40087</v>
+        <v>38924</v>
       </c>
       <c r="F41" t="n">
-        <v>3358</v>
+        <v>3150</v>
       </c>
       <c r="G41" t="n">
-        <v>126.4888888888889</v>
+        <v>123.2518518518519</v>
       </c>
       <c r="H41" t="n">
-        <v>11.7</v>
+        <v>10.84074074074074</v>
       </c>
       <c r="I41" t="n">
-        <v>11.7</v>
+        <v>10.84074074074074</v>
       </c>
       <c r="J41" t="n">
-        <v>10.14814814814815</v>
+        <v>9.9</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1148148148148148</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01851851851851852</v>
+        <v>0.01481481481481482</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="P41" t="n">
-        <v>126.2259259259259</v>
+        <v>122.8259259259259</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>111/270</t>
+          <t>84/270</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>41.11111111111111</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>138/270</t>
+          <t>149/270</t>
         </is>
       </c>
       <c r="T41" t="n">
-        <v>51.11111111111111</v>
+        <v>55.18518518518518</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>24/27</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>74.07407407407408</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>16/27</t>
-        </is>
-      </c>
-      <c r="X41" t="n">
-        <v>59.25925925925925</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="X41" s="16" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="Y41" t="n">
-        <v>34152</v>
+        <v>33278</v>
       </c>
       <c r="Z41" t="n">
-        <v>3159</v>
+        <v>2927</v>
       </c>
       <c r="AA41" t="n">
-        <v>37311</v>
+        <v>36205</v>
       </c>
       <c r="AB41" t="n">
-        <v>2402</v>
+        <v>2270</v>
       </c>
       <c r="AC41" t="n">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="AD41" t="n">
-        <v>2740</v>
+        <v>2673</v>
       </c>
       <c r="AE41" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AF41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG41" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AH41" s="17" t="n">
-        <v>139274940000</v>
+        <v>135086220000</v>
       </c>
       <c r="AI41" s="17" t="n">
-        <v>168388278120</v>
+        <v>179319866340</v>
       </c>
       <c r="AJ41" s="17" t="n">
-        <v>29113338120</v>
+        <v>44233646340</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5555,116 +5555,116 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>120.1030829930568</v>
+        <v>131.3061087059805</v>
       </c>
       <c r="E42" t="n">
-        <v>39642</v>
+        <v>38933</v>
       </c>
       <c r="F42" t="n">
-        <v>3252</v>
+        <v>3060</v>
       </c>
       <c r="G42" t="n">
-        <v>125.3185185185185</v>
+        <v>123.537037037037</v>
       </c>
       <c r="H42" t="n">
-        <v>11.31111111111111</v>
+        <v>10.56296296296296</v>
       </c>
       <c r="I42" t="n">
-        <v>11.31111111111111</v>
+        <v>10.56296296296296</v>
       </c>
       <c r="J42" t="n">
-        <v>10.05555555555556</v>
+        <v>9.911111111111111</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.1814814814814815</v>
       </c>
       <c r="N42" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.003703703703703704</v>
       </c>
       <c r="O42" t="n">
-        <v>0.137037037037037</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="P42" t="n">
-        <v>125.0518518518519</v>
+        <v>123.1740740740741</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>100/270</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
-        <v>37.03703703703704</v>
+          <t>79/270</t>
+        </is>
+      </c>
+      <c r="R42" s="15" t="n">
+        <v>29.25925925925926</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>139/270</t>
+          <t>148/270</t>
         </is>
       </c>
       <c r="T42" t="n">
-        <v>51.48148148148148</v>
+        <v>54.81481481481482</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
           <t>23/27</t>
         </is>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>85.18518518518519</v>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>19/27</t>
-        </is>
-      </c>
-      <c r="X42" t="n">
-        <v>70.37037037037037</v>
-      </c>
       <c r="Y42" t="n">
-        <v>33836</v>
+        <v>33355</v>
       </c>
       <c r="Z42" t="n">
-        <v>3054</v>
+        <v>2852</v>
       </c>
       <c r="AA42" t="n">
-        <v>36890</v>
+        <v>36207</v>
       </c>
       <c r="AB42" t="n">
-        <v>2372</v>
+        <v>2269</v>
       </c>
       <c r="AC42" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="AD42" t="n">
-        <v>2715</v>
+        <v>2676</v>
       </c>
       <c r="AE42" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="AF42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="AG42" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="AH42" s="17" t="n">
-        <v>137704170000</v>
+        <v>135086220000</v>
       </c>
       <c r="AI42" s="17" t="n">
-        <v>165386953580</v>
+        <v>177376458880</v>
       </c>
       <c r="AJ42" s="17" t="n">
-        <v>27682783580</v>
+        <v>42290238880</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5677,116 +5677,116 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>120.0642029213235</v>
+        <v>131.7624941200105</v>
       </c>
       <c r="E43" t="n">
-        <v>39735</v>
+        <v>40738</v>
       </c>
       <c r="F43" t="n">
-        <v>3325</v>
+        <v>3379</v>
       </c>
       <c r="G43" t="n">
-        <v>125.2851851851852</v>
+        <v>128.5703703703704</v>
       </c>
       <c r="H43" t="n">
-        <v>11.55185185185185</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="I43" t="n">
-        <v>11.55185185185185</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="J43" t="n">
-        <v>10.18888888888889</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="M43" t="n">
-        <v>0.137037037037037</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N43" t="n">
-        <v>0.003703703703703704</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1407407407407407</v>
+        <v>0.1925925925925926</v>
       </c>
       <c r="P43" t="n">
-        <v>125.3111111111111</v>
+        <v>128.2222222222222</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>95/270</t>
-        </is>
-      </c>
-      <c r="R43" t="n">
-        <v>35.18518518518518</v>
+          <t>84/270</t>
+        </is>
+      </c>
+      <c r="R43" s="15" t="n">
+        <v>31.11111111111111</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>149/270</t>
+          <t>161/270</t>
         </is>
       </c>
       <c r="T43" t="n">
-        <v>55.18518518518518</v>
+        <v>59.62962962962963</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>20/27</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>74.07407407407408</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V43" s="7" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>23/27</t>
         </is>
       </c>
       <c r="X43" t="n">
-        <v>70.37037037037037</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y43" t="n">
-        <v>33827</v>
+        <v>34714</v>
       </c>
       <c r="Z43" t="n">
-        <v>3119</v>
+        <v>3170</v>
       </c>
       <c r="AA43" t="n">
-        <v>36946</v>
+        <v>37884</v>
       </c>
       <c r="AB43" t="n">
-        <v>2394</v>
+        <v>2387</v>
       </c>
       <c r="AC43" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AD43" t="n">
-        <v>2751</v>
+        <v>2802</v>
       </c>
       <c r="AE43" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AF43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>38</v>
+        <v>2</v>
+      </c>
+      <c r="AG43" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="AH43" s="17" t="n">
-        <v>138227760000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI43" s="17" t="n">
-        <v>165962058260</v>
+        <v>186271715600</v>
       </c>
       <c r="AJ43" s="17" t="n">
-        <v>27734298260</v>
+        <v>44902415600</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5799,116 +5799,116 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>119.7483337771863</v>
+        <v>131.2077959358927</v>
       </c>
       <c r="E44" t="n">
-        <v>40221</v>
+        <v>40728</v>
       </c>
       <c r="F44" t="n">
-        <v>3383</v>
+        <v>3325</v>
       </c>
       <c r="G44" t="n">
-        <v>126.8888888888889</v>
+        <v>128.8148148148148</v>
       </c>
       <c r="H44" t="n">
-        <v>11.71481481481482</v>
+        <v>11.5037037037037</v>
       </c>
       <c r="I44" t="n">
-        <v>11.71481481481482</v>
+        <v>11.5037037037037</v>
       </c>
       <c r="J44" t="n">
-        <v>10.22222222222222</v>
+        <v>10.35185185185185</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7925925925925926</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7925925925925926</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1407407407407407</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1407407407407407</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="P44" t="n">
-        <v>126.6555555555556</v>
+        <v>128.4333333333333</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>84/270</t>
+          <t>88/270</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>31.11111111111111</v>
+        <v>32.5925925925926</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>157/270</t>
+          <t>151/270</t>
         </is>
       </c>
       <c r="T44" s="16" t="n">
-        <v>58.14814814814815</v>
+        <v>55.92592592592592</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>25/27</t>
-        </is>
-      </c>
-      <c r="V44" s="7" t="n">
-        <v>92.5925925925926</v>
+          <t>24/27</t>
+        </is>
+      </c>
+      <c r="V44" s="15" t="n">
+        <v>88.88888888888889</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>23/27</t>
         </is>
       </c>
       <c r="X44" t="n">
-        <v>81.48148148148148</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y44" t="n">
-        <v>34260</v>
+        <v>34780</v>
       </c>
       <c r="Z44" t="n">
-        <v>3163</v>
+        <v>3106</v>
       </c>
       <c r="AA44" t="n">
-        <v>37423</v>
+        <v>37886</v>
       </c>
       <c r="AB44" t="n">
-        <v>2388</v>
+        <v>2393</v>
       </c>
       <c r="AC44" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AD44" t="n">
-        <v>2760</v>
+        <v>2795</v>
       </c>
       <c r="AE44" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>38</v>
+        <v>5</v>
+      </c>
+      <c r="AG44" s="15" t="n">
+        <v>47</v>
       </c>
       <c r="AH44" s="17" t="n">
-        <v>139798530000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI44" s="17" t="n">
-        <v>167406410320</v>
+        <v>185487542660</v>
       </c>
       <c r="AJ44" s="17" t="n">
-        <v>27607880320</v>
+        <v>44118242660</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5921,111 +5921,111 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>112.9008574114774</v>
+        <v>128.7079858947466</v>
       </c>
       <c r="E45" t="n">
-        <v>39889</v>
+        <v>38741</v>
       </c>
       <c r="F45" t="n">
-        <v>3275</v>
+        <v>3218</v>
       </c>
       <c r="G45" t="n">
-        <v>126.0444444444445</v>
+        <v>122.4</v>
       </c>
       <c r="H45" t="n">
-        <v>11.41111111111111</v>
+        <v>11.0962962962963</v>
       </c>
       <c r="I45" t="n">
-        <v>11.41111111111111</v>
+        <v>11.0962962962963</v>
       </c>
       <c r="J45" t="n">
-        <v>10.15925925925926</v>
+        <v>9.837037037037037</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.8074074074074075</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7185185185185186</v>
+        <v>0.8074074074074075</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.137037037037037</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.01481481481481482</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.1518518518518518</v>
       </c>
       <c r="P45" t="n">
-        <v>126.0111111111111</v>
+        <v>122.0518518518519</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>99/270</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>36.66666666666666</v>
+          <t>75/270</t>
+        </is>
+      </c>
+      <c r="R45" s="15" t="n">
+        <v>27.77777777777778</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>143/270</t>
+          <t>151/270</t>
         </is>
       </c>
       <c r="T45" t="n">
-        <v>52.96296296296297</v>
+        <v>55.92592592592592</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>23/27</t>
-        </is>
-      </c>
-      <c r="V45" t="n">
-        <v>85.18518518518519</v>
+          <t>25/27</t>
+        </is>
+      </c>
+      <c r="V45" s="7" t="n">
+        <v>92.5925925925926</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="X45" t="n">
-        <v>74.07407407407408</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="Y45" t="n">
-        <v>34032</v>
+        <v>33048</v>
       </c>
       <c r="Z45" t="n">
-        <v>3081</v>
+        <v>2996</v>
       </c>
       <c r="AA45" t="n">
-        <v>37113</v>
+        <v>36044</v>
       </c>
       <c r="AB45" t="n">
-        <v>2417</v>
+        <v>2274</v>
       </c>
       <c r="AC45" t="n">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="AD45" t="n">
-        <v>2743</v>
+        <v>2656</v>
       </c>
       <c r="AE45" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG45" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AH45" s="17" t="n">
-        <v>138751350000</v>
+        <v>134562630000</v>
       </c>
       <c r="AI45" s="17" t="n">
-        <v>156651463820</v>
+        <v>173192850840</v>
       </c>
       <c r="AJ45" s="17" t="n">
-        <v>17900113820</v>
+        <v>38630220840</v>
       </c>
     </row>
     <row r="46">
@@ -6071,7 +6071,7 @@
   </sheetData>
   <autoFilter ref="A2:AM2">
     <sortState ref="A3:AM53">
-      <sortCondition descending="1" ref="D2"/>
+      <sortCondition descending="1" ref="AH2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D15ACE6-F8D7-4A0F-B320-84069F5A49C1}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2280C5B8-FC77-43CE-8509-94BC28D90651}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="2170" windowWidth="25410" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7380" yWindow="2820" windowWidth="25410" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -460,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -507,6 +507,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -826,33 +827,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Y1" s="22" t="s">
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Y1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="25" t="s">
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="24" t="s">
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -966,7 +967,7 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" s="13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -974,109 +975,109 @@
       <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="15">
-        <v>143.94343354603859</v>
-      </c>
-      <c r="E3" s="20">
-        <v>40738</v>
+      <c r="D3" s="16">
+        <v>137.9997796126882</v>
+      </c>
+      <c r="E3" s="16">
+        <v>40780</v>
       </c>
       <c r="F3" s="20">
-        <v>3404</v>
+        <v>3352</v>
       </c>
       <c r="G3">
-        <v>128.67037037037039</v>
+        <v>128.93703703703699</v>
       </c>
       <c r="H3">
-        <v>11.640740740740741</v>
+        <v>11.577777777777779</v>
       </c>
       <c r="I3">
-        <v>11.640740740740741</v>
+        <v>11.577777777777779</v>
       </c>
       <c r="J3">
-        <v>10.37777777777778</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K3">
-        <v>0.93333333333333335</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="L3">
-        <v>0.93333333333333335</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="M3">
-        <v>0.15925925925925929</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N3">
-        <v>3.3333333333333333E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O3" s="16">
-        <v>0.19259259259259259</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P3">
-        <v>128.14074074074071</v>
+        <v>128.33333333333329</v>
       </c>
       <c r="Q3" t="s">
-        <v>75</v>
-      </c>
-      <c r="R3" s="15">
-        <v>24.444444444444439</v>
+        <v>55</v>
+      </c>
+      <c r="R3" s="22">
+        <v>31.481481481481481</v>
       </c>
       <c r="S3" t="s">
-        <v>76</v>
-      </c>
-      <c r="T3" s="15">
-        <v>61.851851851851848</v>
+        <v>56</v>
+      </c>
+      <c r="T3" s="22">
+        <v>57.037037037037038</v>
       </c>
       <c r="U3" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" s="7">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="V3" s="22">
+        <v>88.888888888888886</v>
       </c>
       <c r="W3" t="s">
-        <v>61</v>
-      </c>
-      <c r="X3" s="15">
-        <v>92.592592592592595</v>
+        <v>57</v>
+      </c>
+      <c r="X3" s="22">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y3">
-        <v>34741</v>
+        <v>34813</v>
       </c>
       <c r="Z3">
-        <v>3143</v>
+        <v>3126</v>
       </c>
       <c r="AA3">
-        <v>37884</v>
+        <v>37939</v>
       </c>
       <c r="AB3">
-        <v>2342</v>
+        <v>2356</v>
       </c>
       <c r="AC3">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="AD3">
-        <v>2802</v>
+        <v>2788</v>
       </c>
       <c r="AE3">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AF3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG3" s="15">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AH3" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI3" s="17">
-        <v>203491824400</v>
+        <v>195089322440</v>
       </c>
       <c r="AJ3" s="18">
-        <v>62122524400</v>
+        <v>53720022440</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
-        <v>46</v>
+      <c r="A4" s="22">
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -1084,109 +1085,109 @@
       <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="15">
-        <v>139.09968645243339</v>
+      <c r="D4" s="22">
+        <v>113.2579520588982</v>
       </c>
       <c r="E4" s="20">
-        <v>40771</v>
-      </c>
-      <c r="F4" s="20">
-        <v>3410</v>
+        <v>40645</v>
+      </c>
+      <c r="F4" s="22">
+        <v>3337</v>
       </c>
       <c r="G4">
-        <v>128.7074074074074</v>
+        <v>128.43333333333331</v>
       </c>
       <c r="H4">
-        <v>11.75185185185185</v>
+        <v>11.62592592592593</v>
       </c>
       <c r="I4">
-        <v>11.75185185185185</v>
+        <v>11.62592592592593</v>
       </c>
       <c r="J4">
-        <v>10.34074074074074</v>
+        <v>10.351851851851849</v>
       </c>
       <c r="K4">
-        <v>0.86296296296296293</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L4">
-        <v>0.86296296296296293</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M4">
-        <v>0.18888888888888891</v>
+        <v>0.12592592592592591</v>
       </c>
       <c r="N4">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O4" s="15">
-        <v>0.20370370370370369</v>
+        <v>0</v>
+      </c>
+      <c r="O4" s="22">
+        <v>0.12592592592592591</v>
       </c>
       <c r="P4">
-        <v>128.10740740740741</v>
+        <v>128.38888888888891</v>
       </c>
       <c r="Q4" t="s">
-        <v>83</v>
-      </c>
-      <c r="R4" s="15">
-        <v>30</v>
+        <v>50</v>
+      </c>
+      <c r="R4" s="22">
+        <v>37.037037037037038</v>
       </c>
       <c r="S4" t="s">
-        <v>84</v>
-      </c>
-      <c r="T4" s="15">
-        <v>62.592592592592588</v>
+        <v>70</v>
+      </c>
+      <c r="T4" s="22">
+        <v>54.444444444444443</v>
       </c>
       <c r="U4" t="s">
-        <v>35</v>
-      </c>
-      <c r="V4" s="19">
-        <v>96.296296296296291</v>
+        <v>39</v>
+      </c>
+      <c r="V4" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="W4" t="s">
-        <v>35</v>
-      </c>
-      <c r="X4" s="15">
-        <v>96.296296296296291</v>
+        <v>49</v>
+      </c>
+      <c r="X4" s="22">
+        <v>74.074074074074076</v>
       </c>
       <c r="Y4">
-        <v>34751</v>
+        <v>34677</v>
       </c>
       <c r="Z4">
-        <v>3173</v>
+        <v>3139</v>
       </c>
       <c r="AA4">
-        <v>37924</v>
+        <v>37816</v>
       </c>
       <c r="AB4">
-        <v>2339</v>
+        <v>2461</v>
       </c>
       <c r="AC4">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="AD4">
-        <v>2792</v>
+        <v>2795</v>
       </c>
       <c r="AE4">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="AF4">
-        <v>4</v>
-      </c>
-      <c r="AG4" s="15">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="22">
+        <v>34</v>
       </c>
       <c r="AH4" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI4" s="17">
-        <v>196644253040</v>
-      </c>
-      <c r="AJ4" s="18">
-        <v>55274953040</v>
+        <v>160111974020</v>
+      </c>
+      <c r="AJ4" s="17">
+        <v>18742674020</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
-        <v>45</v>
+      <c r="A5" s="22">
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -1194,109 +1195,109 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="15">
-        <v>139.06906642389831</v>
+      <c r="D5" s="22">
+        <v>132.25466087757391</v>
       </c>
       <c r="E5" s="20">
-        <v>40771</v>
+        <v>40777</v>
       </c>
       <c r="F5" s="20">
-        <v>3393</v>
+        <v>3411</v>
       </c>
       <c r="G5">
-        <v>128.69999999999999</v>
+        <v>128.72962962962961</v>
       </c>
       <c r="H5">
-        <v>11.75925925925926</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="I5">
-        <v>11.75925925925926</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="J5">
-        <v>10.34074074074074</v>
+        <v>10.3</v>
       </c>
       <c r="K5">
-        <v>0.78518518518518521</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L5">
-        <v>0.78518518518518521</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M5">
         <v>0.18148148148148149</v>
       </c>
       <c r="N5">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O5" s="15">
-        <v>0.20370370370370369</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O5" s="22">
+        <v>0.18888888888888891</v>
       </c>
       <c r="P5">
-        <v>128.17037037037039</v>
+        <v>128.11481481481479</v>
       </c>
       <c r="Q5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" s="20">
-        <v>31.111111111111111</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S5" t="s">
-        <v>66</v>
-      </c>
-      <c r="T5" s="16">
-        <v>58.148148148148152</v>
+        <v>80</v>
+      </c>
+      <c r="T5" s="15">
+        <v>60</v>
       </c>
       <c r="U5" t="s">
-        <v>59</v>
-      </c>
-      <c r="V5" s="15">
-        <v>100</v>
+        <v>61</v>
+      </c>
+      <c r="V5" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W5" t="s">
-        <v>61</v>
-      </c>
-      <c r="X5" s="15">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="X5" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y5">
-        <v>34749</v>
+        <v>34757</v>
       </c>
       <c r="Z5">
-        <v>3175</v>
+        <v>3188</v>
       </c>
       <c r="AA5">
-        <v>37924</v>
+        <v>37945</v>
       </c>
       <c r="AB5">
-        <v>2360</v>
+        <v>2356</v>
       </c>
       <c r="AC5">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AD5">
-        <v>2792</v>
+        <v>2781</v>
       </c>
       <c r="AE5">
         <v>49</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG5" s="15">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AH5" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI5" s="17">
-        <v>196600965720</v>
-      </c>
-      <c r="AJ5" s="18">
-        <v>55231665720</v>
+        <v>186967488300</v>
+      </c>
+      <c r="AJ5" s="17">
+        <v>45598188300</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
-        <v>50</v>
+      <c r="A6" s="22">
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1304,109 +1305,109 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="16">
-        <v>138.5605110020351</v>
-      </c>
-      <c r="E6" s="15">
-        <v>40801</v>
-      </c>
-      <c r="F6" s="15">
-        <v>3423</v>
+      <c r="D6" s="22">
+        <v>128.11040201171329</v>
+      </c>
+      <c r="E6" s="22">
+        <v>39530</v>
+      </c>
+      <c r="F6" s="22">
+        <v>3326</v>
       </c>
       <c r="G6">
-        <v>128.737037037037</v>
+        <v>124.7592592592593</v>
       </c>
       <c r="H6">
-        <v>11.85555555555556</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I6">
-        <v>11.85555555555556</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J6">
-        <v>10.31851851851852</v>
+        <v>9.9851851851851858</v>
       </c>
       <c r="K6">
-        <v>0.8037037037037037</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L6">
-        <v>0.8037037037037037</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M6">
-        <v>0.1851851851851852</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N6">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O6" s="15">
-        <v>0.20370370370370369</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O6" s="22">
+        <v>0.15555555555555561</v>
       </c>
       <c r="P6">
-        <v>128.0740740740741</v>
+        <v>124.2592592592593</v>
       </c>
       <c r="Q6" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="R6" s="20">
-        <v>30.74074074074074</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S6" t="s">
-        <v>41</v>
-      </c>
-      <c r="T6" s="16">
-        <v>58.518518518518512</v>
+        <v>51</v>
+      </c>
+      <c r="T6" s="22">
+        <v>54.814814814814817</v>
       </c>
       <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="V6" s="19">
-        <v>96.296296296296291</v>
+        <v>36</v>
+      </c>
+      <c r="V6" s="22">
+        <v>88.888888888888886</v>
       </c>
       <c r="W6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="X6" s="20">
-        <v>85.18518518518519</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y6">
-        <v>34759</v>
+        <v>33685</v>
       </c>
       <c r="Z6">
-        <v>3201</v>
+        <v>3107</v>
       </c>
       <c r="AA6">
-        <v>37960</v>
+        <v>36792</v>
       </c>
       <c r="AB6">
-        <v>2349</v>
+        <v>2313</v>
       </c>
       <c r="AC6">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD6">
-        <v>2786</v>
+        <v>2696</v>
       </c>
       <c r="AE6">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF6">
-        <v>5</v>
-      </c>
-      <c r="AG6" s="15">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="AG6" s="22">
+        <v>42</v>
       </c>
       <c r="AH6" s="17">
-        <v>141369300000</v>
+        <v>137180580000</v>
       </c>
       <c r="AI6" s="17">
-        <v>195882024480</v>
-      </c>
-      <c r="AJ6" s="18">
-        <v>54512724480</v>
+        <v>175742592520</v>
+      </c>
+      <c r="AJ6" s="17">
+        <v>38562012520</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
-        <v>10</v>
+      <c r="A7" s="22">
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1414,50 +1415,50 @@
       <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="16">
-        <v>137.9997796126882</v>
-      </c>
-      <c r="E7" s="16">
-        <v>40780</v>
-      </c>
-      <c r="F7" s="20">
-        <v>3352</v>
+      <c r="D7" s="22">
+        <v>127.4071409280516</v>
+      </c>
+      <c r="E7" s="22">
+        <v>40707</v>
+      </c>
+      <c r="F7" s="15">
+        <v>3470</v>
       </c>
       <c r="G7">
-        <v>128.93703703703699</v>
+        <v>128.28888888888889</v>
       </c>
       <c r="H7">
-        <v>11.577777777777779</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="I7">
-        <v>11.577777777777779</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="J7">
-        <v>10.32592592592593</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K7">
-        <v>0.81481481481481477</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L7">
-        <v>0.81481481481481477</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M7">
-        <v>0.1740740740740741</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N7">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O7" s="16">
-        <v>0.1962962962962963</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O7" s="22">
+        <v>0.162962962962963</v>
       </c>
       <c r="P7">
-        <v>128.33333333333329</v>
+        <v>127.8962962962963</v>
       </c>
       <c r="Q7" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="R7" s="20">
-        <v>31.481481481481481</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S7" t="s">
         <v>56</v>
@@ -1468,55 +1469,55 @@
       <c r="U7" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="20">
+      <c r="V7" s="22">
         <v>88.888888888888886</v>
       </c>
       <c r="W7" t="s">
         <v>57</v>
       </c>
-      <c r="X7" s="20">
+      <c r="X7" s="22">
         <v>81.481481481481481</v>
       </c>
       <c r="Y7">
-        <v>34813</v>
+        <v>34638</v>
       </c>
       <c r="Z7">
-        <v>3126</v>
+        <v>3239</v>
       </c>
       <c r="AA7">
-        <v>37939</v>
+        <v>37877</v>
       </c>
       <c r="AB7">
-        <v>2356</v>
+        <v>2381</v>
       </c>
       <c r="AC7">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="AD7">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="AE7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AF7">
-        <v>6</v>
-      </c>
-      <c r="AG7" s="15">
-        <v>53</v>
+        <v>2</v>
+      </c>
+      <c r="AG7" s="22">
+        <v>44</v>
       </c>
       <c r="AH7" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI7" s="17">
-        <v>195089322440</v>
-      </c>
-      <c r="AJ7" s="18">
-        <v>53720022440</v>
+        <v>180114583280</v>
+      </c>
+      <c r="AJ7" s="17">
+        <v>38745283280</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -1524,56 +1525,56 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="16">
-        <v>137.232633421825</v>
-      </c>
-      <c r="E8" s="20">
+      <c r="D8" s="15">
+        <v>143.94343354603859</v>
+      </c>
+      <c r="E8" s="22">
         <v>40738</v>
       </c>
       <c r="F8" s="20">
-        <v>3383</v>
+        <v>3404</v>
       </c>
       <c r="G8">
-        <v>128.64814814814821</v>
+        <v>128.67037037037039</v>
       </c>
       <c r="H8">
-        <v>11.662962962962959</v>
+        <v>11.640740740740741</v>
       </c>
       <c r="I8">
-        <v>11.662962962962959</v>
+        <v>11.640740740740741</v>
       </c>
       <c r="J8">
         <v>10.37777777777778</v>
       </c>
       <c r="K8">
-        <v>0.8481481481481481</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="L8">
-        <v>0.8481481481481481</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M8">
-        <v>0.1740740740740741</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N8">
-        <v>1.8518518518518521E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="O8" s="16">
         <v>0.19259259259259259</v>
       </c>
       <c r="P8">
-        <v>128.22592592592591</v>
+        <v>128.14074074074071</v>
       </c>
       <c r="Q8" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="R8" s="15">
-        <v>30</v>
+        <v>24.444444444444439</v>
       </c>
       <c r="S8" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="T8" s="15">
-        <v>64.074074074074076</v>
+        <v>61.851851851851848</v>
       </c>
       <c r="U8" t="s">
         <v>61</v>
@@ -1582,34 +1583,34 @@
         <v>92.592592592592595</v>
       </c>
       <c r="W8" t="s">
-        <v>36</v>
-      </c>
-      <c r="X8" s="16">
-        <v>88.888888888888886</v>
+        <v>61</v>
+      </c>
+      <c r="X8" s="15">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y8">
-        <v>34735</v>
+        <v>34741</v>
       </c>
       <c r="Z8">
-        <v>3149</v>
+        <v>3143</v>
       </c>
       <c r="AA8">
         <v>37884</v>
       </c>
       <c r="AB8">
-        <v>2365</v>
+        <v>2342</v>
       </c>
       <c r="AC8">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="AD8">
         <v>2802</v>
       </c>
       <c r="AE8">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AF8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG8" s="15">
         <v>52</v>
@@ -1618,15 +1619,15 @@
         <v>141369300000</v>
       </c>
       <c r="AI8" s="17">
-        <v>194004813240</v>
+        <v>203491824400</v>
       </c>
       <c r="AJ8" s="18">
-        <v>52635513240</v>
+        <v>62122524400</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
-        <v>43</v>
+      <c r="A9" s="22">
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1634,62 +1635,62 @@
       <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="16">
-        <v>136.81623945227139</v>
-      </c>
-      <c r="E9" s="20">
-        <v>40738</v>
-      </c>
-      <c r="F9" s="15">
-        <v>3461</v>
+      <c r="D9" s="22">
+        <v>132.3466032724219</v>
+      </c>
+      <c r="E9" s="22">
+        <v>40737</v>
+      </c>
+      <c r="F9" s="22">
+        <v>3403</v>
       </c>
       <c r="G9">
-        <v>128.33333333333329</v>
+        <v>128.59629629629629</v>
       </c>
       <c r="H9">
-        <v>11.97777777777778</v>
+        <v>11.78888888888889</v>
       </c>
       <c r="I9">
-        <v>11.97777777777778</v>
+        <v>11.78888888888889</v>
       </c>
       <c r="J9">
-        <v>10.37777777777778</v>
+        <v>10.31481481481481</v>
       </c>
       <c r="K9">
-        <v>0.82222222222222219</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L9">
-        <v>0.82222222222222219</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M9">
-        <v>0.1740740740740741</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N9">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O9" s="16">
-        <v>0.19259259259259259</v>
+      <c r="O9" s="22">
+        <v>0.17777777777777781</v>
       </c>
       <c r="P9">
-        <v>127.89259259259261</v>
+        <v>128.14444444444439</v>
       </c>
       <c r="Q9" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="R9" s="20">
-        <v>31.111111111111111</v>
+        <v>34.074074074074083</v>
       </c>
       <c r="S9" t="s">
-        <v>84</v>
-      </c>
-      <c r="T9" s="15">
-        <v>62.592592592592588</v>
+        <v>58</v>
+      </c>
+      <c r="T9" s="22">
+        <v>57.407407407407398</v>
       </c>
       <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="V9" s="19">
-        <v>96.296296296296291</v>
+        <v>36</v>
+      </c>
+      <c r="V9" s="22">
+        <v>88.888888888888886</v>
       </c>
       <c r="W9" t="s">
         <v>39</v>
@@ -1698,45 +1699,45 @@
         <v>85.18518518518519</v>
       </c>
       <c r="Y9">
-        <v>34650</v>
+        <v>34721</v>
       </c>
       <c r="Z9">
-        <v>3234</v>
+        <v>3183</v>
       </c>
       <c r="AA9">
-        <v>37884</v>
+        <v>37904</v>
       </c>
       <c r="AB9">
-        <v>2372</v>
+        <v>2378</v>
       </c>
       <c r="AC9">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AD9">
-        <v>2802</v>
+        <v>2785</v>
       </c>
       <c r="AE9">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AF9">
         <v>5</v>
       </c>
-      <c r="AG9" s="15">
-        <v>52</v>
+      <c r="AG9" s="22">
+        <v>48</v>
       </c>
       <c r="AH9" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI9" s="17">
-        <v>193416160000</v>
+        <v>187097466620</v>
       </c>
       <c r="AJ9" s="17">
-        <v>52046860000</v>
+        <v>45728166620</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <v>49</v>
+      <c r="A10" s="22">
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1744,109 +1745,109 @@
       <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="16">
-        <v>136.1734986025962</v>
-      </c>
-      <c r="E10" s="15">
-        <v>40801</v>
-      </c>
-      <c r="F10" s="20">
-        <v>3370</v>
+      <c r="D10" s="22">
+        <v>128.3768819680086</v>
+      </c>
+      <c r="E10" s="22">
+        <v>40700</v>
+      </c>
+      <c r="F10" s="22">
+        <v>3369</v>
       </c>
       <c r="G10">
-        <v>128.88888888888891</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H10">
-        <v>11.703703703703701</v>
+        <v>11.614814814814819</v>
       </c>
       <c r="I10">
-        <v>11.703703703703701</v>
+        <v>11.614814814814819</v>
       </c>
       <c r="J10">
-        <v>10.31851851851852</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K10">
-        <v>0.76296296296296295</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L10">
-        <v>0.76296296296296295</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M10">
-        <v>0.18888888888888891</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N10">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O10" s="15">
-        <v>0.20370370370370369</v>
+      <c r="O10" s="22">
+        <v>0.15925925925925929</v>
       </c>
       <c r="P10">
-        <v>128.28148148148151</v>
+        <v>128.27037037037039</v>
       </c>
       <c r="Q10" t="s">
-        <v>37</v>
-      </c>
-      <c r="R10" s="20">
-        <v>34.074074074074083</v>
+        <v>89</v>
+      </c>
+      <c r="R10" s="15">
+        <v>29.25925925925926</v>
       </c>
       <c r="S10" t="s">
-        <v>38</v>
-      </c>
-      <c r="T10" s="20">
-        <v>55.925925925925917</v>
+        <v>43</v>
+      </c>
+      <c r="T10" s="16">
+        <v>58.888888888888893</v>
       </c>
       <c r="U10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V10" s="7">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W10" t="s">
+        <v>57</v>
+      </c>
+      <c r="X10" s="20">
+        <v>81.481481481481481</v>
+      </c>
+      <c r="Y10">
+        <v>34731</v>
+      </c>
+      <c r="Z10">
+        <v>3136</v>
+      </c>
+      <c r="AA10">
+        <v>37867</v>
+      </c>
+      <c r="AB10">
+        <v>2389</v>
+      </c>
+      <c r="AC10">
+        <v>229</v>
+      </c>
+      <c r="AD10">
+        <v>2790</v>
+      </c>
+      <c r="AE10">
         <v>39</v>
-      </c>
-      <c r="V10" s="20">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="W10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X10" s="20">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y10">
-        <v>34800</v>
-      </c>
-      <c r="Z10">
-        <v>3160</v>
-      </c>
-      <c r="AA10">
-        <v>37960</v>
-      </c>
-      <c r="AB10">
-        <v>2360</v>
-      </c>
-      <c r="AC10">
-        <v>206</v>
-      </c>
-      <c r="AD10">
-        <v>2786</v>
-      </c>
-      <c r="AE10">
-        <v>51</v>
       </c>
       <c r="AF10">
         <v>4</v>
       </c>
-      <c r="AG10" s="15">
-        <v>55</v>
+      <c r="AG10" s="22">
+        <v>43</v>
       </c>
       <c r="AH10" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI10" s="17">
-        <v>192507521760</v>
-      </c>
-      <c r="AJ10" s="18">
-        <v>51138221760</v>
+        <v>181485499400</v>
+      </c>
+      <c r="AJ10" s="17">
+        <v>40116199400</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
-        <v>47</v>
+      <c r="A11" s="22">
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1854,109 +1855,109 @@
       <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="20">
-        <v>135.74983728433261</v>
+      <c r="D11" s="22">
+        <v>130.98891603764039</v>
       </c>
       <c r="E11" s="20">
-        <v>40780</v>
+        <v>40715</v>
       </c>
       <c r="F11" s="20">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="G11">
-        <v>128.9851851851852</v>
+        <v>128.85925925925929</v>
       </c>
       <c r="H11">
-        <v>11.52962962962963</v>
+        <v>11.4037037037037</v>
       </c>
       <c r="I11">
-        <v>11.52962962962963</v>
+        <v>11.4037037037037</v>
       </c>
       <c r="J11">
-        <v>10.32592592592593</v>
+        <v>10.36296296296296</v>
       </c>
       <c r="K11">
-        <v>0.73703703703703705</v>
+        <v>0.85555555555555551</v>
       </c>
       <c r="L11">
-        <v>0.73703703703703705</v>
+        <v>0.85555555555555551</v>
       </c>
       <c r="M11">
-        <v>0.1740740740740741</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N11">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O11" s="16">
-        <v>0.1962962962962963</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O11" s="22">
+        <v>0.17037037037037039</v>
       </c>
       <c r="P11">
-        <v>128.44444444444451</v>
+        <v>128.47407407407411</v>
       </c>
       <c r="Q11" t="s">
-        <v>86</v>
-      </c>
-      <c r="R11" s="20">
-        <v>37.777777777777779</v>
+        <v>64</v>
+      </c>
+      <c r="R11" s="22">
+        <v>32.222222222222221</v>
       </c>
       <c r="S11" t="s">
-        <v>68</v>
-      </c>
-      <c r="T11" s="20">
-        <v>51.851851851851848</v>
+        <v>41</v>
+      </c>
+      <c r="T11" s="16">
+        <v>58.518518518518512</v>
       </c>
       <c r="U11" t="s">
         <v>36</v>
       </c>
-      <c r="V11" s="20">
+      <c r="V11" s="22">
         <v>88.888888888888886</v>
       </c>
       <c r="W11" t="s">
-        <v>57</v>
-      </c>
-      <c r="X11" s="20">
-        <v>81.481481481481481</v>
+        <v>39</v>
+      </c>
+      <c r="X11" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y11">
-        <v>34826</v>
+        <v>34792</v>
       </c>
       <c r="Z11">
-        <v>3113</v>
+        <v>3079</v>
       </c>
       <c r="AA11">
-        <v>37939</v>
+        <v>37871</v>
       </c>
       <c r="AB11">
-        <v>2377</v>
+        <v>2383</v>
       </c>
       <c r="AC11">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="AD11">
-        <v>2788</v>
+        <v>2798</v>
       </c>
       <c r="AE11">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AF11">
-        <v>6</v>
-      </c>
-      <c r="AG11" s="15">
-        <v>53</v>
+        <v>4</v>
+      </c>
+      <c r="AG11" s="22">
+        <v>46</v>
       </c>
       <c r="AH11" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI11" s="17">
-        <v>191908594720</v>
+        <v>185178113680</v>
       </c>
       <c r="AJ11" s="17">
-        <v>50539294720</v>
+        <v>43808813680</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="20">
-        <v>48</v>
+      <c r="A12" s="22">
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1964,108 +1965,108 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="20">
-        <v>135.08681222868049</v>
+      <c r="D12" s="22">
+        <v>121.16360259264211</v>
       </c>
       <c r="E12" s="20">
-        <v>40780</v>
-      </c>
-      <c r="F12" s="15">
-        <v>3454</v>
+        <v>40700</v>
+      </c>
+      <c r="F12" s="22">
+        <v>3338</v>
       </c>
       <c r="G12">
-        <v>128.58148148148149</v>
+        <v>128.67037037037039</v>
       </c>
       <c r="H12">
-        <v>11.93333333333333</v>
+        <v>11.6</v>
       </c>
       <c r="I12">
-        <v>11.93333333333333</v>
+        <v>11.6</v>
       </c>
       <c r="J12">
         <v>10.32592592592593</v>
       </c>
       <c r="K12">
-        <v>0.85185185185185186</v>
+        <v>0.75185185185185188</v>
       </c>
       <c r="L12">
-        <v>0.85185185185185186</v>
+        <v>0.75185185185185188</v>
       </c>
       <c r="M12">
-        <v>0.18888888888888891</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="N12">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O12" s="16">
-        <v>0.1962962962962963</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O12" s="22">
+        <v>0.1444444444444444</v>
       </c>
       <c r="P12">
-        <v>127.99629629629629</v>
+        <v>128.38518518518521</v>
       </c>
       <c r="Q12" t="s">
-        <v>87</v>
-      </c>
-      <c r="R12" s="15">
-        <v>25.92592592592592</v>
+        <v>81</v>
+      </c>
+      <c r="R12" s="22">
+        <v>37.407407407407398</v>
       </c>
       <c r="S12" t="s">
-        <v>85</v>
-      </c>
-      <c r="T12" s="15">
-        <v>64.074074074074076</v>
+        <v>82</v>
+      </c>
+      <c r="T12" s="22">
+        <v>52.962962962962969</v>
       </c>
       <c r="U12" t="s">
-        <v>36</v>
-      </c>
-      <c r="V12" s="20">
-        <v>88.888888888888886</v>
+        <v>39</v>
+      </c>
+      <c r="V12" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="W12" t="s">
-        <v>57</v>
-      </c>
-      <c r="X12" s="20">
-        <v>81.481481481481481</v>
+        <v>49</v>
+      </c>
+      <c r="X12" s="22">
+        <v>74.074074074074076</v>
       </c>
       <c r="Y12">
-        <v>34717</v>
+        <v>34741</v>
       </c>
       <c r="Z12">
-        <v>3222</v>
+        <v>3132</v>
       </c>
       <c r="AA12">
-        <v>37939</v>
+        <v>37873</v>
       </c>
       <c r="AB12">
-        <v>2346</v>
+        <v>2429</v>
       </c>
       <c r="AC12">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="AD12">
         <v>2788</v>
       </c>
       <c r="AE12">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="AF12">
-        <v>2</v>
-      </c>
-      <c r="AG12" s="15">
-        <v>53</v>
+        <v>3</v>
+      </c>
+      <c r="AG12" s="22">
+        <v>39</v>
       </c>
       <c r="AH12" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI12" s="17">
-        <v>190971280840</v>
+        <v>171288136840</v>
       </c>
       <c r="AJ12" s="17">
-        <v>49601980840</v>
+        <v>29918836840</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
+      <c r="A13" s="22">
         <v>20</v>
       </c>
       <c r="B13" t="s">
@@ -2074,7 +2075,7 @@
       <c r="C13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <v>134.7273627300977</v>
       </c>
       <c r="E13" s="16">
@@ -2122,7 +2123,7 @@
       <c r="S13" t="s">
         <v>58</v>
       </c>
-      <c r="T13" s="20">
+      <c r="T13" s="22">
         <v>57.407407407407398</v>
       </c>
       <c r="U13" t="s">
@@ -2175,8 +2176,8 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A14" s="20">
-        <v>44</v>
+      <c r="A14" s="22">
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -2184,109 +2185,109 @@
       <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="20">
-        <v>134.43323094901089</v>
-      </c>
-      <c r="E14" s="20">
-        <v>40738</v>
-      </c>
-      <c r="F14" s="20">
-        <v>3283</v>
+      <c r="D14" s="22">
+        <v>120.4952906182601</v>
+      </c>
+      <c r="E14" s="22">
+        <v>40686</v>
+      </c>
+      <c r="F14" s="22">
+        <v>3412</v>
       </c>
       <c r="G14">
-        <v>128.9296296296296</v>
+        <v>128.3666666666667</v>
       </c>
       <c r="H14">
-        <v>11.38148148148148</v>
+        <v>11.885185185185181</v>
       </c>
       <c r="I14">
-        <v>11.38148148148148</v>
+        <v>11.885185185185181</v>
       </c>
       <c r="J14">
-        <v>10.37777777777778</v>
+        <v>10.3037037037037</v>
       </c>
       <c r="K14">
-        <v>0.7592592592592593</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L14">
-        <v>0.7592592592592593</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M14">
-        <v>0.1740740740740741</v>
+        <v>0.1148148148148148</v>
       </c>
       <c r="N14">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O14" s="16">
-        <v>0.19259259259259259</v>
+      <c r="O14" s="22">
+        <v>0.1333333333333333</v>
       </c>
       <c r="P14">
-        <v>128.61111111111109</v>
+        <v>128.11111111111109</v>
       </c>
       <c r="Q14" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="R14" s="20">
-        <v>33.703703703703702</v>
+        <v>41.481481481481481</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
-      </c>
-      <c r="T14" s="16">
-        <v>58.888888888888893</v>
+        <v>68</v>
+      </c>
+      <c r="T14" s="22">
+        <v>51.851851851851848</v>
       </c>
       <c r="U14" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14" s="20">
-        <v>88.888888888888886</v>
+        <v>49</v>
+      </c>
+      <c r="V14" s="22">
+        <v>74.074074074074076</v>
       </c>
       <c r="W14" t="s">
-        <v>36</v>
-      </c>
-      <c r="X14" s="16">
-        <v>88.888888888888886</v>
+        <v>69</v>
+      </c>
+      <c r="X14" s="22">
+        <v>59.259259259259252</v>
       </c>
       <c r="Y14">
-        <v>34811</v>
+        <v>34659</v>
       </c>
       <c r="Z14">
-        <v>3073</v>
+        <v>3209</v>
       </c>
       <c r="AA14">
-        <v>37884</v>
+        <v>37868</v>
       </c>
       <c r="AB14">
-        <v>2389</v>
+        <v>2440</v>
       </c>
       <c r="AC14">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="AD14">
-        <v>2802</v>
+        <v>2782</v>
       </c>
       <c r="AE14">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="AF14">
         <v>5</v>
       </c>
-      <c r="AG14" s="15">
-        <v>52</v>
+      <c r="AG14" s="22">
+        <v>36</v>
       </c>
       <c r="AH14" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI14" s="17">
-        <v>190047317560</v>
+        <v>170343348880</v>
       </c>
       <c r="AJ14" s="17">
-        <v>48678017560</v>
+        <v>28974048880</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A15" s="20">
-        <v>36</v>
+      <c r="A15" s="22">
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2294,109 +2295,109 @@
       <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="20">
-        <v>134.21853146981681</v>
-      </c>
-      <c r="E15" s="15">
-        <v>40773</v>
+      <c r="D15" s="22">
+        <v>120.5562728400013</v>
+      </c>
+      <c r="E15" s="22">
+        <v>40635</v>
       </c>
       <c r="F15" s="20">
-        <v>3382</v>
+        <v>3414</v>
       </c>
       <c r="G15">
-        <v>128.77407407407409</v>
+        <v>128.07777777777781</v>
       </c>
       <c r="H15">
-        <v>11.707407407407411</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="I15">
-        <v>11.707407407407411</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="J15">
-        <v>10.34814814814815</v>
+        <v>10.425925925925929</v>
       </c>
       <c r="K15">
-        <v>0.79629629629629628</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="L15">
-        <v>0.79629629629629628</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="M15">
-        <v>0.15925925925925929</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N15">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O15" s="20">
-        <v>0.18148148148148149</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O15" s="22">
+        <v>0.1444444444444444</v>
       </c>
       <c r="P15">
-        <v>128.30000000000001</v>
+        <v>128.1037037037037</v>
       </c>
       <c r="Q15" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="R15" s="20">
-        <v>33.703703703703702</v>
+        <v>35.555555555555557</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
-      </c>
-      <c r="T15" s="16">
-        <v>58.888888888888893</v>
+        <v>56</v>
+      </c>
+      <c r="T15" s="22">
+        <v>57.037037037037038</v>
       </c>
       <c r="U15" t="s">
-        <v>35</v>
-      </c>
-      <c r="V15" s="19">
-        <v>96.296296296296291</v>
+        <v>57</v>
+      </c>
+      <c r="V15" s="22">
+        <v>81.481481481481481</v>
       </c>
       <c r="W15" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15" s="16">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="X15" s="22">
+        <v>70.370370370370367</v>
       </c>
       <c r="Y15">
-        <v>34769</v>
+        <v>34581</v>
       </c>
       <c r="Z15">
-        <v>3161</v>
+        <v>3200</v>
       </c>
       <c r="AA15">
-        <v>37930</v>
+        <v>37781</v>
       </c>
       <c r="AB15">
-        <v>2383</v>
+        <v>2446</v>
       </c>
       <c r="AC15">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AD15">
-        <v>2794</v>
+        <v>2815</v>
       </c>
       <c r="AE15">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AF15">
-        <v>6</v>
-      </c>
-      <c r="AG15" s="20">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="AG15" s="22">
+        <v>39</v>
       </c>
       <c r="AH15" s="17">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI15" s="17">
-        <v>189856139320</v>
+        <v>170429559020</v>
       </c>
       <c r="AJ15" s="17">
-        <v>48403139320</v>
+        <v>29060259020</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A16" s="20">
-        <v>31</v>
+      <c r="A16" s="22">
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -2404,109 +2405,109 @@
       <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="20">
-        <v>133.5813685998304</v>
+      <c r="D16" s="22">
+        <v>122.0712722776445</v>
       </c>
       <c r="E16" s="20">
-        <v>40771</v>
+        <v>40670</v>
       </c>
       <c r="F16" s="20">
-        <v>3348</v>
+        <v>3413</v>
       </c>
       <c r="G16">
-        <v>128.81481481481481</v>
+        <v>128.37407407407409</v>
       </c>
       <c r="H16">
-        <v>11.64444444444444</v>
+        <v>11.792592592592589</v>
       </c>
       <c r="I16">
-        <v>11.64444444444444</v>
+        <v>11.792592592592589</v>
       </c>
       <c r="J16">
-        <v>10.34074074074074</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K16">
-        <v>0.74814814814814812</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="L16">
-        <v>0.74814814814814812</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="M16">
-        <v>0.1962962962962963</v>
+        <v>0.12592592592592591</v>
       </c>
       <c r="N16">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O16" s="15">
-        <v>0.20370370370370369</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O16" s="22">
+        <v>0.13703703703703701</v>
       </c>
       <c r="P16">
-        <v>128.34814814814811</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q16" t="s">
-        <v>71</v>
-      </c>
-      <c r="R16" s="20">
-        <v>31.111111111111111</v>
+        <v>42</v>
+      </c>
+      <c r="R16" s="22">
+        <v>33.703703703703702</v>
       </c>
       <c r="S16" t="s">
-        <v>53</v>
-      </c>
-      <c r="T16" s="20">
-        <v>56.666666666666657</v>
+        <v>41</v>
+      </c>
+      <c r="T16" s="16">
+        <v>58.518518518518512</v>
       </c>
       <c r="U16" t="s">
         <v>36</v>
       </c>
-      <c r="V16" s="20">
+      <c r="V16" s="22">
         <v>88.888888888888886</v>
       </c>
       <c r="W16" t="s">
-        <v>54</v>
-      </c>
-      <c r="X16" s="20">
-        <v>77.777777777777786</v>
+        <v>78</v>
+      </c>
+      <c r="X16" s="22">
+        <v>66.666666666666657</v>
       </c>
       <c r="Y16">
-        <v>34780</v>
+        <v>34661</v>
       </c>
       <c r="Z16">
-        <v>3144</v>
+        <v>3184</v>
       </c>
       <c r="AA16">
-        <v>37924</v>
+        <v>37845</v>
       </c>
       <c r="AB16">
-        <v>2370</v>
+        <v>2414</v>
       </c>
       <c r="AC16">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="AD16">
-        <v>2792</v>
+        <v>2788</v>
       </c>
       <c r="AE16">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="AF16">
-        <v>2</v>
-      </c>
-      <c r="AG16" s="15">
-        <v>55</v>
+        <v>3</v>
+      </c>
+      <c r="AG16" s="22">
+        <v>37</v>
       </c>
       <c r="AH16" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI16" s="17">
-        <v>188843045720</v>
+        <v>172571303120</v>
       </c>
       <c r="AJ16" s="17">
-        <v>47473745720</v>
+        <v>31202003120</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A17" s="20">
-        <v>38</v>
+      <c r="A17" s="22">
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -2514,56 +2515,56 @@
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="20">
-        <v>133.24790789873671</v>
+      <c r="D17" s="22">
+        <v>119.321995058333</v>
       </c>
       <c r="E17" s="20">
-        <v>40755</v>
-      </c>
-      <c r="F17" s="15">
-        <v>3426</v>
+        <v>40671</v>
+      </c>
+      <c r="F17" s="22">
+        <v>3419</v>
       </c>
       <c r="G17">
-        <v>128.6037037037037</v>
+        <v>128.31851851851849</v>
       </c>
       <c r="H17">
-        <v>11.851851851851849</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="I17">
-        <v>11.851851851851849</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="J17">
-        <v>10.31851851851852</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K17">
-        <v>0.81111111111111112</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L17">
-        <v>0.81111111111111112</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M17">
-        <v>0.1444444444444444</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N17">
-        <v>2.5925925925925929E-2</v>
-      </c>
-      <c r="O17" s="20">
-        <v>0.17037037037037039</v>
+        <v>0</v>
+      </c>
+      <c r="O17" s="22">
+        <v>0.14074074074074069</v>
       </c>
       <c r="P17">
-        <v>128.137037037037</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q17" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="R17" s="20">
-        <v>32.962962962962962</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="S17" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="T17" s="16">
-        <v>58.148148148148152</v>
+        <v>58.518518518518512</v>
       </c>
       <c r="U17" t="s">
         <v>61</v>
@@ -2572,51 +2573,51 @@
         <v>92.592592592592595</v>
       </c>
       <c r="W17" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="X17" s="20">
-        <v>85.18518518518519</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="Y17">
-        <v>34723</v>
+        <v>34646</v>
       </c>
       <c r="Z17">
-        <v>3200</v>
+        <v>3197</v>
       </c>
       <c r="AA17">
-        <v>37923</v>
+        <v>37843</v>
       </c>
       <c r="AB17">
-        <v>2383</v>
+        <v>2416</v>
       </c>
       <c r="AC17">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AD17">
-        <v>2786</v>
+        <v>2790</v>
       </c>
       <c r="AE17">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF17">
-        <v>7</v>
-      </c>
-      <c r="AG17" s="20">
-        <v>46</v>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="22">
+        <v>38</v>
       </c>
       <c r="AH17" s="17">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI17" s="17">
-        <v>188483163160</v>
+        <v>168684669160</v>
       </c>
       <c r="AJ17" s="17">
-        <v>47030163160</v>
+        <v>27315369160</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A18" s="20">
-        <v>16</v>
+      <c r="A18" s="22">
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -2624,109 +2625,109 @@
       <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="20">
-        <v>132.3466032724219</v>
-      </c>
-      <c r="E18" s="20">
-        <v>40737</v>
+      <c r="D18" s="22">
+        <v>126.6790426209934</v>
+      </c>
+      <c r="E18" s="22">
+        <v>40732</v>
       </c>
       <c r="F18" s="20">
-        <v>3403</v>
+        <v>3363</v>
       </c>
       <c r="G18">
-        <v>128.59629629629629</v>
+        <v>128.76666666666671</v>
       </c>
       <c r="H18">
-        <v>11.78888888888889</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I18">
-        <v>11.78888888888889</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J18">
-        <v>10.31481481481481</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K18">
-        <v>0.79629629629629628</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="L18">
-        <v>0.79629629629629628</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="M18">
-        <v>0.15925925925925929</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="N18">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O18" s="20">
-        <v>0.17777777777777781</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O18" s="22">
+        <v>0.16666666666666671</v>
       </c>
       <c r="P18">
-        <v>128.14444444444439</v>
+        <v>128.2925925925926</v>
       </c>
       <c r="Q18" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="R18" s="20">
-        <v>34.074074074074083</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="S18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T18" s="20">
-        <v>57.407407407407398</v>
+        <v>57.037037037037038</v>
       </c>
       <c r="U18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V18" s="20">
-        <v>88.888888888888886</v>
+        <v>61</v>
+      </c>
+      <c r="V18" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W18" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="X18" s="20">
-        <v>85.18518518518519</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="Y18">
-        <v>34721</v>
+        <v>34767</v>
       </c>
       <c r="Z18">
-        <v>3183</v>
+        <v>3134</v>
       </c>
       <c r="AA18">
-        <v>37904</v>
+        <v>37901</v>
       </c>
       <c r="AB18">
         <v>2378</v>
       </c>
       <c r="AC18">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AD18">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="AE18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF18">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="20">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="AG18" s="22">
+        <v>45</v>
       </c>
       <c r="AH18" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI18" s="17">
-        <v>187097466620</v>
+        <v>179085275800</v>
       </c>
       <c r="AJ18" s="17">
-        <v>45728166620</v>
+        <v>37715975800</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19" s="20">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -2735,55 +2736,55 @@
         <v>32</v>
       </c>
       <c r="D19" s="20">
-        <v>132.25466087757391</v>
+        <v>129.8896579809053</v>
       </c>
       <c r="E19" s="20">
-        <v>40777</v>
+        <v>40727</v>
       </c>
       <c r="F19" s="20">
-        <v>3411</v>
+        <v>3298</v>
       </c>
       <c r="G19">
-        <v>128.72962962962961</v>
+        <v>128.9148148148148</v>
       </c>
       <c r="H19">
-        <v>11.80740740740741</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="I19">
-        <v>11.80740740740741</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="J19">
-        <v>10.3</v>
+        <v>10.37407407407407</v>
       </c>
       <c r="K19">
-        <v>0.81851851851851853</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L19">
-        <v>0.81851851851851853</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M19">
-        <v>0.18148148148148149</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="N19">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O19" s="20">
-        <v>0.18888888888888891</v>
+      <c r="O19" s="22">
+        <v>0.17777777777777781</v>
       </c>
       <c r="P19">
-        <v>128.11481481481479</v>
+        <v>128.5333333333333</v>
       </c>
       <c r="Q19" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="R19" s="20">
-        <v>33.333333333333329</v>
+        <v>35.185185185185183</v>
       </c>
       <c r="S19" t="s">
-        <v>80</v>
-      </c>
-      <c r="T19" s="15">
-        <v>60</v>
+        <v>63</v>
+      </c>
+      <c r="T19" s="22">
+        <v>54.074074074074083</v>
       </c>
       <c r="U19" t="s">
         <v>61</v>
@@ -2792,51 +2793,51 @@
         <v>92.592592592592595</v>
       </c>
       <c r="W19" t="s">
-        <v>36</v>
-      </c>
-      <c r="X19" s="16">
-        <v>88.888888888888886</v>
+        <v>39</v>
+      </c>
+      <c r="X19" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y19">
-        <v>34757</v>
+        <v>34807</v>
       </c>
       <c r="Z19">
-        <v>3188</v>
+        <v>3071</v>
       </c>
       <c r="AA19">
-        <v>37945</v>
+        <v>37878</v>
       </c>
       <c r="AB19">
-        <v>2356</v>
+        <v>2384</v>
       </c>
       <c r="AC19">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AD19">
-        <v>2781</v>
+        <v>2801</v>
       </c>
       <c r="AE19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>2</v>
       </c>
-      <c r="AG19" s="15">
-        <v>51</v>
+      <c r="AG19" s="22">
+        <v>48</v>
       </c>
       <c r="AH19" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI19" s="17">
-        <v>186967488300</v>
+        <v>183624100260</v>
       </c>
       <c r="AJ19" s="17">
-        <v>45598188300</v>
+        <v>42254800260</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20" s="20">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -2845,108 +2846,108 @@
         <v>32</v>
       </c>
       <c r="D20" s="20">
-        <v>131.7624941200105</v>
+        <v>129.8617456689677</v>
       </c>
       <c r="E20" s="20">
-        <v>40738</v>
-      </c>
-      <c r="F20">
-        <v>3379</v>
+        <v>40740</v>
+      </c>
+      <c r="F20" s="22">
+        <v>3322</v>
       </c>
       <c r="G20">
-        <v>128.5703703703704</v>
+        <v>128.78518518518521</v>
       </c>
       <c r="H20">
-        <v>11.74074074074074</v>
+        <v>11.525925925925931</v>
       </c>
       <c r="I20">
-        <v>11.74074074074074</v>
+        <v>11.525925925925931</v>
       </c>
       <c r="J20">
-        <v>10.37777777777778</v>
+        <v>10.388888888888889</v>
       </c>
       <c r="K20">
-        <v>0.76666666666666672</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="L20">
-        <v>0.76666666666666672</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="M20">
         <v>0.1851851851851852</v>
       </c>
       <c r="N20">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O20" s="16">
-        <v>0.19259259259259259</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O20" s="22">
+        <v>0.18888888888888891</v>
       </c>
       <c r="P20">
-        <v>128.2222222222222</v>
+        <v>128.44444444444451</v>
       </c>
       <c r="Q20" t="s">
-        <v>71</v>
-      </c>
-      <c r="R20" s="15">
-        <v>31.111111111111111</v>
+        <v>42</v>
+      </c>
+      <c r="R20" s="22">
+        <v>33.703703703703702</v>
       </c>
       <c r="S20" t="s">
-        <v>88</v>
-      </c>
-      <c r="T20" s="16">
-        <v>59.629629629629633</v>
+        <v>70</v>
+      </c>
+      <c r="T20" s="22">
+        <v>54.444444444444443</v>
       </c>
       <c r="U20" t="s">
+        <v>59</v>
+      </c>
+      <c r="V20" s="19">
+        <v>100</v>
+      </c>
+      <c r="W20" t="s">
         <v>36</v>
       </c>
-      <c r="V20" s="20">
+      <c r="X20" s="16">
         <v>88.888888888888886</v>
       </c>
-      <c r="W20" t="s">
-        <v>39</v>
-      </c>
-      <c r="X20" s="20">
-        <v>85.18518518518519</v>
-      </c>
       <c r="Y20">
-        <v>34714</v>
+        <v>34772</v>
       </c>
       <c r="Z20">
-        <v>3170</v>
+        <v>3112</v>
       </c>
       <c r="AA20">
         <v>37884</v>
       </c>
       <c r="AB20">
-        <v>2387</v>
+        <v>2392</v>
       </c>
       <c r="AC20">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AD20">
-        <v>2802</v>
+        <v>2805</v>
       </c>
       <c r="AE20">
         <v>50</v>
       </c>
       <c r="AF20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="15">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AH20" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI20" s="17">
-        <v>186271715600</v>
+        <v>183584640820</v>
       </c>
       <c r="AJ20" s="17">
-        <v>44902415600</v>
+        <v>42215340820</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21" s="20">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -2955,108 +2956,108 @@
         <v>32</v>
       </c>
       <c r="D21" s="20">
-        <v>131.30895267925919</v>
-      </c>
-      <c r="E21" s="20">
-        <v>40738</v>
+        <v>126.4057725970207</v>
+      </c>
+      <c r="E21" s="22">
+        <v>40733</v>
       </c>
       <c r="F21" s="20">
-        <v>3222</v>
+        <v>3334</v>
       </c>
       <c r="G21">
-        <v>129.1925925925926</v>
+        <v>128.72592592592591</v>
       </c>
       <c r="H21">
-        <v>11.11851851851852</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I21">
-        <v>11.11851851851852</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J21">
-        <v>10.37777777777778</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="K21">
-        <v>0.81111111111111112</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L21">
-        <v>0.81111111111111112</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M21">
-        <v>0.18888888888888891</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N21">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O21" s="16">
-        <v>0.19259259259259259</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O21" s="22">
+        <v>0.1740740740740741</v>
       </c>
       <c r="P21">
-        <v>128.83703703703699</v>
+        <v>128.4</v>
       </c>
       <c r="Q21" t="s">
-        <v>83</v>
-      </c>
-      <c r="R21" s="15">
-        <v>30</v>
+        <v>73</v>
+      </c>
+      <c r="R21" s="22">
+        <v>34.444444444444443</v>
       </c>
       <c r="S21" t="s">
-        <v>66</v>
-      </c>
-      <c r="T21" s="16">
-        <v>58.148148148148152</v>
+        <v>74</v>
+      </c>
+      <c r="T21" s="22">
+        <v>51.111111111111107</v>
       </c>
       <c r="U21" t="s">
-        <v>36</v>
-      </c>
-      <c r="V21" s="20">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V21" s="19">
+        <v>96.296296296296291</v>
       </c>
       <c r="W21" t="s">
-        <v>39</v>
-      </c>
-      <c r="X21" s="20">
-        <v>85.18518518518519</v>
+        <v>54</v>
+      </c>
+      <c r="X21" s="22">
+        <v>77.777777777777786</v>
       </c>
       <c r="Y21">
-        <v>34882</v>
+        <v>34756</v>
       </c>
       <c r="Z21">
-        <v>3002</v>
+        <v>3134</v>
       </c>
       <c r="AA21">
-        <v>37884</v>
+        <v>37890</v>
       </c>
       <c r="AB21">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="AC21">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="AD21">
-        <v>2802</v>
+        <v>2796</v>
       </c>
       <c r="AE21">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="15">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="AG21" s="22">
+        <v>47</v>
       </c>
       <c r="AH21" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI21" s="17">
-        <v>185630547240</v>
+        <v>178698955880</v>
       </c>
       <c r="AJ21" s="17">
-        <v>44261247240</v>
+        <v>37329655880</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22" s="20">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -3065,43 +3066,43 @@
         <v>32</v>
       </c>
       <c r="D22" s="20">
-        <v>131.2077959358927</v>
-      </c>
-      <c r="E22" s="20">
-        <v>40728</v>
+        <v>126.3272132492698</v>
+      </c>
+      <c r="E22" s="15">
+        <v>40684</v>
       </c>
       <c r="F22" s="20">
-        <v>3325</v>
+        <v>3338</v>
       </c>
       <c r="G22">
-        <v>128.81481481481481</v>
+        <v>128.62222222222221</v>
       </c>
       <c r="H22">
-        <v>11.5037037037037</v>
+        <v>11.514814814814811</v>
       </c>
       <c r="I22">
-        <v>11.5037037037037</v>
+        <v>11.514814814814811</v>
       </c>
       <c r="J22">
-        <v>10.351851851851849</v>
+        <v>10.392592592592591</v>
       </c>
       <c r="K22">
-        <v>0.79259259259259263</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L22">
-        <v>0.79259259259259263</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M22">
-        <v>0.15555555555555561</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N22">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O22" s="20">
-        <v>0.1740740740740741</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O22" s="22">
+        <v>0.15185185185185179</v>
       </c>
       <c r="P22">
-        <v>128.43333333333331</v>
+        <v>128.38518518518521</v>
       </c>
       <c r="Q22" t="s">
         <v>44</v>
@@ -3110,10 +3111,10 @@
         <v>32.592592592592602</v>
       </c>
       <c r="S22" t="s">
-        <v>38</v>
-      </c>
-      <c r="T22" s="16">
-        <v>55.925925925925917</v>
+        <v>45</v>
+      </c>
+      <c r="T22" s="22">
+        <v>53.333333333333343</v>
       </c>
       <c r="U22" t="s">
         <v>36</v>
@@ -3122,51 +3123,51 @@
         <v>88.888888888888886</v>
       </c>
       <c r="W22" t="s">
-        <v>39</v>
-      </c>
-      <c r="X22" s="20">
-        <v>85.18518518518519</v>
+        <v>46</v>
+      </c>
+      <c r="X22" s="22">
+        <v>70.370370370370367</v>
       </c>
       <c r="Y22">
-        <v>34780</v>
+        <v>34728</v>
       </c>
       <c r="Z22">
-        <v>3106</v>
+        <v>3109</v>
       </c>
       <c r="AA22">
-        <v>37886</v>
+        <v>37837</v>
       </c>
       <c r="AB22">
-        <v>2393</v>
+        <v>2417</v>
       </c>
       <c r="AC22">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="AD22">
-        <v>2795</v>
+        <v>2806</v>
       </c>
       <c r="AE22">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AF22">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="20">
-        <v>47</v>
+        <v>4</v>
+      </c>
+      <c r="AG22" s="22">
+        <v>41</v>
       </c>
       <c r="AH22" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI22" s="17">
-        <v>185487542660</v>
+        <v>178587897080</v>
       </c>
       <c r="AJ22" s="17">
-        <v>44118242660</v>
+        <v>37218597080</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -3175,108 +3176,108 @@
         <v>32</v>
       </c>
       <c r="D23" s="20">
-        <v>130.98891603764039</v>
+        <v>129.4359784054954</v>
       </c>
       <c r="E23" s="20">
-        <v>40715</v>
+        <v>40730</v>
       </c>
       <c r="F23" s="20">
-        <v>3314</v>
+        <v>3412</v>
       </c>
       <c r="G23">
-        <v>128.85925925925929</v>
+        <v>128.65555555555559</v>
       </c>
       <c r="H23">
-        <v>11.4037037037037</v>
+        <v>11.733333333333331</v>
       </c>
       <c r="I23">
-        <v>11.4037037037037</v>
+        <v>11.733333333333331</v>
       </c>
       <c r="J23">
-        <v>10.36296296296296</v>
+        <v>10.3</v>
       </c>
       <c r="K23">
-        <v>0.85555555555555551</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="L23">
-        <v>0.85555555555555551</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="M23">
-        <v>0.15555555555555561</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N23">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O23" s="20">
-        <v>0.17037037037037039</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O23" s="22">
+        <v>0.162962962962963</v>
       </c>
       <c r="P23">
-        <v>128.47407407407411</v>
+        <v>128.11111111111109</v>
       </c>
       <c r="Q23" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="R23" s="20">
-        <v>32.222222222222221</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S23" t="s">
+        <v>79</v>
+      </c>
+      <c r="T23" s="22">
+        <v>57.777777777777771</v>
+      </c>
+      <c r="U23" t="s">
+        <v>39</v>
+      </c>
+      <c r="V23" s="20">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="W23" t="s">
+        <v>49</v>
+      </c>
+      <c r="X23" s="20">
+        <v>74.074074074074076</v>
+      </c>
+      <c r="Y23">
+        <v>34737</v>
+      </c>
+      <c r="Z23">
+        <v>3168</v>
+      </c>
+      <c r="AA23">
+        <v>37905</v>
+      </c>
+      <c r="AB23">
+        <v>2364</v>
+      </c>
+      <c r="AC23">
+        <v>241</v>
+      </c>
+      <c r="AD23">
+        <v>2781</v>
+      </c>
+      <c r="AE23">
         <v>41</v>
       </c>
-      <c r="T23" s="16">
-        <v>58.518518518518512</v>
-      </c>
-      <c r="U23" t="s">
-        <v>36</v>
-      </c>
-      <c r="V23" s="20">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W23" t="s">
-        <v>39</v>
-      </c>
-      <c r="X23" s="20">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y23">
-        <v>34792</v>
-      </c>
-      <c r="Z23">
-        <v>3079</v>
-      </c>
-      <c r="AA23">
-        <v>37871</v>
-      </c>
-      <c r="AB23">
-        <v>2383</v>
-      </c>
-      <c r="AC23">
-        <v>231</v>
-      </c>
-      <c r="AD23">
-        <v>2798</v>
-      </c>
-      <c r="AE23">
-        <v>42</v>
-      </c>
       <c r="AF23">
-        <v>4</v>
-      </c>
-      <c r="AG23" s="20">
-        <v>46</v>
+        <v>3</v>
+      </c>
+      <c r="AG23" s="22">
+        <v>44</v>
       </c>
       <c r="AH23" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI23" s="17">
-        <v>185178113680</v>
+        <v>182982736620</v>
       </c>
       <c r="AJ23" s="17">
-        <v>43808813680</v>
+        <v>41613436620</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24" s="20">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -3285,108 +3286,108 @@
         <v>32</v>
       </c>
       <c r="D24" s="20">
-        <v>129.8896579809053</v>
+        <v>133.5813685998304</v>
       </c>
       <c r="E24" s="20">
-        <v>40727</v>
+        <v>40771</v>
       </c>
       <c r="F24" s="20">
-        <v>3298</v>
+        <v>3348</v>
       </c>
       <c r="G24">
-        <v>128.9148148148148</v>
+        <v>128.81481481481481</v>
       </c>
       <c r="H24">
-        <v>11.37407407407407</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="I24">
-        <v>11.37407407407407</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="J24">
-        <v>10.37407407407407</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K24">
-        <v>0.83333333333333337</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="L24">
-        <v>0.83333333333333337</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="M24">
-        <v>0.17037037037037039</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N24">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O24" s="20">
-        <v>0.17777777777777781</v>
+      <c r="O24" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P24">
-        <v>128.5333333333333</v>
+        <v>128.34814814814811</v>
       </c>
       <c r="Q24" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="R24" s="20">
-        <v>35.185185185185183</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="T24" s="20">
-        <v>54.074074074074083</v>
+        <v>56.666666666666657</v>
       </c>
       <c r="U24" t="s">
-        <v>61</v>
-      </c>
-      <c r="V24" s="7">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="V24" s="22">
+        <v>88.888888888888886</v>
       </c>
       <c r="W24" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="X24">
-        <v>85.18518518518519</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y24">
-        <v>34807</v>
+        <v>34780</v>
       </c>
       <c r="Z24">
-        <v>3071</v>
+        <v>3144</v>
       </c>
       <c r="AA24">
-        <v>37878</v>
+        <v>37924</v>
       </c>
       <c r="AB24">
-        <v>2384</v>
+        <v>2370</v>
       </c>
       <c r="AC24">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="AD24">
-        <v>2801</v>
+        <v>2792</v>
       </c>
       <c r="AE24">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="AF24">
         <v>2</v>
       </c>
-      <c r="AG24" s="20">
-        <v>48</v>
+      <c r="AG24" s="15">
+        <v>55</v>
       </c>
       <c r="AH24" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI24" s="17">
-        <v>183624100260</v>
+        <v>188843045720</v>
       </c>
       <c r="AJ24" s="17">
-        <v>42254800260</v>
+        <v>47473745720</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25" s="20">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -3395,108 +3396,108 @@
         <v>32</v>
       </c>
       <c r="D25" s="20">
-        <v>129.8617456689677</v>
-      </c>
-      <c r="E25" s="20">
-        <v>40740</v>
-      </c>
-      <c r="F25" s="20">
-        <v>3322</v>
+        <v>127.7335127851654</v>
+      </c>
+      <c r="E25" s="16">
+        <v>40773</v>
+      </c>
+      <c r="F25" s="15">
+        <v>3434</v>
       </c>
       <c r="G25">
-        <v>128.78518518518521</v>
+        <v>128.65185185185189</v>
       </c>
       <c r="H25">
-        <v>11.525925925925931</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="I25">
-        <v>11.525925925925931</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="J25">
-        <v>10.388888888888889</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K25">
-        <v>0.77407407407407403</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="L25">
-        <v>0.77407407407407403</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="M25">
-        <v>0.1851851851851852</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N25">
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="O25" s="20">
-        <v>0.18888888888888891</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P25">
-        <v>128.44444444444451</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q25" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R25" s="20">
-        <v>33.703703703703702</v>
+        <v>30.37037037037037</v>
       </c>
       <c r="S25" t="s">
-        <v>70</v>
-      </c>
-      <c r="T25" s="20">
-        <v>54.444444444444443</v>
+        <v>48</v>
+      </c>
+      <c r="T25" s="15">
+        <v>62.962962962962962</v>
       </c>
       <c r="U25" t="s">
-        <v>59</v>
-      </c>
-      <c r="V25" s="19">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="V25" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="W25" t="s">
-        <v>36</v>
-      </c>
-      <c r="X25" s="16">
-        <v>88.888888888888886</v>
+        <v>49</v>
+      </c>
+      <c r="X25" s="22">
+        <v>74.074074074074076</v>
       </c>
       <c r="Y25">
-        <v>34772</v>
+        <v>34736</v>
       </c>
       <c r="Z25">
-        <v>3112</v>
+        <v>3205</v>
       </c>
       <c r="AA25">
-        <v>37884</v>
+        <v>37941</v>
       </c>
       <c r="AB25">
-        <v>2392</v>
+        <v>2374</v>
       </c>
       <c r="AC25">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="AD25">
-        <v>2805</v>
+        <v>2786</v>
       </c>
       <c r="AE25">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF25">
         <v>1</v>
       </c>
-      <c r="AG25" s="15">
-        <v>51</v>
+      <c r="AG25" s="22">
+        <v>46</v>
       </c>
       <c r="AH25" s="17">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI25" s="17">
-        <v>183584640820</v>
+        <v>180682885840</v>
       </c>
       <c r="AJ25" s="17">
-        <v>42215340820</v>
+        <v>39229885840</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -3505,108 +3506,108 @@
         <v>32</v>
       </c>
       <c r="D26" s="20">
-        <v>129.4359784054954</v>
+        <v>128.77770443893019</v>
       </c>
       <c r="E26" s="20">
-        <v>40730</v>
+        <v>40788</v>
       </c>
       <c r="F26">
-        <v>3412</v>
+        <v>3325</v>
       </c>
       <c r="G26">
-        <v>128.65555555555559</v>
+        <v>129.04814814814819</v>
       </c>
       <c r="H26">
-        <v>11.733333333333331</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I26">
-        <v>11.733333333333331</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J26">
-        <v>10.3</v>
+        <v>10.329629629629631</v>
       </c>
       <c r="K26">
-        <v>0.8925925925925926</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L26">
-        <v>0.8925925925925926</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M26">
-        <v>0.15185185185185179</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="N26">
-        <v>1.111111111111111E-2</v>
-      </c>
-      <c r="O26" s="20">
-        <v>0.162962962962963</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O26" s="22">
+        <v>0.18148148148148149</v>
       </c>
       <c r="P26">
-        <v>128.11111111111109</v>
+        <v>128.51111111111109</v>
       </c>
       <c r="Q26" t="s">
-        <v>40</v>
-      </c>
-      <c r="R26" s="20">
-        <v>30.74074074074074</v>
+        <v>72</v>
+      </c>
+      <c r="R26" s="22">
+        <v>33.333333333333329</v>
       </c>
       <c r="S26" t="s">
-        <v>79</v>
-      </c>
-      <c r="T26" s="20">
-        <v>57.777777777777771</v>
+        <v>53</v>
+      </c>
+      <c r="T26" s="22">
+        <v>56.666666666666657</v>
       </c>
       <c r="U26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V26" s="20">
-        <v>85.18518518518519</v>
+        <v>61</v>
+      </c>
+      <c r="V26" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W26" t="s">
+        <v>61</v>
+      </c>
+      <c r="X26" s="15">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="Y26">
+        <v>34843</v>
+      </c>
+      <c r="Z26">
+        <v>3107</v>
+      </c>
+      <c r="AA26">
+        <v>37950</v>
+      </c>
+      <c r="AB26">
+        <v>2376</v>
+      </c>
+      <c r="AC26">
+        <v>217</v>
+      </c>
+      <c r="AD26">
+        <v>2789</v>
+      </c>
+      <c r="AE26">
+        <v>48</v>
+      </c>
+      <c r="AF26">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="22">
         <v>49</v>
       </c>
-      <c r="X26" s="20">
-        <v>74.074074074074076</v>
-      </c>
-      <c r="Y26">
-        <v>34737</v>
-      </c>
-      <c r="Z26">
-        <v>3168</v>
-      </c>
-      <c r="AA26">
-        <v>37905</v>
-      </c>
-      <c r="AB26">
-        <v>2364</v>
-      </c>
-      <c r="AC26">
-        <v>241</v>
-      </c>
-      <c r="AD26">
-        <v>2781</v>
-      </c>
-      <c r="AE26">
-        <v>41</v>
-      </c>
-      <c r="AF26">
-        <v>3</v>
-      </c>
-      <c r="AG26">
-        <v>44</v>
-      </c>
       <c r="AH26" s="17">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI26" s="17">
-        <v>182982736620</v>
+        <v>182159926260</v>
       </c>
       <c r="AJ26" s="17">
-        <v>41613436620</v>
+        <v>40706926260</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -3615,108 +3616,108 @@
         <v>32</v>
       </c>
       <c r="D27">
-        <v>128.77770443893019</v>
+        <v>126.70595083879449</v>
       </c>
       <c r="E27" s="20">
-        <v>40788</v>
+        <v>40752</v>
       </c>
       <c r="F27" s="20">
-        <v>3325</v>
+        <v>3420</v>
       </c>
       <c r="G27">
-        <v>129.04814814814819</v>
+        <v>128.66666666666671</v>
       </c>
       <c r="H27">
-        <v>11.50740740740741</v>
+        <v>11.796296296296299</v>
       </c>
       <c r="I27">
-        <v>11.50740740740741</v>
+        <v>11.796296296296299</v>
       </c>
       <c r="J27">
-        <v>10.329629629629631</v>
+        <v>10.31111111111111</v>
       </c>
       <c r="K27">
-        <v>0.8037037037037037</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L27">
-        <v>0.8037037037037037</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M27">
-        <v>0.17777777777777781</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N27">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O27">
-        <v>0.18148148148148149</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O27" s="22">
+        <v>0.15925925925925929</v>
       </c>
       <c r="P27">
-        <v>128.51111111111109</v>
+        <v>128.1592592592593</v>
       </c>
       <c r="Q27" t="s">
-        <v>72</v>
-      </c>
-      <c r="R27" s="20">
-        <v>33.333333333333329</v>
+        <v>64</v>
+      </c>
+      <c r="R27" s="22">
+        <v>32.222222222222221</v>
       </c>
       <c r="S27" t="s">
-        <v>53</v>
-      </c>
-      <c r="T27" s="20">
-        <v>56.666666666666657</v>
+        <v>65</v>
+      </c>
+      <c r="T27" s="22">
+        <v>56.296296296296298</v>
       </c>
       <c r="U27" t="s">
-        <v>61</v>
-      </c>
-      <c r="V27" s="7">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V27" s="19">
+        <v>96.296296296296291</v>
       </c>
       <c r="W27" t="s">
-        <v>61</v>
-      </c>
-      <c r="X27" s="15">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="X27" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y27">
-        <v>34843</v>
+        <v>34740</v>
       </c>
       <c r="Z27">
-        <v>3107</v>
+        <v>3185</v>
       </c>
       <c r="AA27">
-        <v>37950</v>
+        <v>37925</v>
       </c>
       <c r="AB27">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="AC27">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="AD27">
-        <v>2789</v>
+        <v>2784</v>
       </c>
       <c r="AE27">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AF27">
-        <v>1</v>
-      </c>
-      <c r="AG27">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="AG27" s="22">
+        <v>43</v>
       </c>
       <c r="AH27" s="17">
         <v>141453000000</v>
       </c>
       <c r="AI27" s="17">
-        <v>182159926260</v>
+        <v>179229368640</v>
       </c>
       <c r="AJ27" s="17">
-        <v>40706926260</v>
+        <v>37776368640</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28" s="20">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -3725,31 +3726,31 @@
         <v>32</v>
       </c>
       <c r="D28" s="20">
-        <v>128.3768819680086</v>
-      </c>
-      <c r="E28" s="20">
-        <v>40700</v>
+        <v>126.3735355064933</v>
+      </c>
+      <c r="E28" s="15">
+        <v>40759</v>
       </c>
       <c r="F28" s="20">
-        <v>3369</v>
+        <v>3357</v>
       </c>
       <c r="G28">
-        <v>128.6333333333333</v>
+        <v>128.862962962963</v>
       </c>
       <c r="H28">
-        <v>11.614814814814819</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="I28">
-        <v>11.614814814814819</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="J28">
-        <v>10.33333333333333</v>
+        <v>10.3</v>
       </c>
       <c r="K28">
-        <v>0.8481481481481481</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="L28">
-        <v>0.8481481481481481</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="M28">
         <v>0.1444444444444444</v>
@@ -3761,49 +3762,49 @@
         <v>0.15925925925925929</v>
       </c>
       <c r="P28">
-        <v>128.27037037037039</v>
+        <v>128.39259259259259</v>
       </c>
       <c r="Q28" t="s">
-        <v>89</v>
-      </c>
-      <c r="R28" s="15">
-        <v>29.25925925925926</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="22">
+        <v>34.814814814814817</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
-      </c>
-      <c r="T28" s="16">
-        <v>58.888888888888893</v>
+        <v>34</v>
+      </c>
+      <c r="T28" s="22">
+        <v>55.185185185185183</v>
       </c>
       <c r="U28" t="s">
-        <v>61</v>
-      </c>
-      <c r="V28" s="7">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V28" s="19">
+        <v>96.296296296296291</v>
       </c>
       <c r="W28" t="s">
-        <v>57</v>
-      </c>
-      <c r="X28" s="20">
-        <v>81.481481481481481</v>
+        <v>36</v>
+      </c>
+      <c r="X28" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y28">
-        <v>34731</v>
+        <v>34793</v>
       </c>
       <c r="Z28">
-        <v>3136</v>
+        <v>3142</v>
       </c>
       <c r="AA28">
-        <v>37867</v>
+        <v>37935</v>
       </c>
       <c r="AB28">
-        <v>2389</v>
+        <v>2398</v>
       </c>
       <c r="AC28">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AD28">
-        <v>2790</v>
+        <v>2781</v>
       </c>
       <c r="AE28">
         <v>39</v>
@@ -3815,18 +3816,18 @@
         <v>43</v>
       </c>
       <c r="AH28" s="17">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI28" s="17">
-        <v>181485499400</v>
+        <v>178759157180</v>
       </c>
       <c r="AJ28" s="17">
-        <v>40116199400</v>
+        <v>37306157180</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29" s="20">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -3835,25 +3836,25 @@
         <v>32</v>
       </c>
       <c r="D29" s="20">
-        <v>128.11040201171329</v>
-      </c>
-      <c r="E29" s="20">
-        <v>39530</v>
+        <v>134.21853146981681</v>
+      </c>
+      <c r="E29" s="15">
+        <v>40773</v>
       </c>
       <c r="F29" s="20">
-        <v>3326</v>
+        <v>3382</v>
       </c>
       <c r="G29">
-        <v>124.7592592592593</v>
+        <v>128.77407407407409</v>
       </c>
       <c r="H29">
-        <v>11.50740740740741</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="I29">
-        <v>11.50740740740741</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="J29">
-        <v>9.9851851851851858</v>
+        <v>10.34814814814815</v>
       </c>
       <c r="K29">
         <v>0.79629629629629628</v>
@@ -3862,81 +3863,81 @@
         <v>0.79629629629629628</v>
       </c>
       <c r="M29">
-        <v>0.14074074074074069</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N29">
-        <v>1.4814814814814821E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O29" s="20">
-        <v>0.15555555555555561</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="P29">
-        <v>124.2592592592593</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="Q29" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="R29" s="20">
-        <v>34.444444444444443</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S29" t="s">
-        <v>51</v>
-      </c>
-      <c r="T29" s="20">
-        <v>54.814814814814817</v>
+        <v>43</v>
+      </c>
+      <c r="T29" s="16">
+        <v>58.888888888888893</v>
       </c>
       <c r="U29" t="s">
+        <v>35</v>
+      </c>
+      <c r="V29" s="19">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W29" t="s">
         <v>36</v>
       </c>
-      <c r="V29" s="20">
+      <c r="X29" s="16">
         <v>88.888888888888886</v>
       </c>
-      <c r="W29" t="s">
-        <v>54</v>
-      </c>
-      <c r="X29" s="20">
-        <v>77.777777777777786</v>
-      </c>
       <c r="Y29">
-        <v>33685</v>
+        <v>34769</v>
       </c>
       <c r="Z29">
-        <v>3107</v>
+        <v>3161</v>
       </c>
       <c r="AA29">
-        <v>36792</v>
+        <v>37930</v>
       </c>
       <c r="AB29">
-        <v>2313</v>
+        <v>2383</v>
       </c>
       <c r="AC29">
         <v>215</v>
       </c>
       <c r="AD29">
-        <v>2696</v>
+        <v>2794</v>
       </c>
       <c r="AE29">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AF29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG29">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AH29" s="17">
-        <v>137180580000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI29" s="17">
-        <v>175742592520</v>
+        <v>189856139320</v>
       </c>
       <c r="AJ29" s="17">
-        <v>38562012520</v>
+        <v>48403139320</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30" s="20">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -3945,60 +3946,60 @@
         <v>32</v>
       </c>
       <c r="D30" s="20">
-        <v>127.7335127851654</v>
+        <v>125.45177072243079</v>
       </c>
       <c r="E30" s="16">
-        <v>40773</v>
-      </c>
-      <c r="F30" s="15">
-        <v>3434</v>
+        <v>40718</v>
+      </c>
+      <c r="F30" s="22">
+        <v>3381</v>
       </c>
       <c r="G30">
-        <v>128.65185185185189</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H30">
-        <v>11.87037037037037</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="I30">
-        <v>11.87037037037037</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="J30">
         <v>10.31851851851852</v>
       </c>
       <c r="K30">
-        <v>0.84444444444444444</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L30">
-        <v>0.84444444444444444</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M30">
-        <v>0.16666666666666671</v>
+        <v>0.12962962962962959</v>
       </c>
       <c r="N30">
-        <v>3.7037037037037038E-3</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O30">
-        <v>0.17037037037037039</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="P30">
-        <v>128.10740740740741</v>
+        <v>128.30370370370369</v>
       </c>
       <c r="Q30" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R30">
-        <v>30.37037037037037</v>
+        <v>37.037037037037038</v>
       </c>
       <c r="S30" t="s">
-        <v>48</v>
-      </c>
-      <c r="T30" s="15">
-        <v>62.962962962962962</v>
+        <v>51</v>
+      </c>
+      <c r="T30" s="22">
+        <v>54.814814814814817</v>
       </c>
       <c r="U30" t="s">
         <v>39</v>
       </c>
-      <c r="V30" s="20">
+      <c r="V30" s="22">
         <v>85.18518518518519</v>
       </c>
       <c r="W30" t="s">
@@ -4008,45 +4009,45 @@
         <v>74.074074074074076</v>
       </c>
       <c r="Y30">
-        <v>34736</v>
+        <v>34731</v>
       </c>
       <c r="Z30">
-        <v>3205</v>
+        <v>3161</v>
       </c>
       <c r="AA30">
-        <v>37941</v>
+        <v>37892</v>
       </c>
       <c r="AB30">
-        <v>2374</v>
+        <v>2411</v>
       </c>
       <c r="AC30">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="AD30">
         <v>2786</v>
       </c>
       <c r="AE30">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AF30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG30" s="20">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AH30" s="17">
         <v>141453000000</v>
       </c>
       <c r="AI30" s="17">
-        <v>180682885840</v>
+        <v>177455293240</v>
       </c>
       <c r="AJ30" s="17">
-        <v>39229885840</v>
+        <v>36002293240</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4055,108 +4056,108 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <v>127.4071409280516</v>
+        <v>133.24790789873671</v>
       </c>
       <c r="E31" s="20">
-        <v>40707</v>
+        <v>40755</v>
       </c>
       <c r="F31" s="15">
-        <v>3470</v>
+        <v>3426</v>
       </c>
       <c r="G31">
-        <v>128.28888888888889</v>
+        <v>128.6037037037037</v>
       </c>
       <c r="H31">
-        <v>11.9962962962963</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="I31">
-        <v>11.9962962962963</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="J31">
         <v>10.31851851851852</v>
       </c>
       <c r="K31">
-        <v>0.8481481481481481</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L31">
-        <v>0.8481481481481481</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M31">
-        <v>0.15555555555555561</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N31">
-        <v>7.4074074074074077E-3</v>
+        <v>2.5925925925925929E-2</v>
       </c>
       <c r="O31" s="20">
-        <v>0.162962962962963</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P31">
-        <v>127.8962962962963</v>
+        <v>128.137037037037</v>
       </c>
       <c r="Q31" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="R31" s="20">
-        <v>34.444444444444443</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S31" t="s">
-        <v>56</v>
-      </c>
-      <c r="T31" s="20">
-        <v>57.037037037037038</v>
+        <v>66</v>
+      </c>
+      <c r="T31" s="16">
+        <v>58.148148148148152</v>
       </c>
       <c r="U31" t="s">
-        <v>36</v>
-      </c>
-      <c r="V31" s="20">
-        <v>88.888888888888886</v>
+        <v>61</v>
+      </c>
+      <c r="V31" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W31" t="s">
-        <v>57</v>
-      </c>
-      <c r="X31" s="20">
-        <v>81.481481481481481</v>
+        <v>39</v>
+      </c>
+      <c r="X31" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y31">
-        <v>34638</v>
+        <v>34723</v>
       </c>
       <c r="Z31">
-        <v>3239</v>
+        <v>3200</v>
       </c>
       <c r="AA31">
-        <v>37877</v>
+        <v>37923</v>
       </c>
       <c r="AB31">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="AC31">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="AD31">
         <v>2786</v>
       </c>
       <c r="AE31">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AF31">
-        <v>2</v>
-      </c>
-      <c r="AG31" s="20">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="AG31" s="22">
+        <v>46</v>
       </c>
       <c r="AH31" s="17">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI31" s="17">
-        <v>180114583280</v>
+        <v>188483163160</v>
       </c>
       <c r="AJ31" s="17">
-        <v>38745283280</v>
+        <v>47030163160</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -4165,108 +4166,108 @@
         <v>32</v>
       </c>
       <c r="D32" s="20">
-        <v>126.70595083879449</v>
-      </c>
-      <c r="E32" s="20">
-        <v>40752</v>
-      </c>
-      <c r="F32" s="20">
-        <v>3420</v>
+        <v>123.7648688681046</v>
+      </c>
+      <c r="E32" s="16">
+        <v>40737</v>
+      </c>
+      <c r="F32" s="15">
+        <v>3458</v>
       </c>
       <c r="G32">
-        <v>128.66666666666671</v>
+        <v>128.41851851851851</v>
       </c>
       <c r="H32">
-        <v>11.796296296296299</v>
+        <v>11.988888888888891</v>
       </c>
       <c r="I32">
-        <v>11.796296296296299</v>
+        <v>11.988888888888891</v>
       </c>
       <c r="J32">
-        <v>10.31111111111111</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K32">
-        <v>0.86296296296296293</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L32">
-        <v>0.86296296296296293</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M32">
-        <v>0.15185185185185179</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N32">
         <v>7.4074074074074077E-3</v>
       </c>
       <c r="O32" s="20">
-        <v>0.15925925925925929</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="P32">
-        <v>128.1592592592593</v>
+        <v>128.0185185185185</v>
       </c>
       <c r="Q32" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="R32" s="20">
-        <v>32.222222222222221</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S32" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="T32" s="20">
-        <v>56.296296296296298</v>
+        <v>56.666666666666657</v>
       </c>
       <c r="U32" t="s">
-        <v>35</v>
-      </c>
-      <c r="V32" s="19">
-        <v>96.296296296296291</v>
+        <v>54</v>
+      </c>
+      <c r="V32" s="22">
+        <v>77.777777777777786</v>
       </c>
       <c r="W32" t="s">
-        <v>36</v>
-      </c>
-      <c r="X32" s="16">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="X32" s="22">
+        <v>70.370370370370367</v>
       </c>
       <c r="Y32">
-        <v>34740</v>
+        <v>34673</v>
       </c>
       <c r="Z32">
-        <v>3185</v>
+        <v>3237</v>
       </c>
       <c r="AA32">
-        <v>37925</v>
+        <v>37910</v>
       </c>
       <c r="AB32">
-        <v>2379</v>
+        <v>2403</v>
       </c>
       <c r="AC32">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="AD32">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="AE32">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF32">
         <v>2</v>
       </c>
       <c r="AG32" s="20">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH32" s="17">
         <v>141453000000</v>
       </c>
       <c r="AI32" s="17">
-        <v>179229368640</v>
+        <v>175069119960</v>
       </c>
       <c r="AJ32" s="17">
-        <v>37776368640</v>
+        <v>33616119960</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -4275,108 +4276,108 @@
         <v>32</v>
       </c>
       <c r="D33" s="20">
-        <v>126.6790426209934</v>
+        <v>131.30895267925919</v>
       </c>
       <c r="E33" s="20">
-        <v>40732</v>
+        <v>40738</v>
       </c>
       <c r="F33" s="20">
-        <v>3363</v>
+        <v>3222</v>
       </c>
       <c r="G33">
-        <v>128.76666666666671</v>
+        <v>129.1925925925926</v>
       </c>
       <c r="H33">
-        <v>11.607407407407409</v>
+        <v>11.11851851851852</v>
       </c>
       <c r="I33">
-        <v>11.607407407407409</v>
+        <v>11.11851851851852</v>
       </c>
       <c r="J33">
-        <v>10.31851851851852</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K33">
-        <v>0.84444444444444444</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L33">
-        <v>0.84444444444444444</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M33">
-        <v>0.162962962962963</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N33">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O33" s="20">
-        <v>0.16666666666666671</v>
+      <c r="O33" s="16">
+        <v>0.19259259259259259</v>
       </c>
       <c r="P33">
-        <v>128.2925925925926</v>
+        <v>128.83703703703699</v>
       </c>
       <c r="Q33" t="s">
-        <v>60</v>
-      </c>
-      <c r="R33" s="20">
-        <v>31.851851851851851</v>
+        <v>83</v>
+      </c>
+      <c r="R33" s="15">
+        <v>30</v>
       </c>
       <c r="S33" t="s">
-        <v>56</v>
-      </c>
-      <c r="T33" s="20">
-        <v>57.037037037037038</v>
+        <v>66</v>
+      </c>
+      <c r="T33" s="16">
+        <v>58.148148148148152</v>
       </c>
       <c r="U33" t="s">
-        <v>61</v>
-      </c>
-      <c r="V33" s="7">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="V33" s="22">
+        <v>88.888888888888886</v>
       </c>
       <c r="W33" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="X33" s="20">
-        <v>81.481481481481481</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y33">
-        <v>34767</v>
+        <v>34882</v>
       </c>
       <c r="Z33">
-        <v>3134</v>
+        <v>3002</v>
       </c>
       <c r="AA33">
-        <v>37901</v>
+        <v>37884</v>
       </c>
       <c r="AB33">
-        <v>2378</v>
+        <v>2375</v>
       </c>
       <c r="AC33">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AD33">
-        <v>2786</v>
+        <v>2802</v>
       </c>
       <c r="AE33">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AF33">
         <v>1</v>
       </c>
-      <c r="AG33" s="20">
-        <v>45</v>
+      <c r="AG33" s="15">
+        <v>52</v>
       </c>
       <c r="AH33" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI33" s="17">
-        <v>179085275800</v>
+        <v>185630547240</v>
       </c>
       <c r="AJ33" s="17">
-        <v>37715975800</v>
+        <v>44261247240</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A34" s="20">
-        <v>28</v>
+      <c r="A34" s="13">
+        <v>41</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -4384,109 +4385,109 @@
       <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="20">
-        <v>126.4057725970207</v>
+      <c r="D34" s="16">
+        <v>137.232633421825</v>
       </c>
       <c r="E34" s="20">
-        <v>40733</v>
-      </c>
-      <c r="F34" s="20">
-        <v>3334</v>
+        <v>40738</v>
+      </c>
+      <c r="F34" s="22">
+        <v>3383</v>
       </c>
       <c r="G34">
-        <v>128.72592592592591</v>
+        <v>128.64814814814821</v>
       </c>
       <c r="H34">
-        <v>11.607407407407409</v>
+        <v>11.662962962962959</v>
       </c>
       <c r="I34">
-        <v>11.607407407407409</v>
+        <v>11.662962962962959</v>
       </c>
       <c r="J34">
-        <v>10.35555555555556</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K34">
-        <v>0.73333333333333328</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L34">
-        <v>0.73333333333333328</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M34">
-        <v>0.16666666666666671</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N34">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O34" s="20">
-        <v>0.1740740740740741</v>
+        <v>1.8518518518518521E-2</v>
+      </c>
+      <c r="O34" s="16">
+        <v>0.19259259259259259</v>
       </c>
       <c r="P34">
-        <v>128.4</v>
+        <v>128.22592592592591</v>
       </c>
       <c r="Q34" t="s">
-        <v>73</v>
-      </c>
-      <c r="R34" s="20">
-        <v>34.444444444444443</v>
+        <v>83</v>
+      </c>
+      <c r="R34" s="15">
+        <v>30</v>
       </c>
       <c r="S34" t="s">
-        <v>74</v>
-      </c>
-      <c r="T34" s="20">
-        <v>51.111111111111107</v>
+        <v>85</v>
+      </c>
+      <c r="T34" s="15">
+        <v>64.074074074074076</v>
       </c>
       <c r="U34" t="s">
-        <v>35</v>
-      </c>
-      <c r="V34" s="19">
-        <v>96.296296296296291</v>
+        <v>61</v>
+      </c>
+      <c r="V34" s="7">
+        <v>92.592592592592595</v>
       </c>
       <c r="W34" t="s">
-        <v>54</v>
-      </c>
-      <c r="X34" s="20">
-        <v>77.777777777777786</v>
+        <v>36</v>
+      </c>
+      <c r="X34" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y34">
-        <v>34756</v>
+        <v>34735</v>
       </c>
       <c r="Z34">
-        <v>3134</v>
+        <v>3149</v>
       </c>
       <c r="AA34">
-        <v>37890</v>
+        <v>37884</v>
       </c>
       <c r="AB34">
-        <v>2410</v>
+        <v>2365</v>
       </c>
       <c r="AC34">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="AD34">
-        <v>2796</v>
+        <v>2802</v>
       </c>
       <c r="AE34">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF34">
-        <v>2</v>
-      </c>
-      <c r="AG34" s="20">
-        <v>47</v>
+        <v>5</v>
+      </c>
+      <c r="AG34" s="15">
+        <v>52</v>
       </c>
       <c r="AH34" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI34" s="17">
-        <v>178698955880</v>
-      </c>
-      <c r="AJ34" s="17">
-        <v>37329655880</v>
+        <v>194004813240</v>
+      </c>
+      <c r="AJ34" s="18">
+        <v>52635513240</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35" s="20">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -4495,108 +4496,108 @@
         <v>32</v>
       </c>
       <c r="D35" s="20">
-        <v>126.3735355064933</v>
-      </c>
-      <c r="E35" s="15">
-        <v>40759</v>
+        <v>131.7624941200105</v>
+      </c>
+      <c r="E35" s="22">
+        <v>40738</v>
       </c>
       <c r="F35" s="20">
-        <v>3357</v>
+        <v>3379</v>
       </c>
       <c r="G35">
-        <v>128.862962962963</v>
+        <v>128.5703703703704</v>
       </c>
       <c r="H35">
-        <v>11.63703703703704</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="I35">
-        <v>11.63703703703704</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="J35">
-        <v>10.3</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K35">
-        <v>0.78148148148148144</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="L35">
-        <v>0.78148148148148144</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="M35">
-        <v>0.1444444444444444</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N35">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O35">
-        <v>0.15925925925925929</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O35" s="16">
+        <v>0.19259259259259259</v>
       </c>
       <c r="P35">
-        <v>128.39259259259259</v>
+        <v>128.2222222222222</v>
       </c>
       <c r="Q35" t="s">
-        <v>33</v>
-      </c>
-      <c r="R35" s="20">
-        <v>34.814814814814817</v>
+        <v>71</v>
+      </c>
+      <c r="R35" s="15">
+        <v>31.111111111111111</v>
       </c>
       <c r="S35" t="s">
-        <v>34</v>
-      </c>
-      <c r="T35" s="20">
-        <v>55.185185185185183</v>
+        <v>88</v>
+      </c>
+      <c r="T35" s="16">
+        <v>59.629629629629633</v>
       </c>
       <c r="U35" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35" s="19">
-        <v>96.296296296296291</v>
+        <v>36</v>
+      </c>
+      <c r="V35" s="22">
+        <v>88.888888888888886</v>
       </c>
       <c r="W35" t="s">
-        <v>36</v>
-      </c>
-      <c r="X35" s="16">
-        <v>88.888888888888886</v>
+        <v>39</v>
+      </c>
+      <c r="X35" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y35">
-        <v>34793</v>
+        <v>34714</v>
       </c>
       <c r="Z35">
-        <v>3142</v>
+        <v>3170</v>
       </c>
       <c r="AA35">
-        <v>37935</v>
+        <v>37884</v>
       </c>
       <c r="AB35">
-        <v>2398</v>
+        <v>2387</v>
       </c>
       <c r="AC35">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AD35">
-        <v>2781</v>
+        <v>2802</v>
       </c>
       <c r="AE35">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AF35">
-        <v>4</v>
-      </c>
-      <c r="AG35" s="20">
-        <v>43</v>
+        <v>2</v>
+      </c>
+      <c r="AG35" s="15">
+        <v>52</v>
       </c>
       <c r="AH35" s="17">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI35" s="17">
-        <v>178759157180</v>
+        <v>186271715600</v>
       </c>
       <c r="AJ35" s="17">
-        <v>37306157180</v>
+        <v>44902415600</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A36" s="20">
-        <v>29</v>
+      <c r="A36" s="13">
+        <v>43</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
@@ -4604,109 +4605,109 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="20">
-        <v>126.3272132492698</v>
-      </c>
-      <c r="E36" s="15">
-        <v>40684</v>
-      </c>
-      <c r="F36" s="20">
-        <v>3338</v>
+      <c r="D36" s="16">
+        <v>136.81623945227139</v>
+      </c>
+      <c r="E36" s="22">
+        <v>40738</v>
+      </c>
+      <c r="F36" s="15">
+        <v>3461</v>
       </c>
       <c r="G36">
-        <v>128.62222222222221</v>
+        <v>128.33333333333329</v>
       </c>
       <c r="H36">
-        <v>11.514814814814811</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="I36">
-        <v>11.514814814814811</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="J36">
-        <v>10.392592592592591</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K36">
-        <v>0.83333333333333337</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L36">
-        <v>0.83333333333333337</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M36">
-        <v>0.13703703703703701</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N36">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O36" s="20">
-        <v>0.15185185185185179</v>
+        <v>1.8518518518518521E-2</v>
+      </c>
+      <c r="O36" s="16">
+        <v>0.19259259259259259</v>
       </c>
       <c r="P36">
-        <v>128.38518518518521</v>
+        <v>127.89259259259261</v>
       </c>
       <c r="Q36" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="R36" s="20">
-        <v>32.592592592592602</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S36" t="s">
-        <v>45</v>
-      </c>
-      <c r="T36" s="20">
-        <v>53.333333333333343</v>
+        <v>84</v>
+      </c>
+      <c r="T36" s="15">
+        <v>62.592592592592588</v>
       </c>
       <c r="U36" t="s">
-        <v>36</v>
-      </c>
-      <c r="V36" s="20">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V36" s="19">
+        <v>96.296296296296291</v>
       </c>
       <c r="W36" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="X36" s="20">
-        <v>70.370370370370367</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y36">
-        <v>34728</v>
+        <v>34650</v>
       </c>
       <c r="Z36">
-        <v>3109</v>
+        <v>3234</v>
       </c>
       <c r="AA36">
-        <v>37837</v>
+        <v>37884</v>
       </c>
       <c r="AB36">
-        <v>2417</v>
+        <v>2372</v>
       </c>
       <c r="AC36">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AD36">
-        <v>2806</v>
+        <v>2802</v>
       </c>
       <c r="AE36">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="AF36">
-        <v>4</v>
-      </c>
-      <c r="AG36" s="20">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="AG36" s="15">
+        <v>52</v>
       </c>
       <c r="AH36" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI36" s="17">
-        <v>178587897080</v>
+        <v>193416160000</v>
       </c>
       <c r="AJ36" s="17">
-        <v>37218597080</v>
+        <v>52046860000</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37" s="20">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -4715,108 +4716,108 @@
         <v>32</v>
       </c>
       <c r="D37" s="20">
-        <v>125.45177072243079</v>
-      </c>
-      <c r="E37" s="16">
-        <v>40718</v>
+        <v>134.43323094901089</v>
+      </c>
+      <c r="E37" s="22">
+        <v>40738</v>
       </c>
       <c r="F37" s="20">
-        <v>3381</v>
+        <v>3283</v>
       </c>
       <c r="G37">
-        <v>128.6333333333333</v>
+        <v>128.9296296296296</v>
       </c>
       <c r="H37">
-        <v>11.707407407407411</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="I37">
-        <v>11.707407407407411</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="J37">
-        <v>10.31851851851852</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K37">
-        <v>0.79629629629629628</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="L37">
-        <v>0.79629629629629628</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="M37">
-        <v>0.12962962962962959</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N37">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O37" s="20">
-        <v>0.14814814814814811</v>
+      <c r="O37" s="16">
+        <v>0.19259259259259259</v>
       </c>
       <c r="P37">
-        <v>128.30370370370369</v>
+        <v>128.61111111111109</v>
       </c>
       <c r="Q37" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R37">
-        <v>37.037037037037038</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S37" t="s">
-        <v>51</v>
-      </c>
-      <c r="T37" s="20">
-        <v>54.814814814814817</v>
+        <v>43</v>
+      </c>
+      <c r="T37" s="16">
+        <v>58.888888888888893</v>
       </c>
       <c r="U37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="V37" s="20">
-        <v>85.18518518518519</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="W37" t="s">
-        <v>49</v>
-      </c>
-      <c r="X37" s="20">
-        <v>74.074074074074076</v>
+        <v>36</v>
+      </c>
+      <c r="X37" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y37">
-        <v>34731</v>
+        <v>34811</v>
       </c>
       <c r="Z37">
-        <v>3161</v>
+        <v>3073</v>
       </c>
       <c r="AA37">
-        <v>37892</v>
+        <v>37884</v>
       </c>
       <c r="AB37">
-        <v>2411</v>
+        <v>2389</v>
       </c>
       <c r="AC37">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="AD37">
-        <v>2786</v>
+        <v>2802</v>
       </c>
       <c r="AE37">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="AF37">
         <v>5</v>
       </c>
-      <c r="AG37" s="20">
-        <v>40</v>
+      <c r="AG37" s="15">
+        <v>52</v>
       </c>
       <c r="AH37" s="17">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI37" s="17">
-        <v>177455293240</v>
+        <v>190047317560</v>
       </c>
       <c r="AJ37" s="17">
-        <v>36002293240</v>
+        <v>48678017560</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A38" s="20">
-        <v>39</v>
+      <c r="A38" s="13">
+        <v>45</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -4824,109 +4825,109 @@
       <c r="C38" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="20">
-        <v>123.7648688681046</v>
-      </c>
-      <c r="E38" s="16">
-        <v>40737</v>
-      </c>
-      <c r="F38" s="15">
-        <v>3458</v>
+      <c r="D38" s="15">
+        <v>139.06906642389831</v>
+      </c>
+      <c r="E38" s="22">
+        <v>40771</v>
+      </c>
+      <c r="F38" s="22">
+        <v>3393</v>
       </c>
       <c r="G38">
-        <v>128.41851851851851</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="H38">
-        <v>11.988888888888891</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="I38">
-        <v>11.988888888888891</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="J38">
-        <v>10.31851851851852</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K38">
-        <v>0.81111111111111112</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="L38">
-        <v>0.81111111111111112</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="M38">
-        <v>0.1444444444444444</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N38">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O38" s="20">
-        <v>0.15185185185185179</v>
+        <v>2.222222222222222E-2</v>
+      </c>
+      <c r="O38" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P38">
-        <v>128.0185185185185</v>
+        <v>128.17037037037039</v>
       </c>
       <c r="Q38" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="R38" s="20">
-        <v>32.962962962962962</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S38" t="s">
-        <v>53</v>
-      </c>
-      <c r="T38" s="20">
-        <v>56.666666666666657</v>
+        <v>66</v>
+      </c>
+      <c r="T38" s="16">
+        <v>58.148148148148152</v>
       </c>
       <c r="U38" t="s">
-        <v>54</v>
-      </c>
-      <c r="V38" s="20">
-        <v>77.777777777777786</v>
+        <v>59</v>
+      </c>
+      <c r="V38" s="15">
+        <v>100</v>
       </c>
       <c r="W38" t="s">
-        <v>46</v>
-      </c>
-      <c r="X38" s="20">
-        <v>70.370370370370367</v>
+        <v>61</v>
+      </c>
+      <c r="X38" s="15">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y38">
-        <v>34673</v>
+        <v>34749</v>
       </c>
       <c r="Z38">
-        <v>3237</v>
+        <v>3175</v>
       </c>
       <c r="AA38">
-        <v>37910</v>
+        <v>37924</v>
       </c>
       <c r="AB38">
-        <v>2403</v>
+        <v>2360</v>
       </c>
       <c r="AC38">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AD38">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="AE38">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="AF38">
-        <v>2</v>
-      </c>
-      <c r="AG38" s="20">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="AG38" s="15">
+        <v>55</v>
       </c>
       <c r="AH38" s="17">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI38" s="17">
-        <v>175069119960</v>
-      </c>
-      <c r="AJ38" s="17">
-        <v>33616119960</v>
+        <v>196600965720</v>
+      </c>
+      <c r="AJ38" s="18">
+        <v>55231665720</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A39" s="20">
-        <v>23</v>
+      <c r="A39" s="13">
+        <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
@@ -4934,109 +4935,109 @@
       <c r="C39" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="20">
-        <v>122.0712722776445</v>
+      <c r="D39" s="15">
+        <v>139.09968645243339</v>
       </c>
       <c r="E39" s="20">
-        <v>40670</v>
+        <v>40771</v>
       </c>
       <c r="F39" s="20">
-        <v>3413</v>
+        <v>3410</v>
       </c>
       <c r="G39">
-        <v>128.37407407407409</v>
+        <v>128.7074074074074</v>
       </c>
       <c r="H39">
-        <v>11.792592592592589</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="I39">
-        <v>11.792592592592589</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="J39">
-        <v>10.32592592592593</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K39">
-        <v>0.83703703703703702</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L39">
-        <v>0.83703703703703702</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M39">
-        <v>0.12592592592592591</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N39">
-        <v>1.111111111111111E-2</v>
-      </c>
-      <c r="O39" s="20">
-        <v>0.13703703703703701</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O39" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P39">
         <v>128.10740740740741</v>
       </c>
       <c r="Q39" t="s">
-        <v>42</v>
-      </c>
-      <c r="R39" s="20">
-        <v>33.703703703703702</v>
+        <v>83</v>
+      </c>
+      <c r="R39" s="15">
+        <v>30</v>
       </c>
       <c r="S39" t="s">
-        <v>41</v>
-      </c>
-      <c r="T39" s="16">
-        <v>58.518518518518512</v>
+        <v>84</v>
+      </c>
+      <c r="T39" s="15">
+        <v>62.592592592592588</v>
       </c>
       <c r="U39" t="s">
-        <v>36</v>
-      </c>
-      <c r="V39" s="20">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V39" s="19">
+        <v>96.296296296296291</v>
       </c>
       <c r="W39" t="s">
-        <v>78</v>
-      </c>
-      <c r="X39" s="20">
-        <v>66.666666666666657</v>
+        <v>35</v>
+      </c>
+      <c r="X39" s="15">
+        <v>96.296296296296291</v>
       </c>
       <c r="Y39">
-        <v>34661</v>
+        <v>34751</v>
       </c>
       <c r="Z39">
-        <v>3184</v>
+        <v>3173</v>
       </c>
       <c r="AA39">
-        <v>37845</v>
+        <v>37924</v>
       </c>
       <c r="AB39">
-        <v>2414</v>
+        <v>2339</v>
       </c>
       <c r="AC39">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AD39">
-        <v>2788</v>
+        <v>2792</v>
       </c>
       <c r="AE39">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="AF39">
-        <v>3</v>
-      </c>
-      <c r="AG39" s="20">
-        <v>37</v>
+        <v>4</v>
+      </c>
+      <c r="AG39" s="15">
+        <v>55</v>
       </c>
       <c r="AH39" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI39" s="17">
-        <v>172571303120</v>
-      </c>
-      <c r="AJ39" s="17">
-        <v>31202003120</v>
+        <v>196644253040</v>
+      </c>
+      <c r="AJ39" s="18">
+        <v>55274953040</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
@@ -5045,108 +5046,108 @@
         <v>32</v>
       </c>
       <c r="D40">
-        <v>121.16360259264211</v>
+        <v>135.74983728433261</v>
       </c>
       <c r="E40" s="20">
-        <v>40700</v>
+        <v>40780</v>
       </c>
       <c r="F40" s="20">
-        <v>3338</v>
+        <v>3318</v>
       </c>
       <c r="G40">
-        <v>128.67037037037039</v>
+        <v>128.9851851851852</v>
       </c>
       <c r="H40">
-        <v>11.6</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="I40">
-        <v>11.6</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="J40">
         <v>10.32592592592593</v>
       </c>
       <c r="K40">
-        <v>0.75185185185185188</v>
+        <v>0.73703703703703705</v>
       </c>
       <c r="L40">
-        <v>0.75185185185185188</v>
+        <v>0.73703703703703705</v>
       </c>
       <c r="M40">
-        <v>0.1333333333333333</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N40">
-        <v>1.111111111111111E-2</v>
-      </c>
-      <c r="O40" s="20">
-        <v>0.1444444444444444</v>
+        <v>2.222222222222222E-2</v>
+      </c>
+      <c r="O40" s="16">
+        <v>0.1962962962962963</v>
       </c>
       <c r="P40">
-        <v>128.38518518518521</v>
+        <v>128.44444444444451</v>
       </c>
       <c r="Q40" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="R40" s="20">
-        <v>37.407407407407398</v>
+        <v>37.777777777777779</v>
       </c>
       <c r="S40" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="T40" s="20">
-        <v>52.962962962962969</v>
+        <v>51.851851851851848</v>
       </c>
       <c r="U40" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="V40" s="20">
-        <v>85.18518518518519</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="W40" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="X40">
-        <v>74.074074074074076</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="Y40">
-        <v>34741</v>
+        <v>34826</v>
       </c>
       <c r="Z40">
-        <v>3132</v>
+        <v>3113</v>
       </c>
       <c r="AA40">
-        <v>37873</v>
+        <v>37939</v>
       </c>
       <c r="AB40">
-        <v>2429</v>
+        <v>2377</v>
       </c>
       <c r="AC40">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AD40">
         <v>2788</v>
       </c>
       <c r="AE40">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AF40">
-        <v>3</v>
-      </c>
-      <c r="AG40" s="20">
-        <v>39</v>
+        <v>6</v>
+      </c>
+      <c r="AG40" s="15">
+        <v>53</v>
       </c>
       <c r="AH40" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI40" s="17">
-        <v>171288136840</v>
+        <v>191908594720</v>
       </c>
       <c r="AJ40" s="17">
-        <v>29918836840</v>
+        <v>50539294720</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>31</v>
@@ -5155,108 +5156,108 @@
         <v>32</v>
       </c>
       <c r="D41">
-        <v>120.5562728400013</v>
+        <v>135.08681222868049</v>
       </c>
       <c r="E41" s="20">
-        <v>40635</v>
-      </c>
-      <c r="F41" s="20">
-        <v>3414</v>
+        <v>40780</v>
+      </c>
+      <c r="F41" s="15">
+        <v>3454</v>
       </c>
       <c r="G41">
-        <v>128.07777777777781</v>
+        <v>128.58148148148149</v>
       </c>
       <c r="H41">
-        <v>11.851851851851849</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="I41">
-        <v>11.851851851851849</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="J41">
-        <v>10.425925925925929</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K41">
-        <v>0.78888888888888886</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="L41">
-        <v>0.78888888888888886</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="M41">
-        <v>0.14074074074074069</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N41">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O41">
-        <v>0.1444444444444444</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O41" s="16">
+        <v>0.1962962962962963</v>
       </c>
       <c r="P41">
-        <v>128.1037037037037</v>
+        <v>127.99629629629629</v>
       </c>
       <c r="Q41" t="s">
-        <v>77</v>
-      </c>
-      <c r="R41" s="20">
-        <v>35.555555555555557</v>
+        <v>87</v>
+      </c>
+      <c r="R41" s="15">
+        <v>25.92592592592592</v>
       </c>
       <c r="S41" t="s">
-        <v>56</v>
-      </c>
-      <c r="T41" s="20">
-        <v>57.037037037037038</v>
+        <v>85</v>
+      </c>
+      <c r="T41" s="15">
+        <v>64.074074074074076</v>
       </c>
       <c r="U41" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" s="20">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W41" t="s">
         <v>57</v>
       </c>
-      <c r="V41" s="20">
+      <c r="X41" s="20">
         <v>81.481481481481481</v>
       </c>
-      <c r="W41" t="s">
-        <v>46</v>
-      </c>
-      <c r="X41" s="20">
-        <v>70.370370370370367</v>
-      </c>
       <c r="Y41">
-        <v>34581</v>
+        <v>34717</v>
       </c>
       <c r="Z41">
-        <v>3200</v>
+        <v>3222</v>
       </c>
       <c r="AA41">
-        <v>37781</v>
+        <v>37939</v>
       </c>
       <c r="AB41">
-        <v>2446</v>
+        <v>2346</v>
       </c>
       <c r="AC41">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="AD41">
-        <v>2815</v>
+        <v>2788</v>
       </c>
       <c r="AE41">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="AF41">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="20">
-        <v>39</v>
+        <v>2</v>
+      </c>
+      <c r="AG41" s="15">
+        <v>53</v>
       </c>
       <c r="AH41" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI41" s="17">
-        <v>170429559020</v>
+        <v>190971280840</v>
       </c>
       <c r="AJ41" s="17">
-        <v>29060259020</v>
+        <v>49601980840</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A42" s="20">
-        <v>21</v>
+      <c r="A42" s="13">
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
@@ -5264,109 +5265,109 @@
       <c r="C42" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="20">
-        <v>120.4952906182601</v>
-      </c>
-      <c r="E42" s="20">
-        <v>40686</v>
+      <c r="D42" s="16">
+        <v>136.1734986025962</v>
+      </c>
+      <c r="E42" s="15">
+        <v>40801</v>
       </c>
       <c r="F42" s="20">
-        <v>3412</v>
+        <v>3370</v>
       </c>
       <c r="G42">
-        <v>128.3666666666667</v>
+        <v>128.88888888888891</v>
       </c>
       <c r="H42">
-        <v>11.885185185185181</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="I42">
-        <v>11.885185185185181</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="J42">
-        <v>10.3037037037037</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K42">
-        <v>0.73333333333333328</v>
+        <v>0.76296296296296295</v>
       </c>
       <c r="L42">
-        <v>0.73333333333333328</v>
+        <v>0.76296296296296295</v>
       </c>
       <c r="M42">
-        <v>0.1148148148148148</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N42">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O42" s="20">
-        <v>0.1333333333333333</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O42" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P42">
-        <v>128.11111111111109</v>
+        <v>128.28148148148151</v>
       </c>
       <c r="Q42" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="R42" s="20">
-        <v>41.481481481481481</v>
+        <v>34.074074074074083</v>
       </c>
       <c r="S42" t="s">
-        <v>68</v>
-      </c>
-      <c r="T42" s="20">
-        <v>51.851851851851848</v>
+        <v>38</v>
+      </c>
+      <c r="T42" s="22">
+        <v>55.925925925925917</v>
       </c>
       <c r="U42" t="s">
-        <v>49</v>
-      </c>
-      <c r="V42" s="20">
-        <v>74.074074074074076</v>
+        <v>39</v>
+      </c>
+      <c r="V42" s="22">
+        <v>85.18518518518519</v>
       </c>
       <c r="W42" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="X42">
-        <v>59.259259259259252</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y42">
-        <v>34659</v>
+        <v>34800</v>
       </c>
       <c r="Z42">
-        <v>3209</v>
+        <v>3160</v>
       </c>
       <c r="AA42">
-        <v>37868</v>
+        <v>37960</v>
       </c>
       <c r="AB42">
-        <v>2440</v>
+        <v>2360</v>
       </c>
       <c r="AC42">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AD42">
-        <v>2782</v>
+        <v>2786</v>
       </c>
       <c r="AE42">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="AF42">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="20">
-        <v>36</v>
+        <v>4</v>
+      </c>
+      <c r="AG42" s="15">
+        <v>55</v>
       </c>
       <c r="AH42" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI42" s="17">
-        <v>170343348880</v>
-      </c>
-      <c r="AJ42" s="17">
-        <v>28974048880</v>
+        <v>192507521760</v>
+      </c>
+      <c r="AJ42" s="18">
+        <v>51138221760</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A43" s="20">
-        <v>24</v>
+      <c r="A43" s="13">
+        <v>50</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
@@ -5374,50 +5375,50 @@
       <c r="C43" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="20">
-        <v>119.321995058333</v>
-      </c>
-      <c r="E43" s="20">
-        <v>40671</v>
-      </c>
-      <c r="F43" s="20">
-        <v>3419</v>
+      <c r="D43" s="16">
+        <v>138.5605110020351</v>
+      </c>
+      <c r="E43" s="15">
+        <v>40801</v>
+      </c>
+      <c r="F43" s="15">
+        <v>3423</v>
       </c>
       <c r="G43">
-        <v>128.31851851851849</v>
+        <v>128.737037037037</v>
       </c>
       <c r="H43">
-        <v>11.84074074074074</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="I43">
-        <v>11.84074074074074</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="J43">
-        <v>10.33333333333333</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K43">
-        <v>0.82222222222222219</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L43">
-        <v>0.82222222222222219</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M43">
-        <v>0.14074074074074069</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" s="20">
-        <v>0.14074074074074069</v>
+        <v>1.8518518518518521E-2</v>
+      </c>
+      <c r="O43" s="15">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P43">
-        <v>128.0851851851852</v>
+        <v>128.0740740740741</v>
       </c>
       <c r="Q43" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R43" s="20">
-        <v>31.851851851851851</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S43" t="s">
         <v>41</v>
@@ -5426,57 +5427,57 @@
         <v>58.518518518518512</v>
       </c>
       <c r="U43" t="s">
-        <v>61</v>
-      </c>
-      <c r="V43" s="7">
-        <v>92.592592592592595</v>
+        <v>35</v>
+      </c>
+      <c r="V43" s="19">
+        <v>96.296296296296291</v>
       </c>
       <c r="W43" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="X43" s="20">
-        <v>81.481481481481481</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y43">
-        <v>34646</v>
+        <v>34759</v>
       </c>
       <c r="Z43">
-        <v>3197</v>
+        <v>3201</v>
       </c>
       <c r="AA43">
-        <v>37843</v>
+        <v>37960</v>
       </c>
       <c r="AB43">
-        <v>2416</v>
+        <v>2349</v>
       </c>
       <c r="AC43">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AD43">
-        <v>2790</v>
+        <v>2786</v>
       </c>
       <c r="AE43">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="20">
-        <v>38</v>
+        <v>5</v>
+      </c>
+      <c r="AG43" s="15">
+        <v>55</v>
       </c>
       <c r="AH43" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI43" s="17">
-        <v>168684669160</v>
-      </c>
-      <c r="AJ43" s="17">
-        <v>27315369160</v>
+        <v>195882024480</v>
+      </c>
+      <c r="AJ43" s="18">
+        <v>54512724480</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -5485,103 +5486,103 @@
         <v>32</v>
       </c>
       <c r="D44">
-        <v>113.2579520588982</v>
+        <v>131.2077959358927</v>
       </c>
       <c r="E44" s="20">
-        <v>40645</v>
+        <v>40728</v>
       </c>
       <c r="F44" s="20">
-        <v>3337</v>
+        <v>3325</v>
       </c>
       <c r="G44">
-        <v>128.43333333333331</v>
+        <v>128.81481481481481</v>
       </c>
       <c r="H44">
-        <v>11.62592592592593</v>
+        <v>11.5037037037037</v>
       </c>
       <c r="I44">
-        <v>11.62592592592593</v>
+        <v>11.5037037037037</v>
       </c>
       <c r="J44">
         <v>10.351851851851849</v>
       </c>
       <c r="K44">
-        <v>0.73333333333333328</v>
+        <v>0.79259259259259263</v>
       </c>
       <c r="L44">
-        <v>0.73333333333333328</v>
+        <v>0.79259259259259263</v>
       </c>
       <c r="M44">
-        <v>0.12592592592592591</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O44">
-        <v>0.12592592592592591</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="P44">
-        <v>128.38888888888891</v>
+        <v>128.43333333333331</v>
       </c>
       <c r="Q44" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="R44" s="20">
-        <v>37.037037037037038</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S44" t="s">
-        <v>70</v>
-      </c>
-      <c r="T44" s="20">
-        <v>54.444444444444443</v>
+        <v>38</v>
+      </c>
+      <c r="T44" s="16">
+        <v>55.925925925925917</v>
       </c>
       <c r="U44" t="s">
+        <v>36</v>
+      </c>
+      <c r="V44" s="20">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W44" t="s">
         <v>39</v>
       </c>
-      <c r="V44" s="20">
+      <c r="X44" s="20">
         <v>85.18518518518519</v>
       </c>
-      <c r="W44" t="s">
-        <v>49</v>
-      </c>
-      <c r="X44" s="20">
-        <v>74.074074074074076</v>
-      </c>
       <c r="Y44">
-        <v>34677</v>
+        <v>34780</v>
       </c>
       <c r="Z44">
-        <v>3139</v>
+        <v>3106</v>
       </c>
       <c r="AA44">
-        <v>37816</v>
+        <v>37886</v>
       </c>
       <c r="AB44">
-        <v>2461</v>
+        <v>2393</v>
       </c>
       <c r="AC44">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="AD44">
         <v>2795</v>
       </c>
       <c r="AE44">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG44" s="20">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AH44" s="17">
         <v>141369300000</v>
       </c>
       <c r="AI44" s="17">
-        <v>160111974020</v>
+        <v>185487542660</v>
       </c>
       <c r="AJ44" s="17">
-        <v>18742674020</v>
+        <v>44118242660</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.35">
@@ -5662,7 +5663,7 @@
   </sheetData>
   <autoFilter ref="A2:AM2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AM53">
-      <sortCondition descending="1" ref="D2"/>
+      <sortCondition ref="A2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2280C5B8-FC77-43CE-8509-94BC28D90651}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8CE7B9-0C72-4646-8480-CD9CBC9AC53E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="2820" windowWidth="25410" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7380" yWindow="2820" windowWidth="22860" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -136,175 +136,175 @@
     <t>270</t>
   </si>
   <si>
+    <t>85/270</t>
+  </si>
+  <si>
+    <t>154/270</t>
+  </si>
+  <si>
+    <t>24/27</t>
+  </si>
+  <si>
+    <t>22/27</t>
+  </si>
+  <si>
+    <t>100/270</t>
+  </si>
+  <si>
+    <t>147/270</t>
+  </si>
+  <si>
+    <t>23/27</t>
+  </si>
+  <si>
+    <t>20/27</t>
+  </si>
+  <si>
+    <t>90/270</t>
+  </si>
+  <si>
+    <t>162/270</t>
+  </si>
+  <si>
+    <t>25/27</t>
+  </si>
+  <si>
+    <t>95/270</t>
+  </si>
+  <si>
+    <t>153/270</t>
+  </si>
+  <si>
+    <t>21/27</t>
+  </si>
+  <si>
+    <t>93/270</t>
+  </si>
+  <si>
+    <t>66/270</t>
+  </si>
+  <si>
+    <t>167/270</t>
+  </si>
+  <si>
+    <t>92/270</t>
+  </si>
+  <si>
+    <t>155/270</t>
+  </si>
+  <si>
+    <t>79/270</t>
+  </si>
+  <si>
+    <t>159/270</t>
+  </si>
+  <si>
+    <t>87/270</t>
+  </si>
+  <si>
+    <t>158/270</t>
+  </si>
+  <si>
+    <t>101/270</t>
+  </si>
+  <si>
+    <t>143/270</t>
+  </si>
+  <si>
+    <t>91/270</t>
+  </si>
+  <si>
+    <t>27/27</t>
+  </si>
+  <si>
+    <t>26/27</t>
+  </si>
+  <si>
+    <t>112/270</t>
+  </si>
+  <si>
+    <t>140/270</t>
+  </si>
+  <si>
+    <t>16/27</t>
+  </si>
+  <si>
+    <t>96/270</t>
+  </si>
+  <si>
+    <t>19/27</t>
+  </si>
+  <si>
+    <t>18/27</t>
+  </si>
+  <si>
+    <t>86/270</t>
+  </si>
+  <si>
+    <t>146/270</t>
+  </si>
+  <si>
+    <t>138/270</t>
+  </si>
+  <si>
+    <t>88/270</t>
+  </si>
+  <si>
+    <t>144/270</t>
+  </si>
+  <si>
+    <t>83/270</t>
+  </si>
+  <si>
+    <t>156/270</t>
+  </si>
+  <si>
+    <t>84/270</t>
+  </si>
+  <si>
+    <t>82/270</t>
+  </si>
+  <si>
+    <t>170/270</t>
+  </si>
+  <si>
+    <t>152/270</t>
+  </si>
+  <si>
     <t>94/270</t>
   </si>
   <si>
     <t>149/270</t>
   </si>
   <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>24/27</t>
-  </si>
-  <si>
-    <t>92/270</t>
+    <t>148/270</t>
+  </si>
+  <si>
+    <t>89/270</t>
+  </si>
+  <si>
+    <t>157/270</t>
+  </si>
+  <si>
+    <t>81/270</t>
+  </si>
+  <si>
+    <t>173/270</t>
+  </si>
+  <si>
+    <t>161/270</t>
+  </si>
+  <si>
+    <t>169/270</t>
+  </si>
+  <si>
+    <t>102/270</t>
+  </si>
+  <si>
+    <t>70/270</t>
   </si>
   <si>
     <t>151/270</t>
-  </si>
-  <si>
-    <t>23/27</t>
-  </si>
-  <si>
-    <t>83/270</t>
-  </si>
-  <si>
-    <t>158/270</t>
-  </si>
-  <si>
-    <t>91/270</t>
-  </si>
-  <si>
-    <t>159/270</t>
-  </si>
-  <si>
-    <t>88/270</t>
-  </si>
-  <si>
-    <t>144/270</t>
-  </si>
-  <si>
-    <t>19/27</t>
-  </si>
-  <si>
-    <t>82/270</t>
-  </si>
-  <si>
-    <t>170/270</t>
-  </si>
-  <si>
-    <t>20/27</t>
-  </si>
-  <si>
-    <t>100/270</t>
-  </si>
-  <si>
-    <t>148/270</t>
-  </si>
-  <si>
-    <t>89/270</t>
-  </si>
-  <si>
-    <t>153/270</t>
-  </si>
-  <si>
-    <t>21/27</t>
-  </si>
-  <si>
-    <t>85/270</t>
-  </si>
-  <si>
-    <t>154/270</t>
-  </si>
-  <si>
-    <t>22/27</t>
-  </si>
-  <si>
-    <t>155/270</t>
-  </si>
-  <si>
-    <t>27/27</t>
-  </si>
-  <si>
-    <t>86/270</t>
-  </si>
-  <si>
-    <t>25/27</t>
-  </si>
-  <si>
-    <t>95/270</t>
-  </si>
-  <si>
-    <t>146/270</t>
-  </si>
-  <si>
-    <t>87/270</t>
-  </si>
-  <si>
-    <t>152/270</t>
-  </si>
-  <si>
-    <t>157/270</t>
-  </si>
-  <si>
-    <t>112/270</t>
-  </si>
-  <si>
-    <t>140/270</t>
-  </si>
-  <si>
-    <t>16/27</t>
-  </si>
-  <si>
-    <t>147/270</t>
-  </si>
-  <si>
-    <t>84/270</t>
-  </si>
-  <si>
-    <t>90/270</t>
-  </si>
-  <si>
-    <t>93/270</t>
-  </si>
-  <si>
-    <t>138/270</t>
-  </si>
-  <si>
-    <t>66/270</t>
-  </si>
-  <si>
-    <t>167/270</t>
-  </si>
-  <si>
-    <t>96/270</t>
-  </si>
-  <si>
-    <t>18/27</t>
-  </si>
-  <si>
-    <t>156/270</t>
-  </si>
-  <si>
-    <t>162/270</t>
-  </si>
-  <si>
-    <t>101/270</t>
-  </si>
-  <si>
-    <t>143/270</t>
-  </si>
-  <si>
-    <t>81/270</t>
-  </si>
-  <si>
-    <t>169/270</t>
-  </si>
-  <si>
-    <t>173/270</t>
-  </si>
-  <si>
-    <t>102/270</t>
-  </si>
-  <si>
-    <t>70/270</t>
-  </si>
-  <si>
-    <t>161/270</t>
-  </si>
-  <si>
-    <t>79/270</t>
   </si>
   <si>
     <t>100-350</t>
@@ -460,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -507,7 +507,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -827,33 +826,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Y1" s="23" t="s">
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Y1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="26" t="s">
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="25" t="s">
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -981,7 +980,7 @@
       <c r="E3" s="16">
         <v>40780</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3">
         <v>3352</v>
       </c>
       <c r="G3">
@@ -1015,27 +1014,27 @@
         <v>128.33333333333329</v>
       </c>
       <c r="Q3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="22">
+        <v>33</v>
+      </c>
+      <c r="R3">
         <v>31.481481481481481</v>
       </c>
       <c r="S3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T3" s="22">
+        <v>34</v>
+      </c>
+      <c r="T3">
         <v>57.037037037037038</v>
       </c>
       <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W3" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="22">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W3" t="s">
-        <v>57</v>
-      </c>
-      <c r="X3" s="22">
+      <c r="X3">
         <v>81.481481481481481</v>
       </c>
       <c r="Y3">
@@ -1076,7 +1075,7 @@
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A4" s="22">
+      <c r="A4">
         <v>11</v>
       </c>
       <c r="B4" t="s">
@@ -1085,13 +1084,13 @@
       <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4">
         <v>113.2579520588982</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4">
         <v>40645</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4">
         <v>3337</v>
       </c>
       <c r="G4">
@@ -1118,34 +1117,34 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="22">
+      <c r="O4">
         <v>0.12592592592592591</v>
       </c>
       <c r="P4">
         <v>128.38888888888891</v>
       </c>
       <c r="Q4" t="s">
-        <v>50</v>
-      </c>
-      <c r="R4" s="22">
+        <v>37</v>
+      </c>
+      <c r="R4">
         <v>37.037037037037038</v>
       </c>
       <c r="S4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="22">
+        <v>38</v>
+      </c>
+      <c r="T4">
         <v>54.444444444444443</v>
       </c>
       <c r="U4" t="s">
         <v>39</v>
       </c>
-      <c r="V4" s="22">
+      <c r="V4">
         <v>85.18518518518519</v>
       </c>
       <c r="W4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" s="22">
+        <v>40</v>
+      </c>
+      <c r="X4">
         <v>74.074074074074076</v>
       </c>
       <c r="Y4">
@@ -1172,7 +1171,7 @@
       <c r="AF4">
         <v>0</v>
       </c>
-      <c r="AG4" s="22">
+      <c r="AG4">
         <v>34</v>
       </c>
       <c r="AH4" s="17">
@@ -1186,7 +1185,7 @@
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A5" s="22">
+      <c r="A5">
         <v>12</v>
       </c>
       <c r="B5" t="s">
@@ -1195,13 +1194,13 @@
       <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5">
         <v>132.25466087757391</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5">
         <v>40777</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5">
         <v>3411</v>
       </c>
       <c r="G5">
@@ -1228,32 +1227,32 @@
       <c r="N5">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5">
         <v>0.18888888888888891</v>
       </c>
       <c r="P5">
         <v>128.11481481481479</v>
       </c>
       <c r="Q5" t="s">
-        <v>72</v>
-      </c>
-      <c r="R5" s="20">
+        <v>41</v>
+      </c>
+      <c r="R5">
         <v>33.333333333333329</v>
       </c>
       <c r="S5" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="T5" s="15">
         <v>60</v>
       </c>
       <c r="U5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V5" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X5" s="16">
         <v>88.888888888888886</v>
@@ -1296,7 +1295,7 @@
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A6" s="22">
+      <c r="A6">
         <v>13</v>
       </c>
       <c r="B6" t="s">
@@ -1305,108 +1304,108 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="22">
-        <v>128.11040201171329</v>
-      </c>
-      <c r="E6" s="22">
-        <v>39530</v>
-      </c>
-      <c r="F6" s="22">
-        <v>3326</v>
+      <c r="D6">
+        <v>128.49359344638481</v>
+      </c>
+      <c r="E6">
+        <v>40743</v>
+      </c>
+      <c r="F6">
+        <v>3419</v>
       </c>
       <c r="G6">
-        <v>124.7592592592593</v>
+        <v>128.6185185185185</v>
       </c>
       <c r="H6">
-        <v>11.50740740740741</v>
+        <v>11.829629629629631</v>
       </c>
       <c r="I6">
-        <v>11.50740740740741</v>
+        <v>11.829629629629631</v>
       </c>
       <c r="J6">
-        <v>9.9851851851851858</v>
+        <v>10.28888888888889</v>
       </c>
       <c r="K6">
-        <v>0.79629629629629628</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L6">
-        <v>0.79629629629629628</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M6">
-        <v>0.14074074074074069</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="N6">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O6" s="22">
-        <v>0.15555555555555561</v>
+      <c r="O6">
+        <v>0.162962962962963</v>
       </c>
       <c r="P6">
-        <v>124.2592592592593</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="20">
-        <v>34.444444444444443</v>
+        <v>44</v>
+      </c>
+      <c r="R6">
+        <v>35.185185185185183</v>
       </c>
       <c r="S6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T6" s="22">
-        <v>54.814814814814817</v>
+        <v>45</v>
+      </c>
+      <c r="T6">
+        <v>56.666666666666657</v>
       </c>
       <c r="U6" t="s">
-        <v>36</v>
-      </c>
-      <c r="V6" s="22">
+        <v>35</v>
+      </c>
+      <c r="V6">
         <v>88.888888888888886</v>
       </c>
       <c r="W6" t="s">
-        <v>54</v>
-      </c>
-      <c r="X6" s="20">
+        <v>46</v>
+      </c>
+      <c r="X6">
         <v>77.777777777777786</v>
       </c>
       <c r="Y6">
-        <v>33685</v>
+        <v>34727</v>
       </c>
       <c r="Z6">
-        <v>3107</v>
+        <v>3194</v>
       </c>
       <c r="AA6">
-        <v>36792</v>
+        <v>37921</v>
       </c>
       <c r="AB6">
-        <v>2313</v>
+        <v>2381</v>
       </c>
       <c r="AC6">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AD6">
-        <v>2696</v>
+        <v>2778</v>
       </c>
       <c r="AE6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF6">
         <v>4</v>
       </c>
-      <c r="AG6" s="22">
-        <v>42</v>
+      <c r="AG6">
+        <v>44</v>
       </c>
       <c r="AH6" s="17">
-        <v>137180580000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI6" s="17">
-        <v>175742592520</v>
+        <v>181650493600</v>
       </c>
       <c r="AJ6" s="17">
-        <v>38562012520</v>
+        <v>40281193600</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A7" s="22">
+      <c r="A7">
         <v>14</v>
       </c>
       <c r="B7" t="s">
@@ -1415,10 +1414,10 @@
       <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7">
         <v>127.4071409280516</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7">
         <v>40707</v>
       </c>
       <c r="F7" s="15">
@@ -1448,34 +1447,34 @@
       <c r="N7">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7">
         <v>0.162962962962963</v>
       </c>
       <c r="P7">
         <v>127.8962962962963</v>
       </c>
       <c r="Q7" t="s">
-        <v>73</v>
-      </c>
-      <c r="R7" s="20">
+        <v>47</v>
+      </c>
+      <c r="R7">
         <v>34.444444444444443</v>
       </c>
       <c r="S7" t="s">
-        <v>56</v>
-      </c>
-      <c r="T7" s="20">
+        <v>34</v>
+      </c>
+      <c r="T7">
         <v>57.037037037037038</v>
       </c>
       <c r="U7" t="s">
+        <v>35</v>
+      </c>
+      <c r="V7">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W7" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="22">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W7" t="s">
-        <v>57</v>
-      </c>
-      <c r="X7" s="22">
+      <c r="X7">
         <v>81.481481481481481</v>
       </c>
       <c r="Y7">
@@ -1502,7 +1501,7 @@
       <c r="AF7">
         <v>2</v>
       </c>
-      <c r="AG7" s="22">
+      <c r="AG7">
         <v>44</v>
       </c>
       <c r="AH7" s="17">
@@ -1528,10 +1527,10 @@
       <c r="D8" s="15">
         <v>143.94343354603859</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8">
         <v>40738</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8">
         <v>3404</v>
       </c>
       <c r="G8">
@@ -1565,25 +1564,25 @@
         <v>128.14074074074071</v>
       </c>
       <c r="Q8" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="R8" s="15">
         <v>24.444444444444439</v>
       </c>
       <c r="S8" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="T8" s="15">
         <v>61.851851851851848</v>
       </c>
       <c r="U8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V8" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="X8" s="15">
         <v>92.592592592592595</v>
@@ -1626,7 +1625,7 @@
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="22">
+      <c r="A9">
         <v>16</v>
       </c>
       <c r="B9" t="s">
@@ -1635,13 +1634,13 @@
       <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9">
         <v>132.3466032724219</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9">
         <v>40737</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9">
         <v>3403</v>
       </c>
       <c r="G9">
@@ -1668,34 +1667,34 @@
       <c r="N9">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9">
         <v>0.17777777777777781</v>
       </c>
       <c r="P9">
         <v>128.14444444444439</v>
       </c>
       <c r="Q9" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" s="20">
+        <v>50</v>
+      </c>
+      <c r="R9">
         <v>34.074074074074083</v>
       </c>
       <c r="S9" t="s">
-        <v>58</v>
-      </c>
-      <c r="T9" s="22">
+        <v>51</v>
+      </c>
+      <c r="T9">
         <v>57.407407407407398</v>
       </c>
       <c r="U9" t="s">
-        <v>36</v>
-      </c>
-      <c r="V9" s="22">
+        <v>35</v>
+      </c>
+      <c r="V9">
         <v>88.888888888888886</v>
       </c>
       <c r="W9" t="s">
         <v>39</v>
       </c>
-      <c r="X9" s="20">
+      <c r="X9">
         <v>85.18518518518519</v>
       </c>
       <c r="Y9">
@@ -1722,7 +1721,7 @@
       <c r="AF9">
         <v>5</v>
       </c>
-      <c r="AG9" s="22">
+      <c r="AG9">
         <v>48</v>
       </c>
       <c r="AH9" s="17">
@@ -1736,7 +1735,7 @@
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A10" s="22">
+      <c r="A10">
         <v>17</v>
       </c>
       <c r="B10" t="s">
@@ -1745,13 +1744,13 @@
       <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10">
         <v>128.3768819680086</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10">
         <v>40700</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10">
         <v>3369</v>
       </c>
       <c r="G10">
@@ -1778,34 +1777,34 @@
       <c r="N10">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10">
         <v>0.15925925925925929</v>
       </c>
       <c r="P10">
         <v>128.27037037037039</v>
       </c>
       <c r="Q10" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="R10" s="15">
         <v>29.25925925925926</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T10" s="16">
         <v>58.888888888888893</v>
       </c>
       <c r="U10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V10" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W10" t="s">
-        <v>57</v>
-      </c>
-      <c r="X10" s="20">
+        <v>36</v>
+      </c>
+      <c r="X10">
         <v>81.481481481481481</v>
       </c>
       <c r="Y10">
@@ -1832,7 +1831,7 @@
       <c r="AF10">
         <v>4</v>
       </c>
-      <c r="AG10" s="22">
+      <c r="AG10">
         <v>43</v>
       </c>
       <c r="AH10" s="17">
@@ -1846,7 +1845,7 @@
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="22">
+      <c r="A11">
         <v>18</v>
       </c>
       <c r="B11" t="s">
@@ -1855,13 +1854,13 @@
       <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11">
         <v>130.98891603764039</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11">
         <v>40715</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11">
         <v>3314</v>
       </c>
       <c r="G11">
@@ -1888,34 +1887,34 @@
       <c r="N11">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11">
         <v>0.17037037037037039</v>
       </c>
       <c r="P11">
         <v>128.47407407407411</v>
       </c>
       <c r="Q11" t="s">
-        <v>64</v>
-      </c>
-      <c r="R11" s="22">
+        <v>54</v>
+      </c>
+      <c r="R11">
         <v>32.222222222222221</v>
       </c>
       <c r="S11" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="T11" s="16">
         <v>58.518518518518512</v>
       </c>
       <c r="U11" t="s">
-        <v>36</v>
-      </c>
-      <c r="V11" s="22">
+        <v>35</v>
+      </c>
+      <c r="V11">
         <v>88.888888888888886</v>
       </c>
       <c r="W11" t="s">
         <v>39</v>
       </c>
-      <c r="X11" s="22">
+      <c r="X11">
         <v>85.18518518518519</v>
       </c>
       <c r="Y11">
@@ -1942,7 +1941,7 @@
       <c r="AF11">
         <v>4</v>
       </c>
-      <c r="AG11" s="22">
+      <c r="AG11">
         <v>46</v>
       </c>
       <c r="AH11" s="17">
@@ -1956,7 +1955,7 @@
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="22">
+      <c r="A12">
         <v>19</v>
       </c>
       <c r="B12" t="s">
@@ -1965,13 +1964,13 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12">
         <v>121.16360259264211</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12">
         <v>40700</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12">
         <v>3338</v>
       </c>
       <c r="G12">
@@ -1998,34 +1997,34 @@
       <c r="N12">
         <v>1.111111111111111E-2</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O12">
         <v>0.1444444444444444</v>
       </c>
       <c r="P12">
         <v>128.38518518518521</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
-      </c>
-      <c r="R12" s="22">
+        <v>56</v>
+      </c>
+      <c r="R12">
         <v>37.407407407407398</v>
       </c>
       <c r="S12" t="s">
-        <v>82</v>
-      </c>
-      <c r="T12" s="22">
+        <v>57</v>
+      </c>
+      <c r="T12">
         <v>52.962962962962969</v>
       </c>
       <c r="U12" t="s">
         <v>39</v>
       </c>
-      <c r="V12" s="22">
+      <c r="V12">
         <v>85.18518518518519</v>
       </c>
       <c r="W12" t="s">
-        <v>49</v>
-      </c>
-      <c r="X12" s="22">
+        <v>40</v>
+      </c>
+      <c r="X12">
         <v>74.074074074074076</v>
       </c>
       <c r="Y12">
@@ -2052,7 +2051,7 @@
       <c r="AF12">
         <v>3</v>
       </c>
-      <c r="AG12" s="22">
+      <c r="AG12">
         <v>39</v>
       </c>
       <c r="AH12" s="17">
@@ -2066,7 +2065,7 @@
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="22">
+      <c r="A13">
         <v>20</v>
       </c>
       <c r="B13" t="s">
@@ -2075,13 +2074,13 @@
       <c r="C13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13">
         <v>134.7273627300977</v>
       </c>
       <c r="E13" s="16">
         <v>40771</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13">
         <v>3411</v>
       </c>
       <c r="G13">
@@ -2115,15 +2114,15 @@
         <v>128.11481481481479</v>
       </c>
       <c r="Q13" t="s">
-        <v>42</v>
-      </c>
-      <c r="R13" s="20">
+        <v>58</v>
+      </c>
+      <c r="R13">
         <v>33.703703703703702</v>
       </c>
       <c r="S13" t="s">
-        <v>58</v>
-      </c>
-      <c r="T13" s="22">
+        <v>51</v>
+      </c>
+      <c r="T13">
         <v>57.407407407407398</v>
       </c>
       <c r="U13" t="s">
@@ -2133,7 +2132,7 @@
         <v>100</v>
       </c>
       <c r="W13" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="X13" s="15">
         <v>96.296296296296291</v>
@@ -2176,7 +2175,7 @@
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A14" s="22">
+      <c r="A14">
         <v>21</v>
       </c>
       <c r="B14" t="s">
@@ -2185,13 +2184,13 @@
       <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14">
         <v>120.4952906182601</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14">
         <v>40686</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14">
         <v>3412</v>
       </c>
       <c r="G14">
@@ -2218,34 +2217,34 @@
       <c r="N14">
         <v>1.8518518518518521E-2</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14">
         <v>0.1333333333333333</v>
       </c>
       <c r="P14">
         <v>128.11111111111109</v>
       </c>
       <c r="Q14" t="s">
-        <v>67</v>
-      </c>
-      <c r="R14" s="20">
+        <v>61</v>
+      </c>
+      <c r="R14">
         <v>41.481481481481481</v>
       </c>
       <c r="S14" t="s">
-        <v>68</v>
-      </c>
-      <c r="T14" s="22">
+        <v>62</v>
+      </c>
+      <c r="T14">
         <v>51.851851851851848</v>
       </c>
       <c r="U14" t="s">
-        <v>49</v>
-      </c>
-      <c r="V14" s="22">
+        <v>40</v>
+      </c>
+      <c r="V14">
         <v>74.074074074074076</v>
       </c>
       <c r="W14" t="s">
-        <v>69</v>
-      </c>
-      <c r="X14" s="22">
+        <v>63</v>
+      </c>
+      <c r="X14">
         <v>59.259259259259252</v>
       </c>
       <c r="Y14">
@@ -2272,7 +2271,7 @@
       <c r="AF14">
         <v>5</v>
       </c>
-      <c r="AG14" s="22">
+      <c r="AG14">
         <v>36</v>
       </c>
       <c r="AH14" s="17">
@@ -2286,7 +2285,7 @@
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A15" s="22">
+      <c r="A15">
         <v>22</v>
       </c>
       <c r="B15" t="s">
@@ -2295,13 +2294,13 @@
       <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15">
         <v>120.5562728400013</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15">
         <v>40635</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15">
         <v>3414</v>
       </c>
       <c r="G15">
@@ -2328,34 +2327,34 @@
       <c r="N15">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15">
         <v>0.1444444444444444</v>
       </c>
       <c r="P15">
         <v>128.1037037037037</v>
       </c>
       <c r="Q15" t="s">
-        <v>77</v>
-      </c>
-      <c r="R15" s="20">
+        <v>64</v>
+      </c>
+      <c r="R15">
         <v>35.555555555555557</v>
       </c>
       <c r="S15" t="s">
-        <v>56</v>
-      </c>
-      <c r="T15" s="22">
+        <v>34</v>
+      </c>
+      <c r="T15">
         <v>57.037037037037038</v>
       </c>
       <c r="U15" t="s">
-        <v>57</v>
-      </c>
-      <c r="V15" s="22">
+        <v>36</v>
+      </c>
+      <c r="V15">
         <v>81.481481481481481</v>
       </c>
       <c r="W15" t="s">
-        <v>46</v>
-      </c>
-      <c r="X15" s="22">
+        <v>65</v>
+      </c>
+      <c r="X15">
         <v>70.370370370370367</v>
       </c>
       <c r="Y15">
@@ -2382,7 +2381,7 @@
       <c r="AF15">
         <v>1</v>
       </c>
-      <c r="AG15" s="22">
+      <c r="AG15">
         <v>39</v>
       </c>
       <c r="AH15" s="17">
@@ -2396,7 +2395,7 @@
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A16" s="22">
+      <c r="A16">
         <v>23</v>
       </c>
       <c r="B16" t="s">
@@ -2405,13 +2404,13 @@
       <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16">
         <v>122.0712722776445</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16">
         <v>40670</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16">
         <v>3413</v>
       </c>
       <c r="G16">
@@ -2438,34 +2437,34 @@
       <c r="N16">
         <v>1.111111111111111E-2</v>
       </c>
-      <c r="O16" s="22">
+      <c r="O16">
         <v>0.13703703703703701</v>
       </c>
       <c r="P16">
         <v>128.10740740740741</v>
       </c>
       <c r="Q16" t="s">
-        <v>42</v>
-      </c>
-      <c r="R16" s="22">
+        <v>58</v>
+      </c>
+      <c r="R16">
         <v>33.703703703703702</v>
       </c>
       <c r="S16" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="T16" s="16">
         <v>58.518518518518512</v>
       </c>
       <c r="U16" t="s">
-        <v>36</v>
-      </c>
-      <c r="V16" s="22">
+        <v>35</v>
+      </c>
+      <c r="V16">
         <v>88.888888888888886</v>
       </c>
       <c r="W16" t="s">
-        <v>78</v>
-      </c>
-      <c r="X16" s="22">
+        <v>66</v>
+      </c>
+      <c r="X16">
         <v>66.666666666666657</v>
       </c>
       <c r="Y16">
@@ -2492,7 +2491,7 @@
       <c r="AF16">
         <v>3</v>
       </c>
-      <c r="AG16" s="22">
+      <c r="AG16">
         <v>37</v>
       </c>
       <c r="AH16" s="17">
@@ -2506,7 +2505,7 @@
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A17" s="22">
+      <c r="A17">
         <v>24</v>
       </c>
       <c r="B17" t="s">
@@ -2515,13 +2514,13 @@
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17">
         <v>119.321995058333</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17">
         <v>40671</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17">
         <v>3419</v>
       </c>
       <c r="G17">
@@ -2548,34 +2547,34 @@
       <c r="N17">
         <v>0</v>
       </c>
-      <c r="O17" s="22">
+      <c r="O17">
         <v>0.14074074074074069</v>
       </c>
       <c r="P17">
         <v>128.0851851851852</v>
       </c>
       <c r="Q17" t="s">
-        <v>60</v>
-      </c>
-      <c r="R17" s="20">
+        <v>67</v>
+      </c>
+      <c r="R17">
         <v>31.851851851851851</v>
       </c>
       <c r="S17" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="T17" s="16">
         <v>58.518518518518512</v>
       </c>
       <c r="U17" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V17" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W17" t="s">
-        <v>57</v>
-      </c>
-      <c r="X17" s="20">
+        <v>36</v>
+      </c>
+      <c r="X17">
         <v>81.481481481481481</v>
       </c>
       <c r="Y17">
@@ -2602,7 +2601,7 @@
       <c r="AF17">
         <v>0</v>
       </c>
-      <c r="AG17" s="22">
+      <c r="AG17">
         <v>38</v>
       </c>
       <c r="AH17" s="17">
@@ -2616,7 +2615,7 @@
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A18" s="22">
+      <c r="A18">
         <v>25</v>
       </c>
       <c r="B18" t="s">
@@ -2625,13 +2624,13 @@
       <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18">
         <v>126.6790426209934</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18">
         <v>40732</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18">
         <v>3363</v>
       </c>
       <c r="G18">
@@ -2658,34 +2657,34 @@
       <c r="N18">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O18" s="22">
+      <c r="O18">
         <v>0.16666666666666671</v>
       </c>
       <c r="P18">
         <v>128.2925925925926</v>
       </c>
       <c r="Q18" t="s">
-        <v>60</v>
-      </c>
-      <c r="R18" s="20">
+        <v>67</v>
+      </c>
+      <c r="R18">
         <v>31.851851851851851</v>
       </c>
       <c r="S18" t="s">
-        <v>56</v>
-      </c>
-      <c r="T18" s="20">
+        <v>34</v>
+      </c>
+      <c r="T18">
         <v>57.037037037037038</v>
       </c>
       <c r="U18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V18" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W18" t="s">
-        <v>57</v>
-      </c>
-      <c r="X18" s="20">
+        <v>36</v>
+      </c>
+      <c r="X18">
         <v>81.481481481481481</v>
       </c>
       <c r="Y18">
@@ -2712,7 +2711,7 @@
       <c r="AF18">
         <v>1</v>
       </c>
-      <c r="AG18" s="22">
+      <c r="AG18">
         <v>45</v>
       </c>
       <c r="AH18" s="17">
@@ -2726,7 +2725,7 @@
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A19" s="20">
+      <c r="A19">
         <v>26</v>
       </c>
       <c r="B19" t="s">
@@ -2735,13 +2734,13 @@
       <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19">
         <v>129.8896579809053</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19">
         <v>40727</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19">
         <v>3298</v>
       </c>
       <c r="G19">
@@ -2768,26 +2767,26 @@
       <c r="N19">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O19" s="22">
+      <c r="O19">
         <v>0.17777777777777781</v>
       </c>
       <c r="P19">
         <v>128.5333333333333</v>
       </c>
       <c r="Q19" t="s">
-        <v>62</v>
-      </c>
-      <c r="R19" s="20">
+        <v>44</v>
+      </c>
+      <c r="R19">
         <v>35.185185185185183</v>
       </c>
       <c r="S19" t="s">
-        <v>63</v>
-      </c>
-      <c r="T19" s="22">
+        <v>68</v>
+      </c>
+      <c r="T19">
         <v>54.074074074074083</v>
       </c>
       <c r="U19" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V19" s="7">
         <v>92.592592592592595</v>
@@ -2795,7 +2794,7 @@
       <c r="W19" t="s">
         <v>39</v>
       </c>
-      <c r="X19" s="22">
+      <c r="X19">
         <v>85.18518518518519</v>
       </c>
       <c r="Y19">
@@ -2822,7 +2821,7 @@
       <c r="AF19">
         <v>2</v>
       </c>
-      <c r="AG19" s="22">
+      <c r="AG19">
         <v>48</v>
       </c>
       <c r="AH19" s="17">
@@ -2836,7 +2835,7 @@
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A20" s="20">
+      <c r="A20">
         <v>27</v>
       </c>
       <c r="B20" t="s">
@@ -2845,13 +2844,13 @@
       <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20">
         <v>129.8617456689677</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20">
         <v>40740</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20">
         <v>3322</v>
       </c>
       <c r="G20">
@@ -2878,22 +2877,22 @@
       <c r="N20">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O20" s="22">
+      <c r="O20">
         <v>0.18888888888888891</v>
       </c>
       <c r="P20">
         <v>128.44444444444451</v>
       </c>
       <c r="Q20" t="s">
-        <v>42</v>
-      </c>
-      <c r="R20" s="22">
+        <v>58</v>
+      </c>
+      <c r="R20">
         <v>33.703703703703702</v>
       </c>
       <c r="S20" t="s">
-        <v>70</v>
-      </c>
-      <c r="T20" s="22">
+        <v>38</v>
+      </c>
+      <c r="T20">
         <v>54.444444444444443</v>
       </c>
       <c r="U20" t="s">
@@ -2903,7 +2902,7 @@
         <v>100</v>
       </c>
       <c r="W20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X20" s="16">
         <v>88.888888888888886</v>
@@ -2946,7 +2945,7 @@
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A21" s="20">
+      <c r="A21">
         <v>28</v>
       </c>
       <c r="B21" t="s">
@@ -2955,13 +2954,13 @@
       <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21">
         <v>126.4057725970207</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21">
         <v>40733</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21">
         <v>3334</v>
       </c>
       <c r="G21">
@@ -2988,34 +2987,34 @@
       <c r="N21">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O21" s="22">
+      <c r="O21">
         <v>0.1740740740740741</v>
       </c>
       <c r="P21">
         <v>128.4</v>
       </c>
       <c r="Q21" t="s">
-        <v>73</v>
-      </c>
-      <c r="R21" s="22">
+        <v>47</v>
+      </c>
+      <c r="R21">
         <v>34.444444444444443</v>
       </c>
       <c r="S21" t="s">
-        <v>74</v>
-      </c>
-      <c r="T21" s="22">
+        <v>69</v>
+      </c>
+      <c r="T21">
         <v>51.111111111111107</v>
       </c>
       <c r="U21" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V21" s="19">
         <v>96.296296296296291</v>
       </c>
       <c r="W21" t="s">
-        <v>54</v>
-      </c>
-      <c r="X21" s="22">
+        <v>46</v>
+      </c>
+      <c r="X21">
         <v>77.777777777777786</v>
       </c>
       <c r="Y21">
@@ -3042,7 +3041,7 @@
       <c r="AF21">
         <v>2</v>
       </c>
-      <c r="AG21" s="22">
+      <c r="AG21">
         <v>47</v>
       </c>
       <c r="AH21" s="17">
@@ -3056,7 +3055,7 @@
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A22" s="20">
+      <c r="A22">
         <v>29</v>
       </c>
       <c r="B22" t="s">
@@ -3065,13 +3064,13 @@
       <c r="C22" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22">
         <v>126.3272132492698</v>
       </c>
       <c r="E22" s="15">
         <v>40684</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22">
         <v>3338</v>
       </c>
       <c r="G22">
@@ -3098,34 +3097,34 @@
       <c r="N22">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O22" s="22">
+      <c r="O22">
         <v>0.15185185185185179</v>
       </c>
       <c r="P22">
         <v>128.38518518518521</v>
       </c>
       <c r="Q22" t="s">
-        <v>44</v>
-      </c>
-      <c r="R22" s="20">
+        <v>70</v>
+      </c>
+      <c r="R22">
         <v>32.592592592592602</v>
       </c>
       <c r="S22" t="s">
-        <v>45</v>
-      </c>
-      <c r="T22" s="22">
+        <v>71</v>
+      </c>
+      <c r="T22">
         <v>53.333333333333343</v>
       </c>
       <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" s="20">
+        <v>35</v>
+      </c>
+      <c r="V22">
         <v>88.888888888888886</v>
       </c>
       <c r="W22" t="s">
-        <v>46</v>
-      </c>
-      <c r="X22" s="22">
+        <v>65</v>
+      </c>
+      <c r="X22">
         <v>70.370370370370367</v>
       </c>
       <c r="Y22">
@@ -3152,7 +3151,7 @@
       <c r="AF22">
         <v>4</v>
       </c>
-      <c r="AG22" s="22">
+      <c r="AG22">
         <v>41</v>
       </c>
       <c r="AH22" s="17">
@@ -3166,7 +3165,7 @@
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A23" s="20">
+      <c r="A23">
         <v>30</v>
       </c>
       <c r="B23" t="s">
@@ -3175,13 +3174,13 @@
       <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23">
         <v>129.4359784054954</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23">
         <v>40730</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23">
         <v>3412</v>
       </c>
       <c r="G23">
@@ -3208,34 +3207,34 @@
       <c r="N23">
         <v>1.111111111111111E-2</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23">
         <v>0.162962962962963</v>
       </c>
       <c r="P23">
         <v>128.11111111111109</v>
       </c>
       <c r="Q23" t="s">
-        <v>40</v>
-      </c>
-      <c r="R23" s="20">
+        <v>72</v>
+      </c>
+      <c r="R23">
         <v>30.74074074074074</v>
       </c>
       <c r="S23" t="s">
-        <v>79</v>
-      </c>
-      <c r="T23" s="22">
+        <v>73</v>
+      </c>
+      <c r="T23">
         <v>57.777777777777771</v>
       </c>
       <c r="U23" t="s">
         <v>39</v>
       </c>
-      <c r="V23" s="20">
+      <c r="V23">
         <v>85.18518518518519</v>
       </c>
       <c r="W23" t="s">
-        <v>49</v>
-      </c>
-      <c r="X23" s="20">
+        <v>40</v>
+      </c>
+      <c r="X23">
         <v>74.074074074074076</v>
       </c>
       <c r="Y23">
@@ -3262,7 +3261,7 @@
       <c r="AF23">
         <v>3</v>
       </c>
-      <c r="AG23" s="22">
+      <c r="AG23">
         <v>44</v>
       </c>
       <c r="AH23" s="17">
@@ -3276,7 +3275,7 @@
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A24" s="20">
+      <c r="A24">
         <v>31</v>
       </c>
       <c r="B24" t="s">
@@ -3285,13 +3284,13 @@
       <c r="C24" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24">
         <v>133.5813685998304</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24">
         <v>40771</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24">
         <v>3348</v>
       </c>
       <c r="G24">
@@ -3325,25 +3324,25 @@
         <v>128.34814814814811</v>
       </c>
       <c r="Q24" t="s">
-        <v>71</v>
-      </c>
-      <c r="R24" s="20">
+        <v>74</v>
+      </c>
+      <c r="R24">
         <v>31.111111111111111</v>
       </c>
       <c r="S24" t="s">
-        <v>53</v>
-      </c>
-      <c r="T24" s="20">
+        <v>45</v>
+      </c>
+      <c r="T24">
         <v>56.666666666666657</v>
       </c>
       <c r="U24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24" s="22">
+        <v>35</v>
+      </c>
+      <c r="V24">
         <v>88.888888888888886</v>
       </c>
       <c r="W24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="X24">
         <v>77.777777777777786</v>
@@ -3386,7 +3385,7 @@
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A25" s="20">
+      <c r="A25">
         <v>32</v>
       </c>
       <c r="B25" t="s">
@@ -3395,7 +3394,7 @@
       <c r="C25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25">
         <v>127.7335127851654</v>
       </c>
       <c r="E25" s="16">
@@ -3428,20 +3427,20 @@
       <c r="N25">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O25" s="20">
+      <c r="O25">
         <v>0.17037037037037039</v>
       </c>
       <c r="P25">
         <v>128.10740740740741</v>
       </c>
       <c r="Q25" t="s">
-        <v>47</v>
-      </c>
-      <c r="R25" s="20">
+        <v>75</v>
+      </c>
+      <c r="R25">
         <v>30.37037037037037</v>
       </c>
       <c r="S25" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="T25" s="15">
         <v>62.962962962962962</v>
@@ -3449,13 +3448,13 @@
       <c r="U25" t="s">
         <v>39</v>
       </c>
-      <c r="V25" s="22">
+      <c r="V25">
         <v>85.18518518518519</v>
       </c>
       <c r="W25" t="s">
-        <v>49</v>
-      </c>
-      <c r="X25" s="22">
+        <v>40</v>
+      </c>
+      <c r="X25">
         <v>74.074074074074076</v>
       </c>
       <c r="Y25">
@@ -3482,7 +3481,7 @@
       <c r="AF25">
         <v>1</v>
       </c>
-      <c r="AG25" s="22">
+      <c r="AG25">
         <v>46</v>
       </c>
       <c r="AH25" s="17">
@@ -3496,7 +3495,7 @@
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A26" s="20">
+      <c r="A26">
         <v>33</v>
       </c>
       <c r="B26" t="s">
@@ -3505,10 +3504,10 @@
       <c r="C26" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26">
         <v>128.77770443893019</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26">
         <v>40788</v>
       </c>
       <c r="F26">
@@ -3538,32 +3537,32 @@
       <c r="N26">
         <v>3.7037037037037038E-3</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26">
         <v>0.18148148148148149</v>
       </c>
       <c r="P26">
         <v>128.51111111111109</v>
       </c>
       <c r="Q26" t="s">
-        <v>72</v>
-      </c>
-      <c r="R26" s="22">
+        <v>41</v>
+      </c>
+      <c r="R26">
         <v>33.333333333333329</v>
       </c>
       <c r="S26" t="s">
-        <v>53</v>
-      </c>
-      <c r="T26" s="22">
+        <v>45</v>
+      </c>
+      <c r="T26">
         <v>56.666666666666657</v>
       </c>
       <c r="U26" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V26" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W26" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="X26" s="15">
         <v>92.592592592592595</v>
@@ -3592,7 +3591,7 @@
       <c r="AF26">
         <v>1</v>
       </c>
-      <c r="AG26" s="22">
+      <c r="AG26">
         <v>49</v>
       </c>
       <c r="AH26" s="17">
@@ -3618,10 +3617,10 @@
       <c r="D27">
         <v>126.70595083879449</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27">
         <v>40752</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27">
         <v>3420</v>
       </c>
       <c r="G27">
@@ -3648,32 +3647,32 @@
       <c r="N27">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27">
         <v>0.15925925925925929</v>
       </c>
       <c r="P27">
         <v>128.1592592592593</v>
       </c>
       <c r="Q27" t="s">
-        <v>64</v>
-      </c>
-      <c r="R27" s="22">
+        <v>54</v>
+      </c>
+      <c r="R27">
         <v>32.222222222222221</v>
       </c>
       <c r="S27" t="s">
-        <v>65</v>
-      </c>
-      <c r="T27" s="22">
+        <v>77</v>
+      </c>
+      <c r="T27">
         <v>56.296296296296298</v>
       </c>
       <c r="U27" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V27" s="19">
         <v>96.296296296296291</v>
       </c>
       <c r="W27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X27" s="16">
         <v>88.888888888888886</v>
@@ -3702,7 +3701,7 @@
       <c r="AF27">
         <v>2</v>
       </c>
-      <c r="AG27" s="22">
+      <c r="AG27">
         <v>43</v>
       </c>
       <c r="AH27" s="17">
@@ -3716,7 +3715,7 @@
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A28" s="20">
+      <c r="A28">
         <v>35</v>
       </c>
       <c r="B28" t="s">
@@ -3725,13 +3724,13 @@
       <c r="C28" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28">
         <v>126.3735355064933</v>
       </c>
       <c r="E28" s="15">
         <v>40759</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28">
         <v>3357</v>
       </c>
       <c r="G28">
@@ -3758,32 +3757,32 @@
       <c r="N28">
         <v>1.4814814814814821E-2</v>
       </c>
-      <c r="O28" s="20">
+      <c r="O28">
         <v>0.15925925925925929</v>
       </c>
       <c r="P28">
         <v>128.39259259259259</v>
       </c>
       <c r="Q28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" s="22">
+        <v>78</v>
+      </c>
+      <c r="R28">
         <v>34.814814814814817</v>
       </c>
       <c r="S28" t="s">
-        <v>34</v>
-      </c>
-      <c r="T28" s="22">
+        <v>79</v>
+      </c>
+      <c r="T28">
         <v>55.185185185185183</v>
       </c>
       <c r="U28" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V28" s="19">
         <v>96.296296296296291</v>
       </c>
       <c r="W28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X28" s="16">
         <v>88.888888888888886</v>
@@ -3812,7 +3811,7 @@
       <c r="AF28">
         <v>4</v>
       </c>
-      <c r="AG28" s="20">
+      <c r="AG28">
         <v>43</v>
       </c>
       <c r="AH28" s="17">
@@ -3826,7 +3825,7 @@
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A29" s="20">
+      <c r="A29">
         <v>36</v>
       </c>
       <c r="B29" t="s">
@@ -3835,13 +3834,13 @@
       <c r="C29" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29">
         <v>134.21853146981681</v>
       </c>
       <c r="E29" s="15">
         <v>40773</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29">
         <v>3382</v>
       </c>
       <c r="G29">
@@ -3868,32 +3867,32 @@
       <c r="N29">
         <v>2.222222222222222E-2</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29">
         <v>0.18148148148148149</v>
       </c>
       <c r="P29">
         <v>128.30000000000001</v>
       </c>
       <c r="Q29" t="s">
-        <v>42</v>
-      </c>
-      <c r="R29" s="20">
+        <v>58</v>
+      </c>
+      <c r="R29">
         <v>33.703703703703702</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T29" s="16">
         <v>58.888888888888893</v>
       </c>
       <c r="U29" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V29" s="19">
         <v>96.296296296296291</v>
       </c>
       <c r="W29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X29" s="16">
         <v>88.888888888888886</v>
@@ -3936,7 +3935,7 @@
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A30" s="20">
+      <c r="A30">
         <v>37</v>
       </c>
       <c r="B30" t="s">
@@ -3945,13 +3944,13 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30">
         <v>125.45177072243079</v>
       </c>
       <c r="E30" s="16">
         <v>40718</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30">
         <v>3381</v>
       </c>
       <c r="G30">
@@ -3985,27 +3984,27 @@
         <v>128.30370370370369</v>
       </c>
       <c r="Q30" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R30">
         <v>37.037037037037038</v>
       </c>
       <c r="S30" t="s">
-        <v>51</v>
-      </c>
-      <c r="T30" s="22">
+        <v>80</v>
+      </c>
+      <c r="T30">
         <v>54.814814814814817</v>
       </c>
       <c r="U30" t="s">
         <v>39</v>
       </c>
-      <c r="V30" s="22">
+      <c r="V30">
         <v>85.18518518518519</v>
       </c>
       <c r="W30" t="s">
-        <v>49</v>
-      </c>
-      <c r="X30" s="20">
+        <v>40</v>
+      </c>
+      <c r="X30">
         <v>74.074074074074076</v>
       </c>
       <c r="Y30">
@@ -4032,7 +4031,7 @@
       <c r="AF30">
         <v>5</v>
       </c>
-      <c r="AG30" s="20">
+      <c r="AG30">
         <v>40</v>
       </c>
       <c r="AH30" s="17">
@@ -4058,7 +4057,7 @@
       <c r="D31">
         <v>133.24790789873671</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31">
         <v>40755</v>
       </c>
       <c r="F31" s="15">
@@ -4088,26 +4087,26 @@
       <c r="N31">
         <v>2.5925925925925929E-2</v>
       </c>
-      <c r="O31" s="20">
+      <c r="O31">
         <v>0.17037037037037039</v>
       </c>
       <c r="P31">
         <v>128.137037037037</v>
       </c>
       <c r="Q31" t="s">
-        <v>52</v>
-      </c>
-      <c r="R31" s="20">
+        <v>81</v>
+      </c>
+      <c r="R31">
         <v>32.962962962962962</v>
       </c>
       <c r="S31" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="T31" s="16">
         <v>58.148148148148152</v>
       </c>
       <c r="U31" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V31" s="7">
         <v>92.592592592592595</v>
@@ -4115,7 +4114,7 @@
       <c r="W31" t="s">
         <v>39</v>
       </c>
-      <c r="X31" s="22">
+      <c r="X31">
         <v>85.18518518518519</v>
       </c>
       <c r="Y31">
@@ -4142,7 +4141,7 @@
       <c r="AF31">
         <v>7</v>
       </c>
-      <c r="AG31" s="22">
+      <c r="AG31">
         <v>46</v>
       </c>
       <c r="AH31" s="17">
@@ -4156,7 +4155,7 @@
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A32" s="20">
+      <c r="A32">
         <v>39</v>
       </c>
       <c r="B32" t="s">
@@ -4165,7 +4164,7 @@
       <c r="C32" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32">
         <v>123.7648688681046</v>
       </c>
       <c r="E32" s="16">
@@ -4198,34 +4197,34 @@
       <c r="N32">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O32" s="20">
+      <c r="O32">
         <v>0.15185185185185179</v>
       </c>
       <c r="P32">
         <v>128.0185185185185</v>
       </c>
       <c r="Q32" t="s">
-        <v>52</v>
-      </c>
-      <c r="R32" s="20">
+        <v>81</v>
+      </c>
+      <c r="R32">
         <v>32.962962962962962</v>
       </c>
       <c r="S32" t="s">
-        <v>53</v>
-      </c>
-      <c r="T32" s="20">
+        <v>45</v>
+      </c>
+      <c r="T32">
         <v>56.666666666666657</v>
       </c>
       <c r="U32" t="s">
-        <v>54</v>
-      </c>
-      <c r="V32" s="22">
+        <v>46</v>
+      </c>
+      <c r="V32">
         <v>77.777777777777786</v>
       </c>
       <c r="W32" t="s">
-        <v>46</v>
-      </c>
-      <c r="X32" s="22">
+        <v>65</v>
+      </c>
+      <c r="X32">
         <v>70.370370370370367</v>
       </c>
       <c r="Y32">
@@ -4252,7 +4251,7 @@
       <c r="AF32">
         <v>2</v>
       </c>
-      <c r="AG32" s="20">
+      <c r="AG32">
         <v>41</v>
       </c>
       <c r="AH32" s="17">
@@ -4266,7 +4265,7 @@
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A33" s="20">
+      <c r="A33">
         <v>40</v>
       </c>
       <c r="B33" t="s">
@@ -4275,13 +4274,13 @@
       <c r="C33" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33">
         <v>131.30895267925919</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33">
         <v>40738</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33">
         <v>3222</v>
       </c>
       <c r="G33">
@@ -4321,21 +4320,21 @@
         <v>30</v>
       </c>
       <c r="S33" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="T33" s="16">
         <v>58.148148148148152</v>
       </c>
       <c r="U33" t="s">
-        <v>36</v>
-      </c>
-      <c r="V33" s="22">
+        <v>35</v>
+      </c>
+      <c r="V33">
         <v>88.888888888888886</v>
       </c>
       <c r="W33" t="s">
         <v>39</v>
       </c>
-      <c r="X33" s="20">
+      <c r="X33">
         <v>85.18518518518519</v>
       </c>
       <c r="Y33">
@@ -4388,10 +4387,10 @@
       <c r="D34" s="16">
         <v>137.232633421825</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34">
         <v>40738</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34">
         <v>3383</v>
       </c>
       <c r="G34">
@@ -4431,19 +4430,19 @@
         <v>30</v>
       </c>
       <c r="S34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T34" s="15">
         <v>64.074074074074076</v>
       </c>
       <c r="U34" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="V34" s="7">
         <v>92.592592592592595</v>
       </c>
       <c r="W34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X34" s="16">
         <v>88.888888888888886</v>
@@ -4486,7 +4485,7 @@
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A35" s="20">
+      <c r="A35">
         <v>42</v>
       </c>
       <c r="B35" t="s">
@@ -4495,13 +4494,13 @@
       <c r="C35" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35">
         <v>131.7624941200105</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35">
         <v>40738</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35">
         <v>3379</v>
       </c>
       <c r="G35">
@@ -4535,27 +4534,27 @@
         <v>128.2222222222222</v>
       </c>
       <c r="Q35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R35" s="15">
         <v>31.111111111111111</v>
       </c>
       <c r="S35" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="T35" s="16">
         <v>59.629629629629633</v>
       </c>
       <c r="U35" t="s">
-        <v>36</v>
-      </c>
-      <c r="V35" s="22">
+        <v>35</v>
+      </c>
+      <c r="V35">
         <v>88.888888888888886</v>
       </c>
       <c r="W35" t="s">
         <v>39</v>
       </c>
-      <c r="X35" s="22">
+      <c r="X35">
         <v>85.18518518518519</v>
       </c>
       <c r="Y35">
@@ -4608,7 +4607,7 @@
       <c r="D36" s="16">
         <v>136.81623945227139</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36">
         <v>40738</v>
       </c>
       <c r="F36" s="15">
@@ -4645,19 +4644,19 @@
         <v>127.89259259259261</v>
       </c>
       <c r="Q36" t="s">
-        <v>71</v>
-      </c>
-      <c r="R36" s="20">
+        <v>74</v>
+      </c>
+      <c r="R36">
         <v>31.111111111111111</v>
       </c>
       <c r="S36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T36" s="15">
         <v>62.592592592592588</v>
       </c>
       <c r="U36" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V36" s="19">
         <v>96.296296296296291</v>
@@ -4665,7 +4664,7 @@
       <c r="W36" t="s">
         <v>39</v>
       </c>
-      <c r="X36" s="20">
+      <c r="X36">
         <v>85.18518518518519</v>
       </c>
       <c r="Y36">
@@ -4706,7 +4705,7 @@
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A37" s="20">
+      <c r="A37">
         <v>44</v>
       </c>
       <c r="B37" t="s">
@@ -4715,13 +4714,13 @@
       <c r="C37" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37">
         <v>134.43323094901089</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37">
         <v>40738</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37">
         <v>3283</v>
       </c>
       <c r="G37">
@@ -4755,25 +4754,25 @@
         <v>128.61111111111109</v>
       </c>
       <c r="Q37" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="R37">
         <v>33.703703703703702</v>
       </c>
       <c r="S37" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="T37" s="16">
         <v>58.888888888888893</v>
       </c>
       <c r="U37" t="s">
-        <v>36</v>
-      </c>
-      <c r="V37" s="20">
+        <v>35</v>
+      </c>
+      <c r="V37">
         <v>88.888888888888886</v>
       </c>
       <c r="W37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X37" s="16">
         <v>88.888888888888886</v>
@@ -4828,10 +4827,10 @@
       <c r="D38" s="15">
         <v>139.06906642389831</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38">
         <v>40771</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38">
         <v>3393</v>
       </c>
       <c r="G38">
@@ -4865,13 +4864,13 @@
         <v>128.17037037037039</v>
       </c>
       <c r="Q38" t="s">
-        <v>71</v>
-      </c>
-      <c r="R38" s="20">
+        <v>74</v>
+      </c>
+      <c r="R38">
         <v>31.111111111111111</v>
       </c>
       <c r="S38" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="T38" s="16">
         <v>58.148148148148152</v>
@@ -4883,7 +4882,7 @@
         <v>100</v>
       </c>
       <c r="W38" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="X38" s="15">
         <v>92.592592592592595</v>
@@ -4938,10 +4937,10 @@
       <c r="D39" s="15">
         <v>139.09968645243339</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39">
         <v>40771</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39">
         <v>3410</v>
       </c>
       <c r="G39">
@@ -4981,19 +4980,19 @@
         <v>30</v>
       </c>
       <c r="S39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T39" s="15">
         <v>62.592592592592588</v>
       </c>
       <c r="U39" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V39" s="19">
         <v>96.296296296296291</v>
       </c>
       <c r="W39" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="X39" s="15">
         <v>96.296296296296291</v>
@@ -5048,10 +5047,10 @@
       <c r="D40">
         <v>135.74983728433261</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40">
         <v>40780</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40">
         <v>3318</v>
       </c>
       <c r="G40">
@@ -5085,25 +5084,25 @@
         <v>128.44444444444451</v>
       </c>
       <c r="Q40" t="s">
-        <v>86</v>
-      </c>
-      <c r="R40" s="20">
+        <v>87</v>
+      </c>
+      <c r="R40">
         <v>37.777777777777779</v>
       </c>
       <c r="S40" t="s">
-        <v>68</v>
-      </c>
-      <c r="T40" s="20">
+        <v>62</v>
+      </c>
+      <c r="T40">
         <v>51.851851851851848</v>
       </c>
       <c r="U40" t="s">
+        <v>35</v>
+      </c>
+      <c r="V40">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W40" t="s">
         <v>36</v>
-      </c>
-      <c r="V40" s="20">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W40" t="s">
-        <v>57</v>
       </c>
       <c r="X40">
         <v>81.481481481481481</v>
@@ -5158,7 +5157,7 @@
       <c r="D41">
         <v>135.08681222868049</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41">
         <v>40780</v>
       </c>
       <c r="F41" s="15">
@@ -5195,27 +5194,27 @@
         <v>127.99629629629629</v>
       </c>
       <c r="Q41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R41" s="15">
         <v>25.92592592592592</v>
       </c>
       <c r="S41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T41" s="15">
         <v>64.074074074074076</v>
       </c>
       <c r="U41" t="s">
+        <v>35</v>
+      </c>
+      <c r="V41">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W41" t="s">
         <v>36</v>
       </c>
-      <c r="V41" s="20">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W41" t="s">
-        <v>57</v>
-      </c>
-      <c r="X41" s="20">
+      <c r="X41">
         <v>81.481481481481481</v>
       </c>
       <c r="Y41">
@@ -5271,7 +5270,7 @@
       <c r="E42" s="15">
         <v>40801</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42">
         <v>3370</v>
       </c>
       <c r="G42">
@@ -5305,21 +5304,21 @@
         <v>128.28148148148151</v>
       </c>
       <c r="Q42" t="s">
-        <v>37</v>
-      </c>
-      <c r="R42" s="20">
+        <v>50</v>
+      </c>
+      <c r="R42">
         <v>34.074074074074083</v>
       </c>
       <c r="S42" t="s">
-        <v>38</v>
-      </c>
-      <c r="T42" s="22">
+        <v>89</v>
+      </c>
+      <c r="T42">
         <v>55.925925925925917</v>
       </c>
       <c r="U42" t="s">
         <v>39</v>
       </c>
-      <c r="V42" s="22">
+      <c r="V42">
         <v>85.18518518518519</v>
       </c>
       <c r="W42" t="s">
@@ -5415,19 +5414,19 @@
         <v>128.0740740740741</v>
       </c>
       <c r="Q43" t="s">
-        <v>40</v>
-      </c>
-      <c r="R43" s="20">
+        <v>72</v>
+      </c>
+      <c r="R43">
         <v>30.74074074074074</v>
       </c>
       <c r="S43" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="T43" s="16">
         <v>58.518518518518512</v>
       </c>
       <c r="U43" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="V43" s="19">
         <v>96.296296296296291</v>
@@ -5435,7 +5434,7 @@
       <c r="W43" t="s">
         <v>39</v>
       </c>
-      <c r="X43" s="20">
+      <c r="X43">
         <v>85.18518518518519</v>
       </c>
       <c r="Y43">
@@ -5488,10 +5487,10 @@
       <c r="D44">
         <v>131.2077959358927</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44">
         <v>40728</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44">
         <v>3325</v>
       </c>
       <c r="G44">
@@ -5525,27 +5524,27 @@
         <v>128.43333333333331</v>
       </c>
       <c r="Q44" t="s">
-        <v>44</v>
-      </c>
-      <c r="R44" s="20">
+        <v>70</v>
+      </c>
+      <c r="R44">
         <v>32.592592592592602</v>
       </c>
       <c r="S44" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="T44" s="16">
         <v>55.925925925925917</v>
       </c>
       <c r="U44" t="s">
-        <v>36</v>
-      </c>
-      <c r="V44" s="20">
+        <v>35</v>
+      </c>
+      <c r="V44">
         <v>88.888888888888886</v>
       </c>
       <c r="W44" t="s">
         <v>39</v>
       </c>
-      <c r="X44" s="20">
+      <c r="X44">
         <v>85.18518518518519</v>
       </c>
       <c r="Y44">
@@ -5572,7 +5571,7 @@
       <c r="AF44">
         <v>5</v>
       </c>
-      <c r="AG44" s="20">
+      <c r="AG44">
         <v>47</v>
       </c>
       <c r="AH44" s="17">
@@ -5589,73 +5588,81 @@
       <c r="A45">
         <v>52</v>
       </c>
-      <c r="B45"/>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
       <c r="S45"/>
-      <c r="T45" s="16"/>
+      <c r="T45"/>
       <c r="U45"/>
+      <c r="V45"/>
       <c r="W45"/>
-      <c r="X45" s="16"/>
+      <c r="X45"/>
       <c r="Y45"/>
       <c r="Z45"/>
       <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45"/>
-      <c r="AE45"/>
       <c r="AF45"/>
-      <c r="AG45" s="15"/>
+      <c r="AG45"/>
+      <c r="AH45"/>
+      <c r="AI45"/>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>53</v>
       </c>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AF46"/>
+      <c r="AG46"/>
+      <c r="AH46"/>
+      <c r="AI46"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>54</v>
       </c>
+      <c r="AF47"/>
+      <c r="AG47"/>
+      <c r="AH47"/>
+      <c r="AI47"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>55</v>
       </c>
+      <c r="AF48"/>
+      <c r="AG48"/>
+      <c r="AH48"/>
+      <c r="AI48"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>56</v>
       </c>
+      <c r="AF49"/>
+      <c r="AG49"/>
+      <c r="AH49"/>
+      <c r="AI49"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>60</v>
       </c>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8CE7B9-0C72-4646-8480-CD9CBC9AC53E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADAD014-03D1-4306-90EC-F90C352FB4FE}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="2820" windowWidth="22860" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="130" windowWidth="28800" windowHeight="18710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="95">
   <si>
     <t>Trung bình/Kỳ</t>
   </si>
@@ -139,172 +139,172 @@
     <t>85/270</t>
   </si>
   <si>
-    <t>154/270</t>
+    <t>178/270</t>
+  </si>
+  <si>
+    <t>25/27</t>
+  </si>
+  <si>
+    <t>22/27</t>
+  </si>
+  <si>
+    <t>100/270</t>
+  </si>
+  <si>
+    <t>168/270</t>
   </si>
   <si>
     <t>24/27</t>
   </si>
   <si>
-    <t>22/27</t>
-  </si>
-  <si>
-    <t>100/270</t>
-  </si>
-  <si>
-    <t>147/270</t>
+    <t>21/27</t>
+  </si>
+  <si>
+    <t>90/270</t>
+  </si>
+  <si>
+    <t>176/270</t>
+  </si>
+  <si>
+    <t>95/270</t>
+  </si>
+  <si>
+    <t>170/270</t>
+  </si>
+  <si>
+    <t>93/270</t>
+  </si>
+  <si>
+    <t>26/27</t>
   </si>
   <si>
     <t>23/27</t>
   </si>
   <si>
+    <t>66/270</t>
+  </si>
+  <si>
+    <t>197/270</t>
+  </si>
+  <si>
+    <t>92/270</t>
+  </si>
+  <si>
+    <t>175/270</t>
+  </si>
+  <si>
+    <t>79/270</t>
+  </si>
+  <si>
+    <t>187/270</t>
+  </si>
+  <si>
+    <t>27/27</t>
+  </si>
+  <si>
+    <t>87/270</t>
+  </si>
+  <si>
+    <t>101/270</t>
+  </si>
+  <si>
+    <t>164/270</t>
+  </si>
+  <si>
+    <t>91/270</t>
+  </si>
+  <si>
+    <t>177/270</t>
+  </si>
+  <si>
+    <t>112/270</t>
+  </si>
+  <si>
+    <t>157/270</t>
+  </si>
+  <si>
+    <t>18/27</t>
+  </si>
+  <si>
+    <t>96/270</t>
+  </si>
+  <si>
+    <t>171/270</t>
+  </si>
+  <si>
+    <t>19/27</t>
+  </si>
+  <si>
+    <t>86/270</t>
+  </si>
+  <si>
+    <t>166/270</t>
+  </si>
+  <si>
+    <t>88/270</t>
+  </si>
+  <si>
+    <t>83/270</t>
+  </si>
+  <si>
+    <t>183/270</t>
+  </si>
+  <si>
     <t>20/27</t>
   </si>
   <si>
-    <t>90/270</t>
+    <t>84/270</t>
+  </si>
+  <si>
+    <t>82/270</t>
+  </si>
+  <si>
+    <t>185/270</t>
+  </si>
+  <si>
+    <t>174/270</t>
+  </si>
+  <si>
+    <t>180/270</t>
+  </si>
+  <si>
+    <t>94/270</t>
+  </si>
+  <si>
+    <t>169/270</t>
+  </si>
+  <si>
+    <t>89/270</t>
+  </si>
+  <si>
+    <t>81/270</t>
+  </si>
+  <si>
+    <t>182/270</t>
+  </si>
+  <si>
+    <t>186/270</t>
+  </si>
+  <si>
+    <t>102/270</t>
+  </si>
+  <si>
+    <t>163/270</t>
+  </si>
+  <si>
+    <t>70/270</t>
+  </si>
+  <si>
+    <t>196/270</t>
+  </si>
+  <si>
+    <t>172/270</t>
   </si>
   <si>
     <t>162/270</t>
   </si>
   <si>
-    <t>25/27</t>
-  </si>
-  <si>
-    <t>95/270</t>
-  </si>
-  <si>
-    <t>153/270</t>
-  </si>
-  <si>
-    <t>21/27</t>
-  </si>
-  <si>
-    <t>93/270</t>
-  </si>
-  <si>
-    <t>66/270</t>
-  </si>
-  <si>
-    <t>167/270</t>
-  </si>
-  <si>
-    <t>92/270</t>
-  </si>
-  <si>
-    <t>155/270</t>
-  </si>
-  <si>
-    <t>79/270</t>
-  </si>
-  <si>
-    <t>159/270</t>
-  </si>
-  <si>
-    <t>87/270</t>
-  </si>
-  <si>
-    <t>158/270</t>
-  </si>
-  <si>
-    <t>101/270</t>
-  </si>
-  <si>
-    <t>143/270</t>
-  </si>
-  <si>
-    <t>91/270</t>
-  </si>
-  <si>
-    <t>27/27</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>112/270</t>
-  </si>
-  <si>
-    <t>140/270</t>
-  </si>
-  <si>
-    <t>16/27</t>
-  </si>
-  <si>
-    <t>96/270</t>
-  </si>
-  <si>
-    <t>19/27</t>
-  </si>
-  <si>
-    <t>18/27</t>
-  </si>
-  <si>
-    <t>86/270</t>
-  </si>
-  <si>
-    <t>146/270</t>
-  </si>
-  <si>
-    <t>138/270</t>
-  </si>
-  <si>
-    <t>88/270</t>
-  </si>
-  <si>
-    <t>144/270</t>
-  </si>
-  <si>
-    <t>83/270</t>
-  </si>
-  <si>
-    <t>156/270</t>
-  </si>
-  <si>
-    <t>84/270</t>
-  </si>
-  <si>
-    <t>82/270</t>
-  </si>
-  <si>
-    <t>170/270</t>
-  </si>
-  <si>
-    <t>152/270</t>
-  </si>
-  <si>
-    <t>94/270</t>
-  </si>
-  <si>
-    <t>149/270</t>
-  </si>
-  <si>
-    <t>148/270</t>
-  </si>
-  <si>
-    <t>89/270</t>
-  </si>
-  <si>
-    <t>157/270</t>
-  </si>
-  <si>
-    <t>81/270</t>
-  </si>
-  <si>
     <t>173/270</t>
-  </si>
-  <si>
-    <t>161/270</t>
-  </si>
-  <si>
-    <t>169/270</t>
-  </si>
-  <si>
-    <t>102/270</t>
-  </si>
-  <si>
-    <t>70/270</t>
-  </si>
-  <si>
-    <t>151/270</t>
   </si>
   <si>
     <t>100-350</t>
@@ -330,7 +330,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,14 +354,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7" tint="0.59999389629810485"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7"/>
+      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -412,24 +405,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -443,6 +418,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -480,8 +473,7 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -493,18 +485,13 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -521,6 +508,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -805,54 +796,55 @@
   <dimension ref="A1:AM53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9" style="20" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" style="20" customWidth="1"/>
-    <col min="7" max="7" width="8.453125" style="20" customWidth="1"/>
-    <col min="8" max="15" width="6.453125" style="20" customWidth="1"/>
-    <col min="16" max="16" width="8" style="20" customWidth="1"/>
-    <col min="17" max="17" width="9" style="20" customWidth="1"/>
-    <col min="18" max="20" width="9.1796875" style="20" customWidth="1"/>
-    <col min="21" max="21" width="17.81640625" style="20" customWidth="1"/>
-    <col min="22" max="24" width="16.90625" style="20" customWidth="1"/>
-    <col min="25" max="29" width="9.26953125" style="20" customWidth="1"/>
-    <col min="30" max="30" width="9.26953125" style="21" customWidth="1"/>
-    <col min="31" max="33" width="9.26953125" style="20" customWidth="1"/>
-    <col min="34" max="34" width="25.7265625" style="17" customWidth="1"/>
-    <col min="35" max="36" width="18.7265625" style="17" customWidth="1"/>
-    <col min="37" max="39" width="6.54296875" style="20" customWidth="1"/>
+    <col min="2" max="2" width="9" style="14" customWidth="1"/>
+    <col min="3" max="3" width="8.36328125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" style="14" customWidth="1"/>
+    <col min="8" max="15" width="6.453125" style="14" customWidth="1"/>
+    <col min="16" max="16" width="8" style="14" customWidth="1"/>
+    <col min="17" max="17" width="9" style="14" customWidth="1"/>
+    <col min="18" max="20" width="9.1796875" style="14" customWidth="1"/>
+    <col min="21" max="21" width="17.81640625" style="14" customWidth="1"/>
+    <col min="22" max="24" width="16.90625" style="14" customWidth="1"/>
+    <col min="25" max="29" width="9.26953125" style="14" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="9.26953125" style="15" customWidth="1"/>
+    <col min="31" max="33" width="9.26953125" style="14" customWidth="1"/>
+    <col min="34" max="34" width="25.7265625" style="13" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="18.7265625" style="13" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="18.7265625" style="13" customWidth="1"/>
+    <col min="37" max="39" width="6.54296875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Y1" s="22" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Y1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="25" t="s">
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="24" t="s">
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -864,7 +856,7 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -909,49 +901,49 @@
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="9">
+      <c r="Y2" s="8">
         <v>3</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="Z2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AA2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AB2" s="9">
+      <c r="AB2" s="8">
         <v>4</v>
       </c>
-      <c r="AC2" s="9" t="s">
+      <c r="AC2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="AE2" s="9">
+      <c r="AE2" s="8">
         <v>5</v>
       </c>
-      <c r="AF2" s="9" t="s">
+      <c r="AF2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AG2" s="9" t="s">
+      <c r="AG2" s="8" t="s">
         <v>27</v>
       </c>
       <c r="AH2" s="6" t="s">
@@ -965,8 +957,8 @@
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A3" s="13">
-        <v>10</v>
+      <c r="A3">
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -974,109 +966,109 @@
       <c r="C3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="16">
-        <v>137.9997796126882</v>
-      </c>
-      <c r="E3" s="16">
-        <v>40780</v>
+      <c r="D3">
+        <v>140.56670090323709</v>
+      </c>
+      <c r="E3">
+        <v>40771</v>
       </c>
       <c r="F3">
-        <v>3352</v>
+        <v>3410</v>
       </c>
       <c r="G3">
-        <v>128.93703703703699</v>
+        <v>128.7074074074074</v>
       </c>
       <c r="H3">
-        <v>11.577777777777779</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="I3">
-        <v>11.577777777777779</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="J3">
-        <v>10.32592592592593</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K3">
-        <v>0.81481481481481477</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L3">
-        <v>0.81481481481481477</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M3">
-        <v>0.1740740740740741</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N3">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O3" s="16">
-        <v>0.1962962962962963</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O3">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P3">
-        <v>128.33333333333329</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3">
-        <v>31.481481481481481</v>
+        <v>80</v>
+      </c>
+      <c r="R3" s="14">
+        <v>30</v>
       </c>
       <c r="S3" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3">
-        <v>57.037037037037038</v>
+        <v>53</v>
+      </c>
+      <c r="T3" s="14">
+        <v>69.259259259259252</v>
       </c>
       <c r="U3" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="V3" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="W3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3">
-        <v>81.481481481481481</v>
+        <v>46</v>
+      </c>
+      <c r="X3" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="Y3">
-        <v>34813</v>
+        <v>34751</v>
       </c>
       <c r="Z3">
-        <v>3126</v>
+        <v>3173</v>
       </c>
       <c r="AA3">
-        <v>37939</v>
+        <v>37924</v>
       </c>
       <c r="AB3">
-        <v>2356</v>
+        <v>2339</v>
       </c>
       <c r="AC3">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="AD3">
-        <v>2788</v>
+        <v>2792</v>
       </c>
       <c r="AE3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AF3">
-        <v>6</v>
-      </c>
-      <c r="AG3" s="15">
-        <v>53</v>
-      </c>
-      <c r="AH3" s="17">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="22">
+        <v>55</v>
+      </c>
+      <c r="AH3" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI3" s="17">
-        <v>195089322440</v>
-      </c>
-      <c r="AJ3" s="18">
-        <v>53720022440</v>
+      <c r="AI3" s="13">
+        <v>198718161100</v>
+      </c>
+      <c r="AJ3" s="25">
+        <v>57348861100</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -1085,108 +1077,108 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>113.2579520588982</v>
+        <v>139.96710940777101</v>
       </c>
       <c r="E4">
-        <v>40645</v>
+        <v>40738</v>
       </c>
       <c r="F4">
-        <v>3337</v>
+        <v>3404</v>
       </c>
       <c r="G4">
-        <v>128.43333333333331</v>
+        <v>128.67037037037039</v>
       </c>
       <c r="H4">
-        <v>11.62592592592593</v>
+        <v>11.640740740740741</v>
       </c>
       <c r="I4">
-        <v>11.62592592592593</v>
+        <v>11.640740740740741</v>
       </c>
       <c r="J4">
-        <v>10.351851851851849</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K4">
-        <v>0.73333333333333328</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="L4">
-        <v>0.73333333333333328</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M4">
-        <v>0.12592592592592591</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="O4">
-        <v>0.12592592592592591</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P4">
-        <v>128.38888888888891</v>
+        <v>128.14074074074071</v>
       </c>
       <c r="Q4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4">
-        <v>37.037037037037038</v>
+        <v>48</v>
+      </c>
+      <c r="R4" s="22">
+        <v>24.444444444444439</v>
       </c>
       <c r="S4" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4">
-        <v>54.444444444444443</v>
+        <v>49</v>
+      </c>
+      <c r="T4" s="22">
+        <v>72.962962962962962</v>
       </c>
       <c r="U4" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="V4" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W4" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4">
-        <v>74.074074074074076</v>
+        <v>35</v>
+      </c>
+      <c r="X4" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y4">
-        <v>34677</v>
+        <v>34741</v>
       </c>
       <c r="Z4">
-        <v>3139</v>
+        <v>3143</v>
       </c>
       <c r="AA4">
-        <v>37816</v>
+        <v>37884</v>
       </c>
       <c r="AB4">
-        <v>2461</v>
+        <v>2342</v>
       </c>
       <c r="AC4">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="AD4">
-        <v>2795</v>
+        <v>2802</v>
       </c>
       <c r="AE4">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>34</v>
-      </c>
-      <c r="AH4" s="17">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="22">
+        <v>52</v>
+      </c>
+      <c r="AH4" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI4" s="17">
-        <v>160111974020</v>
-      </c>
-      <c r="AJ4" s="17">
-        <v>18742674020</v>
+      <c r="AI4" s="13">
+        <v>197870522800</v>
+      </c>
+      <c r="AJ4" s="25">
+        <v>56501222800</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -1195,108 +1187,108 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>132.25466087757391</v>
+        <v>138.82829730358711</v>
       </c>
       <c r="E5">
-        <v>40777</v>
+        <v>40801</v>
       </c>
       <c r="F5">
-        <v>3411</v>
+        <v>3423</v>
       </c>
       <c r="G5">
-        <v>128.72962962962961</v>
+        <v>128.737037037037</v>
       </c>
       <c r="H5">
-        <v>11.80740740740741</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="I5">
-        <v>11.80740740740741</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="J5">
-        <v>10.3</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K5">
-        <v>0.81851851851851853</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L5">
-        <v>0.81851851851851853</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M5">
-        <v>0.18148148148148149</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N5">
-        <v>7.4074074074074077E-3</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O5">
-        <v>0.18888888888888891</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P5">
-        <v>128.11481481481479</v>
+        <v>128.0740740740741</v>
       </c>
       <c r="Q5" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="R5">
-        <v>33.333333333333329</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T5" s="15">
-        <v>60</v>
+        <v>34</v>
+      </c>
+      <c r="T5">
+        <v>65.925925925925924</v>
       </c>
       <c r="U5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V5" s="7">
-        <v>92.592592592592595</v>
+        <v>54</v>
+      </c>
+      <c r="V5" s="22">
+        <v>100</v>
       </c>
       <c r="W5" t="s">
         <v>35</v>
       </c>
-      <c r="X5" s="16">
-        <v>88.888888888888886</v>
+      <c r="X5" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y5">
-        <v>34757</v>
+        <v>34759</v>
       </c>
       <c r="Z5">
-        <v>3188</v>
+        <v>3201</v>
       </c>
       <c r="AA5">
-        <v>37945</v>
+        <v>37960</v>
       </c>
       <c r="AB5">
-        <v>2356</v>
+        <v>2349</v>
       </c>
       <c r="AC5">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AD5">
-        <v>2781</v>
+        <v>2786</v>
       </c>
       <c r="AE5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>2</v>
-      </c>
-      <c r="AG5" s="15">
-        <v>51</v>
-      </c>
-      <c r="AH5" s="17">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="22">
+        <v>55</v>
+      </c>
+      <c r="AH5" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI5" s="17">
-        <v>186967488300</v>
-      </c>
-      <c r="AJ5" s="17">
-        <v>45598188300</v>
+      <c r="AI5" s="13">
+        <v>196260592100</v>
+      </c>
+      <c r="AJ5" s="25">
+        <v>54891292100</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1305,108 +1297,108 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>128.49359344638481</v>
+        <v>138.6072636704009</v>
       </c>
       <c r="E6">
-        <v>40743</v>
+        <v>40780</v>
       </c>
       <c r="F6">
-        <v>3419</v>
+        <v>3454</v>
       </c>
       <c r="G6">
-        <v>128.6185185185185</v>
+        <v>128.58148148148149</v>
       </c>
       <c r="H6">
-        <v>11.829629629629631</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="I6">
-        <v>11.829629629629631</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="J6">
-        <v>10.28888888888889</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K6">
-        <v>0.81851851851851853</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="L6">
-        <v>0.81851851851851853</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="M6">
-        <v>0.14814814814814811</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N6">
-        <v>1.4814814814814821E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O6">
-        <v>0.162962962962963</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P6">
-        <v>128.0851851851852</v>
+        <v>127.99629629629629</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6">
-        <v>35.185185185185183</v>
+        <v>85</v>
+      </c>
+      <c r="R6" s="22">
+        <v>25.92592592592592</v>
       </c>
       <c r="S6" t="s">
-        <v>45</v>
-      </c>
-      <c r="T6">
-        <v>56.666666666666657</v>
+        <v>86</v>
+      </c>
+      <c r="T6" s="22">
+        <v>72.592592592592595</v>
       </c>
       <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="V6">
+        <v>39</v>
+      </c>
+      <c r="V6" s="14">
         <v>88.888888888888886</v>
       </c>
       <c r="W6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X6">
-        <v>77.777777777777786</v>
+        <v>36</v>
+      </c>
+      <c r="X6" s="14">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y6">
-        <v>34727</v>
+        <v>34717</v>
       </c>
       <c r="Z6">
-        <v>3194</v>
+        <v>3222</v>
       </c>
       <c r="AA6">
-        <v>37921</v>
+        <v>37939</v>
       </c>
       <c r="AB6">
-        <v>2381</v>
+        <v>2346</v>
       </c>
       <c r="AC6">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="AD6">
-        <v>2778</v>
+        <v>2788</v>
       </c>
       <c r="AE6">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AF6">
-        <v>4</v>
-      </c>
-      <c r="AG6">
-        <v>44</v>
-      </c>
-      <c r="AH6" s="17">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="22">
+        <v>53</v>
+      </c>
+      <c r="AH6" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI6" s="17">
-        <v>181650493600</v>
-      </c>
-      <c r="AJ6" s="17">
-        <v>40281193600</v>
+      <c r="AI6" s="13">
+        <v>195948118400</v>
+      </c>
+      <c r="AJ6" s="25">
+        <v>54578818400</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1415,108 +1407,108 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>127.4071409280516</v>
+        <v>138.19962750045451</v>
       </c>
       <c r="E7">
-        <v>40707</v>
-      </c>
-      <c r="F7" s="15">
-        <v>3470</v>
+        <v>40771</v>
+      </c>
+      <c r="F7">
+        <v>3393</v>
       </c>
       <c r="G7">
-        <v>128.28888888888889</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="H7">
-        <v>11.9962962962963</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="I7">
-        <v>11.9962962962963</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="J7">
-        <v>10.31851851851852</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K7">
-        <v>0.8481481481481481</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="L7">
-        <v>0.8481481481481481</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="M7">
-        <v>0.15555555555555561</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N7">
-        <v>7.4074074074074077E-3</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O7">
-        <v>0.162962962962963</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P7">
-        <v>127.8962962962963</v>
+        <v>128.17037037037039</v>
       </c>
       <c r="Q7" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="R7">
-        <v>34.444444444444443</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S7" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="T7">
-        <v>57.037037037037038</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="U7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V7">
-        <v>88.888888888888886</v>
+        <v>54</v>
+      </c>
+      <c r="V7" s="22">
+        <v>100</v>
       </c>
       <c r="W7" t="s">
-        <v>36</v>
-      </c>
-      <c r="X7">
-        <v>81.481481481481481</v>
+        <v>46</v>
+      </c>
+      <c r="X7" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="Y7">
-        <v>34638</v>
+        <v>34749</v>
       </c>
       <c r="Z7">
-        <v>3239</v>
+        <v>3175</v>
       </c>
       <c r="AA7">
-        <v>37877</v>
+        <v>37924</v>
       </c>
       <c r="AB7">
-        <v>2381</v>
+        <v>2360</v>
       </c>
       <c r="AC7">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AD7">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="AE7">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AF7">
-        <v>2</v>
-      </c>
-      <c r="AG7">
-        <v>44</v>
-      </c>
-      <c r="AH7" s="17">
+        <v>6</v>
+      </c>
+      <c r="AG7" s="22">
+        <v>55</v>
+      </c>
+      <c r="AH7" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI7" s="17">
-        <v>180114583280</v>
-      </c>
-      <c r="AJ7" s="17">
-        <v>38745283280</v>
+      <c r="AI7" s="13">
+        <v>195371846000</v>
+      </c>
+      <c r="AJ7" s="25">
+        <v>54002546000</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
-        <v>15</v>
+      <c r="A8">
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -1524,109 +1516,109 @@
       <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="15">
-        <v>143.94343354603859</v>
+      <c r="D8">
+        <v>138.19172896802911</v>
       </c>
       <c r="E8">
-        <v>40738</v>
+        <v>40771</v>
       </c>
       <c r="F8">
-        <v>3404</v>
+        <v>3411</v>
       </c>
       <c r="G8">
-        <v>128.67037037037039</v>
+        <v>128.61481481481479</v>
       </c>
       <c r="H8">
-        <v>11.640740740740741</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="I8">
-        <v>11.640740740740741</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="J8">
-        <v>10.37777777777778</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K8">
-        <v>0.93333333333333335</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="L8">
-        <v>0.93333333333333335</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="M8">
-        <v>0.15925925925925929</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N8">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="O8" s="16">
-        <v>0.19259259259259259</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O8">
+        <v>0.20370370370370369</v>
       </c>
       <c r="P8">
-        <v>128.14074074074071</v>
+        <v>128.11481481481479</v>
       </c>
       <c r="Q8" t="s">
-        <v>48</v>
-      </c>
-      <c r="R8" s="15">
-        <v>24.444444444444439</v>
+        <v>58</v>
+      </c>
+      <c r="R8">
+        <v>33.703703703703702</v>
       </c>
       <c r="S8" t="s">
-        <v>49</v>
-      </c>
-      <c r="T8" s="15">
-        <v>61.851851851851848</v>
+        <v>59</v>
+      </c>
+      <c r="T8">
+        <v>65.555555555555557</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
-      </c>
-      <c r="V8" s="7">
-        <v>92.592592592592595</v>
+        <v>54</v>
+      </c>
+      <c r="V8" s="22">
+        <v>100</v>
       </c>
       <c r="W8" t="s">
-        <v>43</v>
-      </c>
-      <c r="X8" s="15">
-        <v>92.592592592592595</v>
+        <v>54</v>
+      </c>
+      <c r="X8" s="22">
+        <v>100</v>
       </c>
       <c r="Y8">
-        <v>34741</v>
+        <v>34726</v>
       </c>
       <c r="Z8">
-        <v>3143</v>
+        <v>3198</v>
       </c>
       <c r="AA8">
-        <v>37884</v>
+        <v>37924</v>
       </c>
       <c r="AB8">
-        <v>2342</v>
+        <v>2361</v>
       </c>
       <c r="AC8">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="AD8">
-        <v>2802</v>
+        <v>2792</v>
       </c>
       <c r="AE8">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="AF8">
-        <v>9</v>
-      </c>
-      <c r="AG8" s="15">
-        <v>52</v>
-      </c>
-      <c r="AH8" s="17">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="22">
+        <v>55</v>
+      </c>
+      <c r="AH8" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI8" s="17">
-        <v>203491824400</v>
-      </c>
-      <c r="AJ8" s="18">
-        <v>62122524400</v>
+      <c r="AI8" s="13">
+        <v>195360679900</v>
+      </c>
+      <c r="AJ8" s="25">
+        <v>53991379900</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1635,108 +1627,108 @@
         <v>32</v>
       </c>
       <c r="D9">
-        <v>132.3466032724219</v>
+        <v>137.4216820766602</v>
       </c>
       <c r="E9">
-        <v>40737</v>
+        <v>40801</v>
       </c>
       <c r="F9">
-        <v>3403</v>
+        <v>3370</v>
       </c>
       <c r="G9">
-        <v>128.59629629629629</v>
+        <v>128.88888888888891</v>
       </c>
       <c r="H9">
-        <v>11.78888888888889</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="I9">
-        <v>11.78888888888889</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="J9">
-        <v>10.31481481481481</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K9">
-        <v>0.79629629629629628</v>
+        <v>0.76296296296296295</v>
       </c>
       <c r="L9">
-        <v>0.79629629629629628</v>
+        <v>0.76296296296296295</v>
       </c>
       <c r="M9">
-        <v>0.15925925925925929</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N9">
-        <v>1.8518518518518521E-2</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O9">
-        <v>0.17777777777777781</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P9">
-        <v>128.14444444444439</v>
+        <v>128.28148148148151</v>
       </c>
       <c r="Q9" t="s">
         <v>50</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="14">
         <v>34.074074074074083</v>
       </c>
       <c r="S9" t="s">
+        <v>87</v>
+      </c>
+      <c r="T9" s="14">
+        <v>63.703703703703709</v>
+      </c>
+      <c r="U9" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" s="14">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W9" t="s">
+        <v>47</v>
+      </c>
+      <c r="X9" s="14">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="Y9">
+        <v>34800</v>
+      </c>
+      <c r="Z9">
+        <v>3160</v>
+      </c>
+      <c r="AA9">
+        <v>37960</v>
+      </c>
+      <c r="AB9">
+        <v>2360</v>
+      </c>
+      <c r="AC9">
+        <v>206</v>
+      </c>
+      <c r="AD9">
+        <v>2786</v>
+      </c>
+      <c r="AE9">
         <v>51</v>
       </c>
-      <c r="T9">
-        <v>57.407407407407398</v>
-      </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="V9">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X9">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y9">
-        <v>34721</v>
-      </c>
-      <c r="Z9">
-        <v>3183</v>
-      </c>
-      <c r="AA9">
-        <v>37904</v>
-      </c>
-      <c r="AB9">
-        <v>2378</v>
-      </c>
-      <c r="AC9">
-        <v>215</v>
-      </c>
-      <c r="AD9">
-        <v>2785</v>
-      </c>
-      <c r="AE9">
-        <v>43</v>
-      </c>
       <c r="AF9">
-        <v>5</v>
-      </c>
-      <c r="AG9">
-        <v>48</v>
-      </c>
-      <c r="AH9" s="17">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="22">
+        <v>55</v>
+      </c>
+      <c r="AH9" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI9" s="17">
-        <v>187097466620</v>
-      </c>
-      <c r="AJ9" s="17">
-        <v>45728166620</v>
+      <c r="AI9" s="13">
+        <v>194272070000</v>
+      </c>
+      <c r="AJ9" s="25">
+        <v>52902770000</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1745,25 +1737,25 @@
         <v>32</v>
       </c>
       <c r="D10">
-        <v>128.3768819680086</v>
+        <v>137.40609276554389</v>
       </c>
       <c r="E10">
-        <v>40700</v>
+        <v>40738</v>
       </c>
       <c r="F10">
-        <v>3369</v>
+        <v>3383</v>
       </c>
       <c r="G10">
-        <v>128.6333333333333</v>
+        <v>128.64814814814821</v>
       </c>
       <c r="H10">
-        <v>11.614814814814819</v>
+        <v>11.662962962962959</v>
       </c>
       <c r="I10">
-        <v>11.614814814814819</v>
+        <v>11.662962962962959</v>
       </c>
       <c r="J10">
-        <v>10.33333333333333</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K10">
         <v>0.8481481481481481</v>
@@ -1772,81 +1764,81 @@
         <v>0.8481481481481481</v>
       </c>
       <c r="M10">
-        <v>0.1444444444444444</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N10">
-        <v>1.4814814814814821E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O10">
-        <v>0.15925925925925929</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P10">
-        <v>128.27037037037039</v>
+        <v>128.22592592592591</v>
       </c>
       <c r="Q10" t="s">
-        <v>52</v>
-      </c>
-      <c r="R10" s="15">
-        <v>29.25925925925926</v>
+        <v>80</v>
+      </c>
+      <c r="R10">
+        <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>53</v>
-      </c>
-      <c r="T10" s="16">
-        <v>58.888888888888893</v>
+        <v>82</v>
+      </c>
+      <c r="T10">
+        <v>68.888888888888886</v>
       </c>
       <c r="U10" t="s">
-        <v>43</v>
-      </c>
-      <c r="V10" s="7">
-        <v>92.592592592592595</v>
+        <v>46</v>
+      </c>
+      <c r="V10" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="W10" t="s">
-        <v>36</v>
-      </c>
-      <c r="X10">
-        <v>81.481481481481481</v>
+        <v>39</v>
+      </c>
+      <c r="X10" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y10">
-        <v>34731</v>
+        <v>34735</v>
       </c>
       <c r="Z10">
-        <v>3136</v>
+        <v>3149</v>
       </c>
       <c r="AA10">
-        <v>37867</v>
+        <v>37884</v>
       </c>
       <c r="AB10">
-        <v>2389</v>
+        <v>2365</v>
       </c>
       <c r="AC10">
         <v>229</v>
       </c>
       <c r="AD10">
-        <v>2790</v>
+        <v>2802</v>
       </c>
       <c r="AE10">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="AF10">
-        <v>4</v>
-      </c>
-      <c r="AG10">
-        <v>43</v>
-      </c>
-      <c r="AH10" s="17">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="22">
+        <v>52</v>
+      </c>
+      <c r="AH10" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI10" s="17">
-        <v>181485499400</v>
-      </c>
-      <c r="AJ10" s="17">
-        <v>40116199400</v>
+      <c r="AI10" s="13">
+        <v>194250031500</v>
+      </c>
+      <c r="AJ10" s="25">
+        <v>52880731500</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1855,108 +1847,108 @@
         <v>32</v>
       </c>
       <c r="D11">
-        <v>130.98891603764039</v>
+        <v>137.07237809057551</v>
       </c>
       <c r="E11">
-        <v>40715</v>
+        <v>40780</v>
       </c>
       <c r="F11">
-        <v>3314</v>
+        <v>3352</v>
       </c>
       <c r="G11">
-        <v>128.85925925925929</v>
+        <v>128.93703703703699</v>
       </c>
       <c r="H11">
-        <v>11.4037037037037</v>
+        <v>11.577777777777779</v>
       </c>
       <c r="I11">
-        <v>11.4037037037037</v>
+        <v>11.577777777777779</v>
       </c>
       <c r="J11">
-        <v>10.36296296296296</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K11">
-        <v>0.85555555555555551</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="L11">
-        <v>0.85555555555555551</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="M11">
-        <v>0.15555555555555561</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N11">
-        <v>1.4814814814814821E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O11">
-        <v>0.17037037037037039</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P11">
-        <v>128.47407407407411</v>
+        <v>128.33333333333329</v>
       </c>
       <c r="Q11" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="R11">
-        <v>32.222222222222221</v>
+        <v>31.481481481481481</v>
       </c>
       <c r="S11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="16">
-        <v>58.518518518518512</v>
+        <v>34</v>
+      </c>
+      <c r="T11">
+        <v>65.925925925925924</v>
       </c>
       <c r="U11" t="s">
         <v>35</v>
       </c>
-      <c r="V11">
-        <v>88.888888888888886</v>
+      <c r="V11" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W11" t="s">
-        <v>39</v>
-      </c>
-      <c r="X11">
-        <v>85.18518518518519</v>
+        <v>36</v>
+      </c>
+      <c r="X11" s="14">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y11">
-        <v>34792</v>
+        <v>34813</v>
       </c>
       <c r="Z11">
-        <v>3079</v>
+        <v>3126</v>
       </c>
       <c r="AA11">
-        <v>37871</v>
+        <v>37939</v>
       </c>
       <c r="AB11">
-        <v>2383</v>
+        <v>2356</v>
       </c>
       <c r="AC11">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="AD11">
-        <v>2798</v>
+        <v>2788</v>
       </c>
       <c r="AE11">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AF11">
-        <v>4</v>
-      </c>
-      <c r="AG11">
-        <v>46</v>
-      </c>
-      <c r="AH11" s="17">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="22">
+        <v>53</v>
+      </c>
+      <c r="AH11" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI11" s="17">
-        <v>185178113680</v>
-      </c>
-      <c r="AJ11" s="17">
-        <v>43808813680</v>
+      <c r="AI11" s="13">
+        <v>193778261400</v>
+      </c>
+      <c r="AJ11" s="25">
+        <v>52408961400</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1965,108 +1957,108 @@
         <v>32</v>
       </c>
       <c r="D12">
-        <v>121.16360259264211</v>
+        <v>136.9620354631451</v>
       </c>
       <c r="E12">
-        <v>40700</v>
+        <v>40738</v>
       </c>
       <c r="F12">
-        <v>3338</v>
+        <v>3461</v>
       </c>
       <c r="G12">
-        <v>128.67037037037039</v>
+        <v>128.33333333333329</v>
       </c>
       <c r="H12">
-        <v>11.6</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="I12">
-        <v>11.6</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="J12">
-        <v>10.32592592592593</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K12">
-        <v>0.75185185185185188</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L12">
-        <v>0.75185185185185188</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M12">
-        <v>0.1333333333333333</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N12">
-        <v>1.111111111111111E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O12">
-        <v>0.1444444444444444</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P12">
-        <v>128.38518518518521</v>
+        <v>127.89259259259261</v>
       </c>
       <c r="Q12" t="s">
-        <v>56</v>
-      </c>
-      <c r="R12">
-        <v>37.407407407407398</v>
+        <v>72</v>
+      </c>
+      <c r="R12" s="14">
+        <v>31.111111111111111</v>
       </c>
       <c r="S12" t="s">
-        <v>57</v>
-      </c>
-      <c r="T12">
-        <v>52.962962962962969</v>
+        <v>81</v>
+      </c>
+      <c r="T12" s="14">
+        <v>67.407407407407405</v>
       </c>
       <c r="U12" t="s">
+        <v>54</v>
+      </c>
+      <c r="V12" s="22">
+        <v>100</v>
+      </c>
+      <c r="W12" t="s">
         <v>39</v>
       </c>
-      <c r="V12">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="W12" t="s">
-        <v>40</v>
-      </c>
-      <c r="X12">
-        <v>74.074074074074076</v>
+      <c r="X12" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y12">
-        <v>34741</v>
+        <v>34650</v>
       </c>
       <c r="Z12">
-        <v>3132</v>
+        <v>3234</v>
       </c>
       <c r="AA12">
-        <v>37873</v>
+        <v>37884</v>
       </c>
       <c r="AB12">
-        <v>2429</v>
+        <v>2372</v>
       </c>
       <c r="AC12">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="AD12">
-        <v>2788</v>
+        <v>2802</v>
       </c>
       <c r="AE12">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AF12">
-        <v>3</v>
-      </c>
-      <c r="AG12">
-        <v>39</v>
-      </c>
-      <c r="AH12" s="17">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="22">
+        <v>52</v>
+      </c>
+      <c r="AH12" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI12" s="17">
-        <v>171288136840</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>29918836840</v>
+      <c r="AI12" s="13">
+        <v>193622270800</v>
+      </c>
+      <c r="AJ12" s="25">
+        <v>52252970800</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -2075,31 +2067,31 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <v>134.7273627300977</v>
-      </c>
-      <c r="E13" s="16">
+        <v>136.9543797698652</v>
+      </c>
+      <c r="E13">
         <v>40771</v>
       </c>
       <c r="F13">
-        <v>3411</v>
+        <v>3348</v>
       </c>
       <c r="G13">
-        <v>128.61481481481479</v>
+        <v>128.81481481481481</v>
       </c>
       <c r="H13">
-        <v>11.84444444444444</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="I13">
-        <v>11.84444444444444</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="J13">
         <v>10.34074074074074</v>
       </c>
       <c r="K13">
-        <v>0.78148148148148144</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="L13">
-        <v>0.78148148148148144</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="M13">
         <v>0.1962962962962963</v>
@@ -2107,50 +2099,50 @@
       <c r="N13">
         <v>7.4074074074074077E-3</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13">
         <v>0.20370370370370369</v>
       </c>
       <c r="P13">
-        <v>128.11481481481479</v>
+        <v>128.34814814814811</v>
       </c>
       <c r="Q13" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="R13">
-        <v>33.703703703703702</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="T13">
-        <v>57.407407407407398</v>
+        <v>65.925925925925924</v>
       </c>
       <c r="U13" t="s">
-        <v>59</v>
-      </c>
-      <c r="V13" s="15">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="V13" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W13" t="s">
-        <v>60</v>
-      </c>
-      <c r="X13" s="15">
-        <v>96.296296296296291</v>
+        <v>47</v>
+      </c>
+      <c r="X13" s="14">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y13">
-        <v>34726</v>
+        <v>34780</v>
       </c>
       <c r="Z13">
-        <v>3198</v>
+        <v>3144</v>
       </c>
       <c r="AA13">
         <v>37924</v>
       </c>
       <c r="AB13">
-        <v>2361</v>
+        <v>2370</v>
       </c>
       <c r="AC13">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="AD13">
         <v>2792</v>
@@ -2161,22 +2153,22 @@
       <c r="AF13">
         <v>2</v>
       </c>
-      <c r="AG13" s="15">
+      <c r="AG13" s="22">
         <v>55</v>
       </c>
-      <c r="AH13" s="17">
+      <c r="AH13" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI13" s="17">
-        <v>190463129600</v>
-      </c>
-      <c r="AJ13" s="17">
-        <v>49093829600</v>
+      <c r="AI13" s="13">
+        <v>193611448000</v>
+      </c>
+      <c r="AJ13" s="25">
+        <v>52242148000</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -2185,108 +2177,108 @@
         <v>32</v>
       </c>
       <c r="D14">
-        <v>120.4952906182601</v>
+        <v>135.68522974931619</v>
       </c>
       <c r="E14">
-        <v>40686</v>
+        <v>40738</v>
       </c>
       <c r="F14">
-        <v>3412</v>
+        <v>3222</v>
       </c>
       <c r="G14">
-        <v>128.3666666666667</v>
+        <v>129.1925925925926</v>
       </c>
       <c r="H14">
-        <v>11.885185185185181</v>
+        <v>11.11851851851852</v>
       </c>
       <c r="I14">
-        <v>11.885185185185181</v>
+        <v>11.11851851851852</v>
       </c>
       <c r="J14">
-        <v>10.3037037037037</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K14">
-        <v>0.73333333333333328</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L14">
-        <v>0.73333333333333328</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M14">
-        <v>0.1148148148148148</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N14">
-        <v>1.8518518518518521E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O14">
-        <v>0.1333333333333333</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P14">
-        <v>128.11111111111109</v>
+        <v>128.83703703703699</v>
       </c>
       <c r="Q14" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="R14">
-        <v>41.481481481481481</v>
+        <v>30</v>
       </c>
       <c r="S14" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="T14">
-        <v>51.851851851851848</v>
+        <v>67.407407407407405</v>
       </c>
       <c r="U14" t="s">
-        <v>40</v>
-      </c>
-      <c r="V14">
-        <v>74.074074074074076</v>
+        <v>39</v>
+      </c>
+      <c r="V14" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="W14" t="s">
-        <v>63</v>
-      </c>
-      <c r="X14">
-        <v>59.259259259259252</v>
+        <v>47</v>
+      </c>
+      <c r="X14" s="14">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y14">
-        <v>34659</v>
+        <v>34882</v>
       </c>
       <c r="Z14">
-        <v>3209</v>
+        <v>3002</v>
       </c>
       <c r="AA14">
-        <v>37868</v>
+        <v>37884</v>
       </c>
       <c r="AB14">
-        <v>2440</v>
+        <v>2375</v>
       </c>
       <c r="AC14">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="AD14">
-        <v>2782</v>
+        <v>2802</v>
       </c>
       <c r="AE14">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="AF14">
-        <v>5</v>
-      </c>
-      <c r="AG14">
-        <v>36</v>
-      </c>
-      <c r="AH14" s="17">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="22">
+        <v>52</v>
+      </c>
+      <c r="AH14" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI14" s="17">
-        <v>170343348880</v>
-      </c>
-      <c r="AJ14" s="17">
-        <v>28974048880</v>
+      <c r="AI14" s="13">
+        <v>191817259500</v>
+      </c>
+      <c r="AJ14" s="25">
+        <v>50447959500</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2295,108 +2287,108 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <v>120.5562728400013</v>
+        <v>135.58581099291001</v>
       </c>
       <c r="E15">
-        <v>40635</v>
+        <v>40777</v>
       </c>
       <c r="F15">
-        <v>3414</v>
+        <v>3411</v>
       </c>
       <c r="G15">
-        <v>128.07777777777781</v>
+        <v>128.72962962962961</v>
       </c>
       <c r="H15">
-        <v>11.851851851851849</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="I15">
-        <v>11.851851851851849</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="J15">
-        <v>10.425925925925929</v>
+        <v>10.3</v>
       </c>
       <c r="K15">
-        <v>0.78888888888888886</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L15">
-        <v>0.78888888888888886</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M15">
-        <v>0.14074074074074069</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N15">
-        <v>3.7037037037037038E-3</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O15">
-        <v>0.1444444444444444</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="P15">
-        <v>128.1037037037037</v>
+        <v>128.11481481481479</v>
       </c>
       <c r="Q15" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="R15">
-        <v>35.555555555555557</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S15" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T15">
-        <v>57.037037037037038</v>
+        <v>65.18518518518519</v>
       </c>
       <c r="U15" t="s">
-        <v>36</v>
-      </c>
-      <c r="V15">
-        <v>81.481481481481481</v>
+        <v>35</v>
+      </c>
+      <c r="V15" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W15" t="s">
-        <v>65</v>
-      </c>
-      <c r="X15">
-        <v>70.370370370370367</v>
+        <v>35</v>
+      </c>
+      <c r="X15" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y15">
-        <v>34581</v>
+        <v>34757</v>
       </c>
       <c r="Z15">
-        <v>3200</v>
+        <v>3188</v>
       </c>
       <c r="AA15">
-        <v>37781</v>
+        <v>37945</v>
       </c>
       <c r="AB15">
-        <v>2446</v>
+        <v>2356</v>
       </c>
       <c r="AC15">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AD15">
-        <v>2815</v>
+        <v>2781</v>
       </c>
       <c r="AE15">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AG15">
-        <v>39</v>
-      </c>
-      <c r="AH15" s="17">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="22">
+        <v>51</v>
+      </c>
+      <c r="AH15" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI15" s="17">
-        <v>170429559020</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>29060259020</v>
+      <c r="AI15" s="13">
+        <v>191676711900</v>
+      </c>
+      <c r="AJ15" s="25">
+        <v>50307411900</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -2405,108 +2397,108 @@
         <v>32</v>
       </c>
       <c r="D16">
-        <v>122.0712722776445</v>
+        <v>135.01545052567991</v>
       </c>
       <c r="E16">
-        <v>40670</v>
+        <v>40738</v>
       </c>
       <c r="F16">
-        <v>3413</v>
+        <v>3379</v>
       </c>
       <c r="G16">
-        <v>128.37407407407409</v>
+        <v>128.5703703703704</v>
       </c>
       <c r="H16">
-        <v>11.792592592592589</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="I16">
-        <v>11.792592592592589</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="J16">
-        <v>10.32592592592593</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K16">
-        <v>0.83703703703703702</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="L16">
-        <v>0.83703703703703702</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="M16">
-        <v>0.12592592592592591</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N16">
-        <v>1.111111111111111E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O16">
-        <v>0.13703703703703701</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P16">
-        <v>128.10740740740741</v>
+        <v>128.2222222222222</v>
       </c>
       <c r="Q16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="R16">
-        <v>33.703703703703702</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S16" t="s">
-        <v>55</v>
-      </c>
-      <c r="T16" s="16">
-        <v>58.518518518518512</v>
+        <v>81</v>
+      </c>
+      <c r="T16">
+        <v>67.407407407407405</v>
       </c>
       <c r="U16" t="s">
         <v>35</v>
       </c>
-      <c r="V16">
-        <v>88.888888888888886</v>
+      <c r="V16" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W16" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="X16">
-        <v>66.666666666666657</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y16">
-        <v>34661</v>
+        <v>34714</v>
       </c>
       <c r="Z16">
-        <v>3184</v>
+        <v>3170</v>
       </c>
       <c r="AA16">
-        <v>37845</v>
+        <v>37884</v>
       </c>
       <c r="AB16">
-        <v>2414</v>
+        <v>2387</v>
       </c>
       <c r="AC16">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="AD16">
-        <v>2788</v>
+        <v>2802</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AF16">
-        <v>3</v>
-      </c>
-      <c r="AG16">
-        <v>37</v>
-      </c>
-      <c r="AH16" s="17">
+        <v>2</v>
+      </c>
+      <c r="AG16" s="22">
+        <v>52</v>
+      </c>
+      <c r="AH16" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI16" s="17">
-        <v>172571303120</v>
-      </c>
-      <c r="AJ16" s="17">
-        <v>31202003120</v>
+      <c r="AI16" s="13">
+        <v>190870397300</v>
+      </c>
+      <c r="AJ16" s="13">
+        <v>49501097300</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -2515,60 +2507,60 @@
         <v>32</v>
       </c>
       <c r="D17">
-        <v>119.321995058333</v>
+        <v>134.64788132925611</v>
       </c>
       <c r="E17">
-        <v>40671</v>
+        <v>40780</v>
       </c>
       <c r="F17">
-        <v>3419</v>
+        <v>3318</v>
       </c>
       <c r="G17">
-        <v>128.31851851851849</v>
+        <v>128.9851851851852</v>
       </c>
       <c r="H17">
-        <v>11.84074074074074</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="I17">
-        <v>11.84074074074074</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="J17">
-        <v>10.33333333333333</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K17">
-        <v>0.82222222222222219</v>
+        <v>0.73703703703703705</v>
       </c>
       <c r="L17">
-        <v>0.82222222222222219</v>
+        <v>0.73703703703703705</v>
       </c>
       <c r="M17">
-        <v>0.14074074074074069</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O17">
-        <v>0.14074074074074069</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P17">
-        <v>128.0851851851852</v>
+        <v>128.44444444444451</v>
       </c>
       <c r="Q17" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R17">
-        <v>31.851851851851851</v>
+        <v>37.777777777777779</v>
       </c>
       <c r="S17" t="s">
-        <v>55</v>
-      </c>
-      <c r="T17" s="16">
-        <v>58.518518518518512</v>
+        <v>84</v>
+      </c>
+      <c r="T17">
+        <v>60.370370370370367</v>
       </c>
       <c r="U17" t="s">
-        <v>43</v>
-      </c>
-      <c r="V17" s="7">
+        <v>35</v>
+      </c>
+      <c r="V17" s="24">
         <v>92.592592592592595</v>
       </c>
       <c r="W17" t="s">
@@ -2578,45 +2570,45 @@
         <v>81.481481481481481</v>
       </c>
       <c r="Y17">
-        <v>34646</v>
+        <v>34826</v>
       </c>
       <c r="Z17">
-        <v>3197</v>
+        <v>3113</v>
       </c>
       <c r="AA17">
-        <v>37843</v>
+        <v>37939</v>
       </c>
       <c r="AB17">
-        <v>2416</v>
+        <v>2377</v>
       </c>
       <c r="AC17">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="AD17">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="AE17">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>38</v>
-      </c>
-      <c r="AH17" s="17">
+        <v>6</v>
+      </c>
+      <c r="AG17" s="22">
+        <v>53</v>
+      </c>
+      <c r="AH17" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI17" s="17">
-        <v>168684669160</v>
-      </c>
-      <c r="AJ17" s="17">
-        <v>27315369160</v>
+      <c r="AI17" s="13">
+        <v>190350767300</v>
+      </c>
+      <c r="AJ17" s="13">
+        <v>48981467300</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -2625,108 +2617,108 @@
         <v>32</v>
       </c>
       <c r="D18">
-        <v>126.6790426209934</v>
+        <v>134.38630954528321</v>
       </c>
       <c r="E18">
-        <v>40732</v>
+        <v>40738</v>
       </c>
       <c r="F18">
-        <v>3363</v>
+        <v>3283</v>
       </c>
       <c r="G18">
-        <v>128.76666666666671</v>
+        <v>128.9296296296296</v>
       </c>
       <c r="H18">
-        <v>11.607407407407409</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="I18">
-        <v>11.607407407407409</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="J18">
-        <v>10.31851851851852</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K18">
-        <v>0.84444444444444444</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="L18">
-        <v>0.84444444444444444</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="M18">
-        <v>0.162962962962963</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N18">
-        <v>3.7037037037037038E-3</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O18">
-        <v>0.16666666666666671</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P18">
-        <v>128.2925925925926</v>
+        <v>128.61111111111109</v>
       </c>
       <c r="Q18" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="R18">
-        <v>31.851851851851851</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S18" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="T18">
-        <v>57.037037037037038</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U18" t="s">
-        <v>43</v>
-      </c>
-      <c r="V18" s="7">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="V18" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="W18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="X18">
-        <v>81.481481481481481</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="Y18">
-        <v>34767</v>
+        <v>34811</v>
       </c>
       <c r="Z18">
-        <v>3134</v>
+        <v>3073</v>
       </c>
       <c r="AA18">
-        <v>37901</v>
+        <v>37884</v>
       </c>
       <c r="AB18">
-        <v>2378</v>
+        <v>2389</v>
       </c>
       <c r="AC18">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="AD18">
-        <v>2786</v>
+        <v>2802</v>
       </c>
       <c r="AE18">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AF18">
-        <v>1</v>
-      </c>
-      <c r="AG18">
-        <v>45</v>
-      </c>
-      <c r="AH18" s="17">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="22">
+        <v>52</v>
+      </c>
+      <c r="AH18" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI18" s="17">
-        <v>179085275800</v>
-      </c>
-      <c r="AJ18" s="17">
-        <v>37715975800</v>
+      <c r="AI18" s="13">
+        <v>189980985100</v>
+      </c>
+      <c r="AJ18" s="13">
+        <v>48611685100</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -2735,108 +2727,108 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <v>129.8896579809053</v>
+        <v>134.1387439139898</v>
       </c>
       <c r="E19">
-        <v>40727</v>
+        <v>40740</v>
       </c>
       <c r="F19">
-        <v>3298</v>
+        <v>3322</v>
       </c>
       <c r="G19">
-        <v>128.9148148148148</v>
+        <v>128.78518518518521</v>
       </c>
       <c r="H19">
-        <v>11.37407407407407</v>
+        <v>11.525925925925931</v>
       </c>
       <c r="I19">
-        <v>11.37407407407407</v>
+        <v>11.525925925925931</v>
       </c>
       <c r="J19">
-        <v>10.37407407407407</v>
+        <v>10.388888888888889</v>
       </c>
       <c r="K19">
-        <v>0.83333333333333337</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="L19">
-        <v>0.83333333333333337</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="M19">
-        <v>0.17037037037037039</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N19">
-        <v>7.4074074074074077E-3</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O19">
-        <v>0.17777777777777781</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="P19">
-        <v>128.5333333333333</v>
+        <v>128.44444444444451</v>
       </c>
       <c r="Q19" t="s">
+        <v>58</v>
+      </c>
+      <c r="R19" s="14">
+        <v>33.703703703703702</v>
+      </c>
+      <c r="S19" t="s">
         <v>44</v>
       </c>
-      <c r="R19">
-        <v>35.185185185185183</v>
-      </c>
-      <c r="S19" t="s">
-        <v>68</v>
-      </c>
-      <c r="T19">
-        <v>54.074074074074083</v>
+      <c r="T19" s="14">
+        <v>62.962962962962962</v>
       </c>
       <c r="U19" t="s">
-        <v>43</v>
-      </c>
-      <c r="V19" s="7">
-        <v>92.592592592592595</v>
+        <v>54</v>
+      </c>
+      <c r="V19" s="22">
+        <v>100</v>
       </c>
       <c r="W19" t="s">
-        <v>39</v>
-      </c>
-      <c r="X19">
-        <v>85.18518518518519</v>
+        <v>54</v>
+      </c>
+      <c r="X19" s="22">
+        <v>100</v>
       </c>
       <c r="Y19">
-        <v>34807</v>
+        <v>34772</v>
       </c>
       <c r="Z19">
-        <v>3071</v>
+        <v>3112</v>
       </c>
       <c r="AA19">
-        <v>37878</v>
+        <v>37884</v>
       </c>
       <c r="AB19">
-        <v>2384</v>
+        <v>2392</v>
       </c>
       <c r="AC19">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="AD19">
-        <v>2801</v>
+        <v>2805</v>
       </c>
       <c r="AE19">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF19">
-        <v>2</v>
-      </c>
-      <c r="AG19">
-        <v>48</v>
-      </c>
-      <c r="AH19" s="17">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="22">
+        <v>51</v>
+      </c>
+      <c r="AH19" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI19" s="17">
-        <v>183624100260</v>
-      </c>
-      <c r="AJ19" s="17">
-        <v>42254800260</v>
+      <c r="AI19" s="13">
+        <v>189631003300</v>
+      </c>
+      <c r="AJ19" s="13">
+        <v>48261703300</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -2845,43 +2837,43 @@
         <v>32</v>
       </c>
       <c r="D20">
-        <v>129.8617456689677</v>
+        <v>133.0426598940991</v>
       </c>
       <c r="E20">
-        <v>40740</v>
+        <v>40773</v>
       </c>
       <c r="F20">
-        <v>3322</v>
+        <v>3382</v>
       </c>
       <c r="G20">
-        <v>128.78518518518521</v>
+        <v>128.77407407407409</v>
       </c>
       <c r="H20">
-        <v>11.525925925925931</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="I20">
-        <v>11.525925925925931</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="J20">
-        <v>10.388888888888889</v>
+        <v>10.34814814814815</v>
       </c>
       <c r="K20">
-        <v>0.77407407407407403</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L20">
-        <v>0.77407407407407403</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M20">
-        <v>0.1851851851851852</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N20">
-        <v>3.7037037037037038E-3</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O20">
-        <v>0.18888888888888891</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="P20">
-        <v>128.44444444444451</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="Q20" t="s">
         <v>58</v>
@@ -2890,63 +2882,63 @@
         <v>33.703703703703702</v>
       </c>
       <c r="S20" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="T20">
-        <v>54.444444444444443</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U20" t="s">
-        <v>59</v>
-      </c>
-      <c r="V20" s="19">
-        <v>100</v>
+        <v>46</v>
+      </c>
+      <c r="V20" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="W20" t="s">
         <v>35</v>
       </c>
-      <c r="X20" s="16">
-        <v>88.888888888888886</v>
+      <c r="X20" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y20">
-        <v>34772</v>
+        <v>34769</v>
       </c>
       <c r="Z20">
-        <v>3112</v>
+        <v>3161</v>
       </c>
       <c r="AA20">
-        <v>37884</v>
+        <v>37930</v>
       </c>
       <c r="AB20">
-        <v>2392</v>
+        <v>2383</v>
       </c>
       <c r="AC20">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AD20">
-        <v>2805</v>
+        <v>2794</v>
       </c>
       <c r="AE20">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AF20">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="15">
-        <v>51</v>
-      </c>
-      <c r="AH20" s="17">
-        <v>141369300000</v>
-      </c>
-      <c r="AI20" s="17">
-        <v>183584640820</v>
-      </c>
-      <c r="AJ20" s="17">
-        <v>42215340820</v>
+        <v>6</v>
+      </c>
+      <c r="AG20" s="14">
+        <v>49</v>
+      </c>
+      <c r="AH20" s="13">
+        <v>141453000000</v>
+      </c>
+      <c r="AI20" s="13">
+        <v>188192833700</v>
+      </c>
+      <c r="AJ20" s="13">
+        <v>46739833700</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -2955,108 +2947,108 @@
         <v>32</v>
       </c>
       <c r="D21">
-        <v>126.4057725970207</v>
+        <v>133.03770415500401</v>
       </c>
       <c r="E21">
-        <v>40733</v>
+        <v>40727</v>
       </c>
       <c r="F21">
-        <v>3334</v>
+        <v>3298</v>
       </c>
       <c r="G21">
-        <v>128.72592592592591</v>
+        <v>128.9148148148148</v>
       </c>
       <c r="H21">
-        <v>11.607407407407409</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="I21">
-        <v>11.607407407407409</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="J21">
-        <v>10.35555555555556</v>
+        <v>10.37407407407407</v>
       </c>
       <c r="K21">
-        <v>0.73333333333333328</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L21">
-        <v>0.73333333333333328</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M21">
-        <v>0.16666666666666671</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="N21">
         <v>7.4074074074074077E-3</v>
       </c>
       <c r="O21">
-        <v>0.1740740740740741</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="P21">
-        <v>128.4</v>
+        <v>128.5333333333333</v>
       </c>
       <c r="Q21" t="s">
+        <v>43</v>
+      </c>
+      <c r="R21">
+        <v>35.185185185185183</v>
+      </c>
+      <c r="S21" t="s">
+        <v>67</v>
+      </c>
+      <c r="T21">
+        <v>61.481481481481481</v>
+      </c>
+      <c r="U21" t="s">
+        <v>46</v>
+      </c>
+      <c r="V21" s="23">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W21" t="s">
         <v>47</v>
       </c>
-      <c r="R21">
-        <v>34.444444444444443</v>
-      </c>
-      <c r="S21" t="s">
-        <v>69</v>
-      </c>
-      <c r="T21">
-        <v>51.111111111111107</v>
-      </c>
-      <c r="U21" t="s">
-        <v>60</v>
-      </c>
-      <c r="V21" s="19">
-        <v>96.296296296296291</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="X21">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="Y21">
+        <v>34807</v>
+      </c>
+      <c r="Z21">
+        <v>3071</v>
+      </c>
+      <c r="AA21">
+        <v>37878</v>
+      </c>
+      <c r="AB21">
+        <v>2384</v>
+      </c>
+      <c r="AC21">
+        <v>225</v>
+      </c>
+      <c r="AD21">
+        <v>2801</v>
+      </c>
+      <c r="AE21">
         <v>46</v>
-      </c>
-      <c r="X21">
-        <v>77.777777777777786</v>
-      </c>
-      <c r="Y21">
-        <v>34756</v>
-      </c>
-      <c r="Z21">
-        <v>3134</v>
-      </c>
-      <c r="AA21">
-        <v>37890</v>
-      </c>
-      <c r="AB21">
-        <v>2410</v>
-      </c>
-      <c r="AC21">
-        <v>198</v>
-      </c>
-      <c r="AD21">
-        <v>2796</v>
-      </c>
-      <c r="AE21">
-        <v>45</v>
       </c>
       <c r="AF21">
         <v>2</v>
       </c>
-      <c r="AG21">
-        <v>47</v>
-      </c>
-      <c r="AH21" s="17">
+      <c r="AG21" s="14">
+        <v>48</v>
+      </c>
+      <c r="AH21" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI21" s="17">
-        <v>178698955880</v>
-      </c>
-      <c r="AJ21" s="17">
-        <v>37329655880</v>
+      <c r="AI21" s="13">
+        <v>188074471100</v>
+      </c>
+      <c r="AJ21" s="13">
+        <v>46705171100</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -3065,108 +3057,108 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>126.3272132492698</v>
-      </c>
-      <c r="E22" s="15">
-        <v>40684</v>
+        <v>133.0172042303804</v>
+      </c>
+      <c r="E22">
+        <v>40788</v>
       </c>
       <c r="F22">
-        <v>3338</v>
+        <v>3325</v>
       </c>
       <c r="G22">
-        <v>128.62222222222221</v>
+        <v>129.04814814814819</v>
       </c>
       <c r="H22">
-        <v>11.514814814814811</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I22">
-        <v>11.514814814814811</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J22">
-        <v>10.392592592592591</v>
+        <v>10.329629629629631</v>
       </c>
       <c r="K22">
-        <v>0.83333333333333337</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L22">
-        <v>0.83333333333333337</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M22">
-        <v>0.13703703703703701</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="N22">
-        <v>1.4814814814814821E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O22">
-        <v>0.15185185185185179</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="P22">
-        <v>128.38518518518521</v>
+        <v>128.51111111111109</v>
       </c>
       <c r="Q22" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="R22">
-        <v>32.592592592592602</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S22" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="T22">
-        <v>53.333333333333343</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U22" t="s">
+        <v>46</v>
+      </c>
+      <c r="V22" s="23">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W22" t="s">
         <v>35</v>
       </c>
-      <c r="V22">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W22" t="s">
-        <v>65</v>
-      </c>
-      <c r="X22">
-        <v>70.370370370370367</v>
+      <c r="X22" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y22">
-        <v>34728</v>
+        <v>34843</v>
       </c>
       <c r="Z22">
-        <v>3109</v>
+        <v>3107</v>
       </c>
       <c r="AA22">
-        <v>37837</v>
+        <v>37950</v>
       </c>
       <c r="AB22">
-        <v>2417</v>
+        <v>2376</v>
       </c>
       <c r="AC22">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AD22">
-        <v>2806</v>
+        <v>2789</v>
       </c>
       <c r="AE22">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="AF22">
-        <v>4</v>
-      </c>
-      <c r="AG22">
-        <v>41</v>
-      </c>
-      <c r="AH22" s="17">
-        <v>141369300000</v>
-      </c>
-      <c r="AI22" s="17">
-        <v>178587897080</v>
-      </c>
-      <c r="AJ22" s="17">
-        <v>37218597080</v>
+        <v>1</v>
+      </c>
+      <c r="AG22" s="14">
+        <v>49</v>
+      </c>
+      <c r="AH22" s="13">
+        <v>141453000000</v>
+      </c>
+      <c r="AI22" s="13">
+        <v>188156825900</v>
+      </c>
+      <c r="AJ22" s="13">
+        <v>46703825900</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -3175,108 +3167,108 @@
         <v>32</v>
       </c>
       <c r="D23">
-        <v>129.4359784054954</v>
+        <v>132.21053559719121</v>
       </c>
       <c r="E23">
-        <v>40730</v>
+        <v>40737</v>
       </c>
       <c r="F23">
-        <v>3412</v>
+        <v>3403</v>
       </c>
       <c r="G23">
-        <v>128.65555555555559</v>
+        <v>128.59629629629629</v>
       </c>
       <c r="H23">
-        <v>11.733333333333331</v>
+        <v>11.78888888888889</v>
       </c>
       <c r="I23">
-        <v>11.733333333333331</v>
+        <v>11.78888888888889</v>
       </c>
       <c r="J23">
-        <v>10.3</v>
+        <v>10.31481481481481</v>
       </c>
       <c r="K23">
-        <v>0.8925925925925926</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L23">
-        <v>0.8925925925925926</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M23">
-        <v>0.15185185185185179</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N23">
-        <v>1.111111111111111E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O23">
-        <v>0.162962962962963</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="P23">
-        <v>128.11111111111109</v>
+        <v>128.14444444444439</v>
       </c>
       <c r="Q23" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="R23">
-        <v>30.74074074074074</v>
+        <v>34.074074074074083</v>
       </c>
       <c r="S23" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="T23">
-        <v>57.777777777777771</v>
+        <v>64.81481481481481</v>
       </c>
       <c r="U23" t="s">
+        <v>35</v>
+      </c>
+      <c r="V23" s="24">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W23" t="s">
         <v>39</v>
       </c>
-      <c r="V23">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="W23" t="s">
-        <v>40</v>
-      </c>
       <c r="X23">
-        <v>74.074074074074076</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="Y23">
-        <v>34737</v>
+        <v>34721</v>
       </c>
       <c r="Z23">
-        <v>3168</v>
+        <v>3183</v>
       </c>
       <c r="AA23">
-        <v>37905</v>
+        <v>37904</v>
       </c>
       <c r="AB23">
-        <v>2364</v>
+        <v>2378</v>
       </c>
       <c r="AC23">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="AD23">
-        <v>2781</v>
+        <v>2785</v>
       </c>
       <c r="AE23">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AF23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG23">
-        <v>44</v>
-      </c>
-      <c r="AH23" s="17">
+        <v>48</v>
+      </c>
+      <c r="AH23" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI23" s="17">
-        <v>182982736620</v>
-      </c>
-      <c r="AJ23" s="17">
-        <v>41613436620</v>
+      <c r="AI23" s="13">
+        <v>186905108700</v>
+      </c>
+      <c r="AJ23" s="13">
+        <v>45535808700</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -3285,108 +3277,108 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>133.5813685998304</v>
+        <v>131.9339636487031</v>
       </c>
       <c r="E24">
-        <v>40771</v>
+        <v>40773</v>
       </c>
       <c r="F24">
-        <v>3348</v>
+        <v>3434</v>
       </c>
       <c r="G24">
-        <v>128.81481481481481</v>
+        <v>128.65185185185189</v>
       </c>
       <c r="H24">
-        <v>11.64444444444444</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="I24">
-        <v>11.64444444444444</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="J24">
-        <v>10.34074074074074</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K24">
-        <v>0.74814814814814812</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="L24">
-        <v>0.74814814814814812</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="M24">
-        <v>0.1962962962962963</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N24">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O24" s="15">
-        <v>0.20370370370370369</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O24">
+        <v>0.17037037037037039</v>
       </c>
       <c r="P24">
-        <v>128.34814814814811</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q24" t="s">
+        <v>73</v>
+      </c>
+      <c r="R24">
+        <v>30.37037037037037</v>
+      </c>
+      <c r="S24" t="s">
         <v>74</v>
       </c>
-      <c r="R24">
-        <v>31.111111111111111</v>
-      </c>
-      <c r="S24" t="s">
-        <v>45</v>
-      </c>
       <c r="T24">
-        <v>56.666666666666657</v>
+        <v>68.518518518518519</v>
       </c>
       <c r="U24" t="s">
-        <v>35</v>
-      </c>
-      <c r="V24">
+        <v>39</v>
+      </c>
+      <c r="V24" s="14">
         <v>88.888888888888886</v>
       </c>
       <c r="W24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="X24">
         <v>77.777777777777786</v>
       </c>
       <c r="Y24">
-        <v>34780</v>
+        <v>34736</v>
       </c>
       <c r="Z24">
-        <v>3144</v>
+        <v>3205</v>
       </c>
       <c r="AA24">
-        <v>37924</v>
+        <v>37941</v>
       </c>
       <c r="AB24">
-        <v>2370</v>
+        <v>2374</v>
       </c>
       <c r="AC24">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="AD24">
-        <v>2792</v>
+        <v>2786</v>
       </c>
       <c r="AE24">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>2</v>
-      </c>
-      <c r="AG24" s="15">
-        <v>55</v>
-      </c>
-      <c r="AH24" s="17">
-        <v>141369300000</v>
-      </c>
-      <c r="AI24" s="17">
-        <v>188843045720</v>
-      </c>
-      <c r="AJ24" s="17">
-        <v>47473745720</v>
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>46</v>
+      </c>
+      <c r="AH24" s="13">
+        <v>141453000000</v>
+      </c>
+      <c r="AI24" s="13">
+        <v>186624549600</v>
+      </c>
+      <c r="AJ24" s="13">
+        <v>45171549600</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -3395,108 +3387,108 @@
         <v>32</v>
       </c>
       <c r="D25">
-        <v>127.7335127851654</v>
-      </c>
-      <c r="E25" s="16">
-        <v>40773</v>
-      </c>
-      <c r="F25" s="15">
-        <v>3434</v>
+        <v>131.9139846487179</v>
+      </c>
+      <c r="E25">
+        <v>40715</v>
+      </c>
+      <c r="F25">
+        <v>3314</v>
       </c>
       <c r="G25">
-        <v>128.65185185185189</v>
+        <v>128.85925925925929</v>
       </c>
       <c r="H25">
-        <v>11.87037037037037</v>
+        <v>11.4037037037037</v>
       </c>
       <c r="I25">
-        <v>11.87037037037037</v>
+        <v>11.4037037037037</v>
       </c>
       <c r="J25">
-        <v>10.31851851851852</v>
+        <v>10.36296296296296</v>
       </c>
       <c r="K25">
-        <v>0.84444444444444444</v>
+        <v>0.85555555555555551</v>
       </c>
       <c r="L25">
-        <v>0.84444444444444444</v>
+        <v>0.85555555555555551</v>
       </c>
       <c r="M25">
-        <v>0.16666666666666671</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N25">
-        <v>3.7037037037037038E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O25">
         <v>0.17037037037037039</v>
       </c>
       <c r="P25">
-        <v>128.10740740740741</v>
+        <v>128.47407407407411</v>
       </c>
       <c r="Q25" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="R25">
-        <v>30.37037037037037</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="S25" t="s">
-        <v>76</v>
-      </c>
-      <c r="T25" s="15">
-        <v>62.962962962962962</v>
+        <v>42</v>
+      </c>
+      <c r="T25">
+        <v>65.18518518518519</v>
       </c>
       <c r="U25" t="s">
         <v>39</v>
       </c>
-      <c r="V25">
-        <v>85.18518518518519</v>
+      <c r="V25" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="W25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X25">
-        <v>74.074074074074076</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="Y25">
-        <v>34736</v>
+        <v>34792</v>
       </c>
       <c r="Z25">
-        <v>3205</v>
+        <v>3079</v>
       </c>
       <c r="AA25">
-        <v>37941</v>
+        <v>37871</v>
       </c>
       <c r="AB25">
-        <v>2374</v>
+        <v>2383</v>
       </c>
       <c r="AC25">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AD25">
-        <v>2786</v>
+        <v>2798</v>
       </c>
       <c r="AE25">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AF25">
-        <v>1</v>
-      </c>
-      <c r="AG25">
+        <v>4</v>
+      </c>
+      <c r="AG25" s="14">
         <v>46</v>
       </c>
-      <c r="AH25" s="17">
-        <v>141453000000</v>
-      </c>
-      <c r="AI25" s="17">
-        <v>180682885840</v>
-      </c>
-      <c r="AJ25" s="17">
-        <v>39229885840</v>
+      <c r="AH25" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI25" s="13">
+        <v>186485876700</v>
+      </c>
+      <c r="AJ25" s="13">
+        <v>45116576700</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -3505,108 +3497,108 @@
         <v>32</v>
       </c>
       <c r="D26">
-        <v>128.77770443893019</v>
+        <v>131.4573185974607</v>
       </c>
       <c r="E26">
-        <v>40788</v>
+        <v>40730</v>
       </c>
       <c r="F26">
-        <v>3325</v>
+        <v>3412</v>
       </c>
       <c r="G26">
-        <v>129.04814814814819</v>
+        <v>128.65555555555559</v>
       </c>
       <c r="H26">
-        <v>11.50740740740741</v>
+        <v>11.733333333333331</v>
       </c>
       <c r="I26">
-        <v>11.50740740740741</v>
+        <v>11.733333333333331</v>
       </c>
       <c r="J26">
-        <v>10.329629629629631</v>
+        <v>10.3</v>
       </c>
       <c r="K26">
-        <v>0.8037037037037037</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="L26">
-        <v>0.8037037037037037</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="M26">
-        <v>0.17777777777777781</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N26">
-        <v>3.7037037037037038E-3</v>
+        <v>1.111111111111111E-2</v>
       </c>
       <c r="O26">
-        <v>0.18148148148148149</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P26">
-        <v>128.51111111111109</v>
+        <v>128.11111111111109</v>
       </c>
       <c r="Q26" t="s">
+        <v>69</v>
+      </c>
+      <c r="R26">
+        <v>30.74074074074074</v>
+      </c>
+      <c r="S26" t="s">
+        <v>70</v>
+      </c>
+      <c r="T26">
+        <v>67.777777777777786</v>
+      </c>
+      <c r="U26" t="s">
+        <v>39</v>
+      </c>
+      <c r="V26" s="14">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W26" t="s">
+        <v>71</v>
+      </c>
+      <c r="X26">
+        <v>74.074074074074076</v>
+      </c>
+      <c r="Y26">
+        <v>34737</v>
+      </c>
+      <c r="Z26">
+        <v>3168</v>
+      </c>
+      <c r="AA26">
+        <v>37905</v>
+      </c>
+      <c r="AB26">
+        <v>2364</v>
+      </c>
+      <c r="AC26">
+        <v>241</v>
+      </c>
+      <c r="AD26">
+        <v>2781</v>
+      </c>
+      <c r="AE26">
         <v>41</v>
       </c>
-      <c r="R26">
-        <v>33.333333333333329</v>
-      </c>
-      <c r="S26" t="s">
-        <v>45</v>
-      </c>
-      <c r="T26">
-        <v>56.666666666666657</v>
-      </c>
-      <c r="U26" t="s">
-        <v>43</v>
-      </c>
-      <c r="V26" s="7">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="W26" t="s">
-        <v>43</v>
-      </c>
-      <c r="X26" s="15">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="Y26">
-        <v>34843</v>
-      </c>
-      <c r="Z26">
-        <v>3107</v>
-      </c>
-      <c r="AA26">
-        <v>37950</v>
-      </c>
-      <c r="AB26">
-        <v>2376</v>
-      </c>
-      <c r="AC26">
-        <v>217</v>
-      </c>
-      <c r="AD26">
-        <v>2789</v>
-      </c>
-      <c r="AE26">
-        <v>48</v>
-      </c>
       <c r="AF26">
-        <v>1</v>
-      </c>
-      <c r="AG26">
-        <v>49</v>
-      </c>
-      <c r="AH26" s="17">
-        <v>141453000000</v>
-      </c>
-      <c r="AI26" s="17">
-        <v>182159926260</v>
-      </c>
-      <c r="AJ26" s="17">
-        <v>40706926260</v>
+        <v>3</v>
+      </c>
+      <c r="AG26" s="14">
+        <v>44</v>
+      </c>
+      <c r="AH26" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI26" s="13">
+        <v>185840291100</v>
+      </c>
+      <c r="AJ26" s="13">
+        <v>44470991100</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -3615,108 +3607,108 @@
         <v>32</v>
       </c>
       <c r="D27">
-        <v>126.70595083879449</v>
+        <v>130.87595363831099</v>
       </c>
       <c r="E27">
-        <v>40752</v>
+        <v>40755</v>
       </c>
       <c r="F27">
-        <v>3420</v>
+        <v>3426</v>
       </c>
       <c r="G27">
-        <v>128.66666666666671</v>
+        <v>128.6037037037037</v>
       </c>
       <c r="H27">
-        <v>11.796296296296299</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="I27">
-        <v>11.796296296296299</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="J27">
-        <v>10.31111111111111</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K27">
-        <v>0.86296296296296293</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L27">
-        <v>0.86296296296296293</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M27">
-        <v>0.15185185185185179</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N27">
-        <v>7.4074074074074077E-3</v>
+        <v>2.5925925925925929E-2</v>
       </c>
       <c r="O27">
-        <v>0.15925925925925929</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P27">
-        <v>128.1592592592593</v>
+        <v>128.137037037037</v>
       </c>
       <c r="Q27" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="R27">
-        <v>32.222222222222221</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S27" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="T27">
-        <v>56.296296296296298</v>
+        <v>65.925925925925924</v>
       </c>
       <c r="U27" t="s">
-        <v>60</v>
-      </c>
-      <c r="V27" s="19">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V27" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W27" t="s">
-        <v>35</v>
-      </c>
-      <c r="X27" s="16">
+        <v>39</v>
+      </c>
+      <c r="X27">
         <v>88.888888888888886</v>
       </c>
       <c r="Y27">
-        <v>34740</v>
+        <v>34723</v>
       </c>
       <c r="Z27">
-        <v>3185</v>
+        <v>3200</v>
       </c>
       <c r="AA27">
-        <v>37925</v>
+        <v>37923</v>
       </c>
       <c r="AB27">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="AC27">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="AD27">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="AE27">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF27">
-        <v>2</v>
-      </c>
-      <c r="AG27">
-        <v>43</v>
-      </c>
-      <c r="AH27" s="17">
+        <v>7</v>
+      </c>
+      <c r="AG27" s="14">
+        <v>46</v>
+      </c>
+      <c r="AH27" s="13">
         <v>141453000000</v>
       </c>
-      <c r="AI27" s="17">
-        <v>179229368640</v>
-      </c>
-      <c r="AJ27" s="17">
-        <v>37776368640</v>
+      <c r="AI27" s="13">
+        <v>185127962700</v>
+      </c>
+      <c r="AJ27" s="13">
+        <v>43674962700</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -3725,108 +3717,108 @@
         <v>32</v>
       </c>
       <c r="D28">
-        <v>126.3735355064933</v>
-      </c>
-      <c r="E28" s="15">
-        <v>40759</v>
+        <v>130.80206183379281</v>
+      </c>
+      <c r="E28">
+        <v>40732</v>
       </c>
       <c r="F28">
-        <v>3357</v>
+        <v>3363</v>
       </c>
       <c r="G28">
-        <v>128.862962962963</v>
+        <v>128.76666666666671</v>
       </c>
       <c r="H28">
-        <v>11.63703703703704</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I28">
-        <v>11.63703703703704</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J28">
-        <v>10.3</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K28">
-        <v>0.78148148148148144</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="L28">
-        <v>0.78148148148148144</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="M28">
-        <v>0.1444444444444444</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="N28">
-        <v>1.4814814814814821E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O28">
-        <v>0.15925925925925929</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="P28">
-        <v>128.39259259259259</v>
+        <v>128.2925925925926</v>
       </c>
       <c r="Q28" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="R28">
-        <v>34.814814814814817</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="S28" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="T28">
-        <v>55.185185185185183</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U28" t="s">
-        <v>60</v>
-      </c>
-      <c r="V28" s="19">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V28" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W28" t="s">
-        <v>35</v>
-      </c>
-      <c r="X28" s="16">
-        <v>88.888888888888886</v>
+        <v>36</v>
+      </c>
+      <c r="X28">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y28">
-        <v>34793</v>
+        <v>34767</v>
       </c>
       <c r="Z28">
-        <v>3142</v>
+        <v>3134</v>
       </c>
       <c r="AA28">
-        <v>37935</v>
+        <v>37901</v>
       </c>
       <c r="AB28">
-        <v>2398</v>
+        <v>2378</v>
       </c>
       <c r="AC28">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="AD28">
-        <v>2781</v>
+        <v>2786</v>
       </c>
       <c r="AE28">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AF28">
-        <v>4</v>
-      </c>
-      <c r="AG28">
-        <v>43</v>
-      </c>
-      <c r="AH28" s="17">
-        <v>141453000000</v>
-      </c>
-      <c r="AI28" s="17">
-        <v>178759157180</v>
-      </c>
-      <c r="AJ28" s="17">
-        <v>37306157180</v>
+        <v>1</v>
+      </c>
+      <c r="AG28" s="14">
+        <v>45</v>
+      </c>
+      <c r="AH28" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI28" s="13">
+        <v>184913959200</v>
+      </c>
+      <c r="AJ28" s="13">
+        <v>43544659200</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -3835,108 +3827,108 @@
         <v>32</v>
       </c>
       <c r="D29">
-        <v>134.21853146981681</v>
-      </c>
-      <c r="E29" s="15">
-        <v>40773</v>
+        <v>130.43550537492939</v>
+      </c>
+      <c r="E29">
+        <v>40707</v>
       </c>
       <c r="F29">
-        <v>3382</v>
+        <v>3470</v>
       </c>
       <c r="G29">
-        <v>128.77407407407409</v>
+        <v>128.28888888888889</v>
       </c>
       <c r="H29">
-        <v>11.707407407407411</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="I29">
-        <v>11.707407407407411</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="J29">
-        <v>10.34814814814815</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K29">
-        <v>0.79629629629629628</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L29">
-        <v>0.79629629629629628</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M29">
-        <v>0.15925925925925929</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N29">
-        <v>2.222222222222222E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O29">
-        <v>0.18148148148148149</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P29">
-        <v>128.30000000000001</v>
+        <v>127.8962962962963</v>
       </c>
       <c r="Q29" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="R29">
-        <v>33.703703703703702</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S29" t="s">
-        <v>53</v>
-      </c>
-      <c r="T29" s="16">
-        <v>58.888888888888893</v>
+        <v>44</v>
+      </c>
+      <c r="T29">
+        <v>62.962962962962962</v>
       </c>
       <c r="U29" t="s">
-        <v>60</v>
-      </c>
-      <c r="V29" s="19">
+        <v>46</v>
+      </c>
+      <c r="V29" s="23">
         <v>96.296296296296291</v>
       </c>
       <c r="W29" t="s">
-        <v>35</v>
-      </c>
-      <c r="X29" s="16">
-        <v>88.888888888888886</v>
+        <v>47</v>
+      </c>
+      <c r="X29">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y29">
-        <v>34769</v>
+        <v>34638</v>
       </c>
       <c r="Z29">
-        <v>3161</v>
+        <v>3239</v>
       </c>
       <c r="AA29">
-        <v>37930</v>
+        <v>37877</v>
       </c>
       <c r="AB29">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="AC29">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="AD29">
-        <v>2794</v>
+        <v>2786</v>
       </c>
       <c r="AE29">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF29">
-        <v>6</v>
-      </c>
-      <c r="AG29">
-        <v>49</v>
-      </c>
-      <c r="AH29" s="17">
-        <v>141453000000</v>
-      </c>
-      <c r="AI29" s="17">
-        <v>189856139320</v>
-      </c>
-      <c r="AJ29" s="17">
-        <v>48403139320</v>
+        <v>2</v>
+      </c>
+      <c r="AG29" s="14">
+        <v>44</v>
+      </c>
+      <c r="AH29" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI29" s="13">
+        <v>184395760900</v>
+      </c>
+      <c r="AJ29" s="13">
+        <v>43026460900</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -3945,108 +3937,108 @@
         <v>32</v>
       </c>
       <c r="D30">
-        <v>125.45177072243079</v>
-      </c>
-      <c r="E30" s="16">
-        <v>40718</v>
+        <v>129.69486055438909</v>
+      </c>
+      <c r="E30">
+        <v>40752</v>
       </c>
       <c r="F30">
-        <v>3381</v>
+        <v>3420</v>
       </c>
       <c r="G30">
-        <v>128.6333333333333</v>
+        <v>128.66666666666671</v>
       </c>
       <c r="H30">
-        <v>11.707407407407411</v>
+        <v>11.796296296296299</v>
       </c>
       <c r="I30">
-        <v>11.707407407407411</v>
+        <v>11.796296296296299</v>
       </c>
       <c r="J30">
-        <v>10.31851851851852</v>
+        <v>10.31111111111111</v>
       </c>
       <c r="K30">
-        <v>0.79629629629629628</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L30">
-        <v>0.79629629629629628</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M30">
-        <v>0.12962962962962959</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N30">
-        <v>1.8518518518518521E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O30">
-        <v>0.14814814814814811</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="P30">
-        <v>128.30370370370369</v>
+        <v>128.1592592592593</v>
       </c>
       <c r="Q30" t="s">
-        <v>37</v>
-      </c>
-      <c r="R30">
-        <v>37.037037037037038</v>
+        <v>55</v>
+      </c>
+      <c r="R30" s="14">
+        <v>32.222222222222221</v>
       </c>
       <c r="S30" t="s">
-        <v>80</v>
-      </c>
-      <c r="T30">
-        <v>54.814814814814817</v>
+        <v>76</v>
+      </c>
+      <c r="T30" s="14">
+        <v>66.666666666666657</v>
       </c>
       <c r="U30" t="s">
+        <v>46</v>
+      </c>
+      <c r="V30" s="23">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W30" t="s">
         <v>39</v>
       </c>
-      <c r="V30">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="W30" t="s">
-        <v>40</v>
-      </c>
       <c r="X30">
-        <v>74.074074074074076</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="Y30">
-        <v>34731</v>
+        <v>34740</v>
       </c>
       <c r="Z30">
-        <v>3161</v>
+        <v>3185</v>
       </c>
       <c r="AA30">
-        <v>37892</v>
+        <v>37925</v>
       </c>
       <c r="AB30">
-        <v>2411</v>
+        <v>2379</v>
       </c>
       <c r="AC30">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="AD30">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="AE30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AF30">
-        <v>5</v>
-      </c>
-      <c r="AG30">
-        <v>40</v>
-      </c>
-      <c r="AH30" s="17">
+        <v>2</v>
+      </c>
+      <c r="AG30" s="14">
+        <v>43</v>
+      </c>
+      <c r="AH30" s="13">
         <v>141453000000</v>
       </c>
-      <c r="AI30" s="17">
-        <v>177455293240</v>
-      </c>
-      <c r="AJ30" s="17">
-        <v>36002293240</v>
+      <c r="AI30" s="13">
+        <v>183457271100</v>
+      </c>
+      <c r="AJ30" s="13">
+        <v>42004271100</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4055,108 +4047,108 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <v>133.24790789873671</v>
+        <v>129.30531876439929</v>
       </c>
       <c r="E31">
-        <v>40755</v>
-      </c>
-      <c r="F31" s="15">
-        <v>3426</v>
+        <v>40733</v>
+      </c>
+      <c r="F31">
+        <v>3334</v>
       </c>
       <c r="G31">
-        <v>128.6037037037037</v>
+        <v>128.72592592592591</v>
       </c>
       <c r="H31">
-        <v>11.851851851851849</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I31">
-        <v>11.851851851851849</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J31">
-        <v>10.31851851851852</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="K31">
-        <v>0.81111111111111112</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L31">
-        <v>0.81111111111111112</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M31">
-        <v>0.1444444444444444</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N31">
-        <v>2.5925925925925929E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O31">
-        <v>0.17037037037037039</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="P31">
-        <v>128.137037037037</v>
+        <v>128.4</v>
       </c>
       <c r="Q31" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="R31">
-        <v>32.962962962962962</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S31" t="s">
-        <v>82</v>
-      </c>
-      <c r="T31" s="16">
-        <v>58.148148148148152</v>
+        <v>38</v>
+      </c>
+      <c r="T31">
+        <v>62.222222222222221</v>
       </c>
       <c r="U31" t="s">
-        <v>43</v>
-      </c>
-      <c r="V31" s="7">
-        <v>92.592592592592595</v>
+        <v>46</v>
+      </c>
+      <c r="V31" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="W31" t="s">
         <v>39</v>
       </c>
       <c r="X31">
-        <v>85.18518518518519</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="Y31">
-        <v>34723</v>
+        <v>34756</v>
       </c>
       <c r="Z31">
-        <v>3200</v>
+        <v>3134</v>
       </c>
       <c r="AA31">
-        <v>37923</v>
+        <v>37890</v>
       </c>
       <c r="AB31">
-        <v>2383</v>
+        <v>2410</v>
       </c>
       <c r="AC31">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="AD31">
-        <v>2786</v>
+        <v>2796</v>
       </c>
       <c r="AE31">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="AF31">
-        <v>7</v>
-      </c>
-      <c r="AG31">
-        <v>46</v>
-      </c>
-      <c r="AH31" s="17">
-        <v>141453000000</v>
-      </c>
-      <c r="AI31" s="17">
-        <v>188483163160</v>
-      </c>
-      <c r="AJ31" s="17">
-        <v>47030163160</v>
+        <v>2</v>
+      </c>
+      <c r="AG31" s="14">
+        <v>47</v>
+      </c>
+      <c r="AH31" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI31" s="13">
+        <v>182798024000</v>
+      </c>
+      <c r="AJ31" s="13">
+        <v>41428724000</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -4165,108 +4157,108 @@
         <v>32</v>
       </c>
       <c r="D32">
-        <v>123.7648688681046</v>
-      </c>
-      <c r="E32" s="16">
-        <v>40737</v>
-      </c>
-      <c r="F32" s="15">
-        <v>3458</v>
+        <v>129.28038824553849</v>
+      </c>
+      <c r="E32">
+        <v>40743</v>
+      </c>
+      <c r="F32">
+        <v>3419</v>
       </c>
       <c r="G32">
-        <v>128.41851851851851</v>
+        <v>128.6185185185185</v>
       </c>
       <c r="H32">
-        <v>11.988888888888891</v>
+        <v>11.829629629629631</v>
       </c>
       <c r="I32">
-        <v>11.988888888888891</v>
+        <v>11.829629629629631</v>
       </c>
       <c r="J32">
-        <v>10.31851851851852</v>
+        <v>10.28888888888889</v>
       </c>
       <c r="K32">
-        <v>0.81111111111111112</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L32">
-        <v>0.81111111111111112</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M32">
-        <v>0.1444444444444444</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="N32">
-        <v>7.4074074074074077E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O32">
-        <v>0.15185185185185179</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P32">
-        <v>128.0185185185185</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q32" t="s">
-        <v>81</v>
-      </c>
-      <c r="R32">
-        <v>32.962962962962962</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="14">
+        <v>35.185185185185183</v>
       </c>
       <c r="S32" t="s">
-        <v>45</v>
-      </c>
-      <c r="T32">
-        <v>56.666666666666657</v>
+        <v>44</v>
+      </c>
+      <c r="T32" s="14">
+        <v>62.962962962962962</v>
       </c>
       <c r="U32" t="s">
-        <v>46</v>
-      </c>
-      <c r="V32">
+        <v>35</v>
+      </c>
+      <c r="V32" s="24">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W32" t="s">
+        <v>40</v>
+      </c>
+      <c r="X32">
         <v>77.777777777777786</v>
       </c>
-      <c r="W32" t="s">
-        <v>65</v>
-      </c>
-      <c r="X32">
-        <v>70.370370370370367</v>
-      </c>
       <c r="Y32">
-        <v>34673</v>
+        <v>34727</v>
       </c>
       <c r="Z32">
-        <v>3237</v>
+        <v>3194</v>
       </c>
       <c r="AA32">
-        <v>37910</v>
+        <v>37921</v>
       </c>
       <c r="AB32">
-        <v>2403</v>
+        <v>2381</v>
       </c>
       <c r="AC32">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AD32">
-        <v>2786</v>
+        <v>2778</v>
       </c>
       <c r="AE32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF32">
-        <v>2</v>
-      </c>
-      <c r="AG32">
-        <v>41</v>
-      </c>
-      <c r="AH32" s="17">
-        <v>141453000000</v>
-      </c>
-      <c r="AI32" s="17">
-        <v>175069119960</v>
-      </c>
-      <c r="AJ32" s="17">
-        <v>33616119960</v>
+        <v>4</v>
+      </c>
+      <c r="AG32" s="14">
+        <v>44</v>
+      </c>
+      <c r="AH32" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI32" s="13">
+        <v>182762779900</v>
+      </c>
+      <c r="AJ32" s="13">
+        <v>41393479900</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -4275,108 +4267,108 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>131.30895267925919</v>
+        <v>129.1463196747809</v>
       </c>
       <c r="E33">
-        <v>40738</v>
+        <v>40700</v>
       </c>
       <c r="F33">
-        <v>3222</v>
+        <v>3369</v>
       </c>
       <c r="G33">
-        <v>129.1925925925926</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H33">
-        <v>11.11851851851852</v>
+        <v>11.614814814814819</v>
       </c>
       <c r="I33">
-        <v>11.11851851851852</v>
+        <v>11.614814814814819</v>
       </c>
       <c r="J33">
-        <v>10.37777777777778</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K33">
-        <v>0.81111111111111112</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L33">
-        <v>0.81111111111111112</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M33">
-        <v>0.18888888888888891</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N33">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="O33" s="16">
-        <v>0.19259259259259259</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O33">
+        <v>0.15925925925925929</v>
       </c>
       <c r="P33">
-        <v>128.83703703703699</v>
+        <v>128.27037037037039</v>
       </c>
       <c r="Q33" t="s">
-        <v>83</v>
-      </c>
-      <c r="R33" s="15">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="R33" s="14">
+        <v>29.25925925925926</v>
       </c>
       <c r="S33" t="s">
-        <v>82</v>
-      </c>
-      <c r="T33" s="16">
-        <v>58.148148148148152</v>
+        <v>53</v>
+      </c>
+      <c r="T33" s="14">
+        <v>69.259259259259252</v>
       </c>
       <c r="U33" t="s">
+        <v>54</v>
+      </c>
+      <c r="V33" s="22">
+        <v>100</v>
+      </c>
+      <c r="W33" t="s">
         <v>35</v>
       </c>
-      <c r="V33">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="X33" s="24">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="Y33">
+        <v>34731</v>
+      </c>
+      <c r="Z33">
+        <v>3136</v>
+      </c>
+      <c r="AA33">
+        <v>37867</v>
+      </c>
+      <c r="AB33">
+        <v>2389</v>
+      </c>
+      <c r="AC33">
+        <v>229</v>
+      </c>
+      <c r="AD33">
+        <v>2790</v>
+      </c>
+      <c r="AE33">
         <v>39</v>
       </c>
-      <c r="X33">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y33">
-        <v>34882</v>
-      </c>
-      <c r="Z33">
-        <v>3002</v>
-      </c>
-      <c r="AA33">
-        <v>37884</v>
-      </c>
-      <c r="AB33">
-        <v>2375</v>
-      </c>
-      <c r="AC33">
-        <v>219</v>
-      </c>
-      <c r="AD33">
-        <v>2802</v>
-      </c>
-      <c r="AE33">
-        <v>51</v>
-      </c>
       <c r="AF33">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="15">
-        <v>52</v>
-      </c>
-      <c r="AH33" s="17">
+        <v>4</v>
+      </c>
+      <c r="AG33" s="14">
+        <v>43</v>
+      </c>
+      <c r="AH33" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI33" s="17">
-        <v>185630547240</v>
-      </c>
-      <c r="AJ33" s="17">
-        <v>44261247240</v>
+      <c r="AI33" s="13">
+        <v>182573248100</v>
+      </c>
+      <c r="AJ33" s="13">
+        <v>41203948100</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A34" s="13">
-        <v>41</v>
+      <c r="A34">
+        <v>35</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -4384,109 +4376,109 @@
       <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="16">
-        <v>137.232633421825</v>
+      <c r="D34">
+        <v>127.00580383590309</v>
       </c>
       <c r="E34">
-        <v>40738</v>
+        <v>40759</v>
       </c>
       <c r="F34">
-        <v>3383</v>
+        <v>3357</v>
       </c>
       <c r="G34">
-        <v>128.64814814814821</v>
+        <v>128.862962962963</v>
       </c>
       <c r="H34">
-        <v>11.662962962962959</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="I34">
-        <v>11.662962962962959</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="J34">
-        <v>10.37777777777778</v>
+        <v>10.3</v>
       </c>
       <c r="K34">
-        <v>0.8481481481481481</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="L34">
-        <v>0.8481481481481481</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="M34">
-        <v>0.1740740740740741</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N34">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O34" s="16">
-        <v>0.19259259259259259</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O34">
+        <v>0.15925925925925929</v>
       </c>
       <c r="P34">
-        <v>128.22592592592591</v>
+        <v>128.39259259259259</v>
       </c>
       <c r="Q34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R34" s="15">
-        <v>30</v>
+        <v>77</v>
+      </c>
+      <c r="R34">
+        <v>34.814814814814817</v>
       </c>
       <c r="S34" t="s">
-        <v>84</v>
-      </c>
-      <c r="T34" s="15">
-        <v>64.074074074074076</v>
+        <v>75</v>
+      </c>
+      <c r="T34">
+        <v>64.444444444444443</v>
       </c>
       <c r="U34" t="s">
-        <v>43</v>
-      </c>
-      <c r="V34" s="7">
-        <v>92.592592592592595</v>
+        <v>46</v>
+      </c>
+      <c r="V34" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="W34" t="s">
         <v>35</v>
       </c>
-      <c r="X34" s="16">
-        <v>88.888888888888886</v>
+      <c r="X34" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y34">
-        <v>34735</v>
+        <v>34793</v>
       </c>
       <c r="Z34">
-        <v>3149</v>
+        <v>3142</v>
       </c>
       <c r="AA34">
-        <v>37884</v>
+        <v>37935</v>
       </c>
       <c r="AB34">
-        <v>2365</v>
+        <v>2398</v>
       </c>
       <c r="AC34">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AD34">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="AE34">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="AF34">
-        <v>5</v>
-      </c>
-      <c r="AG34" s="15">
-        <v>52</v>
-      </c>
-      <c r="AH34" s="17">
-        <v>141369300000</v>
-      </c>
-      <c r="AI34" s="17">
-        <v>194004813240</v>
-      </c>
-      <c r="AJ34" s="18">
-        <v>52635513240</v>
+        <v>4</v>
+      </c>
+      <c r="AG34">
+        <v>43</v>
+      </c>
+      <c r="AH34" s="13">
+        <v>141453000000</v>
+      </c>
+      <c r="AI34" s="13">
+        <v>179653519700</v>
+      </c>
+      <c r="AJ34" s="13">
+        <v>38200519700</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -4495,108 +4487,108 @@
         <v>32</v>
       </c>
       <c r="D35">
-        <v>131.7624941200105</v>
+        <v>126.93712022341479</v>
       </c>
       <c r="E35">
-        <v>40738</v>
+        <v>40684</v>
       </c>
       <c r="F35">
-        <v>3379</v>
+        <v>3338</v>
       </c>
       <c r="G35">
-        <v>128.5703703703704</v>
+        <v>128.62222222222221</v>
       </c>
       <c r="H35">
-        <v>11.74074074074074</v>
+        <v>11.514814814814811</v>
       </c>
       <c r="I35">
-        <v>11.74074074074074</v>
+        <v>11.514814814814811</v>
       </c>
       <c r="J35">
-        <v>10.37777777777778</v>
+        <v>10.392592592592591</v>
       </c>
       <c r="K35">
-        <v>0.76666666666666672</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L35">
-        <v>0.76666666666666672</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M35">
-        <v>0.1851851851851852</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N35">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O35" s="16">
-        <v>0.19259259259259259</v>
+        <v>1.4814814814814821E-2</v>
+      </c>
+      <c r="O35">
+        <v>0.15185185185185179</v>
       </c>
       <c r="P35">
-        <v>128.2222222222222</v>
+        <v>128.38518518518521</v>
       </c>
       <c r="Q35" t="s">
-        <v>74</v>
-      </c>
-      <c r="R35" s="15">
-        <v>31.111111111111111</v>
+        <v>68</v>
+      </c>
+      <c r="R35">
+        <v>32.592592592592602</v>
       </c>
       <c r="S35" t="s">
-        <v>85</v>
-      </c>
-      <c r="T35" s="16">
-        <v>59.629629629629633</v>
+        <v>51</v>
+      </c>
+      <c r="T35">
+        <v>64.81481481481481</v>
       </c>
       <c r="U35" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35">
+        <v>39</v>
+      </c>
+      <c r="V35" s="14">
         <v>88.888888888888886</v>
       </c>
       <c r="W35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X35">
-        <v>85.18518518518519</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y35">
-        <v>34714</v>
+        <v>34728</v>
       </c>
       <c r="Z35">
-        <v>3170</v>
+        <v>3109</v>
       </c>
       <c r="AA35">
-        <v>37884</v>
+        <v>37837</v>
       </c>
       <c r="AB35">
-        <v>2387</v>
+        <v>2417</v>
       </c>
       <c r="AC35">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="AD35">
-        <v>2802</v>
+        <v>2806</v>
       </c>
       <c r="AE35">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="AF35">
-        <v>2</v>
-      </c>
-      <c r="AG35" s="15">
-        <v>52</v>
-      </c>
-      <c r="AH35" s="17">
+        <v>4</v>
+      </c>
+      <c r="AG35">
+        <v>41</v>
+      </c>
+      <c r="AH35" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI35" s="17">
-        <v>186271715600</v>
-      </c>
-      <c r="AJ35" s="17">
-        <v>44902415600</v>
+      <c r="AI35" s="13">
+        <v>179450118300</v>
+      </c>
+      <c r="AJ35" s="13">
+        <v>38080818300</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A36" s="13">
-        <v>43</v>
+      <c r="A36">
+        <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
@@ -4604,109 +4596,109 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="16">
-        <v>136.81623945227139</v>
+      <c r="D36">
+        <v>126.5481083469421</v>
       </c>
       <c r="E36">
-        <v>40738</v>
-      </c>
-      <c r="F36" s="15">
-        <v>3461</v>
+        <v>40737</v>
+      </c>
+      <c r="F36">
+        <v>3458</v>
       </c>
       <c r="G36">
-        <v>128.33333333333329</v>
+        <v>128.41851851851851</v>
       </c>
       <c r="H36">
-        <v>11.97777777777778</v>
+        <v>11.988888888888891</v>
       </c>
       <c r="I36">
-        <v>11.97777777777778</v>
+        <v>11.988888888888891</v>
       </c>
       <c r="J36">
-        <v>10.37777777777778</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K36">
-        <v>0.82222222222222219</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L36">
-        <v>0.82222222222222219</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M36">
-        <v>0.1740740740740741</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N36">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O36" s="16">
-        <v>0.19259259259259259</v>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O36">
+        <v>0.15185185185185179</v>
       </c>
       <c r="P36">
-        <v>127.89259259259261</v>
+        <v>128.0185185185185</v>
       </c>
       <c r="Q36" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="R36">
-        <v>31.111111111111111</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S36" t="s">
-        <v>86</v>
-      </c>
-      <c r="T36" s="15">
-        <v>62.592592592592588</v>
+        <v>59</v>
+      </c>
+      <c r="T36">
+        <v>65.555555555555557</v>
       </c>
       <c r="U36" t="s">
-        <v>60</v>
-      </c>
-      <c r="V36" s="19">
-        <v>96.296296296296291</v>
+        <v>36</v>
+      </c>
+      <c r="V36" s="14">
+        <v>81.481481481481481</v>
       </c>
       <c r="W36" t="s">
+        <v>71</v>
+      </c>
+      <c r="X36">
+        <v>74.074074074074076</v>
+      </c>
+      <c r="Y36">
+        <v>34673</v>
+      </c>
+      <c r="Z36">
+        <v>3237</v>
+      </c>
+      <c r="AA36">
+        <v>37910</v>
+      </c>
+      <c r="AB36">
+        <v>2403</v>
+      </c>
+      <c r="AC36">
+        <v>219</v>
+      </c>
+      <c r="AD36">
+        <v>2786</v>
+      </c>
+      <c r="AE36">
         <v>39</v>
       </c>
-      <c r="X36">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y36">
-        <v>34650</v>
-      </c>
-      <c r="Z36">
-        <v>3234</v>
-      </c>
-      <c r="AA36">
-        <v>37884</v>
-      </c>
-      <c r="AB36">
-        <v>2372</v>
-      </c>
-      <c r="AC36">
-        <v>222</v>
-      </c>
-      <c r="AD36">
-        <v>2802</v>
-      </c>
-      <c r="AE36">
-        <v>47</v>
-      </c>
       <c r="AF36">
-        <v>5</v>
-      </c>
-      <c r="AG36" s="15">
-        <v>52</v>
-      </c>
-      <c r="AH36" s="17">
-        <v>141369300000</v>
-      </c>
-      <c r="AI36" s="17">
-        <v>193416160000</v>
-      </c>
-      <c r="AJ36" s="17">
-        <v>52046860000</v>
+        <v>2</v>
+      </c>
+      <c r="AG36">
+        <v>41</v>
+      </c>
+      <c r="AH36" s="13">
+        <v>141453000000</v>
+      </c>
+      <c r="AI36" s="13">
+        <v>179006095700</v>
+      </c>
+      <c r="AJ36" s="13">
+        <v>37553095700</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -4715,108 +4707,108 @@
         <v>32</v>
       </c>
       <c r="D37">
-        <v>134.43323094901089</v>
+        <v>124.8752582066969</v>
       </c>
       <c r="E37">
-        <v>40738</v>
+        <v>40701</v>
       </c>
       <c r="F37">
-        <v>3283</v>
+        <v>3364</v>
       </c>
       <c r="G37">
-        <v>128.9296296296296</v>
+        <v>128.71851851851849</v>
       </c>
       <c r="H37">
-        <v>11.38148148148148</v>
+        <v>11.58888888888889</v>
       </c>
       <c r="I37">
-        <v>11.38148148148148</v>
+        <v>11.58888888888889</v>
       </c>
       <c r="J37">
-        <v>10.37777777777778</v>
+        <v>10.296296296296299</v>
       </c>
       <c r="K37">
-        <v>0.7592592592592593</v>
+        <v>0.85925925925925928</v>
       </c>
       <c r="L37">
-        <v>0.7592592592592593</v>
+        <v>0.85925925925925928</v>
       </c>
       <c r="M37">
-        <v>0.1740740740740741</v>
+        <v>0.12962962962962959</v>
       </c>
       <c r="N37">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O37" s="16">
-        <v>0.19259259259259259</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O37">
+        <v>0.14074074074074069</v>
       </c>
       <c r="P37">
-        <v>128.61111111111109</v>
+        <v>128.28888888888889</v>
       </c>
       <c r="Q37" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="R37">
-        <v>33.703703703703702</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S37" t="s">
-        <v>53</v>
-      </c>
-      <c r="T37" s="16">
-        <v>58.888888888888893</v>
+        <v>89</v>
+      </c>
+      <c r="T37">
+        <v>64.074074074074076</v>
       </c>
       <c r="U37" t="s">
         <v>35</v>
       </c>
-      <c r="V37">
-        <v>88.888888888888886</v>
+      <c r="V37" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W37" t="s">
+        <v>47</v>
+      </c>
+      <c r="X37">
+        <v>85.18518518518519</v>
+      </c>
+      <c r="Y37">
+        <v>34754</v>
+      </c>
+      <c r="Z37">
+        <v>3129</v>
+      </c>
+      <c r="AA37">
+        <v>37883</v>
+      </c>
+      <c r="AB37">
+        <v>2396</v>
+      </c>
+      <c r="AC37">
+        <v>232</v>
+      </c>
+      <c r="AD37">
+        <v>2780</v>
+      </c>
+      <c r="AE37">
         <v>35</v>
       </c>
-      <c r="X37" s="16">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="Y37">
-        <v>34811</v>
-      </c>
-      <c r="Z37">
-        <v>3073</v>
-      </c>
-      <c r="AA37">
-        <v>37884</v>
-      </c>
-      <c r="AB37">
-        <v>2389</v>
-      </c>
-      <c r="AC37">
-        <v>205</v>
-      </c>
-      <c r="AD37">
-        <v>2802</v>
-      </c>
-      <c r="AE37">
-        <v>47</v>
-      </c>
       <c r="AF37">
-        <v>5</v>
-      </c>
-      <c r="AG37" s="15">
-        <v>52</v>
-      </c>
-      <c r="AH37" s="17">
+        <v>3</v>
+      </c>
+      <c r="AG37">
+        <v>38</v>
+      </c>
+      <c r="AH37" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI37" s="17">
-        <v>190047317560</v>
-      </c>
-      <c r="AJ37" s="17">
-        <v>48678017560</v>
+      <c r="AI37" s="13">
+        <v>176535278400</v>
+      </c>
+      <c r="AJ37" s="13">
+        <v>35165978400</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A38" s="13">
-        <v>45</v>
+      <c r="A38">
+        <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -4824,109 +4816,109 @@
       <c r="C38" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="15">
-        <v>139.06906642389831</v>
+      <c r="D38">
+        <v>124.87318254119739</v>
       </c>
       <c r="E38">
-        <v>40771</v>
+        <v>40718</v>
       </c>
       <c r="F38">
-        <v>3393</v>
+        <v>3381</v>
       </c>
       <c r="G38">
-        <v>128.69999999999999</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H38">
-        <v>11.75925925925926</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="I38">
-        <v>11.75925925925926</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="J38">
-        <v>10.34074074074074</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K38">
-        <v>0.78518518518518521</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L38">
-        <v>0.78518518518518521</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M38">
-        <v>0.18148148148148149</v>
+        <v>0.12962962962962959</v>
       </c>
       <c r="N38">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O38" s="15">
-        <v>0.20370370370370369</v>
+        <v>1.8518518518518521E-2</v>
+      </c>
+      <c r="O38">
+        <v>0.14814814814814811</v>
       </c>
       <c r="P38">
-        <v>128.17037037037039</v>
+        <v>128.30370370370369</v>
       </c>
       <c r="Q38" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="R38">
-        <v>31.111111111111111</v>
+        <v>37.037037037037038</v>
       </c>
       <c r="S38" t="s">
-        <v>82</v>
-      </c>
-      <c r="T38" s="16">
-        <v>58.148148148148152</v>
+        <v>78</v>
+      </c>
+      <c r="T38">
+        <v>62.592592592592588</v>
       </c>
       <c r="U38" t="s">
-        <v>59</v>
-      </c>
-      <c r="V38" s="15">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="V38" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="W38" t="s">
-        <v>43</v>
-      </c>
-      <c r="X38" s="15">
-        <v>92.592592592592595</v>
+        <v>40</v>
+      </c>
+      <c r="X38">
+        <v>77.777777777777786</v>
       </c>
       <c r="Y38">
-        <v>34749</v>
+        <v>34731</v>
       </c>
       <c r="Z38">
-        <v>3175</v>
+        <v>3161</v>
       </c>
       <c r="AA38">
-        <v>37924</v>
+        <v>37892</v>
       </c>
       <c r="AB38">
-        <v>2360</v>
+        <v>2411</v>
       </c>
       <c r="AC38">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AD38">
-        <v>2792</v>
+        <v>2786</v>
       </c>
       <c r="AE38">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="AF38">
-        <v>6</v>
-      </c>
-      <c r="AG38" s="15">
-        <v>55</v>
-      </c>
-      <c r="AH38" s="17">
-        <v>141369300000</v>
-      </c>
-      <c r="AI38" s="17">
-        <v>196600965720</v>
-      </c>
-      <c r="AJ38" s="18">
-        <v>55231665720</v>
+        <v>5</v>
+      </c>
+      <c r="AG38" s="14">
+        <v>40</v>
+      </c>
+      <c r="AH38" s="13">
+        <v>141453000000</v>
+      </c>
+      <c r="AI38" s="13">
+        <v>176636862900</v>
+      </c>
+      <c r="AJ38" s="13">
+        <v>35183862900</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A39" s="13">
-        <v>46</v>
+      <c r="A39">
+        <v>22</v>
       </c>
       <c r="B39" t="s">
         <v>31</v>
@@ -4934,109 +4926,109 @@
       <c r="C39" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="15">
-        <v>139.09968645243339</v>
+      <c r="D39">
+        <v>124.2354350626338</v>
       </c>
       <c r="E39">
-        <v>40771</v>
+        <v>40635</v>
       </c>
       <c r="F39">
-        <v>3410</v>
+        <v>3414</v>
       </c>
       <c r="G39">
-        <v>128.7074074074074</v>
+        <v>128.07777777777781</v>
       </c>
       <c r="H39">
-        <v>11.75185185185185</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="I39">
-        <v>11.75185185185185</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="J39">
-        <v>10.34074074074074</v>
+        <v>10.425925925925929</v>
       </c>
       <c r="K39">
-        <v>0.86296296296296293</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="L39">
-        <v>0.86296296296296293</v>
+        <v>0.78888888888888886</v>
       </c>
       <c r="M39">
-        <v>0.18888888888888891</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N39">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O39" s="15">
-        <v>0.20370370370370369</v>
+        <v>3.7037037037037038E-3</v>
+      </c>
+      <c r="O39">
+        <v>0.1444444444444444</v>
       </c>
       <c r="P39">
-        <v>128.10740740740741</v>
+        <v>128.1037037037037</v>
       </c>
       <c r="Q39" t="s">
-        <v>83</v>
-      </c>
-      <c r="R39" s="15">
-        <v>30</v>
+        <v>63</v>
+      </c>
+      <c r="R39">
+        <v>35.555555555555557</v>
       </c>
       <c r="S39" t="s">
-        <v>86</v>
-      </c>
-      <c r="T39" s="15">
-        <v>62.592592592592588</v>
+        <v>64</v>
+      </c>
+      <c r="T39">
+        <v>63.333333333333329</v>
       </c>
       <c r="U39" t="s">
-        <v>60</v>
-      </c>
-      <c r="V39" s="19">
-        <v>96.296296296296291</v>
+        <v>36</v>
+      </c>
+      <c r="V39">
+        <v>81.481481481481481</v>
       </c>
       <c r="W39" t="s">
-        <v>60</v>
-      </c>
-      <c r="X39" s="15">
-        <v>96.296296296296291</v>
+        <v>65</v>
+      </c>
+      <c r="X39">
+        <v>70.370370370370367</v>
       </c>
       <c r="Y39">
-        <v>34751</v>
+        <v>34581</v>
       </c>
       <c r="Z39">
-        <v>3173</v>
+        <v>3200</v>
       </c>
       <c r="AA39">
-        <v>37924</v>
+        <v>37781</v>
       </c>
       <c r="AB39">
-        <v>2339</v>
+        <v>2446</v>
       </c>
       <c r="AC39">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="AD39">
-        <v>2792</v>
+        <v>2815</v>
       </c>
       <c r="AE39">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="AF39">
-        <v>4</v>
-      </c>
-      <c r="AG39" s="15">
-        <v>55</v>
-      </c>
-      <c r="AH39" s="17">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="14">
+        <v>39</v>
+      </c>
+      <c r="AH39" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI39" s="17">
-        <v>196644253040</v>
-      </c>
-      <c r="AJ39" s="18">
-        <v>55274953040</v>
+      <c r="AI39" s="13">
+        <v>175630764900</v>
+      </c>
+      <c r="AJ39" s="13">
+        <v>34261464900</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
@@ -5045,108 +5037,108 @@
         <v>32</v>
       </c>
       <c r="D40">
-        <v>135.74983728433261</v>
+        <v>124.11728883145069</v>
       </c>
       <c r="E40">
-        <v>40780</v>
+        <v>40671</v>
       </c>
       <c r="F40">
-        <v>3318</v>
+        <v>3419</v>
       </c>
       <c r="G40">
-        <v>128.9851851851852</v>
+        <v>128.31851851851849</v>
       </c>
       <c r="H40">
-        <v>11.52962962962963</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="I40">
-        <v>11.52962962962963</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="J40">
-        <v>10.32592592592593</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K40">
-        <v>0.73703703703703705</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L40">
-        <v>0.73703703703703705</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M40">
-        <v>0.1740740740740741</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N40">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O40" s="16">
-        <v>0.1962962962962963</v>
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0.14074074074074069</v>
       </c>
       <c r="P40">
-        <v>128.44444444444451</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q40" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="R40">
-        <v>37.777777777777779</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="S40" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T40">
-        <v>51.851851851851848</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U40" t="s">
         <v>35</v>
       </c>
-      <c r="V40">
-        <v>88.888888888888886</v>
+      <c r="V40" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W40" t="s">
-        <v>36</v>
-      </c>
-      <c r="X40">
-        <v>81.481481481481481</v>
+        <v>35</v>
+      </c>
+      <c r="X40" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y40">
-        <v>34826</v>
+        <v>34646</v>
       </c>
       <c r="Z40">
-        <v>3113</v>
+        <v>3197</v>
       </c>
       <c r="AA40">
-        <v>37939</v>
+        <v>37843</v>
       </c>
       <c r="AB40">
-        <v>2377</v>
+        <v>2416</v>
       </c>
       <c r="AC40">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="AD40">
-        <v>2788</v>
+        <v>2790</v>
       </c>
       <c r="AE40">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="AF40">
-        <v>6</v>
-      </c>
-      <c r="AG40" s="15">
-        <v>53</v>
-      </c>
-      <c r="AH40" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>38</v>
+      </c>
+      <c r="AH40" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI40" s="17">
-        <v>191908594720</v>
-      </c>
-      <c r="AJ40" s="17">
-        <v>50539294720</v>
+      <c r="AI40" s="13">
+        <v>175463742400</v>
+      </c>
+      <c r="AJ40" s="13">
+        <v>34094442400</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
         <v>31</v>
@@ -5155,108 +5147,108 @@
         <v>32</v>
       </c>
       <c r="D41">
-        <v>135.08681222868049</v>
+        <v>123.96480721061791</v>
       </c>
       <c r="E41">
-        <v>40780</v>
-      </c>
-      <c r="F41" s="15">
-        <v>3454</v>
+        <v>40714</v>
+      </c>
+      <c r="F41">
+        <v>3452</v>
       </c>
       <c r="G41">
-        <v>128.58148148148149</v>
+        <v>128.3407407407407</v>
       </c>
       <c r="H41">
-        <v>11.93333333333333</v>
+        <v>12.018518518518521</v>
       </c>
       <c r="I41">
-        <v>11.93333333333333</v>
+        <v>12.018518518518521</v>
       </c>
       <c r="J41">
-        <v>10.32592592592593</v>
+        <v>10.285185185185179</v>
       </c>
       <c r="K41">
-        <v>0.85185185185185186</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="L41">
-        <v>0.85185185185185186</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="M41">
-        <v>0.18888888888888891</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N41">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="O41" s="16">
-        <v>0.1962962962962963</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O41">
+        <v>0.14814814814814811</v>
       </c>
       <c r="P41">
-        <v>127.99629629629629</v>
+        <v>128.01111111111109</v>
       </c>
       <c r="Q41" t="s">
+        <v>37</v>
+      </c>
+      <c r="R41">
+        <v>37.037037037037038</v>
+      </c>
+      <c r="S41" t="s">
         <v>88</v>
       </c>
-      <c r="R41" s="15">
-        <v>25.92592592592592</v>
-      </c>
-      <c r="S41" t="s">
-        <v>84</v>
-      </c>
-      <c r="T41" s="15">
-        <v>64.074074074074076</v>
+      <c r="T41">
+        <v>60</v>
       </c>
       <c r="U41" t="s">
-        <v>35</v>
-      </c>
-      <c r="V41">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="V41" s="23">
+        <v>96.296296296296291</v>
       </c>
       <c r="W41" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="X41">
-        <v>81.481481481481481</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y41">
-        <v>34717</v>
+        <v>34652</v>
       </c>
       <c r="Z41">
-        <v>3222</v>
+        <v>3245</v>
       </c>
       <c r="AA41">
-        <v>37939</v>
+        <v>37897</v>
       </c>
       <c r="AB41">
-        <v>2346</v>
+        <v>2413</v>
       </c>
       <c r="AC41">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="AD41">
-        <v>2788</v>
+        <v>2777</v>
       </c>
       <c r="AE41">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="AF41">
-        <v>2</v>
-      </c>
-      <c r="AG41" s="15">
-        <v>53</v>
-      </c>
-      <c r="AH41" s="17">
+        <v>3</v>
+      </c>
+      <c r="AG41">
+        <v>40</v>
+      </c>
+      <c r="AH41" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI41" s="17">
-        <v>190971280840</v>
-      </c>
-      <c r="AJ41" s="17">
-        <v>49601980840</v>
+      <c r="AI41" s="13">
+        <v>175248180200</v>
+      </c>
+      <c r="AJ41" s="13">
+        <v>33878880200</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A42" s="13">
-        <v>49</v>
+      <c r="A42">
+        <v>23</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
@@ -5264,109 +5256,109 @@
       <c r="C42" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="16">
-        <v>136.1734986025962</v>
-      </c>
-      <c r="E42" s="15">
-        <v>40801</v>
+      <c r="D42">
+        <v>123.5907913528609</v>
+      </c>
+      <c r="E42">
+        <v>40670</v>
       </c>
       <c r="F42">
-        <v>3370</v>
+        <v>3413</v>
       </c>
       <c r="G42">
-        <v>128.88888888888891</v>
+        <v>128.37407407407409</v>
       </c>
       <c r="H42">
-        <v>11.703703703703701</v>
+        <v>11.792592592592589</v>
       </c>
       <c r="I42">
-        <v>11.703703703703701</v>
+        <v>11.792592592592589</v>
       </c>
       <c r="J42">
-        <v>10.31851851851852</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K42">
-        <v>0.76296296296296295</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="L42">
-        <v>0.76296296296296295</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="M42">
-        <v>0.18888888888888891</v>
+        <v>0.12592592592592591</v>
       </c>
       <c r="N42">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="O42" s="15">
-        <v>0.20370370370370369</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O42">
+        <v>0.13703703703703701</v>
       </c>
       <c r="P42">
-        <v>128.28148148148151</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q42" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="R42">
-        <v>34.074074074074083</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S42" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="T42">
-        <v>55.925925925925917</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U42" t="s">
-        <v>39</v>
-      </c>
-      <c r="V42">
-        <v>85.18518518518519</v>
+        <v>35</v>
+      </c>
+      <c r="V42" s="24">
+        <v>92.592592592592595</v>
       </c>
       <c r="W42" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="X42">
-        <v>85.18518518518519</v>
+        <v>70.370370370370367</v>
       </c>
       <c r="Y42">
-        <v>34800</v>
+        <v>34661</v>
       </c>
       <c r="Z42">
-        <v>3160</v>
+        <v>3184</v>
       </c>
       <c r="AA42">
-        <v>37960</v>
+        <v>37845</v>
       </c>
       <c r="AB42">
-        <v>2360</v>
+        <v>2414</v>
       </c>
       <c r="AC42">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="AD42">
-        <v>2786</v>
+        <v>2788</v>
       </c>
       <c r="AE42">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="AF42">
-        <v>4</v>
-      </c>
-      <c r="AG42" s="15">
-        <v>55</v>
-      </c>
-      <c r="AH42" s="17">
+        <v>3</v>
+      </c>
+      <c r="AG42">
+        <v>37</v>
+      </c>
+      <c r="AH42" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI42" s="17">
-        <v>192507521760</v>
-      </c>
-      <c r="AJ42" s="18">
-        <v>51138221760</v>
+      <c r="AI42" s="13">
+        <v>174719436600</v>
+      </c>
+      <c r="AJ42" s="13">
+        <v>33350136600</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A43" s="13">
-        <v>50</v>
+      <c r="A43">
+        <v>19</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
@@ -5374,109 +5366,109 @@
       <c r="C43" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="16">
-        <v>138.5605110020351</v>
-      </c>
-      <c r="E43" s="15">
-        <v>40801</v>
-      </c>
-      <c r="F43" s="15">
-        <v>3423</v>
+      <c r="D43">
+        <v>122.5885974536197</v>
+      </c>
+      <c r="E43">
+        <v>40700</v>
+      </c>
+      <c r="F43">
+        <v>3338</v>
       </c>
       <c r="G43">
-        <v>128.737037037037</v>
+        <v>128.67037037037039</v>
       </c>
       <c r="H43">
-        <v>11.85555555555556</v>
+        <v>11.6</v>
       </c>
       <c r="I43">
-        <v>11.85555555555556</v>
+        <v>11.6</v>
       </c>
       <c r="J43">
-        <v>10.31851851851852</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K43">
-        <v>0.8037037037037037</v>
+        <v>0.75185185185185188</v>
       </c>
       <c r="L43">
-        <v>0.8037037037037037</v>
+        <v>0.75185185185185188</v>
       </c>
       <c r="M43">
-        <v>0.1851851851851852</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="N43">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="O43" s="15">
-        <v>0.20370370370370369</v>
+        <v>1.111111111111111E-2</v>
+      </c>
+      <c r="O43">
+        <v>0.1444444444444444</v>
       </c>
       <c r="P43">
-        <v>128.0740740740741</v>
+        <v>128.38518518518521</v>
       </c>
       <c r="Q43" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="R43">
-        <v>30.74074074074074</v>
+        <v>37.407407407407398</v>
       </c>
       <c r="S43" t="s">
-        <v>55</v>
-      </c>
-      <c r="T43" s="16">
-        <v>58.518518518518512</v>
+        <v>57</v>
+      </c>
+      <c r="T43">
+        <v>60.74074074074074</v>
       </c>
       <c r="U43" t="s">
-        <v>60</v>
-      </c>
-      <c r="V43" s="19">
-        <v>96.296296296296291</v>
+        <v>39</v>
+      </c>
+      <c r="V43" s="14">
+        <v>88.888888888888886</v>
       </c>
       <c r="W43" t="s">
+        <v>36</v>
+      </c>
+      <c r="X43">
+        <v>81.481481481481481</v>
+      </c>
+      <c r="Y43">
+        <v>34741</v>
+      </c>
+      <c r="Z43">
+        <v>3132</v>
+      </c>
+      <c r="AA43">
+        <v>37873</v>
+      </c>
+      <c r="AB43">
+        <v>2429</v>
+      </c>
+      <c r="AC43">
+        <v>203</v>
+      </c>
+      <c r="AD43">
+        <v>2788</v>
+      </c>
+      <c r="AE43">
+        <v>36</v>
+      </c>
+      <c r="AF43">
+        <v>3</v>
+      </c>
+      <c r="AG43">
         <v>39</v>
       </c>
-      <c r="X43">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y43">
-        <v>34759</v>
-      </c>
-      <c r="Z43">
-        <v>3201</v>
-      </c>
-      <c r="AA43">
-        <v>37960</v>
-      </c>
-      <c r="AB43">
-        <v>2349</v>
-      </c>
-      <c r="AC43">
-        <v>217</v>
-      </c>
-      <c r="AD43">
-        <v>2786</v>
-      </c>
-      <c r="AE43">
-        <v>50</v>
-      </c>
-      <c r="AF43">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="15">
-        <v>55</v>
-      </c>
-      <c r="AH43" s="17">
+      <c r="AH43" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI43" s="17">
-        <v>195882024480</v>
-      </c>
-      <c r="AJ43" s="18">
-        <v>54512724480</v>
+      <c r="AI43" s="13">
+        <v>173302642100</v>
+      </c>
+      <c r="AJ43" s="13">
+        <v>31933342100</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -5485,184 +5477,251 @@
         <v>32</v>
       </c>
       <c r="D44">
-        <v>131.2077959358927</v>
+        <v>119.57909319774519</v>
       </c>
       <c r="E44">
-        <v>40728</v>
+        <v>40686</v>
       </c>
       <c r="F44">
-        <v>3325</v>
+        <v>3412</v>
       </c>
       <c r="G44">
-        <v>128.81481481481481</v>
+        <v>128.3666666666667</v>
       </c>
       <c r="H44">
-        <v>11.5037037037037</v>
+        <v>11.885185185185181</v>
       </c>
       <c r="I44">
-        <v>11.5037037037037</v>
+        <v>11.885185185185181</v>
       </c>
       <c r="J44">
-        <v>10.351851851851849</v>
+        <v>10.3037037037037</v>
       </c>
       <c r="K44">
-        <v>0.79259259259259263</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L44">
-        <v>0.79259259259259263</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M44">
-        <v>0.15555555555555561</v>
+        <v>0.1148148148148148</v>
       </c>
       <c r="N44">
         <v>1.8518518518518521E-2</v>
       </c>
       <c r="O44">
-        <v>0.1740740740740741</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="P44">
-        <v>128.43333333333331</v>
+        <v>128.11111111111109</v>
       </c>
       <c r="Q44" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="R44">
-        <v>32.592592592592602</v>
+        <v>41.481481481481481</v>
       </c>
       <c r="S44" t="s">
-        <v>89</v>
-      </c>
-      <c r="T44" s="16">
-        <v>55.925925925925917</v>
+        <v>61</v>
+      </c>
+      <c r="T44">
+        <v>58.148148148148152</v>
       </c>
       <c r="U44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V44">
-        <v>88.888888888888886</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="W44" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="X44">
-        <v>85.18518518518519</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="Y44">
-        <v>34780</v>
+        <v>34659</v>
       </c>
       <c r="Z44">
-        <v>3106</v>
+        <v>3209</v>
       </c>
       <c r="AA44">
-        <v>37886</v>
+        <v>37868</v>
       </c>
       <c r="AB44">
-        <v>2393</v>
+        <v>2440</v>
       </c>
       <c r="AC44">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="AD44">
-        <v>2795</v>
+        <v>2782</v>
       </c>
       <c r="AE44">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AF44">
         <v>5</v>
       </c>
-      <c r="AG44">
-        <v>47</v>
-      </c>
-      <c r="AH44" s="17">
+      <c r="AG44" s="14">
+        <v>36</v>
+      </c>
+      <c r="AH44" s="13">
         <v>141369300000</v>
       </c>
-      <c r="AI44" s="17">
-        <v>185487542660</v>
-      </c>
-      <c r="AJ44" s="17">
-        <v>44118242660</v>
+      <c r="AI44" s="13">
+        <v>169048127000</v>
+      </c>
+      <c r="AJ44" s="13">
+        <v>27678827000</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>52</v>
-      </c>
-      <c r="S45"/>
-      <c r="T45"/>
-      <c r="U45"/>
-      <c r="V45"/>
-      <c r="W45"/>
-      <c r="X45"/>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45"/>
-      <c r="AF45"/>
-      <c r="AG45"/>
-      <c r="AH45"/>
-      <c r="AI45"/>
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45">
+        <v>117.6183000128034</v>
+      </c>
+      <c r="E45">
+        <v>40645</v>
+      </c>
+      <c r="F45">
+        <v>3337</v>
+      </c>
+      <c r="G45">
+        <v>128.43333333333331</v>
+      </c>
+      <c r="H45">
+        <v>11.62592592592593</v>
+      </c>
+      <c r="I45">
+        <v>11.62592592592593</v>
+      </c>
+      <c r="J45">
+        <v>10.351851851851849</v>
+      </c>
+      <c r="K45">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="L45">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="M45">
+        <v>0.12592592592592591</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0.12592592592592591</v>
+      </c>
+      <c r="P45">
+        <v>128.38888888888891</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>37</v>
+      </c>
+      <c r="R45">
+        <v>37.037037037037038</v>
+      </c>
+      <c r="S45" t="s">
+        <v>38</v>
+      </c>
+      <c r="T45">
+        <v>62.222222222222221</v>
+      </c>
+      <c r="U45" t="s">
+        <v>39</v>
+      </c>
+      <c r="V45">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W45" t="s">
+        <v>40</v>
+      </c>
+      <c r="X45">
+        <v>77.777777777777786</v>
+      </c>
+      <c r="Y45">
+        <v>34677</v>
+      </c>
+      <c r="Z45">
+        <v>3139</v>
+      </c>
+      <c r="AA45">
+        <v>37816</v>
+      </c>
+      <c r="AB45">
+        <v>2461</v>
+      </c>
+      <c r="AC45">
+        <v>198</v>
+      </c>
+      <c r="AD45">
+        <v>2795</v>
+      </c>
+      <c r="AE45">
+        <v>34</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>34</v>
+      </c>
+      <c r="AH45" s="13">
+        <v>141369300000</v>
+      </c>
+      <c r="AI45" s="13">
+        <v>166276167400</v>
+      </c>
+      <c r="AJ45" s="13">
+        <v>24906867400</v>
+      </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>53</v>
       </c>
-      <c r="S46"/>
-      <c r="T46"/>
-      <c r="U46"/>
-      <c r="V46"/>
-      <c r="W46"/>
-      <c r="X46"/>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AA46"/>
-      <c r="AF46"/>
-      <c r="AG46"/>
-      <c r="AH46"/>
-      <c r="AI46"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>54</v>
       </c>
-      <c r="AF47"/>
-      <c r="AG47"/>
-      <c r="AH47"/>
-      <c r="AI47"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>55</v>
       </c>
-      <c r="AF48"/>
-      <c r="AG48"/>
-      <c r="AH48"/>
-      <c r="AI48"/>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>56</v>
       </c>
-      <c r="AF49"/>
-      <c r="AG49"/>
-      <c r="AH49"/>
-      <c r="AI49"/>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>60</v>
       </c>
@@ -5670,7 +5729,7 @@
   </sheetData>
   <autoFilter ref="A2:AM2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AM53">
-      <sortCondition ref="A2"/>
+      <sortCondition descending="1" ref="D2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADAD014-03D1-4306-90EC-F90C352FB4FE}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA19CC8-4356-400C-AF92-D75DEB51E997}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4230" yWindow="130" windowWidth="28800" windowHeight="18710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,6 +494,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -508,10 +513,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -818,33 +819,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Y1" s="16" t="s">
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Y1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="19" t="s">
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="18" t="s">
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
     </row>
     <row r="2" spans="1:36" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -958,7 +959,7 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -967,108 +968,108 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>140.56670090323709</v>
+        <v>139.96710940777101</v>
       </c>
       <c r="E3">
-        <v>40771</v>
+        <v>40738</v>
       </c>
       <c r="F3">
-        <v>3410</v>
+        <v>3404</v>
       </c>
       <c r="G3">
-        <v>128.7074074074074</v>
+        <v>128.67037037037039</v>
       </c>
       <c r="H3">
-        <v>11.75185185185185</v>
+        <v>11.640740740740741</v>
       </c>
       <c r="I3">
-        <v>11.75185185185185</v>
+        <v>11.640740740740741</v>
       </c>
       <c r="J3">
-        <v>10.34074074074074</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K3">
-        <v>0.86296296296296293</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="L3">
-        <v>0.86296296296296293</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M3">
-        <v>0.18888888888888891</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N3">
-        <v>1.4814814814814821E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="O3">
-        <v>0.20370370370370369</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P3">
-        <v>128.10740740740741</v>
+        <v>128.14074074074071</v>
       </c>
       <c r="Q3" t="s">
-        <v>80</v>
-      </c>
-      <c r="R3" s="14">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="R3" s="17">
+        <v>24.444444444444439</v>
       </c>
       <c r="S3" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" s="14">
-        <v>69.259259259259252</v>
+        <v>49</v>
+      </c>
+      <c r="T3" s="17">
+        <v>72.962962962962962</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
-      </c>
-      <c r="V3" s="23">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V3" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W3" t="s">
-        <v>46</v>
-      </c>
-      <c r="X3" s="23">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="X3" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y3">
-        <v>34751</v>
+        <v>34741</v>
       </c>
       <c r="Z3">
-        <v>3173</v>
+        <v>3143</v>
       </c>
       <c r="AA3">
-        <v>37924</v>
+        <v>37884</v>
       </c>
       <c r="AB3">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="AC3">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="AD3">
-        <v>2792</v>
+        <v>2802</v>
       </c>
       <c r="AE3">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF3">
-        <v>4</v>
-      </c>
-      <c r="AG3" s="22">
-        <v>55</v>
+        <v>9</v>
+      </c>
+      <c r="AG3" s="17">
+        <v>52</v>
       </c>
       <c r="AH3" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI3" s="13">
-        <v>198718161100</v>
-      </c>
-      <c r="AJ3" s="25">
-        <v>57348861100</v>
+        <v>197870522800</v>
+      </c>
+      <c r="AJ3" s="20">
+        <v>56501222800</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -1077,108 +1078,108 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>139.96710940777101</v>
+        <v>138.6072636704009</v>
       </c>
       <c r="E4">
-        <v>40738</v>
+        <v>40780</v>
       </c>
       <c r="F4">
-        <v>3404</v>
+        <v>3454</v>
       </c>
       <c r="G4">
-        <v>128.67037037037039</v>
+        <v>128.58148148148149</v>
       </c>
       <c r="H4">
-        <v>11.640740740740741</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="I4">
-        <v>11.640740740740741</v>
+        <v>11.93333333333333</v>
       </c>
       <c r="J4">
-        <v>10.37777777777778</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K4">
-        <v>0.93333333333333335</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="L4">
-        <v>0.93333333333333335</v>
+        <v>0.85185185185185186</v>
       </c>
       <c r="M4">
-        <v>0.15925925925925929</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N4">
-        <v>3.3333333333333333E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O4">
-        <v>0.19259259259259259</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P4">
-        <v>128.14074074074071</v>
+        <v>127.99629629629629</v>
       </c>
       <c r="Q4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="22">
-        <v>24.444444444444439</v>
+        <v>85</v>
+      </c>
+      <c r="R4" s="17">
+        <v>25.92592592592592</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" s="22">
-        <v>72.962962962962962</v>
+        <v>86</v>
+      </c>
+      <c r="T4" s="17">
+        <v>72.592592592592595</v>
       </c>
       <c r="U4" t="s">
-        <v>35</v>
-      </c>
-      <c r="V4" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="V4" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W4" t="s">
-        <v>35</v>
-      </c>
-      <c r="X4" s="24">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="X4" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="Y4">
-        <v>34741</v>
+        <v>34717</v>
       </c>
       <c r="Z4">
-        <v>3143</v>
+        <v>3222</v>
       </c>
       <c r="AA4">
-        <v>37884</v>
+        <v>37939</v>
       </c>
       <c r="AB4">
-        <v>2342</v>
+        <v>2346</v>
       </c>
       <c r="AC4">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="AD4">
-        <v>2802</v>
+        <v>2788</v>
       </c>
       <c r="AE4">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AF4">
-        <v>9</v>
-      </c>
-      <c r="AG4" s="22">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="AG4" s="17">
+        <v>53</v>
       </c>
       <c r="AH4" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI4" s="13">
-        <v>197870522800</v>
-      </c>
-      <c r="AJ4" s="25">
-        <v>56501222800</v>
+        <v>195948118400</v>
+      </c>
+      <c r="AJ4" s="20">
+        <v>54578818400</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -1187,108 +1188,108 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>138.82829730358711</v>
+        <v>129.1463196747809</v>
       </c>
       <c r="E5">
-        <v>40801</v>
+        <v>40700</v>
       </c>
       <c r="F5">
-        <v>3423</v>
+        <v>3369</v>
       </c>
       <c r="G5">
-        <v>128.737037037037</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H5">
-        <v>11.85555555555556</v>
+        <v>11.614814814814819</v>
       </c>
       <c r="I5">
-        <v>11.85555555555556</v>
+        <v>11.614814814814819</v>
       </c>
       <c r="J5">
-        <v>10.31851851851852</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K5">
-        <v>0.8037037037037037</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L5">
-        <v>0.8037037037037037</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M5">
-        <v>0.1851851851851852</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N5">
-        <v>1.8518518518518521E-2</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O5">
-        <v>0.20370370370370369</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="P5">
-        <v>128.0740740740741</v>
+        <v>128.27037037037039</v>
       </c>
       <c r="Q5" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="R5">
-        <v>30.74074074074074</v>
+        <v>29.25925925925926</v>
       </c>
       <c r="S5" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="T5">
-        <v>65.925925925925924</v>
+        <v>69.259259259259252</v>
       </c>
       <c r="U5" t="s">
         <v>54</v>
       </c>
-      <c r="V5" s="22">
+      <c r="V5" s="17">
         <v>100</v>
       </c>
       <c r="W5" t="s">
         <v>35</v>
       </c>
-      <c r="X5" s="24">
+      <c r="X5" s="19">
         <v>92.592592592592595</v>
       </c>
       <c r="Y5">
-        <v>34759</v>
+        <v>34731</v>
       </c>
       <c r="Z5">
-        <v>3201</v>
+        <v>3136</v>
       </c>
       <c r="AA5">
-        <v>37960</v>
+        <v>37867</v>
       </c>
       <c r="AB5">
-        <v>2349</v>
+        <v>2389</v>
       </c>
       <c r="AC5">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="AD5">
-        <v>2786</v>
+        <v>2790</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AF5">
-        <v>5</v>
-      </c>
-      <c r="AG5" s="22">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="AG5" s="16">
+        <v>43</v>
       </c>
       <c r="AH5" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI5" s="13">
-        <v>196260592100</v>
-      </c>
-      <c r="AJ5" s="25">
-        <v>54891292100</v>
+        <v>182573248100</v>
+      </c>
+      <c r="AJ5" s="13">
+        <v>41203948100</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1297,108 +1298,108 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>138.6072636704009</v>
+        <v>140.56670090323709</v>
       </c>
       <c r="E6">
-        <v>40780</v>
+        <v>40771</v>
       </c>
       <c r="F6">
-        <v>3454</v>
+        <v>3410</v>
       </c>
       <c r="G6">
-        <v>128.58148148148149</v>
+        <v>128.7074074074074</v>
       </c>
       <c r="H6">
-        <v>11.93333333333333</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="I6">
-        <v>11.93333333333333</v>
+        <v>11.75185185185185</v>
       </c>
       <c r="J6">
-        <v>10.32592592592593</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K6">
-        <v>0.85185185185185186</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L6">
-        <v>0.85185185185185186</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M6">
         <v>0.18888888888888891</v>
       </c>
       <c r="N6">
-        <v>7.4074074074074077E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O6">
-        <v>0.1962962962962963</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P6">
-        <v>127.99629629629629</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q6" t="s">
-        <v>85</v>
-      </c>
-      <c r="R6" s="22">
-        <v>25.92592592592592</v>
+        <v>80</v>
+      </c>
+      <c r="R6" s="16">
+        <v>30</v>
       </c>
       <c r="S6" t="s">
-        <v>86</v>
-      </c>
-      <c r="T6" s="22">
-        <v>72.592592592592595</v>
+        <v>53</v>
+      </c>
+      <c r="T6" s="16">
+        <v>69.259259259259252</v>
       </c>
       <c r="U6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V6" s="14">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="V6" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="W6" t="s">
-        <v>36</v>
-      </c>
-      <c r="X6" s="14">
-        <v>81.481481481481481</v>
+        <v>46</v>
+      </c>
+      <c r="X6" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="Y6">
-        <v>34717</v>
+        <v>34751</v>
       </c>
       <c r="Z6">
-        <v>3222</v>
+        <v>3173</v>
       </c>
       <c r="AA6">
-        <v>37939</v>
+        <v>37924</v>
       </c>
       <c r="AB6">
-        <v>2346</v>
+        <v>2339</v>
       </c>
       <c r="AC6">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AD6">
-        <v>2788</v>
+        <v>2792</v>
       </c>
       <c r="AE6">
         <v>51</v>
       </c>
       <c r="AF6">
-        <v>2</v>
-      </c>
-      <c r="AG6" s="22">
-        <v>53</v>
+        <v>4</v>
+      </c>
+      <c r="AG6" s="17">
+        <v>55</v>
       </c>
       <c r="AH6" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI6" s="13">
-        <v>195948118400</v>
-      </c>
-      <c r="AJ6" s="25">
-        <v>54578818400</v>
+        <v>198718161100</v>
+      </c>
+      <c r="AJ6" s="20">
+        <v>57348861100</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
@@ -1407,108 +1408,108 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>138.19962750045451</v>
+        <v>137.40609276554389</v>
       </c>
       <c r="E7">
-        <v>40771</v>
+        <v>40738</v>
       </c>
       <c r="F7">
-        <v>3393</v>
+        <v>3383</v>
       </c>
       <c r="G7">
-        <v>128.69999999999999</v>
+        <v>128.64814814814821</v>
       </c>
       <c r="H7">
-        <v>11.75925925925926</v>
+        <v>11.662962962962959</v>
       </c>
       <c r="I7">
-        <v>11.75925925925926</v>
+        <v>11.662962962962959</v>
       </c>
       <c r="J7">
-        <v>10.34074074074074</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K7">
-        <v>0.78518518518518521</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L7">
-        <v>0.78518518518518521</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M7">
-        <v>0.18148148148148149</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N7">
-        <v>2.222222222222222E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O7">
-        <v>0.20370370370370369</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P7">
-        <v>128.17037037037039</v>
+        <v>128.22592592592591</v>
       </c>
       <c r="Q7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="R7">
-        <v>31.111111111111111</v>
+        <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="T7">
-        <v>66.666666666666657</v>
+        <v>68.888888888888886</v>
       </c>
       <c r="U7" t="s">
-        <v>54</v>
-      </c>
-      <c r="V7" s="22">
-        <v>100</v>
+        <v>46</v>
+      </c>
+      <c r="V7" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="W7" t="s">
-        <v>46</v>
-      </c>
-      <c r="X7" s="23">
-        <v>96.296296296296291</v>
+        <v>39</v>
+      </c>
+      <c r="X7" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y7">
-        <v>34749</v>
+        <v>34735</v>
       </c>
       <c r="Z7">
-        <v>3175</v>
+        <v>3149</v>
       </c>
       <c r="AA7">
-        <v>37924</v>
+        <v>37884</v>
       </c>
       <c r="AB7">
-        <v>2360</v>
+        <v>2365</v>
       </c>
       <c r="AC7">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="AD7">
-        <v>2792</v>
+        <v>2802</v>
       </c>
       <c r="AE7">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF7">
-        <v>6</v>
-      </c>
-      <c r="AG7" s="22">
-        <v>55</v>
+        <v>5</v>
+      </c>
+      <c r="AG7" s="17">
+        <v>52</v>
       </c>
       <c r="AH7" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI7" s="13">
-        <v>195371846000</v>
-      </c>
-      <c r="AJ7" s="25">
-        <v>54002546000</v>
+        <v>194250031500</v>
+      </c>
+      <c r="AJ7" s="20">
+        <v>52880731500</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -1517,108 +1518,108 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>138.19172896802911</v>
+        <v>135.68522974931619</v>
       </c>
       <c r="E8">
-        <v>40771</v>
+        <v>40738</v>
       </c>
       <c r="F8">
-        <v>3411</v>
+        <v>3222</v>
       </c>
       <c r="G8">
-        <v>128.61481481481479</v>
+        <v>129.1925925925926</v>
       </c>
       <c r="H8">
-        <v>11.84444444444444</v>
+        <v>11.11851851851852</v>
       </c>
       <c r="I8">
-        <v>11.84444444444444</v>
+        <v>11.11851851851852</v>
       </c>
       <c r="J8">
-        <v>10.34074074074074</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K8">
-        <v>0.78148148148148144</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L8">
-        <v>0.78148148148148144</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M8">
-        <v>0.1962962962962963</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N8">
-        <v>7.4074074074074077E-3</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O8">
-        <v>0.20370370370370369</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P8">
-        <v>128.11481481481479</v>
+        <v>128.83703703703699</v>
       </c>
       <c r="Q8" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="R8">
-        <v>33.703703703703702</v>
+        <v>30</v>
       </c>
       <c r="S8" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="T8">
-        <v>65.555555555555557</v>
+        <v>67.407407407407405</v>
       </c>
       <c r="U8" t="s">
-        <v>54</v>
-      </c>
-      <c r="V8" s="22">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="V8" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W8" t="s">
-        <v>54</v>
-      </c>
-      <c r="X8" s="22">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="X8" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y8">
-        <v>34726</v>
+        <v>34882</v>
       </c>
       <c r="Z8">
-        <v>3198</v>
+        <v>3002</v>
       </c>
       <c r="AA8">
-        <v>37924</v>
+        <v>37884</v>
       </c>
       <c r="AB8">
-        <v>2361</v>
+        <v>2375</v>
       </c>
       <c r="AC8">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="AD8">
-        <v>2792</v>
+        <v>2802</v>
       </c>
       <c r="AE8">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AF8">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="22">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="AG8" s="17">
+        <v>52</v>
       </c>
       <c r="AH8" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI8" s="13">
-        <v>195360679900</v>
-      </c>
-      <c r="AJ8" s="25">
-        <v>53991379900</v>
+        <v>191817259500</v>
+      </c>
+      <c r="AJ8" s="20">
+        <v>50447959500</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1627,55 +1628,55 @@
         <v>32</v>
       </c>
       <c r="D9">
-        <v>137.4216820766602</v>
+        <v>131.9339636487031</v>
       </c>
       <c r="E9">
-        <v>40801</v>
+        <v>40773</v>
       </c>
       <c r="F9">
-        <v>3370</v>
+        <v>3434</v>
       </c>
       <c r="G9">
-        <v>128.88888888888891</v>
+        <v>128.65185185185189</v>
       </c>
       <c r="H9">
-        <v>11.703703703703701</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="I9">
-        <v>11.703703703703701</v>
+        <v>11.87037037037037</v>
       </c>
       <c r="J9">
         <v>10.31851851851852</v>
       </c>
       <c r="K9">
-        <v>0.76296296296296295</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="L9">
-        <v>0.76296296296296295</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="M9">
-        <v>0.18888888888888891</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N9">
-        <v>1.4814814814814821E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O9">
-        <v>0.20370370370370369</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P9">
-        <v>128.28148148148151</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q9" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="R9" s="14">
-        <v>34.074074074074083</v>
+        <v>30.37037037037037</v>
       </c>
       <c r="S9" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="T9" s="14">
-        <v>63.703703703703709</v>
+        <v>68.518518518518519</v>
       </c>
       <c r="U9" t="s">
         <v>39</v>
@@ -1684,51 +1685,51 @@
         <v>88.888888888888886</v>
       </c>
       <c r="W9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="X9" s="14">
-        <v>85.18518518518519</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y9">
-        <v>34800</v>
+        <v>34736</v>
       </c>
       <c r="Z9">
-        <v>3160</v>
+        <v>3205</v>
       </c>
       <c r="AA9">
-        <v>37960</v>
+        <v>37941</v>
       </c>
       <c r="AB9">
-        <v>2360</v>
+        <v>2374</v>
       </c>
       <c r="AC9">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="AD9">
         <v>2786</v>
       </c>
       <c r="AE9">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>4</v>
-      </c>
-      <c r="AG9" s="22">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="AG9" s="16">
+        <v>46</v>
       </c>
       <c r="AH9" s="13">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI9" s="13">
-        <v>194272070000</v>
-      </c>
-      <c r="AJ9" s="25">
-        <v>52902770000</v>
+        <v>186624549600</v>
+      </c>
+      <c r="AJ9" s="13">
+        <v>45171549600</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1737,108 +1738,108 @@
         <v>32</v>
       </c>
       <c r="D10">
-        <v>137.40609276554389</v>
+        <v>138.82829730358711</v>
       </c>
       <c r="E10">
-        <v>40738</v>
+        <v>40801</v>
       </c>
       <c r="F10">
-        <v>3383</v>
+        <v>3423</v>
       </c>
       <c r="G10">
-        <v>128.64814814814821</v>
+        <v>128.737037037037</v>
       </c>
       <c r="H10">
-        <v>11.662962962962959</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="I10">
-        <v>11.662962962962959</v>
+        <v>11.85555555555556</v>
       </c>
       <c r="J10">
-        <v>10.37777777777778</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K10">
-        <v>0.8481481481481481</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L10">
-        <v>0.8481481481481481</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M10">
-        <v>0.1740740740740741</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N10">
         <v>1.8518518518518521E-2</v>
       </c>
       <c r="O10">
-        <v>0.19259259259259259</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P10">
-        <v>128.22592592592591</v>
+        <v>128.0740740740741</v>
       </c>
       <c r="Q10" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="R10">
-        <v>30</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S10" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="T10">
-        <v>68.888888888888886</v>
+        <v>65.925925925925924</v>
       </c>
       <c r="U10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V10" s="23">
-        <v>96.296296296296291</v>
+        <v>54</v>
+      </c>
+      <c r="V10" s="17">
+        <v>100</v>
       </c>
       <c r="W10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X10" s="14">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="X10" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y10">
-        <v>34735</v>
+        <v>34759</v>
       </c>
       <c r="Z10">
-        <v>3149</v>
+        <v>3201</v>
       </c>
       <c r="AA10">
-        <v>37884</v>
+        <v>37960</v>
       </c>
       <c r="AB10">
-        <v>2365</v>
+        <v>2349</v>
       </c>
       <c r="AC10">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="AD10">
-        <v>2802</v>
+        <v>2786</v>
       </c>
       <c r="AE10">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AF10">
         <v>5</v>
       </c>
-      <c r="AG10" s="22">
-        <v>52</v>
+      <c r="AG10" s="17">
+        <v>55</v>
       </c>
       <c r="AH10" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI10" s="13">
-        <v>194250031500</v>
-      </c>
-      <c r="AJ10" s="25">
-        <v>52880731500</v>
+        <v>196260592100</v>
+      </c>
+      <c r="AJ10" s="20">
+        <v>54891292100</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1847,108 +1848,108 @@
         <v>32</v>
       </c>
       <c r="D11">
-        <v>137.07237809057551</v>
+        <v>131.4573185974607</v>
       </c>
       <c r="E11">
-        <v>40780</v>
+        <v>40730</v>
       </c>
       <c r="F11">
-        <v>3352</v>
+        <v>3412</v>
       </c>
       <c r="G11">
-        <v>128.93703703703699</v>
+        <v>128.65555555555559</v>
       </c>
       <c r="H11">
-        <v>11.577777777777779</v>
+        <v>11.733333333333331</v>
       </c>
       <c r="I11">
-        <v>11.577777777777779</v>
+        <v>11.733333333333331</v>
       </c>
       <c r="J11">
-        <v>10.32592592592593</v>
+        <v>10.3</v>
       </c>
       <c r="K11">
-        <v>0.81481481481481477</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="L11">
-        <v>0.81481481481481477</v>
+        <v>0.8925925925925926</v>
       </c>
       <c r="M11">
-        <v>0.1740740740740741</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="N11">
-        <v>2.222222222222222E-2</v>
+        <v>1.111111111111111E-2</v>
       </c>
       <c r="O11">
-        <v>0.1962962962962963</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P11">
-        <v>128.33333333333329</v>
+        <v>128.11111111111109</v>
       </c>
       <c r="Q11" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="R11">
-        <v>31.481481481481481</v>
+        <v>30.74074074074074</v>
       </c>
       <c r="S11" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="T11">
-        <v>65.925925925925924</v>
+        <v>67.777777777777786</v>
       </c>
       <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="V11" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W11" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="X11" s="14">
-        <v>81.481481481481481</v>
+        <v>74.074074074074076</v>
       </c>
       <c r="Y11">
-        <v>34813</v>
+        <v>34737</v>
       </c>
       <c r="Z11">
-        <v>3126</v>
+        <v>3168</v>
       </c>
       <c r="AA11">
-        <v>37939</v>
+        <v>37905</v>
       </c>
       <c r="AB11">
-        <v>2356</v>
+        <v>2364</v>
       </c>
       <c r="AC11">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="AD11">
-        <v>2788</v>
+        <v>2781</v>
       </c>
       <c r="AE11">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AF11">
-        <v>6</v>
-      </c>
-      <c r="AG11" s="22">
-        <v>53</v>
+        <v>3</v>
+      </c>
+      <c r="AG11" s="16">
+        <v>44</v>
       </c>
       <c r="AH11" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI11" s="13">
-        <v>193778261400</v>
-      </c>
-      <c r="AJ11" s="25">
-        <v>52408961400</v>
+        <v>185840291100</v>
+      </c>
+      <c r="AJ11" s="13">
+        <v>44470991100</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1957,43 +1958,43 @@
         <v>32</v>
       </c>
       <c r="D12">
-        <v>136.9620354631451</v>
+        <v>138.19962750045451</v>
       </c>
       <c r="E12">
-        <v>40738</v>
+        <v>40771</v>
       </c>
       <c r="F12">
-        <v>3461</v>
+        <v>3393</v>
       </c>
       <c r="G12">
-        <v>128.33333333333329</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="H12">
-        <v>11.97777777777778</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="I12">
-        <v>11.97777777777778</v>
+        <v>11.75925925925926</v>
       </c>
       <c r="J12">
-        <v>10.37777777777778</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K12">
-        <v>0.82222222222222219</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="L12">
-        <v>0.82222222222222219</v>
+        <v>0.78518518518518521</v>
       </c>
       <c r="M12">
-        <v>0.1740740740740741</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N12">
-        <v>1.8518518518518521E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O12">
-        <v>0.19259259259259259</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P12">
-        <v>127.89259259259261</v>
+        <v>128.17037037037039</v>
       </c>
       <c r="Q12" t="s">
         <v>72</v>
@@ -2002,63 +2003,63 @@
         <v>31.111111111111111</v>
       </c>
       <c r="S12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="T12" s="14">
-        <v>67.407407407407405</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="U12" t="s">
         <v>54</v>
       </c>
-      <c r="V12" s="22">
+      <c r="V12" s="17">
         <v>100</v>
       </c>
       <c r="W12" t="s">
-        <v>39</v>
-      </c>
-      <c r="X12" s="14">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="X12" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="Y12">
-        <v>34650</v>
+        <v>34749</v>
       </c>
       <c r="Z12">
-        <v>3234</v>
+        <v>3175</v>
       </c>
       <c r="AA12">
-        <v>37884</v>
+        <v>37924</v>
       </c>
       <c r="AB12">
-        <v>2372</v>
+        <v>2360</v>
       </c>
       <c r="AC12">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="AD12">
-        <v>2802</v>
+        <v>2792</v>
       </c>
       <c r="AE12">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF12">
-        <v>5</v>
-      </c>
-      <c r="AG12" s="22">
-        <v>52</v>
+        <v>6</v>
+      </c>
+      <c r="AG12" s="17">
+        <v>55</v>
       </c>
       <c r="AH12" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI12" s="13">
-        <v>193622270800</v>
-      </c>
-      <c r="AJ12" s="25">
-        <v>52252970800</v>
+        <v>195371846000</v>
+      </c>
+      <c r="AJ12" s="20">
+        <v>54002546000</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -2067,43 +2068,43 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <v>136.9543797698652</v>
+        <v>136.9620354631451</v>
       </c>
       <c r="E13">
-        <v>40771</v>
+        <v>40738</v>
       </c>
       <c r="F13">
-        <v>3348</v>
+        <v>3461</v>
       </c>
       <c r="G13">
-        <v>128.81481481481481</v>
+        <v>128.33333333333329</v>
       </c>
       <c r="H13">
-        <v>11.64444444444444</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="I13">
-        <v>11.64444444444444</v>
+        <v>11.97777777777778</v>
       </c>
       <c r="J13">
-        <v>10.34074074074074</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K13">
-        <v>0.74814814814814812</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L13">
-        <v>0.74814814814814812</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M13">
-        <v>0.1962962962962963</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N13">
-        <v>7.4074074074074077E-3</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O13">
-        <v>0.20370370370370369</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P13">
-        <v>128.34814814814811</v>
+        <v>127.89259259259261</v>
       </c>
       <c r="Q13" t="s">
         <v>72</v>
@@ -2112,63 +2113,63 @@
         <v>31.111111111111111</v>
       </c>
       <c r="S13" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="T13">
-        <v>65.925925925925924</v>
+        <v>67.407407407407405</v>
       </c>
       <c r="U13" t="s">
-        <v>35</v>
-      </c>
-      <c r="V13" s="24">
-        <v>92.592592592592595</v>
+        <v>54</v>
+      </c>
+      <c r="V13" s="17">
+        <v>100</v>
       </c>
       <c r="W13" t="s">
+        <v>39</v>
+      </c>
+      <c r="X13" s="14">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="Y13">
+        <v>34650</v>
+      </c>
+      <c r="Z13">
+        <v>3234</v>
+      </c>
+      <c r="AA13">
+        <v>37884</v>
+      </c>
+      <c r="AB13">
+        <v>2372</v>
+      </c>
+      <c r="AC13">
+        <v>222</v>
+      </c>
+      <c r="AD13">
+        <v>2802</v>
+      </c>
+      <c r="AE13">
         <v>47</v>
       </c>
-      <c r="X13" s="14">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y13">
-        <v>34780</v>
-      </c>
-      <c r="Z13">
-        <v>3144</v>
-      </c>
-      <c r="AA13">
-        <v>37924</v>
-      </c>
-      <c r="AB13">
-        <v>2370</v>
-      </c>
-      <c r="AC13">
-        <v>202</v>
-      </c>
-      <c r="AD13">
-        <v>2792</v>
-      </c>
-      <c r="AE13">
-        <v>53</v>
-      </c>
       <c r="AF13">
-        <v>2</v>
-      </c>
-      <c r="AG13" s="22">
-        <v>55</v>
+        <v>5</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>52</v>
       </c>
       <c r="AH13" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI13" s="13">
-        <v>193611448000</v>
-      </c>
-      <c r="AJ13" s="25">
-        <v>52242148000</v>
+        <v>193622270800</v>
+      </c>
+      <c r="AJ13" s="20">
+        <v>52252970800</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -2177,61 +2178,61 @@
         <v>32</v>
       </c>
       <c r="D14">
-        <v>135.68522974931619</v>
+        <v>136.9543797698652</v>
       </c>
       <c r="E14">
-        <v>40738</v>
+        <v>40771</v>
       </c>
       <c r="F14">
-        <v>3222</v>
+        <v>3348</v>
       </c>
       <c r="G14">
-        <v>129.1925925925926</v>
+        <v>128.81481481481481</v>
       </c>
       <c r="H14">
-        <v>11.11851851851852</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="I14">
-        <v>11.11851851851852</v>
+        <v>11.64444444444444</v>
       </c>
       <c r="J14">
-        <v>10.37777777777778</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K14">
-        <v>0.81111111111111112</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="L14">
-        <v>0.81111111111111112</v>
+        <v>0.74814814814814812</v>
       </c>
       <c r="M14">
-        <v>0.18888888888888891</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N14">
-        <v>3.7037037037037038E-3</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O14">
-        <v>0.19259259259259259</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P14">
-        <v>128.83703703703699</v>
+        <v>128.34814814814811</v>
       </c>
       <c r="Q14" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="R14">
-        <v>30</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S14" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="T14">
-        <v>67.407407407407405</v>
+        <v>65.925925925925924</v>
       </c>
       <c r="U14" t="s">
-        <v>39</v>
-      </c>
-      <c r="V14" s="14">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V14" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W14" t="s">
         <v>47</v>
@@ -2240,45 +2241,45 @@
         <v>85.18518518518519</v>
       </c>
       <c r="Y14">
-        <v>34882</v>
+        <v>34780</v>
       </c>
       <c r="Z14">
-        <v>3002</v>
+        <v>3144</v>
       </c>
       <c r="AA14">
-        <v>37884</v>
+        <v>37924</v>
       </c>
       <c r="AB14">
-        <v>2375</v>
+        <v>2370</v>
       </c>
       <c r="AC14">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="AD14">
-        <v>2802</v>
+        <v>2792</v>
       </c>
       <c r="AE14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AF14">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="22">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="AG14" s="17">
+        <v>55</v>
       </c>
       <c r="AH14" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI14" s="13">
-        <v>191817259500</v>
-      </c>
-      <c r="AJ14" s="25">
-        <v>50447959500</v>
+        <v>193611448000</v>
+      </c>
+      <c r="AJ14" s="20">
+        <v>52242148000</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2287,108 +2288,108 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <v>135.58581099291001</v>
+        <v>135.01545052567991</v>
       </c>
       <c r="E15">
-        <v>40777</v>
+        <v>40738</v>
       </c>
       <c r="F15">
-        <v>3411</v>
+        <v>3379</v>
       </c>
       <c r="G15">
-        <v>128.72962962962961</v>
+        <v>128.5703703703704</v>
       </c>
       <c r="H15">
-        <v>11.80740740740741</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="I15">
-        <v>11.80740740740741</v>
+        <v>11.74074074074074</v>
       </c>
       <c r="J15">
-        <v>10.3</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K15">
-        <v>0.81851851851851853</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="L15">
-        <v>0.81851851851851853</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="M15">
-        <v>0.18148148148148149</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N15">
         <v>7.4074074074074077E-3</v>
       </c>
       <c r="O15">
-        <v>0.18888888888888891</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P15">
-        <v>128.11481481481479</v>
+        <v>128.2222222222222</v>
       </c>
       <c r="Q15" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="R15">
-        <v>33.333333333333329</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="S15" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="T15">
-        <v>65.18518518518519</v>
+        <v>67.407407407407405</v>
       </c>
       <c r="U15" t="s">
         <v>35</v>
       </c>
-      <c r="V15" s="24">
+      <c r="V15" s="19">
         <v>92.592592592592595</v>
       </c>
       <c r="W15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X15" s="24">
-        <v>92.592592592592595</v>
+        <v>47</v>
+      </c>
+      <c r="X15" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y15">
-        <v>34757</v>
+        <v>34714</v>
       </c>
       <c r="Z15">
-        <v>3188</v>
+        <v>3170</v>
       </c>
       <c r="AA15">
-        <v>37945</v>
+        <v>37884</v>
       </c>
       <c r="AB15">
-        <v>2356</v>
+        <v>2387</v>
       </c>
       <c r="AC15">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="AD15">
-        <v>2781</v>
+        <v>2802</v>
       </c>
       <c r="AE15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF15">
         <v>2</v>
       </c>
-      <c r="AG15" s="22">
-        <v>51</v>
+      <c r="AG15" s="17">
+        <v>52</v>
       </c>
       <c r="AH15" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI15" s="13">
-        <v>191676711900</v>
-      </c>
-      <c r="AJ15" s="25">
-        <v>50307411900</v>
+        <v>190870397300</v>
+      </c>
+      <c r="AJ15" s="13">
+        <v>49501097300</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -2397,108 +2398,108 @@
         <v>32</v>
       </c>
       <c r="D16">
-        <v>135.01545052567991</v>
+        <v>137.07237809057551</v>
       </c>
       <c r="E16">
-        <v>40738</v>
+        <v>40780</v>
       </c>
       <c r="F16">
-        <v>3379</v>
+        <v>3352</v>
       </c>
       <c r="G16">
-        <v>128.5703703703704</v>
+        <v>128.93703703703699</v>
       </c>
       <c r="H16">
-        <v>11.74074074074074</v>
+        <v>11.577777777777779</v>
       </c>
       <c r="I16">
-        <v>11.74074074074074</v>
+        <v>11.577777777777779</v>
       </c>
       <c r="J16">
-        <v>10.37777777777778</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K16">
-        <v>0.76666666666666672</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="L16">
-        <v>0.76666666666666672</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="M16">
-        <v>0.1851851851851852</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N16">
-        <v>7.4074074074074077E-3</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O16">
-        <v>0.19259259259259259</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P16">
-        <v>128.2222222222222</v>
+        <v>128.33333333333329</v>
       </c>
       <c r="Q16" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="R16">
-        <v>31.111111111111111</v>
+        <v>31.481481481481481</v>
       </c>
       <c r="S16" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="T16">
-        <v>67.407407407407405</v>
+        <v>65.925925925925924</v>
       </c>
       <c r="U16" t="s">
         <v>35</v>
       </c>
-      <c r="V16" s="24">
+      <c r="V16" s="19">
         <v>92.592592592592595</v>
       </c>
       <c r="W16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16">
+        <v>81.481481481481481</v>
+      </c>
+      <c r="Y16">
+        <v>34813</v>
+      </c>
+      <c r="Z16">
+        <v>3126</v>
+      </c>
+      <c r="AA16">
+        <v>37939</v>
+      </c>
+      <c r="AB16">
+        <v>2356</v>
+      </c>
+      <c r="AC16">
+        <v>220</v>
+      </c>
+      <c r="AD16">
+        <v>2788</v>
+      </c>
+      <c r="AE16">
         <v>47</v>
       </c>
-      <c r="X16">
-        <v>85.18518518518519</v>
-      </c>
-      <c r="Y16">
-        <v>34714</v>
-      </c>
-      <c r="Z16">
-        <v>3170</v>
-      </c>
-      <c r="AA16">
-        <v>37884</v>
-      </c>
-      <c r="AB16">
-        <v>2387</v>
-      </c>
-      <c r="AC16">
-        <v>207</v>
-      </c>
-      <c r="AD16">
-        <v>2802</v>
-      </c>
-      <c r="AE16">
-        <v>50</v>
-      </c>
       <c r="AF16">
-        <v>2</v>
-      </c>
-      <c r="AG16" s="22">
-        <v>52</v>
+        <v>6</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>53</v>
       </c>
       <c r="AH16" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI16" s="13">
-        <v>190870397300</v>
-      </c>
-      <c r="AJ16" s="13">
-        <v>49501097300</v>
+        <v>193778261400</v>
+      </c>
+      <c r="AJ16" s="20">
+        <v>52408961400</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -2507,60 +2508,60 @@
         <v>32</v>
       </c>
       <c r="D17">
-        <v>134.64788132925611</v>
+        <v>130.80206183379281</v>
       </c>
       <c r="E17">
-        <v>40780</v>
+        <v>40732</v>
       </c>
       <c r="F17">
-        <v>3318</v>
+        <v>3363</v>
       </c>
       <c r="G17">
-        <v>128.9851851851852</v>
+        <v>128.76666666666671</v>
       </c>
       <c r="H17">
-        <v>11.52962962962963</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I17">
-        <v>11.52962962962963</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J17">
-        <v>10.32592592592593</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K17">
-        <v>0.73703703703703705</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="L17">
-        <v>0.73703703703703705</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="M17">
-        <v>0.1740740740740741</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="N17">
-        <v>2.222222222222222E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O17">
-        <v>0.1962962962962963</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="P17">
-        <v>128.44444444444451</v>
+        <v>128.2925925925926</v>
       </c>
       <c r="Q17" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="R17">
-        <v>37.777777777777779</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="S17" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="T17">
-        <v>60.370370370370367</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U17" t="s">
         <v>35</v>
       </c>
-      <c r="V17" s="24">
+      <c r="V17" s="19">
         <v>92.592592592592595</v>
       </c>
       <c r="W17" t="s">
@@ -2570,45 +2571,45 @@
         <v>81.481481481481481</v>
       </c>
       <c r="Y17">
-        <v>34826</v>
+        <v>34767</v>
       </c>
       <c r="Z17">
-        <v>3113</v>
+        <v>3134</v>
       </c>
       <c r="AA17">
-        <v>37939</v>
+        <v>37901</v>
       </c>
       <c r="AB17">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="AC17">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="AD17">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="AE17">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AF17">
-        <v>6</v>
-      </c>
-      <c r="AG17" s="22">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="AG17" s="16">
+        <v>45</v>
       </c>
       <c r="AH17" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI17" s="13">
-        <v>190350767300</v>
+        <v>184913959200</v>
       </c>
       <c r="AJ17" s="13">
-        <v>48981467300</v>
+        <v>43544659200</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -2617,108 +2618,108 @@
         <v>32</v>
       </c>
       <c r="D18">
-        <v>134.38630954528321</v>
+        <v>124.11728883145069</v>
       </c>
       <c r="E18">
-        <v>40738</v>
+        <v>40671</v>
       </c>
       <c r="F18">
-        <v>3283</v>
+        <v>3419</v>
       </c>
       <c r="G18">
-        <v>128.9296296296296</v>
+        <v>128.31851851851849</v>
       </c>
       <c r="H18">
-        <v>11.38148148148148</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="I18">
-        <v>11.38148148148148</v>
+        <v>11.84074074074074</v>
       </c>
       <c r="J18">
-        <v>10.37777777777778</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K18">
-        <v>0.7592592592592593</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="L18">
-        <v>0.7592592592592593</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="M18">
-        <v>0.1740740740740741</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="N18">
-        <v>1.8518518518518521E-2</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>0.19259259259259259</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="P18">
-        <v>128.61111111111109</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q18" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R18">
-        <v>33.703703703703702</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="S18" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="T18">
-        <v>64.444444444444443</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U18" t="s">
-        <v>39</v>
-      </c>
-      <c r="V18" s="14">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V18" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W18" t="s">
-        <v>39</v>
-      </c>
-      <c r="X18">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="X18" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y18">
-        <v>34811</v>
+        <v>34646</v>
       </c>
       <c r="Z18">
-        <v>3073</v>
+        <v>3197</v>
       </c>
       <c r="AA18">
-        <v>37884</v>
+        <v>37843</v>
       </c>
       <c r="AB18">
-        <v>2389</v>
+        <v>2416</v>
       </c>
       <c r="AC18">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="AD18">
-        <v>2802</v>
+        <v>2790</v>
       </c>
       <c r="AE18">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="AF18">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="22">
-        <v>52</v>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="16">
+        <v>38</v>
       </c>
       <c r="AH18" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI18" s="13">
-        <v>189980985100</v>
+        <v>175463742400</v>
       </c>
       <c r="AJ18" s="13">
-        <v>48611685100</v>
+        <v>34094442400</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -2727,108 +2728,108 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <v>134.1387439139898</v>
+        <v>131.9139846487179</v>
       </c>
       <c r="E19">
-        <v>40740</v>
+        <v>40715</v>
       </c>
       <c r="F19">
-        <v>3322</v>
+        <v>3314</v>
       </c>
       <c r="G19">
-        <v>128.78518518518521</v>
+        <v>128.85925925925929</v>
       </c>
       <c r="H19">
-        <v>11.525925925925931</v>
+        <v>11.4037037037037</v>
       </c>
       <c r="I19">
-        <v>11.525925925925931</v>
+        <v>11.4037037037037</v>
       </c>
       <c r="J19">
-        <v>10.388888888888889</v>
+        <v>10.36296296296296</v>
       </c>
       <c r="K19">
-        <v>0.77407407407407403</v>
+        <v>0.85555555555555551</v>
       </c>
       <c r="L19">
-        <v>0.77407407407407403</v>
+        <v>0.85555555555555551</v>
       </c>
       <c r="M19">
-        <v>0.1851851851851852</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N19">
-        <v>3.7037037037037038E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O19">
-        <v>0.18888888888888891</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P19">
-        <v>128.44444444444451</v>
+        <v>128.47407407407411</v>
       </c>
       <c r="Q19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R19" s="14">
-        <v>33.703703703703702</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T19" s="14">
-        <v>62.962962962962962</v>
+        <v>65.18518518518519</v>
       </c>
       <c r="U19" t="s">
-        <v>54</v>
-      </c>
-      <c r="V19" s="22">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="V19" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W19" t="s">
-        <v>54</v>
-      </c>
-      <c r="X19" s="22">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="X19" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y19">
-        <v>34772</v>
+        <v>34792</v>
       </c>
       <c r="Z19">
-        <v>3112</v>
+        <v>3079</v>
       </c>
       <c r="AA19">
-        <v>37884</v>
+        <v>37871</v>
       </c>
       <c r="AB19">
-        <v>2392</v>
+        <v>2383</v>
       </c>
       <c r="AC19">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="AD19">
-        <v>2805</v>
+        <v>2798</v>
       </c>
       <c r="AE19">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF19">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="22">
-        <v>51</v>
+        <v>4</v>
+      </c>
+      <c r="AG19" s="16">
+        <v>46</v>
       </c>
       <c r="AH19" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI19" s="13">
-        <v>189631003300</v>
+        <v>186485876700</v>
       </c>
       <c r="AJ19" s="13">
-        <v>48261703300</v>
+        <v>45116576700</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -2837,108 +2838,108 @@
         <v>32</v>
       </c>
       <c r="D20">
-        <v>133.0426598940991</v>
+        <v>129.69486055438909</v>
       </c>
       <c r="E20">
-        <v>40773</v>
+        <v>40752</v>
       </c>
       <c r="F20">
-        <v>3382</v>
+        <v>3420</v>
       </c>
       <c r="G20">
-        <v>128.77407407407409</v>
+        <v>128.66666666666671</v>
       </c>
       <c r="H20">
-        <v>11.707407407407411</v>
+        <v>11.796296296296299</v>
       </c>
       <c r="I20">
-        <v>11.707407407407411</v>
+        <v>11.796296296296299</v>
       </c>
       <c r="J20">
-        <v>10.34814814814815</v>
+        <v>10.31111111111111</v>
       </c>
       <c r="K20">
-        <v>0.79629629629629628</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="L20">
-        <v>0.79629629629629628</v>
+        <v>0.86296296296296293</v>
       </c>
       <c r="M20">
+        <v>0.15185185185185179</v>
+      </c>
+      <c r="N20">
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="O20">
         <v>0.15925925925925929</v>
       </c>
-      <c r="N20">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="O20">
-        <v>0.18148148148148149</v>
-      </c>
       <c r="P20">
-        <v>128.30000000000001</v>
+        <v>128.1592592592593</v>
       </c>
       <c r="Q20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R20">
-        <v>33.703703703703702</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="S20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T20">
-        <v>64.444444444444443</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="U20" t="s">
         <v>46</v>
       </c>
-      <c r="V20" s="23">
+      <c r="V20" s="18">
         <v>96.296296296296291</v>
       </c>
       <c r="W20" t="s">
-        <v>35</v>
-      </c>
-      <c r="X20" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="X20" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y20">
-        <v>34769</v>
+        <v>34740</v>
       </c>
       <c r="Z20">
-        <v>3161</v>
+        <v>3185</v>
       </c>
       <c r="AA20">
-        <v>37930</v>
+        <v>37925</v>
       </c>
       <c r="AB20">
-        <v>2383</v>
+        <v>2379</v>
       </c>
       <c r="AC20">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="AD20">
-        <v>2794</v>
+        <v>2784</v>
       </c>
       <c r="AE20">
+        <v>41</v>
+      </c>
+      <c r="AF20">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="14">
         <v>43</v>
-      </c>
-      <c r="AF20">
-        <v>6</v>
-      </c>
-      <c r="AG20" s="14">
-        <v>49</v>
       </c>
       <c r="AH20" s="13">
         <v>141453000000</v>
       </c>
       <c r="AI20" s="13">
-        <v>188192833700</v>
+        <v>183457271100</v>
       </c>
       <c r="AJ20" s="13">
-        <v>46739833700</v>
+        <v>42004271100</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -2947,25 +2948,25 @@
         <v>32</v>
       </c>
       <c r="D21">
-        <v>133.03770415500401</v>
+        <v>126.93712022341479</v>
       </c>
       <c r="E21">
-        <v>40727</v>
+        <v>40684</v>
       </c>
       <c r="F21">
-        <v>3298</v>
+        <v>3338</v>
       </c>
       <c r="G21">
-        <v>128.9148148148148</v>
+        <v>128.62222222222221</v>
       </c>
       <c r="H21">
-        <v>11.37407407407407</v>
+        <v>11.514814814814811</v>
       </c>
       <c r="I21">
-        <v>11.37407407407407</v>
+        <v>11.514814814814811</v>
       </c>
       <c r="J21">
-        <v>10.37407407407407</v>
+        <v>10.392592592592591</v>
       </c>
       <c r="K21">
         <v>0.83333333333333337</v>
@@ -2974,81 +2975,81 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="M21">
-        <v>0.17037037037037039</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="N21">
-        <v>7.4074074074074077E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O21">
-        <v>0.17777777777777781</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="P21">
-        <v>128.5333333333333</v>
+        <v>128.38518518518521</v>
       </c>
       <c r="Q21" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="R21">
-        <v>35.185185185185183</v>
+        <v>32.592592592592602</v>
       </c>
       <c r="S21" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="T21">
-        <v>61.481481481481481</v>
+        <v>64.81481481481481</v>
       </c>
       <c r="U21" t="s">
-        <v>46</v>
-      </c>
-      <c r="V21" s="23">
-        <v>96.296296296296291</v>
+        <v>39</v>
+      </c>
+      <c r="V21" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W21" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="X21">
-        <v>85.18518518518519</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y21">
-        <v>34807</v>
+        <v>34728</v>
       </c>
       <c r="Z21">
-        <v>3071</v>
+        <v>3109</v>
       </c>
       <c r="AA21">
-        <v>37878</v>
+        <v>37837</v>
       </c>
       <c r="AB21">
-        <v>2384</v>
+        <v>2417</v>
       </c>
       <c r="AC21">
         <v>225</v>
       </c>
       <c r="AD21">
-        <v>2801</v>
+        <v>2806</v>
       </c>
       <c r="AE21">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AF21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG21" s="14">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AH21" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI21" s="13">
-        <v>188074471100</v>
+        <v>179450118300</v>
       </c>
       <c r="AJ21" s="13">
-        <v>46705171100</v>
+        <v>38080818300</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -3057,108 +3058,108 @@
         <v>32</v>
       </c>
       <c r="D22">
-        <v>133.0172042303804</v>
+        <v>130.87595363831099</v>
       </c>
       <c r="E22">
-        <v>40788</v>
+        <v>40755</v>
       </c>
       <c r="F22">
-        <v>3325</v>
+        <v>3426</v>
       </c>
       <c r="G22">
-        <v>129.04814814814819</v>
+        <v>128.6037037037037</v>
       </c>
       <c r="H22">
-        <v>11.50740740740741</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="I22">
-        <v>11.50740740740741</v>
+        <v>11.851851851851849</v>
       </c>
       <c r="J22">
-        <v>10.329629629629631</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K22">
-        <v>0.8037037037037037</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L22">
-        <v>0.8037037037037037</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M22">
-        <v>0.17777777777777781</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N22">
-        <v>3.7037037037037038E-3</v>
+        <v>2.5925925925925929E-2</v>
       </c>
       <c r="O22">
-        <v>0.18148148148148149</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="P22">
-        <v>128.51111111111109</v>
+        <v>128.137037037037</v>
       </c>
       <c r="Q22" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="R22">
-        <v>33.333333333333329</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S22" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="T22">
-        <v>64.444444444444443</v>
+        <v>65.925925925925924</v>
       </c>
       <c r="U22" t="s">
+        <v>35</v>
+      </c>
+      <c r="V22" s="19">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W22" t="s">
+        <v>39</v>
+      </c>
+      <c r="X22" s="16">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="Y22">
+        <v>34723</v>
+      </c>
+      <c r="Z22">
+        <v>3200</v>
+      </c>
+      <c r="AA22">
+        <v>37923</v>
+      </c>
+      <c r="AB22">
+        <v>2383</v>
+      </c>
+      <c r="AC22">
+        <v>219</v>
+      </c>
+      <c r="AD22">
+        <v>2786</v>
+      </c>
+      <c r="AE22">
+        <v>39</v>
+      </c>
+      <c r="AF22">
+        <v>7</v>
+      </c>
+      <c r="AG22" s="14">
         <v>46</v>
-      </c>
-      <c r="V22" s="23">
-        <v>96.296296296296291</v>
-      </c>
-      <c r="W22" t="s">
-        <v>35</v>
-      </c>
-      <c r="X22" s="24">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="Y22">
-        <v>34843</v>
-      </c>
-      <c r="Z22">
-        <v>3107</v>
-      </c>
-      <c r="AA22">
-        <v>37950</v>
-      </c>
-      <c r="AB22">
-        <v>2376</v>
-      </c>
-      <c r="AC22">
-        <v>217</v>
-      </c>
-      <c r="AD22">
-        <v>2789</v>
-      </c>
-      <c r="AE22">
-        <v>48</v>
-      </c>
-      <c r="AF22">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="14">
-        <v>49</v>
       </c>
       <c r="AH22" s="13">
         <v>141453000000</v>
       </c>
       <c r="AI22" s="13">
-        <v>188156825900</v>
+        <v>185127962700</v>
       </c>
       <c r="AJ22" s="13">
-        <v>46703825900</v>
+        <v>43674962700</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -3167,108 +3168,108 @@
         <v>32</v>
       </c>
       <c r="D23">
-        <v>132.21053559719121</v>
+        <v>126.5481083469421</v>
       </c>
       <c r="E23">
         <v>40737</v>
       </c>
       <c r="F23">
-        <v>3403</v>
+        <v>3458</v>
       </c>
       <c r="G23">
-        <v>128.59629629629629</v>
+        <v>128.41851851851851</v>
       </c>
       <c r="H23">
-        <v>11.78888888888889</v>
+        <v>11.988888888888891</v>
       </c>
       <c r="I23">
-        <v>11.78888888888889</v>
+        <v>11.988888888888891</v>
       </c>
       <c r="J23">
-        <v>10.31481481481481</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K23">
-        <v>0.79629629629629628</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="L23">
-        <v>0.79629629629629628</v>
+        <v>0.81111111111111112</v>
       </c>
       <c r="M23">
-        <v>0.15925925925925929</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="N23">
-        <v>1.8518518518518521E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O23">
-        <v>0.17777777777777781</v>
+        <v>0.15185185185185179</v>
       </c>
       <c r="P23">
-        <v>128.14444444444439</v>
+        <v>128.0185185185185</v>
       </c>
       <c r="Q23" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="R23">
-        <v>34.074074074074083</v>
+        <v>32.962962962962962</v>
       </c>
       <c r="S23" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="T23">
-        <v>64.81481481481481</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U23" t="s">
-        <v>35</v>
-      </c>
-      <c r="V23" s="24">
-        <v>92.592592592592595</v>
+        <v>36</v>
+      </c>
+      <c r="V23" s="16">
+        <v>81.481481481481481</v>
       </c>
       <c r="W23" t="s">
+        <v>71</v>
+      </c>
+      <c r="X23">
+        <v>74.074074074074076</v>
+      </c>
+      <c r="Y23">
+        <v>34673</v>
+      </c>
+      <c r="Z23">
+        <v>3237</v>
+      </c>
+      <c r="AA23">
+        <v>37910</v>
+      </c>
+      <c r="AB23">
+        <v>2403</v>
+      </c>
+      <c r="AC23">
+        <v>219</v>
+      </c>
+      <c r="AD23">
+        <v>2786</v>
+      </c>
+      <c r="AE23">
         <v>39</v>
       </c>
-      <c r="X23">
-        <v>88.888888888888886</v>
-      </c>
-      <c r="Y23">
-        <v>34721</v>
-      </c>
-      <c r="Z23">
-        <v>3183</v>
-      </c>
-      <c r="AA23">
-        <v>37904</v>
-      </c>
-      <c r="AB23">
-        <v>2378</v>
-      </c>
-      <c r="AC23">
-        <v>215</v>
-      </c>
-      <c r="AD23">
-        <v>2785</v>
-      </c>
-      <c r="AE23">
-        <v>43</v>
-      </c>
       <c r="AF23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG23">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="AH23" s="13">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI23" s="13">
-        <v>186905108700</v>
+        <v>179006095700</v>
       </c>
       <c r="AJ23" s="13">
-        <v>45535808700</v>
+        <v>37553095700</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -3277,108 +3278,108 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>131.9339636487031</v>
+        <v>135.58581099291001</v>
       </c>
       <c r="E24">
-        <v>40773</v>
+        <v>40777</v>
       </c>
       <c r="F24">
-        <v>3434</v>
+        <v>3411</v>
       </c>
       <c r="G24">
-        <v>128.65185185185189</v>
+        <v>128.72962962962961</v>
       </c>
       <c r="H24">
-        <v>11.87037037037037</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="I24">
-        <v>11.87037037037037</v>
+        <v>11.80740740740741</v>
       </c>
       <c r="J24">
-        <v>10.31851851851852</v>
+        <v>10.3</v>
       </c>
       <c r="K24">
-        <v>0.84444444444444444</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L24">
-        <v>0.84444444444444444</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M24">
-        <v>0.16666666666666671</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="N24">
-        <v>3.7037037037037038E-3</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O24">
-        <v>0.17037037037037039</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="P24">
-        <v>128.10740740740741</v>
+        <v>128.11481481481479</v>
       </c>
       <c r="Q24" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="R24">
-        <v>30.37037037037037</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="T24">
-        <v>68.518518518518519</v>
+        <v>65.18518518518519</v>
       </c>
       <c r="U24" t="s">
-        <v>39</v>
-      </c>
-      <c r="V24" s="14">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V24" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W24" t="s">
-        <v>40</v>
-      </c>
-      <c r="X24">
-        <v>77.777777777777786</v>
+        <v>35</v>
+      </c>
+      <c r="X24" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y24">
-        <v>34736</v>
+        <v>34757</v>
       </c>
       <c r="Z24">
-        <v>3205</v>
+        <v>3188</v>
       </c>
       <c r="AA24">
-        <v>37941</v>
+        <v>37945</v>
       </c>
       <c r="AB24">
-        <v>2374</v>
+        <v>2356</v>
       </c>
       <c r="AC24">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AD24">
-        <v>2786</v>
+        <v>2781</v>
       </c>
       <c r="AE24">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF24">
-        <v>1</v>
-      </c>
-      <c r="AG24">
-        <v>46</v>
+        <v>2</v>
+      </c>
+      <c r="AG24" s="17">
+        <v>51</v>
       </c>
       <c r="AH24" s="13">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI24" s="13">
-        <v>186624549600</v>
-      </c>
-      <c r="AJ24" s="13">
-        <v>45171549600</v>
+        <v>191676711900</v>
+      </c>
+      <c r="AJ24" s="20">
+        <v>50307411900</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -3387,108 +3388,108 @@
         <v>32</v>
       </c>
       <c r="D25">
-        <v>131.9139846487179</v>
+        <v>133.0172042303804</v>
       </c>
       <c r="E25">
-        <v>40715</v>
+        <v>40788</v>
       </c>
       <c r="F25">
-        <v>3314</v>
+        <v>3325</v>
       </c>
       <c r="G25">
-        <v>128.85925925925929</v>
+        <v>129.04814814814819</v>
       </c>
       <c r="H25">
-        <v>11.4037037037037</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="I25">
-        <v>11.4037037037037</v>
+        <v>11.50740740740741</v>
       </c>
       <c r="J25">
-        <v>10.36296296296296</v>
+        <v>10.329629629629631</v>
       </c>
       <c r="K25">
-        <v>0.85555555555555551</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="L25">
-        <v>0.85555555555555551</v>
+        <v>0.8037037037037037</v>
       </c>
       <c r="M25">
-        <v>0.15555555555555561</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="N25">
-        <v>1.4814814814814821E-2</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O25">
-        <v>0.17037037037037039</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="P25">
-        <v>128.47407407407411</v>
+        <v>128.51111111111109</v>
       </c>
       <c r="Q25" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="R25">
-        <v>32.222222222222221</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S25" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="T25">
-        <v>65.18518518518519</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U25" t="s">
-        <v>39</v>
-      </c>
-      <c r="V25" s="14">
-        <v>88.888888888888886</v>
+        <v>46</v>
+      </c>
+      <c r="V25" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="W25" t="s">
-        <v>39</v>
-      </c>
-      <c r="X25">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="X25" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y25">
-        <v>34792</v>
+        <v>34843</v>
       </c>
       <c r="Z25">
-        <v>3079</v>
+        <v>3107</v>
       </c>
       <c r="AA25">
-        <v>37871</v>
+        <v>37950</v>
       </c>
       <c r="AB25">
-        <v>2383</v>
+        <v>2376</v>
       </c>
       <c r="AC25">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="AD25">
-        <v>2798</v>
+        <v>2789</v>
       </c>
       <c r="AE25">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG25" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AH25" s="13">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI25" s="13">
-        <v>186485876700</v>
+        <v>188156825900</v>
       </c>
       <c r="AJ25" s="13">
-        <v>45116576700</v>
+        <v>46703825900</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -3497,108 +3498,108 @@
         <v>32</v>
       </c>
       <c r="D26">
-        <v>131.4573185974607</v>
+        <v>124.8752582066969</v>
       </c>
       <c r="E26">
-        <v>40730</v>
+        <v>40701</v>
       </c>
       <c r="F26">
-        <v>3412</v>
+        <v>3364</v>
       </c>
       <c r="G26">
-        <v>128.65555555555559</v>
+        <v>128.71851851851849</v>
       </c>
       <c r="H26">
-        <v>11.733333333333331</v>
+        <v>11.58888888888889</v>
       </c>
       <c r="I26">
-        <v>11.733333333333331</v>
+        <v>11.58888888888889</v>
       </c>
       <c r="J26">
-        <v>10.3</v>
+        <v>10.296296296296299</v>
       </c>
       <c r="K26">
-        <v>0.8925925925925926</v>
+        <v>0.85925925925925928</v>
       </c>
       <c r="L26">
-        <v>0.8925925925925926</v>
+        <v>0.85925925925925928</v>
       </c>
       <c r="M26">
-        <v>0.15185185185185179</v>
+        <v>0.12962962962962959</v>
       </c>
       <c r="N26">
         <v>1.111111111111111E-2</v>
       </c>
       <c r="O26">
-        <v>0.162962962962963</v>
+        <v>0.14074074074074069</v>
       </c>
       <c r="P26">
-        <v>128.11111111111109</v>
+        <v>128.28888888888889</v>
       </c>
       <c r="Q26" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="R26">
-        <v>30.74074074074074</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="S26" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="T26">
-        <v>67.777777777777786</v>
+        <v>64.074074074074076</v>
       </c>
       <c r="U26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V26" s="14">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V26" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W26" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="X26">
-        <v>74.074074074074076</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y26">
-        <v>34737</v>
+        <v>34754</v>
       </c>
       <c r="Z26">
-        <v>3168</v>
+        <v>3129</v>
       </c>
       <c r="AA26">
-        <v>37905</v>
+        <v>37883</v>
       </c>
       <c r="AB26">
-        <v>2364</v>
+        <v>2396</v>
       </c>
       <c r="AC26">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AD26">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="AE26">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AF26">
         <v>3</v>
       </c>
       <c r="AG26" s="14">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AH26" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI26" s="13">
-        <v>185840291100</v>
+        <v>176535278400</v>
       </c>
       <c r="AJ26" s="13">
-        <v>44470991100</v>
+        <v>35165978400</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -3607,108 +3608,108 @@
         <v>32</v>
       </c>
       <c r="D27">
-        <v>130.87595363831099</v>
+        <v>138.19172896802911</v>
       </c>
       <c r="E27">
-        <v>40755</v>
+        <v>40771</v>
       </c>
       <c r="F27">
-        <v>3426</v>
+        <v>3411</v>
       </c>
       <c r="G27">
-        <v>128.6037037037037</v>
+        <v>128.61481481481479</v>
       </c>
       <c r="H27">
-        <v>11.851851851851849</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="I27">
-        <v>11.851851851851849</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="J27">
-        <v>10.31851851851852</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="K27">
-        <v>0.81111111111111112</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="L27">
-        <v>0.81111111111111112</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="M27">
-        <v>0.1444444444444444</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="N27">
-        <v>2.5925925925925929E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O27">
-        <v>0.17037037037037039</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P27">
-        <v>128.137037037037</v>
+        <v>128.11481481481479</v>
       </c>
       <c r="Q27" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="R27">
-        <v>32.962962962962962</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S27" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="T27">
-        <v>65.925925925925924</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U27" t="s">
-        <v>35</v>
-      </c>
-      <c r="V27" s="24">
-        <v>92.592592592592595</v>
+        <v>54</v>
+      </c>
+      <c r="V27" s="17">
+        <v>100</v>
       </c>
       <c r="W27" t="s">
-        <v>39</v>
-      </c>
-      <c r="X27">
-        <v>88.888888888888886</v>
+        <v>54</v>
+      </c>
+      <c r="X27" s="17">
+        <v>100</v>
       </c>
       <c r="Y27">
-        <v>34723</v>
+        <v>34726</v>
       </c>
       <c r="Z27">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="AA27">
-        <v>37923</v>
+        <v>37924</v>
       </c>
       <c r="AB27">
-        <v>2383</v>
+        <v>2361</v>
       </c>
       <c r="AC27">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AD27">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="AE27">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AF27">
-        <v>7</v>
-      </c>
-      <c r="AG27" s="14">
-        <v>46</v>
+        <v>2</v>
+      </c>
+      <c r="AG27" s="17">
+        <v>55</v>
       </c>
       <c r="AH27" s="13">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI27" s="13">
-        <v>185127962700</v>
-      </c>
-      <c r="AJ27" s="13">
-        <v>43674962700</v>
+        <v>195360679900</v>
+      </c>
+      <c r="AJ27" s="20">
+        <v>53991379900</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -3717,108 +3718,108 @@
         <v>32</v>
       </c>
       <c r="D28">
-        <v>130.80206183379281</v>
+        <v>134.38630954528321</v>
       </c>
       <c r="E28">
-        <v>40732</v>
+        <v>40738</v>
       </c>
       <c r="F28">
-        <v>3363</v>
+        <v>3283</v>
       </c>
       <c r="G28">
-        <v>128.76666666666671</v>
+        <v>128.9296296296296</v>
       </c>
       <c r="H28">
-        <v>11.607407407407409</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="I28">
-        <v>11.607407407407409</v>
+        <v>11.38148148148148</v>
       </c>
       <c r="J28">
-        <v>10.31851851851852</v>
+        <v>10.37777777777778</v>
       </c>
       <c r="K28">
-        <v>0.84444444444444444</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="L28">
-        <v>0.84444444444444444</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="M28">
-        <v>0.162962962962963</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N28">
-        <v>3.7037037037037038E-3</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O28">
-        <v>0.16666666666666671</v>
+        <v>0.19259259259259259</v>
       </c>
       <c r="P28">
-        <v>128.2925925925926</v>
+        <v>128.61111111111109</v>
       </c>
       <c r="Q28" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="R28">
-        <v>31.851851851851851</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S28" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="T28">
-        <v>65.555555555555557</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U28" t="s">
-        <v>35</v>
-      </c>
-      <c r="V28" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="V28" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W28" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="X28">
-        <v>81.481481481481481</v>
+        <v>88.888888888888886</v>
       </c>
       <c r="Y28">
-        <v>34767</v>
+        <v>34811</v>
       </c>
       <c r="Z28">
-        <v>3134</v>
+        <v>3073</v>
       </c>
       <c r="AA28">
-        <v>37901</v>
+        <v>37884</v>
       </c>
       <c r="AB28">
-        <v>2378</v>
+        <v>2389</v>
       </c>
       <c r="AC28">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="AD28">
-        <v>2786</v>
+        <v>2802</v>
       </c>
       <c r="AE28">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AF28">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="14">
-        <v>45</v>
+        <v>5</v>
+      </c>
+      <c r="AG28" s="17">
+        <v>52</v>
       </c>
       <c r="AH28" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI28" s="13">
-        <v>184913959200</v>
+        <v>189980985100</v>
       </c>
       <c r="AJ28" s="13">
-        <v>43544659200</v>
+        <v>48611685100</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -3827,49 +3828,49 @@
         <v>32</v>
       </c>
       <c r="D29">
-        <v>130.43550537492939</v>
+        <v>134.1387439139898</v>
       </c>
       <c r="E29">
-        <v>40707</v>
+        <v>40740</v>
       </c>
       <c r="F29">
-        <v>3470</v>
+        <v>3322</v>
       </c>
       <c r="G29">
-        <v>128.28888888888889</v>
+        <v>128.78518518518521</v>
       </c>
       <c r="H29">
-        <v>11.9962962962963</v>
+        <v>11.525925925925931</v>
       </c>
       <c r="I29">
-        <v>11.9962962962963</v>
+        <v>11.525925925925931</v>
       </c>
       <c r="J29">
-        <v>10.31851851851852</v>
+        <v>10.388888888888889</v>
       </c>
       <c r="K29">
-        <v>0.8481481481481481</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="L29">
-        <v>0.8481481481481481</v>
+        <v>0.77407407407407403</v>
       </c>
       <c r="M29">
-        <v>0.15555555555555561</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="N29">
-        <v>7.4074074074074077E-3</v>
+        <v>3.7037037037037038E-3</v>
       </c>
       <c r="O29">
-        <v>0.162962962962963</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="P29">
-        <v>127.8962962962963</v>
+        <v>128.44444444444451</v>
       </c>
       <c r="Q29" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="R29">
-        <v>34.444444444444443</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S29" t="s">
         <v>44</v>
@@ -3878,57 +3879,57 @@
         <v>62.962962962962962</v>
       </c>
       <c r="U29" t="s">
-        <v>46</v>
-      </c>
-      <c r="V29" s="23">
-        <v>96.296296296296291</v>
+        <v>54</v>
+      </c>
+      <c r="V29" s="17">
+        <v>100</v>
       </c>
       <c r="W29" t="s">
-        <v>47</v>
-      </c>
-      <c r="X29">
-        <v>85.18518518518519</v>
+        <v>54</v>
+      </c>
+      <c r="X29" s="17">
+        <v>100</v>
       </c>
       <c r="Y29">
-        <v>34638</v>
+        <v>34772</v>
       </c>
       <c r="Z29">
-        <v>3239</v>
+        <v>3112</v>
       </c>
       <c r="AA29">
-        <v>37877</v>
+        <v>37884</v>
       </c>
       <c r="AB29">
-        <v>2381</v>
+        <v>2392</v>
       </c>
       <c r="AC29">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="AD29">
-        <v>2786</v>
+        <v>2805</v>
       </c>
       <c r="AE29">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF29">
-        <v>2</v>
-      </c>
-      <c r="AG29" s="14">
-        <v>44</v>
+        <v>1</v>
+      </c>
+      <c r="AG29" s="17">
+        <v>51</v>
       </c>
       <c r="AH29" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI29" s="13">
-        <v>184395760900</v>
+        <v>189631003300</v>
       </c>
       <c r="AJ29" s="13">
-        <v>43026460900</v>
+        <v>48261703300</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -3937,108 +3938,108 @@
         <v>32</v>
       </c>
       <c r="D30">
-        <v>129.69486055438909</v>
+        <v>133.0426598940991</v>
       </c>
       <c r="E30">
-        <v>40752</v>
+        <v>40773</v>
       </c>
       <c r="F30">
-        <v>3420</v>
+        <v>3382</v>
       </c>
       <c r="G30">
-        <v>128.66666666666671</v>
+        <v>128.77407407407409</v>
       </c>
       <c r="H30">
-        <v>11.796296296296299</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="I30">
-        <v>11.796296296296299</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="J30">
-        <v>10.31111111111111</v>
+        <v>10.34814814814815</v>
       </c>
       <c r="K30">
-        <v>0.86296296296296293</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L30">
-        <v>0.86296296296296293</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M30">
-        <v>0.15185185185185179</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N30">
-        <v>7.4074074074074077E-3</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O30">
-        <v>0.15925925925925929</v>
+        <v>0.18148148148148149</v>
       </c>
       <c r="P30">
-        <v>128.1592592592593</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="Q30" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R30" s="14">
-        <v>32.222222222222221</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="T30" s="14">
-        <v>66.666666666666657</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U30" t="s">
         <v>46</v>
       </c>
-      <c r="V30" s="23">
+      <c r="V30" s="18">
         <v>96.296296296296291</v>
       </c>
       <c r="W30" t="s">
-        <v>39</v>
-      </c>
-      <c r="X30">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="X30" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y30">
-        <v>34740</v>
+        <v>34769</v>
       </c>
       <c r="Z30">
-        <v>3185</v>
+        <v>3161</v>
       </c>
       <c r="AA30">
-        <v>37925</v>
+        <v>37930</v>
       </c>
       <c r="AB30">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="AC30">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="AD30">
-        <v>2784</v>
+        <v>2794</v>
       </c>
       <c r="AE30">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AF30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG30" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AH30" s="13">
         <v>141453000000</v>
       </c>
       <c r="AI30" s="13">
-        <v>183457271100</v>
+        <v>188192833700</v>
       </c>
       <c r="AJ30" s="13">
-        <v>42004271100</v>
+        <v>46739833700</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4047,108 +4048,108 @@
         <v>32</v>
       </c>
       <c r="D31">
-        <v>129.30531876439929</v>
+        <v>123.5907913528609</v>
       </c>
       <c r="E31">
-        <v>40733</v>
+        <v>40670</v>
       </c>
       <c r="F31">
-        <v>3334</v>
+        <v>3413</v>
       </c>
       <c r="G31">
-        <v>128.72592592592591</v>
+        <v>128.37407407407409</v>
       </c>
       <c r="H31">
-        <v>11.607407407407409</v>
+        <v>11.792592592592589</v>
       </c>
       <c r="I31">
-        <v>11.607407407407409</v>
+        <v>11.792592592592589</v>
       </c>
       <c r="J31">
-        <v>10.35555555555556</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K31">
-        <v>0.73333333333333328</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="L31">
-        <v>0.73333333333333328</v>
+        <v>0.83703703703703702</v>
       </c>
       <c r="M31">
-        <v>0.16666666666666671</v>
+        <v>0.12592592592592591</v>
       </c>
       <c r="N31">
-        <v>7.4074074074074077E-3</v>
+        <v>1.111111111111111E-2</v>
       </c>
       <c r="O31">
-        <v>0.1740740740740741</v>
+        <v>0.13703703703703701</v>
       </c>
       <c r="P31">
-        <v>128.4</v>
+        <v>128.10740740740741</v>
       </c>
       <c r="Q31" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="R31">
-        <v>34.444444444444443</v>
+        <v>33.703703703703702</v>
       </c>
       <c r="S31" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="T31">
-        <v>62.222222222222221</v>
+        <v>65.555555555555557</v>
       </c>
       <c r="U31" t="s">
-        <v>46</v>
-      </c>
-      <c r="V31" s="23">
-        <v>96.296296296296291</v>
+        <v>35</v>
+      </c>
+      <c r="V31" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W31" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="X31">
-        <v>88.888888888888886</v>
+        <v>70.370370370370367</v>
       </c>
       <c r="Y31">
-        <v>34756</v>
+        <v>34661</v>
       </c>
       <c r="Z31">
-        <v>3134</v>
+        <v>3184</v>
       </c>
       <c r="AA31">
-        <v>37890</v>
+        <v>37845</v>
       </c>
       <c r="AB31">
-        <v>2410</v>
+        <v>2414</v>
       </c>
       <c r="AC31">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="AD31">
-        <v>2796</v>
+        <v>2788</v>
       </c>
       <c r="AE31">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="AF31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG31" s="14">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="AH31" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI31" s="13">
-        <v>182798024000</v>
+        <v>174719436600</v>
       </c>
       <c r="AJ31" s="13">
-        <v>41428724000</v>
+        <v>33350136600</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -4157,108 +4158,108 @@
         <v>32</v>
       </c>
       <c r="D32">
-        <v>129.28038824553849</v>
+        <v>137.4216820766602</v>
       </c>
       <c r="E32">
-        <v>40743</v>
+        <v>40801</v>
       </c>
       <c r="F32">
-        <v>3419</v>
+        <v>3370</v>
       </c>
       <c r="G32">
-        <v>128.6185185185185</v>
+        <v>128.88888888888891</v>
       </c>
       <c r="H32">
-        <v>11.829629629629631</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="I32">
-        <v>11.829629629629631</v>
+        <v>11.703703703703701</v>
       </c>
       <c r="J32">
-        <v>10.28888888888889</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K32">
-        <v>0.81851851851851853</v>
+        <v>0.76296296296296295</v>
       </c>
       <c r="L32">
-        <v>0.81851851851851853</v>
+        <v>0.76296296296296295</v>
       </c>
       <c r="M32">
-        <v>0.14814814814814811</v>
+        <v>0.18888888888888891</v>
       </c>
       <c r="N32">
         <v>1.4814814814814821E-2</v>
       </c>
       <c r="O32">
-        <v>0.162962962962963</v>
+        <v>0.20370370370370369</v>
       </c>
       <c r="P32">
-        <v>128.0851851851852</v>
+        <v>128.28148148148151</v>
       </c>
       <c r="Q32" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="R32" s="14">
-        <v>35.185185185185183</v>
+        <v>34.074074074074083</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="T32" s="14">
-        <v>62.962962962962962</v>
+        <v>63.703703703703709</v>
       </c>
       <c r="U32" t="s">
-        <v>35</v>
-      </c>
-      <c r="V32" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="V32" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W32" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="X32">
-        <v>77.777777777777786</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="Y32">
-        <v>34727</v>
+        <v>34800</v>
       </c>
       <c r="Z32">
-        <v>3194</v>
+        <v>3160</v>
       </c>
       <c r="AA32">
-        <v>37921</v>
+        <v>37960</v>
       </c>
       <c r="AB32">
-        <v>2381</v>
+        <v>2360</v>
       </c>
       <c r="AC32">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="AD32">
-        <v>2778</v>
+        <v>2786</v>
       </c>
       <c r="AE32">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AF32">
         <v>4</v>
       </c>
-      <c r="AG32" s="14">
-        <v>44</v>
+      <c r="AG32" s="17">
+        <v>55</v>
       </c>
       <c r="AH32" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI32" s="13">
-        <v>182762779900</v>
-      </c>
-      <c r="AJ32" s="13">
-        <v>41393479900</v>
+        <v>194272070000</v>
+      </c>
+      <c r="AJ32" s="20">
+        <v>52902770000</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -4267,108 +4268,108 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>129.1463196747809</v>
+        <v>132.21053559719121</v>
       </c>
       <c r="E33">
-        <v>40700</v>
+        <v>40737</v>
       </c>
       <c r="F33">
-        <v>3369</v>
+        <v>3403</v>
       </c>
       <c r="G33">
-        <v>128.6333333333333</v>
+        <v>128.59629629629629</v>
       </c>
       <c r="H33">
-        <v>11.614814814814819</v>
+        <v>11.78888888888889</v>
       </c>
       <c r="I33">
-        <v>11.614814814814819</v>
+        <v>11.78888888888889</v>
       </c>
       <c r="J33">
-        <v>10.33333333333333</v>
+        <v>10.31481481481481</v>
       </c>
       <c r="K33">
-        <v>0.8481481481481481</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L33">
-        <v>0.8481481481481481</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M33">
-        <v>0.1444444444444444</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="N33">
-        <v>1.4814814814814821E-2</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O33">
-        <v>0.15925925925925929</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="P33">
-        <v>128.27037037037039</v>
+        <v>128.14444444444439</v>
       </c>
       <c r="Q33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R33" s="14">
-        <v>29.25925925925926</v>
+        <v>34.074074074074083</v>
       </c>
       <c r="S33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T33" s="14">
-        <v>69.259259259259252</v>
+        <v>64.81481481481481</v>
       </c>
       <c r="U33" t="s">
-        <v>54</v>
-      </c>
-      <c r="V33" s="22">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="V33" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W33" t="s">
-        <v>35</v>
-      </c>
-      <c r="X33" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="X33" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="Y33">
-        <v>34731</v>
+        <v>34721</v>
       </c>
       <c r="Z33">
-        <v>3136</v>
+        <v>3183</v>
       </c>
       <c r="AA33">
-        <v>37867</v>
+        <v>37904</v>
       </c>
       <c r="AB33">
-        <v>2389</v>
+        <v>2378</v>
       </c>
       <c r="AC33">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AD33">
-        <v>2790</v>
+        <v>2785</v>
       </c>
       <c r="AE33">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AF33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG33" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="AH33" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI33" s="13">
-        <v>182573248100</v>
+        <v>186905108700</v>
       </c>
       <c r="AJ33" s="13">
-        <v>41203948100</v>
+        <v>45535808700</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -4377,108 +4378,108 @@
         <v>32</v>
       </c>
       <c r="D34">
-        <v>127.00580383590309</v>
+        <v>130.43550537492939</v>
       </c>
       <c r="E34">
-        <v>40759</v>
+        <v>40707</v>
       </c>
       <c r="F34">
-        <v>3357</v>
+        <v>3470</v>
       </c>
       <c r="G34">
-        <v>128.862962962963</v>
+        <v>128.28888888888889</v>
       </c>
       <c r="H34">
-        <v>11.63703703703704</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="I34">
-        <v>11.63703703703704</v>
+        <v>11.9962962962963</v>
       </c>
       <c r="J34">
-        <v>10.3</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K34">
-        <v>0.78148148148148144</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="L34">
-        <v>0.78148148148148144</v>
+        <v>0.8481481481481481</v>
       </c>
       <c r="M34">
-        <v>0.1444444444444444</v>
+        <v>0.15555555555555561</v>
       </c>
       <c r="N34">
-        <v>1.4814814814814821E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O34">
-        <v>0.15925925925925929</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P34">
-        <v>128.39259259259259</v>
+        <v>127.8962962962963</v>
       </c>
       <c r="Q34" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="R34">
-        <v>34.814814814814817</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S34" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="T34">
-        <v>64.444444444444443</v>
+        <v>62.962962962962962</v>
       </c>
       <c r="U34" t="s">
         <v>46</v>
       </c>
-      <c r="V34" s="23">
+      <c r="V34" s="18">
         <v>96.296296296296291</v>
       </c>
       <c r="W34" t="s">
-        <v>35</v>
-      </c>
-      <c r="X34" s="24">
-        <v>92.592592592592595</v>
+        <v>47</v>
+      </c>
+      <c r="X34" s="16">
+        <v>85.18518518518519</v>
       </c>
       <c r="Y34">
-        <v>34793</v>
+        <v>34638</v>
       </c>
       <c r="Z34">
-        <v>3142</v>
+        <v>3239</v>
       </c>
       <c r="AA34">
-        <v>37935</v>
+        <v>37877</v>
       </c>
       <c r="AB34">
-        <v>2398</v>
+        <v>2381</v>
       </c>
       <c r="AC34">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="AD34">
-        <v>2781</v>
+        <v>2786</v>
       </c>
       <c r="AE34">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AF34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH34" s="13">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI34" s="13">
-        <v>179653519700</v>
+        <v>184395760900</v>
       </c>
       <c r="AJ34" s="13">
-        <v>38200519700</v>
+        <v>43026460900</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
         <v>31</v>
@@ -4487,108 +4488,108 @@
         <v>32</v>
       </c>
       <c r="D35">
-        <v>126.93712022341479</v>
+        <v>129.30531876439929</v>
       </c>
       <c r="E35">
-        <v>40684</v>
+        <v>40733</v>
       </c>
       <c r="F35">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="G35">
-        <v>128.62222222222221</v>
+        <v>128.72592592592591</v>
       </c>
       <c r="H35">
-        <v>11.514814814814811</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="I35">
-        <v>11.514814814814811</v>
+        <v>11.607407407407409</v>
       </c>
       <c r="J35">
-        <v>10.392592592592591</v>
+        <v>10.35555555555556</v>
       </c>
       <c r="K35">
-        <v>0.83333333333333337</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L35">
-        <v>0.83333333333333337</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M35">
-        <v>0.13703703703703701</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="N35">
-        <v>1.4814814814814821E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O35">
-        <v>0.15185185185185179</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="P35">
-        <v>128.38518518518521</v>
+        <v>128.4</v>
       </c>
       <c r="Q35" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="R35">
-        <v>32.592592592592602</v>
+        <v>34.444444444444443</v>
       </c>
       <c r="S35" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="T35">
-        <v>64.81481481481481</v>
+        <v>62.222222222222221</v>
       </c>
       <c r="U35" t="s">
+        <v>46</v>
+      </c>
+      <c r="V35" s="18">
+        <v>96.296296296296291</v>
+      </c>
+      <c r="W35" t="s">
         <v>39</v>
       </c>
-      <c r="V35" s="14">
+      <c r="X35">
         <v>88.888888888888886</v>
       </c>
-      <c r="W35" t="s">
-        <v>40</v>
-      </c>
-      <c r="X35">
-        <v>77.777777777777786</v>
-      </c>
       <c r="Y35">
-        <v>34728</v>
+        <v>34756</v>
       </c>
       <c r="Z35">
-        <v>3109</v>
+        <v>3134</v>
       </c>
       <c r="AA35">
-        <v>37837</v>
+        <v>37890</v>
       </c>
       <c r="AB35">
-        <v>2417</v>
+        <v>2410</v>
       </c>
       <c r="AC35">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="AD35">
-        <v>2806</v>
+        <v>2796</v>
       </c>
       <c r="AE35">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AF35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG35">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AH35" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI35" s="13">
-        <v>179450118300</v>
+        <v>182798024000</v>
       </c>
       <c r="AJ35" s="13">
-        <v>38080818300</v>
+        <v>41428724000</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>31</v>
@@ -4597,108 +4598,108 @@
         <v>32</v>
       </c>
       <c r="D36">
-        <v>126.5481083469421</v>
+        <v>127.00580383590309</v>
       </c>
       <c r="E36">
-        <v>40737</v>
+        <v>40759</v>
       </c>
       <c r="F36">
-        <v>3458</v>
+        <v>3357</v>
       </c>
       <c r="G36">
-        <v>128.41851851851851</v>
+        <v>128.862962962963</v>
       </c>
       <c r="H36">
-        <v>11.988888888888891</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="I36">
-        <v>11.988888888888891</v>
+        <v>11.63703703703704</v>
       </c>
       <c r="J36">
-        <v>10.31851851851852</v>
+        <v>10.3</v>
       </c>
       <c r="K36">
-        <v>0.81111111111111112</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="L36">
-        <v>0.81111111111111112</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="M36">
         <v>0.1444444444444444</v>
       </c>
       <c r="N36">
-        <v>7.4074074074074077E-3</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O36">
-        <v>0.15185185185185179</v>
+        <v>0.15925925925925929</v>
       </c>
       <c r="P36">
-        <v>128.0185185185185</v>
+        <v>128.39259259259259</v>
       </c>
       <c r="Q36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R36">
-        <v>32.962962962962962</v>
+        <v>34.814814814814817</v>
       </c>
       <c r="S36" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="T36">
-        <v>65.555555555555557</v>
+        <v>64.444444444444443</v>
       </c>
       <c r="U36" t="s">
-        <v>36</v>
-      </c>
-      <c r="V36" s="14">
-        <v>81.481481481481481</v>
+        <v>46</v>
+      </c>
+      <c r="V36" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="W36" t="s">
-        <v>71</v>
-      </c>
-      <c r="X36">
-        <v>74.074074074074076</v>
+        <v>35</v>
+      </c>
+      <c r="X36" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="Y36">
-        <v>34673</v>
+        <v>34793</v>
       </c>
       <c r="Z36">
-        <v>3237</v>
+        <v>3142</v>
       </c>
       <c r="AA36">
-        <v>37910</v>
+        <v>37935</v>
       </c>
       <c r="AB36">
-        <v>2403</v>
+        <v>2398</v>
       </c>
       <c r="AC36">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AD36">
-        <v>2786</v>
+        <v>2781</v>
       </c>
       <c r="AE36">
         <v>39</v>
       </c>
       <c r="AF36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG36">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH36" s="13">
         <v>141453000000</v>
       </c>
       <c r="AI36" s="13">
-        <v>179006095700</v>
+        <v>179653519700</v>
       </c>
       <c r="AJ36" s="13">
-        <v>37553095700</v>
+        <v>38200519700</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -4707,61 +4708,61 @@
         <v>32</v>
       </c>
       <c r="D37">
-        <v>124.8752582066969</v>
+        <v>133.03770415500401</v>
       </c>
       <c r="E37">
-        <v>40701</v>
+        <v>40727</v>
       </c>
       <c r="F37">
-        <v>3364</v>
+        <v>3298</v>
       </c>
       <c r="G37">
-        <v>128.71851851851849</v>
+        <v>128.9148148148148</v>
       </c>
       <c r="H37">
-        <v>11.58888888888889</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="I37">
-        <v>11.58888888888889</v>
+        <v>11.37407407407407</v>
       </c>
       <c r="J37">
-        <v>10.296296296296299</v>
+        <v>10.37407407407407</v>
       </c>
       <c r="K37">
-        <v>0.85925925925925928</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L37">
-        <v>0.85925925925925928</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M37">
-        <v>0.12962962962962959</v>
+        <v>0.17037037037037039</v>
       </c>
       <c r="N37">
-        <v>1.111111111111111E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="O37">
-        <v>0.14074074074074069</v>
+        <v>0.17777777777777781</v>
       </c>
       <c r="P37">
-        <v>128.28888888888889</v>
+        <v>128.5333333333333</v>
       </c>
       <c r="Q37" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R37">
-        <v>33.333333333333329</v>
+        <v>35.185185185185183</v>
       </c>
       <c r="S37" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="T37">
-        <v>64.074074074074076</v>
+        <v>61.481481481481481</v>
       </c>
       <c r="U37" t="s">
-        <v>35</v>
-      </c>
-      <c r="V37" s="24">
-        <v>92.592592592592595</v>
+        <v>46</v>
+      </c>
+      <c r="V37" s="18">
+        <v>96.296296296296291</v>
       </c>
       <c r="W37" t="s">
         <v>47</v>
@@ -4770,45 +4771,45 @@
         <v>85.18518518518519</v>
       </c>
       <c r="Y37">
-        <v>34754</v>
+        <v>34807</v>
       </c>
       <c r="Z37">
-        <v>3129</v>
+        <v>3071</v>
       </c>
       <c r="AA37">
-        <v>37883</v>
+        <v>37878</v>
       </c>
       <c r="AB37">
-        <v>2396</v>
+        <v>2384</v>
       </c>
       <c r="AC37">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="AD37">
-        <v>2780</v>
+        <v>2801</v>
       </c>
       <c r="AE37">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="AF37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG37">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AH37" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI37" s="13">
-        <v>176535278400</v>
+        <v>188074471100</v>
       </c>
       <c r="AJ37" s="13">
-        <v>35165978400</v>
+        <v>46705171100</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
         <v>31</v>
@@ -4817,61 +4818,61 @@
         <v>32</v>
       </c>
       <c r="D38">
-        <v>124.87318254119739</v>
+        <v>129.28038824553849</v>
       </c>
       <c r="E38">
-        <v>40718</v>
+        <v>40743</v>
       </c>
       <c r="F38">
-        <v>3381</v>
+        <v>3419</v>
       </c>
       <c r="G38">
-        <v>128.6333333333333</v>
+        <v>128.6185185185185</v>
       </c>
       <c r="H38">
-        <v>11.707407407407411</v>
+        <v>11.829629629629631</v>
       </c>
       <c r="I38">
-        <v>11.707407407407411</v>
+        <v>11.829629629629631</v>
       </c>
       <c r="J38">
-        <v>10.31851851851852</v>
+        <v>10.28888888888889</v>
       </c>
       <c r="K38">
-        <v>0.79629629629629628</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="L38">
-        <v>0.79629629629629628</v>
+        <v>0.81851851851851853</v>
       </c>
       <c r="M38">
-        <v>0.12962962962962959</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="N38">
-        <v>1.8518518518518521E-2</v>
+        <v>1.4814814814814821E-2</v>
       </c>
       <c r="O38">
-        <v>0.14814814814814811</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="P38">
-        <v>128.30370370370369</v>
+        <v>128.0851851851852</v>
       </c>
       <c r="Q38" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="R38">
-        <v>37.037037037037038</v>
+        <v>35.185185185185183</v>
       </c>
       <c r="S38" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="T38">
-        <v>62.592592592592588</v>
+        <v>62.962962962962962</v>
       </c>
       <c r="U38" t="s">
-        <v>39</v>
-      </c>
-      <c r="V38" s="14">
-        <v>88.888888888888886</v>
+        <v>35</v>
+      </c>
+      <c r="V38" s="19">
+        <v>92.592592592592595</v>
       </c>
       <c r="W38" t="s">
         <v>40</v>
@@ -4880,40 +4881,40 @@
         <v>77.777777777777786</v>
       </c>
       <c r="Y38">
-        <v>34731</v>
+        <v>34727</v>
       </c>
       <c r="Z38">
-        <v>3161</v>
+        <v>3194</v>
       </c>
       <c r="AA38">
-        <v>37892</v>
+        <v>37921</v>
       </c>
       <c r="AB38">
-        <v>2411</v>
+        <v>2381</v>
       </c>
       <c r="AC38">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AD38">
-        <v>2786</v>
+        <v>2778</v>
       </c>
       <c r="AE38">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AF38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG38" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AH38" s="13">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AI38" s="13">
-        <v>176636862900</v>
+        <v>182762779900</v>
       </c>
       <c r="AJ38" s="13">
-        <v>35183862900</v>
+        <v>41393479900</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.35">
@@ -5028,7 +5029,7 @@
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
         <v>31</v>
@@ -5037,103 +5038,103 @@
         <v>32</v>
       </c>
       <c r="D40">
-        <v>124.11728883145069</v>
+        <v>124.87318254119739</v>
       </c>
       <c r="E40">
-        <v>40671</v>
+        <v>40718</v>
       </c>
       <c r="F40">
-        <v>3419</v>
+        <v>3381</v>
       </c>
       <c r="G40">
-        <v>128.31851851851849</v>
+        <v>128.6333333333333</v>
       </c>
       <c r="H40">
-        <v>11.84074074074074</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="I40">
-        <v>11.84074074074074</v>
+        <v>11.707407407407411</v>
       </c>
       <c r="J40">
-        <v>10.33333333333333</v>
+        <v>10.31851851851852</v>
       </c>
       <c r="K40">
-        <v>0.82222222222222219</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="L40">
-        <v>0.82222222222222219</v>
+        <v>0.79629629629629628</v>
       </c>
       <c r="M40">
-        <v>0.14074074074074069</v>
+        <v>0.12962962962962959</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O40">
-        <v>0.14074074074074069</v>
+        <v>0.14814814814814811</v>
       </c>
       <c r="P40">
-        <v>128.0851851851852</v>
+        <v>128.30370370370369</v>
       </c>
       <c r="Q40" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="R40">
-        <v>31.851851851851851</v>
+        <v>37.037037037037038</v>
       </c>
       <c r="S40" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="T40">
-        <v>65.555555555555557</v>
+        <v>62.592592592592588</v>
       </c>
       <c r="U40" t="s">
+        <v>39</v>
+      </c>
+      <c r="V40" s="16">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W40" t="s">
+        <v>40</v>
+      </c>
+      <c r="X40" s="16">
+        <v>77.777777777777786</v>
+      </c>
+      <c r="Y40">
+        <v>34731</v>
+      </c>
+      <c r="Z40">
+        <v>3161</v>
+      </c>
+      <c r="AA40">
+        <v>37892</v>
+      </c>
+      <c r="AB40">
+        <v>2411</v>
+      </c>
+      <c r="AC40">
+        <v>215</v>
+      </c>
+      <c r="AD40">
+        <v>2786</v>
+      </c>
+      <c r="AE40">
         <v>35</v>
       </c>
-      <c r="V40" s="24">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="W40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X40" s="24">
-        <v>92.592592592592595</v>
-      </c>
-      <c r="Y40">
-        <v>34646</v>
-      </c>
-      <c r="Z40">
-        <v>3197</v>
-      </c>
-      <c r="AA40">
-        <v>37843</v>
-      </c>
-      <c r="AB40">
-        <v>2416</v>
-      </c>
-      <c r="AC40">
-        <v>222</v>
-      </c>
-      <c r="AD40">
-        <v>2790</v>
-      </c>
-      <c r="AE40">
-        <v>38</v>
-      </c>
       <c r="AF40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG40">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AH40" s="13">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AI40" s="13">
-        <v>175463742400</v>
+        <v>176636862900</v>
       </c>
       <c r="AJ40" s="13">
-        <v>34094442400</v>
+        <v>35183862900</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.35">
@@ -5200,7 +5201,7 @@
       <c r="U41" t="s">
         <v>46</v>
       </c>
-      <c r="V41" s="23">
+      <c r="V41" s="18">
         <v>96.296296296296291</v>
       </c>
       <c r="W41" t="s">
@@ -5248,7 +5249,7 @@
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
         <v>31</v>
@@ -5257,103 +5258,103 @@
         <v>32</v>
       </c>
       <c r="D42">
-        <v>123.5907913528609</v>
+        <v>117.6183000128034</v>
       </c>
       <c r="E42">
-        <v>40670</v>
+        <v>40645</v>
       </c>
       <c r="F42">
-        <v>3413</v>
+        <v>3337</v>
       </c>
       <c r="G42">
-        <v>128.37407407407409</v>
+        <v>128.43333333333331</v>
       </c>
       <c r="H42">
-        <v>11.792592592592589</v>
+        <v>11.62592592592593</v>
       </c>
       <c r="I42">
-        <v>11.792592592592589</v>
+        <v>11.62592592592593</v>
       </c>
       <c r="J42">
-        <v>10.32592592592593</v>
+        <v>10.351851851851849</v>
       </c>
       <c r="K42">
-        <v>0.83703703703703702</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="L42">
-        <v>0.83703703703703702</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="M42">
         <v>0.12592592592592591</v>
       </c>
       <c r="N42">
-        <v>1.111111111111111E-2</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>0.13703703703703701</v>
+        <v>0.12592592592592591</v>
       </c>
       <c r="P42">
-        <v>128.10740740740741</v>
+        <v>128.38888888888891</v>
       </c>
       <c r="Q42" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="R42">
-        <v>33.703703703703702</v>
+        <v>37.037037037037038</v>
       </c>
       <c r="S42" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="T42">
-        <v>65.555555555555557</v>
+        <v>62.222222222222221</v>
       </c>
       <c r="U42" t="s">
-        <v>35</v>
-      </c>
-      <c r="V42" s="24">
-        <v>92.592592592592595</v>
+        <v>39</v>
+      </c>
+      <c r="V42" s="16">
+        <v>88.888888888888886</v>
       </c>
       <c r="W42" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="X42">
-        <v>70.370370370370367</v>
+        <v>77.777777777777786</v>
       </c>
       <c r="Y42">
-        <v>34661</v>
+        <v>34677</v>
       </c>
       <c r="Z42">
-        <v>3184</v>
+        <v>3139</v>
       </c>
       <c r="AA42">
-        <v>37845</v>
+        <v>37816</v>
       </c>
       <c r="AB42">
-        <v>2414</v>
+        <v>2461</v>
       </c>
       <c r="AC42">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="AD42">
-        <v>2788</v>
+        <v>2795</v>
       </c>
       <c r="AE42">
         <v>34</v>
       </c>
       <c r="AF42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AH42" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI42" s="13">
-        <v>174719436600</v>
+        <v>166276167400</v>
       </c>
       <c r="AJ42" s="13">
-        <v>33350136600</v>
+        <v>24906867400</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.35">
@@ -5468,7 +5469,7 @@
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -5477,108 +5478,108 @@
         <v>32</v>
       </c>
       <c r="D44">
-        <v>119.57909319774519</v>
+        <v>134.64788132925611</v>
       </c>
       <c r="E44">
-        <v>40686</v>
+        <v>40780</v>
       </c>
       <c r="F44">
-        <v>3412</v>
+        <v>3318</v>
       </c>
       <c r="G44">
-        <v>128.3666666666667</v>
+        <v>128.9851851851852</v>
       </c>
       <c r="H44">
-        <v>11.885185185185181</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="I44">
-        <v>11.885185185185181</v>
+        <v>11.52962962962963</v>
       </c>
       <c r="J44">
-        <v>10.3037037037037</v>
+        <v>10.32592592592593</v>
       </c>
       <c r="K44">
-        <v>0.73333333333333328</v>
+        <v>0.73703703703703705</v>
       </c>
       <c r="L44">
-        <v>0.73333333333333328</v>
+        <v>0.73703703703703705</v>
       </c>
       <c r="M44">
-        <v>0.1148148148148148</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="N44">
-        <v>1.8518518518518521E-2</v>
+        <v>2.222222222222222E-2</v>
       </c>
       <c r="O44">
-        <v>0.1333333333333333</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="P44">
-        <v>128.11111111111109</v>
+        <v>128.44444444444451</v>
       </c>
       <c r="Q44" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="R44">
-        <v>41.481481481481481</v>
+        <v>37.777777777777779</v>
       </c>
       <c r="S44" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="T44">
-        <v>58.148148148148152</v>
+        <v>60.370370370370367</v>
       </c>
       <c r="U44" t="s">
+        <v>35</v>
+      </c>
+      <c r="V44" s="19">
+        <v>92.592592592592595</v>
+      </c>
+      <c r="W44" t="s">
         <v>36</v>
       </c>
-      <c r="V44">
+      <c r="X44">
         <v>81.481481481481481</v>
       </c>
-      <c r="W44" t="s">
-        <v>62</v>
-      </c>
-      <c r="X44">
-        <v>66.666666666666657</v>
-      </c>
       <c r="Y44">
-        <v>34659</v>
+        <v>34826</v>
       </c>
       <c r="Z44">
-        <v>3209</v>
+        <v>3113</v>
       </c>
       <c r="AA44">
-        <v>37868</v>
+        <v>37939</v>
       </c>
       <c r="AB44">
-        <v>2440</v>
+        <v>2377</v>
       </c>
       <c r="AC44">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD44">
-        <v>2782</v>
+        <v>2788</v>
       </c>
       <c r="AE44">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="AF44">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="14">
-        <v>36</v>
+        <v>6</v>
+      </c>
+      <c r="AG44" s="17">
+        <v>53</v>
       </c>
       <c r="AH44" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI44" s="13">
-        <v>169048127000</v>
+        <v>190350767300</v>
       </c>
       <c r="AJ44" s="13">
-        <v>27678827000</v>
+        <v>48981467300</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
         <v>31</v>
@@ -5587,25 +5588,25 @@
         <v>32</v>
       </c>
       <c r="D45">
-        <v>117.6183000128034</v>
+        <v>119.57909319774519</v>
       </c>
       <c r="E45">
-        <v>40645</v>
+        <v>40686</v>
       </c>
       <c r="F45">
-        <v>3337</v>
+        <v>3412</v>
       </c>
       <c r="G45">
-        <v>128.43333333333331</v>
+        <v>128.3666666666667</v>
       </c>
       <c r="H45">
-        <v>11.62592592592593</v>
+        <v>11.885185185185181</v>
       </c>
       <c r="I45">
-        <v>11.62592592592593</v>
+        <v>11.885185185185181</v>
       </c>
       <c r="J45">
-        <v>10.351851851851849</v>
+        <v>10.3037037037037</v>
       </c>
       <c r="K45">
         <v>0.73333333333333328</v>
@@ -5614,76 +5615,76 @@
         <v>0.73333333333333328</v>
       </c>
       <c r="M45">
-        <v>0.12592592592592591</v>
+        <v>0.1148148148148148</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.8518518518518521E-2</v>
       </c>
       <c r="O45">
-        <v>0.12592592592592591</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="P45">
-        <v>128.38888888888891</v>
+        <v>128.11111111111109</v>
       </c>
       <c r="Q45" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="R45">
-        <v>37.037037037037038</v>
+        <v>41.481481481481481</v>
       </c>
       <c r="S45" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="T45">
-        <v>62.222222222222221</v>
+        <v>58.148148148148152</v>
       </c>
       <c r="U45" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="V45">
-        <v>88.888888888888886</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="W45" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="X45">
-        <v>77.777777777777786</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="Y45">
-        <v>34677</v>
+        <v>34659</v>
       </c>
       <c r="Z45">
-        <v>3139</v>
+        <v>3209</v>
       </c>
       <c r="AA45">
-        <v>37816</v>
+        <v>37868</v>
       </c>
       <c r="AB45">
-        <v>2461</v>
+        <v>2440</v>
       </c>
       <c r="AC45">
         <v>198</v>
       </c>
       <c r="AD45">
-        <v>2795</v>
+        <v>2782</v>
       </c>
       <c r="AE45">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG45">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH45" s="13">
         <v>141369300000</v>
       </c>
       <c r="AI45" s="13">
-        <v>166276167400</v>
+        <v>169048127000</v>
       </c>
       <c r="AJ45" s="13">
-        <v>24906867400</v>
+        <v>27678827000</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.35">
@@ -5729,7 +5730,7 @@
   </sheetData>
   <autoFilter ref="A2:AM2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AM53">
-      <sortCondition descending="1" ref="D2"/>
+      <sortCondition ref="R2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AC9526-6833-492E-92F1-EA73DC427143}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3F248C-8DA2-44CB-9CA7-57B9DCA268A6}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,85 +164,406 @@
     <t>270</t>
   </si>
   <si>
+    <t>83/270</t>
+  </si>
+  <si>
+    <t>178/270</t>
+  </si>
+  <si>
+    <t>74/270</t>
+  </si>
+  <si>
+    <t>58/270</t>
+  </si>
+  <si>
+    <t>27/27</t>
+  </si>
+  <si>
+    <t>25/27</t>
+  </si>
+  <si>
+    <t>141369300000</t>
+  </si>
+  <si>
+    <t>196260592100.0</t>
+  </si>
+  <si>
+    <t>85/270</t>
+  </si>
+  <si>
+    <t>67/270</t>
+  </si>
+  <si>
+    <t>22/27</t>
+  </si>
+  <si>
+    <t>193778261400.0</t>
+  </si>
+  <si>
+    <t>81/270</t>
+  </si>
+  <si>
+    <t>187/270</t>
+  </si>
+  <si>
+    <t>72/270</t>
+  </si>
+  <si>
+    <t>57/270</t>
+  </si>
+  <si>
+    <t>26/27</t>
+  </si>
+  <si>
+    <t>198718161100.0</t>
+  </si>
+  <si>
+    <t>84/270</t>
+  </si>
+  <si>
+    <t>180/270</t>
+  </si>
+  <si>
+    <t>195371846000.0</t>
+  </si>
+  <si>
+    <t>69/270</t>
+  </si>
+  <si>
+    <t>23/27</t>
+  </si>
+  <si>
+    <t>193611448000.0</t>
+  </si>
+  <si>
+    <t>91/270</t>
+  </si>
+  <si>
+    <t>177/270</t>
+  </si>
+  <si>
+    <t>195360679900.0</t>
+  </si>
+  <si>
+    <t>92/270</t>
+  </si>
+  <si>
+    <t>172/270</t>
+  </si>
+  <si>
+    <t>24/27</t>
+  </si>
+  <si>
+    <t>194272070000.0</t>
+  </si>
+  <si>
+    <t>102/270</t>
+  </si>
+  <si>
+    <t>163/270</t>
+  </si>
+  <si>
+    <t>65/270</t>
+  </si>
+  <si>
+    <t>56/270</t>
+  </si>
+  <si>
+    <t>190350767300.0</t>
+  </si>
+  <si>
+    <t>66/270</t>
+  </si>
+  <si>
+    <t>197/270</t>
+  </si>
+  <si>
+    <t>55/270</t>
+  </si>
+  <si>
+    <t>197870522800.0</t>
+  </si>
+  <si>
+    <t>70/270</t>
+  </si>
+  <si>
+    <t>196/270</t>
+  </si>
+  <si>
+    <t>195948118400.0</t>
+  </si>
+  <si>
+    <t>182/270</t>
+  </si>
+  <si>
+    <t>193622270800.0</t>
+  </si>
+  <si>
+    <t>193/270</t>
+  </si>
+  <si>
+    <t>194638545700.0</t>
+  </si>
+  <si>
+    <t>54/270</t>
+  </si>
+  <si>
+    <t>191817259500.0</t>
+  </si>
+  <si>
+    <t>90/270</t>
+  </si>
+  <si>
+    <t>63/270</t>
+  </si>
+  <si>
+    <t>191413982800.0</t>
+  </si>
+  <si>
+    <t>170/270</t>
+  </si>
+  <si>
+    <t>68/270</t>
+  </si>
+  <si>
+    <t>189631003300.0</t>
+  </si>
+  <si>
+    <t>100/270</t>
+  </si>
+  <si>
+    <t>62/270</t>
+  </si>
+  <si>
+    <t>53/270</t>
+  </si>
+  <si>
+    <t>188182914000.0</t>
+  </si>
+  <si>
+    <t>186/270</t>
+  </si>
+  <si>
+    <t>64/270</t>
+  </si>
+  <si>
+    <t>194250031500.0</t>
+  </si>
+  <si>
+    <t>176/270</t>
+  </si>
+  <si>
+    <t>191676711900.0</t>
+  </si>
+  <si>
+    <t>174/270</t>
+  </si>
+  <si>
+    <t>59/270</t>
+  </si>
+  <si>
+    <t>141453000000</t>
+  </si>
+  <si>
+    <t>188156825900.0</t>
+  </si>
+  <si>
+    <t>71/270</t>
+  </si>
+  <si>
+    <t>189980985100.0</t>
+  </si>
+  <si>
+    <t>95/270</t>
+  </si>
+  <si>
+    <t>166/270</t>
+  </si>
+  <si>
+    <t>188074471100.0</t>
+  </si>
+  <si>
+    <t>60/270</t>
+  </si>
+  <si>
+    <t>52/270</t>
+  </si>
+  <si>
+    <t>190870397300.0</t>
+  </si>
+  <si>
+    <t>87/270</t>
+  </si>
+  <si>
+    <t>186485876700.0</t>
+  </si>
+  <si>
+    <t>188192833700.0</t>
+  </si>
+  <si>
+    <t>97/270</t>
+  </si>
+  <si>
+    <t>165/270</t>
+  </si>
+  <si>
+    <t>189977084700.0</t>
+  </si>
+  <si>
+    <t>93/270</t>
+  </si>
+  <si>
+    <t>61/270</t>
+  </si>
+  <si>
+    <t>50/270</t>
+  </si>
+  <si>
+    <t>184395760900.0</t>
+  </si>
+  <si>
+    <t>21/27</t>
+  </si>
+  <si>
+    <t>182762779900.0</t>
+  </si>
+  <si>
+    <t>86/270</t>
+  </si>
+  <si>
+    <t>49/270</t>
+  </si>
+  <si>
+    <t>184913959200.0</t>
+  </si>
+  <si>
+    <t>168/270</t>
+  </si>
+  <si>
+    <t>182798024000.0</t>
+  </si>
+  <si>
+    <t>82/270</t>
+  </si>
+  <si>
+    <t>185/270</t>
+  </si>
+  <si>
+    <t>48/270</t>
+  </si>
+  <si>
+    <t>186624549600.0</t>
+  </si>
+  <si>
+    <t>183/270</t>
+  </si>
+  <si>
+    <t>20/27</t>
+  </si>
+  <si>
+    <t>185840291100.0</t>
+  </si>
+  <si>
+    <t>46/270</t>
+  </si>
+  <si>
+    <t>183457271100.0</t>
+  </si>
+  <si>
+    <t>94/270</t>
+  </si>
+  <si>
+    <t>179653519700.0</t>
+  </si>
+  <si>
+    <t>89/270</t>
+  </si>
+  <si>
+    <t>44/270</t>
+  </si>
+  <si>
+    <t>185127962700.0</t>
+  </si>
+  <si>
+    <t>88/270</t>
+  </si>
+  <si>
+    <t>175/270</t>
+  </si>
+  <si>
+    <t>179450118300.0</t>
+  </si>
+  <si>
+    <t>79/270</t>
+  </si>
+  <si>
+    <t>43/270</t>
+  </si>
+  <si>
+    <t>182573248100.0</t>
+  </si>
+  <si>
     <t>96/270</t>
   </si>
   <si>
     <t>171/270</t>
   </si>
   <si>
-    <t>61/270</t>
-  </si>
-  <si>
     <t>42/270</t>
   </si>
   <si>
-    <t>22/27</t>
-  </si>
-  <si>
     <t>19/27</t>
   </si>
   <si>
-    <t>141369300000</t>
-  </si>
-  <si>
     <t>175630764900.0</t>
   </si>
   <si>
-    <t>88/270</t>
-  </si>
-  <si>
-    <t>175/270</t>
-  </si>
-  <si>
-    <t>58/270</t>
-  </si>
-  <si>
-    <t>44/270</t>
-  </si>
-  <si>
-    <t>24/27</t>
-  </si>
-  <si>
-    <t>21/27</t>
-  </si>
-  <si>
-    <t>179450118300.0</t>
-  </si>
-  <si>
-    <t>87/270</t>
-  </si>
-  <si>
-    <t>176/270</t>
-  </si>
-  <si>
-    <t>66/270</t>
-  </si>
-  <si>
-    <t>52/270</t>
-  </si>
-  <si>
-    <t>186485876700.0</t>
-  </si>
-  <si>
-    <t>93/270</t>
-  </si>
-  <si>
-    <t>168/270</t>
-  </si>
-  <si>
-    <t>63/270</t>
-  </si>
-  <si>
-    <t>49/270</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>182798024000.0</t>
-  </si>
-  <si>
-    <t>100/270</t>
+    <t>169/270</t>
+  </si>
+  <si>
+    <t>176636862900.0</t>
+  </si>
+  <si>
+    <t>51/270</t>
+  </si>
+  <si>
+    <t>41/270</t>
+  </si>
+  <si>
+    <t>175463742400.0</t>
+  </si>
+  <si>
+    <t>101/270</t>
+  </si>
+  <si>
+    <t>164/270</t>
+  </si>
+  <si>
+    <t>173302642100.0</t>
+  </si>
+  <si>
+    <t>40/270</t>
+  </si>
+  <si>
+    <t>179006095700.0</t>
+  </si>
+  <si>
+    <t>38/270</t>
+  </si>
+  <si>
+    <t>174719436600.0</t>
+  </si>
+  <si>
+    <t>112/270</t>
+  </si>
+  <si>
+    <t>157/270</t>
+  </si>
+  <si>
+    <t>18/27</t>
+  </si>
+  <si>
+    <t>169048127000.0</t>
   </si>
   <si>
     <t>45/270</t>
@@ -252,327 +573,6 @@
   </si>
   <si>
     <t>166276167400.0</t>
-  </si>
-  <si>
-    <t>91/270</t>
-  </si>
-  <si>
-    <t>170/270</t>
-  </si>
-  <si>
-    <t>68/270</t>
-  </si>
-  <si>
-    <t>54/270</t>
-  </si>
-  <si>
-    <t>27/27</t>
-  </si>
-  <si>
-    <t>189631003300.0</t>
-  </si>
-  <si>
-    <t>86/270</t>
-  </si>
-  <si>
-    <t>177/270</t>
-  </si>
-  <si>
-    <t>51/270</t>
-  </si>
-  <si>
-    <t>41/270</t>
-  </si>
-  <si>
-    <t>25/27</t>
-  </si>
-  <si>
-    <t>175463742400.0</t>
-  </si>
-  <si>
-    <t>197/270</t>
-  </si>
-  <si>
-    <t>69/270</t>
-  </si>
-  <si>
-    <t>55/270</t>
-  </si>
-  <si>
-    <t>197870522800.0</t>
-  </si>
-  <si>
-    <t>79/270</t>
-  </si>
-  <si>
-    <t>187/270</t>
-  </si>
-  <si>
-    <t>53/270</t>
-  </si>
-  <si>
-    <t>43/270</t>
-  </si>
-  <si>
-    <t>182573248100.0</t>
-  </si>
-  <si>
-    <t>81/270</t>
-  </si>
-  <si>
-    <t>186/270</t>
-  </si>
-  <si>
-    <t>64/270</t>
-  </si>
-  <si>
-    <t>194250031500.0</t>
-  </si>
-  <si>
-    <t>84/270</t>
-  </si>
-  <si>
-    <t>182/270</t>
-  </si>
-  <si>
-    <t>65/270</t>
-  </si>
-  <si>
-    <t>193622270800.0</t>
-  </si>
-  <si>
-    <t>23/27</t>
-  </si>
-  <si>
-    <t>191817259500.0</t>
-  </si>
-  <si>
-    <t>60/270</t>
-  </si>
-  <si>
-    <t>190870397300.0</t>
-  </si>
-  <si>
-    <t>174/270</t>
-  </si>
-  <si>
-    <t>71/270</t>
-  </si>
-  <si>
-    <t>189980985100.0</t>
-  </si>
-  <si>
-    <t>89/270</t>
-  </si>
-  <si>
-    <t>40/270</t>
-  </si>
-  <si>
-    <t>20/27</t>
-  </si>
-  <si>
-    <t>141453000000</t>
-  </si>
-  <si>
-    <t>179006095700.0</t>
-  </si>
-  <si>
-    <t>38/270</t>
-  </si>
-  <si>
-    <t>174719436600.0</t>
-  </si>
-  <si>
-    <t>169/270</t>
-  </si>
-  <si>
-    <t>176636862900.0</t>
-  </si>
-  <si>
-    <t>95/270</t>
-  </si>
-  <si>
-    <t>166/270</t>
-  </si>
-  <si>
-    <t>188074471100.0</t>
-  </si>
-  <si>
-    <t>101/270</t>
-  </si>
-  <si>
-    <t>164/270</t>
-  </si>
-  <si>
-    <t>173302642100.0</t>
-  </si>
-  <si>
-    <t>178/270</t>
-  </si>
-  <si>
-    <t>185127962700.0</t>
-  </si>
-  <si>
-    <t>57/270</t>
-  </si>
-  <si>
-    <t>193611448000.0</t>
-  </si>
-  <si>
-    <t>184913959200.0</t>
-  </si>
-  <si>
-    <t>188192833700.0</t>
-  </si>
-  <si>
-    <t>83/270</t>
-  </si>
-  <si>
-    <t>74/270</t>
-  </si>
-  <si>
-    <t>196260592100.0</t>
-  </si>
-  <si>
-    <t>94/270</t>
-  </si>
-  <si>
-    <t>46/270</t>
-  </si>
-  <si>
-    <t>179653519700.0</t>
-  </si>
-  <si>
-    <t>92/270</t>
-  </si>
-  <si>
-    <t>172/270</t>
-  </si>
-  <si>
-    <t>67/270</t>
-  </si>
-  <si>
-    <t>194272070000.0</t>
-  </si>
-  <si>
-    <t>70/270</t>
-  </si>
-  <si>
-    <t>196/270</t>
-  </si>
-  <si>
-    <t>195948118400.0</t>
-  </si>
-  <si>
-    <t>85/270</t>
-  </si>
-  <si>
-    <t>193778261400.0</t>
-  </si>
-  <si>
-    <t>90/270</t>
-  </si>
-  <si>
-    <t>59/270</t>
-  </si>
-  <si>
-    <t>188156825900.0</t>
-  </si>
-  <si>
-    <t>102/270</t>
-  </si>
-  <si>
-    <t>163/270</t>
-  </si>
-  <si>
-    <t>56/270</t>
-  </si>
-  <si>
-    <t>190350767300.0</t>
-  </si>
-  <si>
-    <t>82/270</t>
-  </si>
-  <si>
-    <t>185/270</t>
-  </si>
-  <si>
-    <t>48/270</t>
-  </si>
-  <si>
-    <t>186624549600.0</t>
-  </si>
-  <si>
-    <t>62/270</t>
-  </si>
-  <si>
-    <t>191676711900.0</t>
-  </si>
-  <si>
-    <t>50/270</t>
-  </si>
-  <si>
-    <t>184395760900.0</t>
-  </si>
-  <si>
-    <t>112/270</t>
-  </si>
-  <si>
-    <t>157/270</t>
-  </si>
-  <si>
-    <t>18/27</t>
-  </si>
-  <si>
-    <t>169048127000.0</t>
-  </si>
-  <si>
-    <t>182762779900.0</t>
-  </si>
-  <si>
-    <t>183/270</t>
-  </si>
-  <si>
-    <t>185840291100.0</t>
-  </si>
-  <si>
-    <t>72/270</t>
-  </si>
-  <si>
-    <t>198718161100.0</t>
-  </si>
-  <si>
-    <t>180/270</t>
-  </si>
-  <si>
-    <t>195371846000.0</t>
-  </si>
-  <si>
-    <t>183457271100.0</t>
-  </si>
-  <si>
-    <t>195360679900.0</t>
-  </si>
-  <si>
-    <t>193/270</t>
-  </si>
-  <si>
-    <t>194638545700.0</t>
-  </si>
-  <si>
-    <t>191413982800.0</t>
-  </si>
-  <si>
-    <t>97/270</t>
-  </si>
-  <si>
-    <t>165/270</t>
-  </si>
-  <si>
-    <t>189977084700.0</t>
-  </si>
-  <si>
-    <t>188182914000.0</t>
   </si>
   <si>
     <t>100-350</t>
@@ -634,7 +634,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,6 +737,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -751,7 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -802,6 +814,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="43" fontId="2" fillId="17" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -816,21 +840,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="2" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="3" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="3" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1119,7 +1136,7 @@
     <col min="3" max="3" width="8.36328125" style="20" customWidth="1"/>
     <col min="4" max="4" width="16.453125" style="20" customWidth="1"/>
     <col min="5" max="6" width="18.7265625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" style="24" customWidth="1"/>
     <col min="8" max="8" width="11.6328125" style="20" customWidth="1"/>
     <col min="9" max="9" width="14.1796875" style="20" customWidth="1"/>
     <col min="10" max="10" width="9" style="20" customWidth="1"/>
@@ -1139,39 +1156,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="22" t="s">
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="24" t="s">
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="26" t="s">
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="27" t="s">
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="23"/>
-      <c r="AK1" s="23"/>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -1189,10 +1206,10 @@
       <c r="E2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="25" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -1207,10 +1224,10 @@
       <c r="K2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="23" t="s">
         <v>17</v>
       </c>
       <c r="N2" s="18" t="s">
@@ -1312,16 +1329,16 @@
         <v>39</v>
       </c>
       <c r="D3" s="13">
-        <v>138.82829730358711</v>
+        <v>138.83000000000001</v>
       </c>
       <c r="E3" s="16">
         <v>54891292100</v>
       </c>
       <c r="F3">
-        <v>62</v>
-      </c>
-      <c r="G3" s="29">
-        <v>23</v>
+        <v>81</v>
+      </c>
+      <c r="G3" s="34">
+        <v>30</v>
       </c>
       <c r="H3">
         <v>40801</v>
@@ -1330,40 +1347,40 @@
         <v>3423</v>
       </c>
       <c r="J3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K3" s="34">
-        <v>30.7</v>
+        <v>40</v>
+      </c>
+      <c r="K3" s="26">
+        <v>30.74</v>
       </c>
       <c r="L3" t="s">
-        <v>121</v>
-      </c>
-      <c r="M3" s="28">
-        <v>65.900000000000006</v>
+        <v>41</v>
+      </c>
+      <c r="M3" s="24">
+        <v>65.930000000000007</v>
       </c>
       <c r="N3" t="s">
-        <v>128</v>
-      </c>
-      <c r="O3" s="33">
-        <v>27.4</v>
+        <v>42</v>
+      </c>
+      <c r="O3" s="27">
+        <v>27.41</v>
       </c>
       <c r="P3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="33">
-        <v>21.5</v>
+        <v>43</v>
+      </c>
+      <c r="Q3" s="27">
+        <v>21.48</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="S3" s="13">
         <v>100</v>
       </c>
       <c r="T3" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="U3" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="V3">
         <v>34759</v>
@@ -1393,40 +1410,40 @@
         <v>55</v>
       </c>
       <c r="AE3">
-        <v>128.737037037037</v>
+        <v>128.74</v>
       </c>
       <c r="AF3">
-        <v>11.85555555555556</v>
+        <v>11.86</v>
       </c>
       <c r="AG3">
-        <v>11.85555555555556</v>
+        <v>11.86</v>
       </c>
       <c r="AH3">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI3">
-        <v>0.8037037037037037</v>
+        <v>0.8</v>
       </c>
       <c r="AJ3">
-        <v>0.8037037037037037</v>
+        <v>0.8</v>
       </c>
       <c r="AK3">
-        <v>0.1851851851851852</v>
+        <v>0.19</v>
       </c>
       <c r="AL3">
-        <v>1.8518518518518521E-2</v>
+        <v>0.02</v>
       </c>
       <c r="AM3" s="13">
-        <v>0.20370370370370369</v>
+        <v>0.2</v>
       </c>
       <c r="AN3">
-        <v>128.0740740740741</v>
+        <v>128.07</v>
       </c>
       <c r="AO3" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP3" s="12" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.35">
@@ -1440,16 +1457,16 @@
         <v>39</v>
       </c>
       <c r="D4" s="20">
-        <v>137.07237809057551</v>
-      </c>
-      <c r="E4" s="16">
+        <v>137.07</v>
+      </c>
+      <c r="E4" s="35">
         <v>52408961400</v>
       </c>
       <c r="F4">
-        <v>61</v>
-      </c>
-      <c r="G4" s="29">
-        <v>22.6</v>
+        <v>81</v>
+      </c>
+      <c r="G4" s="34">
+        <v>30</v>
       </c>
       <c r="H4">
         <v>40780</v>
@@ -1458,40 +1475,40 @@
         <v>3352</v>
       </c>
       <c r="J4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K4" s="28">
-        <v>31.5</v>
+        <v>48</v>
+      </c>
+      <c r="K4" s="24">
+        <v>31.48</v>
       </c>
       <c r="L4" t="s">
-        <v>121</v>
-      </c>
-      <c r="M4" s="28">
-        <v>65.900000000000006</v>
+        <v>41</v>
+      </c>
+      <c r="M4" s="24">
+        <v>65.930000000000007</v>
       </c>
       <c r="N4" t="s">
-        <v>135</v>
-      </c>
-      <c r="O4" s="34">
-        <v>24.8</v>
+        <v>49</v>
+      </c>
+      <c r="O4" s="26">
+        <v>24.81</v>
       </c>
       <c r="P4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="27">
+        <v>21.48</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="15">
+        <v>92.59</v>
+      </c>
+      <c r="T4" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="33">
-        <v>21.5</v>
-      </c>
-      <c r="R4" t="s">
-        <v>80</v>
-      </c>
-      <c r="S4" s="15">
-        <v>92.6</v>
-      </c>
-      <c r="T4" t="s">
-        <v>44</v>
-      </c>
       <c r="U4" s="20">
-        <v>81.5</v>
+        <v>81.48</v>
       </c>
       <c r="V4">
         <v>34813</v>
@@ -1514,52 +1531,52 @@
       <c r="AB4">
         <v>47</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="20">
         <v>6</v>
       </c>
       <c r="AD4" s="13">
         <v>53</v>
       </c>
       <c r="AE4">
-        <v>128.93703703703699</v>
+        <v>128.94</v>
       </c>
       <c r="AF4">
-        <v>11.577777777777779</v>
+        <v>11.58</v>
       </c>
       <c r="AG4">
-        <v>11.577777777777779</v>
+        <v>11.58</v>
       </c>
       <c r="AH4">
-        <v>10.32592592592593</v>
+        <v>10.33</v>
       </c>
       <c r="AI4">
-        <v>0.81481481481481477</v>
+        <v>0.81</v>
       </c>
       <c r="AJ4">
-        <v>0.81481481481481477</v>
+        <v>0.81</v>
       </c>
       <c r="AK4">
-        <v>0.1740740740740741</v>
+        <v>0.17</v>
       </c>
       <c r="AL4">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="AM4" s="20">
-        <v>0.1962962962962963</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM4" s="13">
+        <v>0.2</v>
       </c>
       <c r="AN4">
-        <v>128.33333333333329</v>
+        <v>128.33000000000001</v>
       </c>
       <c r="AO4" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP4" s="12" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
@@ -1568,126 +1585,126 @@
         <v>39</v>
       </c>
       <c r="D5" s="13">
-        <v>140.56670090323709</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="E5" s="16">
-        <v>57348861100</v>
+        <v>54002546000</v>
       </c>
       <c r="F5">
-        <v>54</v>
-      </c>
-      <c r="G5" s="29">
-        <v>20</v>
+        <v>82</v>
+      </c>
+      <c r="G5" s="24">
+        <v>30.37</v>
       </c>
       <c r="H5">
         <v>40771</v>
       </c>
       <c r="I5">
-        <v>3410</v>
+        <v>3393</v>
       </c>
       <c r="J5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K5" s="34">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="K5" s="24">
+        <v>31.11</v>
       </c>
       <c r="L5" t="s">
-        <v>87</v>
-      </c>
-      <c r="M5" s="28">
-        <v>69.3</v>
+        <v>59</v>
+      </c>
+      <c r="M5" s="24">
+        <v>66.67</v>
       </c>
       <c r="N5" t="s">
-        <v>164</v>
-      </c>
-      <c r="O5" s="33">
-        <v>26.7</v>
+        <v>49</v>
+      </c>
+      <c r="O5" s="26">
+        <v>24.81</v>
       </c>
       <c r="P5" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q5" s="33">
-        <v>21.1</v>
+        <v>55</v>
+      </c>
+      <c r="Q5" s="27">
+        <v>21.11</v>
       </c>
       <c r="R5" t="s">
-        <v>64</v>
-      </c>
-      <c r="S5" s="14">
-        <v>96.3</v>
+        <v>44</v>
+      </c>
+      <c r="S5" s="13">
+        <v>100</v>
       </c>
       <c r="T5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="U5" s="14">
         <v>96.3</v>
       </c>
       <c r="V5">
-        <v>34751</v>
+        <v>34749</v>
       </c>
       <c r="W5">
-        <v>3173</v>
+        <v>3175</v>
       </c>
       <c r="X5">
         <v>37924</v>
       </c>
       <c r="Y5">
-        <v>2339</v>
+        <v>2360</v>
       </c>
       <c r="Z5">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="AA5">
         <v>2792</v>
       </c>
       <c r="AB5">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AC5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="13">
         <v>55</v>
       </c>
       <c r="AE5">
-        <v>128.7074074074074</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="AF5">
-        <v>11.75185185185185</v>
+        <v>11.76</v>
       </c>
       <c r="AG5">
-        <v>11.75185185185185</v>
+        <v>11.76</v>
       </c>
       <c r="AH5">
-        <v>10.34074074074074</v>
+        <v>10.34</v>
       </c>
       <c r="AI5">
-        <v>0.86296296296296293</v>
+        <v>0.79</v>
       </c>
       <c r="AJ5">
-        <v>0.86296296296296293</v>
+        <v>0.79</v>
       </c>
       <c r="AK5">
-        <v>0.18888888888888891</v>
+        <v>0.18</v>
       </c>
       <c r="AL5">
-        <v>1.4814814814814821E-2</v>
+        <v>0.02</v>
       </c>
       <c r="AM5" s="13">
-        <v>0.20370370370370369</v>
+        <v>0.2</v>
       </c>
       <c r="AN5">
-        <v>128.10740740740741</v>
+        <v>128.16999999999999</v>
       </c>
       <c r="AO5" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP5" s="12" t="s">
-        <v>165</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -1696,126 +1713,126 @@
         <v>39</v>
       </c>
       <c r="D6" s="13">
-        <v>138.19962750045451</v>
+        <v>140.57</v>
       </c>
       <c r="E6" s="16">
-        <v>54002546000</v>
+        <v>57348861100</v>
       </c>
       <c r="F6">
-        <v>54</v>
-      </c>
-      <c r="G6" s="29">
-        <v>20</v>
+        <v>82</v>
+      </c>
+      <c r="G6" s="34">
+        <v>30.37</v>
       </c>
       <c r="H6">
         <v>40771</v>
       </c>
       <c r="I6">
-        <v>3393</v>
+        <v>3410</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6" s="28">
-        <v>31.1</v>
+        <v>52</v>
+      </c>
+      <c r="K6" s="26">
+        <v>30</v>
       </c>
       <c r="L6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M6" s="28">
-        <v>66.7</v>
+        <v>53</v>
+      </c>
+      <c r="M6" s="24">
+        <v>69.260000000000005</v>
       </c>
       <c r="N6" t="s">
-        <v>135</v>
-      </c>
-      <c r="O6" s="34">
-        <v>24.8</v>
+        <v>54</v>
+      </c>
+      <c r="O6" s="27">
+        <v>26.67</v>
       </c>
       <c r="P6" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q6" s="33">
-        <v>21.1</v>
+        <v>55</v>
+      </c>
+      <c r="Q6" s="27">
+        <v>21.11</v>
       </c>
       <c r="R6" t="s">
-        <v>74</v>
-      </c>
-      <c r="S6" s="13">
-        <v>100</v>
+        <v>56</v>
+      </c>
+      <c r="S6" s="14">
+        <v>96.3</v>
       </c>
       <c r="T6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="U6" s="14">
         <v>96.3</v>
       </c>
       <c r="V6">
-        <v>34749</v>
+        <v>34751</v>
       </c>
       <c r="W6">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="X6">
         <v>37924</v>
       </c>
       <c r="Y6">
-        <v>2360</v>
+        <v>2339</v>
       </c>
       <c r="Z6">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="AA6">
         <v>2792</v>
       </c>
       <c r="AB6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC6" s="20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD6" s="13">
         <v>55</v>
       </c>
       <c r="AE6">
-        <v>128.69999999999999</v>
+        <v>128.71</v>
       </c>
       <c r="AF6">
-        <v>11.75925925925926</v>
+        <v>11.75</v>
       </c>
       <c r="AG6">
-        <v>11.75925925925926</v>
+        <v>11.75</v>
       </c>
       <c r="AH6">
-        <v>10.34074074074074</v>
+        <v>10.34</v>
       </c>
       <c r="AI6">
-        <v>0.78518518518518521</v>
+        <v>0.86</v>
       </c>
       <c r="AJ6">
-        <v>0.78518518518518521</v>
+        <v>0.86</v>
       </c>
       <c r="AK6">
-        <v>0.18148148148148149</v>
+        <v>0.19</v>
       </c>
       <c r="AL6">
-        <v>2.222222222222222E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM6" s="13">
-        <v>0.20370370370370369</v>
+        <v>0.2</v>
       </c>
       <c r="AN6">
-        <v>128.17037037037039</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AO6" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP6" s="12" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
@@ -1824,126 +1841,126 @@
         <v>39</v>
       </c>
       <c r="D7" s="20">
-        <v>136.9543797698652</v>
-      </c>
-      <c r="E7" s="16">
-        <v>52242148000</v>
+        <v>137.41999999999999</v>
+      </c>
+      <c r="E7" s="35">
+        <v>52902770000</v>
       </c>
       <c r="F7">
-        <v>65</v>
-      </c>
-      <c r="G7" s="29">
-        <v>24.1</v>
+        <v>81</v>
+      </c>
+      <c r="G7" s="24">
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>40771</v>
+        <v>40801</v>
       </c>
       <c r="I7">
-        <v>3348</v>
+        <v>3370</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K7" s="28">
-        <v>31.1</v>
+        <v>67</v>
+      </c>
+      <c r="K7" s="24">
+        <v>34.07</v>
       </c>
       <c r="L7" t="s">
-        <v>121</v>
-      </c>
-      <c r="M7" s="28">
-        <v>65.900000000000006</v>
+        <v>68</v>
+      </c>
+      <c r="M7" s="24">
+        <v>63.7</v>
       </c>
       <c r="N7" t="s">
-        <v>83</v>
-      </c>
-      <c r="O7" s="33">
-        <v>25.6</v>
+        <v>49</v>
+      </c>
+      <c r="O7" s="26">
+        <v>24.81</v>
       </c>
       <c r="P7" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q7" s="33">
-        <v>21.1</v>
+        <v>55</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>21.11</v>
       </c>
       <c r="R7" t="s">
-        <v>80</v>
-      </c>
-      <c r="S7" s="15">
-        <v>92.6</v>
+        <v>69</v>
+      </c>
+      <c r="S7" s="20">
+        <v>88.89</v>
       </c>
       <c r="T7" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="U7" s="20">
-        <v>85.2</v>
+        <v>85.19</v>
       </c>
       <c r="V7">
-        <v>34780</v>
+        <v>34800</v>
       </c>
       <c r="W7">
-        <v>3144</v>
+        <v>3160</v>
       </c>
       <c r="X7">
-        <v>37924</v>
+        <v>37960</v>
       </c>
       <c r="Y7">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="Z7">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AA7">
-        <v>2792</v>
+        <v>2786</v>
       </c>
       <c r="AB7">
-        <v>53</v>
-      </c>
-      <c r="AC7">
-        <v>2</v>
+        <v>51</v>
+      </c>
+      <c r="AC7" s="20">
+        <v>4</v>
       </c>
       <c r="AD7" s="13">
         <v>55</v>
       </c>
       <c r="AE7">
-        <v>128.81481481481481</v>
+        <v>128.88999999999999</v>
       </c>
       <c r="AF7">
-        <v>11.64444444444444</v>
+        <v>11.7</v>
       </c>
       <c r="AG7">
-        <v>11.64444444444444</v>
+        <v>11.7</v>
       </c>
       <c r="AH7">
-        <v>10.34074074074074</v>
+        <v>10.32</v>
       </c>
       <c r="AI7">
-        <v>0.74814814814814812</v>
+        <v>0.76</v>
       </c>
       <c r="AJ7">
-        <v>0.74814814814814812</v>
+        <v>0.76</v>
       </c>
       <c r="AK7">
-        <v>0.1962962962962963</v>
+        <v>0.19</v>
       </c>
       <c r="AL7">
-        <v>7.4074074074074077E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AM7" s="13">
-        <v>0.20370370370370369</v>
+        <v>0.2</v>
       </c>
       <c r="AN7">
-        <v>128.34814814814811</v>
+        <v>128.28</v>
       </c>
       <c r="AO7" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP7" s="12" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -1951,74 +1968,74 @@
       <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="13">
-        <v>138.19172896802911</v>
-      </c>
-      <c r="E8" s="16">
-        <v>53991379900</v>
+      <c r="D8" s="20">
+        <v>136.94999999999999</v>
+      </c>
+      <c r="E8" s="35">
+        <v>52242148000</v>
       </c>
       <c r="F8">
-        <v>54</v>
-      </c>
-      <c r="G8" s="29">
-        <v>20</v>
+        <v>85</v>
+      </c>
+      <c r="G8" s="26">
+        <v>31.48</v>
       </c>
       <c r="H8">
         <v>40771</v>
       </c>
       <c r="I8">
-        <v>3411</v>
+        <v>3348</v>
       </c>
       <c r="J8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" s="28">
-        <v>33.700000000000003</v>
+        <v>58</v>
+      </c>
+      <c r="K8" s="24">
+        <v>31.11</v>
       </c>
       <c r="L8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8" s="28">
-        <v>65.599999999999994</v>
+        <v>41</v>
+      </c>
+      <c r="M8" s="24">
+        <v>65.930000000000007</v>
       </c>
       <c r="N8" t="s">
-        <v>83</v>
-      </c>
-      <c r="O8" s="33">
-        <v>25.6</v>
+        <v>61</v>
+      </c>
+      <c r="O8" s="27">
+        <v>25.56</v>
       </c>
       <c r="P8" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q8" s="33">
-        <v>21.1</v>
+        <v>55</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>21.11</v>
       </c>
       <c r="R8" t="s">
-        <v>74</v>
-      </c>
-      <c r="S8" s="13">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="S8" s="15">
+        <v>92.59</v>
       </c>
       <c r="T8" t="s">
-        <v>74</v>
-      </c>
-      <c r="U8" s="13">
-        <v>100</v>
+        <v>62</v>
+      </c>
+      <c r="U8" s="20">
+        <v>85.19</v>
       </c>
       <c r="V8">
-        <v>34726</v>
+        <v>34780</v>
       </c>
       <c r="W8">
-        <v>3198</v>
+        <v>3144</v>
       </c>
       <c r="X8">
         <v>37924</v>
       </c>
       <c r="Y8">
-        <v>2361</v>
+        <v>2370</v>
       </c>
       <c r="Z8">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="AA8">
         <v>2792</v>
@@ -2026,52 +2043,52 @@
       <c r="AB8">
         <v>53</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="20">
         <v>2</v>
       </c>
       <c r="AD8" s="13">
         <v>55</v>
       </c>
       <c r="AE8">
-        <v>128.61481481481479</v>
+        <v>128.81</v>
       </c>
       <c r="AF8">
-        <v>11.84444444444444</v>
+        <v>11.64</v>
       </c>
       <c r="AG8">
-        <v>11.84444444444444</v>
+        <v>11.64</v>
       </c>
       <c r="AH8">
-        <v>10.34074074074074</v>
+        <v>10.34</v>
       </c>
       <c r="AI8">
-        <v>0.78148148148148144</v>
+        <v>0.75</v>
       </c>
       <c r="AJ8">
-        <v>0.78148148148148144</v>
+        <v>0.75</v>
       </c>
       <c r="AK8">
-        <v>0.1962962962962963</v>
+        <v>0.2</v>
       </c>
       <c r="AL8">
-        <v>7.4074074074074077E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AM8" s="13">
-        <v>0.20370370370370369</v>
+        <v>0.2</v>
       </c>
       <c r="AN8">
-        <v>128.11481481481479</v>
+        <v>128.35</v>
       </c>
       <c r="AO8" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP8" s="12" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -2079,122 +2096,122 @@
       <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="20">
-        <v>137.4216820766602</v>
+      <c r="D9" s="13">
+        <v>138.19172896802911</v>
       </c>
       <c r="E9" s="16">
-        <v>52902770000</v>
+        <v>53991379900</v>
       </c>
       <c r="F9">
-        <v>62</v>
-      </c>
-      <c r="G9" s="29">
-        <v>23</v>
+        <v>54</v>
+      </c>
+      <c r="G9" s="24">
+        <v>20</v>
       </c>
       <c r="H9">
-        <v>40801</v>
+        <v>40771</v>
       </c>
       <c r="I9">
-        <v>3370</v>
+        <v>3411</v>
       </c>
       <c r="J9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K9" s="28">
-        <v>34.1</v>
+        <v>64</v>
+      </c>
+      <c r="K9" s="24">
+        <v>33.700000000000003</v>
       </c>
       <c r="L9" t="s">
-        <v>134</v>
-      </c>
-      <c r="M9" s="28">
-        <v>63.7</v>
+        <v>65</v>
+      </c>
+      <c r="M9" s="24">
+        <v>65.599999999999994</v>
       </c>
       <c r="N9" t="s">
-        <v>135</v>
-      </c>
-      <c r="O9" s="34">
-        <v>24.8</v>
+        <v>61</v>
+      </c>
+      <c r="O9" s="27">
+        <v>25.6</v>
       </c>
       <c r="P9" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q9" s="33">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="27">
         <v>21.1</v>
       </c>
       <c r="R9" t="s">
-        <v>52</v>
-      </c>
-      <c r="S9" s="20">
-        <v>88.9</v>
+        <v>44</v>
+      </c>
+      <c r="S9" s="13">
+        <v>100</v>
       </c>
       <c r="T9" t="s">
-        <v>99</v>
-      </c>
-      <c r="U9" s="20">
-        <v>85.2</v>
+        <v>44</v>
+      </c>
+      <c r="U9" s="13">
+        <v>100</v>
       </c>
       <c r="V9">
-        <v>34800</v>
+        <v>34726</v>
       </c>
       <c r="W9">
-        <v>3160</v>
+        <v>3198</v>
       </c>
       <c r="X9">
-        <v>37960</v>
+        <v>37924</v>
       </c>
       <c r="Y9">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="Z9">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AA9">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="AB9">
-        <v>51</v>
-      </c>
-      <c r="AC9" s="20">
-        <v>4</v>
+        <v>53</v>
+      </c>
+      <c r="AC9">
+        <v>2</v>
       </c>
       <c r="AD9" s="13">
         <v>55</v>
       </c>
       <c r="AE9">
-        <v>128.88888888888891</v>
+        <v>128.61481481481479</v>
       </c>
       <c r="AF9">
-        <v>11.703703703703701</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="AG9">
-        <v>11.703703703703701</v>
+        <v>11.84444444444444</v>
       </c>
       <c r="AH9">
-        <v>10.31851851851852</v>
+        <v>10.34074074074074</v>
       </c>
       <c r="AI9">
-        <v>0.76296296296296295</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="AJ9">
-        <v>0.76296296296296295</v>
+        <v>0.78148148148148144</v>
       </c>
       <c r="AK9">
-        <v>0.18888888888888891</v>
+        <v>0.1962962962962963</v>
       </c>
       <c r="AL9">
-        <v>1.4814814814814821E-2</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="AM9" s="13">
         <v>0.20370370370370369</v>
       </c>
       <c r="AN9">
-        <v>128.28148148148151</v>
+        <v>128.11481481481479</v>
       </c>
       <c r="AO9" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP9" s="12" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.35">
@@ -2208,16 +2225,16 @@
         <v>39</v>
       </c>
       <c r="D10" s="20">
-        <v>134.64788132925611</v>
+        <v>134.65</v>
       </c>
       <c r="E10" s="12">
         <v>48981467300</v>
       </c>
       <c r="F10">
-        <v>61</v>
-      </c>
-      <c r="G10" s="29">
-        <v>22.6</v>
+        <v>81</v>
+      </c>
+      <c r="G10" s="34">
+        <v>30</v>
       </c>
       <c r="H10">
         <v>40780</v>
@@ -2226,40 +2243,40 @@
         <v>3318</v>
       </c>
       <c r="J10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K10" s="28">
-        <v>37.799999999999997</v>
+        <v>71</v>
+      </c>
+      <c r="K10" s="24">
+        <v>37.78</v>
       </c>
       <c r="L10" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="28">
-        <v>60.4</v>
+        <v>72</v>
+      </c>
+      <c r="M10" s="24">
+        <v>60.37</v>
       </c>
       <c r="N10" t="s">
-        <v>97</v>
-      </c>
-      <c r="O10" s="34">
-        <v>24.1</v>
+        <v>73</v>
+      </c>
+      <c r="O10" s="26">
+        <v>24.07</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q10" s="34">
-        <v>20.7</v>
+        <v>74</v>
+      </c>
+      <c r="Q10" s="26">
+        <v>20.74</v>
       </c>
       <c r="R10" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="S10" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="U10" s="20">
-        <v>81.5</v>
+        <v>81.48</v>
       </c>
       <c r="V10">
         <v>34826</v>
@@ -2289,45 +2306,45 @@
         <v>53</v>
       </c>
       <c r="AE10">
-        <v>128.9851851851852</v>
+        <v>128.99</v>
       </c>
       <c r="AF10">
-        <v>11.52962962962963</v>
+        <v>11.53</v>
       </c>
       <c r="AG10">
-        <v>11.52962962962963</v>
+        <v>11.53</v>
       </c>
       <c r="AH10">
-        <v>10.32592592592593</v>
+        <v>10.33</v>
       </c>
       <c r="AI10">
-        <v>0.73703703703703705</v>
+        <v>0.74</v>
       </c>
       <c r="AJ10">
-        <v>0.73703703703703705</v>
+        <v>0.74</v>
       </c>
       <c r="AK10">
-        <v>0.1740740740740741</v>
+        <v>0.17</v>
       </c>
       <c r="AL10">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="AM10" s="20">
-        <v>0.1962962962962963</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM10" s="13">
+        <v>0.2</v>
       </c>
       <c r="AN10">
-        <v>128.44444444444451</v>
+        <v>128.44</v>
       </c>
       <c r="AO10" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP10" s="12" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2335,122 +2352,122 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="13">
-        <v>139.96710940777101</v>
-      </c>
-      <c r="E11" s="16">
-        <v>56501222800</v>
+      <c r="D11" s="20">
+        <v>136.96</v>
+      </c>
+      <c r="E11" s="35">
+        <v>52252970800</v>
       </c>
       <c r="F11">
-        <v>72</v>
-      </c>
-      <c r="G11" s="36">
-        <v>26.7</v>
+        <v>94</v>
+      </c>
+      <c r="G11" s="27">
+        <v>34.81</v>
       </c>
       <c r="H11">
         <v>40738</v>
       </c>
       <c r="I11">
-        <v>3404</v>
+        <v>3461</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="33">
-        <v>24.4</v>
+        <v>58</v>
+      </c>
+      <c r="K11" s="24">
+        <v>31.11</v>
       </c>
       <c r="L11" t="s">
-        <v>82</v>
-      </c>
-      <c r="M11" s="33">
+        <v>83</v>
+      </c>
+      <c r="M11" s="24">
+        <v>67.41</v>
+      </c>
+      <c r="N11" t="s">
         <v>73</v>
       </c>
-      <c r="N11" t="s">
-        <v>83</v>
-      </c>
-      <c r="O11" s="33">
-        <v>25.6</v>
+      <c r="O11" s="26">
+        <v>24.07</v>
       </c>
       <c r="P11" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q11" s="34">
-        <v>20.399999999999999</v>
+        <v>78</v>
+      </c>
+      <c r="Q11" s="26">
+        <v>20.37</v>
       </c>
       <c r="R11" t="s">
-        <v>80</v>
-      </c>
-      <c r="S11" s="15">
-        <v>92.6</v>
+        <v>44</v>
+      </c>
+      <c r="S11" s="13">
+        <v>100</v>
       </c>
       <c r="T11" t="s">
-        <v>80</v>
-      </c>
-      <c r="U11" s="15">
-        <v>92.6</v>
+        <v>69</v>
+      </c>
+      <c r="U11" s="20">
+        <v>88.89</v>
       </c>
       <c r="V11">
-        <v>34741</v>
+        <v>34650</v>
       </c>
       <c r="W11">
-        <v>3143</v>
+        <v>3234</v>
       </c>
       <c r="X11">
         <v>37884</v>
       </c>
       <c r="Y11">
-        <v>2342</v>
+        <v>2372</v>
       </c>
       <c r="Z11">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="AA11">
         <v>2802</v>
       </c>
       <c r="AB11">
-        <v>43</v>
-      </c>
-      <c r="AC11" s="13">
-        <v>9</v>
+        <v>47</v>
+      </c>
+      <c r="AC11" s="20">
+        <v>5</v>
       </c>
       <c r="AD11" s="13">
         <v>52</v>
       </c>
       <c r="AE11">
-        <v>128.67037037037039</v>
+        <v>128.33000000000001</v>
       </c>
       <c r="AF11">
-        <v>11.640740740740741</v>
+        <v>11.98</v>
       </c>
       <c r="AG11">
-        <v>11.640740740740741</v>
+        <v>11.98</v>
       </c>
       <c r="AH11">
-        <v>10.37777777777778</v>
+        <v>10.38</v>
       </c>
       <c r="AI11">
-        <v>0.93333333333333335</v>
+        <v>0.82</v>
       </c>
       <c r="AJ11">
-        <v>0.93333333333333335</v>
+        <v>0.82</v>
       </c>
       <c r="AK11">
-        <v>0.15925925925925929</v>
+        <v>0.17</v>
       </c>
       <c r="AL11">
-        <v>3.3333333333333333E-2</v>
+        <v>0.02</v>
       </c>
       <c r="AM11" s="20">
-        <v>0.19259259259259259</v>
+        <v>0.19</v>
       </c>
       <c r="AN11">
-        <v>128.14074074074071</v>
+        <v>127.89</v>
       </c>
       <c r="AO11" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP11" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.35">
@@ -2464,16 +2481,16 @@
         <v>39</v>
       </c>
       <c r="D12" s="13">
-        <v>138.6072636704009</v>
+        <v>138.61000000000001</v>
       </c>
       <c r="E12" s="16">
         <v>54578818400</v>
       </c>
       <c r="F12">
-        <v>61</v>
-      </c>
-      <c r="G12" s="29">
-        <v>22.6</v>
+        <v>81</v>
+      </c>
+      <c r="G12" s="34">
+        <v>30</v>
       </c>
       <c r="H12">
         <v>40780</v>
@@ -2482,40 +2499,40 @@
         <v>3454</v>
       </c>
       <c r="J12" t="s">
-        <v>137</v>
-      </c>
-      <c r="K12" s="33">
-        <v>25.9</v>
+        <v>80</v>
+      </c>
+      <c r="K12" s="27">
+        <v>25.93</v>
       </c>
       <c r="L12" t="s">
-        <v>138</v>
-      </c>
-      <c r="M12" s="33">
-        <v>72.599999999999994</v>
+        <v>81</v>
+      </c>
+      <c r="M12" s="27">
+        <v>72.59</v>
       </c>
       <c r="N12" t="s">
-        <v>57</v>
-      </c>
-      <c r="O12" s="34">
-        <v>24.4</v>
+        <v>76</v>
+      </c>
+      <c r="O12" s="26">
+        <v>24.44</v>
       </c>
       <c r="P12" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q12" s="34">
-        <v>20.399999999999999</v>
+        <v>78</v>
+      </c>
+      <c r="Q12" s="26">
+        <v>20.37</v>
       </c>
       <c r="R12" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S12" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T12" t="s">
-        <v>44</v>
-      </c>
-      <c r="U12">
-        <v>81.5</v>
+        <v>50</v>
+      </c>
+      <c r="U12" s="20">
+        <v>81.48</v>
       </c>
       <c r="V12">
         <v>34717</v>
@@ -2545,45 +2562,45 @@
         <v>53</v>
       </c>
       <c r="AE12">
-        <v>128.58148148148149</v>
+        <v>128.58000000000001</v>
       </c>
       <c r="AF12">
-        <v>11.93333333333333</v>
+        <v>11.93</v>
       </c>
       <c r="AG12">
-        <v>11.93333333333333</v>
+        <v>11.93</v>
       </c>
       <c r="AH12">
-        <v>10.32592592592593</v>
+        <v>10.33</v>
       </c>
       <c r="AI12">
-        <v>0.85185185185185186</v>
+        <v>0.85</v>
       </c>
       <c r="AJ12">
-        <v>0.85185185185185186</v>
+        <v>0.85</v>
       </c>
       <c r="AK12">
-        <v>0.18888888888888891</v>
+        <v>0.19</v>
       </c>
       <c r="AL12">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="AM12" s="20">
-        <v>0.1962962962962963</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM12" s="13">
+        <v>0.2</v>
       </c>
       <c r="AN12">
-        <v>127.99629629629629</v>
+        <v>128</v>
       </c>
       <c r="AO12" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP12" s="12" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -2592,126 +2609,126 @@
         <v>39</v>
       </c>
       <c r="D13" s="20">
-        <v>136.9620354631451</v>
+        <v>137.68</v>
       </c>
       <c r="E13" s="16">
-        <v>52252970800</v>
+        <v>53269245700</v>
       </c>
       <c r="F13">
-        <v>72</v>
-      </c>
-      <c r="G13" s="36">
-        <v>26.7</v>
+        <v>94</v>
+      </c>
+      <c r="G13" s="27">
+        <v>34.81</v>
       </c>
       <c r="H13">
         <v>40738</v>
       </c>
       <c r="I13">
-        <v>3461</v>
+        <v>3399</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" s="28">
-        <v>31.1</v>
+        <v>54</v>
+      </c>
+      <c r="K13" s="27">
+        <v>26.67</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13" s="28">
-        <v>67.400000000000006</v>
+        <v>85</v>
+      </c>
+      <c r="M13" s="27">
+        <v>71.48</v>
       </c>
       <c r="N13" t="s">
-        <v>97</v>
-      </c>
-      <c r="O13" s="34">
-        <v>24.1</v>
+        <v>76</v>
+      </c>
+      <c r="O13" s="26">
+        <v>24.44</v>
       </c>
       <c r="P13" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q13" s="34">
-        <v>20.399999999999999</v>
+        <v>78</v>
+      </c>
+      <c r="Q13" s="26">
+        <v>20.37</v>
       </c>
       <c r="R13" t="s">
-        <v>74</v>
-      </c>
-      <c r="S13" s="13">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="S13" s="14">
+        <v>92.59</v>
       </c>
       <c r="T13" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U13" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="V13">
-        <v>34650</v>
+        <v>34722</v>
       </c>
       <c r="W13">
-        <v>3234</v>
+        <v>3162</v>
       </c>
       <c r="X13">
         <v>37884</v>
       </c>
       <c r="Y13">
-        <v>2372</v>
+        <v>2363</v>
       </c>
       <c r="Z13">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AA13">
         <v>2802</v>
       </c>
       <c r="AB13">
-        <v>47</v>
-      </c>
-      <c r="AC13">
-        <v>5</v>
+        <v>46</v>
+      </c>
+      <c r="AC13" s="20">
+        <v>6</v>
       </c>
       <c r="AD13" s="13">
         <v>52</v>
       </c>
       <c r="AE13">
-        <v>128.33333333333329</v>
+        <v>128.6</v>
       </c>
       <c r="AF13">
-        <v>11.97777777777778</v>
+        <v>11.71</v>
       </c>
       <c r="AG13">
-        <v>11.97777777777778</v>
+        <v>11.71</v>
       </c>
       <c r="AH13">
-        <v>10.37777777777778</v>
+        <v>10.38</v>
       </c>
       <c r="AI13">
-        <v>0.82222222222222219</v>
+        <v>0.86</v>
       </c>
       <c r="AJ13">
-        <v>0.82222222222222219</v>
+        <v>0.86</v>
       </c>
       <c r="AK13">
-        <v>0.1740740740740741</v>
+        <v>0.17</v>
       </c>
       <c r="AL13">
-        <v>1.8518518518518521E-2</v>
+        <v>0.02</v>
       </c>
       <c r="AM13" s="20">
-        <v>0.19259259259259259</v>
+        <v>0.19</v>
       </c>
       <c r="AN13">
-        <v>127.89259259259261</v>
+        <v>128.13999999999999</v>
       </c>
       <c r="AO13" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP13" s="12" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -2719,127 +2736,127 @@
       <c r="C14" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="20">
-        <v>137.68091495112449</v>
-      </c>
-      <c r="E14" s="12">
-        <v>53269245700</v>
+      <c r="D14" s="13">
+        <v>139.97</v>
+      </c>
+      <c r="E14" s="16">
+        <v>56501222800</v>
       </c>
       <c r="F14">
-        <v>72</v>
-      </c>
-      <c r="G14" s="36">
-        <v>26.67</v>
+        <v>94</v>
+      </c>
+      <c r="G14" s="27">
+        <v>34.81</v>
       </c>
       <c r="H14">
         <v>40738</v>
       </c>
       <c r="I14">
-        <v>3399</v>
+        <v>3404</v>
       </c>
       <c r="J14" t="s">
-        <v>164</v>
-      </c>
-      <c r="K14" s="33">
-        <v>26.67</v>
+        <v>76</v>
+      </c>
+      <c r="K14" s="27">
+        <v>24.44</v>
       </c>
       <c r="L14" t="s">
-        <v>170</v>
-      </c>
-      <c r="M14" s="33">
-        <v>71.48</v>
+        <v>77</v>
+      </c>
+      <c r="M14" s="27">
+        <v>72.959999999999994</v>
       </c>
       <c r="N14" t="s">
-        <v>57</v>
-      </c>
-      <c r="O14" s="34">
-        <v>24.44</v>
+        <v>61</v>
+      </c>
+      <c r="O14" s="27">
+        <v>25.56</v>
       </c>
       <c r="P14" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q14" s="34">
+        <v>78</v>
+      </c>
+      <c r="Q14" s="26">
         <v>20.37</v>
       </c>
       <c r="R14" t="s">
-        <v>80</v>
-      </c>
-      <c r="S14" s="14">
+        <v>45</v>
+      </c>
+      <c r="S14" s="15">
         <v>92.59</v>
       </c>
       <c r="T14" t="s">
-        <v>52</v>
-      </c>
-      <c r="U14" s="20">
-        <v>88.89</v>
+        <v>45</v>
+      </c>
+      <c r="U14" s="15">
+        <v>92.59</v>
       </c>
       <c r="V14">
-        <v>34722</v>
+        <v>34741</v>
       </c>
       <c r="W14">
-        <v>3162</v>
+        <v>3143</v>
       </c>
       <c r="X14">
         <v>37884</v>
       </c>
       <c r="Y14">
-        <v>2363</v>
+        <v>2342</v>
       </c>
       <c r="Z14">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="AA14">
         <v>2802</v>
       </c>
       <c r="AB14">
-        <v>46</v>
-      </c>
-      <c r="AC14">
-        <v>6</v>
-      </c>
-      <c r="AD14" s="20">
+        <v>43</v>
+      </c>
+      <c r="AC14" s="13">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="13">
         <v>52</v>
       </c>
       <c r="AE14">
-        <v>128.6</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="AF14">
-        <v>11.71111111111111</v>
+        <v>11.64</v>
       </c>
       <c r="AG14">
-        <v>11.71111111111111</v>
+        <v>11.64</v>
       </c>
       <c r="AH14">
-        <v>10.37777777777778</v>
+        <v>10.38</v>
       </c>
       <c r="AI14">
-        <v>0.85555555555555551</v>
+        <v>0.93</v>
       </c>
       <c r="AJ14">
-        <v>0.85555555555555551</v>
+        <v>0.93</v>
       </c>
       <c r="AK14">
-        <v>0.17037037037037039</v>
+        <v>0.16</v>
       </c>
       <c r="AL14">
-        <v>2.222222222222222E-2</v>
+        <v>0.03</v>
       </c>
       <c r="AM14" s="20">
-        <v>0.19259259259259259</v>
+        <v>0.19</v>
       </c>
       <c r="AN14">
-        <v>128.137037037037</v>
+        <v>128.13999999999999</v>
       </c>
       <c r="AO14" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP14" s="12" t="s">
-        <v>171</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
@@ -2848,126 +2865,126 @@
         <v>39</v>
       </c>
       <c r="D15">
-        <v>135.68522974931619</v>
-      </c>
-      <c r="E15" s="16">
-        <v>50447959500</v>
+        <v>135.4</v>
+      </c>
+      <c r="E15" s="35">
+        <v>50044682800</v>
       </c>
       <c r="F15">
-        <v>72</v>
-      </c>
-      <c r="G15" s="36">
-        <v>26.7</v>
+        <v>94</v>
+      </c>
+      <c r="G15" s="27">
+        <v>34.81</v>
       </c>
       <c r="H15">
         <v>40738</v>
       </c>
       <c r="I15">
-        <v>3222</v>
+        <v>3346</v>
       </c>
       <c r="J15" t="s">
-        <v>91</v>
-      </c>
-      <c r="K15" s="34">
-        <v>30</v>
+        <v>89</v>
+      </c>
+      <c r="K15" s="24">
+        <v>33.33</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
-      </c>
-      <c r="M15" s="28">
-        <v>67.400000000000006</v>
+        <v>65</v>
+      </c>
+      <c r="M15" s="24">
+        <v>65.56</v>
       </c>
       <c r="N15" t="s">
-        <v>57</v>
-      </c>
-      <c r="O15" s="34">
-        <v>24.4</v>
+        <v>90</v>
+      </c>
+      <c r="O15" s="24">
+        <v>23.33</v>
       </c>
       <c r="P15" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="34">
+        <v>87</v>
+      </c>
+      <c r="Q15" s="26">
         <v>20</v>
       </c>
       <c r="R15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="S15" s="20">
-        <v>88.9</v>
+        <v>96.3</v>
       </c>
       <c r="T15" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="U15" s="20">
-        <v>85.2</v>
+        <v>88.89</v>
       </c>
       <c r="V15">
-        <v>34882</v>
+        <v>34756</v>
       </c>
       <c r="W15">
-        <v>3002</v>
+        <v>3128</v>
       </c>
       <c r="X15">
         <v>37884</v>
       </c>
       <c r="Y15">
-        <v>2375</v>
+        <v>2382</v>
       </c>
       <c r="Z15">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AA15">
         <v>2802</v>
       </c>
       <c r="AB15">
-        <v>51</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="AC15" s="20">
+        <v>6</v>
       </c>
       <c r="AD15" s="13">
         <v>52</v>
       </c>
       <c r="AE15">
-        <v>129.1925925925926</v>
+        <v>128.72999999999999</v>
       </c>
       <c r="AF15">
-        <v>11.11851851851852</v>
+        <v>11.59</v>
       </c>
       <c r="AG15">
-        <v>11.11851851851852</v>
+        <v>11.59</v>
       </c>
       <c r="AH15">
-        <v>10.37777777777778</v>
+        <v>10.38</v>
       </c>
       <c r="AI15">
-        <v>0.81111111111111112</v>
+        <v>0.79</v>
       </c>
       <c r="AJ15">
-        <v>0.81111111111111112</v>
+        <v>0.79</v>
       </c>
       <c r="AK15">
-        <v>0.18888888888888891</v>
+        <v>0.17</v>
       </c>
       <c r="AL15">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="AM15" s="20">
-        <v>0.19259259259259259</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM15">
+        <v>0.19</v>
       </c>
       <c r="AN15">
-        <v>128.83703703703699</v>
-      </c>
-      <c r="AO15" s="12" t="s">
+        <v>128.38999999999999</v>
+      </c>
+      <c r="AO15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="AP15" s="12" t="s">
-        <v>100</v>
+      <c r="AP15" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
@@ -2975,127 +2992,127 @@
       <c r="C16" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="20">
-        <v>135.3999650560624</v>
+      <c r="D16">
+        <v>134.13999999999999</v>
       </c>
       <c r="E16" s="12">
-        <v>50044682800</v>
+        <v>48261703300</v>
       </c>
       <c r="F16">
-        <v>72</v>
-      </c>
-      <c r="G16" s="36">
-        <v>26.67</v>
+        <v>95</v>
+      </c>
+      <c r="G16" s="27">
+        <v>35.19</v>
       </c>
       <c r="H16">
-        <v>40738</v>
+        <v>40740</v>
       </c>
       <c r="I16">
-        <v>3346</v>
+        <v>3322</v>
       </c>
       <c r="J16" t="s">
-        <v>142</v>
-      </c>
-      <c r="K16" s="28">
-        <v>33.33</v>
+        <v>64</v>
+      </c>
+      <c r="K16" s="24">
+        <v>33.700000000000003</v>
       </c>
       <c r="L16" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" s="28">
-        <v>65.56</v>
+        <v>92</v>
+      </c>
+      <c r="M16" s="24">
+        <v>62.96</v>
       </c>
       <c r="N16" t="s">
-        <v>62</v>
-      </c>
-      <c r="O16" s="28">
-        <v>23.33</v>
+        <v>93</v>
+      </c>
+      <c r="O16" s="27">
+        <v>25.19</v>
       </c>
       <c r="P16" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="34">
+        <v>87</v>
+      </c>
+      <c r="Q16" s="26">
         <v>20</v>
       </c>
       <c r="R16" t="s">
-        <v>64</v>
-      </c>
-      <c r="S16" s="20">
-        <v>96.3</v>
+        <v>44</v>
+      </c>
+      <c r="S16" s="13">
+        <v>100</v>
       </c>
       <c r="T16" t="s">
-        <v>52</v>
-      </c>
-      <c r="U16" s="20">
-        <v>88.89</v>
+        <v>44</v>
+      </c>
+      <c r="U16" s="13">
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>34756</v>
+        <v>34772</v>
       </c>
       <c r="W16">
-        <v>3128</v>
+        <v>3112</v>
       </c>
       <c r="X16">
         <v>37884</v>
       </c>
       <c r="Y16">
-        <v>2382</v>
+        <v>2392</v>
       </c>
       <c r="Z16">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AA16">
-        <v>2802</v>
+        <v>2805</v>
       </c>
       <c r="AB16">
+        <v>50</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="13">
+        <v>51</v>
+      </c>
+      <c r="AE16">
+        <v>128.79</v>
+      </c>
+      <c r="AF16">
+        <v>11.53</v>
+      </c>
+      <c r="AG16">
+        <v>11.53</v>
+      </c>
+      <c r="AH16">
+        <v>10.39</v>
+      </c>
+      <c r="AI16">
+        <v>0.77</v>
+      </c>
+      <c r="AJ16">
+        <v>0.77</v>
+      </c>
+      <c r="AK16">
+        <v>0.19</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0.19</v>
+      </c>
+      <c r="AN16">
+        <v>128.44</v>
+      </c>
+      <c r="AO16" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AC16">
-        <v>6</v>
-      </c>
-      <c r="AD16" s="20">
-        <v>52</v>
-      </c>
-      <c r="AE16">
-        <v>128.72592592592591</v>
-      </c>
-      <c r="AF16">
-        <v>11.585185185185191</v>
-      </c>
-      <c r="AG16">
-        <v>11.585185185185191</v>
-      </c>
-      <c r="AH16">
-        <v>10.37777777777778</v>
-      </c>
-      <c r="AI16">
-        <v>0.78518518518518521</v>
-      </c>
-      <c r="AJ16">
-        <v>0.78518518518518521</v>
-      </c>
-      <c r="AK16">
-        <v>0.17037037037037039</v>
-      </c>
-      <c r="AL16">
-        <v>2.222222222222222E-2</v>
-      </c>
-      <c r="AM16" s="20">
-        <v>0.19259259259259259</v>
-      </c>
-      <c r="AN16">
-        <v>128.38518518518521</v>
-      </c>
-      <c r="AO16" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="AP16" s="20" t="s">
-        <v>172</v>
+      <c r="AP16" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
@@ -3104,126 +3121,126 @@
         <v>39</v>
       </c>
       <c r="D17">
-        <v>134.1387439139898</v>
-      </c>
-      <c r="E17" s="12">
-        <v>48261703300</v>
+        <v>135.69</v>
+      </c>
+      <c r="E17" s="35">
+        <v>50447959500</v>
       </c>
       <c r="F17">
-        <v>74</v>
-      </c>
-      <c r="G17" s="35">
-        <v>27.4</v>
+        <v>94</v>
+      </c>
+      <c r="G17" s="27">
+        <v>34.81</v>
       </c>
       <c r="H17">
-        <v>40740</v>
+        <v>40738</v>
       </c>
       <c r="I17">
-        <v>3322</v>
+        <v>3222</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="28">
-        <v>33.700000000000003</v>
+        <v>52</v>
+      </c>
+      <c r="K17" s="26">
+        <v>30</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
-      </c>
-      <c r="M17" s="28">
-        <v>63</v>
+        <v>83</v>
+      </c>
+      <c r="M17" s="24">
+        <v>67.41</v>
       </c>
       <c r="N17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O17" s="33">
-        <v>25.2</v>
+        <v>76</v>
+      </c>
+      <c r="O17" s="26">
+        <v>24.44</v>
       </c>
       <c r="P17" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="34">
+        <v>87</v>
+      </c>
+      <c r="Q17" s="26">
         <v>20</v>
       </c>
       <c r="R17" t="s">
-        <v>74</v>
-      </c>
-      <c r="S17" s="13">
-        <v>100</v>
+        <v>69</v>
+      </c>
+      <c r="S17" s="20">
+        <v>88.89</v>
       </c>
       <c r="T17" t="s">
-        <v>74</v>
-      </c>
-      <c r="U17" s="13">
-        <v>100</v>
+        <v>62</v>
+      </c>
+      <c r="U17" s="20">
+        <v>85.19</v>
       </c>
       <c r="V17">
-        <v>34772</v>
+        <v>34882</v>
       </c>
       <c r="W17">
-        <v>3112</v>
+        <v>3002</v>
       </c>
       <c r="X17">
         <v>37884</v>
       </c>
       <c r="Y17">
-        <v>2392</v>
+        <v>2375</v>
       </c>
       <c r="Z17">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="AA17">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="AB17">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC17">
         <v>1</v>
       </c>
       <c r="AD17" s="13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AE17">
-        <v>128.78518518518521</v>
+        <v>129.19</v>
       </c>
       <c r="AF17">
-        <v>11.525925925925931</v>
+        <v>11.12</v>
       </c>
       <c r="AG17">
-        <v>11.525925925925931</v>
+        <v>11.12</v>
       </c>
       <c r="AH17">
-        <v>10.388888888888889</v>
+        <v>10.38</v>
       </c>
       <c r="AI17">
-        <v>0.77407407407407403</v>
+        <v>0.81</v>
       </c>
       <c r="AJ17">
-        <v>0.77407407407407403</v>
+        <v>0.81</v>
       </c>
       <c r="AK17">
-        <v>0.1851851851851852</v>
+        <v>0.19</v>
       </c>
       <c r="AL17">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="AM17" s="20">
-        <v>0.18888888888888891</v>
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0.19</v>
       </c>
       <c r="AN17">
-        <v>128.44444444444451</v>
+        <v>128.84</v>
       </c>
       <c r="AO17" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP17" s="12" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -3232,121 +3249,121 @@
         <v>39</v>
       </c>
       <c r="D18">
-        <v>133.11441310100571</v>
-      </c>
-      <c r="E18" s="12">
-        <v>46813614000</v>
+        <v>135.59</v>
+      </c>
+      <c r="E18" s="35">
+        <v>50307411900</v>
       </c>
       <c r="F18">
-        <v>72</v>
-      </c>
-      <c r="G18" s="36">
-        <v>26.67</v>
+        <v>77</v>
+      </c>
+      <c r="G18" s="24">
+        <v>28.52</v>
       </c>
       <c r="H18">
-        <v>40738</v>
+        <v>40777</v>
       </c>
       <c r="I18">
-        <v>3257</v>
+        <v>3411</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" s="28">
-        <v>37.04</v>
+        <v>89</v>
+      </c>
+      <c r="K18" s="24">
+        <v>33.33</v>
       </c>
       <c r="L18" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="28">
-        <v>60.37</v>
+        <v>102</v>
+      </c>
+      <c r="M18" s="24">
+        <v>65.19</v>
       </c>
       <c r="N18" t="s">
-        <v>153</v>
-      </c>
-      <c r="O18" s="28">
+        <v>96</v>
+      </c>
+      <c r="O18" s="24">
         <v>22.96</v>
       </c>
       <c r="P18" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" s="28">
+        <v>97</v>
+      </c>
+      <c r="Q18" s="24">
         <v>19.63</v>
       </c>
       <c r="R18" t="s">
-        <v>80</v>
-      </c>
-      <c r="S18" s="20">
+        <v>45</v>
+      </c>
+      <c r="S18" s="15">
         <v>92.59</v>
       </c>
       <c r="T18" t="s">
-        <v>80</v>
-      </c>
-      <c r="U18" s="20">
+        <v>45</v>
+      </c>
+      <c r="U18" s="15">
         <v>92.59</v>
       </c>
       <c r="V18">
-        <v>34821</v>
+        <v>34757</v>
       </c>
       <c r="W18">
-        <v>3063</v>
+        <v>3188</v>
       </c>
       <c r="X18">
-        <v>37884</v>
+        <v>37945</v>
       </c>
       <c r="Y18">
-        <v>2400</v>
+        <v>2356</v>
       </c>
       <c r="Z18">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="AA18">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="AB18">
-        <v>52</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="20">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="AC18" s="20">
+        <v>2</v>
+      </c>
+      <c r="AD18" s="13">
+        <v>51</v>
       </c>
       <c r="AE18">
-        <v>128.9666666666667</v>
+        <v>128.72999999999999</v>
       </c>
       <c r="AF18">
-        <v>11.34444444444444</v>
+        <v>11.81</v>
       </c>
       <c r="AG18">
-        <v>11.34444444444444</v>
+        <v>11.81</v>
       </c>
       <c r="AH18">
-        <v>10.37777777777778</v>
+        <v>10.3</v>
       </c>
       <c r="AI18">
-        <v>0.71851851851851856</v>
+        <v>0.82</v>
       </c>
       <c r="AJ18">
-        <v>0.71851851851851856</v>
+        <v>0.82</v>
       </c>
       <c r="AK18">
-        <v>0.19259259259259259</v>
+        <v>0.18</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM18">
-        <v>0.19259259259259259</v>
+        <v>0.19</v>
       </c>
       <c r="AN18">
-        <v>128.67777777777781</v>
-      </c>
-      <c r="AO18" s="20" t="s">
+        <v>128.11000000000001</v>
+      </c>
+      <c r="AO18" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AP18" s="20" t="s">
-        <v>176</v>
+      <c r="AP18" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.35">
@@ -3359,17 +3376,17 @@
       <c r="C19" t="s">
         <v>39</v>
       </c>
-      <c r="D19">
-        <v>137.40609276554389</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="D19" s="20">
+        <v>137.41</v>
+      </c>
+      <c r="E19" s="35">
         <v>52880731500</v>
       </c>
       <c r="F19">
-        <v>72</v>
-      </c>
-      <c r="G19" s="36">
-        <v>26.7</v>
+        <v>94</v>
+      </c>
+      <c r="G19" s="27">
+        <v>34.81</v>
       </c>
       <c r="H19">
         <v>40738</v>
@@ -3378,40 +3395,40 @@
         <v>3383</v>
       </c>
       <c r="J19" t="s">
-        <v>91</v>
-      </c>
-      <c r="K19" s="34">
+        <v>52</v>
+      </c>
+      <c r="K19" s="26">
         <v>30</v>
       </c>
       <c r="L19" t="s">
-        <v>92</v>
-      </c>
-      <c r="M19" s="28">
-        <v>68.900000000000006</v>
+        <v>99</v>
+      </c>
+      <c r="M19" s="24">
+        <v>68.89</v>
       </c>
       <c r="N19" t="s">
-        <v>93</v>
-      </c>
-      <c r="O19" s="28">
+        <v>100</v>
+      </c>
+      <c r="O19" s="24">
         <v>23.7</v>
       </c>
       <c r="P19" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q19" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>19.63</v>
       </c>
       <c r="R19" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="S19" s="14">
         <v>96.3</v>
       </c>
       <c r="T19" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U19" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="V19">
         <v>34735</v>
@@ -3434,52 +3451,52 @@
       <c r="AB19">
         <v>47</v>
       </c>
-      <c r="AC19" s="20">
+      <c r="AC19">
         <v>5</v>
       </c>
       <c r="AD19" s="13">
         <v>52</v>
       </c>
       <c r="AE19">
-        <v>128.64814814814821</v>
+        <v>128.65</v>
       </c>
       <c r="AF19">
-        <v>11.662962962962959</v>
+        <v>11.66</v>
       </c>
       <c r="AG19">
-        <v>11.662962962962959</v>
+        <v>11.66</v>
       </c>
       <c r="AH19">
-        <v>10.37777777777778</v>
+        <v>10.38</v>
       </c>
       <c r="AI19">
-        <v>0.8481481481481481</v>
+        <v>0.85</v>
       </c>
       <c r="AJ19">
-        <v>0.8481481481481481</v>
+        <v>0.85</v>
       </c>
       <c r="AK19">
-        <v>0.1740740740740741</v>
+        <v>0.17</v>
       </c>
       <c r="AL19">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="AM19">
-        <v>0.19259259259259259</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM19" s="20">
+        <v>0.19</v>
       </c>
       <c r="AN19">
-        <v>128.22592592592591</v>
+        <v>128.22999999999999</v>
       </c>
       <c r="AO19" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP19" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
@@ -3487,127 +3504,127 @@
       <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="D20">
-        <v>135.58581099291001</v>
-      </c>
-      <c r="E20" s="16">
-        <v>50307411900</v>
+      <c r="D20" s="20">
+        <v>133.02000000000001</v>
+      </c>
+      <c r="E20" s="12">
+        <v>46703825900</v>
       </c>
       <c r="F20">
-        <v>59</v>
-      </c>
-      <c r="G20" s="29">
-        <v>21.9</v>
+        <v>80</v>
+      </c>
+      <c r="G20" s="24">
+        <v>29.63</v>
       </c>
       <c r="H20">
-        <v>40777</v>
+        <v>40788</v>
       </c>
       <c r="I20">
-        <v>3411</v>
+        <v>3325</v>
       </c>
       <c r="J20" t="s">
-        <v>142</v>
-      </c>
-      <c r="K20" s="28">
-        <v>33.299999999999997</v>
+        <v>89</v>
+      </c>
+      <c r="K20" s="24">
+        <v>33.33</v>
       </c>
       <c r="L20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="24">
+        <v>64.44</v>
+      </c>
+      <c r="N20" t="s">
+        <v>105</v>
+      </c>
+      <c r="O20" s="24">
+        <v>21.85</v>
+      </c>
+      <c r="P20" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q20" s="24">
+        <v>19.63</v>
+      </c>
+      <c r="R20" t="s">
         <v>56</v>
       </c>
-      <c r="M20" s="28">
-        <v>65.2</v>
-      </c>
-      <c r="N20" t="s">
-        <v>153</v>
-      </c>
-      <c r="O20" s="28">
-        <v>23</v>
-      </c>
-      <c r="P20" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q20" s="28">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="R20" t="s">
-        <v>80</v>
-      </c>
-      <c r="S20" s="15">
-        <v>92.6</v>
+      <c r="S20" s="14">
+        <v>96.3</v>
       </c>
       <c r="T20" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="U20" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="V20">
-        <v>34757</v>
+        <v>34843</v>
       </c>
       <c r="W20">
-        <v>3188</v>
+        <v>3107</v>
       </c>
       <c r="X20">
-        <v>37945</v>
+        <v>37950</v>
       </c>
       <c r="Y20">
-        <v>2356</v>
+        <v>2376</v>
       </c>
       <c r="Z20">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AA20">
-        <v>2781</v>
+        <v>2789</v>
       </c>
       <c r="AB20">
+        <v>48</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="20">
         <v>49</v>
       </c>
-      <c r="AC20" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD20" s="13">
-        <v>51</v>
-      </c>
       <c r="AE20">
-        <v>128.72962962962961</v>
+        <v>129.05000000000001</v>
       </c>
       <c r="AF20">
-        <v>11.80740740740741</v>
+        <v>11.51</v>
       </c>
       <c r="AG20">
-        <v>11.80740740740741</v>
+        <v>11.51</v>
       </c>
       <c r="AH20">
-        <v>10.3</v>
+        <v>10.33</v>
       </c>
       <c r="AI20">
-        <v>0.81851851851851853</v>
+        <v>0.8</v>
       </c>
       <c r="AJ20">
-        <v>0.81851851851851853</v>
+        <v>0.8</v>
       </c>
       <c r="AK20">
-        <v>0.18148148148148149</v>
+        <v>0.18</v>
       </c>
       <c r="AL20">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="AM20">
-        <v>0.18888888888888891</v>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="20">
+        <v>0.18</v>
       </c>
       <c r="AN20">
-        <v>128.11481481481479</v>
+        <v>128.51</v>
       </c>
       <c r="AO20" s="12" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="AP20" s="12" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
@@ -3615,127 +3632,127 @@
       <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="20">
-        <v>133.0172042303804</v>
+      <c r="D21">
+        <v>134.38999999999999</v>
       </c>
       <c r="E21" s="12">
-        <v>46703825900</v>
+        <v>48611685100</v>
       </c>
       <c r="F21">
-        <v>61</v>
-      </c>
-      <c r="G21" s="29">
-        <v>22.6</v>
+        <v>94</v>
+      </c>
+      <c r="G21" s="27">
+        <v>34.81</v>
       </c>
       <c r="H21">
-        <v>40788</v>
+        <v>40738</v>
       </c>
       <c r="I21">
-        <v>3325</v>
+        <v>3283</v>
       </c>
       <c r="J21" t="s">
-        <v>142</v>
-      </c>
-      <c r="K21" s="28">
-        <v>33.299999999999997</v>
+        <v>64</v>
+      </c>
+      <c r="K21" s="24">
+        <v>33.700000000000003</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
-      </c>
-      <c r="M21" s="28">
-        <v>64.400000000000006</v>
+        <v>104</v>
+      </c>
+      <c r="M21" s="24">
+        <v>64.44</v>
       </c>
       <c r="N21" t="s">
-        <v>143</v>
-      </c>
-      <c r="O21" s="28">
-        <v>21.9</v>
+        <v>108</v>
+      </c>
+      <c r="O21" s="27">
+        <v>26.3</v>
       </c>
       <c r="P21" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q21" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="Q21" s="24">
+        <v>19.63</v>
       </c>
       <c r="R21" t="s">
-        <v>64</v>
-      </c>
-      <c r="S21" s="14">
-        <v>96.3</v>
+        <v>69</v>
+      </c>
+      <c r="S21" s="20">
+        <v>88.89</v>
       </c>
       <c r="T21" t="s">
-        <v>80</v>
-      </c>
-      <c r="U21" s="15">
-        <v>92.6</v>
+        <v>69</v>
+      </c>
+      <c r="U21" s="20">
+        <v>88.89</v>
       </c>
       <c r="V21">
-        <v>34843</v>
+        <v>34811</v>
       </c>
       <c r="W21">
-        <v>3107</v>
+        <v>3073</v>
       </c>
       <c r="X21">
-        <v>37950</v>
+        <v>37884</v>
       </c>
       <c r="Y21">
-        <v>2376</v>
+        <v>2389</v>
       </c>
       <c r="Z21">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="AA21">
-        <v>2789</v>
+        <v>2802</v>
       </c>
       <c r="AB21">
-        <v>48</v>
-      </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AD21" s="20">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="AC21" s="20">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="13">
+        <v>52</v>
       </c>
       <c r="AE21">
-        <v>129.04814814814819</v>
+        <v>128.93</v>
       </c>
       <c r="AF21">
-        <v>11.50740740740741</v>
+        <v>11.38</v>
       </c>
       <c r="AG21">
-        <v>11.50740740740741</v>
+        <v>11.38</v>
       </c>
       <c r="AH21">
-        <v>10.329629629629631</v>
+        <v>10.38</v>
       </c>
       <c r="AI21">
-        <v>0.8037037037037037</v>
+        <v>0.76</v>
       </c>
       <c r="AJ21">
-        <v>0.8037037037037037</v>
+        <v>0.76</v>
       </c>
       <c r="AK21">
-        <v>0.17777777777777781</v>
+        <v>0.17</v>
       </c>
       <c r="AL21">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="AM21" s="20">
-        <v>0.18148148148148149</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM21">
+        <v>0.19</v>
       </c>
       <c r="AN21">
-        <v>128.51111111111109</v>
+        <v>128.61000000000001</v>
       </c>
       <c r="AO21" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP21" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="AP21" s="12" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -3744,126 +3761,126 @@
         <v>39</v>
       </c>
       <c r="D22">
-        <v>134.38630954528321</v>
+        <v>133.04</v>
       </c>
       <c r="E22" s="12">
-        <v>48611685100</v>
+        <v>46705171100</v>
       </c>
       <c r="F22">
-        <v>72</v>
-      </c>
-      <c r="G22" s="36">
-        <v>26.7</v>
+        <v>91</v>
+      </c>
+      <c r="G22" s="26">
+        <v>33.700000000000003</v>
       </c>
       <c r="H22">
-        <v>40738</v>
+        <v>40727</v>
       </c>
       <c r="I22">
-        <v>3283</v>
+        <v>3298</v>
       </c>
       <c r="J22" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="28">
-        <v>33.700000000000003</v>
+        <v>110</v>
+      </c>
+      <c r="K22" s="24">
+        <v>35.19</v>
       </c>
       <c r="L22" t="s">
-        <v>103</v>
-      </c>
-      <c r="M22" s="28">
-        <v>64.400000000000006</v>
+        <v>111</v>
+      </c>
+      <c r="M22" s="24">
+        <v>61.48</v>
       </c>
       <c r="N22" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="33">
-        <v>26.3</v>
+        <v>76</v>
+      </c>
+      <c r="O22" s="26">
+        <v>24.44</v>
       </c>
       <c r="P22" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q22" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="Q22" s="24">
+        <v>19.63</v>
       </c>
       <c r="R22" t="s">
-        <v>52</v>
-      </c>
-      <c r="S22" s="20">
-        <v>88.9</v>
+        <v>56</v>
+      </c>
+      <c r="S22" s="14">
+        <v>96.3</v>
       </c>
       <c r="T22" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="U22" s="20">
-        <v>88.9</v>
+        <v>85.19</v>
       </c>
       <c r="V22">
-        <v>34811</v>
+        <v>34807</v>
       </c>
       <c r="W22">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="X22">
-        <v>37884</v>
+        <v>37878</v>
       </c>
       <c r="Y22">
-        <v>2389</v>
+        <v>2384</v>
       </c>
       <c r="Z22">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="AA22">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="AB22">
-        <v>47</v>
-      </c>
-      <c r="AC22" s="20">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="13">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="AC22">
+        <v>2</v>
+      </c>
+      <c r="AD22" s="20">
+        <v>48</v>
       </c>
       <c r="AE22">
-        <v>128.9296296296296</v>
+        <v>128.91</v>
       </c>
       <c r="AF22">
-        <v>11.38148148148148</v>
+        <v>11.37</v>
       </c>
       <c r="AG22">
-        <v>11.38148148148148</v>
+        <v>11.37</v>
       </c>
       <c r="AH22">
-        <v>10.37777777777778</v>
+        <v>10.37</v>
       </c>
       <c r="AI22">
-        <v>0.7592592592592593</v>
+        <v>0.83</v>
       </c>
       <c r="AJ22">
-        <v>0.7592592592592593</v>
+        <v>0.83</v>
       </c>
       <c r="AK22">
-        <v>0.1740740740740741</v>
+        <v>0.17</v>
       </c>
       <c r="AL22">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="AM22">
-        <v>0.19259259259259259</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM22" s="20">
+        <v>0.18</v>
       </c>
       <c r="AN22">
-        <v>128.61111111111109</v>
+        <v>128.53</v>
       </c>
       <c r="AO22" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP22" s="12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
@@ -3872,126 +3889,126 @@
         <v>39</v>
       </c>
       <c r="D23">
-        <v>133.03770415500401</v>
+        <v>133.11000000000001</v>
       </c>
       <c r="E23" s="12">
-        <v>46705171100</v>
+        <v>46813614000</v>
       </c>
       <c r="F23">
-        <v>68</v>
-      </c>
-      <c r="G23" s="29">
-        <v>25.2</v>
+        <v>94</v>
+      </c>
+      <c r="G23" s="27">
+        <v>34.81</v>
       </c>
       <c r="H23">
-        <v>40727</v>
+        <v>40738</v>
       </c>
       <c r="I23">
-        <v>3298</v>
+        <v>3257</v>
       </c>
       <c r="J23" t="s">
-        <v>115</v>
-      </c>
-      <c r="K23" s="28">
-        <v>35.200000000000003</v>
+        <v>95</v>
+      </c>
+      <c r="K23" s="24">
+        <v>37.04</v>
       </c>
       <c r="L23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M23" s="28">
-        <v>61.5</v>
+        <v>72</v>
+      </c>
+      <c r="M23" s="24">
+        <v>60.37</v>
       </c>
       <c r="N23" t="s">
-        <v>57</v>
-      </c>
-      <c r="O23" s="34">
-        <v>24.4</v>
+        <v>96</v>
+      </c>
+      <c r="O23" s="24">
+        <v>22.96</v>
       </c>
       <c r="P23" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q23" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="Q23" s="24">
+        <v>19.63</v>
       </c>
       <c r="R23" t="s">
-        <v>64</v>
-      </c>
-      <c r="S23" s="14">
-        <v>96.3</v>
+        <v>45</v>
+      </c>
+      <c r="S23" s="20">
+        <v>92.59</v>
       </c>
       <c r="T23" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="U23" s="20">
-        <v>85.2</v>
+        <v>92.59</v>
       </c>
       <c r="V23">
-        <v>34807</v>
+        <v>34821</v>
       </c>
       <c r="W23">
-        <v>3071</v>
+        <v>3063</v>
       </c>
       <c r="X23">
-        <v>37878</v>
+        <v>37884</v>
       </c>
       <c r="Y23">
-        <v>2384</v>
+        <v>2400</v>
       </c>
       <c r="Z23">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="AA23">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="AB23">
+        <v>52</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="13">
+        <v>52</v>
+      </c>
+      <c r="AE23">
+        <v>128.97</v>
+      </c>
+      <c r="AF23">
+        <v>11.34</v>
+      </c>
+      <c r="AG23">
+        <v>11.34</v>
+      </c>
+      <c r="AH23">
+        <v>10.38</v>
+      </c>
+      <c r="AI23">
+        <v>0.72</v>
+      </c>
+      <c r="AJ23">
+        <v>0.72</v>
+      </c>
+      <c r="AK23">
+        <v>0.19</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="20">
+        <v>0.19</v>
+      </c>
+      <c r="AN23">
+        <v>128.68</v>
+      </c>
+      <c r="AO23" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="AC23" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD23" s="20">
-        <v>48</v>
-      </c>
-      <c r="AE23">
-        <v>128.9148148148148</v>
-      </c>
-      <c r="AF23">
-        <v>11.37407407407407</v>
-      </c>
-      <c r="AG23">
-        <v>11.37407407407407</v>
-      </c>
-      <c r="AH23">
-        <v>10.37407407407407</v>
-      </c>
-      <c r="AI23">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="AJ23">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="AK23">
-        <v>0.17037037037037039</v>
-      </c>
-      <c r="AL23">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="AM23" s="20">
-        <v>0.17777777777777781</v>
-      </c>
-      <c r="AN23">
-        <v>128.5333333333333</v>
-      </c>
-      <c r="AO23" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="AP23" s="12" t="s">
-        <v>117</v>
+      <c r="AP23" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
@@ -3999,127 +4016,127 @@
       <c r="C24" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="20">
-        <v>135.01545052567991</v>
+      <c r="D24">
+        <v>134.38</v>
       </c>
       <c r="E24" s="12">
-        <v>49501097300</v>
+        <v>48607784700</v>
       </c>
       <c r="F24">
-        <v>72</v>
-      </c>
-      <c r="G24" s="36">
-        <v>26.7</v>
+        <v>94</v>
+      </c>
+      <c r="G24" s="27">
+        <v>34.81</v>
       </c>
       <c r="H24">
         <v>40738</v>
       </c>
       <c r="I24">
-        <v>3379</v>
+        <v>3393</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
-      </c>
-      <c r="K24" s="28">
-        <v>31.1</v>
+        <v>119</v>
+      </c>
+      <c r="K24" s="24">
+        <v>35.93</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
-      </c>
-      <c r="M24" s="28">
-        <v>67.400000000000006</v>
+        <v>120</v>
+      </c>
+      <c r="M24" s="24">
+        <v>61.11</v>
       </c>
       <c r="N24" t="s">
-        <v>101</v>
-      </c>
-      <c r="O24" s="28">
-        <v>22.2</v>
+        <v>113</v>
+      </c>
+      <c r="O24" s="24">
+        <v>22.22</v>
       </c>
       <c r="P24" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q24" s="28">
-        <v>19.3</v>
+        <v>114</v>
+      </c>
+      <c r="Q24" s="24">
+        <v>19.260000000000002</v>
       </c>
       <c r="R24" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="S24" s="15">
-        <v>92.6</v>
+        <v>96.3</v>
       </c>
       <c r="T24" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="U24" s="20">
-        <v>85.2</v>
+        <v>85.19</v>
       </c>
       <c r="V24">
-        <v>34714</v>
+        <v>34700</v>
       </c>
       <c r="W24">
-        <v>3170</v>
+        <v>3184</v>
       </c>
       <c r="X24">
         <v>37884</v>
       </c>
       <c r="Y24">
-        <v>2387</v>
+        <v>2393</v>
       </c>
       <c r="Z24">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AA24">
         <v>2802</v>
       </c>
       <c r="AB24">
-        <v>50</v>
-      </c>
-      <c r="AC24" s="20">
-        <v>2</v>
+        <v>44</v>
+      </c>
+      <c r="AC24" s="13">
+        <v>8</v>
       </c>
       <c r="AD24" s="13">
         <v>52</v>
       </c>
       <c r="AE24">
-        <v>128.5703703703704</v>
+        <v>128.52000000000001</v>
       </c>
       <c r="AF24">
-        <v>11.74074074074074</v>
+        <v>11.79</v>
       </c>
       <c r="AG24">
-        <v>11.74074074074074</v>
+        <v>11.79</v>
       </c>
       <c r="AH24">
-        <v>10.37777777777778</v>
+        <v>10.38</v>
       </c>
       <c r="AI24">
-        <v>0.76666666666666672</v>
+        <v>0.74</v>
       </c>
       <c r="AJ24">
-        <v>0.76666666666666672</v>
+        <v>0.74</v>
       </c>
       <c r="AK24">
-        <v>0.1851851851851852</v>
+        <v>0.16</v>
       </c>
       <c r="AL24">
-        <v>7.4074074074074077E-3</v>
+        <v>0.03</v>
       </c>
       <c r="AM24" s="20">
-        <v>0.19259259259259259</v>
+        <v>0.19</v>
       </c>
       <c r="AN24">
-        <v>128.2222222222222</v>
+        <v>128.22</v>
       </c>
       <c r="AO24" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP24" s="12" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
@@ -4128,121 +4145,121 @@
         <v>39</v>
       </c>
       <c r="D25">
-        <v>131.9139846487179</v>
+        <v>135.02000000000001</v>
       </c>
       <c r="E25" s="12">
-        <v>45116576700</v>
+        <v>49501097300</v>
       </c>
       <c r="F25">
-        <v>78</v>
-      </c>
-      <c r="G25" s="35">
-        <v>28.9</v>
+        <v>94</v>
+      </c>
+      <c r="G25" s="27">
+        <v>34.81</v>
       </c>
       <c r="H25">
-        <v>40715</v>
+        <v>40738</v>
       </c>
       <c r="I25">
-        <v>3314</v>
+        <v>3379</v>
       </c>
       <c r="J25" t="s">
-        <v>55</v>
-      </c>
-      <c r="K25" s="28">
-        <v>32.200000000000003</v>
+        <v>58</v>
+      </c>
+      <c r="K25" s="24">
+        <v>31.11</v>
       </c>
       <c r="L25" t="s">
-        <v>56</v>
-      </c>
-      <c r="M25" s="28">
-        <v>65.2</v>
+        <v>83</v>
+      </c>
+      <c r="M25" s="24">
+        <v>67.41</v>
       </c>
       <c r="N25" t="s">
-        <v>57</v>
-      </c>
-      <c r="O25" s="34">
-        <v>24.4</v>
+        <v>113</v>
+      </c>
+      <c r="O25" s="24">
+        <v>22.22</v>
       </c>
       <c r="P25" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q25" s="28">
-        <v>19.3</v>
+        <v>114</v>
+      </c>
+      <c r="Q25" s="24">
+        <v>19.260000000000002</v>
       </c>
       <c r="R25" t="s">
+        <v>45</v>
+      </c>
+      <c r="S25" s="15">
+        <v>92.59</v>
+      </c>
+      <c r="T25" t="s">
+        <v>62</v>
+      </c>
+      <c r="U25" s="20">
+        <v>85.19</v>
+      </c>
+      <c r="V25">
+        <v>34714</v>
+      </c>
+      <c r="W25">
+        <v>3170</v>
+      </c>
+      <c r="X25">
+        <v>37884</v>
+      </c>
+      <c r="Y25">
+        <v>2387</v>
+      </c>
+      <c r="Z25">
+        <v>207</v>
+      </c>
+      <c r="AA25">
+        <v>2802</v>
+      </c>
+      <c r="AB25">
+        <v>50</v>
+      </c>
+      <c r="AC25">
+        <v>2</v>
+      </c>
+      <c r="AD25" s="13">
         <v>52</v>
       </c>
-      <c r="S25" s="20">
-        <v>88.9</v>
-      </c>
-      <c r="T25" t="s">
-        <v>52</v>
-      </c>
-      <c r="U25" s="20">
-        <v>88.9</v>
-      </c>
-      <c r="V25">
-        <v>34792</v>
-      </c>
-      <c r="W25">
-        <v>3079</v>
-      </c>
-      <c r="X25">
-        <v>37871</v>
-      </c>
-      <c r="Y25">
-        <v>2383</v>
-      </c>
-      <c r="Z25">
-        <v>231</v>
-      </c>
-      <c r="AA25">
-        <v>2798</v>
-      </c>
-      <c r="AB25">
-        <v>42</v>
-      </c>
-      <c r="AC25">
-        <v>4</v>
-      </c>
-      <c r="AD25" s="20">
-        <v>46</v>
-      </c>
       <c r="AE25">
-        <v>128.85925925925929</v>
+        <v>128.57</v>
       </c>
       <c r="AF25">
-        <v>11.4037037037037</v>
+        <v>11.74</v>
       </c>
       <c r="AG25">
-        <v>11.4037037037037</v>
+        <v>11.74</v>
       </c>
       <c r="AH25">
-        <v>10.36296296296296</v>
+        <v>10.38</v>
       </c>
       <c r="AI25">
-        <v>0.85555555555555551</v>
+        <v>0.77</v>
       </c>
       <c r="AJ25">
-        <v>0.85555555555555551</v>
+        <v>0.77</v>
       </c>
       <c r="AK25">
-        <v>0.15555555555555561</v>
+        <v>0.19</v>
       </c>
       <c r="AL25">
-        <v>1.4814814814814821E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM25">
-        <v>0.17037037037037039</v>
+        <v>0.19</v>
       </c>
       <c r="AN25">
-        <v>128.47407407407411</v>
+        <v>128.22</v>
       </c>
       <c r="AO25" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP25" s="12" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.35">
@@ -4256,16 +4273,16 @@
         <v>39</v>
       </c>
       <c r="D26" s="20">
-        <v>133.0426598940991</v>
+        <v>133.04</v>
       </c>
       <c r="E26" s="12">
         <v>46739833700</v>
       </c>
       <c r="F26">
-        <v>63</v>
-      </c>
-      <c r="G26" s="29">
-        <v>23.3</v>
+        <v>87</v>
+      </c>
+      <c r="G26" s="26">
+        <v>32.22</v>
       </c>
       <c r="H26">
         <v>40773</v>
@@ -4274,40 +4291,40 @@
         <v>3382</v>
       </c>
       <c r="J26" t="s">
-        <v>70</v>
-      </c>
-      <c r="K26" s="28">
+        <v>64</v>
+      </c>
+      <c r="K26" s="24">
         <v>33.700000000000003</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
-      </c>
-      <c r="M26" s="28">
-        <v>64.400000000000006</v>
+        <v>104</v>
+      </c>
+      <c r="M26" s="24">
+        <v>64.44</v>
       </c>
       <c r="N26" t="s">
-        <v>57</v>
-      </c>
-      <c r="O26" s="34">
-        <v>24.4</v>
+        <v>76</v>
+      </c>
+      <c r="O26" s="26">
+        <v>24.44</v>
       </c>
       <c r="P26" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" s="28">
-        <v>19.3</v>
+        <v>114</v>
+      </c>
+      <c r="Q26" s="24">
+        <v>19.260000000000002</v>
       </c>
       <c r="R26" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="S26" s="14">
         <v>96.3</v>
       </c>
       <c r="T26" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="U26" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="V26">
         <v>34769</v>
@@ -4330,52 +4347,52 @@
       <c r="AB26">
         <v>43</v>
       </c>
-      <c r="AC26" s="20">
+      <c r="AC26">
         <v>6</v>
       </c>
       <c r="AD26" s="20">
         <v>49</v>
       </c>
       <c r="AE26">
-        <v>128.77407407407409</v>
+        <v>128.77000000000001</v>
       </c>
       <c r="AF26">
-        <v>11.707407407407411</v>
+        <v>11.71</v>
       </c>
       <c r="AG26">
-        <v>11.707407407407411</v>
+        <v>11.71</v>
       </c>
       <c r="AH26">
-        <v>10.34814814814815</v>
+        <v>10.35</v>
       </c>
       <c r="AI26">
-        <v>0.79629629629629628</v>
+        <v>0.8</v>
       </c>
       <c r="AJ26">
-        <v>0.79629629629629628</v>
+        <v>0.8</v>
       </c>
       <c r="AK26">
-        <v>0.15925925925925929</v>
+        <v>0.16</v>
       </c>
       <c r="AL26">
-        <v>2.222222222222222E-2</v>
+        <v>0.02</v>
       </c>
       <c r="AM26" s="20">
-        <v>0.18148148148148149</v>
+        <v>0.18</v>
       </c>
       <c r="AN26">
         <v>128.30000000000001</v>
       </c>
       <c r="AO26" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP26" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>38</v>
@@ -4383,122 +4400,122 @@
       <c r="C27" t="s">
         <v>39</v>
       </c>
-      <c r="D27">
-        <v>134.38355053041931</v>
+      <c r="D27" s="20">
+        <v>131.91</v>
       </c>
       <c r="E27" s="12">
-        <v>48607784700</v>
+        <v>45116576700</v>
       </c>
       <c r="F27">
-        <v>72</v>
-      </c>
-      <c r="G27" s="36">
-        <v>26.67</v>
+        <v>92</v>
+      </c>
+      <c r="G27" s="27">
+        <v>34.07</v>
       </c>
       <c r="H27">
-        <v>40738</v>
+        <v>40715</v>
       </c>
       <c r="I27">
-        <v>3393</v>
+        <v>3314</v>
       </c>
       <c r="J27" t="s">
-        <v>173</v>
-      </c>
-      <c r="K27" s="28">
-        <v>35.93</v>
+        <v>116</v>
+      </c>
+      <c r="K27" s="24">
+        <v>32.22</v>
       </c>
       <c r="L27" t="s">
-        <v>174</v>
-      </c>
-      <c r="M27" s="28">
-        <v>61.11</v>
+        <v>102</v>
+      </c>
+      <c r="M27" s="24">
+        <v>65.19</v>
       </c>
       <c r="N27" t="s">
-        <v>101</v>
-      </c>
-      <c r="O27" s="28">
-        <v>22.22</v>
+        <v>76</v>
+      </c>
+      <c r="O27" s="26">
+        <v>24.44</v>
       </c>
       <c r="P27" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q27" s="28">
+        <v>114</v>
+      </c>
+      <c r="Q27" s="24">
         <v>19.260000000000002</v>
       </c>
       <c r="R27" t="s">
-        <v>64</v>
-      </c>
-      <c r="S27" s="15">
-        <v>96.3</v>
+        <v>69</v>
+      </c>
+      <c r="S27" s="20">
+        <v>88.89</v>
       </c>
       <c r="T27" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="U27" s="20">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="V27">
-        <v>34700</v>
+        <v>34792</v>
       </c>
       <c r="W27">
-        <v>3184</v>
+        <v>3079</v>
       </c>
       <c r="X27">
-        <v>37884</v>
+        <v>37871</v>
       </c>
       <c r="Y27">
-        <v>2393</v>
+        <v>2383</v>
       </c>
       <c r="Z27">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="AA27">
-        <v>2802</v>
+        <v>2798</v>
       </c>
       <c r="AB27">
-        <v>44</v>
-      </c>
-      <c r="AC27" s="13">
-        <v>8</v>
+        <v>42</v>
+      </c>
+      <c r="AC27" s="20">
+        <v>4</v>
       </c>
       <c r="AD27" s="20">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AE27">
-        <v>128.5185185185185</v>
+        <v>128.86000000000001</v>
       </c>
       <c r="AF27">
-        <v>11.792592592592589</v>
+        <v>11.4</v>
       </c>
       <c r="AG27">
-        <v>11.792592592592589</v>
+        <v>11.4</v>
       </c>
       <c r="AH27">
-        <v>10.37777777777778</v>
+        <v>10.36</v>
       </c>
       <c r="AI27">
-        <v>0.74444444444444446</v>
+        <v>0.86</v>
       </c>
       <c r="AJ27">
-        <v>0.74444444444444446</v>
+        <v>0.86</v>
       </c>
       <c r="AK27">
-        <v>0.162962962962963</v>
+        <v>0.16</v>
       </c>
       <c r="AL27">
-        <v>2.9629629629629631E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM27" s="20">
-        <v>0.19259259259259259</v>
+        <v>0.17</v>
       </c>
       <c r="AN27">
-        <v>128.21851851851849</v>
+        <v>128.47</v>
       </c>
       <c r="AO27" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP27" s="12" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.35">
@@ -4512,16 +4529,16 @@
         <v>39</v>
       </c>
       <c r="D28" s="20">
-        <v>130.43550537492939</v>
+        <v>130.44</v>
       </c>
       <c r="E28" s="12">
         <v>43026460900</v>
       </c>
       <c r="F28">
-        <v>57</v>
-      </c>
-      <c r="G28" s="29">
-        <v>21.1</v>
+        <v>80</v>
+      </c>
+      <c r="G28" s="24">
+        <v>29.63</v>
       </c>
       <c r="H28">
         <v>40707</v>
@@ -4530,40 +4547,40 @@
         <v>3470</v>
       </c>
       <c r="J28" t="s">
-        <v>60</v>
-      </c>
-      <c r="K28" s="28">
-        <v>34.4</v>
+        <v>122</v>
+      </c>
+      <c r="K28" s="24">
+        <v>34.44</v>
       </c>
       <c r="L28" t="s">
-        <v>71</v>
-      </c>
-      <c r="M28" s="28">
-        <v>63</v>
+        <v>92</v>
+      </c>
+      <c r="M28" s="24">
+        <v>62.96</v>
       </c>
       <c r="N28" t="s">
-        <v>42</v>
-      </c>
-      <c r="O28" s="28">
-        <v>22.6</v>
+        <v>123</v>
+      </c>
+      <c r="O28" s="24">
+        <v>22.59</v>
       </c>
       <c r="P28" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q28" s="28">
-        <v>18.5</v>
+        <v>124</v>
+      </c>
+      <c r="Q28" s="24">
+        <v>18.52</v>
       </c>
       <c r="R28" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="S28" s="14">
         <v>96.3</v>
       </c>
       <c r="T28" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="U28" s="20">
-        <v>85.2</v>
+        <v>85.19</v>
       </c>
       <c r="V28">
         <v>34638</v>
@@ -4586,47 +4603,47 @@
       <c r="AB28">
         <v>42</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="20">
         <v>2</v>
       </c>
       <c r="AD28" s="20">
         <v>44</v>
       </c>
       <c r="AE28">
-        <v>128.28888888888889</v>
+        <v>128.29</v>
       </c>
       <c r="AF28">
-        <v>11.9962962962963</v>
+        <v>12</v>
       </c>
       <c r="AG28">
-        <v>11.9962962962963</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI28">
-        <v>0.8481481481481481</v>
+        <v>0.85</v>
       </c>
       <c r="AJ28">
-        <v>0.8481481481481481</v>
+        <v>0.85</v>
       </c>
       <c r="AK28">
-        <v>0.15555555555555561</v>
+        <v>0.16</v>
       </c>
       <c r="AL28">
-        <v>7.4074074074074077E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AM28" s="20">
-        <v>0.162962962962963</v>
+        <v>0.16</v>
       </c>
       <c r="AN28">
-        <v>127.8962962962963</v>
+        <v>127.9</v>
       </c>
       <c r="AO28" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP28" s="12" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.35">
@@ -4640,16 +4657,16 @@
         <v>39</v>
       </c>
       <c r="D29" s="20">
-        <v>129.28038824553849</v>
+        <v>129.28</v>
       </c>
       <c r="E29" s="12">
         <v>41393479900</v>
       </c>
       <c r="F29">
-        <v>56</v>
-      </c>
-      <c r="G29" s="29">
-        <v>20.7</v>
+        <v>72</v>
+      </c>
+      <c r="G29" s="24">
+        <v>26.67</v>
       </c>
       <c r="H29">
         <v>40743</v>
@@ -4658,40 +4675,40 @@
         <v>3419</v>
       </c>
       <c r="J29" t="s">
-        <v>115</v>
-      </c>
-      <c r="K29" s="28">
-        <v>35.200000000000003</v>
+        <v>110</v>
+      </c>
+      <c r="K29" s="24">
+        <v>35.19</v>
       </c>
       <c r="L29" t="s">
-        <v>71</v>
-      </c>
-      <c r="M29" s="28">
-        <v>63</v>
+        <v>92</v>
+      </c>
+      <c r="M29" s="24">
+        <v>62.96</v>
       </c>
       <c r="N29" t="s">
-        <v>93</v>
-      </c>
-      <c r="O29" s="28">
+        <v>100</v>
+      </c>
+      <c r="O29" s="24">
         <v>23.7</v>
       </c>
       <c r="P29" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q29" s="28">
-        <v>18.5</v>
+        <v>124</v>
+      </c>
+      <c r="Q29" s="24">
+        <v>18.52</v>
       </c>
       <c r="R29" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="S29" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="T29" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="U29" s="20">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="V29">
         <v>34727</v>
@@ -4714,47 +4731,47 @@
       <c r="AB29">
         <v>40</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="20">
         <v>4</v>
       </c>
       <c r="AD29" s="20">
         <v>44</v>
       </c>
       <c r="AE29">
-        <v>128.6185185185185</v>
+        <v>128.62</v>
       </c>
       <c r="AF29">
-        <v>11.829629629629631</v>
+        <v>11.83</v>
       </c>
       <c r="AG29">
-        <v>11.829629629629631</v>
+        <v>11.83</v>
       </c>
       <c r="AH29">
-        <v>10.28888888888889</v>
+        <v>10.29</v>
       </c>
       <c r="AI29">
-        <v>0.81851851851851853</v>
+        <v>0.82</v>
       </c>
       <c r="AJ29">
-        <v>0.81851851851851853</v>
+        <v>0.82</v>
       </c>
       <c r="AK29">
-        <v>0.14814814814814811</v>
+        <v>0.15</v>
       </c>
       <c r="AL29">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="AM29">
-        <v>0.162962962962963</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM29" s="20">
+        <v>0.16</v>
       </c>
       <c r="AN29">
-        <v>128.0851851851852</v>
+        <v>128.09</v>
       </c>
       <c r="AO29" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP29" s="12" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.35">
@@ -4768,16 +4785,16 @@
         <v>39</v>
       </c>
       <c r="D30" s="20">
-        <v>130.80206183379281</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="E30" s="12">
         <v>43544659200</v>
       </c>
       <c r="F30">
-        <v>65</v>
-      </c>
-      <c r="G30" s="29">
-        <v>24.1</v>
+        <v>81</v>
+      </c>
+      <c r="G30" s="34">
+        <v>30</v>
       </c>
       <c r="H30">
         <v>40732</v>
@@ -4786,40 +4803,40 @@
         <v>3363</v>
       </c>
       <c r="J30" t="s">
-        <v>76</v>
-      </c>
-      <c r="K30" s="28">
-        <v>31.9</v>
+        <v>128</v>
+      </c>
+      <c r="K30" s="24">
+        <v>31.85</v>
       </c>
       <c r="L30" t="s">
-        <v>77</v>
-      </c>
-      <c r="M30" s="28">
-        <v>65.599999999999994</v>
+        <v>65</v>
+      </c>
+      <c r="M30" s="24">
+        <v>65.56</v>
       </c>
       <c r="N30" t="s">
-        <v>42</v>
-      </c>
-      <c r="O30" s="28">
-        <v>22.6</v>
+        <v>123</v>
+      </c>
+      <c r="O30" s="24">
+        <v>22.59</v>
       </c>
       <c r="P30" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q30" s="28">
-        <v>18.100000000000001</v>
+        <v>129</v>
+      </c>
+      <c r="Q30" s="24">
+        <v>18.149999999999999</v>
       </c>
       <c r="R30" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="S30" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="T30" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="U30" s="20">
-        <v>81.5</v>
+        <v>81.48</v>
       </c>
       <c r="V30">
         <v>34767</v>
@@ -4842,47 +4859,47 @@
       <c r="AB30">
         <v>44</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="20">
         <v>1</v>
       </c>
       <c r="AD30" s="20">
         <v>45</v>
       </c>
       <c r="AE30">
-        <v>128.76666666666671</v>
+        <v>128.77000000000001</v>
       </c>
       <c r="AF30">
-        <v>11.607407407407409</v>
+        <v>11.61</v>
       </c>
       <c r="AG30">
-        <v>11.607407407407409</v>
+        <v>11.61</v>
       </c>
       <c r="AH30">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI30">
-        <v>0.84444444444444444</v>
+        <v>0.84</v>
       </c>
       <c r="AJ30">
-        <v>0.84444444444444444</v>
+        <v>0.84</v>
       </c>
       <c r="AK30">
-        <v>0.162962962962963</v>
+        <v>0.16</v>
       </c>
       <c r="AL30">
-        <v>3.7037037037037038E-3</v>
+        <v>0</v>
       </c>
       <c r="AM30" s="20">
-        <v>0.16666666666666671</v>
+        <v>0.17</v>
       </c>
       <c r="AN30">
-        <v>128.2925925925926</v>
+        <v>128.29</v>
       </c>
       <c r="AO30" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP30" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.35">
@@ -4895,17 +4912,17 @@
       <c r="C31" t="s">
         <v>39</v>
       </c>
-      <c r="D31">
-        <v>129.30531876439929</v>
+      <c r="D31" s="20">
+        <v>129.31</v>
       </c>
       <c r="E31" s="12">
         <v>41428724000</v>
       </c>
       <c r="F31">
-        <v>75</v>
-      </c>
-      <c r="G31" s="35">
-        <v>27.8</v>
+        <v>90</v>
+      </c>
+      <c r="G31" s="26">
+        <v>33.33</v>
       </c>
       <c r="H31">
         <v>40733</v>
@@ -4914,40 +4931,40 @@
         <v>3334</v>
       </c>
       <c r="J31" t="s">
-        <v>60</v>
-      </c>
-      <c r="K31" s="28">
-        <v>34.4</v>
+        <v>122</v>
+      </c>
+      <c r="K31" s="24">
+        <v>34.44</v>
       </c>
       <c r="L31" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="28">
-        <v>62.2</v>
+        <v>131</v>
+      </c>
+      <c r="M31" s="24">
+        <v>62.22</v>
       </c>
       <c r="N31" t="s">
-        <v>62</v>
-      </c>
-      <c r="O31" s="28">
-        <v>23.3</v>
+        <v>90</v>
+      </c>
+      <c r="O31" s="24">
+        <v>23.33</v>
       </c>
       <c r="P31" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q31" s="28">
-        <v>18.100000000000001</v>
+        <v>129</v>
+      </c>
+      <c r="Q31" s="24">
+        <v>18.149999999999999</v>
       </c>
       <c r="R31" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="S31" s="14">
         <v>96.3</v>
       </c>
       <c r="T31" t="s">
-        <v>52</v>
-      </c>
-      <c r="U31" s="20">
-        <v>88.9</v>
+        <v>69</v>
+      </c>
+      <c r="U31">
+        <v>88.89</v>
       </c>
       <c r="V31">
         <v>34756</v>
@@ -4977,31 +4994,31 @@
         <v>47</v>
       </c>
       <c r="AE31">
-        <v>128.72592592592591</v>
+        <v>128.72999999999999</v>
       </c>
       <c r="AF31">
-        <v>11.607407407407409</v>
+        <v>11.61</v>
       </c>
       <c r="AG31">
-        <v>11.607407407407409</v>
+        <v>11.61</v>
       </c>
       <c r="AH31">
-        <v>10.35555555555556</v>
+        <v>10.36</v>
       </c>
       <c r="AI31">
-        <v>0.73333333333333328</v>
+        <v>0.73</v>
       </c>
       <c r="AJ31">
-        <v>0.73333333333333328</v>
+        <v>0.73</v>
       </c>
       <c r="AK31">
-        <v>0.16666666666666671</v>
+        <v>0.17</v>
       </c>
       <c r="AL31">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="AM31" s="20">
-        <v>0.1740740740740741</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM31">
+        <v>0.17</v>
       </c>
       <c r="AN31">
         <v>128.4</v>
@@ -5010,7 +5027,7 @@
         <v>46</v>
       </c>
       <c r="AP31" s="12" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.35">
@@ -5023,17 +5040,17 @@
       <c r="C32" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="20">
-        <v>131.9339636487031</v>
+      <c r="D32">
+        <v>131.93</v>
       </c>
       <c r="E32" s="12">
         <v>45171549600</v>
       </c>
       <c r="F32">
-        <v>59</v>
-      </c>
-      <c r="G32" s="29">
-        <v>21.9</v>
+        <v>77</v>
+      </c>
+      <c r="G32" s="24">
+        <v>28.52</v>
       </c>
       <c r="H32">
         <v>40773</v>
@@ -5042,40 +5059,40 @@
         <v>3434</v>
       </c>
       <c r="J32" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="34">
-        <v>30.4</v>
+        <v>133</v>
+      </c>
+      <c r="K32" s="26">
+        <v>30.37</v>
       </c>
       <c r="L32" t="s">
-        <v>150</v>
-      </c>
-      <c r="M32" s="28">
-        <v>68.5</v>
+        <v>134</v>
+      </c>
+      <c r="M32" s="24">
+        <v>68.52</v>
       </c>
       <c r="N32" t="s">
-        <v>123</v>
-      </c>
-      <c r="O32" s="28">
-        <v>21.1</v>
+        <v>55</v>
+      </c>
+      <c r="O32" s="24">
+        <v>21.11</v>
       </c>
       <c r="P32" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q32" s="28">
-        <v>17.8</v>
+        <v>135</v>
+      </c>
+      <c r="Q32" s="24">
+        <v>17.78</v>
       </c>
       <c r="R32" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S32" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T32" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="U32" s="20">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="V32">
         <v>34736</v>
@@ -5098,47 +5115,47 @@
       <c r="AB32">
         <v>45</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="20">
         <v>1</v>
       </c>
       <c r="AD32" s="20">
         <v>46</v>
       </c>
       <c r="AE32">
-        <v>128.65185185185189</v>
+        <v>128.65</v>
       </c>
       <c r="AF32">
-        <v>11.87037037037037</v>
+        <v>11.87</v>
       </c>
       <c r="AG32">
-        <v>11.87037037037037</v>
+        <v>11.87</v>
       </c>
       <c r="AH32">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI32">
-        <v>0.84444444444444444</v>
+        <v>0.84</v>
       </c>
       <c r="AJ32">
-        <v>0.84444444444444444</v>
+        <v>0.84</v>
       </c>
       <c r="AK32">
-        <v>0.16666666666666671</v>
+        <v>0.17</v>
       </c>
       <c r="AL32">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="AM32" s="20">
-        <v>0.17037037037037039</v>
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0.17</v>
       </c>
       <c r="AN32">
-        <v>128.10740740740741</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AO32" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP32" s="12" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.35">
@@ -5151,17 +5168,17 @@
       <c r="C33" t="s">
         <v>39</v>
       </c>
-      <c r="D33">
-        <v>131.4573185974607</v>
+      <c r="D33" s="20">
+        <v>131.46</v>
       </c>
       <c r="E33" s="12">
         <v>44470991100</v>
       </c>
       <c r="F33">
-        <v>55</v>
-      </c>
-      <c r="G33" s="29">
-        <v>20.399999999999999</v>
+        <v>73</v>
+      </c>
+      <c r="G33" s="24">
+        <v>27.04</v>
       </c>
       <c r="H33">
         <v>40730</v>
@@ -5170,40 +5187,40 @@
         <v>3412</v>
       </c>
       <c r="J33" t="s">
-        <v>127</v>
-      </c>
-      <c r="K33" s="34">
-        <v>30.7</v>
+        <v>40</v>
+      </c>
+      <c r="K33" s="26">
+        <v>30.74</v>
       </c>
       <c r="L33" t="s">
-        <v>162</v>
-      </c>
-      <c r="M33" s="28">
-        <v>67.8</v>
+        <v>137</v>
+      </c>
+      <c r="M33" s="24">
+        <v>67.78</v>
       </c>
       <c r="N33" t="s">
-        <v>42</v>
-      </c>
-      <c r="O33" s="28">
-        <v>22.6</v>
+        <v>123</v>
+      </c>
+      <c r="O33" s="24">
+        <v>22.59</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q33" s="28">
-        <v>17.8</v>
+        <v>135</v>
+      </c>
+      <c r="Q33" s="24">
+        <v>17.78</v>
       </c>
       <c r="R33" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S33" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T33" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="U33" s="20">
-        <v>74.099999999999994</v>
+        <v>74.069999999999993</v>
       </c>
       <c r="V33">
         <v>34737</v>
@@ -5233,40 +5250,40 @@
         <v>44</v>
       </c>
       <c r="AE33">
-        <v>128.65555555555559</v>
+        <v>128.66</v>
       </c>
       <c r="AF33">
-        <v>11.733333333333331</v>
+        <v>11.73</v>
       </c>
       <c r="AG33">
-        <v>11.733333333333331</v>
+        <v>11.73</v>
       </c>
       <c r="AH33">
         <v>10.3</v>
       </c>
       <c r="AI33">
-        <v>0.8925925925925926</v>
+        <v>0.89</v>
       </c>
       <c r="AJ33">
-        <v>0.8925925925925926</v>
+        <v>0.89</v>
       </c>
       <c r="AK33">
-        <v>0.15185185185185179</v>
+        <v>0.15</v>
       </c>
       <c r="AL33">
-        <v>1.111111111111111E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM33" s="20">
-        <v>0.162962962962963</v>
+        <v>0.16</v>
       </c>
       <c r="AN33">
-        <v>128.11111111111109</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AO33" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP33" s="12" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.35">
@@ -5280,16 +5297,16 @@
         <v>39</v>
       </c>
       <c r="D34" s="20">
-        <v>129.69486055438909</v>
+        <v>129.69</v>
       </c>
       <c r="E34" s="12">
         <v>42004271100</v>
       </c>
       <c r="F34">
-        <v>54</v>
-      </c>
-      <c r="G34" s="29">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="G34" s="24">
+        <v>27.78</v>
       </c>
       <c r="H34">
         <v>40752</v>
@@ -5298,40 +5315,40 @@
         <v>3420</v>
       </c>
       <c r="J34" t="s">
-        <v>55</v>
-      </c>
-      <c r="K34" s="28">
-        <v>32.200000000000003</v>
+        <v>116</v>
+      </c>
+      <c r="K34" s="24">
+        <v>32.22</v>
       </c>
       <c r="L34" t="s">
-        <v>166</v>
-      </c>
-      <c r="M34" s="28">
-        <v>66.7</v>
+        <v>59</v>
+      </c>
+      <c r="M34" s="24">
+        <v>66.67</v>
       </c>
       <c r="N34" t="s">
-        <v>147</v>
-      </c>
-      <c r="O34" s="28">
-        <v>20.7</v>
+        <v>74</v>
+      </c>
+      <c r="O34" s="24">
+        <v>20.74</v>
       </c>
       <c r="P34" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q34" s="28">
-        <v>17</v>
+        <v>140</v>
+      </c>
+      <c r="Q34" s="24">
+        <v>17.04</v>
       </c>
       <c r="R34" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="S34" s="14">
         <v>96.3</v>
       </c>
       <c r="T34" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U34" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="V34">
         <v>34740</v>
@@ -5354,47 +5371,47 @@
       <c r="AB34">
         <v>41</v>
       </c>
-      <c r="AC34">
+      <c r="AC34" s="20">
         <v>2</v>
       </c>
       <c r="AD34" s="20">
         <v>43</v>
       </c>
       <c r="AE34">
-        <v>128.66666666666671</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="AF34">
-        <v>11.796296296296299</v>
+        <v>11.8</v>
       </c>
       <c r="AG34">
-        <v>11.796296296296299</v>
+        <v>11.8</v>
       </c>
       <c r="AH34">
-        <v>10.31111111111111</v>
+        <v>10.31</v>
       </c>
       <c r="AI34">
-        <v>0.86296296296296293</v>
+        <v>0.86</v>
       </c>
       <c r="AJ34">
-        <v>0.86296296296296293</v>
+        <v>0.86</v>
       </c>
       <c r="AK34">
-        <v>0.15185185185185179</v>
+        <v>0.15</v>
       </c>
       <c r="AL34">
-        <v>7.4074074074074077E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AM34">
-        <v>0.15925925925925929</v>
+        <v>0.16</v>
       </c>
       <c r="AN34">
-        <v>128.1592592592593</v>
+        <v>128.16</v>
       </c>
       <c r="AO34" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP34" s="12" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.35">
@@ -5408,16 +5425,16 @@
         <v>39</v>
       </c>
       <c r="D35">
-        <v>127.00580383590309</v>
+        <v>127.01</v>
       </c>
       <c r="E35" s="12">
         <v>38200519700</v>
       </c>
       <c r="F35">
-        <v>62</v>
-      </c>
-      <c r="G35" s="29">
-        <v>23</v>
+        <v>74</v>
+      </c>
+      <c r="G35" s="24">
+        <v>27.41</v>
       </c>
       <c r="H35">
         <v>40759</v>
@@ -5426,40 +5443,40 @@
         <v>3357</v>
       </c>
       <c r="J35" t="s">
-        <v>130</v>
-      </c>
-      <c r="K35" s="28">
-        <v>34.799999999999997</v>
+        <v>142</v>
+      </c>
+      <c r="K35" s="24">
+        <v>34.81</v>
       </c>
       <c r="L35" t="s">
-        <v>103</v>
-      </c>
-      <c r="M35" s="28">
-        <v>64.400000000000006</v>
+        <v>104</v>
+      </c>
+      <c r="M35" s="24">
+        <v>64.44</v>
       </c>
       <c r="N35" t="s">
-        <v>88</v>
-      </c>
-      <c r="O35" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="O35" s="24">
+        <v>19.63</v>
       </c>
       <c r="P35" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q35" s="28">
-        <v>17</v>
+        <v>140</v>
+      </c>
+      <c r="Q35" s="24">
+        <v>17.04</v>
       </c>
       <c r="R35" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="S35" s="14">
         <v>96.3</v>
       </c>
       <c r="T35" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="U35" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="V35">
         <v>34793</v>
@@ -5482,47 +5499,47 @@
       <c r="AB35">
         <v>39</v>
       </c>
-      <c r="AC35" s="20">
+      <c r="AC35">
         <v>4</v>
       </c>
       <c r="AD35" s="20">
         <v>43</v>
       </c>
       <c r="AE35">
-        <v>128.862962962963</v>
+        <v>128.86000000000001</v>
       </c>
       <c r="AF35">
-        <v>11.63703703703704</v>
+        <v>11.64</v>
       </c>
       <c r="AG35">
-        <v>11.63703703703704</v>
+        <v>11.64</v>
       </c>
       <c r="AH35">
         <v>10.3</v>
       </c>
       <c r="AI35">
-        <v>0.78148148148148144</v>
+        <v>0.78</v>
       </c>
       <c r="AJ35">
-        <v>0.78148148148148144</v>
+        <v>0.78</v>
       </c>
       <c r="AK35">
-        <v>0.1444444444444444</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL35">
-        <v>1.4814814814814821E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM35" s="20">
-        <v>0.15925925925925929</v>
+        <v>0.16</v>
       </c>
       <c r="AN35">
-        <v>128.39259259259259</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AO35" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP35" s="12" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.35">
@@ -5535,17 +5552,17 @@
       <c r="C36" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="20">
-        <v>130.87595363831099</v>
+      <c r="D36">
+        <v>130.88</v>
       </c>
       <c r="E36" s="12">
         <v>43674962700</v>
       </c>
       <c r="F36">
-        <v>67</v>
-      </c>
-      <c r="G36" s="29">
-        <v>24.8</v>
+        <v>80</v>
+      </c>
+      <c r="G36" s="24">
+        <v>29.63</v>
       </c>
       <c r="H36">
         <v>40755</v>
@@ -5554,40 +5571,40 @@
         <v>3426</v>
       </c>
       <c r="J36" t="s">
-        <v>106</v>
-      </c>
-      <c r="K36" s="28">
-        <v>33</v>
+        <v>144</v>
+      </c>
+      <c r="K36" s="24">
+        <v>32.96</v>
       </c>
       <c r="L36" t="s">
-        <v>121</v>
-      </c>
-      <c r="M36" s="28">
-        <v>65.900000000000006</v>
+        <v>41</v>
+      </c>
+      <c r="M36" s="24">
+        <v>65.930000000000007</v>
       </c>
       <c r="N36" t="s">
-        <v>50</v>
-      </c>
-      <c r="O36" s="28">
-        <v>21.5</v>
+        <v>43</v>
+      </c>
+      <c r="O36" s="24">
+        <v>21.48</v>
       </c>
       <c r="P36" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q36" s="28">
+        <v>145</v>
+      </c>
+      <c r="Q36" s="24">
         <v>16.3</v>
       </c>
       <c r="R36" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="S36" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="T36" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="U36" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="V36">
         <v>34723</v>
@@ -5617,40 +5634,40 @@
         <v>46</v>
       </c>
       <c r="AE36">
-        <v>128.6037037037037</v>
+        <v>128.6</v>
       </c>
       <c r="AF36">
-        <v>11.851851851851849</v>
+        <v>11.85</v>
       </c>
       <c r="AG36">
-        <v>11.851851851851849</v>
+        <v>11.85</v>
       </c>
       <c r="AH36">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI36">
-        <v>0.81111111111111112</v>
+        <v>0.81</v>
       </c>
       <c r="AJ36">
-        <v>0.81111111111111112</v>
+        <v>0.81</v>
       </c>
       <c r="AK36">
-        <v>0.1444444444444444</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL36">
-        <v>2.5925925925925929E-2</v>
-      </c>
-      <c r="AM36" s="20">
-        <v>0.17037037037037039</v>
+        <v>0.03</v>
+      </c>
+      <c r="AM36">
+        <v>0.17</v>
       </c>
       <c r="AN36">
-        <v>128.137037037037</v>
+        <v>128.13999999999999</v>
       </c>
       <c r="AO36" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP36" s="12" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.35">
@@ -5663,17 +5680,17 @@
       <c r="C37" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="20">
-        <v>126.93712022341479</v>
+      <c r="D37">
+        <v>126.94</v>
       </c>
       <c r="E37" s="12">
         <v>38080818300</v>
       </c>
       <c r="F37">
-        <v>79</v>
-      </c>
-      <c r="G37" s="35">
-        <v>29.3</v>
+        <v>96</v>
+      </c>
+      <c r="G37" s="27">
+        <v>35.56</v>
       </c>
       <c r="H37">
         <v>40684</v>
@@ -5682,40 +5699,40 @@
         <v>3338</v>
       </c>
       <c r="J37" t="s">
-        <v>48</v>
-      </c>
-      <c r="K37" s="28">
-        <v>32.6</v>
+        <v>147</v>
+      </c>
+      <c r="K37" s="24">
+        <v>32.590000000000003</v>
       </c>
       <c r="L37" t="s">
-        <v>49</v>
-      </c>
-      <c r="M37" s="28">
-        <v>64.8</v>
+        <v>148</v>
+      </c>
+      <c r="M37" s="24">
+        <v>64.81</v>
       </c>
       <c r="N37" t="s">
-        <v>50</v>
-      </c>
-      <c r="O37" s="28">
-        <v>21.5</v>
+        <v>43</v>
+      </c>
+      <c r="O37" s="24">
+        <v>21.48</v>
       </c>
       <c r="P37" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q37" s="28">
+        <v>145</v>
+      </c>
+      <c r="Q37" s="24">
         <v>16.3</v>
       </c>
       <c r="R37" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S37" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T37" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="U37" s="20">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="V37">
         <v>34728</v>
@@ -5738,47 +5755,47 @@
       <c r="AB37">
         <v>37</v>
       </c>
-      <c r="AC37" s="20">
+      <c r="AC37">
         <v>4</v>
       </c>
       <c r="AD37" s="20">
         <v>41</v>
       </c>
       <c r="AE37">
-        <v>128.62222222222221</v>
+        <v>128.62</v>
       </c>
       <c r="AF37">
-        <v>11.514814814814811</v>
+        <v>11.51</v>
       </c>
       <c r="AG37">
-        <v>11.514814814814811</v>
+        <v>11.51</v>
       </c>
       <c r="AH37">
-        <v>10.392592592592591</v>
+        <v>10.39</v>
       </c>
       <c r="AI37">
-        <v>0.83333333333333337</v>
+        <v>0.83</v>
       </c>
       <c r="AJ37">
-        <v>0.83333333333333337</v>
+        <v>0.83</v>
       </c>
       <c r="AK37">
-        <v>0.13703703703703701</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL37">
-        <v>1.4814814814814821E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM37" s="20">
-        <v>0.15185185185185179</v>
+        <v>0.15</v>
       </c>
       <c r="AN37">
-        <v>128.38518518518521</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AO37" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP37" s="12" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.35">
@@ -5791,17 +5808,17 @@
       <c r="C38" t="s">
         <v>39</v>
       </c>
-      <c r="D38">
-        <v>129.1463196747809</v>
+      <c r="D38" s="20">
+        <v>129.15</v>
       </c>
       <c r="E38" s="12">
         <v>41203948100</v>
       </c>
       <c r="F38">
-        <v>72</v>
-      </c>
-      <c r="G38" s="36">
-        <v>26.7</v>
+        <v>85</v>
+      </c>
+      <c r="G38" s="26">
+        <v>31.48</v>
       </c>
       <c r="H38">
         <v>40700</v>
@@ -5810,40 +5827,40 @@
         <v>3369</v>
       </c>
       <c r="J38" t="s">
-        <v>86</v>
-      </c>
-      <c r="K38" s="34">
-        <v>29.3</v>
+        <v>150</v>
+      </c>
+      <c r="K38" s="26">
+        <v>29.26</v>
       </c>
       <c r="L38" t="s">
-        <v>87</v>
-      </c>
-      <c r="M38" s="28">
-        <v>69.3</v>
+        <v>53</v>
+      </c>
+      <c r="M38" s="24">
+        <v>69.260000000000005</v>
       </c>
       <c r="N38" t="s">
-        <v>88</v>
-      </c>
-      <c r="O38" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="O38" s="24">
+        <v>19.63</v>
       </c>
       <c r="P38" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q38" s="28">
-        <v>15.9</v>
+        <v>151</v>
+      </c>
+      <c r="Q38" s="24">
+        <v>15.93</v>
       </c>
       <c r="R38" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="S38" s="13">
         <v>100</v>
       </c>
       <c r="T38" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="U38" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="V38">
         <v>34731</v>
@@ -5866,47 +5883,47 @@
       <c r="AB38">
         <v>39</v>
       </c>
-      <c r="AC38">
+      <c r="AC38" s="20">
         <v>4</v>
       </c>
-      <c r="AD38">
+      <c r="AD38" s="20">
         <v>43</v>
       </c>
       <c r="AE38">
-        <v>128.6333333333333</v>
+        <v>128.63</v>
       </c>
       <c r="AF38">
-        <v>11.614814814814819</v>
+        <v>11.61</v>
       </c>
       <c r="AG38">
-        <v>11.614814814814819</v>
+        <v>11.61</v>
       </c>
       <c r="AH38">
-        <v>10.33333333333333</v>
+        <v>10.33</v>
       </c>
       <c r="AI38">
-        <v>0.8481481481481481</v>
+        <v>0.85</v>
       </c>
       <c r="AJ38">
-        <v>0.8481481481481481</v>
+        <v>0.85</v>
       </c>
       <c r="AK38">
-        <v>0.1444444444444444</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL38">
-        <v>1.4814814814814821E-2</v>
-      </c>
-      <c r="AM38">
-        <v>0.15925925925925929</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM38" s="20">
+        <v>0.16</v>
       </c>
       <c r="AN38">
-        <v>128.27037037037039</v>
+        <v>128.27000000000001</v>
       </c>
       <c r="AO38" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP38" s="12" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.35">
@@ -5920,16 +5937,16 @@
         <v>39</v>
       </c>
       <c r="D39" s="20">
-        <v>124.2354350626338</v>
+        <v>124.24</v>
       </c>
       <c r="E39" s="12">
         <v>34261464900</v>
       </c>
       <c r="F39">
-        <v>83</v>
-      </c>
-      <c r="G39" s="35">
-        <v>30.7</v>
+        <v>104</v>
+      </c>
+      <c r="G39" s="27">
+        <v>38.520000000000003</v>
       </c>
       <c r="H39">
         <v>40635</v>
@@ -5938,40 +5955,40 @@
         <v>3414</v>
       </c>
       <c r="J39" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="28">
-        <v>35.6</v>
+        <v>153</v>
+      </c>
+      <c r="K39" s="24">
+        <v>35.56</v>
       </c>
       <c r="L39" t="s">
-        <v>41</v>
-      </c>
-      <c r="M39" s="28">
-        <v>63.3</v>
+        <v>154</v>
+      </c>
+      <c r="M39" s="24">
+        <v>63.33</v>
       </c>
       <c r="N39" t="s">
-        <v>42</v>
-      </c>
-      <c r="O39" s="28">
-        <v>22.6</v>
+        <v>123</v>
+      </c>
+      <c r="O39" s="24">
+        <v>22.59</v>
       </c>
       <c r="P39" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q39" s="28">
-        <v>15.6</v>
+        <v>155</v>
+      </c>
+      <c r="Q39" s="24">
+        <v>15.56</v>
       </c>
       <c r="R39" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S39" s="20">
-        <v>81.5</v>
+        <v>81.48</v>
       </c>
       <c r="T39" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="U39" s="20">
-        <v>70.400000000000006</v>
+        <v>70.37</v>
       </c>
       <c r="V39">
         <v>34581</v>
@@ -6001,40 +6018,40 @@
         <v>39</v>
       </c>
       <c r="AE39">
-        <v>128.07777777777781</v>
+        <v>128.08000000000001</v>
       </c>
       <c r="AF39">
-        <v>11.851851851851849</v>
+        <v>11.85</v>
       </c>
       <c r="AG39">
-        <v>11.851851851851849</v>
+        <v>11.85</v>
       </c>
       <c r="AH39">
-        <v>10.425925925925929</v>
+        <v>10.43</v>
       </c>
       <c r="AI39">
-        <v>0.78888888888888886</v>
+        <v>0.79</v>
       </c>
       <c r="AJ39">
-        <v>0.78888888888888886</v>
+        <v>0.79</v>
       </c>
       <c r="AK39">
-        <v>0.14074074074074069</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL39">
-        <v>3.7037037037037038E-3</v>
+        <v>0</v>
       </c>
       <c r="AM39" s="20">
-        <v>0.1444444444444444</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN39">
-        <v>128.1037037037037</v>
+        <v>128.1</v>
       </c>
       <c r="AO39" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP39" s="12" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.35">
@@ -6047,17 +6064,17 @@
       <c r="C40" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="20">
-        <v>124.87318254119739</v>
+      <c r="D40">
+        <v>124.87</v>
       </c>
       <c r="E40" s="12">
         <v>35183862900</v>
       </c>
       <c r="F40">
-        <v>68</v>
-      </c>
-      <c r="G40" s="29">
-        <v>25.2</v>
+        <v>83</v>
+      </c>
+      <c r="G40" s="24">
+        <v>30.74</v>
       </c>
       <c r="H40">
         <v>40718</v>
@@ -6066,40 +6083,40 @@
         <v>3381</v>
       </c>
       <c r="J40" t="s">
-        <v>66</v>
-      </c>
-      <c r="K40" s="28">
-        <v>37</v>
+        <v>95</v>
+      </c>
+      <c r="K40" s="24">
+        <v>37.04</v>
       </c>
       <c r="L40" t="s">
-        <v>113</v>
-      </c>
-      <c r="M40" s="28">
-        <v>62.6</v>
+        <v>158</v>
+      </c>
+      <c r="M40" s="24">
+        <v>62.59</v>
       </c>
       <c r="N40" t="s">
-        <v>88</v>
-      </c>
-      <c r="O40" s="28">
-        <v>19.600000000000001</v>
+        <v>97</v>
+      </c>
+      <c r="O40" s="24">
+        <v>19.63</v>
       </c>
       <c r="P40" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q40" s="28">
-        <v>15.6</v>
+        <v>155</v>
+      </c>
+      <c r="Q40" s="24">
+        <v>15.56</v>
       </c>
       <c r="R40" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S40" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T40" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="U40" s="20">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="V40">
         <v>34731</v>
@@ -6122,47 +6139,47 @@
       <c r="AB40">
         <v>35</v>
       </c>
-      <c r="AC40" s="20">
+      <c r="AC40">
         <v>5</v>
       </c>
       <c r="AD40" s="20">
         <v>40</v>
       </c>
       <c r="AE40">
-        <v>128.6333333333333</v>
+        <v>128.63</v>
       </c>
       <c r="AF40">
-        <v>11.707407407407411</v>
+        <v>11.71</v>
       </c>
       <c r="AG40">
-        <v>11.707407407407411</v>
+        <v>11.71</v>
       </c>
       <c r="AH40">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI40">
-        <v>0.79629629629629628</v>
+        <v>0.8</v>
       </c>
       <c r="AJ40">
-        <v>0.79629629629629628</v>
+        <v>0.8</v>
       </c>
       <c r="AK40">
-        <v>0.12962962962962959</v>
+        <v>0.13</v>
       </c>
       <c r="AL40">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="AM40" s="20">
-        <v>0.14814814814814811</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM40">
+        <v>0.15</v>
       </c>
       <c r="AN40">
-        <v>128.30370370370369</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="AO40" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP40" s="12" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.35">
@@ -6175,17 +6192,17 @@
       <c r="C41" t="s">
         <v>39</v>
       </c>
-      <c r="D41">
-        <v>124.11728883145069</v>
+      <c r="D41" s="20">
+        <v>124.12</v>
       </c>
       <c r="E41" s="12">
         <v>34094442400</v>
       </c>
       <c r="F41">
-        <v>73</v>
-      </c>
-      <c r="G41" s="35">
-        <v>27</v>
+        <v>87</v>
+      </c>
+      <c r="G41" s="26">
+        <v>32.22</v>
       </c>
       <c r="H41">
         <v>40671</v>
@@ -6194,40 +6211,40 @@
         <v>3419</v>
       </c>
       <c r="J41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K41" s="28">
-        <v>31.9</v>
+        <v>128</v>
+      </c>
+      <c r="K41" s="24">
+        <v>31.85</v>
       </c>
       <c r="L41" t="s">
-        <v>77</v>
-      </c>
-      <c r="M41" s="28">
-        <v>65.599999999999994</v>
+        <v>65</v>
+      </c>
+      <c r="M41" s="24">
+        <v>65.56</v>
       </c>
       <c r="N41" t="s">
-        <v>78</v>
-      </c>
-      <c r="O41" s="28">
-        <v>18.899999999999999</v>
+        <v>160</v>
+      </c>
+      <c r="O41" s="24">
+        <v>18.89</v>
       </c>
       <c r="P41" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q41" s="28">
-        <v>15.2</v>
+        <v>161</v>
+      </c>
+      <c r="Q41" s="24">
+        <v>15.19</v>
       </c>
       <c r="R41" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="S41" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="T41" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="U41" s="15">
-        <v>92.6</v>
+        <v>92.59</v>
       </c>
       <c r="V41">
         <v>34646</v>
@@ -6257,40 +6274,40 @@
         <v>38</v>
       </c>
       <c r="AE41">
-        <v>128.31851851851849</v>
+        <v>128.32</v>
       </c>
       <c r="AF41">
-        <v>11.84074074074074</v>
+        <v>11.84</v>
       </c>
       <c r="AG41">
-        <v>11.84074074074074</v>
+        <v>11.84</v>
       </c>
       <c r="AH41">
-        <v>10.33333333333333</v>
+        <v>10.33</v>
       </c>
       <c r="AI41">
-        <v>0.82222222222222219</v>
+        <v>0.82</v>
       </c>
       <c r="AJ41">
-        <v>0.82222222222222219</v>
+        <v>0.82</v>
       </c>
       <c r="AK41">
-        <v>0.14074074074074069</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
-      <c r="AM41">
-        <v>0.14074074074074069</v>
+      <c r="AM41" s="20">
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN41">
-        <v>128.0851851851852</v>
+        <v>128.09</v>
       </c>
       <c r="AO41" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP41" s="12" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.35">
@@ -6303,17 +6320,17 @@
       <c r="C42" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="20">
-        <v>122.5885974536197</v>
+      <c r="D42">
+        <v>122.59</v>
       </c>
       <c r="E42" s="12">
         <v>31933342100</v>
       </c>
       <c r="F42">
-        <v>68</v>
-      </c>
-      <c r="G42" s="29">
-        <v>25.2</v>
+        <v>84</v>
+      </c>
+      <c r="G42" s="26">
+        <v>31.11</v>
       </c>
       <c r="H42">
         <v>40700</v>
@@ -6322,40 +6339,40 @@
         <v>3338</v>
       </c>
       <c r="J42" t="s">
-        <v>118</v>
-      </c>
-      <c r="K42" s="28">
-        <v>37.4</v>
+        <v>163</v>
+      </c>
+      <c r="K42" s="24">
+        <v>37.409999999999997</v>
       </c>
       <c r="L42" t="s">
-        <v>119</v>
-      </c>
-      <c r="M42" s="28">
-        <v>60.7</v>
+        <v>164</v>
+      </c>
+      <c r="M42" s="24">
+        <v>60.74</v>
       </c>
       <c r="N42" t="s">
-        <v>78</v>
-      </c>
-      <c r="O42" s="28">
-        <v>18.899999999999999</v>
+        <v>160</v>
+      </c>
+      <c r="O42" s="24">
+        <v>18.89</v>
       </c>
       <c r="P42" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q42" s="28">
-        <v>15.2</v>
+        <v>161</v>
+      </c>
+      <c r="Q42" s="24">
+        <v>15.19</v>
       </c>
       <c r="R42" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S42" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T42" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="U42" s="20">
-        <v>81.5</v>
+        <v>81.48</v>
       </c>
       <c r="V42">
         <v>34741</v>
@@ -6385,7 +6402,7 @@
         <v>39</v>
       </c>
       <c r="AE42">
-        <v>128.67037037037039</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="AF42">
         <v>11.6</v>
@@ -6394,31 +6411,31 @@
         <v>11.6</v>
       </c>
       <c r="AH42">
-        <v>10.32592592592593</v>
+        <v>10.33</v>
       </c>
       <c r="AI42">
-        <v>0.75185185185185188</v>
+        <v>0.75</v>
       </c>
       <c r="AJ42">
-        <v>0.75185185185185188</v>
+        <v>0.75</v>
       </c>
       <c r="AK42">
-        <v>0.1333333333333333</v>
+        <v>0.13</v>
       </c>
       <c r="AL42">
-        <v>1.111111111111111E-2</v>
+        <v>0.01</v>
       </c>
       <c r="AM42" s="20">
-        <v>0.1444444444444444</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN42">
-        <v>128.38518518518521</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AO42" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP42" s="12" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.35">
@@ -6431,17 +6448,17 @@
       <c r="C43" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="20">
-        <v>126.5481083469421</v>
+      <c r="D43">
+        <v>126.55</v>
       </c>
       <c r="E43" s="12">
         <v>37553095700</v>
       </c>
       <c r="F43">
-        <v>71</v>
-      </c>
-      <c r="G43" s="36">
-        <v>26.3</v>
+        <v>81</v>
+      </c>
+      <c r="G43" s="34">
+        <v>30</v>
       </c>
       <c r="H43">
         <v>40737</v>
@@ -6450,40 +6467,40 @@
         <v>3458</v>
       </c>
       <c r="J43" t="s">
-        <v>106</v>
-      </c>
-      <c r="K43" s="28">
-        <v>33</v>
+        <v>144</v>
+      </c>
+      <c r="K43" s="24">
+        <v>32.96</v>
       </c>
       <c r="L43" t="s">
-        <v>77</v>
-      </c>
-      <c r="M43" s="28">
-        <v>65.599999999999994</v>
+        <v>65</v>
+      </c>
+      <c r="M43" s="24">
+        <v>65.56</v>
       </c>
       <c r="N43" t="s">
-        <v>73</v>
-      </c>
-      <c r="O43" s="28">
+        <v>87</v>
+      </c>
+      <c r="O43" s="24">
         <v>20</v>
       </c>
       <c r="P43" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q43" s="28">
-        <v>14.8</v>
+        <v>166</v>
+      </c>
+      <c r="Q43" s="24">
+        <v>14.81</v>
       </c>
       <c r="R43" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S43" s="20">
-        <v>81.5</v>
+        <v>81.48</v>
       </c>
       <c r="T43" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="U43" s="20">
-        <v>74.099999999999994</v>
+        <v>74.069999999999993</v>
       </c>
       <c r="V43">
         <v>34673</v>
@@ -6513,45 +6530,45 @@
         <v>41</v>
       </c>
       <c r="AE43">
-        <v>128.41851851851851</v>
+        <v>128.41999999999999</v>
       </c>
       <c r="AF43">
-        <v>11.988888888888891</v>
+        <v>11.99</v>
       </c>
       <c r="AG43">
-        <v>11.988888888888891</v>
+        <v>11.99</v>
       </c>
       <c r="AH43">
-        <v>10.31851851851852</v>
+        <v>10.32</v>
       </c>
       <c r="AI43">
-        <v>0.81111111111111112</v>
+        <v>0.81</v>
       </c>
       <c r="AJ43">
-        <v>0.81111111111111112</v>
+        <v>0.81</v>
       </c>
       <c r="AK43">
-        <v>0.1444444444444444</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL43">
-        <v>7.4074074074074077E-3</v>
-      </c>
-      <c r="AM43" s="20">
-        <v>0.15185185185185179</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM43">
+        <v>0.15</v>
       </c>
       <c r="AN43">
-        <v>128.0185185185185</v>
+        <v>128.02000000000001</v>
       </c>
       <c r="AO43" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AP43" s="12" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
         <v>38</v>
@@ -6559,127 +6576,127 @@
       <c r="C44" t="s">
         <v>39</v>
       </c>
-      <c r="D44" s="20">
-        <v>123.5907913528609</v>
+      <c r="D44">
+        <v>119.58</v>
       </c>
       <c r="E44" s="12">
-        <v>33350136600</v>
+        <v>27678827000</v>
       </c>
       <c r="F44">
-        <v>71</v>
-      </c>
-      <c r="G44" s="36">
-        <v>26.3</v>
+        <v>76</v>
+      </c>
+      <c r="G44" s="24">
+        <v>28.15</v>
       </c>
       <c r="H44">
-        <v>40670</v>
+        <v>40686</v>
       </c>
       <c r="I44">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="J44" t="s">
-        <v>70</v>
-      </c>
-      <c r="K44" s="28">
-        <v>33.700000000000003</v>
+        <v>170</v>
+      </c>
+      <c r="K44" s="24">
+        <v>41.48</v>
       </c>
       <c r="L44" t="s">
-        <v>77</v>
-      </c>
-      <c r="M44" s="28">
-        <v>65.599999999999994</v>
+        <v>171</v>
+      </c>
+      <c r="M44" s="24">
+        <v>58.15</v>
       </c>
       <c r="N44" t="s">
+        <v>129</v>
+      </c>
+      <c r="O44" s="24">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="P44" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q44" s="24">
+        <v>14.07</v>
+      </c>
+      <c r="R44" t="s">
         <v>50</v>
       </c>
-      <c r="O44" s="28">
-        <v>21.5</v>
-      </c>
-      <c r="P44" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q44" s="28">
-        <v>14.1</v>
-      </c>
-      <c r="R44" t="s">
-        <v>80</v>
-      </c>
-      <c r="S44" s="15">
-        <v>92.6</v>
+      <c r="S44" s="20">
+        <v>81.48</v>
       </c>
       <c r="T44" t="s">
-        <v>45</v>
-      </c>
-      <c r="U44" s="20">
-        <v>70.400000000000006</v>
+        <v>172</v>
+      </c>
+      <c r="U44">
+        <v>66.67</v>
       </c>
       <c r="V44">
-        <v>34661</v>
+        <v>34659</v>
       </c>
       <c r="W44">
-        <v>3184</v>
+        <v>3209</v>
       </c>
       <c r="X44">
-        <v>37845</v>
+        <v>37868</v>
       </c>
       <c r="Y44">
-        <v>2414</v>
+        <v>2440</v>
       </c>
       <c r="Z44">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="AA44">
-        <v>2788</v>
+        <v>2782</v>
       </c>
       <c r="AB44">
-        <v>34</v>
-      </c>
-      <c r="AC44">
-        <v>3</v>
-      </c>
-      <c r="AD44" s="20">
-        <v>37</v>
+        <v>31</v>
+      </c>
+      <c r="AC44" s="20">
+        <v>5</v>
+      </c>
+      <c r="AD44">
+        <v>36</v>
       </c>
       <c r="AE44">
-        <v>128.37407407407409</v>
+        <v>128.37</v>
       </c>
       <c r="AF44">
-        <v>11.792592592592589</v>
+        <v>11.89</v>
       </c>
       <c r="AG44">
-        <v>11.792592592592589</v>
+        <v>11.89</v>
       </c>
       <c r="AH44">
-        <v>10.32592592592593</v>
+        <v>10.3</v>
       </c>
       <c r="AI44">
-        <v>0.83703703703703702</v>
+        <v>0.73</v>
       </c>
       <c r="AJ44">
-        <v>0.83703703703703702</v>
+        <v>0.73</v>
       </c>
       <c r="AK44">
-        <v>0.12592592592592591</v>
+        <v>0.11</v>
       </c>
       <c r="AL44">
-        <v>1.111111111111111E-2</v>
-      </c>
-      <c r="AM44" s="20">
-        <v>0.13703703703703701</v>
+        <v>0.02</v>
+      </c>
+      <c r="AM44">
+        <v>0.13</v>
       </c>
       <c r="AN44">
-        <v>128.10740740740741</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AO44" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP44" s="12" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
         <v>38</v>
@@ -6687,122 +6704,122 @@
       <c r="C45" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="20">
-        <v>119.57909319774519</v>
+      <c r="D45">
+        <v>123.59</v>
       </c>
       <c r="E45" s="12">
-        <v>27678827000</v>
+        <v>33350136600</v>
       </c>
       <c r="F45">
-        <v>57</v>
-      </c>
-      <c r="G45" s="29">
-        <v>21.1</v>
+        <v>81</v>
+      </c>
+      <c r="G45" s="34">
+        <v>30</v>
       </c>
       <c r="H45">
-        <v>40686</v>
+        <v>40670</v>
       </c>
       <c r="I45">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="J45" t="s">
-        <v>157</v>
-      </c>
-      <c r="K45" s="28">
-        <v>41.5</v>
+        <v>64</v>
+      </c>
+      <c r="K45" s="24">
+        <v>33.700000000000003</v>
       </c>
       <c r="L45" t="s">
-        <v>158</v>
-      </c>
-      <c r="M45" s="28">
-        <v>58.1</v>
+        <v>65</v>
+      </c>
+      <c r="M45" s="24">
+        <v>65.56</v>
       </c>
       <c r="N45" t="s">
-        <v>63</v>
-      </c>
-      <c r="O45" s="28">
-        <v>18.100000000000001</v>
+        <v>43</v>
+      </c>
+      <c r="O45" s="24">
+        <v>21.48</v>
       </c>
       <c r="P45" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q45" s="28">
-        <v>14.1</v>
+        <v>168</v>
+      </c>
+      <c r="Q45" s="24">
+        <v>14.07</v>
       </c>
       <c r="R45" t="s">
-        <v>44</v>
-      </c>
-      <c r="S45" s="20">
-        <v>81.5</v>
+        <v>45</v>
+      </c>
+      <c r="S45" s="15">
+        <v>92.59</v>
       </c>
       <c r="T45" t="s">
-        <v>159</v>
-      </c>
-      <c r="U45" s="20">
-        <v>66.7</v>
+        <v>156</v>
+      </c>
+      <c r="U45">
+        <v>70.37</v>
       </c>
       <c r="V45">
-        <v>34659</v>
+        <v>34661</v>
       </c>
       <c r="W45">
-        <v>3209</v>
+        <v>3184</v>
       </c>
       <c r="X45">
-        <v>37868</v>
+        <v>37845</v>
       </c>
       <c r="Y45">
-        <v>2440</v>
+        <v>2414</v>
       </c>
       <c r="Z45">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="AA45">
-        <v>2782</v>
+        <v>2788</v>
       </c>
       <c r="AB45">
-        <v>31</v>
-      </c>
-      <c r="AC45" s="20">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="AC45">
+        <v>3</v>
       </c>
       <c r="AD45" s="20">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE45">
-        <v>128.3666666666667</v>
+        <v>128.37</v>
       </c>
       <c r="AF45">
-        <v>11.885185185185181</v>
+        <v>11.79</v>
       </c>
       <c r="AG45">
-        <v>11.885185185185181</v>
+        <v>11.79</v>
       </c>
       <c r="AH45">
-        <v>10.3037037037037</v>
+        <v>10.33</v>
       </c>
       <c r="AI45">
-        <v>0.73333333333333328</v>
+        <v>0.84</v>
       </c>
       <c r="AJ45">
-        <v>0.73333333333333328</v>
+        <v>0.84</v>
       </c>
       <c r="AK45">
-        <v>0.1148148148148148</v>
+        <v>0.13</v>
       </c>
       <c r="AL45">
-        <v>1.8518518518518521E-2</v>
-      </c>
-      <c r="AM45" s="20">
-        <v>0.1333333333333333</v>
+        <v>0.01</v>
+      </c>
+      <c r="AM45">
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN45">
-        <v>128.11111111111109</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AO45" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP45" s="12" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.35">
@@ -6816,16 +6833,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="20">
-        <v>117.6183000128034</v>
+        <v>117.62</v>
       </c>
       <c r="E46" s="12">
         <v>24906867400</v>
       </c>
       <c r="F46">
-        <v>75</v>
-      </c>
-      <c r="G46" s="35">
-        <v>27.8</v>
+        <v>90</v>
+      </c>
+      <c r="G46" s="26">
+        <v>33.33</v>
       </c>
       <c r="H46">
         <v>40645</v>
@@ -6834,40 +6851,40 @@
         <v>3337</v>
       </c>
       <c r="J46" t="s">
-        <v>66</v>
-      </c>
-      <c r="K46" s="28">
-        <v>37</v>
+        <v>95</v>
+      </c>
+      <c r="K46" s="24">
+        <v>37.04</v>
       </c>
       <c r="L46" t="s">
-        <v>61</v>
-      </c>
-      <c r="M46" s="28">
-        <v>62.2</v>
+        <v>131</v>
+      </c>
+      <c r="M46" s="24">
+        <v>62.22</v>
       </c>
       <c r="N46" t="s">
-        <v>67</v>
-      </c>
-      <c r="O46" s="28">
-        <v>16.7</v>
+        <v>174</v>
+      </c>
+      <c r="O46" s="24">
+        <v>16.670000000000002</v>
       </c>
       <c r="P46" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q46" s="28">
-        <v>13</v>
+        <v>175</v>
+      </c>
+      <c r="Q46" s="24">
+        <v>12.96</v>
       </c>
       <c r="R46" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="S46" s="20">
-        <v>88.9</v>
+        <v>88.89</v>
       </c>
       <c r="T46" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="U46" s="20">
-        <v>77.8</v>
+        <v>77.78</v>
       </c>
       <c r="V46">
         <v>34677</v>
@@ -6890,54 +6907,54 @@
       <c r="AB46">
         <v>34</v>
       </c>
-      <c r="AC46" s="20">
+      <c r="AC46">
         <v>0</v>
       </c>
       <c r="AD46" s="20">
         <v>34</v>
       </c>
       <c r="AE46">
-        <v>128.43333333333331</v>
+        <v>128.43</v>
       </c>
       <c r="AF46">
-        <v>11.62592592592593</v>
+        <v>11.63</v>
       </c>
       <c r="AG46">
-        <v>11.62592592592593</v>
+        <v>11.63</v>
       </c>
       <c r="AH46">
-        <v>10.351851851851849</v>
+        <v>10.35</v>
       </c>
       <c r="AI46">
-        <v>0.73333333333333328</v>
+        <v>0.73</v>
       </c>
       <c r="AJ46">
-        <v>0.73333333333333328</v>
+        <v>0.73</v>
       </c>
       <c r="AK46">
-        <v>0.12592592592592591</v>
+        <v>0.13</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
-      <c r="AM46">
-        <v>0.12592592592592591</v>
+      <c r="AM46" s="20">
+        <v>0.13</v>
       </c>
       <c r="AN46">
-        <v>128.38888888888891</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AO46" s="12" t="s">
         <v>46</v>
       </c>
       <c r="AP46" s="12" t="s">
-        <v>69</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>55</v>
       </c>
-      <c r="Q47" s="28"/>
+      <c r="Q47" s="24"/>
     </row>
     <row r="48" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A48">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\535\daily1689\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFCFB36-0F7A-4343-AE87-6ADA04FCF20A}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C4D4F6-030D-443B-B6D9-BA5807154FDC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="780" windowWidth="27770" windowHeight="16860" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="780" windowWidth="28030" windowHeight="17250" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="131">
   <si>
     <t>CHU KỲ 10 KỲ</t>
   </si>
@@ -446,7 +446,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -622,7 +622,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -697,8 +697,12 @@
     <xf numFmtId="43" fontId="4" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="3" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="4" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -716,8 +720,6 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1028,39 +1030,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="42" t="s">
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="40" t="s">
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="38" t="s">
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="43" t="s">
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="39"/>
-      <c r="AO1" s="39"/>
-      <c r="AP1" s="39"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="43"/>
     </row>
     <row r="2" spans="1:45" s="2" customFormat="1" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -1200,7 +1202,7 @@
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.35">
-      <c r="A3" s="46">
+      <c r="A3" s="41">
         <v>57</v>
       </c>
       <c r="B3" t="s">
@@ -1293,7 +1295,7 @@
       <c r="AE3" s="27">
         <v>4</v>
       </c>
-      <c r="AF3" s="45">
+      <c r="AF3" s="40">
         <v>60</v>
       </c>
       <c r="AG3">
@@ -1339,7 +1341,7 @@
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" s="27">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
@@ -1347,47 +1349,47 @@
       <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="13">
-        <v>140.57</v>
-      </c>
-      <c r="E4" s="16">
-        <v>57348861100</v>
+      <c r="D4" s="38">
+        <v>137.6</v>
+      </c>
+      <c r="E4" s="12">
+        <v>53149326700</v>
       </c>
       <c r="F4">
-        <v>82</v>
-      </c>
-      <c r="G4" s="33">
+        <v>94</v>
+      </c>
+      <c r="G4" s="38">
+        <v>34.81</v>
+      </c>
+      <c r="H4">
+        <v>40738</v>
+      </c>
+      <c r="I4" s="27">
+        <v>3378</v>
+      </c>
+      <c r="J4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" s="14">
         <v>30.37</v>
       </c>
-      <c r="H4">
-        <v>40771</v>
-      </c>
-      <c r="I4" s="27">
-        <v>3410</v>
-      </c>
-      <c r="J4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K4" s="34">
-        <v>30</v>
-      </c>
       <c r="L4" t="s">
-        <v>72</v>
-      </c>
-      <c r="M4" s="31">
-        <v>69.260000000000005</v>
+        <v>111</v>
+      </c>
+      <c r="M4" s="38">
+        <v>67.41</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" s="35">
-        <v>38.15</v>
+        <v>124</v>
+      </c>
+      <c r="O4" s="13">
+        <v>39.26</v>
       </c>
       <c r="P4" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="Q4" s="13">
-        <v>38.15</v>
+        <v>39.26</v>
       </c>
       <c r="R4" t="s">
         <v>81</v>
@@ -1402,49 +1404,49 @@
         <v>96.3</v>
       </c>
       <c r="V4" t="s">
-        <v>63</v>
-      </c>
-      <c r="W4" s="14">
-        <v>96.3</v>
+        <v>47</v>
+      </c>
+      <c r="W4" s="29">
+        <v>92.59</v>
       </c>
       <c r="X4">
-        <v>34751</v>
+        <v>34743</v>
       </c>
       <c r="Y4">
-        <v>3173</v>
+        <v>3141</v>
       </c>
       <c r="Z4">
-        <v>37924</v>
+        <v>37884</v>
       </c>
       <c r="AA4">
-        <v>2339</v>
+        <v>2363</v>
       </c>
       <c r="AB4">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AC4">
-        <v>2792</v>
+        <v>2802</v>
       </c>
       <c r="AD4">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="AE4" s="27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF4" s="13">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AG4">
-        <v>128.71</v>
+        <v>128.68</v>
       </c>
       <c r="AH4">
-        <v>11.75</v>
+        <v>11.63</v>
       </c>
       <c r="AI4">
-        <v>11.75</v>
+        <v>11.63</v>
       </c>
       <c r="AJ4">
-        <v>10.34</v>
+        <v>10.38</v>
       </c>
       <c r="AK4">
         <v>0.86</v>
@@ -1453,169 +1455,169 @@
         <v>0.86</v>
       </c>
       <c r="AM4">
+        <v>0.17</v>
+      </c>
+      <c r="AN4">
+        <v>0.02</v>
+      </c>
+      <c r="AO4" s="38">
         <v>0.19</v>
       </c>
-      <c r="AN4">
-        <v>0.01</v>
-      </c>
-      <c r="AO4" s="13">
-        <v>0.2</v>
-      </c>
       <c r="AP4" s="27">
-        <v>128.11000000000001</v>
+        <v>128.24</v>
       </c>
       <c r="AQ4" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR4" s="16">
+      <c r="AR4" s="12">
+        <v>194518626700</v>
+      </c>
+      <c r="AS4" s="25" t="str">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v55.txt", "Click view")</f>
+        <v>Click view</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A5" s="38">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="13">
+        <v>140.57</v>
+      </c>
+      <c r="E5" s="16">
+        <v>57348861100</v>
+      </c>
+      <c r="F5">
+        <v>82</v>
+      </c>
+      <c r="G5" s="33">
+        <v>30.37</v>
+      </c>
+      <c r="H5">
+        <v>40771</v>
+      </c>
+      <c r="I5">
+        <v>3410</v>
+      </c>
+      <c r="J5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K5" s="34">
+        <v>30</v>
+      </c>
+      <c r="L5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="31">
+        <v>69.260000000000005</v>
+      </c>
+      <c r="N5" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="35">
+        <v>38.15</v>
+      </c>
+      <c r="P5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>38.15</v>
+      </c>
+      <c r="R5" t="s">
+        <v>81</v>
+      </c>
+      <c r="S5" s="35">
+        <v>21.11</v>
+      </c>
+      <c r="T5" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="14">
+        <v>96.3</v>
+      </c>
+      <c r="V5" t="s">
+        <v>63</v>
+      </c>
+      <c r="W5" s="14">
+        <v>96.3</v>
+      </c>
+      <c r="X5">
+        <v>34751</v>
+      </c>
+      <c r="Y5">
+        <v>3173</v>
+      </c>
+      <c r="Z5">
+        <v>37924</v>
+      </c>
+      <c r="AA5">
+        <v>2339</v>
+      </c>
+      <c r="AB5">
+        <v>233</v>
+      </c>
+      <c r="AC5">
+        <v>2792</v>
+      </c>
+      <c r="AD5">
+        <v>51</v>
+      </c>
+      <c r="AE5" s="38">
+        <v>4</v>
+      </c>
+      <c r="AF5" s="13">
+        <v>55</v>
+      </c>
+      <c r="AG5">
+        <v>128.71</v>
+      </c>
+      <c r="AH5">
+        <v>11.75</v>
+      </c>
+      <c r="AI5">
+        <v>11.75</v>
+      </c>
+      <c r="AJ5">
+        <v>10.34</v>
+      </c>
+      <c r="AK5" s="38">
+        <v>0.86</v>
+      </c>
+      <c r="AL5">
+        <v>0.86</v>
+      </c>
+      <c r="AM5">
+        <v>0.19</v>
+      </c>
+      <c r="AN5">
+        <v>0.01</v>
+      </c>
+      <c r="AO5" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="AP5">
+        <v>128.11000000000001</v>
+      </c>
+      <c r="AQ5" s="12">
+        <v>141369300000</v>
+      </c>
+      <c r="AR5" s="16">
         <v>198718161100</v>
       </c>
-      <c r="AS4" s="25" t="str">
+      <c r="AS5" s="25" t="str">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v46.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
-      <c r="A5" s="46">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A6" s="41">
         <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="13">
-        <v>139.97</v>
-      </c>
-      <c r="E5" s="16">
-        <v>56501222800</v>
-      </c>
-      <c r="F5">
-        <v>94</v>
-      </c>
-      <c r="G5" s="35">
-        <v>34.81</v>
-      </c>
-      <c r="H5">
-        <v>40738</v>
-      </c>
-      <c r="I5">
-        <v>3404</v>
-      </c>
-      <c r="J5" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="35">
-        <v>24.44</v>
-      </c>
-      <c r="L5" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" s="35">
-        <v>72.959999999999994</v>
-      </c>
-      <c r="N5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" s="35">
-        <v>38.15</v>
-      </c>
-      <c r="P5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>38.15</v>
-      </c>
-      <c r="R5" t="s">
-        <v>68</v>
-      </c>
-      <c r="S5" s="34">
-        <v>20.37</v>
-      </c>
-      <c r="T5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U5" s="29">
-        <v>92.59</v>
-      </c>
-      <c r="V5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W5" s="29">
-        <v>92.59</v>
-      </c>
-      <c r="X5">
-        <v>34741</v>
-      </c>
-      <c r="Y5">
-        <v>3143</v>
-      </c>
-      <c r="Z5">
-        <v>37884</v>
-      </c>
-      <c r="AA5">
-        <v>2342</v>
-      </c>
-      <c r="AB5">
-        <v>252</v>
-      </c>
-      <c r="AC5">
-        <v>2802</v>
-      </c>
-      <c r="AD5">
-        <v>43</v>
-      </c>
-      <c r="AE5" s="13">
-        <v>9</v>
-      </c>
-      <c r="AF5" s="13">
-        <v>52</v>
-      </c>
-      <c r="AG5">
-        <v>128.66999999999999</v>
-      </c>
-      <c r="AH5">
-        <v>11.64</v>
-      </c>
-      <c r="AI5">
-        <v>11.64</v>
-      </c>
-      <c r="AJ5">
-        <v>10.38</v>
-      </c>
-      <c r="AK5" s="13">
-        <v>0.93</v>
-      </c>
-      <c r="AL5">
-        <v>0.93</v>
-      </c>
-      <c r="AM5">
-        <v>0.16</v>
-      </c>
-      <c r="AN5">
-        <v>0.03</v>
-      </c>
-      <c r="AO5" s="27">
-        <v>0.19</v>
-      </c>
-      <c r="AP5">
-        <v>128.13999999999999</v>
-      </c>
-      <c r="AQ5" s="12">
-        <v>141369300000</v>
-      </c>
-      <c r="AR5" s="16">
-        <v>197870522800</v>
-      </c>
-      <c r="AS5" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v15.txt", "Click view")</f>
-        <v>Click view</v>
-      </c>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
-      <c r="A6" s="27">
-        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>41</v>
@@ -1624,58 +1626,58 @@
         <v>42</v>
       </c>
       <c r="D6" s="13">
-        <v>138.83000000000001</v>
+        <v>139.97</v>
       </c>
       <c r="E6" s="16">
-        <v>54891292100</v>
+        <v>56501222800</v>
       </c>
       <c r="F6">
-        <v>81</v>
-      </c>
-      <c r="G6" s="33">
-        <v>30</v>
+        <v>94</v>
+      </c>
+      <c r="G6" s="35">
+        <v>34.81</v>
       </c>
       <c r="H6">
-        <v>40801</v>
+        <v>40738</v>
       </c>
       <c r="I6">
-        <v>3423</v>
+        <v>3404</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="34">
-        <v>30.74</v>
+        <v>65</v>
+      </c>
+      <c r="K6" s="35">
+        <v>24.44</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="31">
-        <v>65.930000000000007</v>
+        <v>66</v>
+      </c>
+      <c r="M6" s="35">
+        <v>72.959999999999994</v>
       </c>
       <c r="N6" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="37">
-        <v>35.19</v>
+        <v>67</v>
+      </c>
+      <c r="O6" s="35">
+        <v>38.15</v>
       </c>
       <c r="P6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q6" s="27">
-        <v>35.19</v>
+        <v>67</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>38.15</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S6" s="35">
-        <v>21.48</v>
+        <v>68</v>
+      </c>
+      <c r="S6" s="34">
+        <v>20.37</v>
       </c>
       <c r="T6" t="s">
-        <v>70</v>
-      </c>
-      <c r="U6" s="13">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="U6" s="29">
+        <v>92.59</v>
       </c>
       <c r="V6" t="s">
         <v>47</v>
@@ -1684,76 +1686,76 @@
         <v>92.59</v>
       </c>
       <c r="X6">
-        <v>34759</v>
+        <v>34741</v>
       </c>
       <c r="Y6">
-        <v>3201</v>
+        <v>3143</v>
       </c>
       <c r="Z6">
-        <v>37960</v>
+        <v>37884</v>
       </c>
       <c r="AA6">
-        <v>2349</v>
+        <v>2342</v>
       </c>
       <c r="AB6">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="AC6">
-        <v>2786</v>
+        <v>2802</v>
       </c>
       <c r="AD6">
-        <v>50</v>
-      </c>
-      <c r="AE6" s="27">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="AE6" s="13">
+        <v>9</v>
       </c>
       <c r="AF6" s="13">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AG6">
-        <v>128.74</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="AH6">
-        <v>11.86</v>
+        <v>11.64</v>
       </c>
       <c r="AI6">
-        <v>11.86</v>
+        <v>11.64</v>
       </c>
       <c r="AJ6">
-        <v>10.32</v>
-      </c>
-      <c r="AK6" s="27">
-        <v>0.8</v>
+        <v>10.38</v>
+      </c>
+      <c r="AK6" s="13">
+        <v>0.93</v>
       </c>
       <c r="AL6">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AM6">
+        <v>0.16</v>
+      </c>
+      <c r="AN6">
+        <v>0.03</v>
+      </c>
+      <c r="AO6" s="38">
         <v>0.19</v>
       </c>
-      <c r="AN6">
-        <v>0.02</v>
-      </c>
-      <c r="AO6" s="13">
-        <v>0.2</v>
-      </c>
       <c r="AP6">
-        <v>128.07</v>
+        <v>128.13999999999999</v>
       </c>
       <c r="AQ6" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR6" s="16">
-        <v>196260592100</v>
+        <v>197870522800</v>
       </c>
       <c r="AS6" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v16.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v15.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -1761,104 +1763,104 @@
       <c r="C7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="13">
-        <v>138.61000000000001</v>
-      </c>
-      <c r="E7" s="16">
-        <v>54578818400</v>
+      <c r="D7" s="38">
+        <v>137.41</v>
+      </c>
+      <c r="E7" s="22">
+        <v>52880731500</v>
       </c>
       <c r="F7">
-        <v>81</v>
-      </c>
-      <c r="G7" s="33">
+        <v>94</v>
+      </c>
+      <c r="G7" s="35">
+        <v>34.81</v>
+      </c>
+      <c r="H7">
+        <v>40738</v>
+      </c>
+      <c r="I7">
+        <v>3383</v>
+      </c>
+      <c r="J7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" s="34">
         <v>30</v>
       </c>
-      <c r="H7">
-        <v>40780</v>
-      </c>
-      <c r="I7">
-        <v>3454</v>
-      </c>
-      <c r="J7" t="s">
-        <v>117</v>
-      </c>
-      <c r="K7" s="35">
-        <v>25.93</v>
-      </c>
       <c r="L7" t="s">
-        <v>118</v>
-      </c>
-      <c r="M7" s="35">
-        <v>72.59</v>
+        <v>112</v>
+      </c>
+      <c r="M7" s="31">
+        <v>68.89</v>
       </c>
       <c r="N7" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="O7" s="34">
-        <v>36.67</v>
+        <v>37.409999999999997</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7" s="30">
-        <v>36.67</v>
+        <v>77</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>37.409999999999997</v>
       </c>
       <c r="R7" t="s">
-        <v>68</v>
-      </c>
-      <c r="S7" s="34">
-        <v>20.37</v>
+        <v>57</v>
+      </c>
+      <c r="S7" s="36">
+        <v>19.63</v>
       </c>
       <c r="T7" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" s="14">
+        <v>96.3</v>
+      </c>
+      <c r="V7" t="s">
         <v>53</v>
       </c>
-      <c r="U7" s="27">
+      <c r="W7" s="27">
         <v>88.89</v>
       </c>
-      <c r="V7" t="s">
-        <v>48</v>
-      </c>
-      <c r="W7" s="27">
-        <v>81.48</v>
-      </c>
       <c r="X7">
-        <v>34717</v>
+        <v>34735</v>
       </c>
       <c r="Y7">
-        <v>3222</v>
+        <v>3149</v>
       </c>
       <c r="Z7">
-        <v>37939</v>
+        <v>37884</v>
       </c>
       <c r="AA7">
-        <v>2346</v>
+        <v>2365</v>
       </c>
       <c r="AB7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AC7">
-        <v>2788</v>
+        <v>2802</v>
       </c>
       <c r="AD7">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AE7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF7" s="13">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AG7">
-        <v>128.58000000000001</v>
+        <v>128.65</v>
       </c>
       <c r="AH7">
-        <v>11.93</v>
+        <v>11.66</v>
       </c>
       <c r="AI7">
-        <v>11.93</v>
+        <v>11.66</v>
       </c>
       <c r="AJ7">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="AK7">
         <v>0.85</v>
@@ -1867,31 +1869,31 @@
         <v>0.85</v>
       </c>
       <c r="AM7">
+        <v>0.17</v>
+      </c>
+      <c r="AN7">
+        <v>0.02</v>
+      </c>
+      <c r="AO7" s="38">
         <v>0.19</v>
       </c>
-      <c r="AN7">
-        <v>0.01</v>
-      </c>
-      <c r="AO7" s="13">
-        <v>0.2</v>
-      </c>
       <c r="AP7">
-        <v>128</v>
+        <v>128.22999999999999</v>
       </c>
       <c r="AQ7" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR7" s="16">
-        <v>195948118400</v>
+      <c r="AR7" s="12">
+        <v>194250031500</v>
       </c>
       <c r="AS7" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v48.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v41.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
@@ -1899,23 +1901,23 @@
       <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="13">
-        <v>138.19999999999999</v>
-      </c>
-      <c r="E8" s="16">
-        <v>54002546000</v>
+      <c r="D8" s="38">
+        <v>136.96</v>
+      </c>
+      <c r="E8" s="22">
+        <v>52252970800</v>
       </c>
       <c r="F8">
-        <v>82</v>
-      </c>
-      <c r="G8" s="31">
-        <v>30.37</v>
+        <v>94</v>
+      </c>
+      <c r="G8" s="35">
+        <v>34.81</v>
       </c>
       <c r="H8">
-        <v>40771</v>
+        <v>40738</v>
       </c>
       <c r="I8">
-        <v>3393</v>
+        <v>3461</v>
       </c>
       <c r="J8" t="s">
         <v>91</v>
@@ -1924,28 +1926,28 @@
         <v>31.11</v>
       </c>
       <c r="L8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M8" s="31">
-        <v>66.67</v>
+        <v>67.41</v>
       </c>
       <c r="N8" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="O8" s="34">
-        <v>36.67</v>
+        <v>37.409999999999997</v>
       </c>
       <c r="P8" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8" s="30">
-        <v>36.67</v>
+        <v>77</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>37.409999999999997</v>
       </c>
       <c r="R8" t="s">
-        <v>81</v>
-      </c>
-      <c r="S8" s="35">
-        <v>21.11</v>
+        <v>68</v>
+      </c>
+      <c r="S8" s="34">
+        <v>20.37</v>
       </c>
       <c r="T8" t="s">
         <v>70</v>
@@ -1954,82 +1956,82 @@
         <v>100</v>
       </c>
       <c r="V8" t="s">
-        <v>63</v>
-      </c>
-      <c r="W8" s="14">
-        <v>96.3</v>
+        <v>53</v>
+      </c>
+      <c r="W8" s="38">
+        <v>88.89</v>
       </c>
       <c r="X8">
-        <v>34749</v>
+        <v>34650</v>
       </c>
       <c r="Y8">
-        <v>3175</v>
+        <v>3234</v>
       </c>
       <c r="Z8">
-        <v>37924</v>
+        <v>37884</v>
       </c>
       <c r="AA8">
-        <v>2360</v>
+        <v>2372</v>
       </c>
       <c r="AB8">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="AC8">
-        <v>2792</v>
+        <v>2802</v>
       </c>
       <c r="AD8">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AE8" s="27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF8" s="13">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AG8">
-        <v>128.69999999999999</v>
+        <v>128.33000000000001</v>
       </c>
       <c r="AH8">
-        <v>11.76</v>
+        <v>11.98</v>
       </c>
       <c r="AI8">
-        <v>11.76</v>
+        <v>11.98</v>
       </c>
       <c r="AJ8">
-        <v>10.34</v>
+        <v>10.38</v>
       </c>
       <c r="AK8">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="AL8">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="AM8">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN8">
         <v>0.02</v>
       </c>
-      <c r="AO8" s="13">
-        <v>0.2</v>
+      <c r="AO8" s="38">
+        <v>0.19</v>
       </c>
       <c r="AP8" s="27">
-        <v>128.16999999999999</v>
+        <v>127.89</v>
       </c>
       <c r="AQ8" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR8" s="16">
-        <v>195371846000</v>
+      <c r="AR8" s="12">
+        <v>193622270800</v>
       </c>
       <c r="AS8" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v45.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v43.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -2037,53 +2039,53 @@
       <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="23">
-        <v>138.19</v>
-      </c>
-      <c r="E9" s="16">
-        <v>53991379900</v>
+      <c r="D9" s="38">
+        <v>136.32</v>
+      </c>
+      <c r="E9" s="22">
+        <v>51347102400</v>
       </c>
       <c r="F9">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G9" s="31">
-        <v>30.37</v>
+        <v>26.3</v>
       </c>
       <c r="H9">
-        <v>40771</v>
+        <v>40793</v>
       </c>
       <c r="I9">
-        <v>3411</v>
+        <v>3369</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="31">
-        <v>33.700000000000003</v>
+        <v>121</v>
+      </c>
+      <c r="K9" s="34">
+        <v>29.63</v>
       </c>
       <c r="L9" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="M9" s="31">
-        <v>65.56</v>
+        <v>68.52</v>
       </c>
       <c r="N9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" s="37">
-        <v>35.93</v>
+        <v>77</v>
+      </c>
+      <c r="O9" s="34">
+        <v>37.409999999999997</v>
       </c>
       <c r="P9" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="27">
-        <v>35.93</v>
+        <v>77</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>37.409999999999997</v>
       </c>
       <c r="R9" t="s">
-        <v>81</v>
-      </c>
-      <c r="S9" s="35">
-        <v>21.11</v>
+        <v>57</v>
+      </c>
+      <c r="S9" s="36">
+        <v>19.63</v>
       </c>
       <c r="T9" t="s">
         <v>70</v>
@@ -2098,70 +2100,70 @@
         <v>100</v>
       </c>
       <c r="X9">
-        <v>34726</v>
+        <v>34833</v>
       </c>
       <c r="Y9">
-        <v>3198</v>
+        <v>3134</v>
       </c>
       <c r="Z9">
-        <v>37924</v>
+        <v>37967</v>
       </c>
       <c r="AA9">
-        <v>2361</v>
+        <v>2341</v>
       </c>
       <c r="AB9">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="AC9">
-        <v>2792</v>
+        <v>2775</v>
       </c>
       <c r="AD9">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="AE9" s="27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF9" s="13">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AG9">
-        <v>128.61000000000001</v>
+        <v>129.01</v>
       </c>
       <c r="AH9">
-        <v>11.84</v>
+        <v>11.61</v>
       </c>
       <c r="AI9">
-        <v>11.84</v>
+        <v>11.61</v>
       </c>
       <c r="AJ9">
-        <v>10.34</v>
+        <v>10.28</v>
       </c>
       <c r="AK9">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="AL9">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="AM9">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN9">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AO9" s="13">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AP9" s="27">
-        <v>128.11000000000001</v>
+        <v>128.27000000000001</v>
       </c>
       <c r="AQ9" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR9" s="16">
-        <v>195360679900</v>
+      <c r="AR9" s="12">
+        <v>192716402400</v>
       </c>
       <c r="AS9" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v20.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v50.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
@@ -2305,7 +2307,7 @@
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>41</v>
@@ -2313,137 +2315,137 @@
       <c r="C11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="27">
-        <v>137.6</v>
-      </c>
-      <c r="E11" s="12">
-        <v>53149326700</v>
+      <c r="D11" s="13">
+        <v>138.61000000000001</v>
+      </c>
+      <c r="E11" s="16">
+        <v>54578818400</v>
       </c>
       <c r="F11">
-        <v>94</v>
-      </c>
-      <c r="G11" s="27">
-        <v>34.81</v>
+        <v>81</v>
+      </c>
+      <c r="G11" s="33">
+        <v>30</v>
       </c>
       <c r="H11">
-        <v>40738</v>
+        <v>40780</v>
       </c>
       <c r="I11">
-        <v>3378</v>
+        <v>3454</v>
       </c>
       <c r="J11" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="14">
-        <v>30.37</v>
+        <v>117</v>
+      </c>
+      <c r="K11" s="35">
+        <v>25.93</v>
       </c>
       <c r="L11" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" s="27">
-        <v>67.41</v>
+        <v>118</v>
+      </c>
+      <c r="M11" s="35">
+        <v>72.59</v>
       </c>
       <c r="N11" t="s">
-        <v>124</v>
-      </c>
-      <c r="O11" s="13">
-        <v>39.26</v>
+        <v>113</v>
+      </c>
+      <c r="O11" s="34">
+        <v>36.67</v>
       </c>
       <c r="P11" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>39.26</v>
+        <v>113</v>
+      </c>
+      <c r="Q11" s="30">
+        <v>36.67</v>
       </c>
       <c r="R11" t="s">
-        <v>81</v>
-      </c>
-      <c r="S11" s="35">
-        <v>21.11</v>
+        <v>68</v>
+      </c>
+      <c r="S11" s="34">
+        <v>20.37</v>
       </c>
       <c r="T11" t="s">
-        <v>63</v>
-      </c>
-      <c r="U11" s="14">
-        <v>96.3</v>
+        <v>53</v>
+      </c>
+      <c r="U11" s="38">
+        <v>88.89</v>
       </c>
       <c r="V11" t="s">
-        <v>47</v>
-      </c>
-      <c r="W11" s="29">
-        <v>92.59</v>
+        <v>48</v>
+      </c>
+      <c r="W11" s="38">
+        <v>81.48</v>
       </c>
       <c r="X11">
-        <v>34743</v>
+        <v>34717</v>
       </c>
       <c r="Y11">
-        <v>3141</v>
+        <v>3222</v>
       </c>
       <c r="Z11">
-        <v>37884</v>
+        <v>37939</v>
       </c>
       <c r="AA11">
-        <v>2363</v>
+        <v>2346</v>
       </c>
       <c r="AB11">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AC11">
-        <v>2802</v>
+        <v>2788</v>
       </c>
       <c r="AD11">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AE11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF11" s="13">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG11">
-        <v>128.68</v>
+        <v>128.58000000000001</v>
       </c>
       <c r="AH11">
-        <v>11.63</v>
+        <v>11.93</v>
       </c>
       <c r="AI11">
-        <v>11.63</v>
+        <v>11.93</v>
       </c>
       <c r="AJ11">
-        <v>10.38</v>
+        <v>10.33</v>
       </c>
       <c r="AK11">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AL11">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AM11">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AN11">
-        <v>0.02</v>
-      </c>
-      <c r="AO11" s="27">
-        <v>0.19</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO11" s="13">
+        <v>0.2</v>
       </c>
       <c r="AP11">
-        <v>128.24</v>
+        <v>128</v>
       </c>
       <c r="AQ11" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR11" s="12">
-        <v>194518626700</v>
+      <c r="AR11" s="16">
+        <v>195948118400</v>
       </c>
       <c r="AS11" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v55.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v48.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -2451,47 +2453,47 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="27">
-        <v>137.41999999999999</v>
-      </c>
-      <c r="E12" s="22">
-        <v>52902770000</v>
+      <c r="D12" s="13">
+        <v>138.19999999999999</v>
+      </c>
+      <c r="E12" s="16">
+        <v>54002546000</v>
       </c>
       <c r="F12">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="31">
-        <v>30</v>
+        <v>30.37</v>
       </c>
       <c r="H12">
-        <v>40801</v>
+        <v>40771</v>
       </c>
       <c r="I12">
-        <v>3370</v>
+        <v>3393</v>
       </c>
       <c r="J12" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="K12" s="31">
-        <v>34.07</v>
+        <v>31.11</v>
       </c>
       <c r="L12" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="M12" s="31">
-        <v>63.7</v>
+        <v>66.67</v>
       </c>
       <c r="N12" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="O12" s="34">
-        <v>36.299999999999997</v>
+        <v>36.67</v>
       </c>
       <c r="P12" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="Q12" s="30">
-        <v>36.299999999999997</v>
+        <v>36.67</v>
       </c>
       <c r="R12" t="s">
         <v>81</v>
@@ -2500,88 +2502,88 @@
         <v>21.11</v>
       </c>
       <c r="T12" t="s">
-        <v>53</v>
-      </c>
-      <c r="U12" s="27">
-        <v>88.89</v>
+        <v>70</v>
+      </c>
+      <c r="U12" s="13">
+        <v>100</v>
       </c>
       <c r="V12" t="s">
-        <v>64</v>
-      </c>
-      <c r="W12" s="27">
-        <v>85.19</v>
+        <v>63</v>
+      </c>
+      <c r="W12" s="14">
+        <v>96.3</v>
       </c>
       <c r="X12">
-        <v>34800</v>
+        <v>34749</v>
       </c>
       <c r="Y12">
-        <v>3160</v>
+        <v>3175</v>
       </c>
       <c r="Z12">
-        <v>37960</v>
+        <v>37924</v>
       </c>
       <c r="AA12">
         <v>2360</v>
       </c>
       <c r="AB12">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="AC12">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="AD12">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AE12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF12" s="13">
         <v>55</v>
       </c>
       <c r="AG12">
-        <v>128.88999999999999</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="AH12">
-        <v>11.7</v>
+        <v>11.76</v>
       </c>
       <c r="AI12">
-        <v>11.7</v>
+        <v>11.76</v>
       </c>
       <c r="AJ12">
-        <v>10.32</v>
+        <v>10.34</v>
       </c>
       <c r="AK12">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AL12">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AM12">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AN12">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AO12" s="13">
         <v>0.2</v>
       </c>
       <c r="AP12">
-        <v>128.28</v>
+        <v>128.16999999999999</v>
       </c>
       <c r="AQ12" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR12" s="12">
-        <v>194272070000</v>
+      <c r="AR12" s="16">
+        <v>195371846000</v>
       </c>
       <c r="AS12" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v49.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v45.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
@@ -2590,136 +2592,136 @@
         <v>42</v>
       </c>
       <c r="D13" s="27">
-        <v>137.41</v>
+        <v>137.41999999999999</v>
       </c>
       <c r="E13" s="22">
-        <v>52880731500</v>
+        <v>52902770000</v>
       </c>
       <c r="F13">
-        <v>94</v>
-      </c>
-      <c r="G13" s="35">
-        <v>34.81</v>
+        <v>81</v>
+      </c>
+      <c r="G13" s="31">
+        <v>30</v>
       </c>
       <c r="H13">
-        <v>40738</v>
+        <v>40801</v>
       </c>
       <c r="I13">
-        <v>3383</v>
+        <v>3370</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
-      </c>
-      <c r="K13" s="34">
-        <v>30</v>
+        <v>106</v>
+      </c>
+      <c r="K13" s="31">
+        <v>34.07</v>
       </c>
       <c r="L13" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M13" s="31">
-        <v>68.89</v>
+        <v>63.7</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="O13" s="34">
-        <v>37.409999999999997</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="P13" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q13" s="14">
-        <v>37.409999999999997</v>
+        <v>120</v>
+      </c>
+      <c r="Q13" s="30">
+        <v>36.299999999999997</v>
       </c>
       <c r="R13" t="s">
-        <v>57</v>
-      </c>
-      <c r="S13" s="36">
-        <v>19.63</v>
+        <v>81</v>
+      </c>
+      <c r="S13" s="35">
+        <v>21.11</v>
       </c>
       <c r="T13" t="s">
-        <v>63</v>
-      </c>
-      <c r="U13" s="14">
-        <v>96.3</v>
+        <v>53</v>
+      </c>
+      <c r="U13" s="38">
+        <v>88.89</v>
       </c>
       <c r="V13" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="W13" s="27">
-        <v>88.89</v>
+        <v>85.19</v>
       </c>
       <c r="X13">
-        <v>34735</v>
+        <v>34800</v>
       </c>
       <c r="Y13">
-        <v>3149</v>
+        <v>3160</v>
       </c>
       <c r="Z13">
-        <v>37884</v>
+        <v>37960</v>
       </c>
       <c r="AA13">
-        <v>2365</v>
+        <v>2360</v>
       </c>
       <c r="AB13">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="AC13">
-        <v>2802</v>
+        <v>2786</v>
       </c>
       <c r="AD13">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AE13" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF13" s="13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AG13">
-        <v>128.65</v>
+        <v>128.88999999999999</v>
       </c>
       <c r="AH13">
-        <v>11.66</v>
+        <v>11.7</v>
       </c>
       <c r="AI13">
-        <v>11.66</v>
+        <v>11.7</v>
       </c>
       <c r="AJ13">
-        <v>10.38</v>
+        <v>10.32</v>
       </c>
       <c r="AK13">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="AL13">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="AM13">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AN13">
-        <v>0.02</v>
-      </c>
-      <c r="AO13" s="27">
-        <v>0.19</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO13" s="13">
+        <v>0.2</v>
       </c>
       <c r="AP13">
-        <v>128.22999999999999</v>
+        <v>128.28</v>
       </c>
       <c r="AQ13" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR13" s="12">
-        <v>194250031500</v>
+        <v>194272070000</v>
       </c>
       <c r="AS13" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v41.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v49.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>41</v>
@@ -2727,40 +2729,40 @@
       <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="27">
-        <v>137.07</v>
-      </c>
-      <c r="E14" s="22">
-        <v>52408961400</v>
+      <c r="D14" s="23">
+        <v>138.19</v>
+      </c>
+      <c r="E14" s="16">
+        <v>53991379900</v>
       </c>
       <c r="F14">
-        <v>81</v>
-      </c>
-      <c r="G14" s="33">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="G14" s="31">
+        <v>30.37</v>
       </c>
       <c r="H14">
-        <v>40780</v>
+        <v>40771</v>
       </c>
       <c r="I14">
-        <v>3352</v>
+        <v>3411</v>
       </c>
       <c r="J14" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K14" s="31">
-        <v>31.48</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="L14" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="M14" s="31">
-        <v>65.930000000000007</v>
+        <v>65.56</v>
       </c>
       <c r="N14" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="37">
         <v>35.93</v>
       </c>
       <c r="P14" t="s">
@@ -2770,94 +2772,94 @@
         <v>35.93</v>
       </c>
       <c r="R14" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="S14" s="35">
-        <v>21.48</v>
+        <v>21.11</v>
       </c>
       <c r="T14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U14" s="15">
-        <v>92.59</v>
+        <v>70</v>
+      </c>
+      <c r="U14" s="13">
+        <v>100</v>
       </c>
       <c r="V14" t="s">
-        <v>48</v>
-      </c>
-      <c r="W14" s="27">
-        <v>81.48</v>
+        <v>70</v>
+      </c>
+      <c r="W14" s="13">
+        <v>100</v>
       </c>
       <c r="X14">
-        <v>34813</v>
+        <v>34726</v>
       </c>
       <c r="Y14">
-        <v>3126</v>
+        <v>3198</v>
       </c>
       <c r="Z14">
-        <v>37939</v>
+        <v>37924</v>
       </c>
       <c r="AA14">
-        <v>2356</v>
+        <v>2361</v>
       </c>
       <c r="AB14">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AC14">
-        <v>2788</v>
+        <v>2792</v>
       </c>
       <c r="AD14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AE14" s="27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="13">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AG14">
-        <v>128.94</v>
+        <v>128.61000000000001</v>
       </c>
       <c r="AH14">
-        <v>11.58</v>
+        <v>11.84</v>
       </c>
       <c r="AI14">
-        <v>11.58</v>
+        <v>11.84</v>
       </c>
       <c r="AJ14">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="AK14">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="AL14">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="AM14">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AN14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AO14" s="13">
         <v>0.2</v>
       </c>
       <c r="AP14">
-        <v>128.33000000000001</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AQ14" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR14" s="12">
-        <v>193778261400</v>
+      <c r="AR14" s="16">
+        <v>195360679900</v>
       </c>
       <c r="AS14" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v10.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v20.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>41</v>
@@ -2866,109 +2868,109 @@
         <v>42</v>
       </c>
       <c r="D15" s="27">
-        <v>136.96</v>
+        <v>137.07</v>
       </c>
       <c r="E15" s="22">
-        <v>52252970800</v>
+        <v>52408961400</v>
       </c>
       <c r="F15">
-        <v>94</v>
-      </c>
-      <c r="G15" s="35">
-        <v>34.81</v>
+        <v>81</v>
+      </c>
+      <c r="G15" s="33">
+        <v>30</v>
       </c>
       <c r="H15">
-        <v>40738</v>
+        <v>40780</v>
       </c>
       <c r="I15">
-        <v>3461</v>
+        <v>3352</v>
       </c>
       <c r="J15" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="K15" s="31">
-        <v>31.11</v>
+        <v>31.48</v>
       </c>
       <c r="L15" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="M15" s="31">
-        <v>67.41</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="N15" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="O15" s="34">
-        <v>37.409999999999997</v>
+        <v>35.93</v>
       </c>
       <c r="P15" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>37.409999999999997</v>
+        <v>45</v>
+      </c>
+      <c r="Q15" s="38">
+        <v>35.93</v>
       </c>
       <c r="R15" t="s">
-        <v>68</v>
-      </c>
-      <c r="S15" s="34">
-        <v>20.37</v>
+        <v>46</v>
+      </c>
+      <c r="S15" s="35">
+        <v>21.48</v>
       </c>
       <c r="T15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U15" s="13">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="U15" s="15">
+        <v>92.59</v>
       </c>
       <c r="V15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="W15" s="27">
-        <v>88.89</v>
+        <v>81.48</v>
       </c>
       <c r="X15">
-        <v>34650</v>
+        <v>34813</v>
       </c>
       <c r="Y15">
-        <v>3234</v>
+        <v>3126</v>
       </c>
       <c r="Z15">
-        <v>37884</v>
+        <v>37939</v>
       </c>
       <c r="AA15">
-        <v>2372</v>
+        <v>2356</v>
       </c>
       <c r="AB15">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AC15">
-        <v>2802</v>
+        <v>2788</v>
       </c>
       <c r="AD15">
         <v>47</v>
       </c>
       <c r="AE15" s="27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF15" s="13">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG15">
-        <v>128.33000000000001</v>
+        <v>128.94</v>
       </c>
       <c r="AH15">
-        <v>11.98</v>
+        <v>11.58</v>
       </c>
       <c r="AI15">
-        <v>11.98</v>
+        <v>11.58</v>
       </c>
       <c r="AJ15">
-        <v>10.38</v>
+        <v>10.33</v>
       </c>
       <c r="AK15">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AL15">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AM15">
         <v>0.17</v>
@@ -2976,26 +2978,26 @@
       <c r="AN15">
         <v>0.02</v>
       </c>
-      <c r="AO15" s="27">
-        <v>0.19</v>
+      <c r="AO15" s="13">
+        <v>0.2</v>
       </c>
       <c r="AP15">
-        <v>127.89</v>
+        <v>128.33000000000001</v>
       </c>
       <c r="AQ15" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR15" s="12">
-        <v>193622270800</v>
+        <v>193778261400</v>
       </c>
       <c r="AS15" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v43.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v10.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>41</v>
@@ -3004,52 +3006,52 @@
         <v>42</v>
       </c>
       <c r="D16" s="27">
-        <v>136.94999999999999</v>
+        <v>135.59</v>
       </c>
       <c r="E16" s="22">
-        <v>52242148000</v>
+        <v>50307411900</v>
       </c>
       <c r="F16">
-        <v>85</v>
-      </c>
-      <c r="G16" s="34">
-        <v>31.48</v>
+        <v>77</v>
+      </c>
+      <c r="G16" s="31">
+        <v>28.52</v>
       </c>
       <c r="H16">
-        <v>40771</v>
+        <v>40777</v>
       </c>
       <c r="I16">
-        <v>3348</v>
+        <v>3411</v>
       </c>
       <c r="J16" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="K16" s="31">
-        <v>31.11</v>
+        <v>33.33</v>
       </c>
       <c r="L16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="M16" s="31">
-        <v>65.930000000000007</v>
+        <v>65.19</v>
       </c>
       <c r="N16" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="O16" s="37">
-        <v>34.44</v>
+        <v>35.93</v>
       </c>
       <c r="P16" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Q16" s="27">
-        <v>34.44</v>
+        <v>35.93</v>
       </c>
       <c r="R16" t="s">
-        <v>81</v>
-      </c>
-      <c r="S16" s="35">
-        <v>21.11</v>
+        <v>57</v>
+      </c>
+      <c r="S16" s="36">
+        <v>19.63</v>
       </c>
       <c r="T16" t="s">
         <v>47</v>
@@ -3058,82 +3060,82 @@
         <v>92.59</v>
       </c>
       <c r="V16" t="s">
-        <v>64</v>
-      </c>
-      <c r="W16" s="27">
-        <v>85.19</v>
+        <v>47</v>
+      </c>
+      <c r="W16" s="29">
+        <v>92.59</v>
       </c>
       <c r="X16">
-        <v>34780</v>
+        <v>34757</v>
       </c>
       <c r="Y16">
-        <v>3144</v>
+        <v>3188</v>
       </c>
       <c r="Z16">
-        <v>37924</v>
+        <v>37945</v>
       </c>
       <c r="AA16">
-        <v>2370</v>
+        <v>2356</v>
       </c>
       <c r="AB16">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="AC16">
-        <v>2792</v>
+        <v>2781</v>
       </c>
       <c r="AD16">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AE16" s="27">
         <v>2</v>
       </c>
       <c r="AF16" s="13">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AG16">
-        <v>128.81</v>
+        <v>128.72999999999999</v>
       </c>
       <c r="AH16">
-        <v>11.64</v>
+        <v>11.81</v>
       </c>
       <c r="AI16">
-        <v>11.64</v>
+        <v>11.81</v>
       </c>
       <c r="AJ16">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="AK16">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="AL16">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="AM16">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN16">
         <v>0.01</v>
       </c>
-      <c r="AO16" s="13">
-        <v>0.2</v>
+      <c r="AO16" s="38">
+        <v>0.19</v>
       </c>
       <c r="AP16">
-        <v>128.35</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AQ16" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR16" s="12">
-        <v>193611448000</v>
+        <v>191676711900</v>
       </c>
       <c r="AS16" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v31.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v12.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>41</v>
@@ -3142,109 +3144,109 @@
         <v>42</v>
       </c>
       <c r="D17" s="27">
-        <v>136.32</v>
-      </c>
-      <c r="E17" s="22">
-        <v>51347102400</v>
+        <v>134.65</v>
+      </c>
+      <c r="E17" s="12">
+        <v>48981467300</v>
       </c>
       <c r="F17">
-        <v>71</v>
-      </c>
-      <c r="G17" s="31">
-        <v>26.3</v>
+        <v>81</v>
+      </c>
+      <c r="G17" s="33">
+        <v>30</v>
       </c>
       <c r="H17">
-        <v>40793</v>
+        <v>40780</v>
       </c>
       <c r="I17">
-        <v>3369</v>
+        <v>3318</v>
       </c>
       <c r="J17" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="34">
-        <v>29.63</v>
+        <v>114</v>
+      </c>
+      <c r="K17" s="31">
+        <v>37.78</v>
       </c>
       <c r="L17" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="M17" s="31">
-        <v>68.52</v>
+        <v>60.37</v>
       </c>
       <c r="N17" t="s">
-        <v>77</v>
-      </c>
-      <c r="O17" s="34">
-        <v>37.409999999999997</v>
+        <v>86</v>
+      </c>
+      <c r="O17" s="37">
+        <v>35.56</v>
       </c>
       <c r="P17" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q17" s="14">
-        <v>37.409999999999997</v>
+        <v>86</v>
+      </c>
+      <c r="Q17" s="38">
+        <v>35.56</v>
       </c>
       <c r="R17" t="s">
-        <v>57</v>
-      </c>
-      <c r="S17" s="36">
-        <v>19.63</v>
+        <v>116</v>
+      </c>
+      <c r="S17" s="34">
+        <v>20.74</v>
       </c>
       <c r="T17" t="s">
-        <v>70</v>
-      </c>
-      <c r="U17" s="13">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="U17" s="15">
+        <v>92.59</v>
       </c>
       <c r="V17" t="s">
-        <v>70</v>
-      </c>
-      <c r="W17" s="13">
-        <v>100</v>
+        <v>48</v>
+      </c>
+      <c r="W17" s="38">
+        <v>81.48</v>
       </c>
       <c r="X17">
-        <v>34833</v>
+        <v>34826</v>
       </c>
       <c r="Y17">
-        <v>3134</v>
+        <v>3113</v>
       </c>
       <c r="Z17">
-        <v>37967</v>
+        <v>37939</v>
       </c>
       <c r="AA17">
-        <v>2341</v>
+        <v>2377</v>
       </c>
       <c r="AB17">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="AC17">
-        <v>2775</v>
+        <v>2788</v>
       </c>
       <c r="AD17">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17" s="13">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AG17">
-        <v>129.01</v>
+        <v>128.99</v>
       </c>
       <c r="AH17">
-        <v>11.61</v>
+        <v>11.53</v>
       </c>
       <c r="AI17">
-        <v>11.61</v>
+        <v>11.53</v>
       </c>
       <c r="AJ17">
-        <v>10.28</v>
+        <v>10.33</v>
       </c>
       <c r="AK17">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AL17">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AM17">
         <v>0.17</v>
@@ -3253,25 +3255,25 @@
         <v>0.02</v>
       </c>
       <c r="AO17" s="13">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AP17">
-        <v>128.27000000000001</v>
+        <v>128.44</v>
       </c>
       <c r="AQ17" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR17" s="12">
-        <v>192716402400</v>
+        <v>190350767300</v>
       </c>
       <c r="AS17" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v50.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v47.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>41</v>
@@ -3279,137 +3281,137 @@
       <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="27">
-        <v>135.69</v>
-      </c>
-      <c r="E18" s="22">
-        <v>50447959500</v>
+      <c r="D18" s="13">
+        <v>138.83000000000001</v>
+      </c>
+      <c r="E18" s="16">
+        <v>54891292100</v>
       </c>
       <c r="F18">
-        <v>94</v>
-      </c>
-      <c r="G18" s="35">
-        <v>34.81</v>
+        <v>81</v>
+      </c>
+      <c r="G18" s="33">
+        <v>30</v>
       </c>
       <c r="H18">
-        <v>40738</v>
+        <v>40801</v>
       </c>
       <c r="I18">
-        <v>3222</v>
+        <v>3423</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="K18" s="34">
-        <v>30</v>
+        <v>30.74</v>
       </c>
       <c r="L18" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="M18" s="31">
-        <v>67.41</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="O18" s="37">
-        <v>34.07</v>
+        <v>35.19</v>
       </c>
       <c r="P18" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="Q18" s="27">
-        <v>34.07</v>
+        <v>35.19</v>
       </c>
       <c r="R18" t="s">
-        <v>94</v>
-      </c>
-      <c r="S18" s="34">
-        <v>20</v>
+        <v>46</v>
+      </c>
+      <c r="S18" s="35">
+        <v>21.48</v>
       </c>
       <c r="T18" t="s">
-        <v>53</v>
-      </c>
-      <c r="U18" s="27">
-        <v>88.89</v>
+        <v>70</v>
+      </c>
+      <c r="U18" s="13">
+        <v>100</v>
       </c>
       <c r="V18" t="s">
-        <v>64</v>
-      </c>
-      <c r="W18" s="27">
-        <v>85.19</v>
+        <v>47</v>
+      </c>
+      <c r="W18" s="29">
+        <v>92.59</v>
       </c>
       <c r="X18">
-        <v>34882</v>
+        <v>34759</v>
       </c>
       <c r="Y18">
-        <v>3002</v>
+        <v>3201</v>
       </c>
       <c r="Z18">
-        <v>37884</v>
+        <v>37960</v>
       </c>
       <c r="AA18">
-        <v>2375</v>
+        <v>2349</v>
       </c>
       <c r="AB18">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AC18">
-        <v>2802</v>
+        <v>2786</v>
       </c>
       <c r="AD18">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AE18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF18" s="13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AG18">
-        <v>129.19</v>
+        <v>128.74</v>
       </c>
       <c r="AH18">
-        <v>11.12</v>
+        <v>11.86</v>
       </c>
       <c r="AI18">
-        <v>11.12</v>
+        <v>11.86</v>
       </c>
       <c r="AJ18">
-        <v>10.38</v>
+        <v>10.32</v>
       </c>
       <c r="AK18">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="AL18">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="AM18">
         <v>0.19</v>
       </c>
       <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="27">
-        <v>0.19</v>
+        <v>0.02</v>
+      </c>
+      <c r="AO18" s="13">
+        <v>0.2</v>
       </c>
       <c r="AP18">
-        <v>128.84</v>
+        <v>128.07</v>
       </c>
       <c r="AQ18" s="12">
         <v>141369300000</v>
       </c>
-      <c r="AR18" s="12">
-        <v>191817259500</v>
+      <c r="AR18" s="16">
+        <v>196260592100</v>
       </c>
       <c r="AS18" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v40.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v16.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
         <v>41</v>
@@ -3418,22 +3420,22 @@
         <v>42</v>
       </c>
       <c r="D19" s="27">
-        <v>135.59</v>
+        <v>135.4</v>
       </c>
       <c r="E19" s="22">
-        <v>50307411900</v>
+        <v>50044682800</v>
       </c>
       <c r="F19">
-        <v>77</v>
-      </c>
-      <c r="G19" s="31">
-        <v>28.52</v>
+        <v>94</v>
+      </c>
+      <c r="G19" s="35">
+        <v>34.81</v>
       </c>
       <c r="H19">
-        <v>40777</v>
+        <v>40738</v>
       </c>
       <c r="I19">
-        <v>3411</v>
+        <v>3346</v>
       </c>
       <c r="J19" t="s">
         <v>55</v>
@@ -3442,112 +3444,112 @@
         <v>33.33</v>
       </c>
       <c r="L19" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="M19" s="31">
-        <v>65.19</v>
+        <v>65.56</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="O19" s="37">
-        <v>35.93</v>
+        <v>35.19</v>
       </c>
       <c r="P19" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="Q19">
-        <v>35.93</v>
+        <v>35.19</v>
       </c>
       <c r="R19" t="s">
-        <v>57</v>
-      </c>
-      <c r="S19" s="36">
-        <v>19.63</v>
+        <v>94</v>
+      </c>
+      <c r="S19" s="34">
+        <v>20</v>
       </c>
       <c r="T19" t="s">
-        <v>47</v>
-      </c>
-      <c r="U19" s="15">
-        <v>92.59</v>
+        <v>63</v>
+      </c>
+      <c r="U19" s="14">
+        <v>96.3</v>
       </c>
       <c r="V19" t="s">
-        <v>47</v>
-      </c>
-      <c r="W19" s="29">
-        <v>92.59</v>
+        <v>53</v>
+      </c>
+      <c r="W19" s="38">
+        <v>88.89</v>
       </c>
       <c r="X19">
-        <v>34757</v>
+        <v>34756</v>
       </c>
       <c r="Y19">
-        <v>3188</v>
+        <v>3128</v>
       </c>
       <c r="Z19">
-        <v>37945</v>
+        <v>37884</v>
       </c>
       <c r="AA19">
-        <v>2356</v>
+        <v>2382</v>
       </c>
       <c r="AB19">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="AC19">
-        <v>2781</v>
+        <v>2802</v>
       </c>
       <c r="AD19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AE19" s="27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AF19" s="13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG19">
         <v>128.72999999999999</v>
       </c>
       <c r="AH19">
-        <v>11.81</v>
+        <v>11.59</v>
       </c>
       <c r="AI19">
-        <v>11.81</v>
+        <v>11.59</v>
       </c>
       <c r="AJ19">
-        <v>10.3</v>
+        <v>10.38</v>
       </c>
       <c r="AK19">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AL19">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AM19">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN19">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AO19" s="27">
         <v>0.19</v>
       </c>
       <c r="AP19">
-        <v>128.11000000000001</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AQ19" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR19" s="12">
-        <v>191676711900</v>
+        <v>191413982800</v>
       </c>
       <c r="AS19" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v12.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v53.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A20" s="27">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
         <v>41</v>
@@ -3556,34 +3558,34 @@
         <v>42</v>
       </c>
       <c r="D20" s="27">
-        <v>135.4</v>
-      </c>
-      <c r="E20" s="22">
-        <v>50044682800</v>
+        <v>133.04</v>
+      </c>
+      <c r="E20" s="12">
+        <v>46739833700</v>
       </c>
       <c r="F20">
-        <v>94</v>
-      </c>
-      <c r="G20" s="35">
-        <v>34.81</v>
+        <v>87</v>
+      </c>
+      <c r="G20" s="34">
+        <v>32.22</v>
       </c>
       <c r="H20">
-        <v>40738</v>
+        <v>40773</v>
       </c>
       <c r="I20">
-        <v>3346</v>
+        <v>3382</v>
       </c>
       <c r="J20" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K20" s="31">
-        <v>33.33</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="M20" s="31">
-        <v>65.56</v>
+        <v>64.44</v>
       </c>
       <c r="N20" t="s">
         <v>58</v>
@@ -3598,10 +3600,10 @@
         <v>35.19</v>
       </c>
       <c r="R20" t="s">
-        <v>94</v>
-      </c>
-      <c r="S20" s="34">
-        <v>20</v>
+        <v>76</v>
+      </c>
+      <c r="S20" s="36">
+        <v>19.260000000000002</v>
       </c>
       <c r="T20" t="s">
         <v>63</v>
@@ -3610,82 +3612,82 @@
         <v>96.3</v>
       </c>
       <c r="V20" t="s">
-        <v>53</v>
-      </c>
-      <c r="W20" s="27">
-        <v>88.89</v>
+        <v>47</v>
+      </c>
+      <c r="W20" s="29">
+        <v>92.59</v>
       </c>
       <c r="X20">
-        <v>34756</v>
+        <v>34769</v>
       </c>
       <c r="Y20">
-        <v>3128</v>
+        <v>3161</v>
       </c>
       <c r="Z20">
-        <v>37884</v>
+        <v>37930</v>
       </c>
       <c r="AA20">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="AB20">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AC20">
-        <v>2802</v>
+        <v>2794</v>
       </c>
       <c r="AD20">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AE20">
         <v>6</v>
       </c>
-      <c r="AF20" s="13">
-        <v>52</v>
+      <c r="AF20" s="38">
+        <v>49</v>
       </c>
       <c r="AG20">
-        <v>128.72999999999999</v>
+        <v>128.77000000000001</v>
       </c>
       <c r="AH20">
-        <v>11.59</v>
+        <v>11.71</v>
       </c>
       <c r="AI20">
-        <v>11.59</v>
+        <v>11.71</v>
       </c>
       <c r="AJ20">
-        <v>10.38</v>
+        <v>10.35</v>
       </c>
       <c r="AK20">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AL20">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AM20">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AN20">
         <v>0.02</v>
       </c>
       <c r="AO20" s="27">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AP20">
-        <v>128.38999999999999</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="AQ20" s="12">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AR20" s="12">
-        <v>191413982800</v>
+        <v>188192833700</v>
       </c>
       <c r="AS20" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v53.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v36.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
@@ -3694,52 +3696,52 @@
         <v>42</v>
       </c>
       <c r="D21" s="27">
-        <v>135.02000000000001</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="E21" s="12">
-        <v>49501097300</v>
+        <v>43544659200</v>
       </c>
       <c r="F21">
-        <v>94</v>
-      </c>
-      <c r="G21" s="35">
-        <v>34.81</v>
+        <v>81</v>
+      </c>
+      <c r="G21" s="33">
+        <v>30</v>
       </c>
       <c r="H21">
-        <v>40738</v>
+        <v>40732</v>
       </c>
       <c r="I21">
-        <v>3379</v>
+        <v>3363</v>
       </c>
       <c r="J21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K21" s="31">
-        <v>31.11</v>
+        <v>31.85</v>
       </c>
       <c r="L21" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="M21" s="31">
-        <v>67.41</v>
+        <v>65.56</v>
       </c>
       <c r="N21" t="s">
-        <v>97</v>
-      </c>
-      <c r="O21" s="28">
-        <v>32.96</v>
+        <v>58</v>
+      </c>
+      <c r="O21" s="37">
+        <v>35.19</v>
       </c>
       <c r="P21" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="Q21" s="27">
-        <v>32.96</v>
+        <v>35.19</v>
       </c>
       <c r="R21" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="S21" s="36">
-        <v>19.260000000000002</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="T21" t="s">
         <v>47</v>
@@ -3748,82 +3750,82 @@
         <v>92.59</v>
       </c>
       <c r="V21" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="W21" s="27">
-        <v>85.19</v>
+        <v>81.48</v>
       </c>
       <c r="X21">
-        <v>34714</v>
+        <v>34767</v>
       </c>
       <c r="Y21">
-        <v>3170</v>
+        <v>3134</v>
       </c>
       <c r="Z21">
-        <v>37884</v>
+        <v>37901</v>
       </c>
       <c r="AA21">
-        <v>2387</v>
+        <v>2378</v>
       </c>
       <c r="AB21">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="AC21">
-        <v>2802</v>
+        <v>2786</v>
       </c>
       <c r="AD21">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AE21" s="27">
-        <v>2</v>
-      </c>
-      <c r="AF21" s="13">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="AF21" s="38">
+        <v>45</v>
       </c>
       <c r="AG21">
-        <v>128.57</v>
+        <v>128.77000000000001</v>
       </c>
       <c r="AH21">
-        <v>11.74</v>
+        <v>11.61</v>
       </c>
       <c r="AI21">
-        <v>11.74</v>
+        <v>11.61</v>
       </c>
       <c r="AJ21">
-        <v>10.38</v>
+        <v>10.32</v>
       </c>
       <c r="AK21">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="AL21">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="AM21">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="AN21">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="27">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AP21">
-        <v>128.22</v>
+        <v>128.29</v>
       </c>
       <c r="AQ21" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR21" s="12">
-        <v>190870397300</v>
+        <v>184913959200</v>
       </c>
       <c r="AS21" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v42.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v25.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
@@ -3832,136 +3834,136 @@
         <v>42</v>
       </c>
       <c r="D22" s="27">
-        <v>134.65</v>
+        <v>130.44</v>
       </c>
       <c r="E22" s="12">
-        <v>48981467300</v>
+        <v>43026460900</v>
       </c>
       <c r="F22">
-        <v>81</v>
-      </c>
-      <c r="G22" s="33">
-        <v>30</v>
+        <v>80</v>
+      </c>
+      <c r="G22" s="31">
+        <v>29.63</v>
       </c>
       <c r="H22">
-        <v>40780</v>
+        <v>40707</v>
       </c>
       <c r="I22">
-        <v>3318</v>
+        <v>3470</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="K22" s="31">
-        <v>37.78</v>
+        <v>34.44</v>
       </c>
       <c r="L22" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="M22" s="31">
-        <v>60.37</v>
+        <v>62.96</v>
       </c>
       <c r="N22" t="s">
-        <v>86</v>
-      </c>
-      <c r="O22" s="37">
-        <v>35.56</v>
+        <v>58</v>
+      </c>
+      <c r="O22" s="39">
+        <v>35.19</v>
       </c>
       <c r="P22" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="Q22" s="27">
-        <v>35.56</v>
+        <v>35.19</v>
       </c>
       <c r="R22" t="s">
-        <v>116</v>
-      </c>
-      <c r="S22" s="34">
-        <v>20.74</v>
+        <v>61</v>
+      </c>
+      <c r="S22" s="36">
+        <v>18.52</v>
       </c>
       <c r="T22" t="s">
-        <v>47</v>
-      </c>
-      <c r="U22" s="15">
-        <v>92.59</v>
+        <v>63</v>
+      </c>
+      <c r="U22" s="14">
+        <v>96.3</v>
       </c>
       <c r="V22" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="W22" s="27">
-        <v>81.48</v>
+        <v>85.19</v>
       </c>
       <c r="X22">
-        <v>34826</v>
+        <v>34638</v>
       </c>
       <c r="Y22">
-        <v>3113</v>
+        <v>3239</v>
       </c>
       <c r="Z22">
-        <v>37939</v>
+        <v>37877</v>
       </c>
       <c r="AA22">
-        <v>2377</v>
+        <v>2381</v>
       </c>
       <c r="AB22">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="AC22">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="AD22">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AE22" s="27">
-        <v>6</v>
-      </c>
-      <c r="AF22" s="13">
-        <v>53</v>
+        <v>2</v>
+      </c>
+      <c r="AF22" s="38">
+        <v>44</v>
       </c>
       <c r="AG22">
-        <v>128.99</v>
+        <v>128.29</v>
       </c>
       <c r="AH22">
-        <v>11.53</v>
+        <v>12</v>
       </c>
       <c r="AI22">
-        <v>11.53</v>
+        <v>12</v>
       </c>
       <c r="AJ22">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
       <c r="AK22">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="AL22">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="AM22">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AN22">
-        <v>0.02</v>
-      </c>
-      <c r="AO22" s="13">
-        <v>0.2</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO22" s="38">
+        <v>0.16</v>
       </c>
       <c r="AP22">
-        <v>128.44</v>
+        <v>127.9</v>
       </c>
       <c r="AQ22" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR22" s="12">
-        <v>190350767300</v>
+        <v>184395760900</v>
       </c>
       <c r="AS22" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v47.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v14.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -3970,46 +3972,46 @@
         <v>42</v>
       </c>
       <c r="D23" s="27">
-        <v>134.38999999999999</v>
+        <v>133.04</v>
       </c>
       <c r="E23" s="12">
-        <v>48611685100</v>
+        <v>46705171100</v>
       </c>
       <c r="F23">
-        <v>94</v>
-      </c>
-      <c r="G23" s="35">
+        <v>91</v>
+      </c>
+      <c r="G23" s="34">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="H23">
+        <v>40727</v>
+      </c>
+      <c r="I23">
+        <v>3298</v>
+      </c>
+      <c r="J23" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="31">
+        <v>35.19</v>
+      </c>
+      <c r="L23" t="s">
+        <v>93</v>
+      </c>
+      <c r="M23" s="31">
+        <v>61.48</v>
+      </c>
+      <c r="N23" t="s">
+        <v>75</v>
+      </c>
+      <c r="O23" s="37">
         <v>34.81</v>
       </c>
-      <c r="H23">
-        <v>40738</v>
-      </c>
-      <c r="I23">
-        <v>3283</v>
-      </c>
-      <c r="J23" t="s">
-        <v>60</v>
-      </c>
-      <c r="K23" s="31">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="L23" t="s">
-        <v>104</v>
-      </c>
-      <c r="M23" s="31">
-        <v>64.44</v>
-      </c>
-      <c r="N23" t="s">
-        <v>97</v>
-      </c>
-      <c r="O23" s="28">
-        <v>32.96</v>
-      </c>
       <c r="P23" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="Q23" s="27">
-        <v>32.96</v>
+        <v>34.81</v>
       </c>
       <c r="R23" t="s">
         <v>57</v>
@@ -4018,88 +4020,88 @@
         <v>19.63</v>
       </c>
       <c r="T23" t="s">
-        <v>53</v>
-      </c>
-      <c r="U23" s="27">
-        <v>88.89</v>
+        <v>63</v>
+      </c>
+      <c r="U23" s="14">
+        <v>96.3</v>
       </c>
       <c r="V23" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="W23" s="27">
-        <v>88.89</v>
+        <v>85.19</v>
       </c>
       <c r="X23">
-        <v>34811</v>
+        <v>34807</v>
       </c>
       <c r="Y23">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="Z23">
-        <v>37884</v>
+        <v>37878</v>
       </c>
       <c r="AA23">
-        <v>2389</v>
+        <v>2384</v>
       </c>
       <c r="AB23">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="AC23">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="AD23">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AE23" s="27">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="13">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="AF23" s="38">
+        <v>48</v>
       </c>
       <c r="AG23">
-        <v>128.93</v>
+        <v>128.91</v>
       </c>
       <c r="AH23">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="AI23">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="AJ23">
-        <v>10.38</v>
+        <v>10.37</v>
       </c>
       <c r="AK23">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="AL23">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="AM23">
         <v>0.17</v>
       </c>
       <c r="AN23">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AO23" s="27">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AP23">
-        <v>128.61000000000001</v>
+        <v>128.53</v>
       </c>
       <c r="AQ23" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR23" s="12">
-        <v>189980985100</v>
+        <v>188074471100</v>
       </c>
       <c r="AS23" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v44.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v26.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -4108,46 +4110,46 @@
         <v>42</v>
       </c>
       <c r="D24" s="27">
-        <v>134.38</v>
+        <v>131.91</v>
       </c>
       <c r="E24" s="12">
-        <v>48607784700</v>
+        <v>45116576700</v>
       </c>
       <c r="F24">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G24" s="35">
+        <v>34.07</v>
+      </c>
+      <c r="H24">
+        <v>40715</v>
+      </c>
+      <c r="I24">
+        <v>3314</v>
+      </c>
+      <c r="J24" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" s="31">
+        <v>32.22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="31">
+        <v>65.19</v>
+      </c>
+      <c r="N24" t="s">
+        <v>75</v>
+      </c>
+      <c r="O24" s="37">
         <v>34.81</v>
       </c>
-      <c r="H24">
-        <v>40738</v>
-      </c>
-      <c r="I24">
-        <v>3393</v>
-      </c>
-      <c r="J24" t="s">
-        <v>45</v>
-      </c>
-      <c r="K24" s="31">
-        <v>35.93</v>
-      </c>
-      <c r="L24" t="s">
-        <v>123</v>
-      </c>
-      <c r="M24" s="31">
-        <v>61.11</v>
-      </c>
-      <c r="N24" t="s">
-        <v>97</v>
-      </c>
-      <c r="O24" s="28">
-        <v>32.96</v>
-      </c>
       <c r="P24" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="Q24" s="27">
-        <v>32.96</v>
+        <v>34.81</v>
       </c>
       <c r="R24" t="s">
         <v>76</v>
@@ -4156,88 +4158,88 @@
         <v>19.260000000000002</v>
       </c>
       <c r="T24" t="s">
-        <v>63</v>
-      </c>
-      <c r="U24" s="14">
-        <v>96.3</v>
+        <v>53</v>
+      </c>
+      <c r="U24" s="38">
+        <v>88.89</v>
       </c>
       <c r="V24" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="W24" s="27">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="X24">
-        <v>34700</v>
+        <v>34792</v>
       </c>
       <c r="Y24">
-        <v>3184</v>
+        <v>3079</v>
       </c>
       <c r="Z24">
-        <v>37884</v>
+        <v>37871</v>
       </c>
       <c r="AA24">
-        <v>2393</v>
+        <v>2383</v>
       </c>
       <c r="AB24">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="AC24">
-        <v>2802</v>
+        <v>2798</v>
       </c>
       <c r="AD24">
-        <v>44</v>
-      </c>
-      <c r="AE24" s="13">
-        <v>8</v>
-      </c>
-      <c r="AF24" s="13">
-        <v>52</v>
+        <v>42</v>
+      </c>
+      <c r="AE24" s="38">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="38">
+        <v>46</v>
       </c>
       <c r="AG24">
-        <v>128.52000000000001</v>
+        <v>128.86000000000001</v>
       </c>
       <c r="AH24">
-        <v>11.79</v>
+        <v>11.4</v>
       </c>
       <c r="AI24">
-        <v>11.79</v>
+        <v>11.4</v>
       </c>
       <c r="AJ24">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="AK24">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="AL24">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="AM24">
         <v>0.16</v>
       </c>
       <c r="AN24">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AO24" s="27">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AP24">
-        <v>128.22</v>
+        <v>128.47</v>
       </c>
       <c r="AQ24" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR24" s="12">
-        <v>189977084700</v>
+        <v>186485876700</v>
       </c>
       <c r="AS24" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v52.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v18.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
@@ -4246,136 +4248,136 @@
         <v>42</v>
       </c>
       <c r="D25">
-        <v>134.13999999999999</v>
+        <v>131.46</v>
       </c>
       <c r="E25" s="12">
-        <v>48261703300</v>
+        <v>44470991100</v>
       </c>
       <c r="F25">
-        <v>95</v>
-      </c>
-      <c r="G25" s="35">
-        <v>35.19</v>
+        <v>73</v>
+      </c>
+      <c r="G25" s="31">
+        <v>27.04</v>
       </c>
       <c r="H25">
-        <v>40740</v>
+        <v>40730</v>
       </c>
       <c r="I25">
-        <v>3322</v>
+        <v>3412</v>
       </c>
       <c r="J25" t="s">
-        <v>60</v>
-      </c>
-      <c r="K25" s="31">
-        <v>33.700000000000003</v>
+        <v>69</v>
+      </c>
+      <c r="K25" s="34">
+        <v>30.74</v>
       </c>
       <c r="L25" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="M25" s="31">
-        <v>62.96</v>
+        <v>67.78</v>
       </c>
       <c r="N25" t="s">
-        <v>55</v>
-      </c>
-      <c r="O25" s="28">
-        <v>33.33</v>
+        <v>75</v>
+      </c>
+      <c r="O25" s="37">
+        <v>34.81</v>
       </c>
       <c r="P25" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="Q25" s="27">
-        <v>33.33</v>
+        <v>34.81</v>
       </c>
       <c r="R25" t="s">
-        <v>94</v>
-      </c>
-      <c r="S25" s="34">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="S25" s="36">
+        <v>17.78</v>
       </c>
       <c r="T25" t="s">
-        <v>70</v>
-      </c>
-      <c r="U25" s="13">
-        <v>100</v>
+        <v>53</v>
+      </c>
+      <c r="U25" s="38">
+        <v>88.89</v>
       </c>
       <c r="V25" t="s">
-        <v>70</v>
-      </c>
-      <c r="W25" s="13">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="W25" s="38">
+        <v>74.069999999999993</v>
       </c>
       <c r="X25">
-        <v>34772</v>
+        <v>34737</v>
       </c>
       <c r="Y25">
-        <v>3112</v>
+        <v>3168</v>
       </c>
       <c r="Z25">
-        <v>37884</v>
+        <v>37905</v>
       </c>
       <c r="AA25">
-        <v>2392</v>
+        <v>2364</v>
       </c>
       <c r="AB25">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="AC25">
-        <v>2805</v>
+        <v>2781</v>
       </c>
       <c r="AD25">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="AE25" s="27">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="13">
-        <v>51</v>
+        <v>3</v>
+      </c>
+      <c r="AF25" s="38">
+        <v>44</v>
       </c>
       <c r="AG25">
-        <v>128.79</v>
+        <v>128.66</v>
       </c>
       <c r="AH25">
-        <v>11.53</v>
+        <v>11.73</v>
       </c>
       <c r="AI25">
-        <v>11.53</v>
+        <v>11.73</v>
       </c>
       <c r="AJ25">
-        <v>10.39</v>
+        <v>10.3</v>
       </c>
       <c r="AK25">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="AL25">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="AM25">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO25" s="27">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="AP25">
-        <v>128.44</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AQ25" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR25" s="12">
-        <v>189631003300</v>
+        <v>185840291100</v>
       </c>
       <c r="AS25" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v27.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v30.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="26" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
@@ -4384,52 +4386,52 @@
         <v>42</v>
       </c>
       <c r="D26">
-        <v>133.11000000000001</v>
-      </c>
-      <c r="E26" s="12">
-        <v>46813614000</v>
+        <v>136.94999999999999</v>
+      </c>
+      <c r="E26" s="22">
+        <v>52242148000</v>
       </c>
       <c r="F26">
-        <v>94</v>
-      </c>
-      <c r="G26" s="35">
-        <v>34.81</v>
+        <v>85</v>
+      </c>
+      <c r="G26" s="34">
+        <v>31.48</v>
       </c>
       <c r="H26">
-        <v>40738</v>
+        <v>40771</v>
       </c>
       <c r="I26">
-        <v>3257</v>
+        <v>3348</v>
       </c>
       <c r="J26" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="K26" s="31">
-        <v>37.04</v>
+        <v>31.11</v>
       </c>
       <c r="L26" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="M26" s="31">
-        <v>60.37</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="N26" t="s">
-        <v>60</v>
-      </c>
-      <c r="O26" s="28">
-        <v>33.700000000000003</v>
+        <v>62</v>
+      </c>
+      <c r="O26" s="37">
+        <v>34.44</v>
       </c>
       <c r="P26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q26" s="27">
-        <v>33.700000000000003</v>
+        <v>34.44</v>
       </c>
       <c r="R26" t="s">
-        <v>57</v>
-      </c>
-      <c r="S26" s="36">
-        <v>19.63</v>
+        <v>81</v>
+      </c>
+      <c r="S26" s="35">
+        <v>21.11</v>
       </c>
       <c r="T26" t="s">
         <v>47</v>
@@ -4438,82 +4440,82 @@
         <v>92.59</v>
       </c>
       <c r="V26" t="s">
-        <v>47</v>
-      </c>
-      <c r="W26" s="29">
-        <v>92.59</v>
+        <v>64</v>
+      </c>
+      <c r="W26" s="38">
+        <v>85.19</v>
       </c>
       <c r="X26">
-        <v>34821</v>
+        <v>34780</v>
       </c>
       <c r="Y26">
-        <v>3063</v>
+        <v>3144</v>
       </c>
       <c r="Z26">
-        <v>37884</v>
+        <v>37924</v>
       </c>
       <c r="AA26">
-        <v>2400</v>
+        <v>2370</v>
       </c>
       <c r="AB26">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AC26">
-        <v>2802</v>
+        <v>2792</v>
       </c>
       <c r="AD26">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AE26" s="27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF26" s="13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AG26">
-        <v>128.97</v>
+        <v>128.81</v>
       </c>
       <c r="AH26">
-        <v>11.34</v>
+        <v>11.64</v>
       </c>
       <c r="AI26">
-        <v>11.34</v>
+        <v>11.64</v>
       </c>
       <c r="AJ26">
-        <v>10.38</v>
+        <v>10.34</v>
       </c>
       <c r="AK26">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AL26">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AM26">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="27">
-        <v>0.19</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO26" s="13">
+        <v>0.2</v>
       </c>
       <c r="AP26">
-        <v>128.68</v>
+        <v>128.35</v>
       </c>
       <c r="AQ26" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR26" s="12">
-        <v>188182914000</v>
+        <v>193611448000</v>
       </c>
       <c r="AS26" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v54.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v31.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="27" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
@@ -4522,136 +4524,136 @@
         <v>42</v>
       </c>
       <c r="D27" s="27">
-        <v>133.04</v>
-      </c>
-      <c r="E27" s="12">
-        <v>46739833700</v>
+        <v>135.69</v>
+      </c>
+      <c r="E27" s="22">
+        <v>50447959500</v>
       </c>
       <c r="F27">
-        <v>87</v>
-      </c>
-      <c r="G27" s="34">
-        <v>32.22</v>
+        <v>94</v>
+      </c>
+      <c r="G27" s="35">
+        <v>34.81</v>
       </c>
       <c r="H27">
-        <v>40773</v>
+        <v>40738</v>
       </c>
       <c r="I27">
-        <v>3382</v>
+        <v>3222</v>
       </c>
       <c r="J27" t="s">
-        <v>60</v>
-      </c>
-      <c r="K27" s="31">
-        <v>33.700000000000003</v>
+        <v>109</v>
+      </c>
+      <c r="K27" s="34">
+        <v>30</v>
       </c>
       <c r="L27" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M27" s="31">
-        <v>64.44</v>
+        <v>67.41</v>
       </c>
       <c r="N27" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="O27" s="37">
-        <v>35.19</v>
+        <v>34.07</v>
       </c>
       <c r="P27" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="27">
-        <v>35.19</v>
+        <v>34.07</v>
       </c>
       <c r="R27" t="s">
-        <v>76</v>
-      </c>
-      <c r="S27" s="36">
-        <v>19.260000000000002</v>
+        <v>94</v>
+      </c>
+      <c r="S27" s="34">
+        <v>20</v>
       </c>
       <c r="T27" t="s">
-        <v>63</v>
-      </c>
-      <c r="U27" s="14">
-        <v>96.3</v>
+        <v>53</v>
+      </c>
+      <c r="U27" s="38">
+        <v>88.89</v>
       </c>
       <c r="V27" t="s">
-        <v>47</v>
-      </c>
-      <c r="W27" s="29">
-        <v>92.59</v>
+        <v>64</v>
+      </c>
+      <c r="W27" s="38">
+        <v>85.19</v>
       </c>
       <c r="X27">
-        <v>34769</v>
+        <v>34882</v>
       </c>
       <c r="Y27">
-        <v>3161</v>
+        <v>3002</v>
       </c>
       <c r="Z27">
-        <v>37930</v>
+        <v>37884</v>
       </c>
       <c r="AA27">
-        <v>2383</v>
+        <v>2375</v>
       </c>
       <c r="AB27">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AC27">
-        <v>2794</v>
+        <v>2802</v>
       </c>
       <c r="AD27">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AE27" s="27">
-        <v>6</v>
-      </c>
-      <c r="AF27" s="27">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="AF27" s="13">
+        <v>52</v>
       </c>
       <c r="AG27">
-        <v>128.77000000000001</v>
+        <v>129.19</v>
       </c>
       <c r="AH27">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="AI27">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="AJ27">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
       <c r="AK27">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AL27">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AM27">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AN27">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="27">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AP27">
-        <v>128.30000000000001</v>
+        <v>128.84</v>
       </c>
       <c r="AQ27" s="12">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AR27" s="12">
-        <v>188192833700</v>
+        <v>191817259500</v>
       </c>
       <c r="AS27" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v36.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v40.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="28" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
@@ -4660,52 +4662,52 @@
         <v>42</v>
       </c>
       <c r="D28" s="27">
-        <v>133.04</v>
+        <v>129.69</v>
       </c>
       <c r="E28" s="12">
-        <v>46705171100</v>
+        <v>42004271100</v>
       </c>
       <c r="F28">
-        <v>91</v>
-      </c>
-      <c r="G28" s="34">
-        <v>33.700000000000003</v>
+        <v>75</v>
+      </c>
+      <c r="G28" s="31">
+        <v>27.78</v>
       </c>
       <c r="H28">
-        <v>40727</v>
+        <v>40752</v>
       </c>
       <c r="I28">
-        <v>3298</v>
+        <v>3420</v>
       </c>
       <c r="J28" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K28" s="31">
-        <v>35.19</v>
+        <v>32.22</v>
       </c>
       <c r="L28" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="M28" s="31">
-        <v>61.48</v>
+        <v>66.67</v>
       </c>
       <c r="N28" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="O28" s="37">
-        <v>34.81</v>
+        <v>34.07</v>
       </c>
       <c r="P28" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="27">
-        <v>34.81</v>
+        <v>34.07</v>
       </c>
       <c r="R28" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="S28" s="36">
-        <v>19.63</v>
+        <v>17.04</v>
       </c>
       <c r="T28" t="s">
         <v>63</v>
@@ -4714,82 +4716,82 @@
         <v>96.3</v>
       </c>
       <c r="V28" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="W28" s="27">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="X28">
-        <v>34807</v>
+        <v>34740</v>
       </c>
       <c r="Y28">
-        <v>3071</v>
+        <v>3185</v>
       </c>
       <c r="Z28">
-        <v>37878</v>
+        <v>37925</v>
       </c>
       <c r="AA28">
-        <v>2384</v>
+        <v>2379</v>
       </c>
       <c r="AB28">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AC28">
-        <v>2801</v>
+        <v>2784</v>
       </c>
       <c r="AD28">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AE28" s="27">
         <v>2</v>
       </c>
       <c r="AF28" s="27">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AG28">
-        <v>128.91</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="AH28">
-        <v>11.37</v>
+        <v>11.8</v>
       </c>
       <c r="AI28">
-        <v>11.37</v>
+        <v>11.8</v>
       </c>
       <c r="AJ28">
-        <v>10.37</v>
+        <v>10.31</v>
       </c>
       <c r="AK28">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AL28">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AM28">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN28">
         <v>0.01</v>
       </c>
       <c r="AO28" s="27">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="AP28">
-        <v>128.53</v>
+        <v>128.16</v>
       </c>
       <c r="AQ28" s="12">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AR28" s="12">
-        <v>188074471100</v>
+        <v>183457271100</v>
       </c>
       <c r="AS28" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v26.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v34.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="29" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A29" s="27">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -4798,46 +4800,46 @@
         <v>42</v>
       </c>
       <c r="D29" s="27">
-        <v>133.02000000000001</v>
+        <v>133.11000000000001</v>
       </c>
       <c r="E29" s="12">
-        <v>46703825900</v>
+        <v>46813614000</v>
       </c>
       <c r="F29">
-        <v>80</v>
-      </c>
-      <c r="G29" s="31">
-        <v>29.63</v>
+        <v>94</v>
+      </c>
+      <c r="G29" s="35">
+        <v>34.81</v>
       </c>
       <c r="H29">
-        <v>40788</v>
+        <v>40738</v>
       </c>
       <c r="I29" s="27">
-        <v>3325</v>
+        <v>3257</v>
       </c>
       <c r="J29" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K29" s="31">
-        <v>33.33</v>
+        <v>37.04</v>
       </c>
       <c r="L29" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="M29" s="31">
-        <v>64.44</v>
+        <v>60.37</v>
       </c>
       <c r="N29" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O29" s="28">
-        <v>33.33</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="P29" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q29" s="27">
-        <v>33.33</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="R29" t="s">
         <v>57</v>
@@ -4846,10 +4848,10 @@
         <v>19.63</v>
       </c>
       <c r="T29" t="s">
-        <v>63</v>
-      </c>
-      <c r="U29" s="14">
-        <v>96.3</v>
+        <v>47</v>
+      </c>
+      <c r="U29" s="15">
+        <v>92.59</v>
       </c>
       <c r="V29" t="s">
         <v>47</v>
@@ -4858,70 +4860,70 @@
         <v>92.59</v>
       </c>
       <c r="X29">
-        <v>34843</v>
+        <v>34821</v>
       </c>
       <c r="Y29">
-        <v>3107</v>
+        <v>3063</v>
       </c>
       <c r="Z29">
-        <v>37950</v>
+        <v>37884</v>
       </c>
       <c r="AA29">
-        <v>2376</v>
+        <v>2400</v>
       </c>
       <c r="AB29">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="AC29">
-        <v>2789</v>
+        <v>2802</v>
       </c>
       <c r="AD29">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AE29" s="27">
-        <v>1</v>
-      </c>
-      <c r="AF29" s="27">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="13">
+        <v>52</v>
       </c>
       <c r="AG29">
-        <v>129.05000000000001</v>
+        <v>128.97</v>
       </c>
       <c r="AH29">
-        <v>11.51</v>
+        <v>11.34</v>
       </c>
       <c r="AI29">
-        <v>11.51</v>
+        <v>11.34</v>
       </c>
       <c r="AJ29">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="AK29">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="AL29">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="AM29">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AN29">
         <v>0</v>
       </c>
       <c r="AO29" s="27">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AP29" s="27">
-        <v>128.51</v>
+        <v>128.68</v>
       </c>
       <c r="AQ29" s="12">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AR29" s="12">
-        <v>188156825900</v>
+        <v>188182914000</v>
       </c>
       <c r="AS29" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v33.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v54.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
@@ -5065,7 +5067,7 @@
     </row>
     <row r="31" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
@@ -5074,58 +5076,58 @@
         <v>42</v>
       </c>
       <c r="D31" s="27">
-        <v>131.91</v>
+        <v>130.88</v>
       </c>
       <c r="E31" s="12">
-        <v>45116576700</v>
+        <v>43674962700</v>
       </c>
       <c r="F31">
-        <v>92</v>
-      </c>
-      <c r="G31" s="35">
-        <v>34.07</v>
+        <v>80</v>
+      </c>
+      <c r="G31" s="31">
+        <v>29.63</v>
       </c>
       <c r="H31">
-        <v>40715</v>
+        <v>40755</v>
       </c>
       <c r="I31">
-        <v>3314</v>
+        <v>3426</v>
       </c>
       <c r="J31" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="K31" s="31">
-        <v>32.22</v>
+        <v>32.96</v>
       </c>
       <c r="L31" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M31" s="31">
-        <v>65.19</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="N31" t="s">
-        <v>75</v>
-      </c>
-      <c r="O31" s="37">
-        <v>34.81</v>
+        <v>60</v>
+      </c>
+      <c r="O31" s="39">
+        <v>33.700000000000003</v>
       </c>
       <c r="P31" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q31" s="27">
-        <v>34.81</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="R31" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S31" s="36">
-        <v>19.260000000000002</v>
+        <v>16.3</v>
       </c>
       <c r="T31" t="s">
-        <v>53</v>
-      </c>
-      <c r="U31" s="27">
-        <v>88.89</v>
+        <v>47</v>
+      </c>
+      <c r="U31" s="15">
+        <v>92.59</v>
       </c>
       <c r="V31" t="s">
         <v>53</v>
@@ -5134,76 +5136,76 @@
         <v>88.89</v>
       </c>
       <c r="X31">
-        <v>34792</v>
+        <v>34723</v>
       </c>
       <c r="Y31">
-        <v>3079</v>
+        <v>3200</v>
       </c>
       <c r="Z31">
-        <v>37871</v>
+        <v>37923</v>
       </c>
       <c r="AA31">
         <v>2383</v>
       </c>
       <c r="AB31">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="AC31">
-        <v>2798</v>
+        <v>2786</v>
       </c>
       <c r="AD31">
-        <v>42</v>
-      </c>
-      <c r="AE31" s="27">
-        <v>4</v>
+        <v>39</v>
+      </c>
+      <c r="AE31" s="13">
+        <v>7</v>
       </c>
       <c r="AF31" s="27">
         <v>46</v>
       </c>
       <c r="AG31">
-        <v>128.86000000000001</v>
+        <v>128.6</v>
       </c>
       <c r="AH31">
-        <v>11.4</v>
+        <v>11.85</v>
       </c>
       <c r="AI31">
-        <v>11.4</v>
+        <v>11.85</v>
       </c>
       <c r="AJ31">
-        <v>10.36</v>
+        <v>10.32</v>
       </c>
       <c r="AK31">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="AL31">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="AM31">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN31">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AO31" s="27">
         <v>0.17</v>
       </c>
       <c r="AP31">
-        <v>128.47</v>
+        <v>128.13999999999999</v>
       </c>
       <c r="AQ31" s="12">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AR31" s="12">
-        <v>186485876700</v>
+        <v>185127962700</v>
       </c>
       <c r="AS31" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v18.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v38.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="32" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>41</v>
@@ -5212,109 +5214,109 @@
         <v>42</v>
       </c>
       <c r="D32" s="27">
-        <v>131.46</v>
+        <v>129.28</v>
       </c>
       <c r="E32" s="12">
-        <v>44470991100</v>
+        <v>41393479900</v>
       </c>
       <c r="F32">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G32" s="31">
-        <v>27.04</v>
+        <v>26.67</v>
       </c>
       <c r="H32">
-        <v>40730</v>
+        <v>40743</v>
       </c>
       <c r="I32">
-        <v>3412</v>
+        <v>3419</v>
       </c>
       <c r="J32" t="s">
-        <v>69</v>
-      </c>
-      <c r="K32" s="34">
-        <v>30.74</v>
+        <v>58</v>
+      </c>
+      <c r="K32" s="31">
+        <v>35.19</v>
       </c>
       <c r="L32" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="M32" s="31">
-        <v>67.78</v>
+        <v>62.96</v>
       </c>
       <c r="N32" t="s">
-        <v>75</v>
-      </c>
-      <c r="O32" s="37">
-        <v>34.81</v>
+        <v>60</v>
+      </c>
+      <c r="O32" s="39">
+        <v>33.700000000000003</v>
       </c>
       <c r="P32" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q32" s="27">
-        <v>34.81</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="R32" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="S32" s="36">
-        <v>17.78</v>
+        <v>18.52</v>
       </c>
       <c r="T32" t="s">
-        <v>53</v>
-      </c>
-      <c r="U32" s="27">
-        <v>88.89</v>
+        <v>47</v>
+      </c>
+      <c r="U32" s="15">
+        <v>92.59</v>
       </c>
       <c r="V32" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="W32" s="27">
-        <v>74.069999999999993</v>
+        <v>77.78</v>
       </c>
       <c r="X32">
-        <v>34737</v>
+        <v>34727</v>
       </c>
       <c r="Y32">
-        <v>3168</v>
+        <v>3194</v>
       </c>
       <c r="Z32">
-        <v>37905</v>
+        <v>37921</v>
       </c>
       <c r="AA32">
-        <v>2364</v>
+        <v>2381</v>
       </c>
       <c r="AB32">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="AC32">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="AD32">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE32" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF32" s="27">
         <v>44</v>
       </c>
       <c r="AG32">
-        <v>128.66</v>
+        <v>128.62</v>
       </c>
       <c r="AH32">
-        <v>11.73</v>
+        <v>11.83</v>
       </c>
       <c r="AI32">
-        <v>11.73</v>
+        <v>11.83</v>
       </c>
       <c r="AJ32">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="AK32">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="AL32">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="AM32">
         <v>0.15</v>
@@ -5326,22 +5328,22 @@
         <v>0.16</v>
       </c>
       <c r="AP32">
-        <v>128.11000000000001</v>
+        <v>128.09</v>
       </c>
       <c r="AQ32" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR32" s="12">
-        <v>185840291100</v>
+        <v>182762779900</v>
       </c>
       <c r="AS32" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v30.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v13.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="33" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -5350,34 +5352,34 @@
         <v>42</v>
       </c>
       <c r="D33">
-        <v>130.88</v>
+        <v>129.15</v>
       </c>
       <c r="E33" s="12">
-        <v>43674962700</v>
+        <v>41203948100</v>
       </c>
       <c r="F33">
-        <v>80</v>
-      </c>
-      <c r="G33" s="31">
-        <v>29.63</v>
+        <v>85</v>
+      </c>
+      <c r="G33" s="34">
+        <v>31.48</v>
       </c>
       <c r="H33">
-        <v>40755</v>
+        <v>40700</v>
       </c>
       <c r="I33">
-        <v>3426</v>
+        <v>3369</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
-      </c>
-      <c r="K33" s="31">
-        <v>32.96</v>
+        <v>71</v>
+      </c>
+      <c r="K33" s="34">
+        <v>29.26</v>
       </c>
       <c r="L33" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="M33" s="31">
-        <v>65.930000000000007</v>
+        <v>69.260000000000005</v>
       </c>
       <c r="N33" t="s">
         <v>60</v>
@@ -5392,94 +5394,94 @@
         <v>33.700000000000003</v>
       </c>
       <c r="R33" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="S33" s="36">
-        <v>16.3</v>
+        <v>15.93</v>
       </c>
       <c r="T33" t="s">
+        <v>70</v>
+      </c>
+      <c r="U33" s="13">
+        <v>100</v>
+      </c>
+      <c r="V33" t="s">
         <v>47</v>
       </c>
-      <c r="U33" s="15">
+      <c r="W33" s="29">
         <v>92.59</v>
       </c>
-      <c r="V33" t="s">
-        <v>53</v>
-      </c>
-      <c r="W33" s="27">
-        <v>88.89</v>
-      </c>
       <c r="X33">
-        <v>34723</v>
+        <v>34731</v>
       </c>
       <c r="Y33">
-        <v>3200</v>
+        <v>3136</v>
       </c>
       <c r="Z33">
-        <v>37923</v>
+        <v>37867</v>
       </c>
       <c r="AA33">
-        <v>2383</v>
+        <v>2389</v>
       </c>
       <c r="AB33">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AC33">
-        <v>2786</v>
+        <v>2790</v>
       </c>
       <c r="AD33">
         <v>39</v>
       </c>
-      <c r="AE33" s="13">
-        <v>7</v>
+      <c r="AE33" s="38">
+        <v>4</v>
       </c>
       <c r="AF33" s="27">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AG33">
-        <v>128.6</v>
+        <v>128.63</v>
       </c>
       <c r="AH33">
-        <v>11.85</v>
+        <v>11.61</v>
       </c>
       <c r="AI33">
-        <v>11.85</v>
+        <v>11.61</v>
       </c>
       <c r="AJ33">
-        <v>10.32</v>
+        <v>10.33</v>
       </c>
       <c r="AK33">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="AL33">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="AM33">
         <v>0.14000000000000001</v>
       </c>
       <c r="AN33">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AO33" s="27">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AP33">
-        <v>128.13999999999999</v>
+        <v>128.27000000000001</v>
       </c>
       <c r="AQ33" s="12">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AR33" s="12">
-        <v>185127962700</v>
+        <v>182573248100</v>
       </c>
       <c r="AS33" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v38.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v17.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
@@ -5488,52 +5490,52 @@
         <v>42</v>
       </c>
       <c r="D34" s="27">
-        <v>130.80000000000001</v>
+        <v>128.97</v>
       </c>
       <c r="E34" s="12">
-        <v>43544659200</v>
+        <v>40960367800</v>
       </c>
       <c r="F34">
-        <v>81</v>
-      </c>
-      <c r="G34" s="33">
-        <v>30</v>
+        <v>79</v>
+      </c>
+      <c r="G34" s="38">
+        <v>29.26</v>
       </c>
       <c r="H34">
-        <v>40732</v>
+        <v>40709</v>
       </c>
       <c r="I34">
-        <v>3363</v>
+        <v>3420</v>
       </c>
       <c r="J34" t="s">
-        <v>90</v>
-      </c>
-      <c r="K34" s="31">
-        <v>31.85</v>
+        <v>62</v>
+      </c>
+      <c r="K34" s="38">
+        <v>34.44</v>
       </c>
       <c r="L34" t="s">
-        <v>80</v>
-      </c>
-      <c r="M34" s="31">
-        <v>65.56</v>
+        <v>87</v>
+      </c>
+      <c r="M34" s="38">
+        <v>63.33</v>
       </c>
       <c r="N34" t="s">
-        <v>58</v>
-      </c>
-      <c r="O34" s="37">
-        <v>35.19</v>
+        <v>60</v>
+      </c>
+      <c r="O34" s="39">
+        <v>33.700000000000003</v>
       </c>
       <c r="P34" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q34" s="27">
-        <v>35.19</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="R34" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="S34" s="36">
-        <v>18.149999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="T34" t="s">
         <v>47</v>
@@ -5542,55 +5544,55 @@
         <v>92.59</v>
       </c>
       <c r="V34" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="W34" s="27">
-        <v>81.48</v>
+        <v>85.19</v>
       </c>
       <c r="X34">
-        <v>34767</v>
+        <v>34697</v>
       </c>
       <c r="Y34">
-        <v>3134</v>
+        <v>3186</v>
       </c>
       <c r="Z34">
-        <v>37901</v>
+        <v>37883</v>
       </c>
       <c r="AA34">
-        <v>2378</v>
+        <v>2382</v>
       </c>
       <c r="AB34">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AC34">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="AD34">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE34" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="27">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AG34">
-        <v>128.77000000000001</v>
+        <v>128.51</v>
       </c>
       <c r="AH34">
-        <v>11.61</v>
+        <v>11.8</v>
       </c>
       <c r="AI34">
-        <v>11.61</v>
+        <v>11.8</v>
       </c>
       <c r="AJ34">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
       <c r="AK34">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="AL34">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="AM34">
         <v>0.16</v>
@@ -5599,25 +5601,25 @@
         <v>0</v>
       </c>
       <c r="AO34" s="27">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AP34">
-        <v>128.29</v>
+        <v>128.08000000000001</v>
       </c>
       <c r="AQ34" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR34" s="12">
-        <v>184913959200</v>
-      </c>
-      <c r="AS34" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v25.txt", "Click view")</f>
+        <v>182329667800</v>
+      </c>
+      <c r="AS34" s="38" t="str">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v56.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -5626,28 +5628,28 @@
         <v>42</v>
       </c>
       <c r="D35" s="27">
-        <v>130.44</v>
+        <v>134.13999999999999</v>
       </c>
       <c r="E35" s="12">
-        <v>43026460900</v>
+        <v>48261703300</v>
       </c>
       <c r="F35">
-        <v>80</v>
-      </c>
-      <c r="G35" s="31">
-        <v>29.63</v>
+        <v>95</v>
+      </c>
+      <c r="G35" s="35">
+        <v>35.19</v>
       </c>
       <c r="H35">
-        <v>40707</v>
+        <v>40740</v>
       </c>
       <c r="I35">
-        <v>3470</v>
+        <v>3322</v>
       </c>
       <c r="J35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K35" s="31">
-        <v>34.44</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="L35" t="s">
         <v>59</v>
@@ -5656,106 +5658,106 @@
         <v>62.96</v>
       </c>
       <c r="N35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O35" s="28">
-        <v>35.19</v>
+        <v>33.33</v>
       </c>
       <c r="P35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q35" s="27">
-        <v>35.19</v>
+        <v>33.33</v>
       </c>
       <c r="R35" t="s">
-        <v>61</v>
-      </c>
-      <c r="S35" s="36">
-        <v>18.52</v>
+        <v>94</v>
+      </c>
+      <c r="S35" s="34">
+        <v>20</v>
       </c>
       <c r="T35" t="s">
-        <v>63</v>
-      </c>
-      <c r="U35" s="14">
-        <v>96.3</v>
+        <v>70</v>
+      </c>
+      <c r="U35" s="13">
+        <v>100</v>
       </c>
       <c r="V35" t="s">
-        <v>64</v>
-      </c>
-      <c r="W35" s="27">
-        <v>85.19</v>
+        <v>70</v>
+      </c>
+      <c r="W35" s="13">
+        <v>100</v>
       </c>
       <c r="X35">
-        <v>34638</v>
+        <v>34772</v>
       </c>
       <c r="Y35">
-        <v>3239</v>
+        <v>3112</v>
       </c>
       <c r="Z35">
-        <v>37877</v>
+        <v>37884</v>
       </c>
       <c r="AA35">
-        <v>2381</v>
+        <v>2392</v>
       </c>
       <c r="AB35">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="AC35">
-        <v>2786</v>
+        <v>2805</v>
       </c>
       <c r="AD35">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AE35">
-        <v>2</v>
-      </c>
-      <c r="AF35" s="27">
-        <v>44</v>
+        <v>1</v>
+      </c>
+      <c r="AF35" s="13">
+        <v>51</v>
       </c>
       <c r="AG35">
-        <v>128.29</v>
+        <v>128.79</v>
       </c>
       <c r="AH35">
-        <v>12</v>
+        <v>11.53</v>
       </c>
       <c r="AI35">
-        <v>12</v>
+        <v>11.53</v>
       </c>
       <c r="AJ35">
-        <v>10.32</v>
+        <v>10.39</v>
       </c>
       <c r="AK35">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AL35">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AM35">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AN35">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO35" s="27">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AP35">
-        <v>127.9</v>
+        <v>128.44</v>
       </c>
       <c r="AQ35" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR35" s="12">
-        <v>184395760900</v>
+        <v>189631003300</v>
       </c>
       <c r="AS35" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v14.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v27.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>41</v>
@@ -5764,52 +5766,52 @@
         <v>42</v>
       </c>
       <c r="D36" s="27">
-        <v>129.69</v>
+        <v>133.02000000000001</v>
       </c>
       <c r="E36" s="12">
-        <v>42004271100</v>
+        <v>46703825900</v>
       </c>
       <c r="F36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G36" s="31">
-        <v>27.78</v>
+        <v>29.63</v>
       </c>
       <c r="H36">
-        <v>40752</v>
+        <v>40788</v>
       </c>
       <c r="I36">
-        <v>3420</v>
+        <v>3325</v>
       </c>
       <c r="J36" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="K36" s="31">
-        <v>32.22</v>
+        <v>33.33</v>
       </c>
       <c r="L36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M36" s="31">
-        <v>66.67</v>
+        <v>64.44</v>
       </c>
       <c r="N36" t="s">
-        <v>106</v>
-      </c>
-      <c r="O36" s="37">
-        <v>34.07</v>
+        <v>55</v>
+      </c>
+      <c r="O36" s="39">
+        <v>33.33</v>
       </c>
       <c r="P36" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="Q36" s="27">
-        <v>34.07</v>
+        <v>33.33</v>
       </c>
       <c r="R36" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="S36" s="36">
-        <v>17.04</v>
+        <v>19.63</v>
       </c>
       <c r="T36" t="s">
         <v>63</v>
@@ -5818,82 +5820,82 @@
         <v>96.3</v>
       </c>
       <c r="V36" t="s">
-        <v>53</v>
-      </c>
-      <c r="W36" s="27">
-        <v>88.89</v>
+        <v>47</v>
+      </c>
+      <c r="W36" s="29">
+        <v>92.59</v>
       </c>
       <c r="X36">
-        <v>34740</v>
+        <v>34843</v>
       </c>
       <c r="Y36">
-        <v>3185</v>
+        <v>3107</v>
       </c>
       <c r="Z36">
-        <v>37925</v>
+        <v>37950</v>
       </c>
       <c r="AA36">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="AB36">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="AC36">
-        <v>2784</v>
+        <v>2789</v>
       </c>
       <c r="AD36">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="AE36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF36" s="27">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AG36">
-        <v>128.66999999999999</v>
+        <v>129.05000000000001</v>
       </c>
       <c r="AH36">
-        <v>11.8</v>
+        <v>11.51</v>
       </c>
       <c r="AI36">
-        <v>11.8</v>
+        <v>11.51</v>
       </c>
       <c r="AJ36">
-        <v>10.31</v>
+        <v>10.33</v>
       </c>
       <c r="AK36">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AL36">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AM36">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="AN36">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO36" s="27">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="AP36">
-        <v>128.16</v>
+        <v>128.51</v>
       </c>
       <c r="AQ36" s="12">
         <v>141453000000</v>
       </c>
       <c r="AR36" s="12">
-        <v>183457271100</v>
+        <v>188156825900</v>
       </c>
       <c r="AS36" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v34.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v33.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
@@ -5902,136 +5904,136 @@
         <v>42</v>
       </c>
       <c r="D37" s="27">
-        <v>129.31</v>
+        <v>135.02000000000001</v>
       </c>
       <c r="E37" s="12">
-        <v>41428724000</v>
+        <v>49501097300</v>
       </c>
       <c r="F37">
-        <v>90</v>
-      </c>
-      <c r="G37" s="34">
-        <v>33.33</v>
+        <v>94</v>
+      </c>
+      <c r="G37" s="35">
+        <v>34.81</v>
       </c>
       <c r="H37">
-        <v>40733</v>
+        <v>40738</v>
       </c>
       <c r="I37">
-        <v>3334</v>
+        <v>3379</v>
       </c>
       <c r="J37" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="K37" s="31">
-        <v>34.44</v>
+        <v>31.11</v>
       </c>
       <c r="L37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37" s="31">
+        <v>67.41</v>
+      </c>
+      <c r="N37" t="s">
+        <v>97</v>
+      </c>
+      <c r="O37" s="28">
+        <v>32.96</v>
+      </c>
+      <c r="P37" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q37" s="27">
+        <v>32.96</v>
+      </c>
+      <c r="R37" t="s">
+        <v>76</v>
+      </c>
+      <c r="S37" s="36">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="T37" t="s">
+        <v>47</v>
+      </c>
+      <c r="U37" s="15">
+        <v>92.59</v>
+      </c>
+      <c r="V37" t="s">
+        <v>64</v>
+      </c>
+      <c r="W37" s="27">
+        <v>85.19</v>
+      </c>
+      <c r="X37">
+        <v>34714</v>
+      </c>
+      <c r="Y37">
+        <v>3170</v>
+      </c>
+      <c r="Z37">
+        <v>37884</v>
+      </c>
+      <c r="AA37">
+        <v>2387</v>
+      </c>
+      <c r="AB37">
+        <v>207</v>
+      </c>
+      <c r="AC37">
+        <v>2802</v>
+      </c>
+      <c r="AD37">
         <v>50</v>
-      </c>
-      <c r="M37" s="31">
-        <v>62.22</v>
-      </c>
-      <c r="N37" t="s">
-        <v>91</v>
-      </c>
-      <c r="O37" s="28">
-        <v>31.11</v>
-      </c>
-      <c r="P37" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q37" s="27">
-        <v>31.11</v>
-      </c>
-      <c r="R37" t="s">
-        <v>92</v>
-      </c>
-      <c r="S37" s="36">
-        <v>18.149999999999999</v>
-      </c>
-      <c r="T37" t="s">
-        <v>63</v>
-      </c>
-      <c r="U37" s="14">
-        <v>96.3</v>
-      </c>
-      <c r="V37" t="s">
-        <v>53</v>
-      </c>
-      <c r="W37" s="27">
-        <v>88.89</v>
-      </c>
-      <c r="X37">
-        <v>34756</v>
-      </c>
-      <c r="Y37">
-        <v>3134</v>
-      </c>
-      <c r="Z37">
-        <v>37890</v>
-      </c>
-      <c r="AA37">
-        <v>2410</v>
-      </c>
-      <c r="AB37">
-        <v>198</v>
-      </c>
-      <c r="AC37">
-        <v>2796</v>
-      </c>
-      <c r="AD37">
-        <v>45</v>
       </c>
       <c r="AE37">
         <v>2</v>
       </c>
-      <c r="AF37" s="27">
-        <v>47</v>
+      <c r="AF37" s="13">
+        <v>52</v>
       </c>
       <c r="AG37">
-        <v>128.72999999999999</v>
+        <v>128.57</v>
       </c>
       <c r="AH37">
-        <v>11.61</v>
+        <v>11.74</v>
       </c>
       <c r="AI37">
-        <v>11.61</v>
+        <v>11.74</v>
       </c>
       <c r="AJ37">
-        <v>10.36</v>
+        <v>10.38</v>
       </c>
       <c r="AK37">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AL37">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AM37">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AN37">
         <v>0.01</v>
       </c>
       <c r="AO37" s="27">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AP37">
-        <v>128.4</v>
+        <v>128.22</v>
       </c>
       <c r="AQ37" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR37" s="12">
-        <v>182798024000</v>
+        <v>190870397300</v>
       </c>
       <c r="AS37" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v28.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v42.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -6040,136 +6042,136 @@
         <v>42</v>
       </c>
       <c r="D38" s="27">
-        <v>129.28</v>
+        <v>134.38999999999999</v>
       </c>
       <c r="E38" s="12">
-        <v>41393479900</v>
+        <v>48611685100</v>
       </c>
       <c r="F38">
-        <v>72</v>
-      </c>
-      <c r="G38" s="31">
-        <v>26.67</v>
+        <v>94</v>
+      </c>
+      <c r="G38" s="35">
+        <v>34.81</v>
       </c>
       <c r="H38">
-        <v>40743</v>
+        <v>40738</v>
       </c>
       <c r="I38">
-        <v>3419</v>
+        <v>3283</v>
       </c>
       <c r="J38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K38" s="31">
-        <v>35.19</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="L38" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="M38" s="31">
-        <v>62.96</v>
+        <v>64.44</v>
       </c>
       <c r="N38" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="O38" s="28">
-        <v>33.700000000000003</v>
+        <v>32.96</v>
       </c>
       <c r="P38" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="Q38" s="27">
-        <v>33.700000000000003</v>
+        <v>32.96</v>
       </c>
       <c r="R38" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="S38" s="36">
-        <v>18.52</v>
+        <v>19.63</v>
       </c>
       <c r="T38" t="s">
+        <v>53</v>
+      </c>
+      <c r="U38" s="38">
+        <v>88.89</v>
+      </c>
+      <c r="V38" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="27">
+        <v>88.89</v>
+      </c>
+      <c r="X38">
+        <v>34811</v>
+      </c>
+      <c r="Y38">
+        <v>3073</v>
+      </c>
+      <c r="Z38">
+        <v>37884</v>
+      </c>
+      <c r="AA38">
+        <v>2389</v>
+      </c>
+      <c r="AB38">
+        <v>205</v>
+      </c>
+      <c r="AC38">
+        <v>2802</v>
+      </c>
+      <c r="AD38">
         <v>47</v>
       </c>
-      <c r="U38" s="15">
-        <v>92.59</v>
-      </c>
-      <c r="V38" t="s">
-        <v>54</v>
-      </c>
-      <c r="W38" s="27">
-        <v>77.78</v>
-      </c>
-      <c r="X38">
-        <v>34727</v>
-      </c>
-      <c r="Y38">
-        <v>3194</v>
-      </c>
-      <c r="Z38">
-        <v>37921</v>
-      </c>
-      <c r="AA38">
-        <v>2381</v>
-      </c>
-      <c r="AB38">
-        <v>221</v>
-      </c>
-      <c r="AC38">
-        <v>2778</v>
-      </c>
-      <c r="AD38">
-        <v>40</v>
-      </c>
       <c r="AE38" s="27">
-        <v>4</v>
-      </c>
-      <c r="AF38" s="27">
-        <v>44</v>
+        <v>5</v>
+      </c>
+      <c r="AF38" s="13">
+        <v>52</v>
       </c>
       <c r="AG38">
-        <v>128.62</v>
+        <v>128.93</v>
       </c>
       <c r="AH38">
-        <v>11.83</v>
+        <v>11.38</v>
       </c>
       <c r="AI38">
-        <v>11.83</v>
+        <v>11.38</v>
       </c>
       <c r="AJ38">
-        <v>10.29</v>
+        <v>10.38</v>
       </c>
       <c r="AK38">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="AL38">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="AM38">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="AN38">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AO38" s="27">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AP38">
-        <v>128.09</v>
+        <v>128.61000000000001</v>
       </c>
       <c r="AQ38" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR38" s="12">
-        <v>182762779900</v>
+        <v>189980985100</v>
       </c>
       <c r="AS38" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v13.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v44.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>41</v>
@@ -6178,136 +6180,136 @@
         <v>42</v>
       </c>
       <c r="D39" s="27">
-        <v>129.15</v>
+        <v>134.38</v>
       </c>
       <c r="E39" s="12">
-        <v>41203948100</v>
+        <v>48607784700</v>
       </c>
       <c r="F39">
-        <v>85</v>
-      </c>
-      <c r="G39" s="34">
-        <v>31.48</v>
+        <v>94</v>
+      </c>
+      <c r="G39" s="35">
+        <v>34.81</v>
       </c>
       <c r="H39">
-        <v>40700</v>
+        <v>40738</v>
       </c>
       <c r="I39">
-        <v>3369</v>
+        <v>3393</v>
       </c>
       <c r="J39" t="s">
-        <v>71</v>
-      </c>
-      <c r="K39" s="34">
-        <v>29.26</v>
+        <v>45</v>
+      </c>
+      <c r="K39" s="31">
+        <v>35.93</v>
       </c>
       <c r="L39" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="M39" s="31">
-        <v>69.260000000000005</v>
+        <v>61.11</v>
       </c>
       <c r="N39" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="O39" s="28">
-        <v>33.700000000000003</v>
+        <v>32.96</v>
       </c>
       <c r="P39" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="27">
-        <v>33.700000000000003</v>
+        <v>32.96</v>
       </c>
       <c r="R39" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="S39" s="36">
-        <v>15.93</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="T39" t="s">
-        <v>70</v>
-      </c>
-      <c r="U39" s="13">
-        <v>100</v>
+        <v>63</v>
+      </c>
+      <c r="U39" s="14">
+        <v>96.3</v>
       </c>
       <c r="V39" t="s">
-        <v>47</v>
-      </c>
-      <c r="W39" s="29">
-        <v>92.59</v>
+        <v>64</v>
+      </c>
+      <c r="W39" s="38">
+        <v>85.19</v>
       </c>
       <c r="X39">
-        <v>34731</v>
+        <v>34700</v>
       </c>
       <c r="Y39">
-        <v>3136</v>
+        <v>3184</v>
       </c>
       <c r="Z39">
-        <v>37867</v>
+        <v>37884</v>
       </c>
       <c r="AA39">
-        <v>2389</v>
+        <v>2393</v>
       </c>
       <c r="AB39">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="AC39">
-        <v>2790</v>
+        <v>2802</v>
       </c>
       <c r="AD39">
-        <v>39</v>
-      </c>
-      <c r="AE39" s="27">
-        <v>4</v>
-      </c>
-      <c r="AF39" s="27">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="AE39" s="13">
+        <v>8</v>
+      </c>
+      <c r="AF39" s="13">
+        <v>52</v>
       </c>
       <c r="AG39">
-        <v>128.63</v>
+        <v>128.52000000000001</v>
       </c>
       <c r="AH39">
-        <v>11.61</v>
+        <v>11.79</v>
       </c>
       <c r="AI39">
-        <v>11.61</v>
+        <v>11.79</v>
       </c>
       <c r="AJ39">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="AK39">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AL39">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AM39">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="AN39">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AO39" s="27">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="AP39">
-        <v>128.27000000000001</v>
+        <v>128.22</v>
       </c>
       <c r="AQ39" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR39" s="12">
-        <v>182573248100</v>
+        <v>189977084700</v>
       </c>
       <c r="AS39" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v17.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v52.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
@@ -6316,136 +6318,136 @@
         <v>42</v>
       </c>
       <c r="D40" s="27">
-        <v>128.97</v>
+        <v>126.94</v>
       </c>
       <c r="E40" s="12">
-        <v>40960367800</v>
+        <v>38080818300</v>
       </c>
       <c r="F40">
-        <v>79</v>
-      </c>
-      <c r="G40" s="27">
-        <v>29.26</v>
+        <v>96</v>
+      </c>
+      <c r="G40" s="35">
+        <v>35.56</v>
       </c>
       <c r="H40">
-        <v>40709</v>
+        <v>40684</v>
       </c>
       <c r="I40">
-        <v>3420</v>
+        <v>3338</v>
       </c>
       <c r="J40" t="s">
-        <v>62</v>
-      </c>
-      <c r="K40" s="27">
-        <v>34.44</v>
+        <v>95</v>
+      </c>
+      <c r="K40" s="31">
+        <v>32.590000000000003</v>
       </c>
       <c r="L40" t="s">
-        <v>87</v>
-      </c>
-      <c r="M40" s="27">
-        <v>63.33</v>
+        <v>96</v>
+      </c>
+      <c r="M40" s="31">
+        <v>64.81</v>
       </c>
       <c r="N40" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="O40" s="28">
-        <v>33.700000000000003</v>
+        <v>32.96</v>
       </c>
       <c r="P40" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="Q40" s="27">
-        <v>33.700000000000003</v>
+        <v>32.96</v>
       </c>
       <c r="R40" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="S40" s="36">
-        <v>17.04</v>
+        <v>16.3</v>
       </c>
       <c r="T40" t="s">
-        <v>47</v>
-      </c>
-      <c r="U40" s="15">
-        <v>92.59</v>
+        <v>53</v>
+      </c>
+      <c r="U40" s="38">
+        <v>88.89</v>
       </c>
       <c r="V40" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="W40" s="27">
-        <v>85.19</v>
+        <v>77.78</v>
       </c>
       <c r="X40">
-        <v>34697</v>
+        <v>34728</v>
       </c>
       <c r="Y40">
-        <v>3186</v>
+        <v>3109</v>
       </c>
       <c r="Z40">
-        <v>37883</v>
+        <v>37837</v>
       </c>
       <c r="AA40">
-        <v>2382</v>
+        <v>2417</v>
       </c>
       <c r="AB40">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AC40">
-        <v>2784</v>
+        <v>2806</v>
       </c>
       <c r="AD40">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AE40" s="27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF40" s="27">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AG40">
-        <v>128.51</v>
+        <v>128.62</v>
       </c>
       <c r="AH40">
-        <v>11.8</v>
+        <v>11.51</v>
       </c>
       <c r="AI40">
-        <v>11.8</v>
+        <v>11.51</v>
       </c>
       <c r="AJ40">
-        <v>10.31</v>
+        <v>10.39</v>
       </c>
       <c r="AK40">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AL40">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AM40">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO40" s="27">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AP40">
-        <v>128.08000000000001</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AQ40" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR40" s="12">
-        <v>182329667800</v>
-      </c>
-      <c r="AS40" s="27" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v56.txt", "Click view")</f>
+        <v>179450118300</v>
+      </c>
+      <c r="AS40" s="25" t="str">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v29.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
         <v>41</v>
@@ -6454,136 +6456,136 @@
         <v>42</v>
       </c>
       <c r="D41" s="27">
-        <v>127.01</v>
+        <v>124.87</v>
       </c>
       <c r="E41" s="12">
-        <v>38200519700</v>
+        <v>35183862900</v>
       </c>
       <c r="F41">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G41" s="31">
-        <v>27.41</v>
+        <v>30.74</v>
       </c>
       <c r="H41">
-        <v>40759</v>
+        <v>40718</v>
       </c>
       <c r="I41">
-        <v>3357</v>
+        <v>3381</v>
       </c>
       <c r="J41" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="K41" s="31">
-        <v>34.81</v>
+        <v>37.04</v>
       </c>
       <c r="L41" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M41" s="31">
-        <v>64.44</v>
+        <v>62.59</v>
       </c>
       <c r="N41" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O41" s="28">
-        <v>30.37</v>
+        <v>32.96</v>
       </c>
       <c r="P41" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="Q41" s="27">
-        <v>30.37</v>
+        <v>32.96</v>
       </c>
       <c r="R41" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="S41" s="36">
-        <v>17.04</v>
+        <v>15.56</v>
       </c>
       <c r="T41" t="s">
-        <v>63</v>
-      </c>
-      <c r="U41" s="14">
-        <v>96.3</v>
+        <v>53</v>
+      </c>
+      <c r="U41" s="38">
+        <v>88.89</v>
       </c>
       <c r="V41" t="s">
-        <v>47</v>
-      </c>
-      <c r="W41" s="29">
-        <v>92.59</v>
+        <v>54</v>
+      </c>
+      <c r="W41" s="38">
+        <v>77.78</v>
       </c>
       <c r="X41">
-        <v>34793</v>
+        <v>34731</v>
       </c>
       <c r="Y41">
-        <v>3142</v>
+        <v>3161</v>
       </c>
       <c r="Z41">
-        <v>37935</v>
+        <v>37892</v>
       </c>
       <c r="AA41">
-        <v>2398</v>
+        <v>2411</v>
       </c>
       <c r="AB41">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AC41">
-        <v>2781</v>
+        <v>2786</v>
       </c>
       <c r="AD41">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AE41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF41" s="27">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AG41">
-        <v>128.86000000000001</v>
+        <v>128.63</v>
       </c>
       <c r="AH41">
-        <v>11.64</v>
+        <v>11.71</v>
       </c>
       <c r="AI41">
-        <v>11.64</v>
+        <v>11.71</v>
       </c>
       <c r="AJ41">
-        <v>10.3</v>
+        <v>10.32</v>
       </c>
       <c r="AK41">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AL41">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AM41">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AN41">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AO41" s="27">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AP41">
-        <v>128.38999999999999</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="AQ41" s="12">
         <v>141453000000</v>
       </c>
       <c r="AR41" s="12">
-        <v>179653519700</v>
+        <v>176636862900</v>
       </c>
       <c r="AS41" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v35.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v37.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
         <v>41</v>
@@ -6592,136 +6594,136 @@
         <v>42</v>
       </c>
       <c r="D42">
-        <v>126.94</v>
+        <v>124.24</v>
       </c>
       <c r="E42" s="12">
-        <v>38080818300</v>
+        <v>34261464900</v>
       </c>
       <c r="F42">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G42" s="35">
+        <v>38.520000000000003</v>
+      </c>
+      <c r="H42">
+        <v>40635</v>
+      </c>
+      <c r="I42">
+        <v>3414</v>
+      </c>
+      <c r="J42" t="s">
+        <v>86</v>
+      </c>
+      <c r="K42" s="31">
         <v>35.56</v>
       </c>
-      <c r="H42">
-        <v>40684</v>
-      </c>
-      <c r="I42">
-        <v>3338</v>
-      </c>
-      <c r="J42" t="s">
-        <v>95</v>
-      </c>
-      <c r="K42" s="31">
-        <v>32.590000000000003</v>
-      </c>
       <c r="L42" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="M42" s="31">
-        <v>64.81</v>
+        <v>63.33</v>
       </c>
       <c r="N42" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="O42" s="28">
-        <v>32.96</v>
+        <v>32.22</v>
       </c>
       <c r="P42" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="Q42" s="27">
-        <v>32.96</v>
+        <v>32.22</v>
       </c>
       <c r="R42" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="S42" s="36">
-        <v>16.3</v>
+        <v>15.56</v>
       </c>
       <c r="T42" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="U42" s="27">
-        <v>88.89</v>
+        <v>81.48</v>
       </c>
       <c r="V42" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="W42" s="27">
-        <v>77.78</v>
+        <v>70.37</v>
       </c>
       <c r="X42">
-        <v>34728</v>
+        <v>34581</v>
       </c>
       <c r="Y42">
-        <v>3109</v>
+        <v>3200</v>
       </c>
       <c r="Z42">
-        <v>37837</v>
+        <v>37781</v>
       </c>
       <c r="AA42">
-        <v>2417</v>
+        <v>2446</v>
       </c>
       <c r="AB42">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AC42">
-        <v>2806</v>
+        <v>2815</v>
       </c>
       <c r="AD42">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AE42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF42" s="27">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG42">
-        <v>128.62</v>
+        <v>128.08000000000001</v>
       </c>
       <c r="AH42">
-        <v>11.51</v>
+        <v>11.85</v>
       </c>
       <c r="AI42">
-        <v>11.51</v>
+        <v>11.85</v>
       </c>
       <c r="AJ42">
-        <v>10.39</v>
+        <v>10.43</v>
       </c>
       <c r="AK42">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AL42">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AM42">
         <v>0.14000000000000001</v>
       </c>
       <c r="AN42">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AO42" s="27">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AP42">
-        <v>128.38999999999999</v>
+        <v>128.1</v>
       </c>
       <c r="AQ42" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR42" s="12">
-        <v>179450118300</v>
+        <v>175630764900</v>
       </c>
       <c r="AS42" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v29.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v22.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
         <v>41</v>
@@ -6730,10 +6732,10 @@
         <v>42</v>
       </c>
       <c r="D43" s="27">
-        <v>126.55</v>
+        <v>123.59</v>
       </c>
       <c r="E43" s="12">
-        <v>37553095700</v>
+        <v>33350136600</v>
       </c>
       <c r="F43">
         <v>81</v>
@@ -6742,16 +6744,16 @@
         <v>30</v>
       </c>
       <c r="H43">
-        <v>40737</v>
+        <v>40670</v>
       </c>
       <c r="I43">
-        <v>3458</v>
+        <v>3413</v>
       </c>
       <c r="J43" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="K43" s="31">
-        <v>32.96</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="L43" t="s">
         <v>80</v>
@@ -6760,106 +6762,106 @@
         <v>65.56</v>
       </c>
       <c r="N43" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="O43" s="28">
-        <v>30</v>
+        <v>31.85</v>
       </c>
       <c r="P43" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="Q43" s="27">
-        <v>30</v>
+        <v>31.85</v>
       </c>
       <c r="R43" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="S43" s="36">
-        <v>14.81</v>
+        <v>14.07</v>
       </c>
       <c r="T43" t="s">
-        <v>48</v>
-      </c>
-      <c r="U43" s="27">
-        <v>81.48</v>
+        <v>47</v>
+      </c>
+      <c r="U43" s="15">
+        <v>92.59</v>
       </c>
       <c r="V43" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="W43" s="27">
-        <v>74.069999999999993</v>
+        <v>70.37</v>
       </c>
       <c r="X43">
-        <v>34673</v>
+        <v>34661</v>
       </c>
       <c r="Y43">
-        <v>3237</v>
+        <v>3184</v>
       </c>
       <c r="Z43">
-        <v>37910</v>
+        <v>37845</v>
       </c>
       <c r="AA43">
-        <v>2403</v>
+        <v>2414</v>
       </c>
       <c r="AB43">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AC43">
-        <v>2786</v>
+        <v>2788</v>
       </c>
       <c r="AD43">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AE43" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF43" s="27">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AG43">
-        <v>128.41999999999999</v>
+        <v>128.37</v>
       </c>
       <c r="AH43">
-        <v>11.99</v>
+        <v>11.79</v>
       </c>
       <c r="AI43">
-        <v>11.99</v>
+        <v>11.79</v>
       </c>
       <c r="AJ43">
-        <v>10.32</v>
+        <v>10.33</v>
       </c>
       <c r="AK43">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="AL43">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="AM43">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AN43">
         <v>0.01</v>
       </c>
       <c r="AO43" s="27">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AP43">
-        <v>128.02000000000001</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="AQ43" s="12">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AR43" s="12">
-        <v>179006095700</v>
+        <v>174719436600</v>
       </c>
       <c r="AS43" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v39.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v23.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
         <v>41</v>
@@ -6868,52 +6870,52 @@
         <v>42</v>
       </c>
       <c r="D44" s="27">
-        <v>124.87</v>
+        <v>122.59</v>
       </c>
       <c r="E44" s="12">
-        <v>35183862900</v>
+        <v>31933342100</v>
       </c>
       <c r="F44">
-        <v>83</v>
-      </c>
-      <c r="G44" s="31">
-        <v>30.74</v>
+        <v>84</v>
+      </c>
+      <c r="G44" s="34">
+        <v>31.11</v>
       </c>
       <c r="H44">
-        <v>40718</v>
+        <v>40700</v>
       </c>
       <c r="I44">
-        <v>3381</v>
+        <v>3338</v>
       </c>
       <c r="J44" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="K44" s="31">
-        <v>37.04</v>
+        <v>37.409999999999997</v>
       </c>
       <c r="L44" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="M44" s="31">
-        <v>62.59</v>
+        <v>60.74</v>
       </c>
       <c r="N44" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="O44" s="28">
-        <v>32.96</v>
+        <v>31.48</v>
       </c>
       <c r="P44" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="Q44" s="27">
-        <v>32.96</v>
+        <v>31.48</v>
       </c>
       <c r="R44" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="S44" s="36">
-        <v>15.56</v>
+        <v>15.19</v>
       </c>
       <c r="T44" t="s">
         <v>53</v>
@@ -6922,82 +6924,82 @@
         <v>88.89</v>
       </c>
       <c r="V44" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="W44" s="27">
-        <v>77.78</v>
+        <v>81.48</v>
       </c>
       <c r="X44">
-        <v>34731</v>
+        <v>34741</v>
       </c>
       <c r="Y44">
-        <v>3161</v>
+        <v>3132</v>
       </c>
       <c r="Z44">
-        <v>37892</v>
+        <v>37873</v>
       </c>
       <c r="AA44">
-        <v>2411</v>
+        <v>2429</v>
       </c>
       <c r="AB44">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="AC44">
-        <v>2786</v>
+        <v>2788</v>
       </c>
       <c r="AD44">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AE44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF44" s="27">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AG44">
-        <v>128.63</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="AH44">
-        <v>11.71</v>
+        <v>11.6</v>
       </c>
       <c r="AI44">
-        <v>11.71</v>
+        <v>11.6</v>
       </c>
       <c r="AJ44">
-        <v>10.32</v>
+        <v>10.33</v>
       </c>
       <c r="AK44">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AL44">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AM44">
         <v>0.13</v>
       </c>
       <c r="AN44">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AO44">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AP44">
-        <v>128.30000000000001</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AQ44" s="12">
-        <v>141453000000</v>
+        <v>141369300000</v>
       </c>
       <c r="AR44" s="12">
-        <v>176636862900</v>
+        <v>173302642100</v>
       </c>
       <c r="AS44" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v37.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v19.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
         <v>41</v>
@@ -7006,130 +7008,130 @@
         <v>42</v>
       </c>
       <c r="D45" s="27">
-        <v>124.24</v>
+        <v>129.31</v>
       </c>
       <c r="E45" s="12">
-        <v>34261464900</v>
+        <v>41428724000</v>
       </c>
       <c r="F45">
-        <v>104</v>
-      </c>
-      <c r="G45" s="35">
-        <v>38.520000000000003</v>
+        <v>90</v>
+      </c>
+      <c r="G45" s="34">
+        <v>33.33</v>
       </c>
       <c r="H45">
-        <v>40635</v>
+        <v>40733</v>
       </c>
       <c r="I45">
-        <v>3414</v>
+        <v>3334</v>
       </c>
       <c r="J45" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="K45" s="31">
-        <v>35.56</v>
+        <v>34.44</v>
       </c>
       <c r="L45" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="M45" s="31">
-        <v>63.33</v>
+        <v>62.22</v>
       </c>
       <c r="N45" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="O45" s="28">
-        <v>32.22</v>
+        <v>31.11</v>
       </c>
       <c r="P45" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="Q45">
-        <v>32.22</v>
+        <v>31.11</v>
       </c>
       <c r="R45" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S45" s="36">
-        <v>15.56</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="T45" t="s">
-        <v>48</v>
-      </c>
-      <c r="U45" s="27">
-        <v>81.48</v>
+        <v>63</v>
+      </c>
+      <c r="U45" s="14">
+        <v>96.3</v>
       </c>
       <c r="V45" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="W45" s="27">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="X45">
-        <v>34581</v>
+        <v>34756</v>
       </c>
       <c r="Y45">
-        <v>3200</v>
+        <v>3134</v>
       </c>
       <c r="Z45">
-        <v>37781</v>
+        <v>37890</v>
       </c>
       <c r="AA45">
-        <v>2446</v>
+        <v>2410</v>
       </c>
       <c r="AB45">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AC45">
-        <v>2815</v>
+        <v>2796</v>
       </c>
       <c r="AD45">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AE45" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF45" s="27">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="AG45">
-        <v>128.08000000000001</v>
+        <v>128.72999999999999</v>
       </c>
       <c r="AH45">
-        <v>11.85</v>
+        <v>11.61</v>
       </c>
       <c r="AI45">
-        <v>11.85</v>
+        <v>11.61</v>
       </c>
       <c r="AJ45">
-        <v>10.43</v>
+        <v>10.36</v>
       </c>
       <c r="AK45">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AL45">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AM45">
-        <v>0.14000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="AN45">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO45" s="27">
-        <v>0.14000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="AP45">
-        <v>128.1</v>
+        <v>128.4</v>
       </c>
       <c r="AQ45" s="12">
         <v>141369300000</v>
       </c>
       <c r="AR45" s="12">
-        <v>175630764900</v>
+        <v>182798024000</v>
       </c>
       <c r="AS45" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v22.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v28.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
@@ -7273,7 +7275,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
         <v>41</v>
@@ -7282,136 +7284,136 @@
         <v>42</v>
       </c>
       <c r="D47" s="27">
-        <v>123.59</v>
+        <v>127.01</v>
       </c>
       <c r="E47" s="12">
-        <v>33350136600</v>
+        <v>38200519700</v>
       </c>
       <c r="F47">
-        <v>81</v>
-      </c>
-      <c r="G47" s="33">
-        <v>30</v>
+        <v>74</v>
+      </c>
+      <c r="G47" s="31">
+        <v>27.41</v>
       </c>
       <c r="H47">
-        <v>40670</v>
+        <v>40759</v>
       </c>
       <c r="I47">
-        <v>3413</v>
+        <v>3357</v>
       </c>
       <c r="J47" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="K47" s="31">
-        <v>33.700000000000003</v>
+        <v>34.81</v>
       </c>
       <c r="L47" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="M47" s="31">
-        <v>65.56</v>
+        <v>64.44</v>
       </c>
       <c r="N47" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="O47" s="28">
-        <v>31.85</v>
+        <v>30.37</v>
       </c>
       <c r="P47" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="Q47" s="27">
-        <v>31.85</v>
+        <v>30.37</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="S47" s="36">
-        <v>14.07</v>
+        <v>17.04</v>
       </c>
       <c r="T47" t="s">
+        <v>63</v>
+      </c>
+      <c r="U47" s="14">
+        <v>96.3</v>
+      </c>
+      <c r="V47" t="s">
         <v>47</v>
       </c>
-      <c r="U47" s="15">
+      <c r="W47" s="29">
         <v>92.59</v>
       </c>
-      <c r="V47" t="s">
-        <v>89</v>
-      </c>
-      <c r="W47" s="27">
-        <v>70.37</v>
-      </c>
       <c r="X47">
-        <v>34661</v>
+        <v>34793</v>
       </c>
       <c r="Y47">
-        <v>3184</v>
+        <v>3142</v>
       </c>
       <c r="Z47">
-        <v>37845</v>
+        <v>37935</v>
       </c>
       <c r="AA47">
-        <v>2414</v>
+        <v>2398</v>
       </c>
       <c r="AB47">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="AC47">
-        <v>2788</v>
+        <v>2781</v>
       </c>
       <c r="AD47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AE47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF47" s="27">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AG47">
-        <v>128.37</v>
+        <v>128.86000000000001</v>
       </c>
       <c r="AH47">
-        <v>11.79</v>
+        <v>11.64</v>
       </c>
       <c r="AI47">
-        <v>11.79</v>
+        <v>11.64</v>
       </c>
       <c r="AJ47">
-        <v>10.33</v>
+        <v>10.3</v>
       </c>
       <c r="AK47">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="AL47">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="AM47">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN47">
         <v>0.01</v>
       </c>
       <c r="AO47" s="27">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="AP47">
-        <v>128.11000000000001</v>
+        <v>128.38999999999999</v>
       </c>
       <c r="AQ47" s="12">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AR47" s="12">
-        <v>174719436600</v>
+        <v>179653519700</v>
       </c>
       <c r="AS47" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v23.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v35.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
         <v>41</v>
@@ -7420,130 +7422,130 @@
         <v>42</v>
       </c>
       <c r="D48" s="27">
-        <v>122.59</v>
+        <v>126.55</v>
       </c>
       <c r="E48" s="12">
-        <v>31933342100</v>
+        <v>37553095700</v>
       </c>
       <c r="F48">
-        <v>84</v>
-      </c>
-      <c r="G48" s="34">
-        <v>31.11</v>
+        <v>81</v>
+      </c>
+      <c r="G48" s="33">
+        <v>30</v>
       </c>
       <c r="H48">
-        <v>40700</v>
+        <v>40737</v>
       </c>
       <c r="I48">
-        <v>3338</v>
+        <v>3458</v>
       </c>
       <c r="J48" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="K48" s="31">
-        <v>37.409999999999997</v>
+        <v>32.96</v>
       </c>
       <c r="L48" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M48" s="31">
-        <v>60.74</v>
+        <v>65.56</v>
       </c>
       <c r="N48" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="O48" s="28">
-        <v>31.48</v>
+        <v>30</v>
       </c>
       <c r="P48" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="Q48" s="27">
-        <v>31.48</v>
+        <v>30</v>
       </c>
       <c r="R48" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="S48" s="36">
-        <v>15.19</v>
+        <v>14.81</v>
       </c>
       <c r="T48" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="U48" s="27">
-        <v>88.89</v>
+        <v>81.48</v>
       </c>
       <c r="V48" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="W48" s="27">
-        <v>81.48</v>
+        <v>74.069999999999993</v>
       </c>
       <c r="X48">
-        <v>34741</v>
+        <v>34673</v>
       </c>
       <c r="Y48">
-        <v>3132</v>
+        <v>3237</v>
       </c>
       <c r="Z48">
-        <v>37873</v>
+        <v>37910</v>
       </c>
       <c r="AA48">
-        <v>2429</v>
+        <v>2403</v>
       </c>
       <c r="AB48">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="AC48">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="AD48">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AE48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF48" s="27">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG48">
-        <v>128.66999999999999</v>
+        <v>128.41999999999999</v>
       </c>
       <c r="AH48">
-        <v>11.6</v>
+        <v>11.99</v>
       </c>
       <c r="AI48">
-        <v>11.6</v>
+        <v>11.99</v>
       </c>
       <c r="AJ48">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
       <c r="AK48">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="AL48">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="AM48">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN48">
         <v>0.01</v>
       </c>
       <c r="AO48" s="27">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AP48">
-        <v>128.38999999999999</v>
+        <v>128.02000000000001</v>
       </c>
       <c r="AQ48" s="12">
-        <v>141369300000</v>
+        <v>141453000000</v>
       </c>
       <c r="AR48" s="12">
-        <v>173302642100</v>
+        <v>179006095700</v>
       </c>
       <c r="AS48" s="25" t="str">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v19.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v39.txt", "Click view")</f>
         <v>Click view</v>
       </c>
     </row>
@@ -7841,7 +7843,7 @@
   </sheetData>
   <autoFilter ref="A2:AV2" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A3:AV53">
-      <sortCondition descending="1" ref="E2"/>
+      <sortCondition descending="1" ref="Q2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="5">

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -968,11 +968,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1126,11 +1126,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1284,11 +1284,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="386" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="386" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -184,7 +185,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -246,7 +247,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -276,6 +276,7 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -283,6 +284,7 @@
     <xf numFmtId="165" fontId="4" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="165" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,59 +631,59 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AS101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" style="41" min="2" max="2"/>
-    <col width="8.36328125" customWidth="1" style="41" min="3" max="3"/>
-    <col width="16.453125" customWidth="1" style="41" min="4" max="4"/>
-    <col width="18.7265625" customWidth="1" style="12" min="5" max="5"/>
-    <col width="11.6328125" customWidth="1" style="41" min="6" max="6"/>
-    <col width="14.1796875" customWidth="1" style="41" min="7" max="7"/>
-    <col width="9" customWidth="1" style="41" min="8" max="8"/>
-    <col width="9.1796875" customWidth="1" style="41" min="9" max="11"/>
-    <col width="16.90625" customWidth="1" style="41" min="12" max="19"/>
-    <col width="17.81640625" customWidth="1" style="41" min="20" max="20"/>
-    <col width="16.90625" customWidth="1" style="41" min="21" max="23"/>
-    <col width="9.26953125" customWidth="1" style="41" min="24" max="28"/>
-    <col width="9.26953125" customWidth="1" style="43" min="29" max="29"/>
-    <col width="9.26953125" customWidth="1" style="41" min="30" max="32"/>
-    <col width="8.453125" customWidth="1" style="41" min="33" max="33"/>
-    <col width="6.453125" customWidth="1" style="41" min="34" max="41"/>
-    <col width="8" customWidth="1" style="41" min="42" max="42"/>
-    <col width="25.7265625" customWidth="1" style="12" min="43" max="43"/>
-    <col width="18.7265625" customWidth="1" style="12" min="44" max="44"/>
-    <col width="17.54296875" customWidth="1" style="41" min="45" max="45"/>
-    <col width="6.54296875" customWidth="1" style="41" min="46" max="48"/>
+    <col width="9" customWidth="1" style="40" min="2" max="2"/>
+    <col width="8.42578125" customWidth="1" style="40" min="3" max="3"/>
+    <col width="16.42578125" customWidth="1" style="40" min="4" max="4"/>
+    <col width="18.7109375" customWidth="1" style="12" min="5" max="5"/>
+    <col width="11.5703125" customWidth="1" style="40" min="6" max="6"/>
+    <col width="14.140625" customWidth="1" style="40" min="7" max="7"/>
+    <col width="9" customWidth="1" style="40" min="8" max="8"/>
+    <col width="9.140625" customWidth="1" style="40" min="9" max="11"/>
+    <col width="16.85546875" customWidth="1" style="40" min="12" max="19"/>
+    <col width="17.85546875" customWidth="1" style="40" min="20" max="20"/>
+    <col width="16.85546875" customWidth="1" style="40" min="21" max="23"/>
+    <col width="9.28515625" customWidth="1" style="40" min="24" max="28"/>
+    <col width="9.28515625" customWidth="1" style="42" min="29" max="29"/>
+    <col width="9.28515625" customWidth="1" style="40" min="30" max="32"/>
+    <col width="8.42578125" customWidth="1" style="40" min="33" max="33"/>
+    <col width="6.42578125" customWidth="1" style="40" min="34" max="41"/>
+    <col width="8" customWidth="1" style="40" min="42" max="42"/>
+    <col width="25.7109375" customWidth="1" style="12" min="43" max="43"/>
+    <col width="18.7109375" customWidth="1" style="12" min="44" max="44"/>
+    <col width="17.5703125" customWidth="1" style="40" min="45" max="45"/>
+    <col width="6.5703125" customWidth="1" style="40" min="46" max="48"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.5" customHeight="1" s="41">
-      <c r="T1" s="46" t="inlineStr">
+    <row r="1" ht="23.45" customHeight="1" s="40">
+      <c r="T1" s="45" t="inlineStr">
         <is>
           <t>CHU KỲ 10 KỲ</t>
         </is>
       </c>
-      <c r="X1" s="44" t="inlineStr">
+      <c r="X1" s="43" t="inlineStr">
         <is>
           <t>Trúng 3</t>
         </is>
       </c>
-      <c r="AA1" s="42" t="inlineStr">
+      <c r="AA1" s="41" t="inlineStr">
         <is>
           <t>Trúng 4</t>
         </is>
       </c>
-      <c r="AD1" s="40" t="inlineStr">
+      <c r="AD1" s="39" t="inlineStr">
         <is>
           <t>Trúng 5</t>
         </is>
       </c>
-      <c r="AG1" s="45" t="inlineStr">
+      <c r="AG1" s="44" t="inlineStr">
         <is>
           <t>Trung bình/Kỳ</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="65.5" customFormat="1" customHeight="1" s="2">
+    <row r="2" ht="65.45" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Kịch bản
@@ -918,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -931,16 +933,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>135.63</v>
+        <v>133.03</v>
       </c>
       <c r="E3" t="n">
-        <v>12365484081</v>
+        <v>11461794080.99999</v>
       </c>
       <c r="F3" t="n">
-        <v>15251</v>
+        <v>15253</v>
       </c>
       <c r="G3" t="n">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -976,11 +978,11 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>0/10</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1007,76 +1009,76 @@
         <v>100</v>
       </c>
       <c r="X3" t="n">
-        <v>13210</v>
+        <v>13200</v>
       </c>
       <c r="Y3" t="n">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="Z3" t="n">
         <v>14424</v>
       </c>
       <c r="AA3" t="n">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="AB3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="n">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="AH3" t="n">
-        <v>121.4</v>
+        <v>122.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>121.4</v>
+        <v>122.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AM3" t="n">
         <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>4691.6</v>
+        <v>4690.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>34706400000</v>
       </c>
       <c r="AR3" t="n">
-        <v>47071884081</v>
+        <v>46168194080</v>
       </c>
       <c r="AS3">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v8.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v6.txt", "Click view")</f>
         <v/>
       </c>
     </row>
-    <row r="4" s="41">
+    <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1089,16 +1091,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>133.03</v>
+        <v>135.63</v>
       </c>
       <c r="E4" t="n">
-        <v>11461794080.99999</v>
+        <v>12365484081</v>
       </c>
       <c r="F4" t="n">
-        <v>15253</v>
+        <v>15251</v>
       </c>
       <c r="G4" t="n">
-        <v>1296</v>
+        <v>1286</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1134,11 +1136,11 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1165,70 +1167,70 @@
         <v>100</v>
       </c>
       <c r="X4" t="n">
-        <v>13200</v>
+        <v>13210</v>
       </c>
       <c r="Y4" t="n">
-        <v>1224</v>
+        <v>1214</v>
       </c>
       <c r="Z4" t="n">
         <v>14424</v>
       </c>
       <c r="AA4" t="n">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="AB4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AC4" t="n">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AD4" t="n">
         <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="AH4" t="n">
-        <v>122.4</v>
+        <v>121.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>122.4</v>
+        <v>121.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AP4" t="n">
-        <v>4690.6</v>
+        <v>4691.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>34706400000</v>
       </c>
       <c r="AR4" t="n">
-        <v>46168194080</v>
+        <v>47071884081</v>
       </c>
       <c r="AS4">
-        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v6.txt", "Click view")</f>
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v8.txt", "Click view")</f>
         <v/>
       </c>
     </row>
@@ -1404,7 +1406,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="28" t="n">
         <v>137.07</v>
       </c>
       <c r="E6" s="21" t="n">
@@ -1442,11 +1444,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>97/270</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>35.93</v>
+          <t>66/270</t>
+        </is>
+      </c>
+      <c r="O6" s="42" t="n">
+        <v>24.44</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1562,7 +1564,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="42" t="n">
         <v>117.62</v>
       </c>
       <c r="E7" s="12" t="n">
@@ -1595,16 +1597,16 @@
           <t>72/270</t>
         </is>
       </c>
-      <c r="M7" s="43" t="n">
+      <c r="M7" s="42" t="n">
         <v>26.67</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>72/270</t>
+          <t>41/270</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>26.67</v>
+        <v>15.19</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1720,7 +1722,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="28" t="n">
         <v>135.59</v>
       </c>
       <c r="E8" s="21" t="n">
@@ -1758,11 +1760,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>97/270</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>35.93</v>
+          <t>61/270</t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="n">
+        <v>22.59</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1878,7 +1880,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="42" t="n">
         <v>129.28</v>
       </c>
       <c r="E9" s="12" t="n">
@@ -1911,16 +1913,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M9" s="43" t="n">
+      <c r="M9" s="42" t="n">
         <v>33.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>58/270</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>33.7</v>
+        <v>21.48</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -2036,7 +2038,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="42" t="n">
         <v>130.44</v>
       </c>
       <c r="E10" s="12" t="n">
@@ -2069,16 +2071,16 @@
           <t>95/270</t>
         </is>
       </c>
-      <c r="M10" s="43" t="n">
+      <c r="M10" s="42" t="n">
         <v>35.19</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>95/270</t>
+          <t>57/270</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>35.19</v>
+        <v>21.11</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -2181,7 +2183,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="29" t="n">
         <v>15</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2232,11 +2234,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>103/270</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>38.15</v>
+          <t>63/270</t>
+        </is>
+      </c>
+      <c r="O11" s="42" t="n">
+        <v>23.33</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -2390,11 +2392,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>95/270</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>35.19</v>
+          <t>67/270</t>
+        </is>
+      </c>
+      <c r="O12" s="42" t="n">
+        <v>24.81</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -2510,7 +2512,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="42" t="n">
         <v>129.15</v>
       </c>
       <c r="E13" s="12" t="n">
@@ -2543,16 +2545,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M13" s="43" t="n">
+      <c r="M13" s="42" t="n">
         <v>33.7</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>52/270</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>33.7</v>
+        <v>19.26</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2668,7 +2670,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="42" t="n">
         <v>131.91</v>
       </c>
       <c r="E14" s="12" t="n">
@@ -2706,11 +2708,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>94/270</t>
+          <t>59/270</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>34.81</v>
+        <v>21.85</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2826,7 +2828,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="42" t="n">
         <v>122.59</v>
       </c>
       <c r="E15" s="12" t="n">
@@ -2859,16 +2861,16 @@
           <t>85/270</t>
         </is>
       </c>
-      <c r="M15" s="43" t="n">
+      <c r="M15" s="42" t="n">
         <v>31.48</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>85/270</t>
+          <t>48/270</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>31.48</v>
+        <v>17.78</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -3022,11 +3024,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>97/270</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>35.93</v>
+          <t>68/270</t>
+        </is>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>25.19</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -3142,7 +3144,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D17" s="43" t="n">
+      <c r="D17" s="42" t="n">
         <v>119.58</v>
       </c>
       <c r="E17" s="12" t="n">
@@ -3175,16 +3177,16 @@
           <t>79/270</t>
         </is>
       </c>
-      <c r="M17" s="43" t="n">
+      <c r="M17" s="42" t="n">
         <v>29.26</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>79/270</t>
+          <t>45/270</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>29.26</v>
+        <v>16.67</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -3300,7 +3302,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="42" t="n">
         <v>124.24</v>
       </c>
       <c r="E18" s="12" t="n">
@@ -3333,16 +3335,16 @@
           <t>87/270</t>
         </is>
       </c>
-      <c r="M18" s="43" t="n">
+      <c r="M18" s="42" t="n">
         <v>32.22</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>87/270</t>
+          <t>54/270</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>32.22</v>
+        <v>20</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -3458,7 +3460,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D19" s="43" t="n">
+      <c r="D19" s="42" t="n">
         <v>123.59</v>
       </c>
       <c r="E19" s="12" t="n">
@@ -3491,16 +3493,16 @@
           <t>86/270</t>
         </is>
       </c>
-      <c r="M19" s="43" t="n">
+      <c r="M19" s="42" t="n">
         <v>31.85</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>86/270</t>
+          <t>50/270</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>31.85</v>
+        <v>18.52</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -3616,7 +3618,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="42" t="n">
         <v>124.12</v>
       </c>
       <c r="E20" s="12" t="n">
@@ -3649,16 +3651,16 @@
           <t>84/270</t>
         </is>
       </c>
-      <c r="M20" s="43" t="n">
+      <c r="M20" s="42" t="n">
         <v>31.11</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>84/270</t>
+          <t>45/270</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>31.11</v>
+        <v>16.67</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -3774,7 +3776,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="43" t="n">
+      <c r="D21" s="42" t="n">
         <v>130.8</v>
       </c>
       <c r="E21" s="12" t="n">
@@ -3812,11 +3814,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>95/270</t>
+          <t>56/270</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>35.19</v>
+        <v>20.74</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -3932,7 +3934,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D22" s="43" t="n">
+      <c r="D22" s="42" t="n">
         <v>133.04</v>
       </c>
       <c r="E22" s="12" t="n">
@@ -3970,11 +3972,11 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>94/270</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>34.81</v>
+          <t>64/270</t>
+        </is>
+      </c>
+      <c r="O22" s="42" t="n">
+        <v>23.7</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -4090,7 +4092,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="42" t="n">
         <v>134.14</v>
       </c>
       <c r="E23" s="12" t="n">
@@ -4123,16 +4125,16 @@
           <t>90/270</t>
         </is>
       </c>
-      <c r="M23" s="43" t="n">
+      <c r="M23" s="42" t="n">
         <v>33.33</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>90/270</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>33.33</v>
+          <t>66/270</t>
+        </is>
+      </c>
+      <c r="O23" s="42" t="n">
+        <v>24.44</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -4248,7 +4250,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D24" s="42" t="n">
         <v>129.31</v>
       </c>
       <c r="E24" s="12" t="n">
@@ -4281,16 +4283,16 @@
           <t>84/270</t>
         </is>
       </c>
-      <c r="M24" s="43" t="n">
+      <c r="M24" s="42" t="n">
         <v>31.11</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>84/270</t>
+          <t>58/270</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>31.11</v>
+        <v>21.48</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -4406,7 +4408,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D25" s="43" t="n">
+      <c r="D25" s="42" t="n">
         <v>126.94</v>
       </c>
       <c r="E25" s="12" t="n">
@@ -4439,16 +4441,16 @@
           <t>89/270</t>
         </is>
       </c>
-      <c r="M25" s="43" t="n">
+      <c r="M25" s="42" t="n">
         <v>32.96</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>89/270</t>
+          <t>54/270</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>32.96</v>
+        <v>20</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -4564,7 +4566,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D26" s="43" t="n">
+      <c r="D26" s="42" t="n">
         <v>131.46</v>
       </c>
       <c r="E26" s="12" t="n">
@@ -4602,11 +4604,11 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>94/270</t>
+          <t>54/270</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>34.81</v>
+        <v>20</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -4722,7 +4724,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="28" t="n">
         <v>136.95</v>
       </c>
       <c r="E27" s="21" t="n">
@@ -4760,11 +4762,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>93/270</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>34.44</v>
+          <t>62/270</t>
+        </is>
+      </c>
+      <c r="O27" s="42" t="n">
+        <v>22.96</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -4880,7 +4882,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D28" s="43" t="n">
+      <c r="D28" s="42" t="n">
         <v>131.93</v>
       </c>
       <c r="E28" s="12" t="n">
@@ -4913,16 +4915,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M28" s="43" t="n">
+      <c r="M28" s="42" t="n">
         <v>33.7</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>55/270</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>33.7</v>
+        <v>20.37</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -5038,7 +5040,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="42" t="n">
         <v>133.02</v>
       </c>
       <c r="E29" s="12" t="n">
@@ -5071,16 +5073,16 @@
           <t>90/270</t>
         </is>
       </c>
-      <c r="M29" s="43" t="n">
+      <c r="M29" s="42" t="n">
         <v>33.33</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>90/270</t>
+          <t>59/270</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>33.33</v>
+        <v>21.85</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -5196,7 +5198,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D30" s="43" t="n">
+      <c r="D30" s="42" t="n">
         <v>129.69</v>
       </c>
       <c r="E30" s="12" t="n">
@@ -5234,11 +5236,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>92/270</t>
+          <t>54/270</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>34.07</v>
+        <v>20</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -5354,7 +5356,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="42" t="n">
         <v>127.01</v>
       </c>
       <c r="E31" s="12" t="n">
@@ -5387,16 +5389,16 @@
           <t>82/270</t>
         </is>
       </c>
-      <c r="M31" s="43" t="n">
+      <c r="M31" s="42" t="n">
         <v>30.37</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>82/270</t>
+          <t>53/270</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>30.37</v>
+        <v>19.63</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -5512,7 +5514,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D32" s="43" t="n">
+      <c r="D32" s="42" t="n">
         <v>133.04</v>
       </c>
       <c r="E32" s="12" t="n">
@@ -5550,11 +5552,11 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>95/270</t>
+          <t>60/270</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>35.19</v>
+        <v>22.22</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -5670,7 +5672,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="43" t="n">
+      <c r="D33" s="42" t="n">
         <v>124.87</v>
       </c>
       <c r="E33" s="12" t="n">
@@ -5703,16 +5705,16 @@
           <t>89/270</t>
         </is>
       </c>
-      <c r="M33" s="43" t="n">
+      <c r="M33" s="42" t="n">
         <v>32.96</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>89/270</t>
+          <t>48/270</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>32.96</v>
+        <v>17.78</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -5828,7 +5830,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="42" t="n">
         <v>130.88</v>
       </c>
       <c r="E34" s="12" t="n">
@@ -5861,16 +5863,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M34" s="43" t="n">
+      <c r="M34" s="42" t="n">
         <v>33.7</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>52/270</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>33.7</v>
+        <v>19.26</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -5986,7 +5988,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D35" s="43" t="n">
+      <c r="D35" s="42" t="n">
         <v>126.55</v>
       </c>
       <c r="E35" s="12" t="n">
@@ -6019,16 +6021,16 @@
           <t>81/270</t>
         </is>
       </c>
-      <c r="M35" s="43" t="n">
+      <c r="M35" s="42" t="n">
         <v>30</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>81/270</t>
+          <t>48/270</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>30</v>
+        <v>17.78</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -6144,7 +6146,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="28" t="n">
         <v>135.69</v>
       </c>
       <c r="E36" s="21" t="n">
@@ -6182,11 +6184,11 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>92/270</t>
+          <t>60/270</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>34.07</v>
+        <v>22.22</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -6302,7 +6304,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="28" t="n">
         <v>137.41</v>
       </c>
       <c r="E37" s="21" t="n">
@@ -6340,11 +6342,11 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>101/270</t>
-        </is>
-      </c>
-      <c r="O37" s="14" t="n">
-        <v>37.41</v>
+          <t>62/270</t>
+        </is>
+      </c>
+      <c r="O37" s="42" t="n">
+        <v>22.96</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -6460,7 +6462,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="28" t="n">
         <v>135.02</v>
       </c>
       <c r="E38" s="12" t="n">
@@ -6493,16 +6495,16 @@
           <t>89/270</t>
         </is>
       </c>
-      <c r="M38" s="43" t="n">
+      <c r="M38" s="42" t="n">
         <v>32.96</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>89/270</t>
+          <t>57/270</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>32.96</v>
+        <v>21.11</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -6618,7 +6620,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="28" t="n">
         <v>136.96</v>
       </c>
       <c r="E39" s="21" t="n">
@@ -6656,11 +6658,11 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>101/270</t>
-        </is>
-      </c>
-      <c r="O39" s="14" t="n">
-        <v>37.41</v>
+          <t>62/270</t>
+        </is>
+      </c>
+      <c r="O39" s="42" t="n">
+        <v>22.96</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -6776,7 +6778,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D40" s="43" t="n">
+      <c r="D40" s="42" t="n">
         <v>134.39</v>
       </c>
       <c r="E40" s="12" t="n">
@@ -6809,16 +6811,16 @@
           <t>89/270</t>
         </is>
       </c>
-      <c r="M40" s="43" t="n">
+      <c r="M40" s="42" t="n">
         <v>32.96</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>89/270</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>32.96</v>
+          <t>66/270</t>
+        </is>
+      </c>
+      <c r="O40" s="42" t="n">
+        <v>24.44</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -6972,11 +6974,11 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>99/270</t>
-        </is>
-      </c>
-      <c r="O41" s="27" t="n">
-        <v>36.67</v>
+          <t>64/270</t>
+        </is>
+      </c>
+      <c r="O41" s="42" t="n">
+        <v>23.7</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -7079,7 +7081,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="n">
+      <c r="A42" s="27" t="n">
         <v>46</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -7130,11 +7132,11 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>103/270</t>
-        </is>
-      </c>
-      <c r="O42" s="13" t="n">
-        <v>38.15</v>
+          <t>70/270</t>
+        </is>
+      </c>
+      <c r="O42" s="42" t="n">
+        <v>25.93</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -7250,7 +7252,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D43" s="43" t="n">
+      <c r="D43" s="42" t="n">
         <v>134.65</v>
       </c>
       <c r="E43" s="12" t="n">
@@ -7288,11 +7290,11 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>96/270</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>35.56</v>
+          <t>62/270</t>
+        </is>
+      </c>
+      <c r="O43" s="42" t="n">
+        <v>22.96</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -7446,11 +7448,11 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>99/270</t>
-        </is>
-      </c>
-      <c r="O44" s="27" t="n">
-        <v>36.67</v>
+          <t>62/270</t>
+        </is>
+      </c>
+      <c r="O44" s="42" t="n">
+        <v>22.96</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -7566,7 +7568,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="28" t="n">
         <v>137.42</v>
       </c>
       <c r="E45" s="21" t="n">
@@ -7604,11 +7606,11 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>98/270</t>
-        </is>
-      </c>
-      <c r="O45" s="27" t="n">
-        <v>36.3</v>
+          <t>66/270</t>
+        </is>
+      </c>
+      <c r="O45" s="42" t="n">
+        <v>24.44</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -7724,7 +7726,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="28" t="n">
         <v>136.32</v>
       </c>
       <c r="E46" s="21" t="n">
@@ -7762,11 +7764,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>101/270</t>
-        </is>
-      </c>
-      <c r="O46" s="14" t="n">
-        <v>37.41</v>
+          <t>62/270</t>
+        </is>
+      </c>
+      <c r="O46" s="42" t="n">
+        <v>22.96</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -7882,7 +7884,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="28" t="n">
         <v>137.68</v>
       </c>
       <c r="E47" s="16" t="n">
@@ -7920,11 +7922,11 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>100/270</t>
-        </is>
-      </c>
-      <c r="O47" s="14" t="n">
-        <v>37.04</v>
+          <t>63/270</t>
+        </is>
+      </c>
+      <c r="O47" s="42" t="n">
+        <v>23.33</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -8040,7 +8042,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D48" s="43" t="n">
+      <c r="D48" s="42" t="n">
         <v>134.38</v>
       </c>
       <c r="E48" s="12" t="n">
@@ -8073,16 +8075,16 @@
           <t>89/270</t>
         </is>
       </c>
-      <c r="M48" s="43" t="n">
+      <c r="M48" s="42" t="n">
         <v>32.96</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>89/270</t>
+          <t>56/270</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>32.96</v>
+        <v>20.74</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -8198,7 +8200,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="28" t="n">
         <v>135.4</v>
       </c>
       <c r="E49" s="21" t="n">
@@ -8236,11 +8238,11 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>95/270</t>
+          <t>60/270</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>35.19</v>
+        <v>22.22</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -8356,7 +8358,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D50" s="43" t="n">
+      <c r="D50" s="42" t="n">
         <v>133.11</v>
       </c>
       <c r="E50" s="12" t="n">
@@ -8389,16 +8391,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M50" s="43" t="n">
+      <c r="M50" s="42" t="n">
         <v>33.7</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>58/270</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>33.7</v>
+        <v>21.48</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -8514,7 +8516,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="28" t="n">
         <v>137.6</v>
       </c>
       <c r="E51" s="16" t="n">
@@ -8552,11 +8554,11 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>106/270</t>
-        </is>
-      </c>
-      <c r="O51" s="13" t="n">
-        <v>39.26</v>
+          <t>66/270</t>
+        </is>
+      </c>
+      <c r="O51" s="42" t="n">
+        <v>24.44</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -8672,7 +8674,7 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D52" s="43" t="n">
+      <c r="D52" s="42" t="n">
         <v>128.97</v>
       </c>
       <c r="E52" s="12" t="n">
@@ -8705,16 +8707,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M52" s="43" t="n">
+      <c r="M52" s="42" t="n">
         <v>33.7</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>91/270</t>
+          <t>51/270</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>33.7</v>
+        <v>18.89</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -8817,7 +8819,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="28" t="n">
+      <c r="A53" s="27" t="n">
         <v>57</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -8868,11 +8870,11 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>111/270</t>
-        </is>
-      </c>
-      <c r="O53" s="13" t="n">
-        <v>41.11</v>
+          <t>94/270</t>
+        </is>
+      </c>
+      <c r="O53" s="22" t="n">
+        <v>34.81</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -8975,7 +8977,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="n">
+      <c r="A54" s="27" t="n">
         <v>58</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -9026,11 +9028,11 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>110/270</t>
-        </is>
-      </c>
-      <c r="O54" s="13" t="n">
-        <v>40.74</v>
+          <t>84/270</t>
+        </is>
+      </c>
+      <c r="O54" s="22" t="n">
+        <v>31.11</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -9133,7 +9135,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="29" t="n">
         <v>59</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -9184,11 +9186,11 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>104/270</t>
-        </is>
-      </c>
-      <c r="O55" s="13" t="n">
-        <v>38.52</v>
+          <t>70/270</t>
+        </is>
+      </c>
+      <c r="O55" s="42" t="n">
+        <v>25.93</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -9291,7 +9293,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="n">
+      <c r="A56" s="27" t="n">
         <v>60</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -9342,11 +9344,11 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>99/270</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>36.67</v>
+          <t>67/270</t>
+        </is>
+      </c>
+      <c r="O56" s="42" t="n">
+        <v>24.81</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -9500,11 +9502,11 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>95/270</t>
+          <t>50/270</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>35.19</v>
+        <v>18.52</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -9658,11 +9660,11 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>90/270</t>
+          <t>57/270</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>33.33</v>
+        <v>21.11</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -9816,11 +9818,11 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>90/270</t>
-        </is>
-      </c>
-      <c r="O59" t="n">
-        <v>33.33</v>
+          <t>64/270</t>
+        </is>
+      </c>
+      <c r="O59" s="42" t="n">
+        <v>23.7</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -9974,11 +9976,11 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>104/270</t>
-        </is>
-      </c>
-      <c r="O60" s="13" t="n">
-        <v>38.52</v>
+          <t>67/270</t>
+        </is>
+      </c>
+      <c r="O60" s="42" t="n">
+        <v>24.81</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -10132,11 +10134,11 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>102/270</t>
-        </is>
-      </c>
-      <c r="O61" t="n">
-        <v>37.78</v>
+          <t>61/270</t>
+        </is>
+      </c>
+      <c r="O61" s="42" t="n">
+        <v>22.59</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -10285,16 +10287,16 @@
           <t>91/270</t>
         </is>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="54" t="n">
         <v>33.7</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>91/270</t>
-        </is>
-      </c>
-      <c r="O62" t="n">
-        <v>33.7</v>
+          <t>58/270</t>
+        </is>
+      </c>
+      <c r="O62" s="54" t="n">
+        <v>21.48</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -10397,7 +10399,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="28" t="n">
+      <c r="A63" s="27" t="n">
         <v>67</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -10448,11 +10450,11 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>111/270</t>
-        </is>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>41.11</v>
+          <t>94/270</t>
+        </is>
+      </c>
+      <c r="O63" s="22" t="n">
+        <v>34.81</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -10606,11 +10608,11 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>95/270</t>
+          <t>55/270</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>35.19</v>
+        <v>20.37</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -10713,7 +10715,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="27" t="n">
         <v>69</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -10726,10 +10728,10 @@
           <t>270</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="13" t="n">
         <v>145.57</v>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="E65" s="16" t="n">
         <v>64420663000</v>
       </c>
       <c r="F65" t="n">
@@ -10759,23 +10761,23 @@
           <t>109/270</t>
         </is>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="13" t="n">
         <v>40.37</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>109/270</t>
-        </is>
-      </c>
-      <c r="O65" t="n">
-        <v>40.37</v>
+          <t>94/270</t>
+        </is>
+      </c>
+      <c r="O65" s="22" t="n">
+        <v>34.81</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>85/270</t>
         </is>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65" s="13" t="n">
         <v>31.48</v>
       </c>
       <c r="R65" t="inlineStr">
@@ -10791,7 +10793,7 @@
           <t>27/27</t>
         </is>
       </c>
-      <c r="U65" t="n">
+      <c r="U65" s="13" t="n">
         <v>100</v>
       </c>
       <c r="V65" t="inlineStr">
@@ -10799,7 +10801,7 @@
           <t>27/27</t>
         </is>
       </c>
-      <c r="W65" t="n">
+      <c r="W65" s="13" t="n">
         <v>100</v>
       </c>
       <c r="X65" t="n">
@@ -10871,7 +10873,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="28" t="n">
+      <c r="A66" s="27" t="n">
         <v>70</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -10922,11 +10924,11 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>104/270</t>
-        </is>
-      </c>
-      <c r="O66" s="13" t="n">
-        <v>38.52</v>
+          <t>70/270</t>
+        </is>
+      </c>
+      <c r="O66" s="42" t="n">
+        <v>25.93</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -11029,7 +11031,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="28" t="n">
+      <c r="A67" s="27" t="n">
         <v>71</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -11080,11 +11082,11 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>95/270</t>
-        </is>
-      </c>
-      <c r="O67" t="n">
-        <v>35.19</v>
+          <t>63/270</t>
+        </is>
+      </c>
+      <c r="O67" s="42" t="n">
+        <v>23.33</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="386" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2230" yWindow="3820" windowWidth="32470" windowHeight="14220" tabRatio="386" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -231,12 +231,12 @@
     <xf numFmtId="164" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA143"/>
+  <dimension ref="A1:BA148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" style="27" min="2" max="2"/>
@@ -909,13 +909,13 @@
 &gt;90%</t>
         </is>
       </c>
-      <c r="AU2" s="24" t="inlineStr">
+      <c r="AU2" s="21" t="inlineStr">
         <is>
           <t>Thu 
 &gt;100%</t>
         </is>
       </c>
-      <c r="AV2" s="24" t="inlineStr">
+      <c r="AV2" s="21" t="inlineStr">
         <is>
           <t>Tỉ lệ
 &gt;100%</t>
@@ -14390,6 +14390,936 @@
     <row r="143">
       <c r="A143" t="n">
         <v>250</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>6</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>134.89</v>
+      </c>
+      <c r="E144" t="n">
+        <v>13318736400</v>
+      </c>
+      <c r="F144" t="n">
+        <v>16731</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1379</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>100</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U144" t="n">
+        <v>100</v>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W144" t="n">
+        <v>100</v>
+      </c>
+      <c r="X144" t="n">
+        <v>14522</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>1306</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>15828</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>771</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>891</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1320.18</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>118.73</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>118.73</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>81</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>4695</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>51495776400</v>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AV144" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>51495776400</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>13318736400</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>134.89</v>
+      </c>
+      <c r="BA144">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v6.txt", "Click view")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>7</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="E145" t="n">
+        <v>13896120800</v>
+      </c>
+      <c r="F145" t="n">
+        <v>16731</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1419</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>100</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>100</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U145" t="n">
+        <v>100</v>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W145" t="n">
+        <v>100</v>
+      </c>
+      <c r="X145" t="n">
+        <v>14483</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1345</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>15828</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>769</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>891</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>1316.64</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>122.27</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>122.27</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>81</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>4691.36</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>52073160800</v>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AV145" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>52073160800</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>13896120800</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="BA145">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v7.txt", "Click view")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>8</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="E146" t="n">
+        <v>12364389500</v>
+      </c>
+      <c r="F146" t="n">
+        <v>17115</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>100</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>100</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U146" t="n">
+        <v>100</v>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W146" t="n">
+        <v>100</v>
+      </c>
+      <c r="X146" t="n">
+        <v>14797</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1384</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>16181</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>814</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>923</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>1345.18</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>125.82</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>125.82</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>4688.55</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>50541429500</v>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AV146" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>50541429500</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>12364389500</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="BA146">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v8.txt", "Click view")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>9</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340,392</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>134.11</v>
+      </c>
+      <c r="E147" t="n">
+        <v>13023860000</v>
+      </c>
+      <c r="F147" t="n">
+        <v>16804</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1359</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>100</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U147" t="n">
+        <v>100</v>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W147" t="n">
+        <v>100</v>
+      </c>
+      <c r="X147" t="n">
+        <v>14616</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1278</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>15894</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>775</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>899</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1328.73</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>116.18</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>116.18</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>4696.82</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>51200900000</v>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+      <c r="AV147" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>38177040000</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>51200900000</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>13023860000</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>134.11</v>
+      </c>
+      <c r="BA147">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v9.txt", "Click view")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>300</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>38,54,70,96,146,168,192,266,290,340, 392</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>246.23</v>
+      </c>
+      <c r="E148" t="n">
+        <v>305415000</v>
+      </c>
+      <c r="F148" t="n">
+        <v>81</v>
+      </c>
+      <c r="G148" t="n">
+        <v>12</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+      <c r="S148" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="U148" t="n">
+        <v>100</v>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="W148" t="n">
+        <v>100</v>
+      </c>
+      <c r="X148" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>74</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>208860000</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>514275000</v>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+      <c r="AV148" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>208860000</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>514275000</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>305415000</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>246.23</v>
+      </c>
+      <c r="BA148">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v300.txt", "Click view")</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/all-summaries.xlsx
+++ b/all-summaries.xlsx
@@ -12939,6 +12939,185 @@
       <c r="A69" t="n">
         <v>76</v>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>300-349</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-186150600</v>
+      </c>
+      <c r="F69" t="n">
+        <v>127</v>
+      </c>
+      <c r="G69" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>38/50</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>76</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>11/50</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>22</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>8/50</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>16</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>7/50</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>14</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>6/50</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>12</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2/50</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>20</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>112</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>121</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>429040000</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>242889400</v>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>7750000</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>1196000</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>-6554000</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="BA69">
+        <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v76.txt", "Click view")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -15142,107 +15321,107 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>38,54,70,96,146,168,192,266,290,340, 392</t>
+          <t>300-396</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>246.23</v>
+        <v>108.8</v>
       </c>
       <c r="E148" t="n">
-        <v>305415000</v>
+        <v>129985000</v>
       </c>
       <c r="F148" t="n">
-        <v>81</v>
+        <v>615</v>
       </c>
       <c r="G148" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>52/97</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>45.45</v>
+        <v>53.61</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>39/97</t>
         </is>
       </c>
       <c r="K148" t="n">
-        <v>54.55</v>
+        <v>40.21</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>20/97</t>
         </is>
       </c>
       <c r="M148" t="n">
-        <v>36.36</v>
+        <v>20.62</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>12/97</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>36.36</v>
+        <v>12.37</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>10/97</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>36.36</v>
+        <v>10.31</v>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/97</t>
         </is>
       </c>
       <c r="S148" t="n">
-        <v>27.27</v>
+        <v>6.19</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="U148" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="W148" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="X148" t="n">
-        <v>64</v>
+        <v>526</v>
       </c>
       <c r="Y148" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="Z148" t="n">
-        <v>74</v>
+        <v>579</v>
       </c>
       <c r="AA148" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AB148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC148" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AD148" t="n">
         <v>0</v>
@@ -15254,22 +15433,22 @@
         <v>0</v>
       </c>
       <c r="AG148" t="n">
-        <v>5.82</v>
+        <v>5.42</v>
       </c>
       <c r="AH148" t="n">
-        <v>0.91</v>
+        <v>0.55</v>
       </c>
       <c r="AI148" t="n">
-        <v>0.91</v>
+        <v>0.55</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="AK148" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="AL148" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="AM148" t="n">
         <v>0</v>
@@ -15281,41 +15460,41 @@
         <v>0</v>
       </c>
       <c r="AP148" t="n">
-        <v>25.18</v>
+        <v>20.59</v>
       </c>
       <c r="AQ148" t="n">
-        <v>208860000</v>
+        <v>1476480000</v>
       </c>
       <c r="AR148" t="n">
-        <v>514275000</v>
+        <v>1606465000</v>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="AT148" t="n">
-        <v>54.55</v>
+        <v>100</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="AV148" t="n">
-        <v>45.45</v>
+        <v>100</v>
       </c>
       <c r="AW148" t="n">
-        <v>208860000</v>
+        <v>29940000</v>
       </c>
       <c r="AX148" t="n">
-        <v>514275000</v>
+        <v>36491000</v>
       </c>
       <c r="AY148" t="n">
-        <v>305415000</v>
+        <v>6551000</v>
       </c>
       <c r="AZ148" t="n">
-        <v>246.23</v>
+        <v>121.88</v>
       </c>
       <c r="BA148">
         <f>HYPERLINK("https://github.com/lottpicker/daily1689/blob/main/summary-v300.txt", "Click view")</f>
